--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4295AB9D-17A1-4920-AC1C-FB66036FD1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5025254D-6185-4190-A23A-0DBCCFDC518E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="OPLL-EX" sheetId="3" r:id="rId4"/>
     <sheet name="OPL2+ADPCM" sheetId="4" r:id="rId5"/>
     <sheet name="SCC" sheetId="5" r:id="rId6"/>
+    <sheet name="MIXIER" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="415">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -46,13 +47,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>音源</t>
-    <rPh sb="0" eb="2">
-      <t>オンゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>IP</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -70,10 +64,6 @@
   </si>
   <si>
     <t>ADPCM</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DCSG</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -156,18 +146,6 @@
   </si>
   <si>
     <t>https://github.com/plgDavid/misc/wiki/Copyright-free-OPLL(x)-ROM-patches</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://github.com/dnotq/sn76489_audio</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>sn76489_audio</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BSD 3-Clause</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -601,14 +579,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>OPLL2 Register Address</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPLL2 Register Value</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Memory Mapped I/O</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -975,19 +945,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>OPLL2 Register Data</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>OPLL1 Register Data</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPLL1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPLL2</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1067,14 +1025,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>OPL2-1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPL2-2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>08</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1311,13 +1261,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>その他</t>
-    <rPh sb="2" eb="3">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ETY</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1339,22 +1282,6 @@
   </si>
   <si>
     <t>TOM</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPL2-1 Register Address</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPL2-1 Register Value</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPL2-2 Register Address</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPL2-2 Register Value</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1373,14 +1300,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>7FEEh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FEFh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>7FF0h</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1389,99 +1308,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>OPL2-2 Regisger Address</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPL2-2 Register Data</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OPL2-1 Register Data</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FEDh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FECh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DCSG2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DCSG1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DCSG2 Write</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DCSG1 Write</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DCSG2 Access</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DCSG1 Access</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FEBh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FEAh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>SSG Register Address</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>SSG Register Write</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FF7h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FF8h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FF9h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FFAh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FFBh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FFCh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FFDh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FFEh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FFFh</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1571,20 +1402,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#15) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#16) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#17) のときのみ利用可能</t>
     <rPh sb="47" eb="51">
       <t>リヨウカノウ</t>
@@ -1593,34 +1410,6 @@
   </si>
   <si>
     <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#18) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#19) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#20) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#21) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#22) のときのみ利用可能</t>
     <rPh sb="47" eb="51">
       <t>リヨウカノウ</t>
     </rPh>
@@ -2132,6 +1921,234 @@
     <rPh sb="11" eb="13">
       <t>サイダイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL Register Value</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL Register Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ch.1 PAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ch.2 PAN</t>
+  </si>
+  <si>
+    <t>ch.3 PAN</t>
+  </si>
+  <si>
+    <t>ch.4 PAN</t>
+  </si>
+  <si>
+    <t>ch.5 PAN</t>
+  </si>
+  <si>
+    <t>ch.6 PAN</t>
+  </si>
+  <si>
+    <t>ch.7 PAN</t>
+  </si>
+  <si>
+    <t>ch.8 PAN</t>
+  </si>
+  <si>
+    <t>ch.9 PAN</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>FA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト129</t>
+    <rPh sb="2" eb="4">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ミギハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト130</t>
+    <rPh sb="2" eb="4">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ミギハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト131</t>
+    <rPh sb="2" eb="4">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ミギハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト132</t>
+    <rPh sb="2" eb="4">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ミギハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト133</t>
+    <rPh sb="2" eb="4">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ミギハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト134</t>
+    <rPh sb="2" eb="4">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ミギハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト135</t>
+    <rPh sb="2" eb="4">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ミギハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト136</t>
+    <rPh sb="2" eb="4">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ミギハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MIXIERは、MemoryMappedI/Oのみ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF7h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF8h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSG Volume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF9h</t>
+  </si>
+  <si>
+    <t>7FFAh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FFBh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL Volume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2 Volume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADPCM Volume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL Register Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPL2 Register Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0: OFF,～128: MAX, RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#36) のときのみ利用可能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モジュール</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2643,7 +2660,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2830,15 +2847,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2857,6 +2868,81 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2866,70 +2952,22 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2981,33 +3019,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3026,6 +3037,439 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E48642A2-5337-0DDD-22F7-BEB44C05E859}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9353550" y="6419850"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE6EA7A3-909C-6EFE-DCDF-B889394B70C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11410950" y="6419850"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1027" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CEB8E36-6A96-F518-9927-BD459B668996}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10039350" y="2800350"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1028" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9B2F875-83B9-2929-AC00-B97C649820D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10039350" y="2800350"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1029" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F889FD1E-FE36-E2B2-7952-CD9426AE5FF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10039350" y="2800350"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1030" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82F48FB6-8A5F-1B82-146B-C9EC9C38A572}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10039350" y="2800350"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1031" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5FE1C90-E2E1-E105-0ED5-C5B32C1D0C46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10039350" y="2800350"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1032" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA984519-11F6-5858-270C-098D776FAD18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10039350" y="2800350"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>470647</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>22412</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>137548</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8C2A4EA-92FA-C4B9-1C5F-F6A43DE477A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9099176" y="1725706"/>
+          <a:ext cx="5703795" cy="5650842"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3294,7 +3738,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F17"/>
+  <dimension ref="B2:F16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -3313,16 +3757,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.15">
@@ -3330,13 +3774,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -3345,16 +3789,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.15">
@@ -3362,16 +3806,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>366</v>
+        <v>319</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>365</v>
+        <v>318</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>370</v>
+        <v>323</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>367</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.15">
@@ -3379,16 +3823,16 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>369</v>
+        <v>322</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>370</v>
+        <v>323</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>368</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.15">
@@ -3396,16 +3840,16 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.15">
@@ -3413,30 +3857,28 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1"/>
     </row>
@@ -3445,13 +3887,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1"/>
     </row>
@@ -3463,10 +3905,10 @@
         <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -3475,80 +3917,64 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>371</v>
+        <v>325</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B17" s="1">
-        <v>13</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="F6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F15" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="F9" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="F8" r:id="rId5" xr:uid="{D9F07537-65A1-46DF-B5B2-4D161B547953}"/>
+    <hyperlink ref="F9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{D9F07537-65A1-46DF-B5B2-4D161B547953}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId6"/>
+  <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F17AAC-1091-414B-9A6F-EA5ABE92574A}">
-  <dimension ref="B2:O34"/>
+  <dimension ref="B2:O24"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -3557,367 +3983,367 @@
     <col min="4" max="4" width="4" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="15" max="15" width="65.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="90.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C3" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="G3" s="70" t="s">
+        <v>316</v>
+      </c>
+      <c r="G3" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>83</v>
-      </c>
       <c r="O3" s="5" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C4" s="12" t="s">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="86"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="88"/>
-      <c r="N4" s="69" t="s">
-        <v>319</v>
+        <v>7</v>
+      </c>
+      <c r="G4" s="84"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="86"/>
+      <c r="N4" s="67" t="s">
+        <v>278</v>
       </c>
       <c r="O4" s="52" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="66" t="s">
-        <v>314</v>
+      <c r="C5" s="64" t="s">
+        <v>273</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="80" t="s">
-        <v>320</v>
-      </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="82"/>
+        <v>7</v>
+      </c>
+      <c r="G5" s="75" t="s">
+        <v>279</v>
+      </c>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="77"/>
       <c r="O5" s="50" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="67" t="s">
-        <v>315</v>
+      <c r="C6" s="65" t="s">
+        <v>274</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="80" t="s">
-        <v>320</v>
-      </c>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="82"/>
+        <v>7</v>
+      </c>
+      <c r="G6" s="75" t="s">
+        <v>279</v>
+      </c>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="77"/>
       <c r="O6" s="50" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="67" t="s">
-        <v>316</v>
+      <c r="C7" s="65" t="s">
+        <v>275</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="80" t="s">
-        <v>320</v>
-      </c>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="82"/>
+        <v>7</v>
+      </c>
+      <c r="G7" s="75" t="s">
+        <v>279</v>
+      </c>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="76"/>
+      <c r="M7" s="76"/>
+      <c r="N7" s="77"/>
       <c r="O7" s="50" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="65" t="s">
+        <v>276</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="75" t="s">
+        <v>279</v>
+      </c>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="77"/>
+      <c r="O8" s="50" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="65" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="72" t="s">
+        <v>280</v>
+      </c>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="50" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="65" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="72" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="50" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="F11" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="80" t="s">
-        <v>320</v>
-      </c>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
-      <c r="L8" s="81"/>
-      <c r="M8" s="81"/>
-      <c r="N8" s="82"/>
-      <c r="O8" s="50" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="67" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="77" t="s">
-        <v>321</v>
-      </c>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="78"/>
-      <c r="K9" s="78"/>
-      <c r="L9" s="78"/>
-      <c r="M9" s="78"/>
-      <c r="N9" s="79"/>
-      <c r="O9" s="50" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C10" s="67" t="s">
-        <v>308</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="77" t="s">
-        <v>321</v>
-      </c>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="78"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="78"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="50" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="49" t="s">
-        <v>293</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G11" s="92" t="s">
-        <v>294</v>
-      </c>
-      <c r="H11" s="89"/>
-      <c r="I11" s="89"/>
-      <c r="J11" s="89"/>
-      <c r="K11" s="89"/>
-      <c r="L11" s="89"/>
-      <c r="M11" s="89"/>
-      <c r="N11" s="90"/>
+      <c r="G11" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="80"/>
       <c r="O11" s="51" t="s">
-        <v>325</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>40</v>
+        <v>261</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>35</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G12" s="92" t="s">
-        <v>295</v>
-      </c>
-      <c r="H12" s="89"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="89"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="89"/>
-      <c r="M12" s="89"/>
-      <c r="N12" s="90"/>
+        <v>317</v>
+      </c>
+      <c r="G12" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="80"/>
       <c r="O12" s="51" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>40</v>
+      <c r="C13" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>35</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>281</v>
+        <v>345</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G13" s="74" t="s">
-        <v>272</v>
-      </c>
-      <c r="H13" s="89"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="89"/>
-      <c r="K13" s="89"/>
-      <c r="L13" s="89"/>
-      <c r="M13" s="89"/>
-      <c r="N13" s="90"/>
+        <v>317</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>345</v>
+      </c>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="80"/>
       <c r="O13" s="51" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="24" t="s">
-        <v>284</v>
+        <v>97</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G14" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="89"/>
-      <c r="M14" s="89"/>
-      <c r="N14" s="90"/>
+        <v>317</v>
+      </c>
+      <c r="G14" s="81" t="s">
+        <v>412</v>
+      </c>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="80"/>
       <c r="O14" s="51" t="s">
-        <v>330</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>270</v>
+      <c r="C15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G15" s="74" t="s">
-        <v>270</v>
+        <v>317</v>
+      </c>
+      <c r="G15" s="88" t="s">
+        <v>374</v>
       </c>
       <c r="H15" s="89"/>
       <c r="I15" s="89"/>
@@ -3927,24 +4353,24 @@
       <c r="M15" s="89"/>
       <c r="N15" s="90"/>
       <c r="O15" s="51" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>271</v>
+      <c r="C16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G16" s="74" t="s">
-        <v>283</v>
+        <v>317</v>
+      </c>
+      <c r="G16" s="88" t="s">
+        <v>411</v>
       </c>
       <c r="H16" s="89"/>
       <c r="I16" s="89"/>
@@ -3954,476 +4380,244 @@
       <c r="M16" s="89"/>
       <c r="N16" s="90"/>
       <c r="O16" s="51" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="48" t="s">
-        <v>279</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>288</v>
+      <c r="C17" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G17" s="74" t="s">
+        <v>317</v>
+      </c>
+      <c r="G17" s="91"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="92"/>
+      <c r="L17" s="92"/>
+      <c r="M17" s="93"/>
+      <c r="N17" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="51" t="s">
         <v>290</v>
       </c>
-      <c r="H17" s="89"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="89"/>
-      <c r="K17" s="89"/>
-      <c r="L17" s="89"/>
-      <c r="M17" s="89"/>
-      <c r="N17" s="90"/>
-      <c r="O17" s="51" t="s">
-        <v>327</v>
-      </c>
     </row>
     <row r="18" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="H18" s="84"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="86"/>
+      <c r="M18" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="45" t="s">
+        <v>319</v>
+      </c>
+      <c r="O18" s="51" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="G19" s="81"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="82"/>
+      <c r="L19" s="82"/>
+      <c r="M19" s="82"/>
+      <c r="N19" s="83"/>
+      <c r="O19" s="51" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="20" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="G20" s="81"/>
+      <c r="H20" s="82"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="82"/>
+      <c r="L20" s="82"/>
+      <c r="M20" s="82"/>
+      <c r="N20" s="83"/>
+      <c r="O20" s="51" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="G21" s="81"/>
+      <c r="H21" s="82"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="82"/>
+      <c r="K21" s="82"/>
+      <c r="L21" s="82"/>
+      <c r="M21" s="82"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="51" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="G22" s="81"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="82"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="82"/>
+      <c r="M22" s="82"/>
+      <c r="N22" s="83"/>
+      <c r="O22" s="51" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="64" t="s">
+        <v>314</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="72" t="s">
         <v>280</v>
       </c>
-      <c r="D18" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G18" s="74" t="s">
-        <v>291</v>
-      </c>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="89"/>
-      <c r="M18" s="89"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="51" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="19" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G19" s="74" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="89"/>
-      <c r="L19" s="89"/>
-      <c r="M19" s="89"/>
-      <c r="N19" s="90"/>
-      <c r="O19" s="51" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="20" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G20" s="74" t="s">
-        <v>188</v>
-      </c>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="89"/>
-      <c r="N20" s="90"/>
-      <c r="O20" s="51" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G21" s="93" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="94"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="95"/>
-      <c r="O21" s="51" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="22" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C22" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G22" s="93" t="s">
-        <v>189</v>
-      </c>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="95"/>
-      <c r="O22" s="51" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G23" s="83"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="85"/>
-      <c r="M23" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="O23" s="51" t="s">
-        <v>337</v>
+      <c r="H23" s="87"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="50" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C24" s="1" t="s">
-        <v>296</v>
+      <c r="C24" s="66" t="s">
+        <v>315</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="K24" s="87"/>
-      <c r="L24" s="87"/>
-      <c r="M24" s="87"/>
-      <c r="N24" s="88"/>
-      <c r="O24" s="51"/>
-    </row>
-    <row r="25" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
-      <c r="M25" s="87"/>
-      <c r="N25" s="88"/>
-      <c r="O25" s="51"/>
-    </row>
-    <row r="26" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C26" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="87"/>
-      <c r="N26" s="88"/>
-      <c r="O26" s="51"/>
-    </row>
-    <row r="27" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="87"/>
-      <c r="N27" s="88"/>
-      <c r="O27" s="51"/>
-    </row>
-    <row r="28" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C28" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="87"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="87"/>
-      <c r="N28" s="88"/>
-      <c r="O28" s="51"/>
-    </row>
-    <row r="29" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C29" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="86"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="87"/>
-      <c r="N29" s="88"/>
-      <c r="O29" s="51"/>
-    </row>
-    <row r="30" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C30" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="86"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="87"/>
-      <c r="N30" s="88"/>
-      <c r="O30" s="51"/>
-    </row>
-    <row r="31" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C31" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="87"/>
-      <c r="N31" s="88"/>
-      <c r="O31" s="51"/>
-    </row>
-    <row r="32" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C32" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="G32" s="25" t="s">
-        <v>360</v>
-      </c>
-      <c r="H32" s="86"/>
-      <c r="I32" s="88"/>
-      <c r="J32" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="33" t="s">
-        <v>286</v>
-      </c>
-      <c r="L32" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="M32" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="N32" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="O32" s="51" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="66" t="s">
-        <v>361</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G33" s="77" t="s">
-        <v>321</v>
-      </c>
-      <c r="H33" s="91"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
-      <c r="L33" s="78"/>
-      <c r="M33" s="78"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="50" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C34" s="68" t="s">
-        <v>362</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="77" t="s">
-        <v>321</v>
-      </c>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="78"/>
-      <c r="L34" s="78"/>
-      <c r="M34" s="78"/>
-      <c r="N34" s="79"/>
-      <c r="O34" s="50" t="s">
-        <v>324</v>
+        <v>35</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="72" t="s">
+        <v>280</v>
+      </c>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="50" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="21">
     <mergeCell ref="G4:M4"/>
     <mergeCell ref="G9:N9"/>
     <mergeCell ref="G10:N10"/>
-    <mergeCell ref="G33:N33"/>
-    <mergeCell ref="G17:N17"/>
+    <mergeCell ref="G23:N23"/>
     <mergeCell ref="G11:N11"/>
+    <mergeCell ref="G13:N13"/>
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="G15:N15"/>
+    <mergeCell ref="G16:N16"/>
+    <mergeCell ref="G17:M17"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="G24:N24"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="G6:N6"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="G8:N8"/>
     <mergeCell ref="G12:N12"/>
     <mergeCell ref="G19:N19"/>
     <mergeCell ref="G20:N20"/>
     <mergeCell ref="G21:N21"/>
     <mergeCell ref="G22:N22"/>
-    <mergeCell ref="G13:N13"/>
-    <mergeCell ref="G14:N14"/>
-    <mergeCell ref="G15:N15"/>
-    <mergeCell ref="G16:N16"/>
-    <mergeCell ref="G34:N34"/>
-    <mergeCell ref="G5:N5"/>
-    <mergeCell ref="G6:N6"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="G8:N8"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="G24:N24"/>
-    <mergeCell ref="G25:N25"/>
-    <mergeCell ref="G26:N26"/>
-    <mergeCell ref="G27:N27"/>
-    <mergeCell ref="G28:N28"/>
-    <mergeCell ref="G29:N29"/>
-    <mergeCell ref="G30:N30"/>
-    <mergeCell ref="G18:N18"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="G31:N31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4441,421 +4635,421 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>376</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C8" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>373</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C11" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="L11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="M11" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="19" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="71" t="s">
-        <v>192</v>
-      </c>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
+        <v>39</v>
+      </c>
+      <c r="F12" s="94" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="95"/>
+      <c r="K12" s="95"/>
+      <c r="L12" s="95"/>
+      <c r="M12" s="96"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="F13" s="34"/>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="71" t="s">
-        <v>193</v>
-      </c>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="73"/>
+      <c r="J13" s="94" t="s">
+        <v>183</v>
+      </c>
+      <c r="K13" s="95"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="96"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="71" t="s">
-        <v>192</v>
-      </c>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="73"/>
+        <v>41</v>
+      </c>
+      <c r="F14" s="94" t="s">
+        <v>182</v>
+      </c>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="96"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="36"/>
-      <c r="J15" s="71" t="s">
-        <v>193</v>
-      </c>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="73"/>
+      <c r="J15" s="94" t="s">
+        <v>183</v>
+      </c>
+      <c r="K15" s="95"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="96"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="19" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="71" t="s">
-        <v>192</v>
-      </c>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="73"/>
+        <v>43</v>
+      </c>
+      <c r="F16" s="94" t="s">
+        <v>182</v>
+      </c>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="96"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="19" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
-      <c r="J17" s="71" t="s">
-        <v>193</v>
-      </c>
-      <c r="K17" s="72"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="73"/>
+      <c r="J17" s="94" t="s">
+        <v>183</v>
+      </c>
+      <c r="K17" s="95"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="96"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="19" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="35"/>
       <c r="H18" s="36"/>
-      <c r="I18" s="71" t="s">
-        <v>194</v>
-      </c>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="73"/>
+      <c r="I18" s="94" t="s">
+        <v>184</v>
+      </c>
+      <c r="J18" s="95"/>
+      <c r="K18" s="95"/>
+      <c r="L18" s="95"/>
+      <c r="M18" s="96"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="19" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F19" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="L19" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="M19" s="38" t="s">
         <v>84</v>
-      </c>
-      <c r="G19" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="J19" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="K19" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="L19" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="M19" s="38" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="20" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="19" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="35"/>
       <c r="H20" s="36"/>
       <c r="I20" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="J20" s="71" t="s">
-        <v>195</v>
-      </c>
-      <c r="K20" s="72"/>
-      <c r="L20" s="72"/>
-      <c r="M20" s="73"/>
+        <v>88</v>
+      </c>
+      <c r="J20" s="94" t="s">
+        <v>185</v>
+      </c>
+      <c r="K20" s="95"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="96"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F21" s="34"/>
       <c r="G21" s="35"/>
       <c r="H21" s="36"/>
       <c r="I21" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="J21" s="71" t="s">
-        <v>195</v>
-      </c>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="73"/>
+        <v>88</v>
+      </c>
+      <c r="J21" s="94" t="s">
+        <v>185</v>
+      </c>
+      <c r="K21" s="95"/>
+      <c r="L21" s="95"/>
+      <c r="M21" s="96"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F22" s="34"/>
       <c r="G22" s="35"/>
       <c r="H22" s="36"/>
       <c r="I22" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="J22" s="71" t="s">
-        <v>195</v>
-      </c>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="73"/>
+        <v>88</v>
+      </c>
+      <c r="J22" s="94" t="s">
+        <v>185</v>
+      </c>
+      <c r="K22" s="95"/>
+      <c r="L22" s="95"/>
+      <c r="M22" s="96"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="73"/>
+        <v>50</v>
+      </c>
+      <c r="F23" s="94" t="s">
+        <v>186</v>
+      </c>
+      <c r="G23" s="95"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="95"/>
+      <c r="M23" s="96"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="71" t="s">
-        <v>197</v>
-      </c>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="73"/>
+        <v>51</v>
+      </c>
+      <c r="F24" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="95"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="96"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F25" s="34"/>
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
       <c r="I25" s="36"/>
-      <c r="J25" s="71" t="s">
-        <v>198</v>
-      </c>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="73"/>
+      <c r="J25" s="94" t="s">
+        <v>188</v>
+      </c>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="96"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
@@ -4868,13 +5062,13 @@
     </row>
     <row r="27" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="19" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
@@ -4887,327 +5081,327 @@
     </row>
     <row r="28" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="19" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="F28" s="74" t="s">
-        <v>192</v>
-      </c>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="75"/>
-      <c r="K28" s="75"/>
-      <c r="L28" s="75"/>
-      <c r="M28" s="76"/>
+        <v>53</v>
+      </c>
+      <c r="F28" s="81" t="s">
+        <v>182</v>
+      </c>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="82"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="82"/>
+      <c r="L28" s="82"/>
+      <c r="M28" s="83"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="I29" s="28"/>
-      <c r="J29" s="74" t="s">
-        <v>193</v>
-      </c>
-      <c r="K29" s="75"/>
-      <c r="L29" s="75"/>
-      <c r="M29" s="76"/>
+      <c r="J29" s="81" t="s">
+        <v>183</v>
+      </c>
+      <c r="K29" s="82"/>
+      <c r="L29" s="82"/>
+      <c r="M29" s="83"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" s="74" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="75"/>
-      <c r="L30" s="75"/>
-      <c r="M30" s="76"/>
+        <v>55</v>
+      </c>
+      <c r="F30" s="81" t="s">
+        <v>182</v>
+      </c>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="82"/>
+      <c r="K30" s="82"/>
+      <c r="L30" s="82"/>
+      <c r="M30" s="83"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F31" s="26"/>
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="I31" s="28"/>
-      <c r="J31" s="74" t="s">
-        <v>193</v>
-      </c>
-      <c r="K31" s="75"/>
-      <c r="L31" s="75"/>
-      <c r="M31" s="76"/>
+      <c r="J31" s="81" t="s">
+        <v>183</v>
+      </c>
+      <c r="K31" s="82"/>
+      <c r="L31" s="82"/>
+      <c r="M31" s="83"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="F32" s="74" t="s">
-        <v>192</v>
-      </c>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75"/>
-      <c r="L32" s="75"/>
-      <c r="M32" s="76"/>
+        <v>57</v>
+      </c>
+      <c r="F32" s="81" t="s">
+        <v>182</v>
+      </c>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="82"/>
+      <c r="M32" s="83"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F33" s="26"/>
       <c r="G33" s="27"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
-      <c r="J33" s="74" t="s">
-        <v>193</v>
-      </c>
-      <c r="K33" s="75"/>
-      <c r="L33" s="75"/>
-      <c r="M33" s="76"/>
+      <c r="J33" s="81" t="s">
+        <v>183</v>
+      </c>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
+      <c r="M33" s="83"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F34" s="26"/>
       <c r="G34" s="27"/>
       <c r="H34" s="28"/>
-      <c r="I34" s="74" t="s">
-        <v>194</v>
-      </c>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="75"/>
-      <c r="M34" s="76"/>
+      <c r="I34" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+      <c r="M34" s="83"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F35" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="G35" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="I35" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="J35" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="K35" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="L35" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="M35" s="30" t="s">
         <v>84</v>
-      </c>
-      <c r="G35" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="I35" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="J35" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="K35" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="L35" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="M35" s="30" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="19" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F36" s="26"/>
       <c r="G36" s="27"/>
       <c r="H36" s="28"/>
       <c r="I36" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="J36" s="74" t="s">
-        <v>195</v>
-      </c>
-      <c r="K36" s="75"/>
-      <c r="L36" s="75"/>
-      <c r="M36" s="76"/>
+        <v>88</v>
+      </c>
+      <c r="J36" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="K36" s="82"/>
+      <c r="L36" s="82"/>
+      <c r="M36" s="83"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F37" s="26"/>
       <c r="G37" s="27"/>
       <c r="H37" s="28"/>
       <c r="I37" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="J37" s="74" t="s">
-        <v>195</v>
-      </c>
-      <c r="K37" s="75"/>
-      <c r="L37" s="75"/>
-      <c r="M37" s="76"/>
+        <v>88</v>
+      </c>
+      <c r="J37" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
+      <c r="M37" s="83"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F38" s="26"/>
       <c r="G38" s="27"/>
       <c r="H38" s="28"/>
       <c r="I38" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="J38" s="74" t="s">
-        <v>195</v>
-      </c>
-      <c r="K38" s="75"/>
-      <c r="L38" s="75"/>
-      <c r="M38" s="76"/>
+        <v>88</v>
+      </c>
+      <c r="J38" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="K38" s="82"/>
+      <c r="L38" s="82"/>
+      <c r="M38" s="83"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="74" t="s">
-        <v>196</v>
-      </c>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-      <c r="K39" s="75"/>
-      <c r="L39" s="75"/>
-      <c r="M39" s="76"/>
+        <v>64</v>
+      </c>
+      <c r="F39" s="81" t="s">
+        <v>186</v>
+      </c>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
+      <c r="L39" s="82"/>
+      <c r="M39" s="83"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="19" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="F40" s="74" t="s">
-        <v>197</v>
-      </c>
-      <c r="G40" s="75"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
-      <c r="J40" s="75"/>
-      <c r="K40" s="75"/>
-      <c r="L40" s="75"/>
-      <c r="M40" s="76"/>
+        <v>65</v>
+      </c>
+      <c r="F40" s="81" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
+      <c r="M40" s="83"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="19" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="27"/>
       <c r="H41" s="27"/>
       <c r="I41" s="28"/>
-      <c r="J41" s="74" t="s">
-        <v>198</v>
-      </c>
-      <c r="K41" s="75"/>
-      <c r="L41" s="75"/>
-      <c r="M41" s="76"/>
+      <c r="J41" s="81" t="s">
+        <v>188</v>
+      </c>
+      <c r="K41" s="82"/>
+      <c r="L41" s="82"/>
+      <c r="M41" s="83"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="19" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F42" s="26"/>
       <c r="G42" s="27"/>
@@ -5220,106 +5414,106 @@
     </row>
     <row r="43" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="19" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F43" s="113"/>
-      <c r="G43" s="114"/>
-      <c r="H43" s="114"/>
-      <c r="I43" s="115"/>
-      <c r="J43" s="116" t="s">
-        <v>127</v>
-      </c>
-      <c r="K43" s="117"/>
-      <c r="L43" s="117"/>
-      <c r="M43" s="118"/>
+        <v>68</v>
+      </c>
+      <c r="F43" s="69"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="100" t="s">
+        <v>120</v>
+      </c>
+      <c r="K43" s="101"/>
+      <c r="L43" s="101"/>
+      <c r="M43" s="102"/>
     </row>
     <row r="44" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="F44" s="119" t="s">
-        <v>195</v>
-      </c>
-      <c r="G44" s="120"/>
-      <c r="H44" s="120"/>
-      <c r="I44" s="120"/>
-      <c r="J44" s="120"/>
-      <c r="K44" s="120"/>
-      <c r="L44" s="120"/>
-      <c r="M44" s="121"/>
+        <v>346</v>
+      </c>
+      <c r="F44" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="G44" s="98"/>
+      <c r="H44" s="98"/>
+      <c r="I44" s="98"/>
+      <c r="J44" s="98"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="99"/>
       <c r="O44" t="s">
-        <v>419</v>
+        <v>372</v>
       </c>
     </row>
     <row r="45" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="19" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="119" t="s">
-        <v>195</v>
-      </c>
-      <c r="G45" s="120"/>
-      <c r="H45" s="120"/>
-      <c r="I45" s="120"/>
-      <c r="J45" s="120"/>
-      <c r="K45" s="120"/>
-      <c r="L45" s="120"/>
-      <c r="M45" s="121"/>
+        <v>362</v>
+      </c>
+      <c r="F45" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="G45" s="98"/>
+      <c r="H45" s="98"/>
+      <c r="I45" s="98"/>
+      <c r="J45" s="98"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="98"/>
+      <c r="M45" s="99"/>
       <c r="O45" t="s">
-        <v>419</v>
+        <v>372</v>
       </c>
     </row>
     <row r="46" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="19" t="s">
-        <v>395</v>
+        <v>348</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>410</v>
-      </c>
-      <c r="F46" s="119" t="s">
-        <v>195</v>
-      </c>
-      <c r="G46" s="120"/>
-      <c r="H46" s="120"/>
-      <c r="I46" s="120"/>
-      <c r="J46" s="120"/>
-      <c r="K46" s="120"/>
-      <c r="L46" s="120"/>
-      <c r="M46" s="121"/>
+        <v>363</v>
+      </c>
+      <c r="F46" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="G46" s="98"/>
+      <c r="H46" s="98"/>
+      <c r="I46" s="98"/>
+      <c r="J46" s="98"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="98"/>
+      <c r="M46" s="99"/>
       <c r="O46" t="s">
-        <v>419</v>
+        <v>372</v>
       </c>
     </row>
     <row r="47" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="19" t="s">
-        <v>396</v>
+        <v>349</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F47" s="61"/>
       <c r="G47" s="61"/>
@@ -5332,85 +5526,85 @@
     </row>
     <row r="48" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="19" t="s">
-        <v>397</v>
+        <v>350</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>413</v>
-      </c>
-      <c r="F48" s="119" t="s">
-        <v>195</v>
-      </c>
-      <c r="G48" s="120"/>
-      <c r="H48" s="120"/>
-      <c r="I48" s="120"/>
-      <c r="J48" s="120"/>
-      <c r="K48" s="120"/>
-      <c r="L48" s="120"/>
-      <c r="M48" s="121"/>
+        <v>366</v>
+      </c>
+      <c r="F48" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="G48" s="98"/>
+      <c r="H48" s="98"/>
+      <c r="I48" s="98"/>
+      <c r="J48" s="98"/>
+      <c r="K48" s="98"/>
+      <c r="L48" s="98"/>
+      <c r="M48" s="99"/>
       <c r="O48" t="s">
-        <v>419</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="19" t="s">
-        <v>398</v>
+        <v>351</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>414</v>
-      </c>
-      <c r="F49" s="119" t="s">
-        <v>195</v>
-      </c>
-      <c r="G49" s="120"/>
-      <c r="H49" s="120"/>
-      <c r="I49" s="120"/>
-      <c r="J49" s="120"/>
-      <c r="K49" s="120"/>
-      <c r="L49" s="120"/>
-      <c r="M49" s="121"/>
+        <v>367</v>
+      </c>
+      <c r="F49" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="G49" s="98"/>
+      <c r="H49" s="98"/>
+      <c r="I49" s="98"/>
+      <c r="J49" s="98"/>
+      <c r="K49" s="98"/>
+      <c r="L49" s="98"/>
+      <c r="M49" s="99"/>
       <c r="O49" t="s">
-        <v>419</v>
+        <v>372</v>
       </c>
     </row>
     <row r="50" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="19" t="s">
-        <v>399</v>
+        <v>352</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="F50" s="119" t="s">
-        <v>195</v>
-      </c>
-      <c r="G50" s="120"/>
-      <c r="H50" s="120"/>
-      <c r="I50" s="120"/>
-      <c r="J50" s="120"/>
-      <c r="K50" s="120"/>
-      <c r="L50" s="120"/>
-      <c r="M50" s="121"/>
+        <v>368</v>
+      </c>
+      <c r="F50" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="G50" s="98"/>
+      <c r="H50" s="98"/>
+      <c r="I50" s="98"/>
+      <c r="J50" s="98"/>
+      <c r="K50" s="98"/>
+      <c r="L50" s="98"/>
+      <c r="M50" s="99"/>
       <c r="O50" t="s">
-        <v>419</v>
+        <v>372</v>
       </c>
     </row>
     <row r="51" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F51" s="61"/>
       <c r="G51" s="61"/>
@@ -5423,85 +5617,85 @@
     </row>
     <row r="52" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
-        <v>401</v>
+        <v>354</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="F52" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
-      <c r="I52" s="75"/>
-      <c r="J52" s="75"/>
-      <c r="K52" s="75"/>
-      <c r="L52" s="75"/>
-      <c r="M52" s="76"/>
+        <v>347</v>
+      </c>
+      <c r="F52" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G52" s="82"/>
+      <c r="H52" s="82"/>
+      <c r="I52" s="82"/>
+      <c r="J52" s="82"/>
+      <c r="K52" s="82"/>
+      <c r="L52" s="82"/>
+      <c r="M52" s="83"/>
       <c r="O52" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="53" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
-        <v>402</v>
+        <v>355</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>411</v>
-      </c>
-      <c r="F53" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G53" s="75"/>
-      <c r="H53" s="75"/>
-      <c r="I53" s="75"/>
-      <c r="J53" s="75"/>
-      <c r="K53" s="75"/>
-      <c r="L53" s="75"/>
-      <c r="M53" s="76"/>
+        <v>364</v>
+      </c>
+      <c r="F53" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G53" s="82"/>
+      <c r="H53" s="82"/>
+      <c r="I53" s="82"/>
+      <c r="J53" s="82"/>
+      <c r="K53" s="82"/>
+      <c r="L53" s="82"/>
+      <c r="M53" s="83"/>
       <c r="O53" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="54" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>412</v>
-      </c>
-      <c r="F54" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G54" s="75"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="75"/>
-      <c r="J54" s="75"/>
-      <c r="K54" s="75"/>
-      <c r="L54" s="75"/>
-      <c r="M54" s="76"/>
+        <v>365</v>
+      </c>
+      <c r="F54" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
+      <c r="I54" s="82"/>
+      <c r="J54" s="82"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="82"/>
+      <c r="M54" s="83"/>
       <c r="O54" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
-        <v>404</v>
+        <v>357</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F55" s="61"/>
       <c r="G55" s="61"/>
@@ -5514,85 +5708,85 @@
     </row>
     <row r="56" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>416</v>
-      </c>
-      <c r="F56" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G56" s="75"/>
-      <c r="H56" s="75"/>
-      <c r="I56" s="75"/>
-      <c r="J56" s="75"/>
-      <c r="K56" s="75"/>
-      <c r="L56" s="75"/>
-      <c r="M56" s="76"/>
+        <v>369</v>
+      </c>
+      <c r="F56" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G56" s="82"/>
+      <c r="H56" s="82"/>
+      <c r="I56" s="82"/>
+      <c r="J56" s="82"/>
+      <c r="K56" s="82"/>
+      <c r="L56" s="82"/>
+      <c r="M56" s="83"/>
       <c r="O56" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="19" t="s">
-        <v>406</v>
+        <v>359</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="F57" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G57" s="75"/>
-      <c r="H57" s="75"/>
-      <c r="I57" s="75"/>
-      <c r="J57" s="75"/>
-      <c r="K57" s="75"/>
-      <c r="L57" s="75"/>
-      <c r="M57" s="76"/>
+        <v>370</v>
+      </c>
+      <c r="F57" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G57" s="82"/>
+      <c r="H57" s="82"/>
+      <c r="I57" s="82"/>
+      <c r="J57" s="82"/>
+      <c r="K57" s="82"/>
+      <c r="L57" s="82"/>
+      <c r="M57" s="83"/>
       <c r="O57" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
-        <v>407</v>
+        <v>360</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>418</v>
-      </c>
-      <c r="F58" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G58" s="75"/>
-      <c r="H58" s="75"/>
-      <c r="I58" s="75"/>
-      <c r="J58" s="75"/>
-      <c r="K58" s="75"/>
-      <c r="L58" s="75"/>
-      <c r="M58" s="76"/>
+        <v>371</v>
+      </c>
+      <c r="F58" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G58" s="82"/>
+      <c r="H58" s="82"/>
+      <c r="I58" s="82"/>
+      <c r="J58" s="82"/>
+      <c r="K58" s="82"/>
+      <c r="L58" s="82"/>
+      <c r="M58" s="83"/>
       <c r="O58" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="59" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C59" s="20" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F59" s="61"/>
       <c r="G59" s="61"/>
@@ -5605,13 +5799,13 @@
     </row>
     <row r="60" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C60" s="19" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F60" s="61"/>
       <c r="G60" s="61"/>
@@ -5624,7 +5818,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="F56:M56"/>
     <mergeCell ref="F57:M57"/>
     <mergeCell ref="F58:M58"/>
     <mergeCell ref="F49:M49"/>
@@ -5632,19 +5825,31 @@
     <mergeCell ref="F52:M52"/>
     <mergeCell ref="F53:M53"/>
     <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="F45:M45"/>
-    <mergeCell ref="F46:M46"/>
     <mergeCell ref="F48:M48"/>
     <mergeCell ref="F40:M40"/>
     <mergeCell ref="J41:M41"/>
     <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="J31:M31"/>
     <mergeCell ref="J33:M33"/>
     <mergeCell ref="I34:M34"/>
     <mergeCell ref="J36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="F16:M16"/>
     <mergeCell ref="F32:M32"/>
     <mergeCell ref="I18:M18"/>
     <mergeCell ref="J20:M20"/>
@@ -5652,20 +5857,10 @@
     <mergeCell ref="J22:M22"/>
     <mergeCell ref="F23:M23"/>
     <mergeCell ref="F24:M24"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="F16:M16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5680,324 +5875,324 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F6" s="93" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94"/>
-      <c r="M6" s="95"/>
+        <v>92</v>
+      </c>
+      <c r="F6" s="88" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="90"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="93" t="s">
-        <v>189</v>
-      </c>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="95"/>
+        <v>93</v>
+      </c>
+      <c r="F7" s="88" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="89"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="89"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="89"/>
+      <c r="M7" s="90"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
-        <v>374</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="L18" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="M18" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="19" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J19" s="93" t="s">
-        <v>116</v>
-      </c>
-      <c r="K19" s="94"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="95"/>
+        <v>108</v>
+      </c>
+      <c r="J19" s="88" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" s="89"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="90"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="19" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J20" s="93" t="s">
-        <v>116</v>
-      </c>
-      <c r="K20" s="94"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="95"/>
+        <v>108</v>
+      </c>
+      <c r="J20" s="88" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
+      <c r="M20" s="90"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E21" s="6"/>
-      <c r="F21" s="93" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" s="95"/>
-      <c r="H21" s="93" t="s">
-        <v>118</v>
-      </c>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="95"/>
+      <c r="F21" s="88" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="90"/>
+      <c r="H21" s="88" t="s">
+        <v>111</v>
+      </c>
+      <c r="I21" s="89"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="90"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E22" s="6"/>
-      <c r="F22" s="93" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="95"/>
+      <c r="F22" s="88" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="90"/>
       <c r="H22" s="18"/>
       <c r="I22" s="11" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K22" s="93" t="s">
-        <v>119</v>
-      </c>
-      <c r="L22" s="94"/>
-      <c r="M22" s="95"/>
+        <v>113</v>
+      </c>
+      <c r="K22" s="88" t="s">
+        <v>112</v>
+      </c>
+      <c r="L22" s="89"/>
+      <c r="M22" s="90"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="93" t="s">
-        <v>122</v>
-      </c>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="93" t="s">
-        <v>123</v>
-      </c>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="95"/>
+      <c r="F23" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="89"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="88" t="s">
+        <v>116</v>
+      </c>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="90"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="93" t="s">
-        <v>122</v>
-      </c>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="93" t="s">
-        <v>123</v>
-      </c>
-      <c r="K24" s="94"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="95"/>
+      <c r="F24" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="88" t="s">
+        <v>116</v>
+      </c>
+      <c r="K24" s="89"/>
+      <c r="L24" s="89"/>
+      <c r="M24" s="90"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="93" t="s">
-        <v>124</v>
-      </c>
-      <c r="G25" s="94"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="93" t="s">
-        <v>125</v>
-      </c>
-      <c r="K25" s="94"/>
-      <c r="L25" s="94"/>
-      <c r="M25" s="95"/>
+      <c r="F25" s="88" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" s="89"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="90"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="93" t="s">
-        <v>124</v>
-      </c>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="95"/>
-      <c r="J26" s="93" t="s">
-        <v>125</v>
-      </c>
-      <c r="K26" s="94"/>
-      <c r="L26" s="94"/>
-      <c r="M26" s="95"/>
+      <c r="F26" s="88" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="89"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="K26" s="89"/>
+      <c r="L26" s="89"/>
+      <c r="M26" s="90"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="19" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="8"/>
@@ -6011,227 +6206,227 @@
     </row>
     <row r="28" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="19" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="14"/>
       <c r="G28" s="15"/>
       <c r="H28" s="16" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="K28" s="14"/>
       <c r="L28" s="15"/>
       <c r="M28" s="17" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="19" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F29" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G29" s="94"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="94"/>
-      <c r="J29" s="94"/>
-      <c r="K29" s="94"/>
-      <c r="L29" s="94"/>
-      <c r="M29" s="95"/>
+        <v>100</v>
+      </c>
+      <c r="F29" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="90"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E30" s="6"/>
-      <c r="F30" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="94"/>
-      <c r="K30" s="94"/>
-      <c r="L30" s="94"/>
-      <c r="M30" s="95"/>
+      <c r="F30" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
+      <c r="L30" s="89"/>
+      <c r="M30" s="90"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E31" s="6"/>
-      <c r="F31" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G31" s="94"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="94"/>
-      <c r="J31" s="94"/>
-      <c r="K31" s="94"/>
-      <c r="L31" s="94"/>
-      <c r="M31" s="95"/>
+      <c r="F31" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
+      <c r="L31" s="89"/>
+      <c r="M31" s="90"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="94"/>
-      <c r="K32" s="94"/>
-      <c r="L32" s="94"/>
-      <c r="M32" s="95"/>
+      <c r="F32" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" s="89"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="89"/>
+      <c r="K32" s="89"/>
+      <c r="L32" s="89"/>
+      <c r="M32" s="90"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="94"/>
-      <c r="K33" s="94"/>
-      <c r="L33" s="94"/>
-      <c r="M33" s="95"/>
+      <c r="F33" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="89"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="89"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="89"/>
+      <c r="M33" s="90"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="94"/>
-      <c r="L34" s="94"/>
-      <c r="M34" s="95"/>
+      <c r="F34" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G34" s="89"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="89"/>
+      <c r="J34" s="89"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="89"/>
+      <c r="M34" s="90"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G35" s="94"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="94"/>
-      <c r="J35" s="94"/>
-      <c r="K35" s="94"/>
-      <c r="L35" s="94"/>
-      <c r="M35" s="95"/>
+      <c r="F35" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G35" s="89"/>
+      <c r="H35" s="89"/>
+      <c r="I35" s="89"/>
+      <c r="J35" s="89"/>
+      <c r="K35" s="89"/>
+      <c r="L35" s="89"/>
+      <c r="M35" s="90"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="88" t="s">
         <v>145</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G36" s="94"/>
-      <c r="H36" s="94"/>
-      <c r="I36" s="94"/>
-      <c r="J36" s="94"/>
-      <c r="K36" s="94"/>
-      <c r="L36" s="94"/>
-      <c r="M36" s="95"/>
+      <c r="G36" s="89"/>
+      <c r="H36" s="89"/>
+      <c r="I36" s="89"/>
+      <c r="J36" s="89"/>
+      <c r="K36" s="89"/>
+      <c r="L36" s="89"/>
+      <c r="M36" s="90"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G37" s="94"/>
-      <c r="H37" s="94"/>
-      <c r="I37" s="94"/>
-      <c r="J37" s="94"/>
-      <c r="K37" s="94"/>
-      <c r="L37" s="94"/>
-      <c r="M37" s="95"/>
+      <c r="F37" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G37" s="89"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="89"/>
+      <c r="K37" s="89"/>
+      <c r="L37" s="89"/>
+      <c r="M37" s="90"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G38" s="94"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="94"/>
-      <c r="J38" s="94"/>
-      <c r="K38" s="94"/>
-      <c r="L38" s="94"/>
-      <c r="M38" s="95"/>
+      <c r="F38" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="89"/>
+      <c r="M38" s="90"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="8"/>
@@ -6245,235 +6440,235 @@
     </row>
     <row r="40" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="19" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="8"/>
       <c r="G40" s="10"/>
       <c r="H40" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J40" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K40" s="94"/>
-      <c r="L40" s="95"/>
+        <v>143</v>
+      </c>
+      <c r="J40" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="K40" s="89"/>
+      <c r="L40" s="90"/>
       <c r="M40" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="19" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="8"/>
       <c r="G41" s="10"/>
       <c r="H41" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J41" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K41" s="94"/>
-      <c r="L41" s="95"/>
+        <v>143</v>
+      </c>
+      <c r="J41" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="K41" s="89"/>
+      <c r="L41" s="90"/>
       <c r="M41" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="19" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="8"/>
       <c r="G42" s="10"/>
       <c r="H42" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J42" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K42" s="94"/>
-      <c r="L42" s="95"/>
+        <v>143</v>
+      </c>
+      <c r="J42" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="K42" s="89"/>
+      <c r="L42" s="90"/>
       <c r="M42" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="19" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="8"/>
       <c r="G43" s="10"/>
       <c r="H43" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J43" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K43" s="94"/>
-      <c r="L43" s="95"/>
+        <v>143</v>
+      </c>
+      <c r="J43" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="K43" s="89"/>
+      <c r="L43" s="90"/>
       <c r="M43" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="8"/>
       <c r="G44" s="10"/>
       <c r="H44" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J44" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K44" s="94"/>
-      <c r="L44" s="95"/>
+        <v>143</v>
+      </c>
+      <c r="J44" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="K44" s="89"/>
+      <c r="L44" s="90"/>
       <c r="M44" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="19" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="8"/>
       <c r="G45" s="10"/>
       <c r="H45" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J45" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K45" s="94"/>
-      <c r="L45" s="95"/>
+        <v>143</v>
+      </c>
+      <c r="J45" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="K45" s="89"/>
+      <c r="L45" s="90"/>
       <c r="M45" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="19" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="8"/>
       <c r="G46" s="10"/>
       <c r="H46" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J46" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K46" s="94"/>
-      <c r="L46" s="95"/>
+        <v>143</v>
+      </c>
+      <c r="J46" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="K46" s="89"/>
+      <c r="L46" s="90"/>
       <c r="M46" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="19" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="8"/>
       <c r="G47" s="10"/>
       <c r="H47" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J47" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K47" s="94"/>
-      <c r="L47" s="95"/>
+        <v>143</v>
+      </c>
+      <c r="J47" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="K47" s="89"/>
+      <c r="L47" s="90"/>
       <c r="M47" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="19" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="8"/>
       <c r="G48" s="10"/>
       <c r="H48" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J48" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K48" s="94"/>
-      <c r="L48" s="95"/>
+        <v>143</v>
+      </c>
+      <c r="J48" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="K48" s="89"/>
+      <c r="L48" s="90"/>
       <c r="M48" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="19" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="8"/>
@@ -6487,199 +6682,199 @@
     </row>
     <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="19" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="G50" s="94"/>
-      <c r="H50" s="94"/>
-      <c r="I50" s="95"/>
-      <c r="J50" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="K50" s="94"/>
-      <c r="L50" s="94"/>
-      <c r="M50" s="95"/>
+      <c r="F50" s="88" t="s">
+        <v>166</v>
+      </c>
+      <c r="G50" s="89"/>
+      <c r="H50" s="89"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="K50" s="89"/>
+      <c r="L50" s="89"/>
+      <c r="M50" s="90"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="G51" s="94"/>
-      <c r="H51" s="94"/>
-      <c r="I51" s="95"/>
-      <c r="J51" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="K51" s="94"/>
-      <c r="L51" s="94"/>
-      <c r="M51" s="95"/>
+      <c r="F51" s="88" t="s">
+        <v>166</v>
+      </c>
+      <c r="G51" s="89"/>
+      <c r="H51" s="89"/>
+      <c r="I51" s="90"/>
+      <c r="J51" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="K51" s="89"/>
+      <c r="L51" s="89"/>
+      <c r="M51" s="90"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="G52" s="94"/>
-      <c r="H52" s="94"/>
-      <c r="I52" s="95"/>
-      <c r="J52" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="K52" s="94"/>
-      <c r="L52" s="94"/>
-      <c r="M52" s="95"/>
+      <c r="F52" s="88" t="s">
+        <v>166</v>
+      </c>
+      <c r="G52" s="89"/>
+      <c r="H52" s="89"/>
+      <c r="I52" s="90"/>
+      <c r="J52" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="K52" s="89"/>
+      <c r="L52" s="89"/>
+      <c r="M52" s="90"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="88" t="s">
         <v>166</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E53" s="1"/>
-      <c r="F53" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="G53" s="94"/>
-      <c r="H53" s="94"/>
-      <c r="I53" s="95"/>
-      <c r="J53" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="K53" s="94"/>
-      <c r="L53" s="94"/>
-      <c r="M53" s="95"/>
+      <c r="G53" s="89"/>
+      <c r="H53" s="89"/>
+      <c r="I53" s="90"/>
+      <c r="J53" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="K53" s="89"/>
+      <c r="L53" s="89"/>
+      <c r="M53" s="90"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="88" t="s">
+        <v>166</v>
+      </c>
+      <c r="G54" s="89"/>
+      <c r="H54" s="89"/>
+      <c r="I54" s="90"/>
+      <c r="J54" s="88" t="s">
         <v>167</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E54" s="1"/>
-      <c r="F54" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="G54" s="94"/>
-      <c r="H54" s="94"/>
-      <c r="I54" s="95"/>
-      <c r="J54" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="K54" s="94"/>
-      <c r="L54" s="94"/>
-      <c r="M54" s="95"/>
+      <c r="K54" s="89"/>
+      <c r="L54" s="89"/>
+      <c r="M54" s="90"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="G55" s="94"/>
-      <c r="H55" s="94"/>
-      <c r="I55" s="95"/>
-      <c r="J55" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="K55" s="94"/>
-      <c r="L55" s="94"/>
-      <c r="M55" s="95"/>
+      <c r="F55" s="88" t="s">
+        <v>166</v>
+      </c>
+      <c r="G55" s="89"/>
+      <c r="H55" s="89"/>
+      <c r="I55" s="90"/>
+      <c r="J55" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="K55" s="89"/>
+      <c r="L55" s="89"/>
+      <c r="M55" s="90"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="G56" s="94"/>
-      <c r="H56" s="94"/>
-      <c r="I56" s="95"/>
-      <c r="J56" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="K56" s="94"/>
-      <c r="L56" s="94"/>
-      <c r="M56" s="95"/>
+      <c r="F56" s="88" t="s">
+        <v>166</v>
+      </c>
+      <c r="G56" s="89"/>
+      <c r="H56" s="89"/>
+      <c r="I56" s="90"/>
+      <c r="J56" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="K56" s="89"/>
+      <c r="L56" s="89"/>
+      <c r="M56" s="90"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="19" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="G57" s="94"/>
-      <c r="H57" s="94"/>
-      <c r="I57" s="95"/>
-      <c r="J57" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="K57" s="94"/>
-      <c r="L57" s="94"/>
-      <c r="M57" s="95"/>
+      <c r="F57" s="88" t="s">
+        <v>166</v>
+      </c>
+      <c r="G57" s="89"/>
+      <c r="H57" s="89"/>
+      <c r="I57" s="90"/>
+      <c r="J57" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="K57" s="89"/>
+      <c r="L57" s="89"/>
+      <c r="M57" s="90"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="G58" s="94"/>
-      <c r="H58" s="94"/>
-      <c r="I58" s="95"/>
-      <c r="J58" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="K58" s="94"/>
-      <c r="L58" s="94"/>
-      <c r="M58" s="95"/>
+      <c r="F58" s="88" t="s">
+        <v>166</v>
+      </c>
+      <c r="G58" s="89"/>
+      <c r="H58" s="89"/>
+      <c r="I58" s="90"/>
+      <c r="J58" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="K58" s="89"/>
+      <c r="L58" s="89"/>
+      <c r="M58" s="90"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="19" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="8"/>
@@ -6693,13 +6888,13 @@
     </row>
     <row r="60" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="19" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="9"/>
@@ -6707,20 +6902,20 @@
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
       <c r="K60" s="10"/>
-      <c r="L60" s="74" t="s">
-        <v>184</v>
-      </c>
-      <c r="M60" s="90"/>
+      <c r="L60" s="81" t="s">
+        <v>177</v>
+      </c>
+      <c r="M60" s="80"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="19" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="9"/>
@@ -6728,20 +6923,20 @@
       <c r="I61" s="9"/>
       <c r="J61" s="9"/>
       <c r="K61" s="10"/>
-      <c r="L61" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="M61" s="90"/>
+      <c r="L61" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="M61" s="80"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="19" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="9"/>
@@ -6749,20 +6944,20 @@
       <c r="I62" s="9"/>
       <c r="J62" s="9"/>
       <c r="K62" s="10"/>
-      <c r="L62" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="M62" s="90"/>
+      <c r="L62" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="M62" s="80"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="19" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F63" s="8"/>
       <c r="G63" s="9"/>
@@ -6770,20 +6965,20 @@
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
       <c r="K63" s="10"/>
-      <c r="L63" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="M63" s="90"/>
+      <c r="L63" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="M63" s="80"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="19" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="9"/>
@@ -6791,20 +6986,20 @@
       <c r="I64" s="9"/>
       <c r="J64" s="9"/>
       <c r="K64" s="10"/>
-      <c r="L64" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="M64" s="90"/>
+      <c r="L64" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="M64" s="80"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="22" t="s">
         <v>180</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E65" s="22" t="s">
-        <v>187</v>
       </c>
       <c r="F65" s="8"/>
       <c r="G65" s="9"/>
@@ -6812,20 +7007,20 @@
       <c r="I65" s="9"/>
       <c r="J65" s="9"/>
       <c r="K65" s="10"/>
-      <c r="L65" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="M65" s="90"/>
+      <c r="L65" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="M65" s="80"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="19" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="9"/>
@@ -6833,20 +7028,20 @@
       <c r="I66" s="9"/>
       <c r="J66" s="9"/>
       <c r="K66" s="10"/>
-      <c r="L66" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="M66" s="90"/>
+      <c r="L66" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="M66" s="80"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="19" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="9"/>
@@ -6854,20 +7049,20 @@
       <c r="I67" s="9"/>
       <c r="J67" s="9"/>
       <c r="K67" s="10"/>
-      <c r="L67" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="M67" s="90"/>
+      <c r="L67" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="M67" s="80"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="19" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="9"/>
@@ -6875,17 +7070,17 @@
       <c r="I68" s="9"/>
       <c r="J68" s="9"/>
       <c r="K68" s="10"/>
-      <c r="L68" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="M68" s="90"/>
+      <c r="L68" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="M68" s="80"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="19" t="s">
-        <v>377</v>
+        <v>330</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="8"/>
@@ -6899,226 +7094,226 @@
     </row>
     <row r="70" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="19" t="s">
-        <v>378</v>
+        <v>331</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F70" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G70" s="75"/>
-      <c r="H70" s="75"/>
-      <c r="I70" s="75"/>
-      <c r="J70" s="75"/>
-      <c r="K70" s="75"/>
-      <c r="L70" s="75"/>
-      <c r="M70" s="76"/>
+        <v>341</v>
+      </c>
+      <c r="F70" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G70" s="82"/>
+      <c r="H70" s="82"/>
+      <c r="I70" s="82"/>
+      <c r="J70" s="82"/>
+      <c r="K70" s="82"/>
+      <c r="L70" s="82"/>
+      <c r="M70" s="83"/>
       <c r="O70" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="19" t="s">
-        <v>379</v>
+        <v>332</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F71" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G71" s="75"/>
-      <c r="H71" s="75"/>
-      <c r="I71" s="75"/>
-      <c r="J71" s="75"/>
-      <c r="K71" s="75"/>
-      <c r="L71" s="75"/>
-      <c r="M71" s="76"/>
+        <v>341</v>
+      </c>
+      <c r="F71" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G71" s="82"/>
+      <c r="H71" s="82"/>
+      <c r="I71" s="82"/>
+      <c r="J71" s="82"/>
+      <c r="K71" s="82"/>
+      <c r="L71" s="82"/>
+      <c r="M71" s="83"/>
       <c r="O71" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="72" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C72" s="19" t="s">
-        <v>380</v>
+        <v>333</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F72" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G72" s="75"/>
-      <c r="H72" s="75"/>
-      <c r="I72" s="75"/>
-      <c r="J72" s="75"/>
-      <c r="K72" s="75"/>
-      <c r="L72" s="75"/>
-      <c r="M72" s="76"/>
+        <v>341</v>
+      </c>
+      <c r="F72" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G72" s="82"/>
+      <c r="H72" s="82"/>
+      <c r="I72" s="82"/>
+      <c r="J72" s="82"/>
+      <c r="K72" s="82"/>
+      <c r="L72" s="82"/>
+      <c r="M72" s="83"/>
       <c r="O72" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C73" s="19" t="s">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E73" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F73" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G73" s="75"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="75"/>
-      <c r="J73" s="75"/>
-      <c r="K73" s="75"/>
-      <c r="L73" s="75"/>
-      <c r="M73" s="76"/>
+        <v>341</v>
+      </c>
+      <c r="F73" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G73" s="82"/>
+      <c r="H73" s="82"/>
+      <c r="I73" s="82"/>
+      <c r="J73" s="82"/>
+      <c r="K73" s="82"/>
+      <c r="L73" s="82"/>
+      <c r="M73" s="83"/>
       <c r="O73" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C74" s="19" t="s">
-        <v>382</v>
+        <v>335</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F74" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G74" s="75"/>
-      <c r="H74" s="75"/>
-      <c r="I74" s="75"/>
-      <c r="J74" s="75"/>
-      <c r="K74" s="75"/>
-      <c r="L74" s="75"/>
-      <c r="M74" s="76"/>
+        <v>341</v>
+      </c>
+      <c r="F74" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G74" s="82"/>
+      <c r="H74" s="82"/>
+      <c r="I74" s="82"/>
+      <c r="J74" s="82"/>
+      <c r="K74" s="82"/>
+      <c r="L74" s="82"/>
+      <c r="M74" s="83"/>
       <c r="O74" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C75" s="19" t="s">
-        <v>383</v>
+        <v>336</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F75" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G75" s="75"/>
-      <c r="H75" s="75"/>
-      <c r="I75" s="75"/>
-      <c r="J75" s="75"/>
-      <c r="K75" s="75"/>
-      <c r="L75" s="75"/>
-      <c r="M75" s="76"/>
+        <v>341</v>
+      </c>
+      <c r="F75" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G75" s="82"/>
+      <c r="H75" s="82"/>
+      <c r="I75" s="82"/>
+      <c r="J75" s="82"/>
+      <c r="K75" s="82"/>
+      <c r="L75" s="82"/>
+      <c r="M75" s="83"/>
       <c r="O75" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C76" s="19" t="s">
-        <v>384</v>
+        <v>337</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F76" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G76" s="75"/>
-      <c r="H76" s="75"/>
-      <c r="I76" s="75"/>
-      <c r="J76" s="75"/>
-      <c r="K76" s="75"/>
-      <c r="L76" s="75"/>
-      <c r="M76" s="76"/>
+        <v>341</v>
+      </c>
+      <c r="F76" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G76" s="82"/>
+      <c r="H76" s="82"/>
+      <c r="I76" s="82"/>
+      <c r="J76" s="82"/>
+      <c r="K76" s="82"/>
+      <c r="L76" s="82"/>
+      <c r="M76" s="83"/>
       <c r="O76" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C77" s="19" t="s">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F77" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G77" s="75"/>
-      <c r="H77" s="75"/>
-      <c r="I77" s="75"/>
-      <c r="J77" s="75"/>
-      <c r="K77" s="75"/>
-      <c r="L77" s="75"/>
-      <c r="M77" s="76"/>
+        <v>341</v>
+      </c>
+      <c r="F77" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G77" s="82"/>
+      <c r="H77" s="82"/>
+      <c r="I77" s="82"/>
+      <c r="J77" s="82"/>
+      <c r="K77" s="82"/>
+      <c r="L77" s="82"/>
+      <c r="M77" s="83"/>
       <c r="O77" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C78" s="19" t="s">
-        <v>386</v>
+        <v>339</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F78" s="74" t="s">
-        <v>389</v>
-      </c>
-      <c r="G78" s="75"/>
-      <c r="H78" s="75"/>
-      <c r="I78" s="75"/>
-      <c r="J78" s="75"/>
-      <c r="K78" s="75"/>
-      <c r="L78" s="75"/>
-      <c r="M78" s="76"/>
+        <v>341</v>
+      </c>
+      <c r="F78" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G78" s="82"/>
+      <c r="H78" s="82"/>
+      <c r="I78" s="82"/>
+      <c r="J78" s="82"/>
+      <c r="K78" s="82"/>
+      <c r="L78" s="82"/>
+      <c r="M78" s="83"/>
       <c r="O78" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C79" s="19" t="s">
-        <v>387</v>
+        <v>340</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="8"/>
@@ -7153,11 +7348,9 @@
     <mergeCell ref="F52:I52"/>
     <mergeCell ref="J52:M52"/>
     <mergeCell ref="F53:I53"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="J50:M50"/>
     <mergeCell ref="L68:M68"/>
     <mergeCell ref="F58:I58"/>
     <mergeCell ref="J58:M58"/>
@@ -7165,12 +7358,12 @@
     <mergeCell ref="L61:M61"/>
     <mergeCell ref="L62:M62"/>
     <mergeCell ref="L63:M63"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="L67:M67"/>
     <mergeCell ref="J54:M54"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="J50:M50"/>
     <mergeCell ref="F51:I51"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="J45:L45"/>
@@ -7185,6 +7378,8 @@
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="J43:L43"/>
     <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J47:L47"/>
     <mergeCell ref="F32:M32"/>
     <mergeCell ref="F23:I23"/>
     <mergeCell ref="J23:M23"/>
@@ -7211,7 +7406,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC57A460-A3F1-420B-B8CC-FFCC94C867CA}">
-  <dimension ref="B2:N54"/>
+  <dimension ref="B2:N63"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="5.875" customWidth="1"/>
@@ -7224,1029 +7419,1290 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.15">
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.15">
       <c r="C6" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>392</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>391</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="L10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="M10" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C11" s="60" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D11" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="F11" s="96"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="97"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="97"/>
-      <c r="L11" s="97"/>
-      <c r="M11" s="98"/>
+        <v>35</v>
+      </c>
+      <c r="E11" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="103"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="105"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="19" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
+        <v>119</v>
+      </c>
+      <c r="F12" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="74"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="F13" s="77" t="s">
-        <v>219</v>
-      </c>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="79"/>
+        <v>207</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="74"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E14" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="F14" s="77" t="s">
-        <v>220</v>
-      </c>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="79"/>
+        <v>208</v>
+      </c>
+      <c r="F14" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="74"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>356</v>
+        <v>309</v>
       </c>
       <c r="F15" s="45" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="H15" s="45" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="I15" s="55" t="s">
-        <v>357</v>
+        <v>310</v>
       </c>
       <c r="J15" s="55" t="s">
-        <v>358</v>
+        <v>311</v>
       </c>
       <c r="K15" s="44"/>
       <c r="L15" s="45" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="M15" s="45" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="60" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D16" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="63"/>
-      <c r="F16" s="99" t="s">
-        <v>226</v>
-      </c>
-      <c r="G16" s="100"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="100"/>
-      <c r="L16" s="100"/>
-      <c r="M16" s="101"/>
+        <v>35</v>
+      </c>
+      <c r="E16" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F16" s="106" t="s">
+        <v>214</v>
+      </c>
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="107"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="107"/>
+      <c r="M16" s="108"/>
       <c r="N16" s="57" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="60" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D17" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="63"/>
-      <c r="F17" s="99" t="s">
-        <v>227</v>
-      </c>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="100"/>
-      <c r="M17" s="101"/>
+        <v>35</v>
+      </c>
+      <c r="E17" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F17" s="106" t="s">
+        <v>215</v>
+      </c>
+      <c r="G17" s="107"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="107"/>
+      <c r="K17" s="107"/>
+      <c r="L17" s="107"/>
+      <c r="M17" s="108"/>
       <c r="N17" s="57" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="19" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E18" s="43"/>
       <c r="F18" s="55" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="G18" s="55" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="H18" s="55" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="I18" s="55" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="J18" s="56" t="s">
-        <v>232</v>
-      </c>
-      <c r="K18" s="96"/>
-      <c r="L18" s="98"/>
+        <v>220</v>
+      </c>
+      <c r="K18" s="103"/>
+      <c r="L18" s="105"/>
       <c r="M18" s="55" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="N18" s="58" t="s">
-        <v>355</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="19" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E19" s="43"/>
       <c r="F19" s="45" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="H19" s="96"/>
-      <c r="I19" s="98"/>
+        <v>223</v>
+      </c>
+      <c r="H19" s="103"/>
+      <c r="I19" s="105"/>
       <c r="J19" s="56" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="K19" s="56" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="L19" s="56" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="M19" s="56" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="19" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E20" s="43"/>
-      <c r="F20" s="102" t="s">
-        <v>240</v>
-      </c>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
-      <c r="L20" s="103"/>
-      <c r="M20" s="104"/>
+      <c r="F20" s="109" t="s">
+        <v>228</v>
+      </c>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="111"/>
       <c r="N20" t="s">
-        <v>347</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E21" s="42"/>
-      <c r="F21" s="102" t="s">
-        <v>241</v>
-      </c>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
-      <c r="L21" s="103"/>
-      <c r="M21" s="104"/>
+      <c r="F21" s="109" t="s">
+        <v>229</v>
+      </c>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="111"/>
       <c r="N21" t="s">
-        <v>348</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E22" s="42"/>
-      <c r="F22" s="102" t="s">
-        <v>242</v>
-      </c>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="103"/>
-      <c r="L22" s="103"/>
-      <c r="M22" s="104"/>
+      <c r="F22" s="109" t="s">
+        <v>230</v>
+      </c>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="110"/>
+      <c r="M22" s="111"/>
       <c r="N22" t="s">
-        <v>349</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E23" s="42"/>
-      <c r="F23" s="102" t="s">
-        <v>243</v>
-      </c>
-      <c r="G23" s="103"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="103"/>
-      <c r="J23" s="103"/>
-      <c r="K23" s="103"/>
-      <c r="L23" s="103"/>
-      <c r="M23" s="104"/>
+      <c r="F23" s="109" t="s">
+        <v>231</v>
+      </c>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="110"/>
+      <c r="M23" s="111"/>
       <c r="N23" t="s">
-        <v>350</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="60" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D24" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="99" t="s">
-        <v>244</v>
-      </c>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="101"/>
+        <v>35</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F24" s="106" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" s="107"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="107"/>
+      <c r="K24" s="107"/>
+      <c r="L24" s="107"/>
+      <c r="M24" s="108"/>
       <c r="N24" s="59" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="60" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D25" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="96"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="99" t="s">
-        <v>245</v>
-      </c>
-      <c r="L25" s="100"/>
-      <c r="M25" s="101"/>
+        <v>35</v>
+      </c>
+      <c r="E25" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F25" s="103"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="106" t="s">
+        <v>233</v>
+      </c>
+      <c r="L25" s="107"/>
+      <c r="M25" s="108"/>
       <c r="N25" s="57" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D26" s="65" t="s">
-        <v>35</v>
+        <v>131</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>30</v>
       </c>
       <c r="E26" s="42"/>
-      <c r="F26" s="102" t="s">
-        <v>246</v>
-      </c>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="105"/>
-      <c r="M26" s="106"/>
+      <c r="F26" s="109" t="s">
+        <v>234</v>
+      </c>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="113"/>
       <c r="N26" t="s">
-        <v>359</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="19" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E27" s="42"/>
-      <c r="F27" s="102" t="s">
-        <v>247</v>
-      </c>
-      <c r="G27" s="103"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="103"/>
-      <c r="L27" s="103"/>
-      <c r="M27" s="104"/>
+      <c r="F27" s="109" t="s">
+        <v>235</v>
+      </c>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="110"/>
+      <c r="L27" s="110"/>
+      <c r="M27" s="111"/>
       <c r="N27" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E28" s="42"/>
-      <c r="F28" s="102" t="s">
-        <v>248</v>
-      </c>
-      <c r="G28" s="103"/>
-      <c r="H28" s="103"/>
-      <c r="I28" s="103"/>
-      <c r="J28" s="103"/>
-      <c r="K28" s="103"/>
-      <c r="L28" s="103"/>
-      <c r="M28" s="104"/>
+      <c r="F28" s="109" t="s">
+        <v>236</v>
+      </c>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="110"/>
+      <c r="L28" s="110"/>
+      <c r="M28" s="111"/>
       <c r="N28" t="s">
-        <v>352</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="19" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E29" s="42"/>
-      <c r="F29" s="102" t="s">
-        <v>249</v>
-      </c>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="103"/>
-      <c r="J29" s="103"/>
-      <c r="K29" s="103"/>
-      <c r="L29" s="103"/>
-      <c r="M29" s="104"/>
+      <c r="F29" s="109" t="s">
+        <v>237</v>
+      </c>
+      <c r="G29" s="110"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="110"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="110"/>
+      <c r="L29" s="110"/>
+      <c r="M29" s="111"/>
       <c r="N29" t="s">
-        <v>353</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="60" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D30" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="62"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="97"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="97"/>
-      <c r="J30" s="97"/>
-      <c r="K30" s="97"/>
-      <c r="L30" s="97"/>
-      <c r="M30" s="98"/>
+        <v>35</v>
+      </c>
+      <c r="E30" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F30" s="103"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="105"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="60" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D31" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E31" s="62"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="97"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="97"/>
-      <c r="K31" s="97"/>
-      <c r="L31" s="97"/>
-      <c r="M31" s="98"/>
+        <v>35</v>
+      </c>
+      <c r="E31" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F31" s="103"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="105"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="60" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D32" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="62"/>
-      <c r="F32" s="99" t="s">
-        <v>250</v>
-      </c>
-      <c r="G32" s="100"/>
-      <c r="H32" s="100"/>
-      <c r="I32" s="100"/>
-      <c r="J32" s="100"/>
-      <c r="K32" s="100"/>
-      <c r="L32" s="100"/>
-      <c r="M32" s="101"/>
+        <v>35</v>
+      </c>
+      <c r="E32" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F32" s="106" t="s">
+        <v>238</v>
+      </c>
+      <c r="G32" s="107"/>
+      <c r="H32" s="107"/>
+      <c r="I32" s="107"/>
+      <c r="J32" s="107"/>
+      <c r="K32" s="107"/>
+      <c r="L32" s="107"/>
+      <c r="M32" s="108"/>
       <c r="N32" s="57" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="60" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D33" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="63"/>
-      <c r="F33" s="99" t="s">
-        <v>251</v>
-      </c>
-      <c r="G33" s="101"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="97"/>
-      <c r="J33" s="97"/>
-      <c r="K33" s="97"/>
-      <c r="L33" s="97"/>
-      <c r="M33" s="98"/>
+        <v>35</v>
+      </c>
+      <c r="E33" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F33" s="106" t="s">
+        <v>239</v>
+      </c>
+      <c r="G33" s="108"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="104"/>
+      <c r="M33" s="105"/>
       <c r="N33" s="57" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="60" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D34" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="63"/>
-      <c r="F34" s="96"/>
-      <c r="G34" s="97"/>
-      <c r="H34" s="97"/>
-      <c r="I34" s="97"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="99" t="s">
-        <v>252</v>
-      </c>
-      <c r="L34" s="100"/>
-      <c r="M34" s="101"/>
+        <v>35</v>
+      </c>
+      <c r="E34" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F34" s="103"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="106" t="s">
+        <v>240</v>
+      </c>
+      <c r="L34" s="107"/>
+      <c r="M34" s="108"/>
       <c r="N34" s="57" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="60" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D35" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" s="62"/>
-      <c r="F35" s="96"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="99" t="s">
-        <v>253</v>
-      </c>
-      <c r="K35" s="100"/>
-      <c r="L35" s="100"/>
-      <c r="M35" s="101"/>
+        <v>35</v>
+      </c>
+      <c r="E35" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F35" s="103"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="104"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="106" t="s">
+        <v>241</v>
+      </c>
+      <c r="K35" s="107"/>
+      <c r="L35" s="107"/>
+      <c r="M35" s="108"/>
       <c r="N35" s="57" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="36" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="60" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D36" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="62"/>
-      <c r="F36" s="96"/>
-      <c r="G36" s="97"/>
-      <c r="H36" s="97"/>
-      <c r="I36" s="98"/>
-      <c r="J36" s="99" t="s">
-        <v>254</v>
-      </c>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="101"/>
+        <v>30</v>
+      </c>
+      <c r="E36" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F36" s="103"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="104"/>
+      <c r="I36" s="105"/>
+      <c r="J36" s="106" t="s">
+        <v>242</v>
+      </c>
+      <c r="K36" s="107"/>
+      <c r="L36" s="107"/>
+      <c r="M36" s="108"/>
       <c r="N36" s="57" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="60" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D37" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="62"/>
-      <c r="F37" s="99" t="s">
-        <v>255</v>
-      </c>
-      <c r="G37" s="100"/>
-      <c r="H37" s="100"/>
-      <c r="I37" s="100"/>
-      <c r="J37" s="100"/>
-      <c r="K37" s="100"/>
-      <c r="L37" s="100"/>
-      <c r="M37" s="101"/>
+        <v>30</v>
+      </c>
+      <c r="E37" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F37" s="106" t="s">
+        <v>243</v>
+      </c>
+      <c r="G37" s="107"/>
+      <c r="H37" s="107"/>
+      <c r="I37" s="107"/>
+      <c r="J37" s="107"/>
+      <c r="K37" s="107"/>
+      <c r="L37" s="107"/>
+      <c r="M37" s="108"/>
       <c r="N37" s="57" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="60" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D38" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E38" s="62"/>
-      <c r="F38" s="96"/>
-      <c r="G38" s="97"/>
-      <c r="H38" s="97"/>
-      <c r="I38" s="97"/>
-      <c r="J38" s="97"/>
-      <c r="K38" s="97"/>
-      <c r="L38" s="97"/>
-      <c r="M38" s="98"/>
+        <v>35</v>
+      </c>
+      <c r="E38" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F38" s="103"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="104"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="104"/>
+      <c r="K38" s="104"/>
+      <c r="L38" s="104"/>
+      <c r="M38" s="105"/>
     </row>
     <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="60" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D39" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39" s="62"/>
-      <c r="F39" s="96"/>
-      <c r="G39" s="97"/>
-      <c r="H39" s="97"/>
-      <c r="I39" s="97"/>
-      <c r="J39" s="97"/>
-      <c r="K39" s="97"/>
-      <c r="L39" s="97"/>
-      <c r="M39" s="98"/>
+        <v>35</v>
+      </c>
+      <c r="E39" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F39" s="103"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="104"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="104"/>
+      <c r="L39" s="104"/>
+      <c r="M39" s="105"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="60" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D40" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E40" s="62"/>
-      <c r="F40" s="96"/>
-      <c r="G40" s="97"/>
-      <c r="H40" s="97"/>
-      <c r="I40" s="97"/>
-      <c r="J40" s="97"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="97"/>
-      <c r="M40" s="98"/>
+        <v>35</v>
+      </c>
+      <c r="E40" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F40" s="103"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="104"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="104"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="104"/>
+      <c r="M40" s="105"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="60" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D41" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E41" s="62"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="97"/>
-      <c r="H41" s="97"/>
-      <c r="I41" s="97"/>
-      <c r="J41" s="97"/>
-      <c r="K41" s="97"/>
-      <c r="L41" s="97"/>
-      <c r="M41" s="98"/>
+        <v>35</v>
+      </c>
+      <c r="E41" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" s="103"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="104"/>
+      <c r="I41" s="104"/>
+      <c r="J41" s="104"/>
+      <c r="K41" s="104"/>
+      <c r="L41" s="104"/>
+      <c r="M41" s="105"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="60" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D42" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E42" s="62"/>
-      <c r="F42" s="96"/>
-      <c r="G42" s="97"/>
-      <c r="H42" s="97"/>
-      <c r="I42" s="97"/>
-      <c r="J42" s="97"/>
-      <c r="K42" s="97"/>
-      <c r="L42" s="97"/>
-      <c r="M42" s="98"/>
+        <v>35</v>
+      </c>
+      <c r="E42" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" s="103"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="104"/>
+      <c r="M42" s="105"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="20" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E43" s="43"/>
       <c r="F43" s="45" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G43" s="45" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H43" s="45" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="I43" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="J43" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="K43" s="78"/>
-      <c r="L43" s="78"/>
-      <c r="M43" s="79"/>
+        <v>108</v>
+      </c>
+      <c r="J43" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="K43" s="73"/>
+      <c r="L43" s="73"/>
+      <c r="M43" s="74"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E44" s="43"/>
-      <c r="F44" s="77" t="s">
-        <v>265</v>
-      </c>
-      <c r="G44" s="79"/>
-      <c r="H44" s="77" t="s">
-        <v>118</v>
-      </c>
-      <c r="I44" s="78"/>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="L44" s="78"/>
-      <c r="M44" s="79"/>
+      <c r="F44" s="72" t="s">
+        <v>252</v>
+      </c>
+      <c r="G44" s="74"/>
+      <c r="H44" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="I44" s="73"/>
+      <c r="J44" s="73"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="73"/>
+      <c r="M44" s="74"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="19" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E45" s="43"/>
-      <c r="F45" s="107" t="s">
-        <v>122</v>
-      </c>
-      <c r="G45" s="108"/>
-      <c r="H45" s="108"/>
-      <c r="I45" s="109"/>
-      <c r="J45" s="77" t="s">
-        <v>123</v>
-      </c>
-      <c r="K45" s="78"/>
-      <c r="L45" s="78"/>
-      <c r="M45" s="79"/>
+      <c r="F45" s="114" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" s="115"/>
+      <c r="H45" s="115"/>
+      <c r="I45" s="116"/>
+      <c r="J45" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="K45" s="73"/>
+      <c r="L45" s="73"/>
+      <c r="M45" s="74"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="19" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E46" s="6"/>
-      <c r="F46" s="77" t="s">
-        <v>124</v>
-      </c>
-      <c r="G46" s="78"/>
-      <c r="H46" s="78"/>
-      <c r="I46" s="79"/>
-      <c r="J46" s="110" t="s">
-        <v>125</v>
-      </c>
-      <c r="K46" s="111"/>
-      <c r="L46" s="111"/>
-      <c r="M46" s="112"/>
+      <c r="F46" s="72" t="s">
+        <v>117</v>
+      </c>
+      <c r="G46" s="73"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="74"/>
+      <c r="J46" s="117" t="s">
+        <v>118</v>
+      </c>
+      <c r="K46" s="118"/>
+      <c r="L46" s="118"/>
+      <c r="M46" s="119"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="19" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E47" s="6"/>
-      <c r="F47" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="G47" s="94"/>
-      <c r="H47" s="94"/>
-      <c r="I47" s="94"/>
-      <c r="J47" s="94"/>
-      <c r="K47" s="94"/>
-      <c r="L47" s="94"/>
-      <c r="M47" s="95"/>
+      <c r="F47" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" s="89"/>
+      <c r="H47" s="89"/>
+      <c r="I47" s="89"/>
+      <c r="J47" s="89"/>
+      <c r="K47" s="89"/>
+      <c r="L47" s="89"/>
+      <c r="M47" s="90"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="19" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="86"/>
-      <c r="G48" s="88"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="86"/>
       <c r="H48" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="I48" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="J48" s="94"/>
-      <c r="K48" s="95"/>
-      <c r="L48" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="M48" s="95"/>
-    </row>
-    <row r="49" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+      <c r="I48" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="J48" s="89"/>
+      <c r="K48" s="90"/>
+      <c r="L48" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="M48" s="90"/>
+    </row>
+    <row r="49" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="19" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="11" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="M49" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="19" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="86"/>
-      <c r="G50" s="87"/>
-      <c r="H50" s="87"/>
-      <c r="I50" s="88"/>
-      <c r="J50" s="93" t="s">
-        <v>119</v>
-      </c>
-      <c r="K50" s="94"/>
-      <c r="L50" s="95"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="85"/>
+      <c r="H50" s="85"/>
+      <c r="I50" s="86"/>
+      <c r="J50" s="88" t="s">
+        <v>112</v>
+      </c>
+      <c r="K50" s="89"/>
+      <c r="L50" s="90"/>
       <c r="M50" s="13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F51" s="96"/>
-      <c r="G51" s="97"/>
-      <c r="H51" s="97"/>
-      <c r="I51" s="97"/>
-      <c r="J51" s="97"/>
-      <c r="K51" s="98"/>
-      <c r="L51" s="92" t="s">
-        <v>274</v>
-      </c>
-      <c r="M51" s="90"/>
-    </row>
-    <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C52" s="60" t="s">
-        <v>263</v>
-      </c>
-      <c r="D52" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="E52" s="64"/>
-      <c r="F52" s="96"/>
-      <c r="G52" s="97"/>
-      <c r="H52" s="97"/>
-      <c r="I52" s="97"/>
-      <c r="J52" s="97"/>
-      <c r="K52" s="97"/>
-      <c r="L52" s="97"/>
-      <c r="M52" s="98"/>
-    </row>
-    <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="53" t="s">
-        <v>340</v>
-      </c>
-      <c r="D54" t="s">
-        <v>39</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="G54" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="F51" s="103"/>
+      <c r="G51" s="104"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="104"/>
+      <c r="K51" s="105"/>
+      <c r="L51" s="78" t="s">
+        <v>257</v>
+      </c>
+      <c r="M51" s="80"/>
+    </row>
+    <row r="52" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="F52" s="78" t="s">
         <v>342</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="G52" s="79"/>
+      <c r="H52" s="79"/>
+      <c r="I52" s="79"/>
+      <c r="J52" s="79"/>
+      <c r="K52" s="79"/>
+      <c r="L52" s="79"/>
+      <c r="M52" s="80"/>
+      <c r="N52" t="s">
         <v>343</v>
       </c>
-      <c r="I54" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="J54" s="54" t="s">
-        <v>346</v>
-      </c>
-      <c r="K54" s="86"/>
-      <c r="L54" s="88"/>
-      <c r="M54" s="54" t="s">
-        <v>345</v>
+    </row>
+    <row r="53" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C53" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="F53" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="G53" s="79"/>
+      <c r="H53" s="79"/>
+      <c r="I53" s="79"/>
+      <c r="J53" s="79"/>
+      <c r="K53" s="79"/>
+      <c r="L53" s="79"/>
+      <c r="M53" s="80"/>
+      <c r="N53" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C54" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="F54" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="G54" s="79"/>
+      <c r="H54" s="79"/>
+      <c r="I54" s="79"/>
+      <c r="J54" s="79"/>
+      <c r="K54" s="79"/>
+      <c r="L54" s="79"/>
+      <c r="M54" s="80"/>
+      <c r="N54" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C55" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="F55" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="G55" s="79"/>
+      <c r="H55" s="79"/>
+      <c r="I55" s="79"/>
+      <c r="J55" s="79"/>
+      <c r="K55" s="79"/>
+      <c r="L55" s="79"/>
+      <c r="M55" s="80"/>
+      <c r="N55" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="56" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C56" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="F56" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="G56" s="79"/>
+      <c r="H56" s="79"/>
+      <c r="I56" s="79"/>
+      <c r="J56" s="79"/>
+      <c r="K56" s="79"/>
+      <c r="L56" s="79"/>
+      <c r="M56" s="80"/>
+      <c r="N56" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="57" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C57" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="F57" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="G57" s="79"/>
+      <c r="H57" s="79"/>
+      <c r="I57" s="79"/>
+      <c r="J57" s="79"/>
+      <c r="K57" s="79"/>
+      <c r="L57" s="79"/>
+      <c r="M57" s="80"/>
+      <c r="N57" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C58" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="F58" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="G58" s="79"/>
+      <c r="H58" s="79"/>
+      <c r="I58" s="79"/>
+      <c r="J58" s="79"/>
+      <c r="K58" s="79"/>
+      <c r="L58" s="79"/>
+      <c r="M58" s="80"/>
+      <c r="N58" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="F59" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="G59" s="79"/>
+      <c r="H59" s="79"/>
+      <c r="I59" s="79"/>
+      <c r="J59" s="79"/>
+      <c r="K59" s="79"/>
+      <c r="L59" s="79"/>
+      <c r="M59" s="80"/>
+      <c r="N59" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C60" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="F60" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="G60" s="79"/>
+      <c r="H60" s="79"/>
+      <c r="I60" s="79"/>
+      <c r="J60" s="79"/>
+      <c r="K60" s="79"/>
+      <c r="L60" s="79"/>
+      <c r="M60" s="80"/>
+      <c r="N60" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C61" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D61" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F61" s="103"/>
+      <c r="G61" s="104"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="104"/>
+      <c r="K61" s="104"/>
+      <c r="L61" s="104"/>
+      <c r="M61" s="105"/>
+    </row>
+    <row r="62" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="53" t="s">
+        <v>293</v>
+      </c>
+      <c r="D63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="J63" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="K63" s="84"/>
+      <c r="L63" s="86"/>
+      <c r="M63" s="54" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="62">
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F59:M59"/>
+    <mergeCell ref="F60:M60"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F55:M55"/>
+    <mergeCell ref="F56:M56"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="F45:I45"/>
     <mergeCell ref="J45:M45"/>
@@ -8284,10 +8740,10 @@
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="F34:J34"/>
     <mergeCell ref="F21:M21"/>
-    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="K63:L63"/>
     <mergeCell ref="F11:M11"/>
     <mergeCell ref="F13:M13"/>
-    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F61:M61"/>
     <mergeCell ref="L51:M51"/>
     <mergeCell ref="F51:K51"/>
     <mergeCell ref="J50:L50"/>
@@ -8314,7 +8770,23 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>375</v>
+        <v>328</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C089955-300F-45E5-8F89-CCBFB5CCF548}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5025254D-6185-4190-A23A-0DBCCFDC518E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6B71DE-697D-4C18-AEEB-DB905B203FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="417">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -2149,6 +2149,14 @@
   </si>
   <si>
     <t>モジュール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FFCh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCC Volume</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2660,7 +2668,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2877,6 +2885,24 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2886,6 +2912,39 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2895,52 +2954,28 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2952,22 +2987,22 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3003,22 +3038,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3974,7 +3994,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F17AAC-1091-414B-9A6F-EA5ABE92574A}">
-  <dimension ref="B2:O24"/>
+  <dimension ref="B2:O25"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -4045,13 +4065,13 @@
       <c r="F4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="86"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="77"/>
       <c r="N4" s="67" t="s">
         <v>278</v>
       </c>
@@ -4072,16 +4092,16 @@
       <c r="F5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="75" t="s">
+      <c r="G5" s="92" t="s">
         <v>279</v>
       </c>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="77"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="94"/>
       <c r="O5" s="50" t="s">
         <v>282</v>
       </c>
@@ -4099,16 +4119,16 @@
       <c r="F6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="75" t="s">
+      <c r="G6" s="92" t="s">
         <v>279</v>
       </c>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="77"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="94"/>
       <c r="O6" s="50" t="s">
         <v>282</v>
       </c>
@@ -4126,16 +4146,16 @@
       <c r="F7" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="75" t="s">
+      <c r="G7" s="92" t="s">
         <v>279</v>
       </c>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="76"/>
-      <c r="N7" s="77"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="94"/>
       <c r="O7" s="50" t="s">
         <v>282</v>
       </c>
@@ -4153,16 +4173,16 @@
       <c r="F8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="75" t="s">
+      <c r="G8" s="92" t="s">
         <v>279</v>
       </c>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="76"/>
-      <c r="N8" s="77"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="94"/>
       <c r="O8" s="50" t="s">
         <v>282</v>
       </c>
@@ -4180,16 +4200,16 @@
       <c r="F9" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="78" t="s">
         <v>280</v>
       </c>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="73"/>
-      <c r="M9" s="73"/>
-      <c r="N9" s="74"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="79"/>
+      <c r="M9" s="79"/>
+      <c r="N9" s="80"/>
       <c r="O9" s="50" t="s">
         <v>283</v>
       </c>
@@ -4207,16 +4227,16 @@
       <c r="F10" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="78" t="s">
         <v>280</v>
       </c>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="73"/>
-      <c r="L10" s="73"/>
-      <c r="M10" s="73"/>
-      <c r="N10" s="74"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="80"/>
       <c r="O10" s="50" t="s">
         <v>283</v>
       </c>
@@ -4234,16 +4254,16 @@
       <c r="F11" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G11" s="78" t="s">
+      <c r="G11" s="82" t="s">
         <v>262</v>
       </c>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="80"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="84"/>
       <c r="O11" s="51" t="s">
         <v>284</v>
       </c>
@@ -4261,16 +4281,16 @@
       <c r="F12" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G12" s="78" t="s">
+      <c r="G12" s="82" t="s">
         <v>263</v>
       </c>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="80"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="84"/>
       <c r="O12" s="51" t="s">
         <v>285</v>
       </c>
@@ -4288,16 +4308,16 @@
       <c r="F13" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G13" s="81" t="s">
+      <c r="G13" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="79"/>
-      <c r="N13" s="80"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="84"/>
       <c r="O13" s="51" t="s">
         <v>286</v>
       </c>
@@ -4315,16 +4335,16 @@
       <c r="F14" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="85" t="s">
         <v>412</v>
       </c>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="80"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="83"/>
+      <c r="N14" s="84"/>
       <c r="O14" s="51" t="s">
         <v>287</v>
       </c>
@@ -4342,16 +4362,16 @@
       <c r="F15" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G15" s="88" t="s">
+      <c r="G15" s="86" t="s">
         <v>374</v>
       </c>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="89"/>
-      <c r="N15" s="90"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="87"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="87"/>
+      <c r="N15" s="88"/>
       <c r="O15" s="51" t="s">
         <v>288</v>
       </c>
@@ -4369,16 +4389,16 @@
       <c r="F16" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G16" s="88" t="s">
+      <c r="G16" s="86" t="s">
         <v>411</v>
       </c>
-      <c r="H16" s="89"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="89"/>
-      <c r="K16" s="89"/>
-      <c r="L16" s="89"/>
-      <c r="M16" s="89"/>
-      <c r="N16" s="90"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="87"/>
+      <c r="N16" s="88"/>
       <c r="O16" s="51" t="s">
         <v>289</v>
       </c>
@@ -4396,13 +4416,13 @@
       <c r="F17" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G17" s="91"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="93"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="91"/>
       <c r="N17" s="11" t="s">
         <v>5</v>
       </c>
@@ -4426,11 +4446,11 @@
       <c r="G18" s="25" t="s">
         <v>313</v>
       </c>
-      <c r="H18" s="84"/>
-      <c r="I18" s="85"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="86"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="77"/>
       <c r="M18" s="33" t="s">
         <v>3</v>
       </c>
@@ -4454,14 +4474,14 @@
       <c r="F19" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G19" s="81"/>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="83"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="95"/>
+      <c r="L19" s="95"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="96"/>
       <c r="O19" s="51" t="s">
         <v>413</v>
       </c>
@@ -4479,14 +4499,14 @@
       <c r="F20" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G20" s="81"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="82"/>
-      <c r="K20" s="82"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="83"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="96"/>
       <c r="O20" s="51" t="s">
         <v>413</v>
       </c>
@@ -4504,14 +4524,14 @@
       <c r="F21" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G21" s="81"/>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="82"/>
-      <c r="N21" s="83"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="95"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="95"/>
+      <c r="K21" s="95"/>
+      <c r="L21" s="95"/>
+      <c r="M21" s="95"/>
+      <c r="N21" s="96"/>
       <c r="O21" s="51" t="s">
         <v>413</v>
       </c>
@@ -4529,86 +4549,100 @@
       <c r="F22" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G22" s="81"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="83"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="95"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="95"/>
+      <c r="K22" s="95"/>
+      <c r="L22" s="95"/>
+      <c r="M22" s="95"/>
+      <c r="N22" s="96"/>
       <c r="O22" s="51" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="23" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="64" t="s">
-        <v>314</v>
+      <c r="C23" s="12" t="s">
+        <v>415</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>270</v>
+        <v>416</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="72" t="s">
-        <v>280</v>
-      </c>
-      <c r="H23" s="87"/>
+        <v>317</v>
+      </c>
+      <c r="G23" s="72"/>
+      <c r="H23" s="123"/>
       <c r="I23" s="73"/>
       <c r="J23" s="73"/>
       <c r="K23" s="73"/>
       <c r="L23" s="73"/>
       <c r="M23" s="73"/>
       <c r="N23" s="74"/>
-      <c r="O23" s="50" t="s">
-        <v>283</v>
+      <c r="O23" s="51" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C24" s="66" t="s">
-        <v>315</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" s="64" t="s">
+        <v>314</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="72" t="s">
+      <c r="G24" s="78" t="s">
         <v>280</v>
       </c>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="73"/>
-      <c r="K24" s="73"/>
-      <c r="L24" s="73"/>
-      <c r="M24" s="73"/>
-      <c r="N24" s="74"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="80"/>
       <c r="O24" s="50" t="s">
         <v>283</v>
       </c>
     </row>
+    <row r="25" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="66" t="s">
+        <v>315</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="78" t="s">
+        <v>280</v>
+      </c>
+      <c r="H25" s="79"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="79"/>
+      <c r="L25" s="79"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="50" t="s">
+        <v>283</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="G4:M4"/>
-    <mergeCell ref="G9:N9"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="G23:N23"/>
-    <mergeCell ref="G11:N11"/>
-    <mergeCell ref="G13:N13"/>
-    <mergeCell ref="G14:N14"/>
-    <mergeCell ref="G15:N15"/>
-    <mergeCell ref="G16:N16"/>
-    <mergeCell ref="G17:M17"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="G24:N24"/>
+    <mergeCell ref="G25:N25"/>
     <mergeCell ref="G5:N5"/>
     <mergeCell ref="G6:N6"/>
     <mergeCell ref="G7:N7"/>
@@ -4618,6 +4652,17 @@
     <mergeCell ref="G20:N20"/>
     <mergeCell ref="G21:N21"/>
     <mergeCell ref="G22:N22"/>
+    <mergeCell ref="G4:M4"/>
+    <mergeCell ref="G9:N9"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="G24:N24"/>
+    <mergeCell ref="G11:N11"/>
+    <mergeCell ref="G13:N13"/>
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="G15:N15"/>
+    <mergeCell ref="G16:N16"/>
+    <mergeCell ref="G17:M17"/>
+    <mergeCell ref="H18:L18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4737,16 +4782,16 @@
       <c r="E12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="94" t="s">
+      <c r="F12" s="103" t="s">
         <v>182</v>
       </c>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="95"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="95"/>
-      <c r="M12" s="96"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="105"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
@@ -4762,12 +4807,12 @@
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="94" t="s">
+      <c r="J13" s="103" t="s">
         <v>183</v>
       </c>
-      <c r="K13" s="95"/>
-      <c r="L13" s="95"/>
-      <c r="M13" s="96"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="105"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
@@ -4779,16 +4824,16 @@
       <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="94" t="s">
+      <c r="F14" s="103" t="s">
         <v>182</v>
       </c>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="95"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="96"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="105"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
@@ -4804,12 +4849,12 @@
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="36"/>
-      <c r="J15" s="94" t="s">
+      <c r="J15" s="103" t="s">
         <v>183</v>
       </c>
-      <c r="K15" s="95"/>
-      <c r="L15" s="95"/>
-      <c r="M15" s="96"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="105"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="19" t="s">
@@ -4821,16 +4866,16 @@
       <c r="E16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="94" t="s">
+      <c r="F16" s="103" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="96"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="105"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="19" t="s">
@@ -4846,12 +4891,12 @@
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
-      <c r="J17" s="94" t="s">
+      <c r="J17" s="103" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="95"/>
-      <c r="L17" s="95"/>
-      <c r="M17" s="96"/>
+      <c r="K17" s="104"/>
+      <c r="L17" s="104"/>
+      <c r="M17" s="105"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="19" t="s">
@@ -4866,13 +4911,13 @@
       <c r="F18" s="34"/>
       <c r="G18" s="35"/>
       <c r="H18" s="36"/>
-      <c r="I18" s="94" t="s">
+      <c r="I18" s="103" t="s">
         <v>184</v>
       </c>
-      <c r="J18" s="95"/>
-      <c r="K18" s="95"/>
-      <c r="L18" s="95"/>
-      <c r="M18" s="96"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="105"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="19" t="s">
@@ -4925,12 +4970,12 @@
       <c r="I20" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="94" t="s">
+      <c r="J20" s="103" t="s">
         <v>185</v>
       </c>
-      <c r="K20" s="95"/>
-      <c r="L20" s="95"/>
-      <c r="M20" s="96"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="105"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
@@ -4948,12 +4993,12 @@
       <c r="I21" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="94" t="s">
+      <c r="J21" s="103" t="s">
         <v>185</v>
       </c>
-      <c r="K21" s="95"/>
-      <c r="L21" s="95"/>
-      <c r="M21" s="96"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="105"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
@@ -4971,12 +5016,12 @@
       <c r="I22" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="94" t="s">
+      <c r="J22" s="103" t="s">
         <v>185</v>
       </c>
-      <c r="K22" s="95"/>
-      <c r="L22" s="95"/>
-      <c r="M22" s="96"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="105"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
@@ -4988,16 +5033,16 @@
       <c r="E23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F23" s="94" t="s">
+      <c r="F23" s="103" t="s">
         <v>186</v>
       </c>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="95"/>
-      <c r="M23" s="96"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="105"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
@@ -5009,16 +5054,16 @@
       <c r="E24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="94" t="s">
+      <c r="F24" s="103" t="s">
         <v>187</v>
       </c>
-      <c r="G24" s="95"/>
-      <c r="H24" s="95"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="95"/>
-      <c r="K24" s="95"/>
-      <c r="L24" s="95"/>
-      <c r="M24" s="96"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="105"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
@@ -5034,12 +5079,12 @@
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
       <c r="I25" s="36"/>
-      <c r="J25" s="94" t="s">
+      <c r="J25" s="103" t="s">
         <v>188</v>
       </c>
-      <c r="K25" s="95"/>
-      <c r="L25" s="95"/>
-      <c r="M25" s="96"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="105"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
@@ -5089,16 +5134,16 @@
       <c r="E28" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="81" t="s">
+      <c r="F28" s="85" t="s">
         <v>182</v>
       </c>
-      <c r="G28" s="82"/>
-      <c r="H28" s="82"/>
-      <c r="I28" s="82"/>
-      <c r="J28" s="82"/>
-      <c r="K28" s="82"/>
-      <c r="L28" s="82"/>
-      <c r="M28" s="83"/>
+      <c r="G28" s="95"/>
+      <c r="H28" s="95"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="95"/>
+      <c r="M28" s="96"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="19" t="s">
@@ -5114,12 +5159,12 @@
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="I29" s="28"/>
-      <c r="J29" s="81" t="s">
+      <c r="J29" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="K29" s="82"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="83"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="96"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
@@ -5131,16 +5176,16 @@
       <c r="E30" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="81" t="s">
+      <c r="F30" s="85" t="s">
         <v>182</v>
       </c>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
-      <c r="I30" s="82"/>
-      <c r="J30" s="82"/>
-      <c r="K30" s="82"/>
-      <c r="L30" s="82"/>
-      <c r="M30" s="83"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="96"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
@@ -5156,12 +5201,12 @@
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="I31" s="28"/>
-      <c r="J31" s="81" t="s">
+      <c r="J31" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="K31" s="82"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="83"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="96"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
@@ -5173,16 +5218,16 @@
       <c r="E32" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="81" t="s">
+      <c r="F32" s="85" t="s">
         <v>182</v>
       </c>
-      <c r="G32" s="82"/>
-      <c r="H32" s="82"/>
-      <c r="I32" s="82"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="83"/>
+      <c r="G32" s="95"/>
+      <c r="H32" s="95"/>
+      <c r="I32" s="95"/>
+      <c r="J32" s="95"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="96"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
@@ -5198,12 +5243,12 @@
       <c r="G33" s="27"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
-      <c r="J33" s="81" t="s">
+      <c r="J33" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="83"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="96"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
@@ -5218,13 +5263,13 @@
       <c r="F34" s="26"/>
       <c r="G34" s="27"/>
       <c r="H34" s="28"/>
-      <c r="I34" s="81" t="s">
+      <c r="I34" s="85" t="s">
         <v>184</v>
       </c>
-      <c r="J34" s="82"/>
-      <c r="K34" s="82"/>
-      <c r="L34" s="82"/>
-      <c r="M34" s="83"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="96"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
@@ -5277,12 +5322,12 @@
       <c r="I36" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J36" s="81" t="s">
+      <c r="J36" s="85" t="s">
         <v>185</v>
       </c>
-      <c r="K36" s="82"/>
-      <c r="L36" s="82"/>
-      <c r="M36" s="83"/>
+      <c r="K36" s="95"/>
+      <c r="L36" s="95"/>
+      <c r="M36" s="96"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
@@ -5300,12 +5345,12 @@
       <c r="I37" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J37" s="81" t="s">
+      <c r="J37" s="85" t="s">
         <v>185</v>
       </c>
-      <c r="K37" s="82"/>
-      <c r="L37" s="82"/>
-      <c r="M37" s="83"/>
+      <c r="K37" s="95"/>
+      <c r="L37" s="95"/>
+      <c r="M37" s="96"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
@@ -5323,12 +5368,12 @@
       <c r="I38" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J38" s="81" t="s">
+      <c r="J38" s="85" t="s">
         <v>185</v>
       </c>
-      <c r="K38" s="82"/>
-      <c r="L38" s="82"/>
-      <c r="M38" s="83"/>
+      <c r="K38" s="95"/>
+      <c r="L38" s="95"/>
+      <c r="M38" s="96"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
@@ -5340,16 +5385,16 @@
       <c r="E39" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F39" s="81" t="s">
+      <c r="F39" s="85" t="s">
         <v>186</v>
       </c>
-      <c r="G39" s="82"/>
-      <c r="H39" s="82"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="82"/>
-      <c r="K39" s="82"/>
-      <c r="L39" s="82"/>
-      <c r="M39" s="83"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="95"/>
+      <c r="J39" s="95"/>
+      <c r="K39" s="95"/>
+      <c r="L39" s="95"/>
+      <c r="M39" s="96"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="19" t="s">
@@ -5361,16 +5406,16 @@
       <c r="E40" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F40" s="81" t="s">
+      <c r="F40" s="85" t="s">
         <v>187</v>
       </c>
-      <c r="G40" s="82"/>
-      <c r="H40" s="82"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="82"/>
-      <c r="K40" s="82"/>
-      <c r="L40" s="82"/>
-      <c r="M40" s="83"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="95"/>
+      <c r="J40" s="95"/>
+      <c r="K40" s="95"/>
+      <c r="L40" s="95"/>
+      <c r="M40" s="96"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="19" t="s">
@@ -5386,12 +5431,12 @@
       <c r="G41" s="27"/>
       <c r="H41" s="27"/>
       <c r="I41" s="28"/>
-      <c r="J41" s="81" t="s">
+      <c r="J41" s="85" t="s">
         <v>188</v>
       </c>
-      <c r="K41" s="82"/>
-      <c r="L41" s="82"/>
-      <c r="M41" s="83"/>
+      <c r="K41" s="95"/>
+      <c r="L41" s="95"/>
+      <c r="M41" s="96"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="19" t="s">
@@ -5625,16 +5670,16 @@
       <c r="E52" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="F52" s="81" t="s">
+      <c r="F52" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G52" s="82"/>
-      <c r="H52" s="82"/>
-      <c r="I52" s="82"/>
-      <c r="J52" s="82"/>
-      <c r="K52" s="82"/>
-      <c r="L52" s="82"/>
-      <c r="M52" s="83"/>
+      <c r="G52" s="95"/>
+      <c r="H52" s="95"/>
+      <c r="I52" s="95"/>
+      <c r="J52" s="95"/>
+      <c r="K52" s="95"/>
+      <c r="L52" s="95"/>
+      <c r="M52" s="96"/>
       <c r="O52" t="s">
         <v>343</v>
       </c>
@@ -5649,16 +5694,16 @@
       <c r="E53" s="24" t="s">
         <v>364</v>
       </c>
-      <c r="F53" s="81" t="s">
+      <c r="F53" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G53" s="82"/>
-      <c r="H53" s="82"/>
-      <c r="I53" s="82"/>
-      <c r="J53" s="82"/>
-      <c r="K53" s="82"/>
-      <c r="L53" s="82"/>
-      <c r="M53" s="83"/>
+      <c r="G53" s="95"/>
+      <c r="H53" s="95"/>
+      <c r="I53" s="95"/>
+      <c r="J53" s="95"/>
+      <c r="K53" s="95"/>
+      <c r="L53" s="95"/>
+      <c r="M53" s="96"/>
       <c r="O53" t="s">
         <v>343</v>
       </c>
@@ -5673,16 +5718,16 @@
       <c r="E54" s="24" t="s">
         <v>365</v>
       </c>
-      <c r="F54" s="81" t="s">
+      <c r="F54" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="82"/>
-      <c r="L54" s="82"/>
-      <c r="M54" s="83"/>
+      <c r="G54" s="95"/>
+      <c r="H54" s="95"/>
+      <c r="I54" s="95"/>
+      <c r="J54" s="95"/>
+      <c r="K54" s="95"/>
+      <c r="L54" s="95"/>
+      <c r="M54" s="96"/>
       <c r="O54" t="s">
         <v>343</v>
       </c>
@@ -5716,16 +5761,16 @@
       <c r="E56" s="23" t="s">
         <v>369</v>
       </c>
-      <c r="F56" s="81" t="s">
+      <c r="F56" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G56" s="82"/>
-      <c r="H56" s="82"/>
-      <c r="I56" s="82"/>
-      <c r="J56" s="82"/>
-      <c r="K56" s="82"/>
-      <c r="L56" s="82"/>
-      <c r="M56" s="83"/>
+      <c r="G56" s="95"/>
+      <c r="H56" s="95"/>
+      <c r="I56" s="95"/>
+      <c r="J56" s="95"/>
+      <c r="K56" s="95"/>
+      <c r="L56" s="95"/>
+      <c r="M56" s="96"/>
       <c r="O56" t="s">
         <v>343</v>
       </c>
@@ -5740,16 +5785,16 @@
       <c r="E57" s="24" t="s">
         <v>370</v>
       </c>
-      <c r="F57" s="81" t="s">
+      <c r="F57" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="82"/>
-      <c r="H57" s="82"/>
-      <c r="I57" s="82"/>
-      <c r="J57" s="82"/>
-      <c r="K57" s="82"/>
-      <c r="L57" s="82"/>
-      <c r="M57" s="83"/>
+      <c r="G57" s="95"/>
+      <c r="H57" s="95"/>
+      <c r="I57" s="95"/>
+      <c r="J57" s="95"/>
+      <c r="K57" s="95"/>
+      <c r="L57" s="95"/>
+      <c r="M57" s="96"/>
       <c r="O57" t="s">
         <v>343</v>
       </c>
@@ -5764,16 +5809,16 @@
       <c r="E58" s="24" t="s">
         <v>371</v>
       </c>
-      <c r="F58" s="81" t="s">
+      <c r="F58" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G58" s="82"/>
-      <c r="H58" s="82"/>
-      <c r="I58" s="82"/>
-      <c r="J58" s="82"/>
-      <c r="K58" s="82"/>
-      <c r="L58" s="82"/>
-      <c r="M58" s="83"/>
+      <c r="G58" s="95"/>
+      <c r="H58" s="95"/>
+      <c r="I58" s="95"/>
+      <c r="J58" s="95"/>
+      <c r="K58" s="95"/>
+      <c r="L58" s="95"/>
+      <c r="M58" s="96"/>
       <c r="O58" t="s">
         <v>343</v>
       </c>
@@ -5818,29 +5863,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="F50:M50"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F48:M48"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="F45:M45"/>
-    <mergeCell ref="F46:M46"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="J31:M31"/>
     <mergeCell ref="J33:M33"/>
     <mergeCell ref="I34:M34"/>
     <mergeCell ref="J36:M36"/>
@@ -5857,6 +5879,29 @@
     <mergeCell ref="J22:M22"/>
     <mergeCell ref="F23:M23"/>
     <mergeCell ref="F24:M24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F48:M48"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F54:M54"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5931,16 +5976,16 @@
       <c r="E6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="88" t="s">
+      <c r="F6" s="86" t="s">
         <v>92</v>
       </c>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="89"/>
-      <c r="K6" s="89"/>
-      <c r="L6" s="89"/>
-      <c r="M6" s="90"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="88"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
@@ -5952,16 +5997,16 @@
       <c r="E7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="88" t="s">
+      <c r="F7" s="86" t="s">
         <v>181</v>
       </c>
-      <c r="G7" s="89"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="89"/>
-      <c r="J7" s="89"/>
-      <c r="K7" s="89"/>
-      <c r="L7" s="89"/>
-      <c r="M7" s="90"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="88"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
@@ -6023,12 +6068,12 @@
       <c r="I19" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="88" t="s">
+      <c r="J19" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="89"/>
-      <c r="L19" s="89"/>
-      <c r="M19" s="90"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="88"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="19" t="s">
@@ -6050,12 +6095,12 @@
       <c r="I20" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="88" t="s">
+      <c r="J20" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="90"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="87"/>
+      <c r="M20" s="88"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
@@ -6065,18 +6110,18 @@
         <v>35</v>
       </c>
       <c r="E21" s="6"/>
-      <c r="F21" s="88" t="s">
+      <c r="F21" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="90"/>
-      <c r="H21" s="88" t="s">
+      <c r="G21" s="88"/>
+      <c r="H21" s="86" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
-      <c r="K21" s="89"/>
-      <c r="L21" s="89"/>
-      <c r="M21" s="90"/>
+      <c r="I21" s="87"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="88"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
@@ -6086,10 +6131,10 @@
         <v>35</v>
       </c>
       <c r="E22" s="6"/>
-      <c r="F22" s="88" t="s">
+      <c r="F22" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="90"/>
+      <c r="G22" s="88"/>
       <c r="H22" s="18"/>
       <c r="I22" s="11" t="s">
         <v>114</v>
@@ -6097,11 +6142,11 @@
       <c r="J22" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="K22" s="88" t="s">
+      <c r="K22" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="L22" s="89"/>
-      <c r="M22" s="90"/>
+      <c r="L22" s="87"/>
+      <c r="M22" s="88"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
@@ -6111,18 +6156,18 @@
         <v>35</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="88" t="s">
+      <c r="F23" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="G23" s="89"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="88" t="s">
+      <c r="G23" s="87"/>
+      <c r="H23" s="87"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="86" t="s">
         <v>116</v>
       </c>
-      <c r="K23" s="89"/>
-      <c r="L23" s="89"/>
-      <c r="M23" s="90"/>
+      <c r="K23" s="87"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="88"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
@@ -6132,18 +6177,18 @@
         <v>35</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="88" t="s">
+      <c r="F24" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="88" t="s">
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="86" t="s">
         <v>116</v>
       </c>
-      <c r="K24" s="89"/>
-      <c r="L24" s="89"/>
-      <c r="M24" s="90"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="87"/>
+      <c r="M24" s="88"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
@@ -6153,18 +6198,18 @@
         <v>35</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="88" t="s">
+      <c r="F25" s="86" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="89"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="88" t="s">
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="89"/>
-      <c r="L25" s="89"/>
-      <c r="M25" s="90"/>
+      <c r="K25" s="87"/>
+      <c r="L25" s="87"/>
+      <c r="M25" s="88"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
@@ -6174,18 +6219,18 @@
         <v>35</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="88" t="s">
+      <c r="F26" s="86" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="89"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="88" t="s">
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="89"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="90"/>
+      <c r="K26" s="87"/>
+      <c r="L26" s="87"/>
+      <c r="M26" s="88"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="19" t="s">
@@ -6239,16 +6284,16 @@
       <c r="E29" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="88" t="s">
+      <c r="F29" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G29" s="89"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="89"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="90"/>
+      <c r="G29" s="87"/>
+      <c r="H29" s="87"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="87"/>
+      <c r="K29" s="87"/>
+      <c r="L29" s="87"/>
+      <c r="M29" s="88"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
@@ -6258,16 +6303,16 @@
         <v>35</v>
       </c>
       <c r="E30" s="6"/>
-      <c r="F30" s="88" t="s">
+      <c r="F30" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="90"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="87"/>
+      <c r="K30" s="87"/>
+      <c r="L30" s="87"/>
+      <c r="M30" s="88"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
@@ -6277,16 +6322,16 @@
         <v>35</v>
       </c>
       <c r="E31" s="6"/>
-      <c r="F31" s="88" t="s">
+      <c r="F31" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G31" s="89"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="89"/>
-      <c r="K31" s="89"/>
-      <c r="L31" s="89"/>
-      <c r="M31" s="90"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="87"/>
+      <c r="L31" s="87"/>
+      <c r="M31" s="88"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
@@ -6296,16 +6341,16 @@
         <v>35</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="88" t="s">
+      <c r="F32" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G32" s="89"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="89"/>
-      <c r="K32" s="89"/>
-      <c r="L32" s="89"/>
-      <c r="M32" s="90"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="87"/>
+      <c r="K32" s="87"/>
+      <c r="L32" s="87"/>
+      <c r="M32" s="88"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
@@ -6315,16 +6360,16 @@
         <v>35</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="88" t="s">
+      <c r="F33" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G33" s="89"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="89"/>
-      <c r="K33" s="89"/>
-      <c r="L33" s="89"/>
-      <c r="M33" s="90"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="87"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="87"/>
+      <c r="L33" s="87"/>
+      <c r="M33" s="88"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
@@ -6334,16 +6379,16 @@
         <v>35</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="88" t="s">
+      <c r="F34" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="89"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="89"/>
-      <c r="M34" s="90"/>
+      <c r="G34" s="87"/>
+      <c r="H34" s="87"/>
+      <c r="I34" s="87"/>
+      <c r="J34" s="87"/>
+      <c r="K34" s="87"/>
+      <c r="L34" s="87"/>
+      <c r="M34" s="88"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
@@ -6353,16 +6398,16 @@
         <v>35</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="88" t="s">
+      <c r="F35" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="89"/>
-      <c r="J35" s="89"/>
-      <c r="K35" s="89"/>
-      <c r="L35" s="89"/>
-      <c r="M35" s="90"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="87"/>
+      <c r="I35" s="87"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="87"/>
+      <c r="M35" s="88"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="19" t="s">
@@ -6372,16 +6417,16 @@
         <v>35</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="88" t="s">
+      <c r="F36" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="89"/>
-      <c r="J36" s="89"/>
-      <c r="K36" s="89"/>
-      <c r="L36" s="89"/>
-      <c r="M36" s="90"/>
+      <c r="G36" s="87"/>
+      <c r="H36" s="87"/>
+      <c r="I36" s="87"/>
+      <c r="J36" s="87"/>
+      <c r="K36" s="87"/>
+      <c r="L36" s="87"/>
+      <c r="M36" s="88"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
@@ -6391,16 +6436,16 @@
         <v>35</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="88" t="s">
+      <c r="F37" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G37" s="89"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="89"/>
-      <c r="K37" s="89"/>
-      <c r="L37" s="89"/>
-      <c r="M37" s="90"/>
+      <c r="G37" s="87"/>
+      <c r="H37" s="87"/>
+      <c r="I37" s="87"/>
+      <c r="J37" s="87"/>
+      <c r="K37" s="87"/>
+      <c r="L37" s="87"/>
+      <c r="M37" s="88"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
@@ -6410,16 +6455,16 @@
         <v>35</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="88" t="s">
+      <c r="F38" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="89"/>
-      <c r="M38" s="90"/>
+      <c r="G38" s="87"/>
+      <c r="H38" s="87"/>
+      <c r="I38" s="87"/>
+      <c r="J38" s="87"/>
+      <c r="K38" s="87"/>
+      <c r="L38" s="87"/>
+      <c r="M38" s="88"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
@@ -6454,11 +6499,11 @@
       <c r="I40" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J40" s="88" t="s">
+      <c r="J40" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K40" s="89"/>
-      <c r="L40" s="90"/>
+      <c r="K40" s="87"/>
+      <c r="L40" s="88"/>
       <c r="M40" s="13" t="s">
         <v>145</v>
       </c>
@@ -6479,11 +6524,11 @@
       <c r="I41" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J41" s="88" t="s">
+      <c r="J41" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K41" s="89"/>
-      <c r="L41" s="90"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
       <c r="M41" s="13" t="s">
         <v>145</v>
       </c>
@@ -6504,11 +6549,11 @@
       <c r="I42" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J42" s="88" t="s">
+      <c r="J42" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K42" s="89"/>
-      <c r="L42" s="90"/>
+      <c r="K42" s="87"/>
+      <c r="L42" s="88"/>
       <c r="M42" s="13" t="s">
         <v>145</v>
       </c>
@@ -6529,11 +6574,11 @@
       <c r="I43" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J43" s="88" t="s">
+      <c r="J43" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K43" s="89"/>
-      <c r="L43" s="90"/>
+      <c r="K43" s="87"/>
+      <c r="L43" s="88"/>
       <c r="M43" s="13" t="s">
         <v>145</v>
       </c>
@@ -6554,11 +6599,11 @@
       <c r="I44" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J44" s="88" t="s">
+      <c r="J44" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K44" s="89"/>
-      <c r="L44" s="90"/>
+      <c r="K44" s="87"/>
+      <c r="L44" s="88"/>
       <c r="M44" s="13" t="s">
         <v>145</v>
       </c>
@@ -6579,11 +6624,11 @@
       <c r="I45" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J45" s="88" t="s">
+      <c r="J45" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K45" s="89"/>
-      <c r="L45" s="90"/>
+      <c r="K45" s="87"/>
+      <c r="L45" s="88"/>
       <c r="M45" s="13" t="s">
         <v>145</v>
       </c>
@@ -6604,11 +6649,11 @@
       <c r="I46" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J46" s="88" t="s">
+      <c r="J46" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K46" s="89"/>
-      <c r="L46" s="90"/>
+      <c r="K46" s="87"/>
+      <c r="L46" s="88"/>
       <c r="M46" s="13" t="s">
         <v>145</v>
       </c>
@@ -6629,11 +6674,11 @@
       <c r="I47" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J47" s="88" t="s">
+      <c r="J47" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K47" s="89"/>
-      <c r="L47" s="90"/>
+      <c r="K47" s="87"/>
+      <c r="L47" s="88"/>
       <c r="M47" s="13" t="s">
         <v>145</v>
       </c>
@@ -6654,11 +6699,11 @@
       <c r="I48" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J48" s="88" t="s">
+      <c r="J48" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K48" s="89"/>
-      <c r="L48" s="90"/>
+      <c r="K48" s="87"/>
+      <c r="L48" s="88"/>
       <c r="M48" s="13" t="s">
         <v>145</v>
       </c>
@@ -6688,18 +6733,18 @@
         <v>35</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="88" t="s">
+      <c r="F50" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G50" s="89"/>
-      <c r="H50" s="89"/>
-      <c r="I50" s="90"/>
-      <c r="J50" s="88" t="s">
+      <c r="G50" s="87"/>
+      <c r="H50" s="87"/>
+      <c r="I50" s="88"/>
+      <c r="J50" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K50" s="89"/>
-      <c r="L50" s="89"/>
-      <c r="M50" s="90"/>
+      <c r="K50" s="87"/>
+      <c r="L50" s="87"/>
+      <c r="M50" s="88"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
@@ -6709,18 +6754,18 @@
         <v>35</v>
       </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="88" t="s">
+      <c r="F51" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G51" s="89"/>
-      <c r="H51" s="89"/>
-      <c r="I51" s="90"/>
-      <c r="J51" s="88" t="s">
+      <c r="G51" s="87"/>
+      <c r="H51" s="87"/>
+      <c r="I51" s="88"/>
+      <c r="J51" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K51" s="89"/>
-      <c r="L51" s="89"/>
-      <c r="M51" s="90"/>
+      <c r="K51" s="87"/>
+      <c r="L51" s="87"/>
+      <c r="M51" s="88"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
@@ -6730,18 +6775,18 @@
         <v>35</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="88" t="s">
+      <c r="F52" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G52" s="89"/>
-      <c r="H52" s="89"/>
-      <c r="I52" s="90"/>
-      <c r="J52" s="88" t="s">
+      <c r="G52" s="87"/>
+      <c r="H52" s="87"/>
+      <c r="I52" s="88"/>
+      <c r="J52" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K52" s="89"/>
-      <c r="L52" s="89"/>
-      <c r="M52" s="90"/>
+      <c r="K52" s="87"/>
+      <c r="L52" s="87"/>
+      <c r="M52" s="88"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
@@ -6751,18 +6796,18 @@
         <v>35</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="88" t="s">
+      <c r="F53" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G53" s="89"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="90"/>
-      <c r="J53" s="88" t="s">
+      <c r="G53" s="87"/>
+      <c r="H53" s="87"/>
+      <c r="I53" s="88"/>
+      <c r="J53" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K53" s="89"/>
-      <c r="L53" s="89"/>
-      <c r="M53" s="90"/>
+      <c r="K53" s="87"/>
+      <c r="L53" s="87"/>
+      <c r="M53" s="88"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
@@ -6772,18 +6817,18 @@
         <v>35</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="88" t="s">
+      <c r="F54" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G54" s="89"/>
-      <c r="H54" s="89"/>
-      <c r="I54" s="90"/>
-      <c r="J54" s="88" t="s">
+      <c r="G54" s="87"/>
+      <c r="H54" s="87"/>
+      <c r="I54" s="88"/>
+      <c r="J54" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K54" s="89"/>
-      <c r="L54" s="89"/>
-      <c r="M54" s="90"/>
+      <c r="K54" s="87"/>
+      <c r="L54" s="87"/>
+      <c r="M54" s="88"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
@@ -6793,18 +6838,18 @@
         <v>35</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="88" t="s">
+      <c r="F55" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G55" s="89"/>
-      <c r="H55" s="89"/>
-      <c r="I55" s="90"/>
-      <c r="J55" s="88" t="s">
+      <c r="G55" s="87"/>
+      <c r="H55" s="87"/>
+      <c r="I55" s="88"/>
+      <c r="J55" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K55" s="89"/>
-      <c r="L55" s="89"/>
-      <c r="M55" s="90"/>
+      <c r="K55" s="87"/>
+      <c r="L55" s="87"/>
+      <c r="M55" s="88"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
@@ -6814,18 +6859,18 @@
         <v>35</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="88" t="s">
+      <c r="F56" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G56" s="89"/>
-      <c r="H56" s="89"/>
-      <c r="I56" s="90"/>
-      <c r="J56" s="88" t="s">
+      <c r="G56" s="87"/>
+      <c r="H56" s="87"/>
+      <c r="I56" s="88"/>
+      <c r="J56" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K56" s="89"/>
-      <c r="L56" s="89"/>
-      <c r="M56" s="90"/>
+      <c r="K56" s="87"/>
+      <c r="L56" s="87"/>
+      <c r="M56" s="88"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="19" t="s">
@@ -6835,18 +6880,18 @@
         <v>35</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="88" t="s">
+      <c r="F57" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G57" s="89"/>
-      <c r="H57" s="89"/>
-      <c r="I57" s="90"/>
-      <c r="J57" s="88" t="s">
+      <c r="G57" s="87"/>
+      <c r="H57" s="87"/>
+      <c r="I57" s="88"/>
+      <c r="J57" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K57" s="89"/>
-      <c r="L57" s="89"/>
-      <c r="M57" s="90"/>
+      <c r="K57" s="87"/>
+      <c r="L57" s="87"/>
+      <c r="M57" s="88"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
@@ -6856,18 +6901,18 @@
         <v>35</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="88" t="s">
+      <c r="F58" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G58" s="89"/>
-      <c r="H58" s="89"/>
-      <c r="I58" s="90"/>
-      <c r="J58" s="88" t="s">
+      <c r="G58" s="87"/>
+      <c r="H58" s="87"/>
+      <c r="I58" s="88"/>
+      <c r="J58" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K58" s="89"/>
-      <c r="L58" s="89"/>
-      <c r="M58" s="90"/>
+      <c r="K58" s="87"/>
+      <c r="L58" s="87"/>
+      <c r="M58" s="88"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="19" t="s">
@@ -6902,10 +6947,10 @@
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
       <c r="K60" s="10"/>
-      <c r="L60" s="81" t="s">
+      <c r="L60" s="85" t="s">
         <v>177</v>
       </c>
-      <c r="M60" s="80"/>
+      <c r="M60" s="84"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="19" t="s">
@@ -6923,10 +6968,10 @@
       <c r="I61" s="9"/>
       <c r="J61" s="9"/>
       <c r="K61" s="10"/>
-      <c r="L61" s="78" t="s">
+      <c r="L61" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="M61" s="80"/>
+      <c r="M61" s="84"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="19" t="s">
@@ -6944,10 +6989,10 @@
       <c r="I62" s="9"/>
       <c r="J62" s="9"/>
       <c r="K62" s="10"/>
-      <c r="L62" s="78" t="s">
+      <c r="L62" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="M62" s="80"/>
+      <c r="M62" s="84"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="19" t="s">
@@ -6965,10 +7010,10 @@
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
       <c r="K63" s="10"/>
-      <c r="L63" s="78" t="s">
+      <c r="L63" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="M63" s="80"/>
+      <c r="M63" s="84"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="19" t="s">
@@ -6986,10 +7031,10 @@
       <c r="I64" s="9"/>
       <c r="J64" s="9"/>
       <c r="K64" s="10"/>
-      <c r="L64" s="78" t="s">
+      <c r="L64" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="M64" s="80"/>
+      <c r="M64" s="84"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="19" t="s">
@@ -7007,10 +7052,10 @@
       <c r="I65" s="9"/>
       <c r="J65" s="9"/>
       <c r="K65" s="10"/>
-      <c r="L65" s="78" t="s">
+      <c r="L65" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="M65" s="80"/>
+      <c r="M65" s="84"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="19" t="s">
@@ -7028,10 +7073,10 @@
       <c r="I66" s="9"/>
       <c r="J66" s="9"/>
       <c r="K66" s="10"/>
-      <c r="L66" s="78" t="s">
+      <c r="L66" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="M66" s="80"/>
+      <c r="M66" s="84"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="19" t="s">
@@ -7049,10 +7094,10 @@
       <c r="I67" s="9"/>
       <c r="J67" s="9"/>
       <c r="K67" s="10"/>
-      <c r="L67" s="78" t="s">
+      <c r="L67" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="M67" s="80"/>
+      <c r="M67" s="84"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="19" t="s">
@@ -7070,10 +7115,10 @@
       <c r="I68" s="9"/>
       <c r="J68" s="9"/>
       <c r="K68" s="10"/>
-      <c r="L68" s="78" t="s">
+      <c r="L68" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="M68" s="80"/>
+      <c r="M68" s="84"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="19" t="s">
@@ -7102,16 +7147,16 @@
       <c r="E70" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="F70" s="81" t="s">
+      <c r="F70" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G70" s="82"/>
-      <c r="H70" s="82"/>
-      <c r="I70" s="82"/>
-      <c r="J70" s="82"/>
-      <c r="K70" s="82"/>
-      <c r="L70" s="82"/>
-      <c r="M70" s="83"/>
+      <c r="G70" s="95"/>
+      <c r="H70" s="95"/>
+      <c r="I70" s="95"/>
+      <c r="J70" s="95"/>
+      <c r="K70" s="95"/>
+      <c r="L70" s="95"/>
+      <c r="M70" s="96"/>
       <c r="O70" t="s">
         <v>343</v>
       </c>
@@ -7126,16 +7171,16 @@
       <c r="E71" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="F71" s="81" t="s">
+      <c r="F71" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G71" s="82"/>
-      <c r="H71" s="82"/>
-      <c r="I71" s="82"/>
-      <c r="J71" s="82"/>
-      <c r="K71" s="82"/>
-      <c r="L71" s="82"/>
-      <c r="M71" s="83"/>
+      <c r="G71" s="95"/>
+      <c r="H71" s="95"/>
+      <c r="I71" s="95"/>
+      <c r="J71" s="95"/>
+      <c r="K71" s="95"/>
+      <c r="L71" s="95"/>
+      <c r="M71" s="96"/>
       <c r="O71" t="s">
         <v>343</v>
       </c>
@@ -7150,16 +7195,16 @@
       <c r="E72" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="F72" s="81" t="s">
+      <c r="F72" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G72" s="82"/>
-      <c r="H72" s="82"/>
-      <c r="I72" s="82"/>
-      <c r="J72" s="82"/>
-      <c r="K72" s="82"/>
-      <c r="L72" s="82"/>
-      <c r="M72" s="83"/>
+      <c r="G72" s="95"/>
+      <c r="H72" s="95"/>
+      <c r="I72" s="95"/>
+      <c r="J72" s="95"/>
+      <c r="K72" s="95"/>
+      <c r="L72" s="95"/>
+      <c r="M72" s="96"/>
       <c r="O72" t="s">
         <v>343</v>
       </c>
@@ -7174,16 +7219,16 @@
       <c r="E73" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="F73" s="81" t="s">
+      <c r="F73" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G73" s="82"/>
-      <c r="H73" s="82"/>
-      <c r="I73" s="82"/>
-      <c r="J73" s="82"/>
-      <c r="K73" s="82"/>
-      <c r="L73" s="82"/>
-      <c r="M73" s="83"/>
+      <c r="G73" s="95"/>
+      <c r="H73" s="95"/>
+      <c r="I73" s="95"/>
+      <c r="J73" s="95"/>
+      <c r="K73" s="95"/>
+      <c r="L73" s="95"/>
+      <c r="M73" s="96"/>
       <c r="O73" t="s">
         <v>343</v>
       </c>
@@ -7198,16 +7243,16 @@
       <c r="E74" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="F74" s="81" t="s">
+      <c r="F74" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G74" s="82"/>
-      <c r="H74" s="82"/>
-      <c r="I74" s="82"/>
-      <c r="J74" s="82"/>
-      <c r="K74" s="82"/>
-      <c r="L74" s="82"/>
-      <c r="M74" s="83"/>
+      <c r="G74" s="95"/>
+      <c r="H74" s="95"/>
+      <c r="I74" s="95"/>
+      <c r="J74" s="95"/>
+      <c r="K74" s="95"/>
+      <c r="L74" s="95"/>
+      <c r="M74" s="96"/>
       <c r="O74" t="s">
         <v>343</v>
       </c>
@@ -7222,16 +7267,16 @@
       <c r="E75" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="F75" s="81" t="s">
+      <c r="F75" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G75" s="82"/>
-      <c r="H75" s="82"/>
-      <c r="I75" s="82"/>
-      <c r="J75" s="82"/>
-      <c r="K75" s="82"/>
-      <c r="L75" s="82"/>
-      <c r="M75" s="83"/>
+      <c r="G75" s="95"/>
+      <c r="H75" s="95"/>
+      <c r="I75" s="95"/>
+      <c r="J75" s="95"/>
+      <c r="K75" s="95"/>
+      <c r="L75" s="95"/>
+      <c r="M75" s="96"/>
       <c r="O75" t="s">
         <v>343</v>
       </c>
@@ -7246,16 +7291,16 @@
       <c r="E76" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="F76" s="81" t="s">
+      <c r="F76" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G76" s="82"/>
-      <c r="H76" s="82"/>
-      <c r="I76" s="82"/>
-      <c r="J76" s="82"/>
-      <c r="K76" s="82"/>
-      <c r="L76" s="82"/>
-      <c r="M76" s="83"/>
+      <c r="G76" s="95"/>
+      <c r="H76" s="95"/>
+      <c r="I76" s="95"/>
+      <c r="J76" s="95"/>
+      <c r="K76" s="95"/>
+      <c r="L76" s="95"/>
+      <c r="M76" s="96"/>
       <c r="O76" t="s">
         <v>343</v>
       </c>
@@ -7270,16 +7315,16 @@
       <c r="E77" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="F77" s="81" t="s">
+      <c r="F77" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G77" s="82"/>
-      <c r="H77" s="82"/>
-      <c r="I77" s="82"/>
-      <c r="J77" s="82"/>
-      <c r="K77" s="82"/>
-      <c r="L77" s="82"/>
-      <c r="M77" s="83"/>
+      <c r="G77" s="95"/>
+      <c r="H77" s="95"/>
+      <c r="I77" s="95"/>
+      <c r="J77" s="95"/>
+      <c r="K77" s="95"/>
+      <c r="L77" s="95"/>
+      <c r="M77" s="96"/>
       <c r="O77" t="s">
         <v>343</v>
       </c>
@@ -7294,16 +7339,16 @@
       <c r="E78" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="F78" s="81" t="s">
+      <c r="F78" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="G78" s="82"/>
-      <c r="H78" s="82"/>
-      <c r="I78" s="82"/>
-      <c r="J78" s="82"/>
-      <c r="K78" s="82"/>
-      <c r="L78" s="82"/>
-      <c r="M78" s="83"/>
+      <c r="G78" s="95"/>
+      <c r="H78" s="95"/>
+      <c r="I78" s="95"/>
+      <c r="J78" s="95"/>
+      <c r="K78" s="95"/>
+      <c r="L78" s="95"/>
+      <c r="M78" s="96"/>
       <c r="O78" t="s">
         <v>343</v>
       </c>
@@ -7327,11 +7372,56 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="F70:M70"/>
-    <mergeCell ref="F71:M71"/>
-    <mergeCell ref="F72:M72"/>
-    <mergeCell ref="F73:M73"/>
-    <mergeCell ref="F74:M74"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="J54:M54"/>
     <mergeCell ref="F75:M75"/>
     <mergeCell ref="F76:M76"/>
     <mergeCell ref="F77:M77"/>
@@ -7348,56 +7438,11 @@
     <mergeCell ref="F52:I52"/>
     <mergeCell ref="J52:M52"/>
     <mergeCell ref="F53:I53"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F70:M70"/>
+    <mergeCell ref="F71:M71"/>
+    <mergeCell ref="F72:M72"/>
+    <mergeCell ref="F73:M73"/>
+    <mergeCell ref="F74:M74"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7506,14 +7551,14 @@
       <c r="E11" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="103"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="105"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="113"/>
+      <c r="H11" s="113"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="113"/>
+      <c r="K11" s="113"/>
+      <c r="L11" s="113"/>
+      <c r="M11" s="114"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="19" t="s">
@@ -7525,16 +7570,16 @@
       <c r="E12" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="78" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="73"/>
-      <c r="K12" s="73"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="74"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="80"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
@@ -7546,16 +7591,16 @@
       <c r="E13" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="F13" s="72" t="s">
+      <c r="F13" s="78" t="s">
         <v>207</v>
       </c>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
-      <c r="K13" s="73"/>
-      <c r="L13" s="73"/>
-      <c r="M13" s="74"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="80"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
@@ -7567,16 +7612,16 @@
       <c r="E14" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="78" t="s">
         <v>208</v>
       </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="73"/>
-      <c r="M14" s="74"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="80"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
@@ -7621,16 +7666,16 @@
       <c r="E16" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F16" s="106" t="s">
+      <c r="F16" s="115" t="s">
         <v>214</v>
       </c>
-      <c r="G16" s="107"/>
-      <c r="H16" s="107"/>
-      <c r="I16" s="107"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="107"/>
-      <c r="M16" s="108"/>
+      <c r="G16" s="116"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="116"/>
+      <c r="K16" s="116"/>
+      <c r="L16" s="116"/>
+      <c r="M16" s="117"/>
       <c r="N16" s="57" t="s">
         <v>307</v>
       </c>
@@ -7645,16 +7690,16 @@
       <c r="E17" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F17" s="106" t="s">
+      <c r="F17" s="115" t="s">
         <v>215</v>
       </c>
-      <c r="G17" s="107"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="107"/>
-      <c r="M17" s="108"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="116"/>
+      <c r="J17" s="116"/>
+      <c r="K17" s="116"/>
+      <c r="L17" s="116"/>
+      <c r="M17" s="117"/>
       <c r="N17" s="57" t="s">
         <v>307</v>
       </c>
@@ -7682,8 +7727,8 @@
       <c r="J18" s="56" t="s">
         <v>220</v>
       </c>
-      <c r="K18" s="103"/>
-      <c r="L18" s="105"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="114"/>
       <c r="M18" s="55" t="s">
         <v>221</v>
       </c>
@@ -7705,8 +7750,8 @@
       <c r="G19" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="H19" s="103"/>
-      <c r="I19" s="105"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="114"/>
       <c r="J19" s="56" t="s">
         <v>224</v>
       </c>
@@ -7728,16 +7773,16 @@
         <v>35</v>
       </c>
       <c r="E20" s="43"/>
-      <c r="F20" s="109" t="s">
+      <c r="F20" s="118" t="s">
         <v>228</v>
       </c>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="111"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="120"/>
       <c r="N20" t="s">
         <v>300</v>
       </c>
@@ -7750,16 +7795,16 @@
         <v>35</v>
       </c>
       <c r="E21" s="42"/>
-      <c r="F21" s="109" t="s">
+      <c r="F21" s="118" t="s">
         <v>229</v>
       </c>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="111"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="120"/>
       <c r="N21" t="s">
         <v>301</v>
       </c>
@@ -7772,16 +7817,16 @@
         <v>35</v>
       </c>
       <c r="E22" s="42"/>
-      <c r="F22" s="109" t="s">
+      <c r="F22" s="118" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="110"/>
-      <c r="K22" s="110"/>
-      <c r="L22" s="110"/>
-      <c r="M22" s="111"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="120"/>
       <c r="N22" t="s">
         <v>302</v>
       </c>
@@ -7794,16 +7839,16 @@
         <v>35</v>
       </c>
       <c r="E23" s="42"/>
-      <c r="F23" s="109" t="s">
+      <c r="F23" s="118" t="s">
         <v>231</v>
       </c>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="110"/>
-      <c r="M23" s="111"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="120"/>
       <c r="N23" t="s">
         <v>303</v>
       </c>
@@ -7818,16 +7863,16 @@
       <c r="E24" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F24" s="106" t="s">
+      <c r="F24" s="115" t="s">
         <v>232</v>
       </c>
-      <c r="G24" s="107"/>
-      <c r="H24" s="107"/>
-      <c r="I24" s="107"/>
-      <c r="J24" s="107"/>
-      <c r="K24" s="107"/>
-      <c r="L24" s="107"/>
-      <c r="M24" s="108"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="116"/>
+      <c r="L24" s="116"/>
+      <c r="M24" s="117"/>
       <c r="N24" s="59" t="s">
         <v>307</v>
       </c>
@@ -7842,16 +7887,16 @@
       <c r="E25" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F25" s="103"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="106" t="s">
+      <c r="F25" s="112"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="113"/>
+      <c r="J25" s="114"/>
+      <c r="K25" s="115" t="s">
         <v>233</v>
       </c>
-      <c r="L25" s="107"/>
-      <c r="M25" s="108"/>
+      <c r="L25" s="116"/>
+      <c r="M25" s="117"/>
       <c r="N25" s="57" t="s">
         <v>307</v>
       </c>
@@ -7864,16 +7909,16 @@
         <v>30</v>
       </c>
       <c r="E26" s="42"/>
-      <c r="F26" s="109" t="s">
+      <c r="F26" s="118" t="s">
         <v>234</v>
       </c>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="112"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="113"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="121"/>
+      <c r="L26" s="121"/>
+      <c r="M26" s="122"/>
       <c r="N26" t="s">
         <v>312</v>
       </c>
@@ -7886,16 +7931,16 @@
         <v>35</v>
       </c>
       <c r="E27" s="42"/>
-      <c r="F27" s="109" t="s">
+      <c r="F27" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="110"/>
-      <c r="L27" s="110"/>
-      <c r="M27" s="111"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="120"/>
       <c r="N27" t="s">
         <v>304</v>
       </c>
@@ -7908,16 +7953,16 @@
         <v>35</v>
       </c>
       <c r="E28" s="42"/>
-      <c r="F28" s="109" t="s">
+      <c r="F28" s="118" t="s">
         <v>236</v>
       </c>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="111"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="120"/>
       <c r="N28" t="s">
         <v>305</v>
       </c>
@@ -7930,16 +7975,16 @@
         <v>35</v>
       </c>
       <c r="E29" s="42"/>
-      <c r="F29" s="109" t="s">
+      <c r="F29" s="118" t="s">
         <v>237</v>
       </c>
-      <c r="G29" s="110"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="110"/>
-      <c r="L29" s="110"/>
-      <c r="M29" s="111"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="119"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="120"/>
       <c r="N29" t="s">
         <v>306</v>
       </c>
@@ -7954,14 +7999,14 @@
       <c r="E30" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F30" s="103"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="105"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="114"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="60" t="s">
@@ -7973,14 +8018,14 @@
       <c r="E31" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F31" s="103"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="105"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="114"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="60" t="s">
@@ -7992,16 +8037,16 @@
       <c r="E32" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F32" s="106" t="s">
+      <c r="F32" s="115" t="s">
         <v>238</v>
       </c>
-      <c r="G32" s="107"/>
-      <c r="H32" s="107"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="108"/>
+      <c r="G32" s="116"/>
+      <c r="H32" s="116"/>
+      <c r="I32" s="116"/>
+      <c r="J32" s="116"/>
+      <c r="K32" s="116"/>
+      <c r="L32" s="116"/>
+      <c r="M32" s="117"/>
       <c r="N32" s="57" t="s">
         <v>307</v>
       </c>
@@ -8016,16 +8061,16 @@
       <c r="E33" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F33" s="106" t="s">
+      <c r="F33" s="115" t="s">
         <v>239</v>
       </c>
-      <c r="G33" s="108"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="105"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="113"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="113"/>
+      <c r="M33" s="114"/>
       <c r="N33" s="57" t="s">
         <v>307</v>
       </c>
@@ -8040,16 +8085,16 @@
       <c r="E34" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F34" s="103"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="104"/>
-      <c r="I34" s="104"/>
-      <c r="J34" s="105"/>
-      <c r="K34" s="106" t="s">
+      <c r="F34" s="112"/>
+      <c r="G34" s="113"/>
+      <c r="H34" s="113"/>
+      <c r="I34" s="113"/>
+      <c r="J34" s="114"/>
+      <c r="K34" s="115" t="s">
         <v>240</v>
       </c>
-      <c r="L34" s="107"/>
-      <c r="M34" s="108"/>
+      <c r="L34" s="116"/>
+      <c r="M34" s="117"/>
       <c r="N34" s="57" t="s">
         <v>307</v>
       </c>
@@ -8064,16 +8109,16 @@
       <c r="E35" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F35" s="103"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="104"/>
-      <c r="I35" s="105"/>
-      <c r="J35" s="106" t="s">
+      <c r="F35" s="112"/>
+      <c r="G35" s="113"/>
+      <c r="H35" s="113"/>
+      <c r="I35" s="114"/>
+      <c r="J35" s="115" t="s">
         <v>241</v>
       </c>
-      <c r="K35" s="107"/>
-      <c r="L35" s="107"/>
-      <c r="M35" s="108"/>
+      <c r="K35" s="116"/>
+      <c r="L35" s="116"/>
+      <c r="M35" s="117"/>
       <c r="N35" s="57" t="s">
         <v>307</v>
       </c>
@@ -8088,16 +8133,16 @@
       <c r="E36" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F36" s="103"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="104"/>
-      <c r="I36" s="105"/>
-      <c r="J36" s="106" t="s">
+      <c r="F36" s="112"/>
+      <c r="G36" s="113"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="114"/>
+      <c r="J36" s="115" t="s">
         <v>242</v>
       </c>
-      <c r="K36" s="107"/>
-      <c r="L36" s="107"/>
-      <c r="M36" s="108"/>
+      <c r="K36" s="116"/>
+      <c r="L36" s="116"/>
+      <c r="M36" s="117"/>
       <c r="N36" s="57" t="s">
         <v>307</v>
       </c>
@@ -8112,16 +8157,16 @@
       <c r="E37" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F37" s="106" t="s">
+      <c r="F37" s="115" t="s">
         <v>243</v>
       </c>
-      <c r="G37" s="107"/>
-      <c r="H37" s="107"/>
-      <c r="I37" s="107"/>
-      <c r="J37" s="107"/>
-      <c r="K37" s="107"/>
-      <c r="L37" s="107"/>
-      <c r="M37" s="108"/>
+      <c r="G37" s="116"/>
+      <c r="H37" s="116"/>
+      <c r="I37" s="116"/>
+      <c r="J37" s="116"/>
+      <c r="K37" s="116"/>
+      <c r="L37" s="116"/>
+      <c r="M37" s="117"/>
       <c r="N37" s="57" t="s">
         <v>307</v>
       </c>
@@ -8136,14 +8181,14 @@
       <c r="E38" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F38" s="103"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="105"/>
+      <c r="F38" s="112"/>
+      <c r="G38" s="113"/>
+      <c r="H38" s="113"/>
+      <c r="I38" s="113"/>
+      <c r="J38" s="113"/>
+      <c r="K38" s="113"/>
+      <c r="L38" s="113"/>
+      <c r="M38" s="114"/>
     </row>
     <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="60" t="s">
@@ -8155,14 +8200,14 @@
       <c r="E39" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F39" s="103"/>
-      <c r="G39" s="104"/>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="104"/>
-      <c r="K39" s="104"/>
-      <c r="L39" s="104"/>
-      <c r="M39" s="105"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="113"/>
+      <c r="H39" s="113"/>
+      <c r="I39" s="113"/>
+      <c r="J39" s="113"/>
+      <c r="K39" s="113"/>
+      <c r="L39" s="113"/>
+      <c r="M39" s="114"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="60" t="s">
@@ -8174,14 +8219,14 @@
       <c r="E40" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F40" s="103"/>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="105"/>
+      <c r="F40" s="112"/>
+      <c r="G40" s="113"/>
+      <c r="H40" s="113"/>
+      <c r="I40" s="113"/>
+      <c r="J40" s="113"/>
+      <c r="K40" s="113"/>
+      <c r="L40" s="113"/>
+      <c r="M40" s="114"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="60" t="s">
@@ -8193,14 +8238,14 @@
       <c r="E41" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F41" s="103"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="104"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="104"/>
-      <c r="K41" s="104"/>
-      <c r="L41" s="104"/>
-      <c r="M41" s="105"/>
+      <c r="F41" s="112"/>
+      <c r="G41" s="113"/>
+      <c r="H41" s="113"/>
+      <c r="I41" s="113"/>
+      <c r="J41" s="113"/>
+      <c r="K41" s="113"/>
+      <c r="L41" s="113"/>
+      <c r="M41" s="114"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="60" t="s">
@@ -8212,14 +8257,14 @@
       <c r="E42" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F42" s="103"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="104"/>
-      <c r="L42" s="104"/>
-      <c r="M42" s="105"/>
+      <c r="F42" s="112"/>
+      <c r="G42" s="113"/>
+      <c r="H42" s="113"/>
+      <c r="I42" s="113"/>
+      <c r="J42" s="113"/>
+      <c r="K42" s="113"/>
+      <c r="L42" s="113"/>
+      <c r="M42" s="114"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="20" t="s">
@@ -8241,12 +8286,12 @@
       <c r="I43" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="72" t="s">
+      <c r="J43" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="73"/>
-      <c r="L43" s="73"/>
-      <c r="M43" s="74"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="80"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
@@ -8256,18 +8301,18 @@
         <v>35</v>
       </c>
       <c r="E44" s="43"/>
-      <c r="F44" s="72" t="s">
+      <c r="F44" s="78" t="s">
         <v>252</v>
       </c>
-      <c r="G44" s="74"/>
-      <c r="H44" s="72" t="s">
+      <c r="G44" s="80"/>
+      <c r="H44" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="I44" s="73"/>
-      <c r="J44" s="73"/>
-      <c r="K44" s="73"/>
-      <c r="L44" s="73"/>
-      <c r="M44" s="74"/>
+      <c r="I44" s="79"/>
+      <c r="J44" s="79"/>
+      <c r="K44" s="79"/>
+      <c r="L44" s="79"/>
+      <c r="M44" s="80"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="19" t="s">
@@ -8277,18 +8322,18 @@
         <v>35</v>
       </c>
       <c r="E45" s="43"/>
-      <c r="F45" s="114" t="s">
+      <c r="F45" s="106" t="s">
         <v>115</v>
       </c>
-      <c r="G45" s="115"/>
-      <c r="H45" s="115"/>
-      <c r="I45" s="116"/>
-      <c r="J45" s="72" t="s">
+      <c r="G45" s="107"/>
+      <c r="H45" s="107"/>
+      <c r="I45" s="108"/>
+      <c r="J45" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="K45" s="73"/>
-      <c r="L45" s="73"/>
-      <c r="M45" s="74"/>
+      <c r="K45" s="79"/>
+      <c r="L45" s="79"/>
+      <c r="M45" s="80"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="19" t="s">
@@ -8298,18 +8343,18 @@
         <v>35</v>
       </c>
       <c r="E46" s="6"/>
-      <c r="F46" s="72" t="s">
+      <c r="F46" s="78" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="73"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="74"/>
-      <c r="J46" s="117" t="s">
+      <c r="G46" s="79"/>
+      <c r="H46" s="79"/>
+      <c r="I46" s="80"/>
+      <c r="J46" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="K46" s="118"/>
-      <c r="L46" s="118"/>
-      <c r="M46" s="119"/>
+      <c r="K46" s="110"/>
+      <c r="L46" s="110"/>
+      <c r="M46" s="111"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="19" t="s">
@@ -8319,16 +8364,16 @@
         <v>35</v>
       </c>
       <c r="E47" s="6"/>
-      <c r="F47" s="88" t="s">
+      <c r="F47" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G47" s="89"/>
-      <c r="H47" s="89"/>
-      <c r="I47" s="89"/>
-      <c r="J47" s="89"/>
-      <c r="K47" s="89"/>
-      <c r="L47" s="89"/>
-      <c r="M47" s="90"/>
+      <c r="G47" s="87"/>
+      <c r="H47" s="87"/>
+      <c r="I47" s="87"/>
+      <c r="J47" s="87"/>
+      <c r="K47" s="87"/>
+      <c r="L47" s="87"/>
+      <c r="M47" s="88"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="19" t="s">
@@ -8338,20 +8383,20 @@
         <v>35</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="84"/>
-      <c r="G48" s="86"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="77"/>
       <c r="H48" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="I48" s="88" t="s">
+      <c r="I48" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="J48" s="89"/>
-      <c r="K48" s="90"/>
-      <c r="L48" s="88" t="s">
+      <c r="J48" s="87"/>
+      <c r="K48" s="88"/>
+      <c r="L48" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="M48" s="90"/>
+      <c r="M48" s="88"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="19" t="s">
@@ -8394,15 +8439,15 @@
         <v>35</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="84"/>
-      <c r="G50" s="85"/>
-      <c r="H50" s="85"/>
-      <c r="I50" s="86"/>
-      <c r="J50" s="88" t="s">
+      <c r="F50" s="75"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="77"/>
+      <c r="J50" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="K50" s="89"/>
-      <c r="L50" s="90"/>
+      <c r="K50" s="87"/>
+      <c r="L50" s="88"/>
       <c r="M50" s="13" t="s">
         <v>81</v>
       </c>
@@ -8417,16 +8462,16 @@
       <c r="E51" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F51" s="103"/>
-      <c r="G51" s="104"/>
-      <c r="H51" s="104"/>
-      <c r="I51" s="104"/>
-      <c r="J51" s="104"/>
-      <c r="K51" s="105"/>
-      <c r="L51" s="78" t="s">
+      <c r="F51" s="112"/>
+      <c r="G51" s="113"/>
+      <c r="H51" s="113"/>
+      <c r="I51" s="113"/>
+      <c r="J51" s="113"/>
+      <c r="K51" s="114"/>
+      <c r="L51" s="82" t="s">
         <v>257</v>
       </c>
-      <c r="M51" s="80"/>
+      <c r="M51" s="84"/>
     </row>
     <row r="52" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
@@ -8438,16 +8483,16 @@
       <c r="E52" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="F52" s="78" t="s">
+      <c r="F52" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="G52" s="79"/>
-      <c r="H52" s="79"/>
-      <c r="I52" s="79"/>
-      <c r="J52" s="79"/>
-      <c r="K52" s="79"/>
-      <c r="L52" s="79"/>
-      <c r="M52" s="80"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
+      <c r="J52" s="83"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="83"/>
+      <c r="M52" s="84"/>
       <c r="N52" t="s">
         <v>343</v>
       </c>
@@ -8462,16 +8507,16 @@
       <c r="E53" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="F53" s="78" t="s">
+      <c r="F53" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="G53" s="79"/>
-      <c r="H53" s="79"/>
-      <c r="I53" s="79"/>
-      <c r="J53" s="79"/>
-      <c r="K53" s="79"/>
-      <c r="L53" s="79"/>
-      <c r="M53" s="80"/>
+      <c r="G53" s="83"/>
+      <c r="H53" s="83"/>
+      <c r="I53" s="83"/>
+      <c r="J53" s="83"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="83"/>
+      <c r="M53" s="84"/>
       <c r="N53" t="s">
         <v>393</v>
       </c>
@@ -8486,16 +8531,16 @@
       <c r="E54" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="F54" s="78" t="s">
+      <c r="F54" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="G54" s="79"/>
-      <c r="H54" s="79"/>
-      <c r="I54" s="79"/>
-      <c r="J54" s="79"/>
-      <c r="K54" s="79"/>
-      <c r="L54" s="79"/>
-      <c r="M54" s="80"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
+      <c r="I54" s="83"/>
+      <c r="J54" s="83"/>
+      <c r="K54" s="83"/>
+      <c r="L54" s="83"/>
+      <c r="M54" s="84"/>
       <c r="N54" t="s">
         <v>394</v>
       </c>
@@ -8510,16 +8555,16 @@
       <c r="E55" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="F55" s="78" t="s">
+      <c r="F55" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="G55" s="79"/>
-      <c r="H55" s="79"/>
-      <c r="I55" s="79"/>
-      <c r="J55" s="79"/>
-      <c r="K55" s="79"/>
-      <c r="L55" s="79"/>
-      <c r="M55" s="80"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="83"/>
+      <c r="J55" s="83"/>
+      <c r="K55" s="83"/>
+      <c r="L55" s="83"/>
+      <c r="M55" s="84"/>
       <c r="N55" t="s">
         <v>395</v>
       </c>
@@ -8534,16 +8579,16 @@
       <c r="E56" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="F56" s="78" t="s">
+      <c r="F56" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="G56" s="79"/>
-      <c r="H56" s="79"/>
-      <c r="I56" s="79"/>
-      <c r="J56" s="79"/>
-      <c r="K56" s="79"/>
-      <c r="L56" s="79"/>
-      <c r="M56" s="80"/>
+      <c r="G56" s="83"/>
+      <c r="H56" s="83"/>
+      <c r="I56" s="83"/>
+      <c r="J56" s="83"/>
+      <c r="K56" s="83"/>
+      <c r="L56" s="83"/>
+      <c r="M56" s="84"/>
       <c r="N56" t="s">
         <v>396</v>
       </c>
@@ -8558,16 +8603,16 @@
       <c r="E57" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="F57" s="78" t="s">
+      <c r="F57" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="79"/>
-      <c r="H57" s="79"/>
-      <c r="I57" s="79"/>
-      <c r="J57" s="79"/>
-      <c r="K57" s="79"/>
-      <c r="L57" s="79"/>
-      <c r="M57" s="80"/>
+      <c r="G57" s="83"/>
+      <c r="H57" s="83"/>
+      <c r="I57" s="83"/>
+      <c r="J57" s="83"/>
+      <c r="K57" s="83"/>
+      <c r="L57" s="83"/>
+      <c r="M57" s="84"/>
       <c r="N57" t="s">
         <v>397</v>
       </c>
@@ -8582,16 +8627,16 @@
       <c r="E58" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="F58" s="78" t="s">
+      <c r="F58" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="G58" s="79"/>
-      <c r="H58" s="79"/>
-      <c r="I58" s="79"/>
-      <c r="J58" s="79"/>
-      <c r="K58" s="79"/>
-      <c r="L58" s="79"/>
-      <c r="M58" s="80"/>
+      <c r="G58" s="83"/>
+      <c r="H58" s="83"/>
+      <c r="I58" s="83"/>
+      <c r="J58" s="83"/>
+      <c r="K58" s="83"/>
+      <c r="L58" s="83"/>
+      <c r="M58" s="84"/>
       <c r="N58" t="s">
         <v>398</v>
       </c>
@@ -8606,16 +8651,16 @@
       <c r="E59" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="F59" s="78" t="s">
+      <c r="F59" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="G59" s="79"/>
-      <c r="H59" s="79"/>
-      <c r="I59" s="79"/>
-      <c r="J59" s="79"/>
-      <c r="K59" s="79"/>
-      <c r="L59" s="79"/>
-      <c r="M59" s="80"/>
+      <c r="G59" s="83"/>
+      <c r="H59" s="83"/>
+      <c r="I59" s="83"/>
+      <c r="J59" s="83"/>
+      <c r="K59" s="83"/>
+      <c r="L59" s="83"/>
+      <c r="M59" s="84"/>
       <c r="N59" t="s">
         <v>399</v>
       </c>
@@ -8630,16 +8675,16 @@
       <c r="E60" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="F60" s="78" t="s">
+      <c r="F60" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="G60" s="79"/>
-      <c r="H60" s="79"/>
-      <c r="I60" s="79"/>
-      <c r="J60" s="79"/>
-      <c r="K60" s="79"/>
-      <c r="L60" s="79"/>
-      <c r="M60" s="80"/>
+      <c r="G60" s="83"/>
+      <c r="H60" s="83"/>
+      <c r="I60" s="83"/>
+      <c r="J60" s="83"/>
+      <c r="K60" s="83"/>
+      <c r="L60" s="83"/>
+      <c r="M60" s="84"/>
       <c r="N60" t="s">
         <v>400</v>
       </c>
@@ -8654,14 +8699,14 @@
       <c r="E61" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F61" s="103"/>
-      <c r="G61" s="104"/>
-      <c r="H61" s="104"/>
-      <c r="I61" s="104"/>
-      <c r="J61" s="104"/>
-      <c r="K61" s="104"/>
-      <c r="L61" s="104"/>
-      <c r="M61" s="105"/>
+      <c r="F61" s="112"/>
+      <c r="G61" s="113"/>
+      <c r="H61" s="113"/>
+      <c r="I61" s="113"/>
+      <c r="J61" s="113"/>
+      <c r="K61" s="113"/>
+      <c r="L61" s="113"/>
+      <c r="M61" s="114"/>
     </row>
     <row r="62" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="63" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8686,44 +8731,30 @@
       <c r="J63" s="54" t="s">
         <v>299</v>
       </c>
-      <c r="K63" s="84"/>
-      <c r="L63" s="86"/>
+      <c r="K63" s="75"/>
+      <c r="L63" s="77"/>
       <c r="M63" s="54" t="s">
         <v>298</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F59:M59"/>
-    <mergeCell ref="F60:M60"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F55:M55"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="F47:M47"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F23:M23"/>
-    <mergeCell ref="F20:M20"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="F11:M11"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="F61:M61"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="F51:K51"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="F16:M16"/>
     <mergeCell ref="F17:M17"/>
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="F26:M26"/>
@@ -8740,22 +8771,36 @@
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="F34:J34"/>
     <mergeCell ref="F21:M21"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="F11:M11"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="F61:M61"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="F51:K51"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="F20:M20"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="F47:M47"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F59:M59"/>
+    <mergeCell ref="F60:M60"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F55:M55"/>
+    <mergeCell ref="F56:M56"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6B71DE-697D-4C18-AEEB-DB905B203FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60D3DAD-70F2-48D1-94E6-8A6C2442B03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="410">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -1399,62 +1399,6 @@
   </si>
   <si>
     <t>RAM Mode=0 の時のみ利用可能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#17) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#18) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#23) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#24) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#25) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#26) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#27) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#36) のときのみ利用可能</t>
-    <rPh sb="47" eb="51">
-      <t>リヨウカノウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2144,10 +2088,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>0: OFF,～128: MAX, RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#36) のときのみ利用可能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>モジュール</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2157,6 +2097,17 @@
   </si>
   <si>
     <t>SCC Volume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#15) のときのみ利用可能</t>
+    <rPh sb="47" eb="51">
+      <t>リヨウカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0: OFF,～128: MAX, RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#15) のときのみ利用可能</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2894,6 +2845,45 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2903,30 +2893,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2945,19 +2914,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2978,13 +2941,37 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3003,42 +2990,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3777,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -3826,16 +3777,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.15">
@@ -3846,13 +3797,13 @@
         <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.15">
@@ -3954,7 +3905,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>23</v>
@@ -3969,7 +3920,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>11</v>
@@ -4022,7 +3973,7 @@
         <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="G3" s="68" t="s">
         <v>71</v>
@@ -4065,18 +4016,18 @@
       <c r="F4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="75"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="77"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="67" t="s">
         <v>278</v>
       </c>
       <c r="O4" s="52" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4092,16 +4043,16 @@
       <c r="F5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="92" t="s">
+      <c r="G5" s="79" t="s">
         <v>279</v>
       </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="94"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="81"/>
       <c r="O5" s="50" t="s">
         <v>282</v>
       </c>
@@ -4119,16 +4070,16 @@
       <c r="F6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="92" t="s">
+      <c r="G6" s="79" t="s">
         <v>279</v>
       </c>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="94"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="81"/>
       <c r="O6" s="50" t="s">
         <v>282</v>
       </c>
@@ -4146,16 +4097,16 @@
       <c r="F7" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="92" t="s">
+      <c r="G7" s="79" t="s">
         <v>279</v>
       </c>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="94"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="81"/>
       <c r="O7" s="50" t="s">
         <v>282</v>
       </c>
@@ -4173,16 +4124,16 @@
       <c r="F8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="92" t="s">
+      <c r="G8" s="79" t="s">
         <v>279</v>
       </c>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
-      <c r="N8" s="94"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="81"/>
       <c r="O8" s="50" t="s">
         <v>282</v>
       </c>
@@ -4200,16 +4151,16 @@
       <c r="F9" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="78" t="s">
+      <c r="G9" s="76" t="s">
         <v>280</v>
       </c>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79"/>
-      <c r="L9" s="79"/>
-      <c r="M9" s="79"/>
-      <c r="N9" s="80"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="78"/>
       <c r="O9" s="50" t="s">
         <v>283</v>
       </c>
@@ -4227,16 +4178,16 @@
       <c r="F10" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="78" t="s">
+      <c r="G10" s="76" t="s">
         <v>280</v>
       </c>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="80"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="77"/>
+      <c r="N10" s="78"/>
       <c r="O10" s="50" t="s">
         <v>283</v>
       </c>
@@ -4252,7 +4203,7 @@
         <v>262</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G11" s="82" t="s">
         <v>262</v>
@@ -4265,7 +4216,7 @@
       <c r="M11" s="83"/>
       <c r="N11" s="84"/>
       <c r="O11" s="51" t="s">
-        <v>284</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4279,7 +4230,7 @@
         <v>263</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G12" s="82" t="s">
         <v>263</v>
@@ -4292,7 +4243,7 @@
       <c r="M12" s="83"/>
       <c r="N12" s="84"/>
       <c r="O12" s="51" t="s">
-        <v>285</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4303,13 +4254,13 @@
         <v>35</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G13" s="85" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="H13" s="83"/>
       <c r="I13" s="83"/>
@@ -4319,7 +4270,7 @@
       <c r="M13" s="83"/>
       <c r="N13" s="84"/>
       <c r="O13" s="51" t="s">
-        <v>286</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4330,13 +4281,13 @@
         <v>35</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G14" s="85" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="H14" s="83"/>
       <c r="I14" s="83"/>
@@ -4346,7 +4297,7 @@
       <c r="M14" s="83"/>
       <c r="N14" s="84"/>
       <c r="O14" s="51" t="s">
-        <v>287</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4357,23 +4308,23 @@
         <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="G15" s="86" t="s">
-        <v>374</v>
-      </c>
-      <c r="H15" s="87"/>
-      <c r="I15" s="87"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="87"/>
-      <c r="L15" s="87"/>
-      <c r="M15" s="87"/>
-      <c r="N15" s="88"/>
+        <v>309</v>
+      </c>
+      <c r="G15" s="92" t="s">
+        <v>366</v>
+      </c>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="93"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="94"/>
       <c r="O15" s="51" t="s">
-        <v>288</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4384,23 +4335,23 @@
         <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="G16" s="86" t="s">
-        <v>411</v>
-      </c>
-      <c r="H16" s="87"/>
-      <c r="I16" s="87"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="87"/>
-      <c r="L16" s="87"/>
-      <c r="M16" s="87"/>
-      <c r="N16" s="88"/>
+        <v>309</v>
+      </c>
+      <c r="G16" s="92" t="s">
+        <v>403</v>
+      </c>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="93"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="93"/>
+      <c r="N16" s="94"/>
       <c r="O16" s="51" t="s">
-        <v>289</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4414,25 +4365,25 @@
         <v>264</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="G17" s="89"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="90"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="90"/>
-      <c r="M17" s="91"/>
+        <v>309</v>
+      </c>
+      <c r="G17" s="95"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="97"/>
       <c r="N17" s="11" t="s">
         <v>5</v>
       </c>
       <c r="O17" s="51" t="s">
-        <v>290</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>35</v>
@@ -4441,141 +4392,141 @@
         <v>265</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>313</v>
-      </c>
-      <c r="H18" s="75"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="77"/>
+        <v>305</v>
+      </c>
+      <c r="H18" s="88"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="90"/>
       <c r="M18" s="33" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="45" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="O18" s="51" t="s">
-        <v>291</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="12" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G19" s="85"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="95"/>
-      <c r="K19" s="95"/>
-      <c r="L19" s="95"/>
-      <c r="M19" s="95"/>
-      <c r="N19" s="96"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="86"/>
+      <c r="N19" s="87"/>
       <c r="O19" s="51" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="20" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="12" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G20" s="85"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="95"/>
-      <c r="K20" s="95"/>
-      <c r="L20" s="95"/>
-      <c r="M20" s="95"/>
-      <c r="N20" s="96"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="86"/>
+      <c r="N20" s="87"/>
       <c r="O20" s="51" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="12" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="G21" s="85"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="86"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="86"/>
+      <c r="N21" s="87"/>
+      <c r="O21" s="51" t="s">
         <v>409</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="G21" s="85"/>
-      <c r="H21" s="95"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="95"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="95"/>
-      <c r="M21" s="95"/>
-      <c r="N21" s="96"/>
-      <c r="O21" s="51" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="22" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="12" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G22" s="85"/>
-      <c r="H22" s="95"/>
-      <c r="I22" s="95"/>
-      <c r="J22" s="95"/>
-      <c r="K22" s="95"/>
-      <c r="L22" s="95"/>
-      <c r="M22" s="95"/>
-      <c r="N22" s="96"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="86"/>
+      <c r="J22" s="86"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="86"/>
+      <c r="M22" s="86"/>
+      <c r="N22" s="87"/>
       <c r="O22" s="51" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="23" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="12" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G23" s="72"/>
-      <c r="H23" s="123"/>
+      <c r="H23" s="75"/>
       <c r="I23" s="73"/>
       <c r="J23" s="73"/>
       <c r="K23" s="73"/>
@@ -4583,12 +4534,12 @@
       <c r="M23" s="73"/>
       <c r="N23" s="74"/>
       <c r="O23" s="51" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="64" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>35</v>
@@ -4599,23 +4550,23 @@
       <c r="F24" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="78" t="s">
+      <c r="G24" s="76" t="s">
         <v>280</v>
       </c>
-      <c r="H24" s="81"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="79"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="80"/>
+      <c r="H24" s="91"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
+      <c r="K24" s="77"/>
+      <c r="L24" s="77"/>
+      <c r="M24" s="77"/>
+      <c r="N24" s="78"/>
       <c r="O24" s="50" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="25" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="66" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>35</v>
@@ -4626,32 +4577,22 @@
       <c r="F25" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="78" t="s">
+      <c r="G25" s="76" t="s">
         <v>280</v>
       </c>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="80"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
+      <c r="L25" s="77"/>
+      <c r="M25" s="77"/>
+      <c r="N25" s="78"/>
       <c r="O25" s="50" t="s">
         <v>283</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="G25:N25"/>
-    <mergeCell ref="G5:N5"/>
-    <mergeCell ref="G6:N6"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="G8:N8"/>
-    <mergeCell ref="G12:N12"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="G21:N21"/>
-    <mergeCell ref="G22:N22"/>
     <mergeCell ref="G4:M4"/>
     <mergeCell ref="G9:N9"/>
     <mergeCell ref="G10:N10"/>
@@ -4663,6 +4604,16 @@
     <mergeCell ref="G16:N16"/>
     <mergeCell ref="G17:M17"/>
     <mergeCell ref="H18:L18"/>
+    <mergeCell ref="G25:N25"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="G6:N6"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="G8:N8"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="G19:N19"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G21:N21"/>
+    <mergeCell ref="G22:N22"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4680,7 +4631,7 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
@@ -4734,7 +4685,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4782,16 +4733,16 @@
       <c r="E12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="103" t="s">
+      <c r="F12" s="98" t="s">
         <v>182</v>
       </c>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="105"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="100"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
@@ -4807,12 +4758,12 @@
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="103" t="s">
+      <c r="J13" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="105"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="100"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
@@ -4824,16 +4775,16 @@
       <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="103" t="s">
+      <c r="F14" s="98" t="s">
         <v>182</v>
       </c>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="105"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="99"/>
+      <c r="L14" s="99"/>
+      <c r="M14" s="100"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
@@ -4849,12 +4800,12 @@
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="36"/>
-      <c r="J15" s="103" t="s">
+      <c r="J15" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="K15" s="104"/>
-      <c r="L15" s="104"/>
-      <c r="M15" s="105"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="99"/>
+      <c r="M15" s="100"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="19" t="s">
@@ -4866,16 +4817,16 @@
       <c r="E16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="103" t="s">
+      <c r="F16" s="98" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="104"/>
-      <c r="M16" s="105"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="100"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="19" t="s">
@@ -4891,12 +4842,12 @@
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
-      <c r="J17" s="103" t="s">
+      <c r="J17" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="104"/>
-      <c r="L17" s="104"/>
-      <c r="M17" s="105"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="100"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="19" t="s">
@@ -4911,13 +4862,13 @@
       <c r="F18" s="34"/>
       <c r="G18" s="35"/>
       <c r="H18" s="36"/>
-      <c r="I18" s="103" t="s">
+      <c r="I18" s="98" t="s">
         <v>184</v>
       </c>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="105"/>
+      <c r="J18" s="99"/>
+      <c r="K18" s="99"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="100"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="19" t="s">
@@ -4970,12 +4921,12 @@
       <c r="I20" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="103" t="s">
+      <c r="J20" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="105"/>
+      <c r="K20" s="99"/>
+      <c r="L20" s="99"/>
+      <c r="M20" s="100"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
@@ -4993,12 +4944,12 @@
       <c r="I21" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="103" t="s">
+      <c r="J21" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="K21" s="104"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="105"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="99"/>
+      <c r="M21" s="100"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
@@ -5016,12 +4967,12 @@
       <c r="I22" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="103" t="s">
+      <c r="J22" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="K22" s="104"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="105"/>
+      <c r="K22" s="99"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="100"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
@@ -5033,16 +4984,16 @@
       <c r="E23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F23" s="103" t="s">
+      <c r="F23" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="G23" s="104"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="105"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="99"/>
+      <c r="I23" s="99"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="99"/>
+      <c r="L23" s="99"/>
+      <c r="M23" s="100"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
@@ -5054,16 +5005,16 @@
       <c r="E24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="103" t="s">
+      <c r="F24" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="105"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="99"/>
+      <c r="L24" s="99"/>
+      <c r="M24" s="100"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
@@ -5079,12 +5030,12 @@
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
       <c r="I25" s="36"/>
-      <c r="J25" s="103" t="s">
+      <c r="J25" s="98" t="s">
         <v>188</v>
       </c>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="105"/>
+      <c r="K25" s="99"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="100"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
@@ -5137,13 +5088,13 @@
       <c r="F28" s="85" t="s">
         <v>182</v>
       </c>
-      <c r="G28" s="95"/>
-      <c r="H28" s="95"/>
-      <c r="I28" s="95"/>
-      <c r="J28" s="95"/>
-      <c r="K28" s="95"/>
-      <c r="L28" s="95"/>
-      <c r="M28" s="96"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="87"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="19" t="s">
@@ -5162,9 +5113,9 @@
       <c r="J29" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="K29" s="95"/>
-      <c r="L29" s="95"/>
-      <c r="M29" s="96"/>
+      <c r="K29" s="86"/>
+      <c r="L29" s="86"/>
+      <c r="M29" s="87"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
@@ -5179,13 +5130,13 @@
       <c r="F30" s="85" t="s">
         <v>182</v>
       </c>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
-      <c r="I30" s="95"/>
-      <c r="J30" s="95"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="95"/>
-      <c r="M30" s="96"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="K30" s="86"/>
+      <c r="L30" s="86"/>
+      <c r="M30" s="87"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
@@ -5204,9 +5155,9 @@
       <c r="J31" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="K31" s="95"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="96"/>
+      <c r="K31" s="86"/>
+      <c r="L31" s="86"/>
+      <c r="M31" s="87"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
@@ -5221,13 +5172,13 @@
       <c r="F32" s="85" t="s">
         <v>182</v>
       </c>
-      <c r="G32" s="95"/>
-      <c r="H32" s="95"/>
-      <c r="I32" s="95"/>
-      <c r="J32" s="95"/>
-      <c r="K32" s="95"/>
-      <c r="L32" s="95"/>
-      <c r="M32" s="96"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="K32" s="86"/>
+      <c r="L32" s="86"/>
+      <c r="M32" s="87"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
@@ -5246,9 +5197,9 @@
       <c r="J33" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="K33" s="95"/>
-      <c r="L33" s="95"/>
-      <c r="M33" s="96"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="87"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
@@ -5266,10 +5217,10 @@
       <c r="I34" s="85" t="s">
         <v>184</v>
       </c>
-      <c r="J34" s="95"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="95"/>
-      <c r="M34" s="96"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="86"/>
+      <c r="M34" s="87"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
@@ -5325,9 +5276,9 @@
       <c r="J36" s="85" t="s">
         <v>185</v>
       </c>
-      <c r="K36" s="95"/>
-      <c r="L36" s="95"/>
-      <c r="M36" s="96"/>
+      <c r="K36" s="86"/>
+      <c r="L36" s="86"/>
+      <c r="M36" s="87"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
@@ -5348,9 +5299,9 @@
       <c r="J37" s="85" t="s">
         <v>185</v>
       </c>
-      <c r="K37" s="95"/>
-      <c r="L37" s="95"/>
-      <c r="M37" s="96"/>
+      <c r="K37" s="86"/>
+      <c r="L37" s="86"/>
+      <c r="M37" s="87"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
@@ -5371,9 +5322,9 @@
       <c r="J38" s="85" t="s">
         <v>185</v>
       </c>
-      <c r="K38" s="95"/>
-      <c r="L38" s="95"/>
-      <c r="M38" s="96"/>
+      <c r="K38" s="86"/>
+      <c r="L38" s="86"/>
+      <c r="M38" s="87"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
@@ -5388,13 +5339,13 @@
       <c r="F39" s="85" t="s">
         <v>186</v>
       </c>
-      <c r="G39" s="95"/>
-      <c r="H39" s="95"/>
-      <c r="I39" s="95"/>
-      <c r="J39" s="95"/>
-      <c r="K39" s="95"/>
-      <c r="L39" s="95"/>
-      <c r="M39" s="96"/>
+      <c r="G39" s="86"/>
+      <c r="H39" s="86"/>
+      <c r="I39" s="86"/>
+      <c r="J39" s="86"/>
+      <c r="K39" s="86"/>
+      <c r="L39" s="86"/>
+      <c r="M39" s="87"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="19" t="s">
@@ -5409,13 +5360,13 @@
       <c r="F40" s="85" t="s">
         <v>187</v>
       </c>
-      <c r="G40" s="95"/>
-      <c r="H40" s="95"/>
-      <c r="I40" s="95"/>
-      <c r="J40" s="95"/>
-      <c r="K40" s="95"/>
-      <c r="L40" s="95"/>
-      <c r="M40" s="96"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="86"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="86"/>
+      <c r="K40" s="86"/>
+      <c r="L40" s="86"/>
+      <c r="M40" s="87"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="19" t="s">
@@ -5434,9 +5385,9 @@
       <c r="J41" s="85" t="s">
         <v>188</v>
       </c>
-      <c r="K41" s="95"/>
-      <c r="L41" s="95"/>
-      <c r="M41" s="96"/>
+      <c r="K41" s="86"/>
+      <c r="L41" s="86"/>
+      <c r="M41" s="87"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="19" t="s">
@@ -5471,12 +5422,12 @@
       <c r="G43" s="70"/>
       <c r="H43" s="70"/>
       <c r="I43" s="71"/>
-      <c r="J43" s="100" t="s">
+      <c r="J43" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="K43" s="101"/>
-      <c r="L43" s="101"/>
-      <c r="M43" s="102"/>
+      <c r="K43" s="105"/>
+      <c r="L43" s="105"/>
+      <c r="M43" s="106"/>
     </row>
     <row r="44" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
@@ -5486,20 +5437,20 @@
         <v>30</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="F44" s="97" t="s">
+        <v>338</v>
+      </c>
+      <c r="F44" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="G44" s="98"/>
-      <c r="H44" s="98"/>
-      <c r="I44" s="98"/>
-      <c r="J44" s="98"/>
-      <c r="K44" s="98"/>
-      <c r="L44" s="98"/>
-      <c r="M44" s="99"/>
+      <c r="G44" s="102"/>
+      <c r="H44" s="102"/>
+      <c r="I44" s="102"/>
+      <c r="J44" s="102"/>
+      <c r="K44" s="102"/>
+      <c r="L44" s="102"/>
+      <c r="M44" s="103"/>
       <c r="O44" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="45" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5510,49 +5461,49 @@
         <v>30</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="F45" s="97" t="s">
+        <v>354</v>
+      </c>
+      <c r="F45" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="G45" s="98"/>
-      <c r="H45" s="98"/>
-      <c r="I45" s="98"/>
-      <c r="J45" s="98"/>
-      <c r="K45" s="98"/>
-      <c r="L45" s="98"/>
-      <c r="M45" s="99"/>
+      <c r="G45" s="102"/>
+      <c r="H45" s="102"/>
+      <c r="I45" s="102"/>
+      <c r="J45" s="102"/>
+      <c r="K45" s="102"/>
+      <c r="L45" s="102"/>
+      <c r="M45" s="103"/>
       <c r="O45" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="46" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="19" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="F46" s="97" t="s">
+        <v>355</v>
+      </c>
+      <c r="F46" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="G46" s="98"/>
-      <c r="H46" s="98"/>
-      <c r="I46" s="98"/>
-      <c r="J46" s="98"/>
-      <c r="K46" s="98"/>
-      <c r="L46" s="98"/>
-      <c r="M46" s="99"/>
+      <c r="G46" s="102"/>
+      <c r="H46" s="102"/>
+      <c r="I46" s="102"/>
+      <c r="J46" s="102"/>
+      <c r="K46" s="102"/>
+      <c r="L46" s="102"/>
+      <c r="M46" s="103"/>
       <c r="O46" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="47" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="19" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>30</v>
@@ -5571,79 +5522,79 @@
     </row>
     <row r="48" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="19" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="F48" s="97" t="s">
+        <v>358</v>
+      </c>
+      <c r="F48" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="G48" s="98"/>
-      <c r="H48" s="98"/>
-      <c r="I48" s="98"/>
-      <c r="J48" s="98"/>
-      <c r="K48" s="98"/>
-      <c r="L48" s="98"/>
-      <c r="M48" s="99"/>
+      <c r="G48" s="102"/>
+      <c r="H48" s="102"/>
+      <c r="I48" s="102"/>
+      <c r="J48" s="102"/>
+      <c r="K48" s="102"/>
+      <c r="L48" s="102"/>
+      <c r="M48" s="103"/>
       <c r="O48" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="49" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="19" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="F49" s="97" t="s">
+        <v>359</v>
+      </c>
+      <c r="F49" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="G49" s="98"/>
-      <c r="H49" s="98"/>
-      <c r="I49" s="98"/>
-      <c r="J49" s="98"/>
-      <c r="K49" s="98"/>
-      <c r="L49" s="98"/>
-      <c r="M49" s="99"/>
+      <c r="G49" s="102"/>
+      <c r="H49" s="102"/>
+      <c r="I49" s="102"/>
+      <c r="J49" s="102"/>
+      <c r="K49" s="102"/>
+      <c r="L49" s="102"/>
+      <c r="M49" s="103"/>
       <c r="O49" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="50" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="19" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="F50" s="97" t="s">
+        <v>360</v>
+      </c>
+      <c r="F50" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="G50" s="98"/>
-      <c r="H50" s="98"/>
-      <c r="I50" s="98"/>
-      <c r="J50" s="98"/>
-      <c r="K50" s="98"/>
-      <c r="L50" s="98"/>
-      <c r="M50" s="99"/>
+      <c r="G50" s="102"/>
+      <c r="H50" s="102"/>
+      <c r="I50" s="102"/>
+      <c r="J50" s="102"/>
+      <c r="K50" s="102"/>
+      <c r="L50" s="102"/>
+      <c r="M50" s="103"/>
       <c r="O50" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="51" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>30</v>
@@ -5662,79 +5613,79 @@
     </row>
     <row r="52" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="F52" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G52" s="95"/>
-      <c r="H52" s="95"/>
-      <c r="I52" s="95"/>
-      <c r="J52" s="95"/>
-      <c r="K52" s="95"/>
-      <c r="L52" s="95"/>
-      <c r="M52" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G52" s="86"/>
+      <c r="H52" s="86"/>
+      <c r="I52" s="86"/>
+      <c r="J52" s="86"/>
+      <c r="K52" s="86"/>
+      <c r="L52" s="86"/>
+      <c r="M52" s="87"/>
       <c r="O52" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="F53" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G53" s="95"/>
-      <c r="H53" s="95"/>
-      <c r="I53" s="95"/>
-      <c r="J53" s="95"/>
-      <c r="K53" s="95"/>
-      <c r="L53" s="95"/>
-      <c r="M53" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G53" s="86"/>
+      <c r="H53" s="86"/>
+      <c r="I53" s="86"/>
+      <c r="J53" s="86"/>
+      <c r="K53" s="86"/>
+      <c r="L53" s="86"/>
+      <c r="M53" s="87"/>
       <c r="O53" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="54" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F54" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G54" s="95"/>
-      <c r="H54" s="95"/>
-      <c r="I54" s="95"/>
-      <c r="J54" s="95"/>
-      <c r="K54" s="95"/>
-      <c r="L54" s="95"/>
-      <c r="M54" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G54" s="86"/>
+      <c r="H54" s="86"/>
+      <c r="I54" s="86"/>
+      <c r="J54" s="86"/>
+      <c r="K54" s="86"/>
+      <c r="L54" s="86"/>
+      <c r="M54" s="87"/>
       <c r="O54" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>30</v>
@@ -5753,79 +5704,79 @@
     </row>
     <row r="56" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="F56" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G56" s="95"/>
-      <c r="H56" s="95"/>
-      <c r="I56" s="95"/>
-      <c r="J56" s="95"/>
-      <c r="K56" s="95"/>
-      <c r="L56" s="95"/>
-      <c r="M56" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G56" s="86"/>
+      <c r="H56" s="86"/>
+      <c r="I56" s="86"/>
+      <c r="J56" s="86"/>
+      <c r="K56" s="86"/>
+      <c r="L56" s="86"/>
+      <c r="M56" s="87"/>
       <c r="O56" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="19" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="F57" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G57" s="95"/>
-      <c r="H57" s="95"/>
-      <c r="I57" s="95"/>
-      <c r="J57" s="95"/>
-      <c r="K57" s="95"/>
-      <c r="L57" s="95"/>
-      <c r="M57" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G57" s="86"/>
+      <c r="H57" s="86"/>
+      <c r="I57" s="86"/>
+      <c r="J57" s="86"/>
+      <c r="K57" s="86"/>
+      <c r="L57" s="86"/>
+      <c r="M57" s="87"/>
       <c r="O57" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="F58" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G58" s="95"/>
-      <c r="H58" s="95"/>
-      <c r="I58" s="95"/>
-      <c r="J58" s="95"/>
-      <c r="K58" s="95"/>
-      <c r="L58" s="95"/>
-      <c r="M58" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G58" s="86"/>
+      <c r="H58" s="86"/>
+      <c r="I58" s="86"/>
+      <c r="J58" s="86"/>
+      <c r="K58" s="86"/>
+      <c r="L58" s="86"/>
+      <c r="M58" s="87"/>
       <c r="O58" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C59" s="20" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>30</v>
@@ -5863,6 +5814,29 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F48:M48"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="J31:M31"/>
     <mergeCell ref="J33:M33"/>
     <mergeCell ref="I34:M34"/>
     <mergeCell ref="J36:M36"/>
@@ -5879,29 +5853,6 @@
     <mergeCell ref="J22:M22"/>
     <mergeCell ref="F23:M23"/>
     <mergeCell ref="F24:M24"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="F45:M45"/>
-    <mergeCell ref="F46:M46"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F48:M48"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="F50:M50"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F54:M54"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5976,16 +5927,16 @@
       <c r="E6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="86" t="s">
+      <c r="F6" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="87"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="88"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="94"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
@@ -5997,20 +5948,20 @@
       <c r="E7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="86" t="s">
+      <c r="F7" s="92" t="s">
         <v>181</v>
       </c>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="87"/>
-      <c r="L7" s="87"/>
-      <c r="M7" s="88"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="94"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -6068,12 +6019,12 @@
       <c r="I19" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="86" t="s">
+      <c r="J19" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="87"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="88"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="93"/>
+      <c r="M19" s="94"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="19" t="s">
@@ -6095,12 +6046,12 @@
       <c r="I20" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="86" t="s">
+      <c r="J20" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="87"/>
-      <c r="L20" s="87"/>
-      <c r="M20" s="88"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="94"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
@@ -6110,18 +6061,18 @@
         <v>35</v>
       </c>
       <c r="E21" s="6"/>
-      <c r="F21" s="86" t="s">
+      <c r="F21" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="88"/>
-      <c r="H21" s="86" t="s">
+      <c r="G21" s="94"/>
+      <c r="H21" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="87"/>
-      <c r="J21" s="87"/>
-      <c r="K21" s="87"/>
-      <c r="L21" s="87"/>
-      <c r="M21" s="88"/>
+      <c r="I21" s="93"/>
+      <c r="J21" s="93"/>
+      <c r="K21" s="93"/>
+      <c r="L21" s="93"/>
+      <c r="M21" s="94"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
@@ -6131,10 +6082,10 @@
         <v>35</v>
       </c>
       <c r="E22" s="6"/>
-      <c r="F22" s="86" t="s">
+      <c r="F22" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="88"/>
+      <c r="G22" s="94"/>
       <c r="H22" s="18"/>
       <c r="I22" s="11" t="s">
         <v>114</v>
@@ -6142,11 +6093,11 @@
       <c r="J22" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="K22" s="86" t="s">
+      <c r="K22" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="L22" s="87"/>
-      <c r="M22" s="88"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="94"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
@@ -6156,18 +6107,18 @@
         <v>35</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="86" t="s">
+      <c r="F23" s="92" t="s">
         <v>115</v>
       </c>
-      <c r="G23" s="87"/>
-      <c r="H23" s="87"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="86" t="s">
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="92" t="s">
         <v>116</v>
       </c>
-      <c r="K23" s="87"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="88"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="94"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
@@ -6177,18 +6128,18 @@
         <v>35</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="86" t="s">
+      <c r="F24" s="92" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="86" t="s">
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="94"/>
+      <c r="J24" s="92" t="s">
         <v>116</v>
       </c>
-      <c r="K24" s="87"/>
-      <c r="L24" s="87"/>
-      <c r="M24" s="88"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="94"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
@@ -6198,18 +6149,18 @@
         <v>35</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="86" t="s">
+      <c r="F25" s="92" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="88"/>
-      <c r="J25" s="86" t="s">
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="94"/>
+      <c r="J25" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
-      <c r="M25" s="88"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="94"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
@@ -6219,18 +6170,18 @@
         <v>35</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="86" t="s">
+      <c r="F26" s="92" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="86" t="s">
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="88"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
+      <c r="M26" s="94"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="19" t="s">
@@ -6284,16 +6235,16 @@
       <c r="E29" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="86" t="s">
+      <c r="F29" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G29" s="87"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="88"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="93"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="93"/>
+      <c r="M29" s="94"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
@@ -6303,16 +6254,16 @@
         <v>35</v>
       </c>
       <c r="E30" s="6"/>
-      <c r="F30" s="86" t="s">
+      <c r="F30" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G30" s="87"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="88"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="94"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
@@ -6322,16 +6273,16 @@
         <v>35</v>
       </c>
       <c r="E31" s="6"/>
-      <c r="F31" s="86" t="s">
+      <c r="F31" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G31" s="87"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="88"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="94"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
@@ -6341,16 +6292,16 @@
         <v>35</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="86" t="s">
+      <c r="F32" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G32" s="87"/>
-      <c r="H32" s="87"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="K32" s="87"/>
-      <c r="L32" s="87"/>
-      <c r="M32" s="88"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="94"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
@@ -6360,16 +6311,16 @@
         <v>35</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="86" t="s">
+      <c r="F33" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="88"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="94"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
@@ -6379,16 +6330,16 @@
         <v>35</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="86" t="s">
+      <c r="F34" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="87"/>
-      <c r="I34" s="87"/>
-      <c r="J34" s="87"/>
-      <c r="K34" s="87"/>
-      <c r="L34" s="87"/>
-      <c r="M34" s="88"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="93"/>
+      <c r="M34" s="94"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
@@ -6398,16 +6349,16 @@
         <v>35</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="86" t="s">
+      <c r="F35" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G35" s="87"/>
-      <c r="H35" s="87"/>
-      <c r="I35" s="87"/>
-      <c r="J35" s="87"/>
-      <c r="K35" s="87"/>
-      <c r="L35" s="87"/>
-      <c r="M35" s="88"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93"/>
+      <c r="J35" s="93"/>
+      <c r="K35" s="93"/>
+      <c r="L35" s="93"/>
+      <c r="M35" s="94"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="19" t="s">
@@ -6417,16 +6368,16 @@
         <v>35</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="86" t="s">
+      <c r="F36" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G36" s="87"/>
-      <c r="H36" s="87"/>
-      <c r="I36" s="87"/>
-      <c r="J36" s="87"/>
-      <c r="K36" s="87"/>
-      <c r="L36" s="87"/>
-      <c r="M36" s="88"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
+      <c r="J36" s="93"/>
+      <c r="K36" s="93"/>
+      <c r="L36" s="93"/>
+      <c r="M36" s="94"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
@@ -6436,16 +6387,16 @@
         <v>35</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="86" t="s">
+      <c r="F37" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G37" s="87"/>
-      <c r="H37" s="87"/>
-      <c r="I37" s="87"/>
-      <c r="J37" s="87"/>
-      <c r="K37" s="87"/>
-      <c r="L37" s="87"/>
-      <c r="M37" s="88"/>
+      <c r="G37" s="93"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93"/>
+      <c r="J37" s="93"/>
+      <c r="K37" s="93"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="94"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
@@ -6455,16 +6406,16 @@
         <v>35</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="86" t="s">
+      <c r="F38" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G38" s="87"/>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="88"/>
+      <c r="G38" s="93"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
+      <c r="J38" s="93"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="94"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
@@ -6499,11 +6450,11 @@
       <c r="I40" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J40" s="86" t="s">
+      <c r="J40" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="K40" s="87"/>
-      <c r="L40" s="88"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="94"/>
       <c r="M40" s="13" t="s">
         <v>145</v>
       </c>
@@ -6524,11 +6475,11 @@
       <c r="I41" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J41" s="86" t="s">
+      <c r="J41" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="K41" s="87"/>
-      <c r="L41" s="88"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="94"/>
       <c r="M41" s="13" t="s">
         <v>145</v>
       </c>
@@ -6549,11 +6500,11 @@
       <c r="I42" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J42" s="86" t="s">
+      <c r="J42" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="K42" s="87"/>
-      <c r="L42" s="88"/>
+      <c r="K42" s="93"/>
+      <c r="L42" s="94"/>
       <c r="M42" s="13" t="s">
         <v>145</v>
       </c>
@@ -6574,11 +6525,11 @@
       <c r="I43" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J43" s="86" t="s">
+      <c r="J43" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="K43" s="87"/>
-      <c r="L43" s="88"/>
+      <c r="K43" s="93"/>
+      <c r="L43" s="94"/>
       <c r="M43" s="13" t="s">
         <v>145</v>
       </c>
@@ -6599,11 +6550,11 @@
       <c r="I44" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J44" s="86" t="s">
+      <c r="J44" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="K44" s="87"/>
-      <c r="L44" s="88"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="94"/>
       <c r="M44" s="13" t="s">
         <v>145</v>
       </c>
@@ -6624,11 +6575,11 @@
       <c r="I45" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J45" s="86" t="s">
+      <c r="J45" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="K45" s="87"/>
-      <c r="L45" s="88"/>
+      <c r="K45" s="93"/>
+      <c r="L45" s="94"/>
       <c r="M45" s="13" t="s">
         <v>145</v>
       </c>
@@ -6649,11 +6600,11 @@
       <c r="I46" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J46" s="86" t="s">
+      <c r="J46" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="K46" s="87"/>
-      <c r="L46" s="88"/>
+      <c r="K46" s="93"/>
+      <c r="L46" s="94"/>
       <c r="M46" s="13" t="s">
         <v>145</v>
       </c>
@@ -6674,11 +6625,11 @@
       <c r="I47" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J47" s="86" t="s">
+      <c r="J47" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="K47" s="87"/>
-      <c r="L47" s="88"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="94"/>
       <c r="M47" s="13" t="s">
         <v>145</v>
       </c>
@@ -6699,11 +6650,11 @@
       <c r="I48" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J48" s="86" t="s">
+      <c r="J48" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="K48" s="87"/>
-      <c r="L48" s="88"/>
+      <c r="K48" s="93"/>
+      <c r="L48" s="94"/>
       <c r="M48" s="13" t="s">
         <v>145</v>
       </c>
@@ -6733,18 +6684,18 @@
         <v>35</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="86" t="s">
+      <c r="F50" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="G50" s="87"/>
-      <c r="H50" s="87"/>
-      <c r="I50" s="88"/>
-      <c r="J50" s="86" t="s">
+      <c r="G50" s="93"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="94"/>
+      <c r="J50" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="K50" s="87"/>
-      <c r="L50" s="87"/>
-      <c r="M50" s="88"/>
+      <c r="K50" s="93"/>
+      <c r="L50" s="93"/>
+      <c r="M50" s="94"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
@@ -6754,18 +6705,18 @@
         <v>35</v>
       </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="86" t="s">
+      <c r="F51" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="G51" s="87"/>
-      <c r="H51" s="87"/>
-      <c r="I51" s="88"/>
-      <c r="J51" s="86" t="s">
+      <c r="G51" s="93"/>
+      <c r="H51" s="93"/>
+      <c r="I51" s="94"/>
+      <c r="J51" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="K51" s="87"/>
-      <c r="L51" s="87"/>
-      <c r="M51" s="88"/>
+      <c r="K51" s="93"/>
+      <c r="L51" s="93"/>
+      <c r="M51" s="94"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
@@ -6775,18 +6726,18 @@
         <v>35</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="86" t="s">
+      <c r="F52" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="G52" s="87"/>
-      <c r="H52" s="87"/>
-      <c r="I52" s="88"/>
-      <c r="J52" s="86" t="s">
+      <c r="G52" s="93"/>
+      <c r="H52" s="93"/>
+      <c r="I52" s="94"/>
+      <c r="J52" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="K52" s="87"/>
-      <c r="L52" s="87"/>
-      <c r="M52" s="88"/>
+      <c r="K52" s="93"/>
+      <c r="L52" s="93"/>
+      <c r="M52" s="94"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
@@ -6796,18 +6747,18 @@
         <v>35</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="86" t="s">
+      <c r="F53" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="G53" s="87"/>
-      <c r="H53" s="87"/>
-      <c r="I53" s="88"/>
-      <c r="J53" s="86" t="s">
+      <c r="G53" s="93"/>
+      <c r="H53" s="93"/>
+      <c r="I53" s="94"/>
+      <c r="J53" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="K53" s="87"/>
-      <c r="L53" s="87"/>
-      <c r="M53" s="88"/>
+      <c r="K53" s="93"/>
+      <c r="L53" s="93"/>
+      <c r="M53" s="94"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
@@ -6817,18 +6768,18 @@
         <v>35</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="86" t="s">
+      <c r="F54" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="G54" s="87"/>
-      <c r="H54" s="87"/>
-      <c r="I54" s="88"/>
-      <c r="J54" s="86" t="s">
+      <c r="G54" s="93"/>
+      <c r="H54" s="93"/>
+      <c r="I54" s="94"/>
+      <c r="J54" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="K54" s="87"/>
-      <c r="L54" s="87"/>
-      <c r="M54" s="88"/>
+      <c r="K54" s="93"/>
+      <c r="L54" s="93"/>
+      <c r="M54" s="94"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
@@ -6838,18 +6789,18 @@
         <v>35</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="86" t="s">
+      <c r="F55" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="G55" s="87"/>
-      <c r="H55" s="87"/>
-      <c r="I55" s="88"/>
-      <c r="J55" s="86" t="s">
+      <c r="G55" s="93"/>
+      <c r="H55" s="93"/>
+      <c r="I55" s="94"/>
+      <c r="J55" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="K55" s="87"/>
-      <c r="L55" s="87"/>
-      <c r="M55" s="88"/>
+      <c r="K55" s="93"/>
+      <c r="L55" s="93"/>
+      <c r="M55" s="94"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
@@ -6859,18 +6810,18 @@
         <v>35</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="86" t="s">
+      <c r="F56" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="G56" s="87"/>
-      <c r="H56" s="87"/>
-      <c r="I56" s="88"/>
-      <c r="J56" s="86" t="s">
+      <c r="G56" s="93"/>
+      <c r="H56" s="93"/>
+      <c r="I56" s="94"/>
+      <c r="J56" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="K56" s="87"/>
-      <c r="L56" s="87"/>
-      <c r="M56" s="88"/>
+      <c r="K56" s="93"/>
+      <c r="L56" s="93"/>
+      <c r="M56" s="94"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="19" t="s">
@@ -6880,18 +6831,18 @@
         <v>35</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="86" t="s">
+      <c r="F57" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="G57" s="87"/>
-      <c r="H57" s="87"/>
-      <c r="I57" s="88"/>
-      <c r="J57" s="86" t="s">
+      <c r="G57" s="93"/>
+      <c r="H57" s="93"/>
+      <c r="I57" s="94"/>
+      <c r="J57" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="K57" s="87"/>
-      <c r="L57" s="87"/>
-      <c r="M57" s="88"/>
+      <c r="K57" s="93"/>
+      <c r="L57" s="93"/>
+      <c r="M57" s="94"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
@@ -6901,18 +6852,18 @@
         <v>35</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="86" t="s">
+      <c r="F58" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="G58" s="87"/>
-      <c r="H58" s="87"/>
-      <c r="I58" s="88"/>
-      <c r="J58" s="86" t="s">
+      <c r="G58" s="93"/>
+      <c r="H58" s="93"/>
+      <c r="I58" s="94"/>
+      <c r="J58" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="K58" s="87"/>
-      <c r="L58" s="87"/>
-      <c r="M58" s="88"/>
+      <c r="K58" s="93"/>
+      <c r="L58" s="93"/>
+      <c r="M58" s="94"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="19" t="s">
@@ -7122,7 +7073,7 @@
     </row>
     <row r="69" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="19" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>85</v>
@@ -7139,223 +7090,223 @@
     </row>
     <row r="70" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="19" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F70" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G70" s="95"/>
-      <c r="H70" s="95"/>
-      <c r="I70" s="95"/>
-      <c r="J70" s="95"/>
-      <c r="K70" s="95"/>
-      <c r="L70" s="95"/>
-      <c r="M70" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G70" s="86"/>
+      <c r="H70" s="86"/>
+      <c r="I70" s="86"/>
+      <c r="J70" s="86"/>
+      <c r="K70" s="86"/>
+      <c r="L70" s="86"/>
+      <c r="M70" s="87"/>
       <c r="O70" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="19" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F71" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G71" s="95"/>
-      <c r="H71" s="95"/>
-      <c r="I71" s="95"/>
-      <c r="J71" s="95"/>
-      <c r="K71" s="95"/>
-      <c r="L71" s="95"/>
-      <c r="M71" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G71" s="86"/>
+      <c r="H71" s="86"/>
+      <c r="I71" s="86"/>
+      <c r="J71" s="86"/>
+      <c r="K71" s="86"/>
+      <c r="L71" s="86"/>
+      <c r="M71" s="87"/>
       <c r="O71" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C72" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="21" t="s">
-        <v>341</v>
-      </c>
       <c r="F72" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G72" s="95"/>
-      <c r="H72" s="95"/>
-      <c r="I72" s="95"/>
-      <c r="J72" s="95"/>
-      <c r="K72" s="95"/>
-      <c r="L72" s="95"/>
-      <c r="M72" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G72" s="86"/>
+      <c r="H72" s="86"/>
+      <c r="I72" s="86"/>
+      <c r="J72" s="86"/>
+      <c r="K72" s="86"/>
+      <c r="L72" s="86"/>
+      <c r="M72" s="87"/>
       <c r="O72" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C73" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="F73" s="85" t="s">
         <v>334</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="F73" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
-      <c r="I73" s="95"/>
-      <c r="J73" s="95"/>
-      <c r="K73" s="95"/>
-      <c r="L73" s="95"/>
-      <c r="M73" s="96"/>
+      <c r="G73" s="86"/>
+      <c r="H73" s="86"/>
+      <c r="I73" s="86"/>
+      <c r="J73" s="86"/>
+      <c r="K73" s="86"/>
+      <c r="L73" s="86"/>
+      <c r="M73" s="87"/>
       <c r="O73" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C74" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="F74" s="85" t="s">
+        <v>334</v>
+      </c>
+      <c r="G74" s="86"/>
+      <c r="H74" s="86"/>
+      <c r="I74" s="86"/>
+      <c r="J74" s="86"/>
+      <c r="K74" s="86"/>
+      <c r="L74" s="86"/>
+      <c r="M74" s="87"/>
+      <c r="O74" t="s">
         <v>335</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="F74" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G74" s="95"/>
-      <c r="H74" s="95"/>
-      <c r="I74" s="95"/>
-      <c r="J74" s="95"/>
-      <c r="K74" s="95"/>
-      <c r="L74" s="95"/>
-      <c r="M74" s="96"/>
-      <c r="O74" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="75" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C75" s="19" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F75" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G75" s="95"/>
-      <c r="H75" s="95"/>
-      <c r="I75" s="95"/>
-      <c r="J75" s="95"/>
-      <c r="K75" s="95"/>
-      <c r="L75" s="95"/>
-      <c r="M75" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G75" s="86"/>
+      <c r="H75" s="86"/>
+      <c r="I75" s="86"/>
+      <c r="J75" s="86"/>
+      <c r="K75" s="86"/>
+      <c r="L75" s="86"/>
+      <c r="M75" s="87"/>
       <c r="O75" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C76" s="19" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F76" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G76" s="95"/>
-      <c r="H76" s="95"/>
-      <c r="I76" s="95"/>
-      <c r="J76" s="95"/>
-      <c r="K76" s="95"/>
-      <c r="L76" s="95"/>
-      <c r="M76" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G76" s="86"/>
+      <c r="H76" s="86"/>
+      <c r="I76" s="86"/>
+      <c r="J76" s="86"/>
+      <c r="K76" s="86"/>
+      <c r="L76" s="86"/>
+      <c r="M76" s="87"/>
       <c r="O76" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C77" s="19" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F77" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G77" s="95"/>
-      <c r="H77" s="95"/>
-      <c r="I77" s="95"/>
-      <c r="J77" s="95"/>
-      <c r="K77" s="95"/>
-      <c r="L77" s="95"/>
-      <c r="M77" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G77" s="86"/>
+      <c r="H77" s="86"/>
+      <c r="I77" s="86"/>
+      <c r="J77" s="86"/>
+      <c r="K77" s="86"/>
+      <c r="L77" s="86"/>
+      <c r="M77" s="87"/>
       <c r="O77" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C78" s="19" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F78" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="G78" s="95"/>
-      <c r="H78" s="95"/>
-      <c r="I78" s="95"/>
-      <c r="J78" s="95"/>
-      <c r="K78" s="95"/>
-      <c r="L78" s="95"/>
-      <c r="M78" s="96"/>
+        <v>334</v>
+      </c>
+      <c r="G78" s="86"/>
+      <c r="H78" s="86"/>
+      <c r="I78" s="86"/>
+      <c r="J78" s="86"/>
+      <c r="K78" s="86"/>
+      <c r="L78" s="86"/>
+      <c r="M78" s="87"/>
       <c r="O78" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C79" s="19" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>85</v>
@@ -7372,24 +7323,43 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F70:M70"/>
+    <mergeCell ref="F71:M71"/>
+    <mergeCell ref="F72:M72"/>
+    <mergeCell ref="F73:M73"/>
+    <mergeCell ref="F74:M74"/>
+    <mergeCell ref="F75:M75"/>
+    <mergeCell ref="F76:M76"/>
+    <mergeCell ref="F77:M77"/>
+    <mergeCell ref="F78:M78"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="J54:M54"/>
     <mergeCell ref="F51:I51"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="J45:L45"/>
@@ -7406,43 +7376,24 @@
     <mergeCell ref="J44:L44"/>
     <mergeCell ref="J46:L46"/>
     <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="F75:M75"/>
-    <mergeCell ref="F76:M76"/>
-    <mergeCell ref="F77:M77"/>
-    <mergeCell ref="F78:M78"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="F70:M70"/>
-    <mergeCell ref="F71:M71"/>
-    <mergeCell ref="F72:M72"/>
-    <mergeCell ref="F73:M73"/>
-    <mergeCell ref="F74:M74"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="F22:G22"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7489,7 +7440,7 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.15">
@@ -7498,7 +7449,7 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.15">
@@ -7551,14 +7502,14 @@
       <c r="E11" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="112"/>
-      <c r="G11" s="113"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="113"/>
-      <c r="L11" s="113"/>
-      <c r="M11" s="114"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="109"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="19" t="s">
@@ -7570,16 +7521,16 @@
       <c r="E12" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="78" t="s">
+      <c r="F12" s="76" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="80"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="78"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
@@ -7591,16 +7542,16 @@
       <c r="E13" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="F13" s="78" t="s">
+      <c r="F13" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="80"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="78"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
@@ -7612,16 +7563,16 @@
       <c r="E14" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="F14" s="78" t="s">
+      <c r="F14" s="76" t="s">
         <v>208</v>
       </c>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="80"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="78"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
@@ -7631,7 +7582,7 @@
         <v>35</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F15" s="45" t="s">
         <v>209</v>
@@ -7643,10 +7594,10 @@
         <v>211</v>
       </c>
       <c r="I15" s="55" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="J15" s="55" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="K15" s="44"/>
       <c r="L15" s="45" t="s">
@@ -7666,18 +7617,18 @@
       <c r="E16" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F16" s="115" t="s">
+      <c r="F16" s="110" t="s">
         <v>214</v>
       </c>
-      <c r="G16" s="116"/>
-      <c r="H16" s="116"/>
-      <c r="I16" s="116"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="117"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="112"/>
       <c r="N16" s="57" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7690,18 +7641,18 @@
       <c r="E17" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F17" s="115" t="s">
+      <c r="F17" s="110" t="s">
         <v>215</v>
       </c>
-      <c r="G17" s="116"/>
-      <c r="H17" s="116"/>
-      <c r="I17" s="116"/>
-      <c r="J17" s="116"/>
-      <c r="K17" s="116"/>
-      <c r="L17" s="116"/>
-      <c r="M17" s="117"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="112"/>
       <c r="N17" s="57" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7727,13 +7678,13 @@
       <c r="J18" s="56" t="s">
         <v>220</v>
       </c>
-      <c r="K18" s="112"/>
-      <c r="L18" s="114"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="109"/>
       <c r="M18" s="55" t="s">
         <v>221</v>
       </c>
       <c r="N18" s="58" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7750,8 +7701,8 @@
       <c r="G19" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="H19" s="112"/>
-      <c r="I19" s="114"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="109"/>
       <c r="J19" s="56" t="s">
         <v>224</v>
       </c>
@@ -7773,18 +7724,18 @@
         <v>35</v>
       </c>
       <c r="E20" s="43"/>
-      <c r="F20" s="118" t="s">
+      <c r="F20" s="113" t="s">
         <v>228</v>
       </c>
-      <c r="G20" s="119"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="119"/>
-      <c r="J20" s="119"/>
-      <c r="K20" s="119"/>
-      <c r="L20" s="119"/>
-      <c r="M20" s="120"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="114"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="115"/>
       <c r="N20" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7795,18 +7746,18 @@
         <v>35</v>
       </c>
       <c r="E21" s="42"/>
-      <c r="F21" s="118" t="s">
+      <c r="F21" s="113" t="s">
         <v>229</v>
       </c>
-      <c r="G21" s="119"/>
-      <c r="H21" s="119"/>
-      <c r="I21" s="119"/>
-      <c r="J21" s="119"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="119"/>
-      <c r="M21" s="120"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="114"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="115"/>
       <c r="N21" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7817,18 +7768,18 @@
         <v>35</v>
       </c>
       <c r="E22" s="42"/>
-      <c r="F22" s="118" t="s">
+      <c r="F22" s="113" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="119"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="119"/>
-      <c r="J22" s="119"/>
-      <c r="K22" s="119"/>
-      <c r="L22" s="119"/>
-      <c r="M22" s="120"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="115"/>
       <c r="N22" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7839,18 +7790,18 @@
         <v>35</v>
       </c>
       <c r="E23" s="42"/>
-      <c r="F23" s="118" t="s">
+      <c r="F23" s="113" t="s">
         <v>231</v>
       </c>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="119"/>
-      <c r="M23" s="120"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="115"/>
       <c r="N23" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7863,18 +7814,18 @@
       <c r="E24" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F24" s="115" t="s">
+      <c r="F24" s="110" t="s">
         <v>232</v>
       </c>
-      <c r="G24" s="116"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="116"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="116"/>
-      <c r="L24" s="116"/>
-      <c r="M24" s="117"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="112"/>
       <c r="N24" s="59" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7887,18 +7838,18 @@
       <c r="E25" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F25" s="112"/>
-      <c r="G25" s="113"/>
-      <c r="H25" s="113"/>
-      <c r="I25" s="113"/>
-      <c r="J25" s="114"/>
-      <c r="K25" s="115" t="s">
+      <c r="F25" s="107"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="108"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="110" t="s">
         <v>233</v>
       </c>
-      <c r="L25" s="116"/>
-      <c r="M25" s="117"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="112"/>
       <c r="N25" s="57" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7909,18 +7860,18 @@
         <v>30</v>
       </c>
       <c r="E26" s="42"/>
-      <c r="F26" s="118" t="s">
+      <c r="F26" s="113" t="s">
         <v>234</v>
       </c>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="119"/>
-      <c r="J26" s="119"/>
-      <c r="K26" s="121"/>
-      <c r="L26" s="121"/>
-      <c r="M26" s="122"/>
+      <c r="G26" s="114"/>
+      <c r="H26" s="114"/>
+      <c r="I26" s="114"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="116"/>
+      <c r="L26" s="116"/>
+      <c r="M26" s="117"/>
       <c r="N26" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7931,18 +7882,18 @@
         <v>35</v>
       </c>
       <c r="E27" s="42"/>
-      <c r="F27" s="118" t="s">
+      <c r="F27" s="113" t="s">
         <v>235</v>
       </c>
-      <c r="G27" s="119"/>
-      <c r="H27" s="119"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="119"/>
-      <c r="L27" s="119"/>
-      <c r="M27" s="120"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="114"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="114"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="115"/>
       <c r="N27" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7953,18 +7904,18 @@
         <v>35</v>
       </c>
       <c r="E28" s="42"/>
-      <c r="F28" s="118" t="s">
+      <c r="F28" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="119"/>
-      <c r="J28" s="119"/>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="120"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="115"/>
       <c r="N28" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7975,18 +7926,18 @@
         <v>35</v>
       </c>
       <c r="E29" s="42"/>
-      <c r="F29" s="118" t="s">
+      <c r="F29" s="113" t="s">
         <v>237</v>
       </c>
-      <c r="G29" s="119"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="119"/>
-      <c r="K29" s="119"/>
-      <c r="L29" s="119"/>
-      <c r="M29" s="120"/>
+      <c r="G29" s="114"/>
+      <c r="H29" s="114"/>
+      <c r="I29" s="114"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="114"/>
+      <c r="L29" s="114"/>
+      <c r="M29" s="115"/>
       <c r="N29" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7999,14 +7950,14 @@
       <c r="E30" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F30" s="112"/>
-      <c r="G30" s="113"/>
-      <c r="H30" s="113"/>
-      <c r="I30" s="113"/>
-      <c r="J30" s="113"/>
-      <c r="K30" s="113"/>
-      <c r="L30" s="113"/>
-      <c r="M30" s="114"/>
+      <c r="F30" s="107"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="109"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="60" t="s">
@@ -8018,14 +7969,14 @@
       <c r="E31" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F31" s="112"/>
-      <c r="G31" s="113"/>
-      <c r="H31" s="113"/>
-      <c r="I31" s="113"/>
-      <c r="J31" s="113"/>
-      <c r="K31" s="113"/>
-      <c r="L31" s="113"/>
-      <c r="M31" s="114"/>
+      <c r="F31" s="107"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="108"/>
+      <c r="I31" s="108"/>
+      <c r="J31" s="108"/>
+      <c r="K31" s="108"/>
+      <c r="L31" s="108"/>
+      <c r="M31" s="109"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="60" t="s">
@@ -8037,18 +7988,18 @@
       <c r="E32" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F32" s="115" t="s">
+      <c r="F32" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="G32" s="116"/>
-      <c r="H32" s="116"/>
-      <c r="I32" s="116"/>
-      <c r="J32" s="116"/>
-      <c r="K32" s="116"/>
-      <c r="L32" s="116"/>
-      <c r="M32" s="117"/>
+      <c r="G32" s="111"/>
+      <c r="H32" s="111"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="111"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="112"/>
       <c r="N32" s="57" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8061,18 +8012,18 @@
       <c r="E33" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F33" s="115" t="s">
+      <c r="F33" s="110" t="s">
         <v>239</v>
       </c>
-      <c r="G33" s="117"/>
-      <c r="H33" s="112"/>
-      <c r="I33" s="113"/>
-      <c r="J33" s="113"/>
-      <c r="K33" s="113"/>
-      <c r="L33" s="113"/>
-      <c r="M33" s="114"/>
+      <c r="G33" s="112"/>
+      <c r="H33" s="107"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="108"/>
+      <c r="K33" s="108"/>
+      <c r="L33" s="108"/>
+      <c r="M33" s="109"/>
       <c r="N33" s="57" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8085,18 +8036,18 @@
       <c r="E34" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F34" s="112"/>
-      <c r="G34" s="113"/>
-      <c r="H34" s="113"/>
-      <c r="I34" s="113"/>
-      <c r="J34" s="114"/>
-      <c r="K34" s="115" t="s">
+      <c r="F34" s="107"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="109"/>
+      <c r="K34" s="110" t="s">
         <v>240</v>
       </c>
-      <c r="L34" s="116"/>
-      <c r="M34" s="117"/>
+      <c r="L34" s="111"/>
+      <c r="M34" s="112"/>
       <c r="N34" s="57" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8109,18 +8060,18 @@
       <c r="E35" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F35" s="112"/>
-      <c r="G35" s="113"/>
-      <c r="H35" s="113"/>
-      <c r="I35" s="114"/>
-      <c r="J35" s="115" t="s">
+      <c r="F35" s="107"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="108"/>
+      <c r="I35" s="109"/>
+      <c r="J35" s="110" t="s">
         <v>241</v>
       </c>
-      <c r="K35" s="116"/>
-      <c r="L35" s="116"/>
-      <c r="M35" s="117"/>
+      <c r="K35" s="111"/>
+      <c r="L35" s="111"/>
+      <c r="M35" s="112"/>
       <c r="N35" s="57" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8133,18 +8084,18 @@
       <c r="E36" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F36" s="112"/>
-      <c r="G36" s="113"/>
-      <c r="H36" s="113"/>
-      <c r="I36" s="114"/>
-      <c r="J36" s="115" t="s">
+      <c r="F36" s="107"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="108"/>
+      <c r="I36" s="109"/>
+      <c r="J36" s="110" t="s">
         <v>242</v>
       </c>
-      <c r="K36" s="116"/>
-      <c r="L36" s="116"/>
-      <c r="M36" s="117"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="111"/>
+      <c r="M36" s="112"/>
       <c r="N36" s="57" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8157,18 +8108,18 @@
       <c r="E37" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F37" s="115" t="s">
+      <c r="F37" s="110" t="s">
         <v>243</v>
       </c>
-      <c r="G37" s="116"/>
-      <c r="H37" s="116"/>
-      <c r="I37" s="116"/>
-      <c r="J37" s="116"/>
-      <c r="K37" s="116"/>
-      <c r="L37" s="116"/>
-      <c r="M37" s="117"/>
+      <c r="G37" s="111"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="111"/>
+      <c r="J37" s="111"/>
+      <c r="K37" s="111"/>
+      <c r="L37" s="111"/>
+      <c r="M37" s="112"/>
       <c r="N37" s="57" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8181,14 +8132,14 @@
       <c r="E38" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F38" s="112"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="114"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="108"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="108"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="M38" s="109"/>
     </row>
     <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="60" t="s">
@@ -8200,14 +8151,14 @@
       <c r="E39" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F39" s="112"/>
-      <c r="G39" s="113"/>
-      <c r="H39" s="113"/>
-      <c r="I39" s="113"/>
-      <c r="J39" s="113"/>
-      <c r="K39" s="113"/>
-      <c r="L39" s="113"/>
-      <c r="M39" s="114"/>
+      <c r="F39" s="107"/>
+      <c r="G39" s="108"/>
+      <c r="H39" s="108"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
+      <c r="K39" s="108"/>
+      <c r="L39" s="108"/>
+      <c r="M39" s="109"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="60" t="s">
@@ -8219,14 +8170,14 @@
       <c r="E40" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F40" s="112"/>
-      <c r="G40" s="113"/>
-      <c r="H40" s="113"/>
-      <c r="I40" s="113"/>
-      <c r="J40" s="113"/>
-      <c r="K40" s="113"/>
-      <c r="L40" s="113"/>
-      <c r="M40" s="114"/>
+      <c r="F40" s="107"/>
+      <c r="G40" s="108"/>
+      <c r="H40" s="108"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="108"/>
+      <c r="K40" s="108"/>
+      <c r="L40" s="108"/>
+      <c r="M40" s="109"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="60" t="s">
@@ -8238,14 +8189,14 @@
       <c r="E41" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F41" s="112"/>
-      <c r="G41" s="113"/>
-      <c r="H41" s="113"/>
-      <c r="I41" s="113"/>
-      <c r="J41" s="113"/>
-      <c r="K41" s="113"/>
-      <c r="L41" s="113"/>
-      <c r="M41" s="114"/>
+      <c r="F41" s="107"/>
+      <c r="G41" s="108"/>
+      <c r="H41" s="108"/>
+      <c r="I41" s="108"/>
+      <c r="J41" s="108"/>
+      <c r="K41" s="108"/>
+      <c r="L41" s="108"/>
+      <c r="M41" s="109"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="60" t="s">
@@ -8257,14 +8208,14 @@
       <c r="E42" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F42" s="112"/>
-      <c r="G42" s="113"/>
-      <c r="H42" s="113"/>
-      <c r="I42" s="113"/>
-      <c r="J42" s="113"/>
-      <c r="K42" s="113"/>
-      <c r="L42" s="113"/>
-      <c r="M42" s="114"/>
+      <c r="F42" s="107"/>
+      <c r="G42" s="108"/>
+      <c r="H42" s="108"/>
+      <c r="I42" s="108"/>
+      <c r="J42" s="108"/>
+      <c r="K42" s="108"/>
+      <c r="L42" s="108"/>
+      <c r="M42" s="109"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="20" t="s">
@@ -8286,12 +8237,12 @@
       <c r="I43" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="78" t="s">
+      <c r="J43" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="79"/>
-      <c r="L43" s="79"/>
-      <c r="M43" s="80"/>
+      <c r="K43" s="77"/>
+      <c r="L43" s="77"/>
+      <c r="M43" s="78"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
@@ -8301,18 +8252,18 @@
         <v>35</v>
       </c>
       <c r="E44" s="43"/>
-      <c r="F44" s="78" t="s">
+      <c r="F44" s="76" t="s">
         <v>252</v>
       </c>
-      <c r="G44" s="80"/>
-      <c r="H44" s="78" t="s">
+      <c r="G44" s="78"/>
+      <c r="H44" s="76" t="s">
         <v>111</v>
       </c>
-      <c r="I44" s="79"/>
-      <c r="J44" s="79"/>
-      <c r="K44" s="79"/>
-      <c r="L44" s="79"/>
-      <c r="M44" s="80"/>
+      <c r="I44" s="77"/>
+      <c r="J44" s="77"/>
+      <c r="K44" s="77"/>
+      <c r="L44" s="77"/>
+      <c r="M44" s="78"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="19" t="s">
@@ -8322,18 +8273,18 @@
         <v>35</v>
       </c>
       <c r="E45" s="43"/>
-      <c r="F45" s="106" t="s">
+      <c r="F45" s="118" t="s">
         <v>115</v>
       </c>
-      <c r="G45" s="107"/>
-      <c r="H45" s="107"/>
-      <c r="I45" s="108"/>
-      <c r="J45" s="78" t="s">
+      <c r="G45" s="119"/>
+      <c r="H45" s="119"/>
+      <c r="I45" s="120"/>
+      <c r="J45" s="76" t="s">
         <v>116</v>
       </c>
-      <c r="K45" s="79"/>
-      <c r="L45" s="79"/>
-      <c r="M45" s="80"/>
+      <c r="K45" s="77"/>
+      <c r="L45" s="77"/>
+      <c r="M45" s="78"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="19" t="s">
@@ -8343,18 +8294,18 @@
         <v>35</v>
       </c>
       <c r="E46" s="6"/>
-      <c r="F46" s="78" t="s">
+      <c r="F46" s="76" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="79"/>
-      <c r="H46" s="79"/>
-      <c r="I46" s="80"/>
-      <c r="J46" s="109" t="s">
+      <c r="G46" s="77"/>
+      <c r="H46" s="77"/>
+      <c r="I46" s="78"/>
+      <c r="J46" s="121" t="s">
         <v>118</v>
       </c>
-      <c r="K46" s="110"/>
-      <c r="L46" s="110"/>
-      <c r="M46" s="111"/>
+      <c r="K46" s="122"/>
+      <c r="L46" s="122"/>
+      <c r="M46" s="123"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="19" t="s">
@@ -8364,16 +8315,16 @@
         <v>35</v>
       </c>
       <c r="E47" s="6"/>
-      <c r="F47" s="86" t="s">
+      <c r="F47" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="G47" s="87"/>
-      <c r="H47" s="87"/>
-      <c r="I47" s="87"/>
-      <c r="J47" s="87"/>
-      <c r="K47" s="87"/>
-      <c r="L47" s="87"/>
-      <c r="M47" s="88"/>
+      <c r="G47" s="93"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="93"/>
+      <c r="J47" s="93"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="93"/>
+      <c r="M47" s="94"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="19" t="s">
@@ -8383,20 +8334,20 @@
         <v>35</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="77"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="90"/>
       <c r="H48" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="I48" s="86" t="s">
+      <c r="I48" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="J48" s="87"/>
-      <c r="K48" s="88"/>
-      <c r="L48" s="86" t="s">
+      <c r="J48" s="93"/>
+      <c r="K48" s="94"/>
+      <c r="L48" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="M48" s="88"/>
+      <c r="M48" s="94"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="19" t="s">
@@ -8439,15 +8390,15 @@
         <v>35</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="75"/>
-      <c r="G50" s="76"/>
-      <c r="H50" s="76"/>
-      <c r="I50" s="77"/>
-      <c r="J50" s="86" t="s">
+      <c r="F50" s="88"/>
+      <c r="G50" s="89"/>
+      <c r="H50" s="89"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="K50" s="87"/>
-      <c r="L50" s="88"/>
+      <c r="K50" s="93"/>
+      <c r="L50" s="94"/>
       <c r="M50" s="13" t="s">
         <v>81</v>
       </c>
@@ -8462,12 +8413,12 @@
       <c r="E51" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F51" s="112"/>
-      <c r="G51" s="113"/>
-      <c r="H51" s="113"/>
-      <c r="I51" s="113"/>
-      <c r="J51" s="113"/>
-      <c r="K51" s="114"/>
+      <c r="F51" s="107"/>
+      <c r="G51" s="108"/>
+      <c r="H51" s="108"/>
+      <c r="I51" s="108"/>
+      <c r="J51" s="108"/>
+      <c r="K51" s="109"/>
       <c r="L51" s="82" t="s">
         <v>257</v>
       </c>
@@ -8475,16 +8426,16 @@
     </row>
     <row r="52" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="F52" s="82" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G52" s="83"/>
       <c r="H52" s="83"/>
@@ -8494,21 +8445,21 @@
       <c r="L52" s="83"/>
       <c r="M52" s="84"/>
       <c r="N52" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="F53" s="82" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G53" s="83"/>
       <c r="H53" s="83"/>
@@ -8518,21 +8469,21 @@
       <c r="L53" s="83"/>
       <c r="M53" s="84"/>
       <c r="N53" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="F54" s="82" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G54" s="83"/>
       <c r="H54" s="83"/>
@@ -8542,21 +8493,21 @@
       <c r="L54" s="83"/>
       <c r="M54" s="84"/>
       <c r="N54" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="55" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="F55" s="82" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G55" s="83"/>
       <c r="H55" s="83"/>
@@ -8566,21 +8517,21 @@
       <c r="L55" s="83"/>
       <c r="M55" s="84"/>
       <c r="N55" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F56" s="82" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G56" s="83"/>
       <c r="H56" s="83"/>
@@ -8590,7 +8541,7 @@
       <c r="L56" s="83"/>
       <c r="M56" s="84"/>
       <c r="N56" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="57" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8601,10 +8552,10 @@
         <v>35</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="F57" s="82" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G57" s="83"/>
       <c r="H57" s="83"/>
@@ -8614,21 +8565,21 @@
       <c r="L57" s="83"/>
       <c r="M57" s="84"/>
       <c r="N57" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="58" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="F58" s="82" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G58" s="83"/>
       <c r="H58" s="83"/>
@@ -8638,21 +8589,21 @@
       <c r="L58" s="83"/>
       <c r="M58" s="84"/>
       <c r="N58" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
     </row>
     <row r="59" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="19" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="F59" s="82" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G59" s="83"/>
       <c r="H59" s="83"/>
@@ -8662,21 +8613,21 @@
       <c r="L59" s="83"/>
       <c r="M59" s="84"/>
       <c r="N59" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="60" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="19" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="F60" s="82" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G60" s="83"/>
       <c r="H60" s="83"/>
@@ -8686,12 +8637,12 @@
       <c r="L60" s="83"/>
       <c r="M60" s="84"/>
       <c r="N60" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="60" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D61" s="61" t="s">
         <v>35</v>
@@ -8699,46 +8650,92 @@
       <c r="E61" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F61" s="112"/>
-      <c r="G61" s="113"/>
-      <c r="H61" s="113"/>
-      <c r="I61" s="113"/>
-      <c r="J61" s="113"/>
-      <c r="K61" s="113"/>
-      <c r="L61" s="113"/>
-      <c r="M61" s="114"/>
+      <c r="F61" s="107"/>
+      <c r="G61" s="108"/>
+      <c r="H61" s="108"/>
+      <c r="I61" s="108"/>
+      <c r="J61" s="108"/>
+      <c r="K61" s="108"/>
+      <c r="L61" s="108"/>
+      <c r="M61" s="109"/>
     </row>
     <row r="62" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="63" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="53" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D63" t="s">
         <v>34</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="J63" s="54" t="s">
-        <v>299</v>
-      </c>
-      <c r="K63" s="75"/>
-      <c r="L63" s="77"/>
+        <v>291</v>
+      </c>
+      <c r="K63" s="88"/>
+      <c r="L63" s="90"/>
       <c r="M63" s="54" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F59:M59"/>
+    <mergeCell ref="F60:M60"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F55:M55"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="F47:M47"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="F20:M20"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F17:M17"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="F21:M21"/>
     <mergeCell ref="K63:L63"/>
     <mergeCell ref="F11:M11"/>
     <mergeCell ref="F13:M13"/>
@@ -8755,52 +8752,6 @@
     <mergeCell ref="F12:M12"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="F16:M16"/>
-    <mergeCell ref="F17:M17"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="F21:M21"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F23:M23"/>
-    <mergeCell ref="F20:M20"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="F47:M47"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F59:M59"/>
-    <mergeCell ref="F60:M60"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F55:M55"/>
-    <mergeCell ref="F56:M56"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8815,7 +8766,7 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -8831,7 +8782,7 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60D3DAD-70F2-48D1-94E6-8A6C2442B03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3509D6-DF06-4EF8-AD02-5EFF184678FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="403">
   <si>
     <t>Y8960 Cartridge は、MSX用のオーディオ系チップのコンボカートリッジです。</t>
     <rPh sb="21" eb="22">
@@ -1937,110 +1937,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1で左端、128で中央、255で右端。デフォルト129</t>
-    <rPh sb="2" eb="4">
-      <t>ヒダリハシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ミギハシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1で左端、128で中央、255で右端。デフォルト130</t>
-    <rPh sb="2" eb="4">
-      <t>ヒダリハシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ミギハシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1で左端、128で中央、255で右端。デフォルト131</t>
-    <rPh sb="2" eb="4">
-      <t>ヒダリハシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ミギハシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1で左端、128で中央、255で右端。デフォルト132</t>
-    <rPh sb="2" eb="4">
-      <t>ヒダリハシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ミギハシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1で左端、128で中央、255で右端。デフォルト133</t>
-    <rPh sb="2" eb="4">
-      <t>ヒダリハシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ミギハシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1で左端、128で中央、255で右端。デフォルト134</t>
-    <rPh sb="2" eb="4">
-      <t>ヒダリハシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ミギハシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1で左端、128で中央、255で右端。デフォルト135</t>
-    <rPh sb="2" eb="4">
-      <t>ヒダリハシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ミギハシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1で左端、128で中央、255で右端。デフォルト136</t>
-    <rPh sb="2" eb="4">
-      <t>ヒダリハシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ミギハシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>MIXIERは、MemoryMappedI/Oのみ。</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2108,6 +2004,10 @@
   </si>
   <si>
     <t>0: OFF,～128: MAX, RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#15) のときのみ利用可能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADPCM PAN</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2848,6 +2748,21 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2857,6 +2772,69 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2866,15 +2844,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2884,27 +2853,9 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2939,57 +2890,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3728,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -4016,13 +3916,13 @@
       <c r="F4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="88"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="90"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="77"/>
       <c r="N4" s="67" t="s">
         <v>278</v>
       </c>
@@ -4043,16 +3943,16 @@
       <c r="F5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="79" t="s">
+      <c r="G5" s="105" t="s">
         <v>279</v>
       </c>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="81"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="107"/>
       <c r="O5" s="50" t="s">
         <v>282</v>
       </c>
@@ -4070,16 +3970,16 @@
       <c r="F6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="105" t="s">
         <v>279</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="81"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="107"/>
       <c r="O6" s="50" t="s">
         <v>282</v>
       </c>
@@ -4097,16 +3997,16 @@
       <c r="F7" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="105" t="s">
         <v>279</v>
       </c>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="81"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="107"/>
       <c r="O7" s="50" t="s">
         <v>282</v>
       </c>
@@ -4124,16 +4024,16 @@
       <c r="F8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="79" t="s">
+      <c r="G8" s="105" t="s">
         <v>279</v>
       </c>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="81"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="106"/>
+      <c r="K8" s="106"/>
+      <c r="L8" s="106"/>
+      <c r="M8" s="106"/>
+      <c r="N8" s="107"/>
       <c r="O8" s="50" t="s">
         <v>282</v>
       </c>
@@ -4151,16 +4051,16 @@
       <c r="F9" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="76" t="s">
+      <c r="G9" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="77"/>
-      <c r="N9" s="78"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
+      <c r="M9" s="82"/>
+      <c r="N9" s="83"/>
       <c r="O9" s="50" t="s">
         <v>283</v>
       </c>
@@ -4178,16 +4078,16 @@
       <c r="F10" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="76" t="s">
+      <c r="G10" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="77"/>
-      <c r="M10" s="77"/>
-      <c r="N10" s="78"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="82"/>
+      <c r="L10" s="82"/>
+      <c r="M10" s="82"/>
+      <c r="N10" s="83"/>
       <c r="O10" s="50" t="s">
         <v>283</v>
       </c>
@@ -4205,18 +4105,18 @@
       <c r="F11" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G11" s="82" t="s">
+      <c r="G11" s="84" t="s">
         <v>262</v>
       </c>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="84"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="104"/>
+      <c r="N11" s="85"/>
       <c r="O11" s="51" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4232,18 +4132,18 @@
       <c r="F12" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G12" s="82" t="s">
+      <c r="G12" s="84" t="s">
         <v>263</v>
       </c>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="84"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="104"/>
+      <c r="N12" s="85"/>
       <c r="O12" s="51" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4259,18 +4159,18 @@
       <c r="F13" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G13" s="85" t="s">
+      <c r="G13" s="108" t="s">
         <v>337</v>
       </c>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="84"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="85"/>
       <c r="O13" s="51" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4286,18 +4186,18 @@
       <c r="F14" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G14" s="85" t="s">
-        <v>404</v>
-      </c>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="84"/>
+      <c r="G14" s="108" t="s">
+        <v>396</v>
+      </c>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="85"/>
       <c r="O14" s="51" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4313,18 +4213,18 @@
       <c r="F15" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G15" s="92" t="s">
+      <c r="G15" s="86" t="s">
         <v>366</v>
       </c>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="93"/>
-      <c r="K15" s="93"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="94"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="87"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="87"/>
+      <c r="N15" s="88"/>
       <c r="O15" s="51" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4340,18 +4240,18 @@
       <c r="F16" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G16" s="92" t="s">
-        <v>403</v>
-      </c>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="93"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="94"/>
+      <c r="G16" s="86" t="s">
+        <v>395</v>
+      </c>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="87"/>
+      <c r="N16" s="88"/>
       <c r="O16" s="51" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4367,23 +4267,23 @@
       <c r="F17" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G17" s="95"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="97"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="113"/>
+      <c r="M17" s="114"/>
       <c r="N17" s="11" t="s">
         <v>5</v>
       </c>
       <c r="O17" s="51" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>35</v>
@@ -4397,11 +4297,11 @@
       <c r="G18" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="H18" s="88"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="90"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="77"/>
       <c r="M18" s="33" t="s">
         <v>3</v>
       </c>
@@ -4409,118 +4309,118 @@
         <v>311</v>
       </c>
       <c r="O18" s="51" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="12" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G19" s="85"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="86"/>
-      <c r="N19" s="87"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="109"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="109"/>
+      <c r="M19" s="109"/>
+      <c r="N19" s="110"/>
       <c r="O19" s="51" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="12" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G20" s="85"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="86"/>
-      <c r="N20" s="87"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="110"/>
       <c r="O20" s="51" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="21" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="12" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G21" s="85"/>
-      <c r="H21" s="86"/>
-      <c r="I21" s="86"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="86"/>
-      <c r="L21" s="86"/>
-      <c r="M21" s="86"/>
-      <c r="N21" s="87"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="110"/>
       <c r="O21" s="51" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="12" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G22" s="85"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="86"/>
-      <c r="K22" s="86"/>
-      <c r="L22" s="86"/>
-      <c r="M22" s="86"/>
-      <c r="N22" s="87"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
+      <c r="N22" s="110"/>
       <c r="O22" s="51" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="12" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>309</v>
@@ -4534,7 +4434,7 @@
       <c r="M23" s="73"/>
       <c r="N23" s="74"/>
       <c r="O23" s="51" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4550,16 +4450,16 @@
       <c r="F24" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="76" t="s">
+      <c r="G24" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="H24" s="91"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="77"/>
-      <c r="M24" s="77"/>
-      <c r="N24" s="78"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="83"/>
       <c r="O24" s="50" t="s">
         <v>283</v>
       </c>
@@ -4577,16 +4477,16 @@
       <c r="F25" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="76" t="s">
+      <c r="G25" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="77"/>
-      <c r="K25" s="77"/>
-      <c r="L25" s="77"/>
-      <c r="M25" s="77"/>
-      <c r="N25" s="78"/>
+      <c r="H25" s="82"/>
+      <c r="I25" s="82"/>
+      <c r="J25" s="82"/>
+      <c r="K25" s="82"/>
+      <c r="L25" s="82"/>
+      <c r="M25" s="82"/>
+      <c r="N25" s="83"/>
       <c r="O25" s="50" t="s">
         <v>283</v>
       </c>
@@ -4733,16 +4633,16 @@
       <c r="E12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="98" t="s">
+      <c r="F12" s="115" t="s">
         <v>182</v>
       </c>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="100"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="116"/>
+      <c r="L12" s="116"/>
+      <c r="M12" s="117"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
@@ -4758,12 +4658,12 @@
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="98" t="s">
+      <c r="J13" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="100"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="116"/>
+      <c r="M13" s="117"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
@@ -4775,16 +4675,16 @@
       <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="98" t="s">
+      <c r="F14" s="115" t="s">
         <v>182</v>
       </c>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="99"/>
-      <c r="K14" s="99"/>
-      <c r="L14" s="99"/>
-      <c r="M14" s="100"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="116"/>
+      <c r="K14" s="116"/>
+      <c r="L14" s="116"/>
+      <c r="M14" s="117"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
@@ -4800,12 +4700,12 @@
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="36"/>
-      <c r="J15" s="98" t="s">
+      <c r="J15" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="K15" s="99"/>
-      <c r="L15" s="99"/>
-      <c r="M15" s="100"/>
+      <c r="K15" s="116"/>
+      <c r="L15" s="116"/>
+      <c r="M15" s="117"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="19" t="s">
@@ -4817,16 +4717,16 @@
       <c r="E16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="98" t="s">
+      <c r="F16" s="115" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="99"/>
-      <c r="H16" s="99"/>
-      <c r="I16" s="99"/>
-      <c r="J16" s="99"/>
-      <c r="K16" s="99"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="100"/>
+      <c r="G16" s="116"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="116"/>
+      <c r="K16" s="116"/>
+      <c r="L16" s="116"/>
+      <c r="M16" s="117"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="19" t="s">
@@ -4842,12 +4742,12 @@
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
-      <c r="J17" s="98" t="s">
+      <c r="J17" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="99"/>
-      <c r="L17" s="99"/>
-      <c r="M17" s="100"/>
+      <c r="K17" s="116"/>
+      <c r="L17" s="116"/>
+      <c r="M17" s="117"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="19" t="s">
@@ -4862,13 +4762,13 @@
       <c r="F18" s="34"/>
       <c r="G18" s="35"/>
       <c r="H18" s="36"/>
-      <c r="I18" s="98" t="s">
+      <c r="I18" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="J18" s="99"/>
-      <c r="K18" s="99"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="100"/>
+      <c r="J18" s="116"/>
+      <c r="K18" s="116"/>
+      <c r="L18" s="116"/>
+      <c r="M18" s="117"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="19" t="s">
@@ -4921,12 +4821,12 @@
       <c r="I20" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="98" t="s">
+      <c r="J20" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="K20" s="99"/>
-      <c r="L20" s="99"/>
-      <c r="M20" s="100"/>
+      <c r="K20" s="116"/>
+      <c r="L20" s="116"/>
+      <c r="M20" s="117"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
@@ -4944,12 +4844,12 @@
       <c r="I21" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="98" t="s">
+      <c r="J21" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="K21" s="99"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="100"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="117"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
@@ -4967,12 +4867,12 @@
       <c r="I22" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="98" t="s">
+      <c r="J22" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="K22" s="99"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="100"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="117"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
@@ -4984,16 +4884,16 @@
       <c r="E23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F23" s="98" t="s">
+      <c r="F23" s="115" t="s">
         <v>186</v>
       </c>
-      <c r="G23" s="99"/>
-      <c r="H23" s="99"/>
-      <c r="I23" s="99"/>
-      <c r="J23" s="99"/>
-      <c r="K23" s="99"/>
-      <c r="L23" s="99"/>
-      <c r="M23" s="100"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="116"/>
+      <c r="L23" s="116"/>
+      <c r="M23" s="117"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
@@ -5005,16 +4905,16 @@
       <c r="E24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="98" t="s">
+      <c r="F24" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="100"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="116"/>
+      <c r="L24" s="116"/>
+      <c r="M24" s="117"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
@@ -5030,12 +4930,12 @@
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
       <c r="I25" s="36"/>
-      <c r="J25" s="98" t="s">
+      <c r="J25" s="115" t="s">
         <v>188</v>
       </c>
-      <c r="K25" s="99"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="100"/>
+      <c r="K25" s="116"/>
+      <c r="L25" s="116"/>
+      <c r="M25" s="117"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
@@ -5085,16 +4985,16 @@
       <c r="E28" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="85" t="s">
+      <c r="F28" s="108" t="s">
         <v>182</v>
       </c>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="87"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="109"/>
+      <c r="I28" s="109"/>
+      <c r="J28" s="109"/>
+      <c r="K28" s="109"/>
+      <c r="L28" s="109"/>
+      <c r="M28" s="110"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="19" t="s">
@@ -5110,12 +5010,12 @@
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="I29" s="28"/>
-      <c r="J29" s="85" t="s">
+      <c r="J29" s="108" t="s">
         <v>183</v>
       </c>
-      <c r="K29" s="86"/>
-      <c r="L29" s="86"/>
-      <c r="M29" s="87"/>
+      <c r="K29" s="109"/>
+      <c r="L29" s="109"/>
+      <c r="M29" s="110"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
@@ -5127,16 +5027,16 @@
       <c r="E30" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="85" t="s">
+      <c r="F30" s="108" t="s">
         <v>182</v>
       </c>
-      <c r="G30" s="86"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
-      <c r="M30" s="87"/>
+      <c r="G30" s="109"/>
+      <c r="H30" s="109"/>
+      <c r="I30" s="109"/>
+      <c r="J30" s="109"/>
+      <c r="K30" s="109"/>
+      <c r="L30" s="109"/>
+      <c r="M30" s="110"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
@@ -5152,12 +5052,12 @@
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="I31" s="28"/>
-      <c r="J31" s="85" t="s">
+      <c r="J31" s="108" t="s">
         <v>183</v>
       </c>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
-      <c r="M31" s="87"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
+      <c r="M31" s="110"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
@@ -5169,16 +5069,16 @@
       <c r="E32" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="85" t="s">
+      <c r="F32" s="108" t="s">
         <v>182</v>
       </c>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="87"/>
+      <c r="G32" s="109"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="109"/>
+      <c r="J32" s="109"/>
+      <c r="K32" s="109"/>
+      <c r="L32" s="109"/>
+      <c r="M32" s="110"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
@@ -5194,12 +5094,12 @@
       <c r="G33" s="27"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
-      <c r="J33" s="85" t="s">
+      <c r="J33" s="108" t="s">
         <v>183</v>
       </c>
-      <c r="K33" s="86"/>
-      <c r="L33" s="86"/>
-      <c r="M33" s="87"/>
+      <c r="K33" s="109"/>
+      <c r="L33" s="109"/>
+      <c r="M33" s="110"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
@@ -5214,13 +5114,13 @@
       <c r="F34" s="26"/>
       <c r="G34" s="27"/>
       <c r="H34" s="28"/>
-      <c r="I34" s="85" t="s">
+      <c r="I34" s="108" t="s">
         <v>184</v>
       </c>
-      <c r="J34" s="86"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="86"/>
-      <c r="M34" s="87"/>
+      <c r="J34" s="109"/>
+      <c r="K34" s="109"/>
+      <c r="L34" s="109"/>
+      <c r="M34" s="110"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
@@ -5273,12 +5173,12 @@
       <c r="I36" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J36" s="85" t="s">
+      <c r="J36" s="108" t="s">
         <v>185</v>
       </c>
-      <c r="K36" s="86"/>
-      <c r="L36" s="86"/>
-      <c r="M36" s="87"/>
+      <c r="K36" s="109"/>
+      <c r="L36" s="109"/>
+      <c r="M36" s="110"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
@@ -5296,12 +5196,12 @@
       <c r="I37" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J37" s="85" t="s">
+      <c r="J37" s="108" t="s">
         <v>185</v>
       </c>
-      <c r="K37" s="86"/>
-      <c r="L37" s="86"/>
-      <c r="M37" s="87"/>
+      <c r="K37" s="109"/>
+      <c r="L37" s="109"/>
+      <c r="M37" s="110"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
@@ -5319,12 +5219,12 @@
       <c r="I38" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J38" s="85" t="s">
+      <c r="J38" s="108" t="s">
         <v>185</v>
       </c>
-      <c r="K38" s="86"/>
-      <c r="L38" s="86"/>
-      <c r="M38" s="87"/>
+      <c r="K38" s="109"/>
+      <c r="L38" s="109"/>
+      <c r="M38" s="110"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
@@ -5336,16 +5236,16 @@
       <c r="E39" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F39" s="85" t="s">
+      <c r="F39" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="G39" s="86"/>
-      <c r="H39" s="86"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="86"/>
-      <c r="K39" s="86"/>
-      <c r="L39" s="86"/>
-      <c r="M39" s="87"/>
+      <c r="G39" s="109"/>
+      <c r="H39" s="109"/>
+      <c r="I39" s="109"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109"/>
+      <c r="L39" s="109"/>
+      <c r="M39" s="110"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="19" t="s">
@@ -5357,16 +5257,16 @@
       <c r="E40" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F40" s="85" t="s">
+      <c r="F40" s="108" t="s">
         <v>187</v>
       </c>
-      <c r="G40" s="86"/>
-      <c r="H40" s="86"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="86"/>
-      <c r="K40" s="86"/>
-      <c r="L40" s="86"/>
-      <c r="M40" s="87"/>
+      <c r="G40" s="109"/>
+      <c r="H40" s="109"/>
+      <c r="I40" s="109"/>
+      <c r="J40" s="109"/>
+      <c r="K40" s="109"/>
+      <c r="L40" s="109"/>
+      <c r="M40" s="110"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="19" t="s">
@@ -5382,12 +5282,12 @@
       <c r="G41" s="27"/>
       <c r="H41" s="27"/>
       <c r="I41" s="28"/>
-      <c r="J41" s="85" t="s">
+      <c r="J41" s="108" t="s">
         <v>188</v>
       </c>
-      <c r="K41" s="86"/>
-      <c r="L41" s="86"/>
-      <c r="M41" s="87"/>
+      <c r="K41" s="109"/>
+      <c r="L41" s="109"/>
+      <c r="M41" s="110"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="19" t="s">
@@ -5422,12 +5322,12 @@
       <c r="G43" s="70"/>
       <c r="H43" s="70"/>
       <c r="I43" s="71"/>
-      <c r="J43" s="104" t="s">
+      <c r="J43" s="121" t="s">
         <v>120</v>
       </c>
-      <c r="K43" s="105"/>
-      <c r="L43" s="105"/>
-      <c r="M43" s="106"/>
+      <c r="K43" s="122"/>
+      <c r="L43" s="122"/>
+      <c r="M43" s="123"/>
     </row>
     <row r="44" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
@@ -5439,16 +5339,16 @@
       <c r="E44" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="F44" s="101" t="s">
+      <c r="F44" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="G44" s="102"/>
-      <c r="H44" s="102"/>
-      <c r="I44" s="102"/>
-      <c r="J44" s="102"/>
-      <c r="K44" s="102"/>
-      <c r="L44" s="102"/>
-      <c r="M44" s="103"/>
+      <c r="G44" s="119"/>
+      <c r="H44" s="119"/>
+      <c r="I44" s="119"/>
+      <c r="J44" s="119"/>
+      <c r="K44" s="119"/>
+      <c r="L44" s="119"/>
+      <c r="M44" s="120"/>
       <c r="O44" t="s">
         <v>364</v>
       </c>
@@ -5463,16 +5363,16 @@
       <c r="E45" s="24" t="s">
         <v>354</v>
       </c>
-      <c r="F45" s="101" t="s">
+      <c r="F45" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="G45" s="102"/>
-      <c r="H45" s="102"/>
-      <c r="I45" s="102"/>
-      <c r="J45" s="102"/>
-      <c r="K45" s="102"/>
-      <c r="L45" s="102"/>
-      <c r="M45" s="103"/>
+      <c r="G45" s="119"/>
+      <c r="H45" s="119"/>
+      <c r="I45" s="119"/>
+      <c r="J45" s="119"/>
+      <c r="K45" s="119"/>
+      <c r="L45" s="119"/>
+      <c r="M45" s="120"/>
       <c r="O45" t="s">
         <v>364</v>
       </c>
@@ -5487,16 +5387,16 @@
       <c r="E46" s="24" t="s">
         <v>355</v>
       </c>
-      <c r="F46" s="101" t="s">
+      <c r="F46" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="G46" s="102"/>
-      <c r="H46" s="102"/>
-      <c r="I46" s="102"/>
-      <c r="J46" s="102"/>
-      <c r="K46" s="102"/>
-      <c r="L46" s="102"/>
-      <c r="M46" s="103"/>
+      <c r="G46" s="119"/>
+      <c r="H46" s="119"/>
+      <c r="I46" s="119"/>
+      <c r="J46" s="119"/>
+      <c r="K46" s="119"/>
+      <c r="L46" s="119"/>
+      <c r="M46" s="120"/>
       <c r="O46" t="s">
         <v>364</v>
       </c>
@@ -5530,16 +5430,16 @@
       <c r="E48" s="23" t="s">
         <v>358</v>
       </c>
-      <c r="F48" s="101" t="s">
+      <c r="F48" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="G48" s="102"/>
-      <c r="H48" s="102"/>
-      <c r="I48" s="102"/>
-      <c r="J48" s="102"/>
-      <c r="K48" s="102"/>
-      <c r="L48" s="102"/>
-      <c r="M48" s="103"/>
+      <c r="G48" s="119"/>
+      <c r="H48" s="119"/>
+      <c r="I48" s="119"/>
+      <c r="J48" s="119"/>
+      <c r="K48" s="119"/>
+      <c r="L48" s="119"/>
+      <c r="M48" s="120"/>
       <c r="O48" t="s">
         <v>364</v>
       </c>
@@ -5554,16 +5454,16 @@
       <c r="E49" s="24" t="s">
         <v>359</v>
       </c>
-      <c r="F49" s="101" t="s">
+      <c r="F49" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="G49" s="102"/>
-      <c r="H49" s="102"/>
-      <c r="I49" s="102"/>
-      <c r="J49" s="102"/>
-      <c r="K49" s="102"/>
-      <c r="L49" s="102"/>
-      <c r="M49" s="103"/>
+      <c r="G49" s="119"/>
+      <c r="H49" s="119"/>
+      <c r="I49" s="119"/>
+      <c r="J49" s="119"/>
+      <c r="K49" s="119"/>
+      <c r="L49" s="119"/>
+      <c r="M49" s="120"/>
       <c r="O49" t="s">
         <v>364</v>
       </c>
@@ -5578,16 +5478,16 @@
       <c r="E50" s="24" t="s">
         <v>360</v>
       </c>
-      <c r="F50" s="101" t="s">
+      <c r="F50" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="G50" s="102"/>
-      <c r="H50" s="102"/>
-      <c r="I50" s="102"/>
-      <c r="J50" s="102"/>
-      <c r="K50" s="102"/>
-      <c r="L50" s="102"/>
-      <c r="M50" s="103"/>
+      <c r="G50" s="119"/>
+      <c r="H50" s="119"/>
+      <c r="I50" s="119"/>
+      <c r="J50" s="119"/>
+      <c r="K50" s="119"/>
+      <c r="L50" s="119"/>
+      <c r="M50" s="120"/>
       <c r="O50" t="s">
         <v>364</v>
       </c>
@@ -5621,16 +5521,16 @@
       <c r="E52" s="23" t="s">
         <v>339</v>
       </c>
-      <c r="F52" s="85" t="s">
+      <c r="F52" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G52" s="86"/>
-      <c r="H52" s="86"/>
-      <c r="I52" s="86"/>
-      <c r="J52" s="86"/>
-      <c r="K52" s="86"/>
-      <c r="L52" s="86"/>
-      <c r="M52" s="87"/>
+      <c r="G52" s="109"/>
+      <c r="H52" s="109"/>
+      <c r="I52" s="109"/>
+      <c r="J52" s="109"/>
+      <c r="K52" s="109"/>
+      <c r="L52" s="109"/>
+      <c r="M52" s="110"/>
       <c r="O52" t="s">
         <v>335</v>
       </c>
@@ -5645,16 +5545,16 @@
       <c r="E53" s="24" t="s">
         <v>356</v>
       </c>
-      <c r="F53" s="85" t="s">
+      <c r="F53" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G53" s="86"/>
-      <c r="H53" s="86"/>
-      <c r="I53" s="86"/>
-      <c r="J53" s="86"/>
-      <c r="K53" s="86"/>
-      <c r="L53" s="86"/>
-      <c r="M53" s="87"/>
+      <c r="G53" s="109"/>
+      <c r="H53" s="109"/>
+      <c r="I53" s="109"/>
+      <c r="J53" s="109"/>
+      <c r="K53" s="109"/>
+      <c r="L53" s="109"/>
+      <c r="M53" s="110"/>
       <c r="O53" t="s">
         <v>335</v>
       </c>
@@ -5669,16 +5569,16 @@
       <c r="E54" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="F54" s="85" t="s">
+      <c r="F54" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G54" s="86"/>
-      <c r="H54" s="86"/>
-      <c r="I54" s="86"/>
-      <c r="J54" s="86"/>
-      <c r="K54" s="86"/>
-      <c r="L54" s="86"/>
-      <c r="M54" s="87"/>
+      <c r="G54" s="109"/>
+      <c r="H54" s="109"/>
+      <c r="I54" s="109"/>
+      <c r="J54" s="109"/>
+      <c r="K54" s="109"/>
+      <c r="L54" s="109"/>
+      <c r="M54" s="110"/>
       <c r="O54" t="s">
         <v>335</v>
       </c>
@@ -5712,16 +5612,16 @@
       <c r="E56" s="23" t="s">
         <v>361</v>
       </c>
-      <c r="F56" s="85" t="s">
+      <c r="F56" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G56" s="86"/>
-      <c r="H56" s="86"/>
-      <c r="I56" s="86"/>
-      <c r="J56" s="86"/>
-      <c r="K56" s="86"/>
-      <c r="L56" s="86"/>
-      <c r="M56" s="87"/>
+      <c r="G56" s="109"/>
+      <c r="H56" s="109"/>
+      <c r="I56" s="109"/>
+      <c r="J56" s="109"/>
+      <c r="K56" s="109"/>
+      <c r="L56" s="109"/>
+      <c r="M56" s="110"/>
       <c r="O56" t="s">
         <v>335</v>
       </c>
@@ -5736,16 +5636,16 @@
       <c r="E57" s="24" t="s">
         <v>362</v>
       </c>
-      <c r="F57" s="85" t="s">
+      <c r="F57" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G57" s="86"/>
-      <c r="H57" s="86"/>
-      <c r="I57" s="86"/>
-      <c r="J57" s="86"/>
-      <c r="K57" s="86"/>
-      <c r="L57" s="86"/>
-      <c r="M57" s="87"/>
+      <c r="G57" s="109"/>
+      <c r="H57" s="109"/>
+      <c r="I57" s="109"/>
+      <c r="J57" s="109"/>
+      <c r="K57" s="109"/>
+      <c r="L57" s="109"/>
+      <c r="M57" s="110"/>
       <c r="O57" t="s">
         <v>335</v>
       </c>
@@ -5760,16 +5660,16 @@
       <c r="E58" s="24" t="s">
         <v>363</v>
       </c>
-      <c r="F58" s="85" t="s">
+      <c r="F58" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G58" s="86"/>
-      <c r="H58" s="86"/>
-      <c r="I58" s="86"/>
-      <c r="J58" s="86"/>
-      <c r="K58" s="86"/>
-      <c r="L58" s="86"/>
-      <c r="M58" s="87"/>
+      <c r="G58" s="109"/>
+      <c r="H58" s="109"/>
+      <c r="I58" s="109"/>
+      <c r="J58" s="109"/>
+      <c r="K58" s="109"/>
+      <c r="L58" s="109"/>
+      <c r="M58" s="110"/>
       <c r="O58" t="s">
         <v>335</v>
       </c>
@@ -5927,16 +5827,16 @@
       <c r="E6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="92" t="s">
+      <c r="F6" s="86" t="s">
         <v>92</v>
       </c>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="94"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="88"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
@@ -5948,16 +5848,16 @@
       <c r="E7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="92" t="s">
+      <c r="F7" s="86" t="s">
         <v>181</v>
       </c>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="94"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="88"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
@@ -6019,12 +5919,12 @@
       <c r="I19" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="92" t="s">
+      <c r="J19" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="93"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="94"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="88"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="19" t="s">
@@ -6046,12 +5946,12 @@
       <c r="I20" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="92" t="s">
+      <c r="J20" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="94"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="87"/>
+      <c r="M20" s="88"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
@@ -6061,18 +5961,18 @@
         <v>35</v>
       </c>
       <c r="E21" s="6"/>
-      <c r="F21" s="92" t="s">
+      <c r="F21" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="94"/>
-      <c r="H21" s="92" t="s">
+      <c r="G21" s="88"/>
+      <c r="H21" s="86" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="93"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="94"/>
+      <c r="I21" s="87"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="88"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
@@ -6082,10 +5982,10 @@
         <v>35</v>
       </c>
       <c r="E22" s="6"/>
-      <c r="F22" s="92" t="s">
+      <c r="F22" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="94"/>
+      <c r="G22" s="88"/>
       <c r="H22" s="18"/>
       <c r="I22" s="11" t="s">
         <v>114</v>
@@ -6093,11 +5993,11 @@
       <c r="J22" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="K22" s="92" t="s">
+      <c r="K22" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="L22" s="93"/>
-      <c r="M22" s="94"/>
+      <c r="L22" s="87"/>
+      <c r="M22" s="88"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
@@ -6107,18 +6007,18 @@
         <v>35</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="92" t="s">
+      <c r="F23" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="92" t="s">
+      <c r="G23" s="87"/>
+      <c r="H23" s="87"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="86" t="s">
         <v>116</v>
       </c>
-      <c r="K23" s="93"/>
-      <c r="L23" s="93"/>
-      <c r="M23" s="94"/>
+      <c r="K23" s="87"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="88"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
@@ -6128,18 +6028,18 @@
         <v>35</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="92" t="s">
+      <c r="F24" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="92" t="s">
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="86" t="s">
         <v>116</v>
       </c>
-      <c r="K24" s="93"/>
-      <c r="L24" s="93"/>
-      <c r="M24" s="94"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="87"/>
+      <c r="M24" s="88"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
@@ -6149,18 +6049,18 @@
         <v>35</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="92" t="s">
+      <c r="F25" s="86" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="93"/>
-      <c r="H25" s="93"/>
-      <c r="I25" s="94"/>
-      <c r="J25" s="92" t="s">
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="93"/>
-      <c r="L25" s="93"/>
-      <c r="M25" s="94"/>
+      <c r="K25" s="87"/>
+      <c r="L25" s="87"/>
+      <c r="M25" s="88"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
@@ -6170,18 +6070,18 @@
         <v>35</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="92" t="s">
+      <c r="F26" s="86" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="93"/>
-      <c r="H26" s="93"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="92" t="s">
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="93"/>
-      <c r="L26" s="93"/>
-      <c r="M26" s="94"/>
+      <c r="K26" s="87"/>
+      <c r="L26" s="87"/>
+      <c r="M26" s="88"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="19" t="s">
@@ -6235,16 +6135,16 @@
       <c r="E29" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="92" t="s">
+      <c r="F29" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="94"/>
+      <c r="G29" s="87"/>
+      <c r="H29" s="87"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="87"/>
+      <c r="K29" s="87"/>
+      <c r="L29" s="87"/>
+      <c r="M29" s="88"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
@@ -6254,16 +6154,16 @@
         <v>35</v>
       </c>
       <c r="E30" s="6"/>
-      <c r="F30" s="92" t="s">
+      <c r="F30" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G30" s="93"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="94"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="87"/>
+      <c r="K30" s="87"/>
+      <c r="L30" s="87"/>
+      <c r="M30" s="88"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
@@ -6273,16 +6173,16 @@
         <v>35</v>
       </c>
       <c r="E31" s="6"/>
-      <c r="F31" s="92" t="s">
+      <c r="F31" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="94"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="87"/>
+      <c r="L31" s="87"/>
+      <c r="M31" s="88"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
@@ -6292,16 +6192,16 @@
         <v>35</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="92" t="s">
+      <c r="F32" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G32" s="93"/>
-      <c r="H32" s="93"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="93"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="94"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="87"/>
+      <c r="K32" s="87"/>
+      <c r="L32" s="87"/>
+      <c r="M32" s="88"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
@@ -6311,16 +6211,16 @@
         <v>35</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="92" t="s">
+      <c r="F33" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G33" s="93"/>
-      <c r="H33" s="93"/>
-      <c r="I33" s="93"/>
-      <c r="J33" s="93"/>
-      <c r="K33" s="93"/>
-      <c r="L33" s="93"/>
-      <c r="M33" s="94"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="87"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="87"/>
+      <c r="L33" s="87"/>
+      <c r="M33" s="88"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
@@ -6330,16 +6230,16 @@
         <v>35</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="92" t="s">
+      <c r="F34" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G34" s="93"/>
-      <c r="H34" s="93"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="93"/>
-      <c r="K34" s="93"/>
-      <c r="L34" s="93"/>
-      <c r="M34" s="94"/>
+      <c r="G34" s="87"/>
+      <c r="H34" s="87"/>
+      <c r="I34" s="87"/>
+      <c r="J34" s="87"/>
+      <c r="K34" s="87"/>
+      <c r="L34" s="87"/>
+      <c r="M34" s="88"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
@@ -6349,16 +6249,16 @@
         <v>35</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="92" t="s">
+      <c r="F35" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G35" s="93"/>
-      <c r="H35" s="93"/>
-      <c r="I35" s="93"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="93"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="94"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="87"/>
+      <c r="I35" s="87"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="87"/>
+      <c r="M35" s="88"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="19" t="s">
@@ -6368,16 +6268,16 @@
         <v>35</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="92" t="s">
+      <c r="F36" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G36" s="93"/>
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="94"/>
+      <c r="G36" s="87"/>
+      <c r="H36" s="87"/>
+      <c r="I36" s="87"/>
+      <c r="J36" s="87"/>
+      <c r="K36" s="87"/>
+      <c r="L36" s="87"/>
+      <c r="M36" s="88"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
@@ -6387,16 +6287,16 @@
         <v>35</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="92" t="s">
+      <c r="F37" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G37" s="93"/>
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="94"/>
+      <c r="G37" s="87"/>
+      <c r="H37" s="87"/>
+      <c r="I37" s="87"/>
+      <c r="J37" s="87"/>
+      <c r="K37" s="87"/>
+      <c r="L37" s="87"/>
+      <c r="M37" s="88"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
@@ -6406,16 +6306,16 @@
         <v>35</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="92" t="s">
+      <c r="F38" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G38" s="93"/>
-      <c r="H38" s="93"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="94"/>
+      <c r="G38" s="87"/>
+      <c r="H38" s="87"/>
+      <c r="I38" s="87"/>
+      <c r="J38" s="87"/>
+      <c r="K38" s="87"/>
+      <c r="L38" s="87"/>
+      <c r="M38" s="88"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
@@ -6450,11 +6350,11 @@
       <c r="I40" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J40" s="92" t="s">
+      <c r="J40" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K40" s="93"/>
-      <c r="L40" s="94"/>
+      <c r="K40" s="87"/>
+      <c r="L40" s="88"/>
       <c r="M40" s="13" t="s">
         <v>145</v>
       </c>
@@ -6475,11 +6375,11 @@
       <c r="I41" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J41" s="92" t="s">
+      <c r="J41" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K41" s="93"/>
-      <c r="L41" s="94"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
       <c r="M41" s="13" t="s">
         <v>145</v>
       </c>
@@ -6500,11 +6400,11 @@
       <c r="I42" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J42" s="92" t="s">
+      <c r="J42" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K42" s="93"/>
-      <c r="L42" s="94"/>
+      <c r="K42" s="87"/>
+      <c r="L42" s="88"/>
       <c r="M42" s="13" t="s">
         <v>145</v>
       </c>
@@ -6525,11 +6425,11 @@
       <c r="I43" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J43" s="92" t="s">
+      <c r="J43" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K43" s="93"/>
-      <c r="L43" s="94"/>
+      <c r="K43" s="87"/>
+      <c r="L43" s="88"/>
       <c r="M43" s="13" t="s">
         <v>145</v>
       </c>
@@ -6550,11 +6450,11 @@
       <c r="I44" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J44" s="92" t="s">
+      <c r="J44" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K44" s="93"/>
-      <c r="L44" s="94"/>
+      <c r="K44" s="87"/>
+      <c r="L44" s="88"/>
       <c r="M44" s="13" t="s">
         <v>145</v>
       </c>
@@ -6575,11 +6475,11 @@
       <c r="I45" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J45" s="92" t="s">
+      <c r="J45" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K45" s="93"/>
-      <c r="L45" s="94"/>
+      <c r="K45" s="87"/>
+      <c r="L45" s="88"/>
       <c r="M45" s="13" t="s">
         <v>145</v>
       </c>
@@ -6600,11 +6500,11 @@
       <c r="I46" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J46" s="92" t="s">
+      <c r="J46" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K46" s="93"/>
-      <c r="L46" s="94"/>
+      <c r="K46" s="87"/>
+      <c r="L46" s="88"/>
       <c r="M46" s="13" t="s">
         <v>145</v>
       </c>
@@ -6625,11 +6525,11 @@
       <c r="I47" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J47" s="92" t="s">
+      <c r="J47" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K47" s="93"/>
-      <c r="L47" s="94"/>
+      <c r="K47" s="87"/>
+      <c r="L47" s="88"/>
       <c r="M47" s="13" t="s">
         <v>145</v>
       </c>
@@ -6650,11 +6550,11 @@
       <c r="I48" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J48" s="92" t="s">
+      <c r="J48" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="K48" s="93"/>
-      <c r="L48" s="94"/>
+      <c r="K48" s="87"/>
+      <c r="L48" s="88"/>
       <c r="M48" s="13" t="s">
         <v>145</v>
       </c>
@@ -6684,18 +6584,18 @@
         <v>35</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="92" t="s">
+      <c r="F50" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G50" s="93"/>
-      <c r="H50" s="93"/>
-      <c r="I50" s="94"/>
-      <c r="J50" s="92" t="s">
+      <c r="G50" s="87"/>
+      <c r="H50" s="87"/>
+      <c r="I50" s="88"/>
+      <c r="J50" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K50" s="93"/>
-      <c r="L50" s="93"/>
-      <c r="M50" s="94"/>
+      <c r="K50" s="87"/>
+      <c r="L50" s="87"/>
+      <c r="M50" s="88"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
@@ -6705,18 +6605,18 @@
         <v>35</v>
       </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="92" t="s">
+      <c r="F51" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G51" s="93"/>
-      <c r="H51" s="93"/>
-      <c r="I51" s="94"/>
-      <c r="J51" s="92" t="s">
+      <c r="G51" s="87"/>
+      <c r="H51" s="87"/>
+      <c r="I51" s="88"/>
+      <c r="J51" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K51" s="93"/>
-      <c r="L51" s="93"/>
-      <c r="M51" s="94"/>
+      <c r="K51" s="87"/>
+      <c r="L51" s="87"/>
+      <c r="M51" s="88"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
@@ -6726,18 +6626,18 @@
         <v>35</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="92" t="s">
+      <c r="F52" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G52" s="93"/>
-      <c r="H52" s="93"/>
-      <c r="I52" s="94"/>
-      <c r="J52" s="92" t="s">
+      <c r="G52" s="87"/>
+      <c r="H52" s="87"/>
+      <c r="I52" s="88"/>
+      <c r="J52" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K52" s="93"/>
-      <c r="L52" s="93"/>
-      <c r="M52" s="94"/>
+      <c r="K52" s="87"/>
+      <c r="L52" s="87"/>
+      <c r="M52" s="88"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
@@ -6747,18 +6647,18 @@
         <v>35</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="92" t="s">
+      <c r="F53" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G53" s="93"/>
-      <c r="H53" s="93"/>
-      <c r="I53" s="94"/>
-      <c r="J53" s="92" t="s">
+      <c r="G53" s="87"/>
+      <c r="H53" s="87"/>
+      <c r="I53" s="88"/>
+      <c r="J53" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K53" s="93"/>
-      <c r="L53" s="93"/>
-      <c r="M53" s="94"/>
+      <c r="K53" s="87"/>
+      <c r="L53" s="87"/>
+      <c r="M53" s="88"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
@@ -6768,18 +6668,18 @@
         <v>35</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="92" t="s">
+      <c r="F54" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G54" s="93"/>
-      <c r="H54" s="93"/>
-      <c r="I54" s="94"/>
-      <c r="J54" s="92" t="s">
+      <c r="G54" s="87"/>
+      <c r="H54" s="87"/>
+      <c r="I54" s="88"/>
+      <c r="J54" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K54" s="93"/>
-      <c r="L54" s="93"/>
-      <c r="M54" s="94"/>
+      <c r="K54" s="87"/>
+      <c r="L54" s="87"/>
+      <c r="M54" s="88"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
@@ -6789,18 +6689,18 @@
         <v>35</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="92" t="s">
+      <c r="F55" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G55" s="93"/>
-      <c r="H55" s="93"/>
-      <c r="I55" s="94"/>
-      <c r="J55" s="92" t="s">
+      <c r="G55" s="87"/>
+      <c r="H55" s="87"/>
+      <c r="I55" s="88"/>
+      <c r="J55" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K55" s="93"/>
-      <c r="L55" s="93"/>
-      <c r="M55" s="94"/>
+      <c r="K55" s="87"/>
+      <c r="L55" s="87"/>
+      <c r="M55" s="88"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
@@ -6810,18 +6710,18 @@
         <v>35</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="92" t="s">
+      <c r="F56" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G56" s="93"/>
-      <c r="H56" s="93"/>
-      <c r="I56" s="94"/>
-      <c r="J56" s="92" t="s">
+      <c r="G56" s="87"/>
+      <c r="H56" s="87"/>
+      <c r="I56" s="88"/>
+      <c r="J56" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K56" s="93"/>
-      <c r="L56" s="93"/>
-      <c r="M56" s="94"/>
+      <c r="K56" s="87"/>
+      <c r="L56" s="87"/>
+      <c r="M56" s="88"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="19" t="s">
@@ -6831,18 +6731,18 @@
         <v>35</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="92" t="s">
+      <c r="F57" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G57" s="93"/>
-      <c r="H57" s="93"/>
-      <c r="I57" s="94"/>
-      <c r="J57" s="92" t="s">
+      <c r="G57" s="87"/>
+      <c r="H57" s="87"/>
+      <c r="I57" s="88"/>
+      <c r="J57" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K57" s="93"/>
-      <c r="L57" s="93"/>
-      <c r="M57" s="94"/>
+      <c r="K57" s="87"/>
+      <c r="L57" s="87"/>
+      <c r="M57" s="88"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
@@ -6852,18 +6752,18 @@
         <v>35</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="92" t="s">
+      <c r="F58" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="G58" s="93"/>
-      <c r="H58" s="93"/>
-      <c r="I58" s="94"/>
-      <c r="J58" s="92" t="s">
+      <c r="G58" s="87"/>
+      <c r="H58" s="87"/>
+      <c r="I58" s="88"/>
+      <c r="J58" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="K58" s="93"/>
-      <c r="L58" s="93"/>
-      <c r="M58" s="94"/>
+      <c r="K58" s="87"/>
+      <c r="L58" s="87"/>
+      <c r="M58" s="88"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="19" t="s">
@@ -6898,10 +6798,10 @@
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
       <c r="K60" s="10"/>
-      <c r="L60" s="85" t="s">
+      <c r="L60" s="108" t="s">
         <v>177</v>
       </c>
-      <c r="M60" s="84"/>
+      <c r="M60" s="85"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="19" t="s">
@@ -6919,10 +6819,10 @@
       <c r="I61" s="9"/>
       <c r="J61" s="9"/>
       <c r="K61" s="10"/>
-      <c r="L61" s="82" t="s">
+      <c r="L61" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="M61" s="84"/>
+      <c r="M61" s="85"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="19" t="s">
@@ -6940,10 +6840,10 @@
       <c r="I62" s="9"/>
       <c r="J62" s="9"/>
       <c r="K62" s="10"/>
-      <c r="L62" s="82" t="s">
+      <c r="L62" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="M62" s="84"/>
+      <c r="M62" s="85"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="19" t="s">
@@ -6961,10 +6861,10 @@
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
       <c r="K63" s="10"/>
-      <c r="L63" s="82" t="s">
+      <c r="L63" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="M63" s="84"/>
+      <c r="M63" s="85"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="19" t="s">
@@ -6982,10 +6882,10 @@
       <c r="I64" s="9"/>
       <c r="J64" s="9"/>
       <c r="K64" s="10"/>
-      <c r="L64" s="82" t="s">
+      <c r="L64" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="M64" s="84"/>
+      <c r="M64" s="85"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="19" t="s">
@@ -7003,10 +6903,10 @@
       <c r="I65" s="9"/>
       <c r="J65" s="9"/>
       <c r="K65" s="10"/>
-      <c r="L65" s="82" t="s">
+      <c r="L65" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="M65" s="84"/>
+      <c r="M65" s="85"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="19" t="s">
@@ -7024,10 +6924,10 @@
       <c r="I66" s="9"/>
       <c r="J66" s="9"/>
       <c r="K66" s="10"/>
-      <c r="L66" s="82" t="s">
+      <c r="L66" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="M66" s="84"/>
+      <c r="M66" s="85"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="19" t="s">
@@ -7045,10 +6945,10 @@
       <c r="I67" s="9"/>
       <c r="J67" s="9"/>
       <c r="K67" s="10"/>
-      <c r="L67" s="82" t="s">
+      <c r="L67" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="M67" s="84"/>
+      <c r="M67" s="85"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="19" t="s">
@@ -7066,10 +6966,10 @@
       <c r="I68" s="9"/>
       <c r="J68" s="9"/>
       <c r="K68" s="10"/>
-      <c r="L68" s="82" t="s">
+      <c r="L68" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="M68" s="84"/>
+      <c r="M68" s="85"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="19" t="s">
@@ -7098,16 +6998,16 @@
       <c r="E70" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="F70" s="85" t="s">
+      <c r="F70" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G70" s="86"/>
-      <c r="H70" s="86"/>
-      <c r="I70" s="86"/>
-      <c r="J70" s="86"/>
-      <c r="K70" s="86"/>
-      <c r="L70" s="86"/>
-      <c r="M70" s="87"/>
+      <c r="G70" s="109"/>
+      <c r="H70" s="109"/>
+      <c r="I70" s="109"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="109"/>
+      <c r="L70" s="109"/>
+      <c r="M70" s="110"/>
       <c r="O70" t="s">
         <v>335</v>
       </c>
@@ -7122,16 +7022,16 @@
       <c r="E71" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="F71" s="85" t="s">
+      <c r="F71" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G71" s="86"/>
-      <c r="H71" s="86"/>
-      <c r="I71" s="86"/>
-      <c r="J71" s="86"/>
-      <c r="K71" s="86"/>
-      <c r="L71" s="86"/>
-      <c r="M71" s="87"/>
+      <c r="G71" s="109"/>
+      <c r="H71" s="109"/>
+      <c r="I71" s="109"/>
+      <c r="J71" s="109"/>
+      <c r="K71" s="109"/>
+      <c r="L71" s="109"/>
+      <c r="M71" s="110"/>
       <c r="O71" t="s">
         <v>335</v>
       </c>
@@ -7146,16 +7046,16 @@
       <c r="E72" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="F72" s="85" t="s">
+      <c r="F72" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G72" s="86"/>
-      <c r="H72" s="86"/>
-      <c r="I72" s="86"/>
-      <c r="J72" s="86"/>
-      <c r="K72" s="86"/>
-      <c r="L72" s="86"/>
-      <c r="M72" s="87"/>
+      <c r="G72" s="109"/>
+      <c r="H72" s="109"/>
+      <c r="I72" s="109"/>
+      <c r="J72" s="109"/>
+      <c r="K72" s="109"/>
+      <c r="L72" s="109"/>
+      <c r="M72" s="110"/>
       <c r="O72" t="s">
         <v>335</v>
       </c>
@@ -7170,16 +7070,16 @@
       <c r="E73" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="F73" s="85" t="s">
+      <c r="F73" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G73" s="86"/>
-      <c r="H73" s="86"/>
-      <c r="I73" s="86"/>
-      <c r="J73" s="86"/>
-      <c r="K73" s="86"/>
-      <c r="L73" s="86"/>
-      <c r="M73" s="87"/>
+      <c r="G73" s="109"/>
+      <c r="H73" s="109"/>
+      <c r="I73" s="109"/>
+      <c r="J73" s="109"/>
+      <c r="K73" s="109"/>
+      <c r="L73" s="109"/>
+      <c r="M73" s="110"/>
       <c r="O73" t="s">
         <v>335</v>
       </c>
@@ -7194,16 +7094,16 @@
       <c r="E74" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="F74" s="85" t="s">
+      <c r="F74" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G74" s="86"/>
-      <c r="H74" s="86"/>
-      <c r="I74" s="86"/>
-      <c r="J74" s="86"/>
-      <c r="K74" s="86"/>
-      <c r="L74" s="86"/>
-      <c r="M74" s="87"/>
+      <c r="G74" s="109"/>
+      <c r="H74" s="109"/>
+      <c r="I74" s="109"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="109"/>
+      <c r="L74" s="109"/>
+      <c r="M74" s="110"/>
       <c r="O74" t="s">
         <v>335</v>
       </c>
@@ -7218,16 +7118,16 @@
       <c r="E75" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="F75" s="85" t="s">
+      <c r="F75" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G75" s="86"/>
-      <c r="H75" s="86"/>
-      <c r="I75" s="86"/>
-      <c r="J75" s="86"/>
-      <c r="K75" s="86"/>
-      <c r="L75" s="86"/>
-      <c r="M75" s="87"/>
+      <c r="G75" s="109"/>
+      <c r="H75" s="109"/>
+      <c r="I75" s="109"/>
+      <c r="J75" s="109"/>
+      <c r="K75" s="109"/>
+      <c r="L75" s="109"/>
+      <c r="M75" s="110"/>
       <c r="O75" t="s">
         <v>335</v>
       </c>
@@ -7242,16 +7142,16 @@
       <c r="E76" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="85" t="s">
+      <c r="F76" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G76" s="86"/>
-      <c r="H76" s="86"/>
-      <c r="I76" s="86"/>
-      <c r="J76" s="86"/>
-      <c r="K76" s="86"/>
-      <c r="L76" s="86"/>
-      <c r="M76" s="87"/>
+      <c r="G76" s="109"/>
+      <c r="H76" s="109"/>
+      <c r="I76" s="109"/>
+      <c r="J76" s="109"/>
+      <c r="K76" s="109"/>
+      <c r="L76" s="109"/>
+      <c r="M76" s="110"/>
       <c r="O76" t="s">
         <v>335</v>
       </c>
@@ -7266,16 +7166,16 @@
       <c r="E77" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="F77" s="85" t="s">
+      <c r="F77" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G77" s="86"/>
-      <c r="H77" s="86"/>
-      <c r="I77" s="86"/>
-      <c r="J77" s="86"/>
-      <c r="K77" s="86"/>
-      <c r="L77" s="86"/>
-      <c r="M77" s="87"/>
+      <c r="G77" s="109"/>
+      <c r="H77" s="109"/>
+      <c r="I77" s="109"/>
+      <c r="J77" s="109"/>
+      <c r="K77" s="109"/>
+      <c r="L77" s="109"/>
+      <c r="M77" s="110"/>
       <c r="O77" t="s">
         <v>335</v>
       </c>
@@ -7290,16 +7190,16 @@
       <c r="E78" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="F78" s="85" t="s">
+      <c r="F78" s="108" t="s">
         <v>334</v>
       </c>
-      <c r="G78" s="86"/>
-      <c r="H78" s="86"/>
-      <c r="I78" s="86"/>
-      <c r="J78" s="86"/>
-      <c r="K78" s="86"/>
-      <c r="L78" s="86"/>
-      <c r="M78" s="87"/>
+      <c r="G78" s="109"/>
+      <c r="H78" s="109"/>
+      <c r="I78" s="109"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="109"/>
+      <c r="L78" s="109"/>
+      <c r="M78" s="110"/>
       <c r="O78" t="s">
         <v>335</v>
       </c>
@@ -7502,14 +7402,14 @@
       <c r="E11" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="107"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="109"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="80"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="19" t="s">
@@ -7521,16 +7421,16 @@
       <c r="E12" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="76" t="s">
+      <c r="F12" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="78"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="83"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
@@ -7542,16 +7442,16 @@
       <c r="E13" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="F13" s="76" t="s">
+      <c r="F13" s="81" t="s">
         <v>207</v>
       </c>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="77"/>
-      <c r="M13" s="78"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="82"/>
+      <c r="M13" s="83"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
@@ -7563,16 +7463,16 @@
       <c r="E14" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="81" t="s">
         <v>208</v>
       </c>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="78"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82"/>
+      <c r="L14" s="82"/>
+      <c r="M14" s="83"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
@@ -7617,16 +7517,16 @@
       <c r="E16" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F16" s="110" t="s">
+      <c r="F16" s="89" t="s">
         <v>214</v>
       </c>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="112"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="91"/>
       <c r="N16" s="57" t="s">
         <v>299</v>
       </c>
@@ -7641,16 +7541,16 @@
       <c r="E17" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F17" s="110" t="s">
+      <c r="F17" s="89" t="s">
         <v>215</v>
       </c>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="112"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="91"/>
       <c r="N17" s="57" t="s">
         <v>299</v>
       </c>
@@ -7678,8 +7578,8 @@
       <c r="J18" s="56" t="s">
         <v>220</v>
       </c>
-      <c r="K18" s="107"/>
-      <c r="L18" s="109"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="80"/>
       <c r="M18" s="55" t="s">
         <v>221</v>
       </c>
@@ -7701,8 +7601,8 @@
       <c r="G19" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="H19" s="107"/>
-      <c r="I19" s="109"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="80"/>
       <c r="J19" s="56" t="s">
         <v>224</v>
       </c>
@@ -7724,16 +7624,16 @@
         <v>35</v>
       </c>
       <c r="E20" s="43"/>
-      <c r="F20" s="113" t="s">
+      <c r="F20" s="92" t="s">
         <v>228</v>
       </c>
-      <c r="G20" s="114"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="115"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="93"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="94"/>
       <c r="N20" t="s">
         <v>292</v>
       </c>
@@ -7746,16 +7646,16 @@
         <v>35</v>
       </c>
       <c r="E21" s="42"/>
-      <c r="F21" s="113" t="s">
+      <c r="F21" s="92" t="s">
         <v>229</v>
       </c>
-      <c r="G21" s="114"/>
-      <c r="H21" s="114"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="114"/>
-      <c r="L21" s="114"/>
-      <c r="M21" s="115"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="93"/>
+      <c r="J21" s="93"/>
+      <c r="K21" s="93"/>
+      <c r="L21" s="93"/>
+      <c r="M21" s="94"/>
       <c r="N21" t="s">
         <v>293</v>
       </c>
@@ -7768,16 +7668,16 @@
         <v>35</v>
       </c>
       <c r="E22" s="42"/>
-      <c r="F22" s="113" t="s">
+      <c r="F22" s="92" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="114"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="115"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="93"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="94"/>
       <c r="N22" t="s">
         <v>294</v>
       </c>
@@ -7790,16 +7690,16 @@
         <v>35</v>
       </c>
       <c r="E23" s="42"/>
-      <c r="F23" s="113" t="s">
+      <c r="F23" s="92" t="s">
         <v>231</v>
       </c>
-      <c r="G23" s="114"/>
-      <c r="H23" s="114"/>
-      <c r="I23" s="114"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="114"/>
-      <c r="L23" s="114"/>
-      <c r="M23" s="115"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="94"/>
       <c r="N23" t="s">
         <v>295</v>
       </c>
@@ -7814,16 +7714,16 @@
       <c r="E24" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F24" s="110" t="s">
+      <c r="F24" s="89" t="s">
         <v>232</v>
       </c>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="112"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="91"/>
       <c r="N24" s="59" t="s">
         <v>299</v>
       </c>
@@ -7838,16 +7738,16 @@
       <c r="E25" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F25" s="107"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="108"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="110" t="s">
+      <c r="F25" s="78"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="79"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="89" t="s">
         <v>233</v>
       </c>
-      <c r="L25" s="111"/>
-      <c r="M25" s="112"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="91"/>
       <c r="N25" s="57" t="s">
         <v>299</v>
       </c>
@@ -7860,16 +7760,16 @@
         <v>30</v>
       </c>
       <c r="E26" s="42"/>
-      <c r="F26" s="113" t="s">
+      <c r="F26" s="92" t="s">
         <v>234</v>
       </c>
-      <c r="G26" s="114"/>
-      <c r="H26" s="114"/>
-      <c r="I26" s="114"/>
-      <c r="J26" s="114"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="116"/>
-      <c r="M26" s="117"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="93"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="95"/>
+      <c r="M26" s="96"/>
       <c r="N26" t="s">
         <v>304</v>
       </c>
@@ -7882,16 +7782,16 @@
         <v>35</v>
       </c>
       <c r="E27" s="42"/>
-      <c r="F27" s="113" t="s">
+      <c r="F27" s="92" t="s">
         <v>235</v>
       </c>
-      <c r="G27" s="114"/>
-      <c r="H27" s="114"/>
-      <c r="I27" s="114"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="114"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="115"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
+      <c r="M27" s="94"/>
       <c r="N27" t="s">
         <v>296</v>
       </c>
@@ -7904,16 +7804,16 @@
         <v>35</v>
       </c>
       <c r="E28" s="42"/>
-      <c r="F28" s="113" t="s">
+      <c r="F28" s="92" t="s">
         <v>236</v>
       </c>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="114"/>
-      <c r="L28" s="114"/>
-      <c r="M28" s="115"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="93"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="93"/>
+      <c r="M28" s="94"/>
       <c r="N28" t="s">
         <v>297</v>
       </c>
@@ -7926,16 +7826,16 @@
         <v>35</v>
       </c>
       <c r="E29" s="42"/>
-      <c r="F29" s="113" t="s">
+      <c r="F29" s="92" t="s">
         <v>237</v>
       </c>
-      <c r="G29" s="114"/>
-      <c r="H29" s="114"/>
-      <c r="I29" s="114"/>
-      <c r="J29" s="114"/>
-      <c r="K29" s="114"/>
-      <c r="L29" s="114"/>
-      <c r="M29" s="115"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="93"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="93"/>
+      <c r="M29" s="94"/>
       <c r="N29" t="s">
         <v>298</v>
       </c>
@@ -7950,14 +7850,14 @@
       <c r="E30" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F30" s="107"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="108"/>
-      <c r="I30" s="108"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="108"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="109"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="80"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="60" t="s">
@@ -7969,14 +7869,14 @@
       <c r="E31" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F31" s="107"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="108"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="108"/>
-      <c r="K31" s="108"/>
-      <c r="L31" s="108"/>
-      <c r="M31" s="109"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="79"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="80"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="60" t="s">
@@ -7988,16 +7888,16 @@
       <c r="E32" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F32" s="110" t="s">
+      <c r="F32" s="89" t="s">
         <v>238</v>
       </c>
-      <c r="G32" s="111"/>
-      <c r="H32" s="111"/>
-      <c r="I32" s="111"/>
-      <c r="J32" s="111"/>
-      <c r="K32" s="111"/>
-      <c r="L32" s="111"/>
-      <c r="M32" s="112"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="90"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="91"/>
       <c r="N32" s="57" t="s">
         <v>299</v>
       </c>
@@ -8012,16 +7912,16 @@
       <c r="E33" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F33" s="110" t="s">
+      <c r="F33" s="89" t="s">
         <v>239</v>
       </c>
-      <c r="G33" s="112"/>
-      <c r="H33" s="107"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="108"/>
-      <c r="K33" s="108"/>
-      <c r="L33" s="108"/>
-      <c r="M33" s="109"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="80"/>
       <c r="N33" s="57" t="s">
         <v>299</v>
       </c>
@@ -8036,16 +7936,16 @@
       <c r="E34" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F34" s="107"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="108"/>
-      <c r="I34" s="108"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="110" t="s">
+      <c r="F34" s="78"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="89" t="s">
         <v>240</v>
       </c>
-      <c r="L34" s="111"/>
-      <c r="M34" s="112"/>
+      <c r="L34" s="90"/>
+      <c r="M34" s="91"/>
       <c r="N34" s="57" t="s">
         <v>299</v>
       </c>
@@ -8060,16 +7960,16 @@
       <c r="E35" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F35" s="107"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="108"/>
-      <c r="I35" s="109"/>
-      <c r="J35" s="110" t="s">
+      <c r="F35" s="78"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="80"/>
+      <c r="J35" s="89" t="s">
         <v>241</v>
       </c>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="112"/>
+      <c r="K35" s="90"/>
+      <c r="L35" s="90"/>
+      <c r="M35" s="91"/>
       <c r="N35" s="57" t="s">
         <v>299</v>
       </c>
@@ -8084,16 +7984,16 @@
       <c r="E36" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F36" s="107"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="108"/>
-      <c r="I36" s="109"/>
-      <c r="J36" s="110" t="s">
+      <c r="F36" s="78"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="89" t="s">
         <v>242</v>
       </c>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="112"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="91"/>
       <c r="N36" s="57" t="s">
         <v>299</v>
       </c>
@@ -8108,16 +8008,16 @@
       <c r="E37" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F37" s="110" t="s">
+      <c r="F37" s="89" t="s">
         <v>243</v>
       </c>
-      <c r="G37" s="111"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="111"/>
-      <c r="J37" s="111"/>
-      <c r="K37" s="111"/>
-      <c r="L37" s="111"/>
-      <c r="M37" s="112"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="90"/>
+      <c r="I37" s="90"/>
+      <c r="J37" s="90"/>
+      <c r="K37" s="90"/>
+      <c r="L37" s="90"/>
+      <c r="M37" s="91"/>
       <c r="N37" s="57" t="s">
         <v>299</v>
       </c>
@@ -8132,14 +8032,14 @@
       <c r="E38" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F38" s="107"/>
-      <c r="G38" s="108"/>
-      <c r="H38" s="108"/>
-      <c r="I38" s="108"/>
-      <c r="J38" s="108"/>
-      <c r="K38" s="108"/>
-      <c r="L38" s="108"/>
-      <c r="M38" s="109"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="79"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="79"/>
+      <c r="J38" s="79"/>
+      <c r="K38" s="79"/>
+      <c r="L38" s="79"/>
+      <c r="M38" s="80"/>
     </row>
     <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="60" t="s">
@@ -8151,14 +8051,14 @@
       <c r="E39" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F39" s="107"/>
-      <c r="G39" s="108"/>
-      <c r="H39" s="108"/>
-      <c r="I39" s="108"/>
-      <c r="J39" s="108"/>
-      <c r="K39" s="108"/>
-      <c r="L39" s="108"/>
-      <c r="M39" s="109"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="79"/>
+      <c r="M39" s="80"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="60" t="s">
@@ -8170,14 +8070,14 @@
       <c r="E40" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F40" s="107"/>
-      <c r="G40" s="108"/>
-      <c r="H40" s="108"/>
-      <c r="I40" s="108"/>
-      <c r="J40" s="108"/>
-      <c r="K40" s="108"/>
-      <c r="L40" s="108"/>
-      <c r="M40" s="109"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="79"/>
+      <c r="L40" s="79"/>
+      <c r="M40" s="80"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="60" t="s">
@@ -8189,14 +8089,14 @@
       <c r="E41" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F41" s="107"/>
-      <c r="G41" s="108"/>
-      <c r="H41" s="108"/>
-      <c r="I41" s="108"/>
-      <c r="J41" s="108"/>
-      <c r="K41" s="108"/>
-      <c r="L41" s="108"/>
-      <c r="M41" s="109"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="79"/>
+      <c r="H41" s="79"/>
+      <c r="I41" s="79"/>
+      <c r="J41" s="79"/>
+      <c r="K41" s="79"/>
+      <c r="L41" s="79"/>
+      <c r="M41" s="80"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="60" t="s">
@@ -8208,14 +8108,14 @@
       <c r="E42" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F42" s="107"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="108"/>
-      <c r="I42" s="108"/>
-      <c r="J42" s="108"/>
-      <c r="K42" s="108"/>
-      <c r="L42" s="108"/>
-      <c r="M42" s="109"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="79"/>
+      <c r="I42" s="79"/>
+      <c r="J42" s="79"/>
+      <c r="K42" s="79"/>
+      <c r="L42" s="79"/>
+      <c r="M42" s="80"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="20" t="s">
@@ -8237,12 +8137,12 @@
       <c r="I43" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="76" t="s">
+      <c r="J43" s="81" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="77"/>
-      <c r="L43" s="77"/>
-      <c r="M43" s="78"/>
+      <c r="K43" s="82"/>
+      <c r="L43" s="82"/>
+      <c r="M43" s="83"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
@@ -8252,18 +8152,18 @@
         <v>35</v>
       </c>
       <c r="E44" s="43"/>
-      <c r="F44" s="76" t="s">
+      <c r="F44" s="81" t="s">
         <v>252</v>
       </c>
-      <c r="G44" s="78"/>
-      <c r="H44" s="76" t="s">
+      <c r="G44" s="83"/>
+      <c r="H44" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="I44" s="77"/>
-      <c r="J44" s="77"/>
-      <c r="K44" s="77"/>
-      <c r="L44" s="77"/>
-      <c r="M44" s="78"/>
+      <c r="I44" s="82"/>
+      <c r="J44" s="82"/>
+      <c r="K44" s="82"/>
+      <c r="L44" s="82"/>
+      <c r="M44" s="83"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="19" t="s">
@@ -8273,18 +8173,18 @@
         <v>35</v>
       </c>
       <c r="E45" s="43"/>
-      <c r="F45" s="118" t="s">
+      <c r="F45" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="G45" s="119"/>
-      <c r="H45" s="119"/>
-      <c r="I45" s="120"/>
-      <c r="J45" s="76" t="s">
+      <c r="G45" s="99"/>
+      <c r="H45" s="99"/>
+      <c r="I45" s="100"/>
+      <c r="J45" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="K45" s="77"/>
-      <c r="L45" s="77"/>
-      <c r="M45" s="78"/>
+      <c r="K45" s="82"/>
+      <c r="L45" s="82"/>
+      <c r="M45" s="83"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="19" t="s">
@@ -8294,18 +8194,18 @@
         <v>35</v>
       </c>
       <c r="E46" s="6"/>
-      <c r="F46" s="76" t="s">
+      <c r="F46" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="77"/>
-      <c r="H46" s="77"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="121" t="s">
+      <c r="G46" s="82"/>
+      <c r="H46" s="82"/>
+      <c r="I46" s="83"/>
+      <c r="J46" s="101" t="s">
         <v>118</v>
       </c>
-      <c r="K46" s="122"/>
-      <c r="L46" s="122"/>
-      <c r="M46" s="123"/>
+      <c r="K46" s="102"/>
+      <c r="L46" s="102"/>
+      <c r="M46" s="103"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="19" t="s">
@@ -8315,16 +8215,16 @@
         <v>35</v>
       </c>
       <c r="E47" s="6"/>
-      <c r="F47" s="92" t="s">
+      <c r="F47" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="G47" s="93"/>
-      <c r="H47" s="93"/>
-      <c r="I47" s="93"/>
-      <c r="J47" s="93"/>
-      <c r="K47" s="93"/>
-      <c r="L47" s="93"/>
-      <c r="M47" s="94"/>
+      <c r="G47" s="87"/>
+      <c r="H47" s="87"/>
+      <c r="I47" s="87"/>
+      <c r="J47" s="87"/>
+      <c r="K47" s="87"/>
+      <c r="L47" s="87"/>
+      <c r="M47" s="88"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="19" t="s">
@@ -8334,20 +8234,20 @@
         <v>35</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="90"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="77"/>
       <c r="H48" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="I48" s="92" t="s">
+      <c r="I48" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="J48" s="93"/>
-      <c r="K48" s="94"/>
-      <c r="L48" s="92" t="s">
+      <c r="J48" s="87"/>
+      <c r="K48" s="88"/>
+      <c r="L48" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="M48" s="94"/>
+      <c r="M48" s="88"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="19" t="s">
@@ -8390,15 +8290,15 @@
         <v>35</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="88"/>
-      <c r="G50" s="89"/>
-      <c r="H50" s="89"/>
-      <c r="I50" s="90"/>
-      <c r="J50" s="92" t="s">
+      <c r="F50" s="76"/>
+      <c r="G50" s="97"/>
+      <c r="H50" s="97"/>
+      <c r="I50" s="77"/>
+      <c r="J50" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="K50" s="93"/>
-      <c r="L50" s="94"/>
+      <c r="K50" s="87"/>
+      <c r="L50" s="88"/>
       <c r="M50" s="13" t="s">
         <v>81</v>
       </c>
@@ -8413,16 +8313,16 @@
       <c r="E51" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F51" s="107"/>
-      <c r="G51" s="108"/>
-      <c r="H51" s="108"/>
-      <c r="I51" s="108"/>
-      <c r="J51" s="108"/>
-      <c r="K51" s="109"/>
-      <c r="L51" s="82" t="s">
+      <c r="F51" s="78"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="79"/>
+      <c r="I51" s="79"/>
+      <c r="J51" s="79"/>
+      <c r="K51" s="80"/>
+      <c r="L51" s="84" t="s">
         <v>257</v>
       </c>
-      <c r="M51" s="84"/>
+      <c r="M51" s="85"/>
     </row>
     <row r="52" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
@@ -8434,16 +8334,16 @@
       <c r="E52" s="21" t="s">
         <v>368</v>
       </c>
-      <c r="F52" s="82" t="s">
+      <c r="F52" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="84"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="104"/>
+      <c r="M52" s="85"/>
       <c r="N52" t="s">
         <v>335</v>
       </c>
@@ -8458,18 +8358,18 @@
       <c r="E53" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="F53" s="82" t="s">
+      <c r="F53" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="84"/>
+      <c r="G53" s="104"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="104"/>
+      <c r="M53" s="85"/>
       <c r="N53" t="s">
-        <v>385</v>
+        <v>335</v>
       </c>
     </row>
     <row r="54" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8482,18 +8382,18 @@
       <c r="E54" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="F54" s="82" t="s">
+      <c r="F54" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="83"/>
-      <c r="J54" s="83"/>
-      <c r="K54" s="83"/>
-      <c r="L54" s="83"/>
-      <c r="M54" s="84"/>
+      <c r="G54" s="104"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="104"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="104"/>
+      <c r="M54" s="85"/>
       <c r="N54" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8506,18 +8406,18 @@
       <c r="E55" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="F55" s="82" t="s">
+      <c r="F55" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="G55" s="83"/>
-      <c r="H55" s="83"/>
-      <c r="I55" s="83"/>
-      <c r="J55" s="83"/>
-      <c r="K55" s="83"/>
-      <c r="L55" s="83"/>
-      <c r="M55" s="84"/>
+      <c r="G55" s="104"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="104"/>
+      <c r="K55" s="104"/>
+      <c r="L55" s="104"/>
+      <c r="M55" s="85"/>
       <c r="N55" t="s">
-        <v>387</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8530,18 +8430,18 @@
       <c r="E56" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="F56" s="82" t="s">
+      <c r="F56" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="83"/>
-      <c r="J56" s="83"/>
-      <c r="K56" s="83"/>
-      <c r="L56" s="83"/>
-      <c r="M56" s="84"/>
+      <c r="G56" s="104"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="104"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="104"/>
+      <c r="M56" s="85"/>
       <c r="N56" t="s">
-        <v>388</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8554,18 +8454,18 @@
       <c r="E57" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="F57" s="82" t="s">
+      <c r="F57" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="83"/>
-      <c r="J57" s="83"/>
-      <c r="K57" s="83"/>
-      <c r="L57" s="83"/>
-      <c r="M57" s="84"/>
+      <c r="G57" s="104"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="104"/>
+      <c r="K57" s="104"/>
+      <c r="L57" s="104"/>
+      <c r="M57" s="85"/>
       <c r="N57" t="s">
-        <v>389</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8578,18 +8478,18 @@
       <c r="E58" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="F58" s="82" t="s">
+      <c r="F58" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="83"/>
-      <c r="J58" s="83"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="84"/>
+      <c r="G58" s="104"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="104"/>
+      <c r="K58" s="104"/>
+      <c r="L58" s="104"/>
+      <c r="M58" s="85"/>
       <c r="N58" t="s">
-        <v>390</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8602,18 +8502,18 @@
       <c r="E59" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="F59" s="82" t="s">
+      <c r="F59" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="G59" s="83"/>
-      <c r="H59" s="83"/>
-      <c r="I59" s="83"/>
-      <c r="J59" s="83"/>
-      <c r="K59" s="83"/>
-      <c r="L59" s="83"/>
-      <c r="M59" s="84"/>
+      <c r="G59" s="104"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="104"/>
+      <c r="K59" s="104"/>
+      <c r="L59" s="104"/>
+      <c r="M59" s="85"/>
       <c r="N59" t="s">
-        <v>391</v>
+        <v>335</v>
       </c>
     </row>
     <row r="60" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8626,38 +8526,43 @@
       <c r="E60" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="F60" s="82" t="s">
+      <c r="F60" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="G60" s="83"/>
-      <c r="H60" s="83"/>
-      <c r="I60" s="83"/>
-      <c r="J60" s="83"/>
-      <c r="K60" s="83"/>
-      <c r="L60" s="83"/>
-      <c r="M60" s="84"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="104"/>
+      <c r="L60" s="104"/>
+      <c r="M60" s="85"/>
       <c r="N60" t="s">
-        <v>392</v>
+        <v>335</v>
       </c>
     </row>
     <row r="61" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C61" s="60" t="s">
+      <c r="C61" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="D61" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="E61" s="62" t="s">
-        <v>206</v>
-      </c>
-      <c r="F61" s="107"/>
-      <c r="G61" s="108"/>
-      <c r="H61" s="108"/>
-      <c r="I61" s="108"/>
-      <c r="J61" s="108"/>
-      <c r="K61" s="108"/>
-      <c r="L61" s="108"/>
-      <c r="M61" s="109"/>
+      <c r="D61" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="F61" s="84" t="s">
+        <v>334</v>
+      </c>
+      <c r="G61" s="104"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="104"/>
+      <c r="K61" s="104"/>
+      <c r="L61" s="104"/>
+      <c r="M61" s="85"/>
+      <c r="N61" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="62" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="63" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8682,8 +8587,8 @@
       <c r="J63" s="54" t="s">
         <v>291</v>
       </c>
-      <c r="K63" s="88"/>
-      <c r="L63" s="90"/>
+      <c r="K63" s="76"/>
+      <c r="L63" s="77"/>
       <c r="M63" s="54" t="s">
         <v>290</v>
       </c>
@@ -8782,7 +8687,7 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3509D6-DF06-4EF8-AD02-5EFF184678FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBAAC76-ED9A-4480-B2F2-33D7E5CE2C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -1317,10 +1317,6 @@
   </si>
   <si>
     <t>I/O Enabler1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>I/O Enabler2(Mirror 3FFFh)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1953,9 +1949,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>7FF9h</t>
-  </si>
-  <si>
     <t>7FFAh</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1985,10 +1978,6 @@
   </si>
   <si>
     <t>モジュール</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7FFCh</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2008,6 +1997,18 @@
   </si>
   <si>
     <t>ADPCM PAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FFFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF9h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I/O Enabler2</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2748,12 +2749,60 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2763,30 +2812,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2811,28 +2836,19 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2844,25 +2860,28 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2872,24 +2891,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3628,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -3677,16 +3678,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.15">
@@ -3697,13 +3698,13 @@
         <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.15">
@@ -3805,7 +3806,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>23</v>
@@ -3820,7 +3821,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>11</v>
@@ -3873,7 +3874,7 @@
         <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G3" s="68" t="s">
         <v>71</v>
@@ -3900,196 +3901,196 @@
         <v>78</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C4" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="76"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="77"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="81"/>
       <c r="N4" s="67" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O4" s="52" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C5" s="64" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="105" t="s">
-        <v>279</v>
-      </c>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="106"/>
-      <c r="L5" s="106"/>
-      <c r="M5" s="106"/>
-      <c r="N5" s="107"/>
+      <c r="G5" s="110" t="s">
+        <v>278</v>
+      </c>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="111"/>
+      <c r="N5" s="112"/>
       <c r="O5" s="50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C6" s="65" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="105" t="s">
-        <v>279</v>
-      </c>
-      <c r="H6" s="106"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="107"/>
+      <c r="G6" s="110" t="s">
+        <v>278</v>
+      </c>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="112"/>
       <c r="O6" s="50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="105" t="s">
-        <v>279</v>
-      </c>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="107"/>
+      <c r="G7" s="110" t="s">
+        <v>278</v>
+      </c>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="111"/>
+      <c r="N7" s="112"/>
       <c r="O7" s="50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C8" s="65" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="105" t="s">
-        <v>279</v>
-      </c>
-      <c r="H8" s="106"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="106"/>
-      <c r="K8" s="106"/>
-      <c r="L8" s="106"/>
-      <c r="M8" s="106"/>
-      <c r="N8" s="107"/>
+      <c r="G8" s="110" t="s">
+        <v>278</v>
+      </c>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="112"/>
       <c r="O8" s="50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C9" s="65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="81" t="s">
-        <v>280</v>
-      </c>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="83"/>
+      <c r="G9" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
+      <c r="M9" s="86"/>
+      <c r="N9" s="87"/>
       <c r="O9" s="50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C10" s="65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="81" t="s">
-        <v>280</v>
-      </c>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="82"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="83"/>
+      <c r="G10" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="86"/>
+      <c r="K10" s="86"/>
+      <c r="L10" s="86"/>
+      <c r="M10" s="86"/>
+      <c r="N10" s="87"/>
       <c r="O10" s="50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4103,20 +4104,20 @@
         <v>262</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G11" s="84" t="s">
+        <v>308</v>
+      </c>
+      <c r="G11" s="76" t="s">
         <v>262</v>
       </c>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="104"/>
-      <c r="N11" s="85"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="78"/>
       <c r="O11" s="51" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4130,20 +4131,20 @@
         <v>263</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G12" s="84" t="s">
+        <v>308</v>
+      </c>
+      <c r="G12" s="76" t="s">
         <v>263</v>
       </c>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="104"/>
-      <c r="N12" s="85"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="77"/>
+      <c r="N12" s="78"/>
       <c r="O12" s="51" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4154,23 +4155,23 @@
         <v>35</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G13" s="108" t="s">
-        <v>337</v>
-      </c>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="85"/>
+        <v>308</v>
+      </c>
+      <c r="G13" s="106" t="s">
+        <v>336</v>
+      </c>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="77"/>
+      <c r="N13" s="78"/>
       <c r="O13" s="51" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4181,23 +4182,23 @@
         <v>35</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G14" s="108" t="s">
-        <v>396</v>
-      </c>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="104"/>
-      <c r="N14" s="85"/>
+        <v>308</v>
+      </c>
+      <c r="G14" s="106" t="s">
+        <v>394</v>
+      </c>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="77"/>
+      <c r="N14" s="78"/>
       <c r="O14" s="51" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4208,23 +4209,23 @@
         <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G15" s="86" t="s">
-        <v>366</v>
-      </c>
-      <c r="H15" s="87"/>
-      <c r="I15" s="87"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="87"/>
-      <c r="L15" s="87"/>
-      <c r="M15" s="87"/>
-      <c r="N15" s="88"/>
+        <v>308</v>
+      </c>
+      <c r="G15" s="91" t="s">
+        <v>365</v>
+      </c>
+      <c r="H15" s="92"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="93"/>
       <c r="O15" s="51" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4235,23 +4236,23 @@
         <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G16" s="86" t="s">
-        <v>395</v>
-      </c>
-      <c r="H16" s="87"/>
-      <c r="I16" s="87"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="87"/>
-      <c r="L16" s="87"/>
-      <c r="M16" s="87"/>
-      <c r="N16" s="88"/>
+        <v>308</v>
+      </c>
+      <c r="G16" s="91" t="s">
+        <v>393</v>
+      </c>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="92"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="93"/>
       <c r="O16" s="51" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4265,234 +4266,244 @@
         <v>264</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G17" s="112"/>
-      <c r="H17" s="113"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="113"/>
-      <c r="K17" s="113"/>
-      <c r="L17" s="113"/>
-      <c r="M17" s="114"/>
+        <v>308</v>
+      </c>
+      <c r="G17" s="107"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="109"/>
       <c r="N17" s="11" t="s">
         <v>5</v>
       </c>
       <c r="O17" s="51" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="C18" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>265</v>
+        <v>387</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="H18" s="76"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="77"/>
-      <c r="M18" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="45" t="s">
-        <v>311</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="G18" s="106"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="113"/>
+      <c r="L18" s="113"/>
+      <c r="M18" s="113"/>
+      <c r="N18" s="114"/>
       <c r="O18" s="51" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G19" s="108"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="109"/>
-      <c r="L19" s="109"/>
-      <c r="M19" s="109"/>
-      <c r="N19" s="110"/>
+        <v>308</v>
+      </c>
+      <c r="G19" s="106"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="113"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="113"/>
+      <c r="L19" s="113"/>
+      <c r="M19" s="113"/>
+      <c r="N19" s="114"/>
       <c r="O19" s="51" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="12" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G20" s="108"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="110"/>
+        <v>308</v>
+      </c>
+      <c r="G20" s="106"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="113"/>
+      <c r="J20" s="113"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="113"/>
+      <c r="N20" s="114"/>
       <c r="O20" s="51" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G21" s="108"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="110"/>
+        <v>308</v>
+      </c>
+      <c r="G21" s="106"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="113"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="113"/>
+      <c r="N21" s="114"/>
       <c r="O21" s="51" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G22" s="108"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="110"/>
+        <v>308</v>
+      </c>
+      <c r="G22" s="72"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
       <c r="O22" s="51" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="C23" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G23" s="72"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="73"/>
-      <c r="K23" s="73"/>
-      <c r="L23" s="73"/>
-      <c r="M23" s="73"/>
-      <c r="N23" s="74"/>
+        <v>308</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="H23" s="79"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="80"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="45" t="s">
+        <v>310</v>
+      </c>
       <c r="O23" s="51" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="64" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="81" t="s">
-        <v>280</v>
-      </c>
-      <c r="H24" s="111"/>
-      <c r="I24" s="82"/>
-      <c r="J24" s="82"/>
-      <c r="K24" s="82"/>
-      <c r="L24" s="82"/>
-      <c r="M24" s="82"/>
-      <c r="N24" s="83"/>
+      <c r="G24" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="H24" s="105"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="86"/>
+      <c r="N24" s="87"/>
       <c r="O24" s="50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="66" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="81" t="s">
-        <v>280</v>
-      </c>
-      <c r="H25" s="82"/>
-      <c r="I25" s="82"/>
-      <c r="J25" s="82"/>
-      <c r="K25" s="82"/>
-      <c r="L25" s="82"/>
-      <c r="M25" s="82"/>
-      <c r="N25" s="83"/>
+      <c r="G25" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="87"/>
       <c r="O25" s="50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="G25:N25"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="G6:N6"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="G8:N8"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="G18:N18"/>
+    <mergeCell ref="G19:N19"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G21:N21"/>
     <mergeCell ref="G4:M4"/>
     <mergeCell ref="G9:N9"/>
     <mergeCell ref="G10:N10"/>
@@ -4503,17 +4514,7 @@
     <mergeCell ref="G15:N15"/>
     <mergeCell ref="G16:N16"/>
     <mergeCell ref="G17:M17"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="G25:N25"/>
-    <mergeCell ref="G5:N5"/>
-    <mergeCell ref="G6:N6"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="G8:N8"/>
-    <mergeCell ref="G12:N12"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="G21:N21"/>
-    <mergeCell ref="G22:N22"/>
+    <mergeCell ref="H23:L23"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4531,7 +4532,7 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
@@ -4585,7 +4586,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -4633,16 +4634,16 @@
       <c r="E12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="115" t="s">
+      <c r="F12" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="G12" s="116"/>
-      <c r="H12" s="116"/>
-      <c r="I12" s="116"/>
-      <c r="J12" s="116"/>
-      <c r="K12" s="116"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="117"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="123"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
@@ -4658,12 +4659,12 @@
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="115" t="s">
+      <c r="J13" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="K13" s="116"/>
-      <c r="L13" s="116"/>
-      <c r="M13" s="117"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="123"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
@@ -4675,16 +4676,16 @@
       <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="115" t="s">
+      <c r="F14" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="G14" s="116"/>
-      <c r="H14" s="116"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="116"/>
-      <c r="M14" s="117"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="123"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
@@ -4700,12 +4701,12 @@
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="36"/>
-      <c r="J15" s="115" t="s">
+      <c r="J15" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="K15" s="116"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="117"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="123"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="19" t="s">
@@ -4717,16 +4718,16 @@
       <c r="E16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="115" t="s">
+      <c r="F16" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="116"/>
-      <c r="H16" s="116"/>
-      <c r="I16" s="116"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="117"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="122"/>
+      <c r="K16" s="122"/>
+      <c r="L16" s="122"/>
+      <c r="M16" s="123"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="19" t="s">
@@ -4742,12 +4743,12 @@
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
-      <c r="J17" s="115" t="s">
+      <c r="J17" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="116"/>
-      <c r="L17" s="116"/>
-      <c r="M17" s="117"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="123"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="19" t="s">
@@ -4762,13 +4763,13 @@
       <c r="F18" s="34"/>
       <c r="G18" s="35"/>
       <c r="H18" s="36"/>
-      <c r="I18" s="115" t="s">
+      <c r="I18" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="J18" s="116"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="117"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="123"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="19" t="s">
@@ -4821,12 +4822,12 @@
       <c r="I20" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="115" t="s">
+      <c r="J20" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="117"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="123"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
@@ -4844,12 +4845,12 @@
       <c r="I21" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="115" t="s">
+      <c r="J21" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="117"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="122"/>
+      <c r="M21" s="123"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
@@ -4867,12 +4868,12 @@
       <c r="I22" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="115" t="s">
+      <c r="J22" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="117"/>
+      <c r="K22" s="122"/>
+      <c r="L22" s="122"/>
+      <c r="M22" s="123"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
@@ -4884,16 +4885,16 @@
       <c r="E23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F23" s="115" t="s">
+      <c r="F23" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="G23" s="116"/>
-      <c r="H23" s="116"/>
-      <c r="I23" s="116"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="116"/>
-      <c r="L23" s="116"/>
-      <c r="M23" s="117"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="122"/>
+      <c r="I23" s="122"/>
+      <c r="J23" s="122"/>
+      <c r="K23" s="122"/>
+      <c r="L23" s="122"/>
+      <c r="M23" s="123"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
@@ -4905,16 +4906,16 @@
       <c r="E24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="115" t="s">
+      <c r="F24" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="G24" s="116"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="116"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="116"/>
-      <c r="L24" s="116"/>
-      <c r="M24" s="117"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="122"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="123"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
@@ -4930,12 +4931,12 @@
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
       <c r="I25" s="36"/>
-      <c r="J25" s="115" t="s">
+      <c r="J25" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="K25" s="116"/>
-      <c r="L25" s="116"/>
-      <c r="M25" s="117"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="122"/>
+      <c r="M25" s="123"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
@@ -4985,16 +4986,16 @@
       <c r="E28" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="108" t="s">
+      <c r="F28" s="106" t="s">
         <v>182</v>
       </c>
-      <c r="G28" s="109"/>
-      <c r="H28" s="109"/>
-      <c r="I28" s="109"/>
-      <c r="J28" s="109"/>
-      <c r="K28" s="109"/>
-      <c r="L28" s="109"/>
-      <c r="M28" s="110"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="113"/>
+      <c r="J28" s="113"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="114"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="19" t="s">
@@ -5010,12 +5011,12 @@
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="I29" s="28"/>
-      <c r="J29" s="108" t="s">
+      <c r="J29" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="K29" s="109"/>
-      <c r="L29" s="109"/>
-      <c r="M29" s="110"/>
+      <c r="K29" s="113"/>
+      <c r="L29" s="113"/>
+      <c r="M29" s="114"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
@@ -5027,16 +5028,16 @@
       <c r="E30" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="108" t="s">
+      <c r="F30" s="106" t="s">
         <v>182</v>
       </c>
-      <c r="G30" s="109"/>
-      <c r="H30" s="109"/>
-      <c r="I30" s="109"/>
-      <c r="J30" s="109"/>
-      <c r="K30" s="109"/>
-      <c r="L30" s="109"/>
-      <c r="M30" s="110"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="114"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
@@ -5052,12 +5053,12 @@
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="I31" s="28"/>
-      <c r="J31" s="108" t="s">
+      <c r="J31" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="K31" s="109"/>
-      <c r="L31" s="109"/>
-      <c r="M31" s="110"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="114"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
@@ -5069,16 +5070,16 @@
       <c r="E32" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="108" t="s">
+      <c r="F32" s="106" t="s">
         <v>182</v>
       </c>
-      <c r="G32" s="109"/>
-      <c r="H32" s="109"/>
-      <c r="I32" s="109"/>
-      <c r="J32" s="109"/>
-      <c r="K32" s="109"/>
-      <c r="L32" s="109"/>
-      <c r="M32" s="110"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="113"/>
+      <c r="I32" s="113"/>
+      <c r="J32" s="113"/>
+      <c r="K32" s="113"/>
+      <c r="L32" s="113"/>
+      <c r="M32" s="114"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
@@ -5094,12 +5095,12 @@
       <c r="G33" s="27"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
-      <c r="J33" s="108" t="s">
+      <c r="J33" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="K33" s="109"/>
-      <c r="L33" s="109"/>
-      <c r="M33" s="110"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="113"/>
+      <c r="M33" s="114"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
@@ -5114,13 +5115,13 @@
       <c r="F34" s="26"/>
       <c r="G34" s="27"/>
       <c r="H34" s="28"/>
-      <c r="I34" s="108" t="s">
+      <c r="I34" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="110"/>
+      <c r="J34" s="113"/>
+      <c r="K34" s="113"/>
+      <c r="L34" s="113"/>
+      <c r="M34" s="114"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
@@ -5173,12 +5174,12 @@
       <c r="I36" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J36" s="108" t="s">
+      <c r="J36" s="106" t="s">
         <v>185</v>
       </c>
-      <c r="K36" s="109"/>
-      <c r="L36" s="109"/>
-      <c r="M36" s="110"/>
+      <c r="K36" s="113"/>
+      <c r="L36" s="113"/>
+      <c r="M36" s="114"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
@@ -5196,12 +5197,12 @@
       <c r="I37" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J37" s="108" t="s">
+      <c r="J37" s="106" t="s">
         <v>185</v>
       </c>
-      <c r="K37" s="109"/>
-      <c r="L37" s="109"/>
-      <c r="M37" s="110"/>
+      <c r="K37" s="113"/>
+      <c r="L37" s="113"/>
+      <c r="M37" s="114"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
@@ -5219,12 +5220,12 @@
       <c r="I38" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J38" s="108" t="s">
+      <c r="J38" s="106" t="s">
         <v>185</v>
       </c>
-      <c r="K38" s="109"/>
-      <c r="L38" s="109"/>
-      <c r="M38" s="110"/>
+      <c r="K38" s="113"/>
+      <c r="L38" s="113"/>
+      <c r="M38" s="114"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
@@ -5236,16 +5237,16 @@
       <c r="E39" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F39" s="108" t="s">
+      <c r="F39" s="106" t="s">
         <v>186</v>
       </c>
-      <c r="G39" s="109"/>
-      <c r="H39" s="109"/>
-      <c r="I39" s="109"/>
-      <c r="J39" s="109"/>
-      <c r="K39" s="109"/>
-      <c r="L39" s="109"/>
-      <c r="M39" s="110"/>
+      <c r="G39" s="113"/>
+      <c r="H39" s="113"/>
+      <c r="I39" s="113"/>
+      <c r="J39" s="113"/>
+      <c r="K39" s="113"/>
+      <c r="L39" s="113"/>
+      <c r="M39" s="114"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="19" t="s">
@@ -5257,16 +5258,16 @@
       <c r="E40" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F40" s="108" t="s">
+      <c r="F40" s="106" t="s">
         <v>187</v>
       </c>
-      <c r="G40" s="109"/>
-      <c r="H40" s="109"/>
-      <c r="I40" s="109"/>
-      <c r="J40" s="109"/>
-      <c r="K40" s="109"/>
-      <c r="L40" s="109"/>
-      <c r="M40" s="110"/>
+      <c r="G40" s="113"/>
+      <c r="H40" s="113"/>
+      <c r="I40" s="113"/>
+      <c r="J40" s="113"/>
+      <c r="K40" s="113"/>
+      <c r="L40" s="113"/>
+      <c r="M40" s="114"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="19" t="s">
@@ -5282,12 +5283,12 @@
       <c r="G41" s="27"/>
       <c r="H41" s="27"/>
       <c r="I41" s="28"/>
-      <c r="J41" s="108" t="s">
+      <c r="J41" s="106" t="s">
         <v>188</v>
       </c>
-      <c r="K41" s="109"/>
-      <c r="L41" s="109"/>
-      <c r="M41" s="110"/>
+      <c r="K41" s="113"/>
+      <c r="L41" s="113"/>
+      <c r="M41" s="114"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="19" t="s">
@@ -5322,12 +5323,12 @@
       <c r="G43" s="70"/>
       <c r="H43" s="70"/>
       <c r="I43" s="71"/>
-      <c r="J43" s="121" t="s">
+      <c r="J43" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="K43" s="122"/>
-      <c r="L43" s="122"/>
-      <c r="M43" s="123"/>
+      <c r="K43" s="119"/>
+      <c r="L43" s="119"/>
+      <c r="M43" s="120"/>
     </row>
     <row r="44" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
@@ -5337,20 +5338,20 @@
         <v>30</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="F44" s="118" t="s">
+        <v>337</v>
+      </c>
+      <c r="F44" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="G44" s="119"/>
-      <c r="H44" s="119"/>
-      <c r="I44" s="119"/>
-      <c r="J44" s="119"/>
-      <c r="K44" s="119"/>
-      <c r="L44" s="119"/>
-      <c r="M44" s="120"/>
+      <c r="G44" s="116"/>
+      <c r="H44" s="116"/>
+      <c r="I44" s="116"/>
+      <c r="J44" s="116"/>
+      <c r="K44" s="116"/>
+      <c r="L44" s="116"/>
+      <c r="M44" s="117"/>
       <c r="O44" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5361,49 +5362,49 @@
         <v>30</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>354</v>
-      </c>
-      <c r="F45" s="118" t="s">
+        <v>353</v>
+      </c>
+      <c r="F45" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="G45" s="119"/>
-      <c r="H45" s="119"/>
-      <c r="I45" s="119"/>
-      <c r="J45" s="119"/>
-      <c r="K45" s="119"/>
-      <c r="L45" s="119"/>
-      <c r="M45" s="120"/>
+      <c r="G45" s="116"/>
+      <c r="H45" s="116"/>
+      <c r="I45" s="116"/>
+      <c r="J45" s="116"/>
+      <c r="K45" s="116"/>
+      <c r="L45" s="116"/>
+      <c r="M45" s="117"/>
       <c r="O45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>355</v>
-      </c>
-      <c r="F46" s="118" t="s">
+        <v>354</v>
+      </c>
+      <c r="F46" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="G46" s="119"/>
-      <c r="H46" s="119"/>
-      <c r="I46" s="119"/>
-      <c r="J46" s="119"/>
-      <c r="K46" s="119"/>
-      <c r="L46" s="119"/>
-      <c r="M46" s="120"/>
+      <c r="G46" s="116"/>
+      <c r="H46" s="116"/>
+      <c r="I46" s="116"/>
+      <c r="J46" s="116"/>
+      <c r="K46" s="116"/>
+      <c r="L46" s="116"/>
+      <c r="M46" s="117"/>
       <c r="O46" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>30</v>
@@ -5422,79 +5423,79 @@
     </row>
     <row r="48" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="F48" s="118" t="s">
+        <v>357</v>
+      </c>
+      <c r="F48" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="G48" s="119"/>
-      <c r="H48" s="119"/>
-      <c r="I48" s="119"/>
-      <c r="J48" s="119"/>
-      <c r="K48" s="119"/>
-      <c r="L48" s="119"/>
-      <c r="M48" s="120"/>
+      <c r="G48" s="116"/>
+      <c r="H48" s="116"/>
+      <c r="I48" s="116"/>
+      <c r="J48" s="116"/>
+      <c r="K48" s="116"/>
+      <c r="L48" s="116"/>
+      <c r="M48" s="117"/>
       <c r="O48" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>359</v>
-      </c>
-      <c r="F49" s="118" t="s">
+        <v>358</v>
+      </c>
+      <c r="F49" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="G49" s="119"/>
-      <c r="H49" s="119"/>
-      <c r="I49" s="119"/>
-      <c r="J49" s="119"/>
-      <c r="K49" s="119"/>
-      <c r="L49" s="119"/>
-      <c r="M49" s="120"/>
+      <c r="G49" s="116"/>
+      <c r="H49" s="116"/>
+      <c r="I49" s="116"/>
+      <c r="J49" s="116"/>
+      <c r="K49" s="116"/>
+      <c r="L49" s="116"/>
+      <c r="M49" s="117"/>
       <c r="O49" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="F50" s="118" t="s">
+        <v>359</v>
+      </c>
+      <c r="F50" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="G50" s="119"/>
-      <c r="H50" s="119"/>
-      <c r="I50" s="119"/>
-      <c r="J50" s="119"/>
-      <c r="K50" s="119"/>
-      <c r="L50" s="119"/>
-      <c r="M50" s="120"/>
+      <c r="G50" s="116"/>
+      <c r="H50" s="116"/>
+      <c r="I50" s="116"/>
+      <c r="J50" s="116"/>
+      <c r="K50" s="116"/>
+      <c r="L50" s="116"/>
+      <c r="M50" s="117"/>
       <c r="O50" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>30</v>
@@ -5513,79 +5514,79 @@
     </row>
     <row r="52" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F52" s="108" t="s">
+        <v>338</v>
+      </c>
+      <c r="F52" s="106" t="s">
+        <v>333</v>
+      </c>
+      <c r="G52" s="113"/>
+      <c r="H52" s="113"/>
+      <c r="I52" s="113"/>
+      <c r="J52" s="113"/>
+      <c r="K52" s="113"/>
+      <c r="L52" s="113"/>
+      <c r="M52" s="114"/>
+      <c r="O52" t="s">
         <v>334</v>
-      </c>
-      <c r="G52" s="109"/>
-      <c r="H52" s="109"/>
-      <c r="I52" s="109"/>
-      <c r="J52" s="109"/>
-      <c r="K52" s="109"/>
-      <c r="L52" s="109"/>
-      <c r="M52" s="110"/>
-      <c r="O52" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="53" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>356</v>
-      </c>
-      <c r="F53" s="108" t="s">
+        <v>355</v>
+      </c>
+      <c r="F53" s="106" t="s">
+        <v>333</v>
+      </c>
+      <c r="G53" s="113"/>
+      <c r="H53" s="113"/>
+      <c r="I53" s="113"/>
+      <c r="J53" s="113"/>
+      <c r="K53" s="113"/>
+      <c r="L53" s="113"/>
+      <c r="M53" s="114"/>
+      <c r="O53" t="s">
         <v>334</v>
-      </c>
-      <c r="G53" s="109"/>
-      <c r="H53" s="109"/>
-      <c r="I53" s="109"/>
-      <c r="J53" s="109"/>
-      <c r="K53" s="109"/>
-      <c r="L53" s="109"/>
-      <c r="M53" s="110"/>
-      <c r="O53" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="54" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>357</v>
-      </c>
-      <c r="F54" s="108" t="s">
+        <v>356</v>
+      </c>
+      <c r="F54" s="106" t="s">
+        <v>333</v>
+      </c>
+      <c r="G54" s="113"/>
+      <c r="H54" s="113"/>
+      <c r="I54" s="113"/>
+      <c r="J54" s="113"/>
+      <c r="K54" s="113"/>
+      <c r="L54" s="113"/>
+      <c r="M54" s="114"/>
+      <c r="O54" t="s">
         <v>334</v>
-      </c>
-      <c r="G54" s="109"/>
-      <c r="H54" s="109"/>
-      <c r="I54" s="109"/>
-      <c r="J54" s="109"/>
-      <c r="K54" s="109"/>
-      <c r="L54" s="109"/>
-      <c r="M54" s="110"/>
-      <c r="O54" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="55" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>30</v>
@@ -5604,79 +5605,79 @@
     </row>
     <row r="56" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="F56" s="108" t="s">
+        <v>360</v>
+      </c>
+      <c r="F56" s="106" t="s">
+        <v>333</v>
+      </c>
+      <c r="G56" s="113"/>
+      <c r="H56" s="113"/>
+      <c r="I56" s="113"/>
+      <c r="J56" s="113"/>
+      <c r="K56" s="113"/>
+      <c r="L56" s="113"/>
+      <c r="M56" s="114"/>
+      <c r="O56" t="s">
         <v>334</v>
-      </c>
-      <c r="G56" s="109"/>
-      <c r="H56" s="109"/>
-      <c r="I56" s="109"/>
-      <c r="J56" s="109"/>
-      <c r="K56" s="109"/>
-      <c r="L56" s="109"/>
-      <c r="M56" s="110"/>
-      <c r="O56" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="57" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="F57" s="108" t="s">
+        <v>361</v>
+      </c>
+      <c r="F57" s="106" t="s">
+        <v>333</v>
+      </c>
+      <c r="G57" s="113"/>
+      <c r="H57" s="113"/>
+      <c r="I57" s="113"/>
+      <c r="J57" s="113"/>
+      <c r="K57" s="113"/>
+      <c r="L57" s="113"/>
+      <c r="M57" s="114"/>
+      <c r="O57" t="s">
         <v>334</v>
-      </c>
-      <c r="G57" s="109"/>
-      <c r="H57" s="109"/>
-      <c r="I57" s="109"/>
-      <c r="J57" s="109"/>
-      <c r="K57" s="109"/>
-      <c r="L57" s="109"/>
-      <c r="M57" s="110"/>
-      <c r="O57" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="58" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="F58" s="108" t="s">
+        <v>362</v>
+      </c>
+      <c r="F58" s="106" t="s">
+        <v>333</v>
+      </c>
+      <c r="G58" s="113"/>
+      <c r="H58" s="113"/>
+      <c r="I58" s="113"/>
+      <c r="J58" s="113"/>
+      <c r="K58" s="113"/>
+      <c r="L58" s="113"/>
+      <c r="M58" s="114"/>
+      <c r="O58" t="s">
         <v>334</v>
-      </c>
-      <c r="G58" s="109"/>
-      <c r="H58" s="109"/>
-      <c r="I58" s="109"/>
-      <c r="J58" s="109"/>
-      <c r="K58" s="109"/>
-      <c r="L58" s="109"/>
-      <c r="M58" s="110"/>
-      <c r="O58" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="59" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C59" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>30</v>
@@ -5714,29 +5715,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="F50:M50"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F48:M48"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="F45:M45"/>
-    <mergeCell ref="F46:M46"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="J31:M31"/>
     <mergeCell ref="J33:M33"/>
     <mergeCell ref="I34:M34"/>
     <mergeCell ref="J36:M36"/>
@@ -5753,6 +5731,29 @@
     <mergeCell ref="J22:M22"/>
     <mergeCell ref="F23:M23"/>
     <mergeCell ref="F24:M24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F48:M48"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F54:M54"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5827,16 +5828,16 @@
       <c r="E6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="86" t="s">
+      <c r="F6" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="87"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="88"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="93"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
@@ -5848,20 +5849,20 @@
       <c r="E7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="86" t="s">
+      <c r="F7" s="91" t="s">
         <v>181</v>
       </c>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="87"/>
-      <c r="L7" s="87"/>
-      <c r="M7" s="88"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="93"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -5919,12 +5920,12 @@
       <c r="I19" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="86" t="s">
+      <c r="J19" s="91" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="87"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="88"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="93"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="19" t="s">
@@ -5946,12 +5947,12 @@
       <c r="I20" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="86" t="s">
+      <c r="J20" s="91" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="87"/>
-      <c r="L20" s="87"/>
-      <c r="M20" s="88"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="92"/>
+      <c r="M20" s="93"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="19" t="s">
@@ -5961,18 +5962,18 @@
         <v>35</v>
       </c>
       <c r="E21" s="6"/>
-      <c r="F21" s="86" t="s">
+      <c r="F21" s="91" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="88"/>
-      <c r="H21" s="86" t="s">
+      <c r="G21" s="93"/>
+      <c r="H21" s="91" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="87"/>
-      <c r="J21" s="87"/>
-      <c r="K21" s="87"/>
-      <c r="L21" s="87"/>
-      <c r="M21" s="88"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="93"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="19" t="s">
@@ -5982,10 +5983,10 @@
         <v>35</v>
       </c>
       <c r="E22" s="6"/>
-      <c r="F22" s="86" t="s">
+      <c r="F22" s="91" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="88"/>
+      <c r="G22" s="93"/>
       <c r="H22" s="18"/>
       <c r="I22" s="11" t="s">
         <v>114</v>
@@ -5993,11 +5994,11 @@
       <c r="J22" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="K22" s="86" t="s">
+      <c r="K22" s="91" t="s">
         <v>112</v>
       </c>
-      <c r="L22" s="87"/>
-      <c r="M22" s="88"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="93"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="19" t="s">
@@ -6007,18 +6008,18 @@
         <v>35</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="86" t="s">
+      <c r="F23" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="G23" s="87"/>
-      <c r="H23" s="87"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="86" t="s">
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="K23" s="87"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="88"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="93"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="19" t="s">
@@ -6028,18 +6029,18 @@
         <v>35</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="86" t="s">
+      <c r="F24" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="86" t="s">
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="K24" s="87"/>
-      <c r="L24" s="87"/>
-      <c r="M24" s="88"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="92"/>
+      <c r="M24" s="93"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="19" t="s">
@@ -6049,18 +6050,18 @@
         <v>35</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="86" t="s">
+      <c r="F25" s="91" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="88"/>
-      <c r="J25" s="86" t="s">
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="91" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
-      <c r="M25" s="88"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="92"/>
+      <c r="M25" s="93"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="19" t="s">
@@ -6070,18 +6071,18 @@
         <v>35</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="86" t="s">
+      <c r="F26" s="91" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="86" t="s">
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="91" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="88"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="93"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="19" t="s">
@@ -6135,16 +6136,16 @@
       <c r="E29" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="86" t="s">
+      <c r="F29" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G29" s="87"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="88"/>
+      <c r="G29" s="92"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="92"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="92"/>
+      <c r="L29" s="92"/>
+      <c r="M29" s="93"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="19" t="s">
@@ -6154,16 +6155,16 @@
         <v>35</v>
       </c>
       <c r="E30" s="6"/>
-      <c r="F30" s="86" t="s">
+      <c r="F30" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G30" s="87"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="88"/>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="92"/>
+      <c r="L30" s="92"/>
+      <c r="M30" s="93"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="19" t="s">
@@ -6173,16 +6174,16 @@
         <v>35</v>
       </c>
       <c r="E31" s="6"/>
-      <c r="F31" s="86" t="s">
+      <c r="F31" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G31" s="87"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="88"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="92"/>
+      <c r="K31" s="92"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="93"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="19" t="s">
@@ -6192,16 +6193,16 @@
         <v>35</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="86" t="s">
+      <c r="F32" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G32" s="87"/>
-      <c r="H32" s="87"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="K32" s="87"/>
-      <c r="L32" s="87"/>
-      <c r="M32" s="88"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="93"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="19" t="s">
@@ -6211,16 +6212,16 @@
         <v>35</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="86" t="s">
+      <c r="F33" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="88"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="93"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="19" t="s">
@@ -6230,16 +6231,16 @@
         <v>35</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="86" t="s">
+      <c r="F34" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="87"/>
-      <c r="I34" s="87"/>
-      <c r="J34" s="87"/>
-      <c r="K34" s="87"/>
-      <c r="L34" s="87"/>
-      <c r="M34" s="88"/>
+      <c r="G34" s="92"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="92"/>
+      <c r="M34" s="93"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="19" t="s">
@@ -6249,16 +6250,16 @@
         <v>35</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="86" t="s">
+      <c r="F35" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G35" s="87"/>
-      <c r="H35" s="87"/>
-      <c r="I35" s="87"/>
-      <c r="J35" s="87"/>
-      <c r="K35" s="87"/>
-      <c r="L35" s="87"/>
-      <c r="M35" s="88"/>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="93"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="19" t="s">
@@ -6268,16 +6269,16 @@
         <v>35</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="86" t="s">
+      <c r="F36" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G36" s="87"/>
-      <c r="H36" s="87"/>
-      <c r="I36" s="87"/>
-      <c r="J36" s="87"/>
-      <c r="K36" s="87"/>
-      <c r="L36" s="87"/>
-      <c r="M36" s="88"/>
+      <c r="G36" s="92"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="92"/>
+      <c r="J36" s="92"/>
+      <c r="K36" s="92"/>
+      <c r="L36" s="92"/>
+      <c r="M36" s="93"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="19" t="s">
@@ -6287,16 +6288,16 @@
         <v>35</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="86" t="s">
+      <c r="F37" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G37" s="87"/>
-      <c r="H37" s="87"/>
-      <c r="I37" s="87"/>
-      <c r="J37" s="87"/>
-      <c r="K37" s="87"/>
-      <c r="L37" s="87"/>
-      <c r="M37" s="88"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="92"/>
+      <c r="K37" s="92"/>
+      <c r="L37" s="92"/>
+      <c r="M37" s="93"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="19" t="s">
@@ -6306,16 +6307,16 @@
         <v>35</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="86" t="s">
+      <c r="F38" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G38" s="87"/>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="88"/>
+      <c r="G38" s="92"/>
+      <c r="H38" s="92"/>
+      <c r="I38" s="92"/>
+      <c r="J38" s="92"/>
+      <c r="K38" s="92"/>
+      <c r="L38" s="92"/>
+      <c r="M38" s="93"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="19" t="s">
@@ -6350,11 +6351,11 @@
       <c r="I40" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J40" s="86" t="s">
+      <c r="J40" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="K40" s="87"/>
-      <c r="L40" s="88"/>
+      <c r="K40" s="92"/>
+      <c r="L40" s="93"/>
       <c r="M40" s="13" t="s">
         <v>145</v>
       </c>
@@ -6375,11 +6376,11 @@
       <c r="I41" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J41" s="86" t="s">
+      <c r="J41" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="K41" s="87"/>
-      <c r="L41" s="88"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="93"/>
       <c r="M41" s="13" t="s">
         <v>145</v>
       </c>
@@ -6400,11 +6401,11 @@
       <c r="I42" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J42" s="86" t="s">
+      <c r="J42" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="K42" s="87"/>
-      <c r="L42" s="88"/>
+      <c r="K42" s="92"/>
+      <c r="L42" s="93"/>
       <c r="M42" s="13" t="s">
         <v>145</v>
       </c>
@@ -6425,11 +6426,11 @@
       <c r="I43" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J43" s="86" t="s">
+      <c r="J43" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="K43" s="87"/>
-      <c r="L43" s="88"/>
+      <c r="K43" s="92"/>
+      <c r="L43" s="93"/>
       <c r="M43" s="13" t="s">
         <v>145</v>
       </c>
@@ -6450,11 +6451,11 @@
       <c r="I44" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J44" s="86" t="s">
+      <c r="J44" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="K44" s="87"/>
-      <c r="L44" s="88"/>
+      <c r="K44" s="92"/>
+      <c r="L44" s="93"/>
       <c r="M44" s="13" t="s">
         <v>145</v>
       </c>
@@ -6475,11 +6476,11 @@
       <c r="I45" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J45" s="86" t="s">
+      <c r="J45" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="K45" s="87"/>
-      <c r="L45" s="88"/>
+      <c r="K45" s="92"/>
+      <c r="L45" s="93"/>
       <c r="M45" s="13" t="s">
         <v>145</v>
       </c>
@@ -6500,11 +6501,11 @@
       <c r="I46" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J46" s="86" t="s">
+      <c r="J46" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="K46" s="87"/>
-      <c r="L46" s="88"/>
+      <c r="K46" s="92"/>
+      <c r="L46" s="93"/>
       <c r="M46" s="13" t="s">
         <v>145</v>
       </c>
@@ -6525,11 +6526,11 @@
       <c r="I47" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J47" s="86" t="s">
+      <c r="J47" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="K47" s="87"/>
-      <c r="L47" s="88"/>
+      <c r="K47" s="92"/>
+      <c r="L47" s="93"/>
       <c r="M47" s="13" t="s">
         <v>145</v>
       </c>
@@ -6550,11 +6551,11 @@
       <c r="I48" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="J48" s="86" t="s">
+      <c r="J48" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="K48" s="87"/>
-      <c r="L48" s="88"/>
+      <c r="K48" s="92"/>
+      <c r="L48" s="93"/>
       <c r="M48" s="13" t="s">
         <v>145</v>
       </c>
@@ -6584,18 +6585,18 @@
         <v>35</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="86" t="s">
+      <c r="F50" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="G50" s="87"/>
-      <c r="H50" s="87"/>
-      <c r="I50" s="88"/>
-      <c r="J50" s="86" t="s">
+      <c r="G50" s="92"/>
+      <c r="H50" s="92"/>
+      <c r="I50" s="93"/>
+      <c r="J50" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="K50" s="87"/>
-      <c r="L50" s="87"/>
-      <c r="M50" s="88"/>
+      <c r="K50" s="92"/>
+      <c r="L50" s="92"/>
+      <c r="M50" s="93"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="20" t="s">
@@ -6605,18 +6606,18 @@
         <v>35</v>
       </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="86" t="s">
+      <c r="F51" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="G51" s="87"/>
-      <c r="H51" s="87"/>
-      <c r="I51" s="88"/>
-      <c r="J51" s="86" t="s">
+      <c r="G51" s="92"/>
+      <c r="H51" s="92"/>
+      <c r="I51" s="93"/>
+      <c r="J51" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="K51" s="87"/>
-      <c r="L51" s="87"/>
-      <c r="M51" s="88"/>
+      <c r="K51" s="92"/>
+      <c r="L51" s="92"/>
+      <c r="M51" s="93"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
@@ -6626,18 +6627,18 @@
         <v>35</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="86" t="s">
+      <c r="F52" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="G52" s="87"/>
-      <c r="H52" s="87"/>
-      <c r="I52" s="88"/>
-      <c r="J52" s="86" t="s">
+      <c r="G52" s="92"/>
+      <c r="H52" s="92"/>
+      <c r="I52" s="93"/>
+      <c r="J52" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="K52" s="87"/>
-      <c r="L52" s="87"/>
-      <c r="M52" s="88"/>
+      <c r="K52" s="92"/>
+      <c r="L52" s="92"/>
+      <c r="M52" s="93"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
@@ -6647,18 +6648,18 @@
         <v>35</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="86" t="s">
+      <c r="F53" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="G53" s="87"/>
-      <c r="H53" s="87"/>
-      <c r="I53" s="88"/>
-      <c r="J53" s="86" t="s">
+      <c r="G53" s="92"/>
+      <c r="H53" s="92"/>
+      <c r="I53" s="93"/>
+      <c r="J53" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="K53" s="87"/>
-      <c r="L53" s="87"/>
-      <c r="M53" s="88"/>
+      <c r="K53" s="92"/>
+      <c r="L53" s="92"/>
+      <c r="M53" s="93"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
@@ -6668,18 +6669,18 @@
         <v>35</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="86" t="s">
+      <c r="F54" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="G54" s="87"/>
-      <c r="H54" s="87"/>
-      <c r="I54" s="88"/>
-      <c r="J54" s="86" t="s">
+      <c r="G54" s="92"/>
+      <c r="H54" s="92"/>
+      <c r="I54" s="93"/>
+      <c r="J54" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="K54" s="87"/>
-      <c r="L54" s="87"/>
-      <c r="M54" s="88"/>
+      <c r="K54" s="92"/>
+      <c r="L54" s="92"/>
+      <c r="M54" s="93"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
@@ -6689,18 +6690,18 @@
         <v>35</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="86" t="s">
+      <c r="F55" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="G55" s="87"/>
-      <c r="H55" s="87"/>
-      <c r="I55" s="88"/>
-      <c r="J55" s="86" t="s">
+      <c r="G55" s="92"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="93"/>
+      <c r="J55" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="K55" s="87"/>
-      <c r="L55" s="87"/>
-      <c r="M55" s="88"/>
+      <c r="K55" s="92"/>
+      <c r="L55" s="92"/>
+      <c r="M55" s="93"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
@@ -6710,18 +6711,18 @@
         <v>35</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="86" t="s">
+      <c r="F56" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="G56" s="87"/>
-      <c r="H56" s="87"/>
-      <c r="I56" s="88"/>
-      <c r="J56" s="86" t="s">
+      <c r="G56" s="92"/>
+      <c r="H56" s="92"/>
+      <c r="I56" s="93"/>
+      <c r="J56" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="K56" s="87"/>
-      <c r="L56" s="87"/>
-      <c r="M56" s="88"/>
+      <c r="K56" s="92"/>
+      <c r="L56" s="92"/>
+      <c r="M56" s="93"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="19" t="s">
@@ -6731,18 +6732,18 @@
         <v>35</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="86" t="s">
+      <c r="F57" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="G57" s="87"/>
-      <c r="H57" s="87"/>
-      <c r="I57" s="88"/>
-      <c r="J57" s="86" t="s">
+      <c r="G57" s="92"/>
+      <c r="H57" s="92"/>
+      <c r="I57" s="93"/>
+      <c r="J57" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="K57" s="87"/>
-      <c r="L57" s="87"/>
-      <c r="M57" s="88"/>
+      <c r="K57" s="92"/>
+      <c r="L57" s="92"/>
+      <c r="M57" s="93"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
@@ -6752,18 +6753,18 @@
         <v>35</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="86" t="s">
+      <c r="F58" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="G58" s="87"/>
-      <c r="H58" s="87"/>
-      <c r="I58" s="88"/>
-      <c r="J58" s="86" t="s">
+      <c r="G58" s="92"/>
+      <c r="H58" s="92"/>
+      <c r="I58" s="93"/>
+      <c r="J58" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="K58" s="87"/>
-      <c r="L58" s="87"/>
-      <c r="M58" s="88"/>
+      <c r="K58" s="92"/>
+      <c r="L58" s="92"/>
+      <c r="M58" s="93"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="19" t="s">
@@ -6798,10 +6799,10 @@
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
       <c r="K60" s="10"/>
-      <c r="L60" s="108" t="s">
+      <c r="L60" s="106" t="s">
         <v>177</v>
       </c>
-      <c r="M60" s="85"/>
+      <c r="M60" s="78"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="19" t="s">
@@ -6819,10 +6820,10 @@
       <c r="I61" s="9"/>
       <c r="J61" s="9"/>
       <c r="K61" s="10"/>
-      <c r="L61" s="84" t="s">
+      <c r="L61" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="M61" s="85"/>
+      <c r="M61" s="78"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="19" t="s">
@@ -6840,10 +6841,10 @@
       <c r="I62" s="9"/>
       <c r="J62" s="9"/>
       <c r="K62" s="10"/>
-      <c r="L62" s="84" t="s">
+      <c r="L62" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="M62" s="85"/>
+      <c r="M62" s="78"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="19" t="s">
@@ -6861,10 +6862,10 @@
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
       <c r="K63" s="10"/>
-      <c r="L63" s="84" t="s">
+      <c r="L63" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="M63" s="85"/>
+      <c r="M63" s="78"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="19" t="s">
@@ -6882,10 +6883,10 @@
       <c r="I64" s="9"/>
       <c r="J64" s="9"/>
       <c r="K64" s="10"/>
-      <c r="L64" s="84" t="s">
+      <c r="L64" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="M64" s="85"/>
+      <c r="M64" s="78"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="19" t="s">
@@ -6903,10 +6904,10 @@
       <c r="I65" s="9"/>
       <c r="J65" s="9"/>
       <c r="K65" s="10"/>
-      <c r="L65" s="84" t="s">
+      <c r="L65" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="M65" s="85"/>
+      <c r="M65" s="78"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="19" t="s">
@@ -6924,10 +6925,10 @@
       <c r="I66" s="9"/>
       <c r="J66" s="9"/>
       <c r="K66" s="10"/>
-      <c r="L66" s="84" t="s">
+      <c r="L66" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="M66" s="85"/>
+      <c r="M66" s="78"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="19" t="s">
@@ -6945,10 +6946,10 @@
       <c r="I67" s="9"/>
       <c r="J67" s="9"/>
       <c r="K67" s="10"/>
-      <c r="L67" s="84" t="s">
+      <c r="L67" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="M67" s="85"/>
+      <c r="M67" s="78"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="19" t="s">
@@ -6966,14 +6967,14 @@
       <c r="I68" s="9"/>
       <c r="J68" s="9"/>
       <c r="K68" s="10"/>
-      <c r="L68" s="84" t="s">
+      <c r="L68" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="M68" s="85"/>
+      <c r="M68" s="78"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>85</v>
@@ -6990,223 +6991,223 @@
     </row>
     <row r="70" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E70" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F70" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="F70" s="108" t="s">
+      <c r="G70" s="113"/>
+      <c r="H70" s="113"/>
+      <c r="I70" s="113"/>
+      <c r="J70" s="113"/>
+      <c r="K70" s="113"/>
+      <c r="L70" s="113"/>
+      <c r="M70" s="114"/>
+      <c r="O70" t="s">
         <v>334</v>
-      </c>
-      <c r="G70" s="109"/>
-      <c r="H70" s="109"/>
-      <c r="I70" s="109"/>
-      <c r="J70" s="109"/>
-      <c r="K70" s="109"/>
-      <c r="L70" s="109"/>
-      <c r="M70" s="110"/>
-      <c r="O70" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="71" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E71" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F71" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="F71" s="108" t="s">
+      <c r="G71" s="113"/>
+      <c r="H71" s="113"/>
+      <c r="I71" s="113"/>
+      <c r="J71" s="113"/>
+      <c r="K71" s="113"/>
+      <c r="L71" s="113"/>
+      <c r="M71" s="114"/>
+      <c r="O71" t="s">
         <v>334</v>
-      </c>
-      <c r="G71" s="109"/>
-      <c r="H71" s="109"/>
-      <c r="I71" s="109"/>
-      <c r="J71" s="109"/>
-      <c r="K71" s="109"/>
-      <c r="L71" s="109"/>
-      <c r="M71" s="110"/>
-      <c r="O71" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="72" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C72" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E72" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F72" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="F72" s="108" t="s">
+      <c r="G72" s="113"/>
+      <c r="H72" s="113"/>
+      <c r="I72" s="113"/>
+      <c r="J72" s="113"/>
+      <c r="K72" s="113"/>
+      <c r="L72" s="113"/>
+      <c r="M72" s="114"/>
+      <c r="O72" t="s">
         <v>334</v>
-      </c>
-      <c r="G72" s="109"/>
-      <c r="H72" s="109"/>
-      <c r="I72" s="109"/>
-      <c r="J72" s="109"/>
-      <c r="K72" s="109"/>
-      <c r="L72" s="109"/>
-      <c r="M72" s="110"/>
-      <c r="O72" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="73" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C73" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E73" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F73" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="F73" s="108" t="s">
+      <c r="G73" s="113"/>
+      <c r="H73" s="113"/>
+      <c r="I73" s="113"/>
+      <c r="J73" s="113"/>
+      <c r="K73" s="113"/>
+      <c r="L73" s="113"/>
+      <c r="M73" s="114"/>
+      <c r="O73" t="s">
         <v>334</v>
-      </c>
-      <c r="G73" s="109"/>
-      <c r="H73" s="109"/>
-      <c r="I73" s="109"/>
-      <c r="J73" s="109"/>
-      <c r="K73" s="109"/>
-      <c r="L73" s="109"/>
-      <c r="M73" s="110"/>
-      <c r="O73" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="74" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C74" s="19" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E74" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F74" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="F74" s="108" t="s">
+      <c r="G74" s="113"/>
+      <c r="H74" s="113"/>
+      <c r="I74" s="113"/>
+      <c r="J74" s="113"/>
+      <c r="K74" s="113"/>
+      <c r="L74" s="113"/>
+      <c r="M74" s="114"/>
+      <c r="O74" t="s">
         <v>334</v>
-      </c>
-      <c r="G74" s="109"/>
-      <c r="H74" s="109"/>
-      <c r="I74" s="109"/>
-      <c r="J74" s="109"/>
-      <c r="K74" s="109"/>
-      <c r="L74" s="109"/>
-      <c r="M74" s="110"/>
-      <c r="O74" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="75" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C75" s="19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E75" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F75" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="F75" s="108" t="s">
+      <c r="G75" s="113"/>
+      <c r="H75" s="113"/>
+      <c r="I75" s="113"/>
+      <c r="J75" s="113"/>
+      <c r="K75" s="113"/>
+      <c r="L75" s="113"/>
+      <c r="M75" s="114"/>
+      <c r="O75" t="s">
         <v>334</v>
-      </c>
-      <c r="G75" s="109"/>
-      <c r="H75" s="109"/>
-      <c r="I75" s="109"/>
-      <c r="J75" s="109"/>
-      <c r="K75" s="109"/>
-      <c r="L75" s="109"/>
-      <c r="M75" s="110"/>
-      <c r="O75" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="76" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C76" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E76" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F76" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="108" t="s">
+      <c r="G76" s="113"/>
+      <c r="H76" s="113"/>
+      <c r="I76" s="113"/>
+      <c r="J76" s="113"/>
+      <c r="K76" s="113"/>
+      <c r="L76" s="113"/>
+      <c r="M76" s="114"/>
+      <c r="O76" t="s">
         <v>334</v>
-      </c>
-      <c r="G76" s="109"/>
-      <c r="H76" s="109"/>
-      <c r="I76" s="109"/>
-      <c r="J76" s="109"/>
-      <c r="K76" s="109"/>
-      <c r="L76" s="109"/>
-      <c r="M76" s="110"/>
-      <c r="O76" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="77" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C77" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E77" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F77" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="F77" s="108" t="s">
+      <c r="G77" s="113"/>
+      <c r="H77" s="113"/>
+      <c r="I77" s="113"/>
+      <c r="J77" s="113"/>
+      <c r="K77" s="113"/>
+      <c r="L77" s="113"/>
+      <c r="M77" s="114"/>
+      <c r="O77" t="s">
         <v>334</v>
-      </c>
-      <c r="G77" s="109"/>
-      <c r="H77" s="109"/>
-      <c r="I77" s="109"/>
-      <c r="J77" s="109"/>
-      <c r="K77" s="109"/>
-      <c r="L77" s="109"/>
-      <c r="M77" s="110"/>
-      <c r="O77" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="78" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C78" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E78" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F78" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="F78" s="108" t="s">
+      <c r="G78" s="113"/>
+      <c r="H78" s="113"/>
+      <c r="I78" s="113"/>
+      <c r="J78" s="113"/>
+      <c r="K78" s="113"/>
+      <c r="L78" s="113"/>
+      <c r="M78" s="114"/>
+      <c r="O78" t="s">
         <v>334</v>
-      </c>
-      <c r="G78" s="109"/>
-      <c r="H78" s="109"/>
-      <c r="I78" s="109"/>
-      <c r="J78" s="109"/>
-      <c r="K78" s="109"/>
-      <c r="L78" s="109"/>
-      <c r="M78" s="110"/>
-      <c r="O78" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="79" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C79" s="19" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>85</v>
@@ -7223,11 +7224,56 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="F70:M70"/>
-    <mergeCell ref="F71:M71"/>
-    <mergeCell ref="F72:M72"/>
-    <mergeCell ref="F73:M73"/>
-    <mergeCell ref="F74:M74"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="J54:M54"/>
     <mergeCell ref="F75:M75"/>
     <mergeCell ref="F76:M76"/>
     <mergeCell ref="F77:M77"/>
@@ -7244,56 +7290,11 @@
     <mergeCell ref="F52:I52"/>
     <mergeCell ref="J52:M52"/>
     <mergeCell ref="F53:I53"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F70:M70"/>
+    <mergeCell ref="F71:M71"/>
+    <mergeCell ref="F72:M72"/>
+    <mergeCell ref="F73:M73"/>
+    <mergeCell ref="F74:M74"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7340,7 +7341,7 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.15">
@@ -7349,7 +7350,7 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.15">
@@ -7402,14 +7403,14 @@
       <c r="E11" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="78"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="80"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="95"/>
+      <c r="J11" s="95"/>
+      <c r="K11" s="95"/>
+      <c r="L11" s="95"/>
+      <c r="M11" s="96"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="19" t="s">
@@ -7421,16 +7422,16 @@
       <c r="E12" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="81" t="s">
+      <c r="F12" s="85" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="83"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="87"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="19" t="s">
@@ -7442,16 +7443,16 @@
       <c r="E13" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="F13" s="81" t="s">
+      <c r="F13" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="83"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="87"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="19" t="s">
@@ -7463,16 +7464,16 @@
       <c r="E14" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="F14" s="81" t="s">
+      <c r="F14" s="85" t="s">
         <v>208</v>
       </c>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="83"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
+      <c r="M14" s="87"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="19" t="s">
@@ -7482,7 +7483,7 @@
         <v>35</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F15" s="45" t="s">
         <v>209</v>
@@ -7494,10 +7495,10 @@
         <v>211</v>
       </c>
       <c r="I15" s="55" t="s">
+        <v>301</v>
+      </c>
+      <c r="J15" s="55" t="s">
         <v>302</v>
-      </c>
-      <c r="J15" s="55" t="s">
-        <v>303</v>
       </c>
       <c r="K15" s="44"/>
       <c r="L15" s="45" t="s">
@@ -7517,18 +7518,18 @@
       <c r="E16" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F16" s="89" t="s">
+      <c r="F16" s="97" t="s">
         <v>214</v>
       </c>
-      <c r="G16" s="90"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="90"/>
-      <c r="J16" s="90"/>
-      <c r="K16" s="90"/>
-      <c r="L16" s="90"/>
-      <c r="M16" s="91"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="98"/>
+      <c r="M16" s="99"/>
       <c r="N16" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7541,18 +7542,18 @@
       <c r="E17" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F17" s="89" t="s">
+      <c r="F17" s="97" t="s">
         <v>215</v>
       </c>
-      <c r="G17" s="90"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="90"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="90"/>
-      <c r="M17" s="91"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="98"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="99"/>
       <c r="N17" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7578,13 +7579,13 @@
       <c r="J18" s="56" t="s">
         <v>220</v>
       </c>
-      <c r="K18" s="78"/>
-      <c r="L18" s="80"/>
+      <c r="K18" s="94"/>
+      <c r="L18" s="96"/>
       <c r="M18" s="55" t="s">
         <v>221</v>
       </c>
       <c r="N18" s="58" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7601,8 +7602,8 @@
       <c r="G19" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="H19" s="78"/>
-      <c r="I19" s="80"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="96"/>
       <c r="J19" s="56" t="s">
         <v>224</v>
       </c>
@@ -7624,18 +7625,18 @@
         <v>35</v>
       </c>
       <c r="E20" s="43"/>
-      <c r="F20" s="92" t="s">
+      <c r="F20" s="100" t="s">
         <v>228</v>
       </c>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="93"/>
-      <c r="J20" s="93"/>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="94"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="101"/>
+      <c r="J20" s="101"/>
+      <c r="K20" s="101"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="102"/>
       <c r="N20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7646,18 +7647,18 @@
         <v>35</v>
       </c>
       <c r="E21" s="42"/>
-      <c r="F21" s="92" t="s">
+      <c r="F21" s="100" t="s">
         <v>229</v>
       </c>
-      <c r="G21" s="93"/>
-      <c r="H21" s="93"/>
-      <c r="I21" s="93"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="94"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="102"/>
       <c r="N21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7668,18 +7669,18 @@
         <v>35</v>
       </c>
       <c r="E22" s="42"/>
-      <c r="F22" s="92" t="s">
+      <c r="F22" s="100" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="93"/>
-      <c r="H22" s="93"/>
-      <c r="I22" s="93"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="93"/>
-      <c r="L22" s="93"/>
-      <c r="M22" s="94"/>
+      <c r="G22" s="101"/>
+      <c r="H22" s="101"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="101"/>
+      <c r="K22" s="101"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="102"/>
       <c r="N22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7690,18 +7691,18 @@
         <v>35</v>
       </c>
       <c r="E23" s="42"/>
-      <c r="F23" s="92" t="s">
+      <c r="F23" s="100" t="s">
         <v>231</v>
       </c>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="93"/>
-      <c r="L23" s="93"/>
-      <c r="M23" s="94"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="101"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="102"/>
       <c r="N23" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7714,18 +7715,18 @@
       <c r="E24" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F24" s="89" t="s">
+      <c r="F24" s="97" t="s">
         <v>232</v>
       </c>
-      <c r="G24" s="90"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="90"/>
-      <c r="K24" s="90"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="91"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="98"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="99"/>
       <c r="N24" s="59" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7738,18 +7739,18 @@
       <c r="E25" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F25" s="78"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="80"/>
-      <c r="K25" s="89" t="s">
+      <c r="F25" s="94"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="97" t="s">
         <v>233</v>
       </c>
-      <c r="L25" s="90"/>
-      <c r="M25" s="91"/>
+      <c r="L25" s="98"/>
+      <c r="M25" s="99"/>
       <c r="N25" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7760,18 +7761,18 @@
         <v>30</v>
       </c>
       <c r="E26" s="42"/>
-      <c r="F26" s="92" t="s">
+      <c r="F26" s="100" t="s">
         <v>234</v>
       </c>
-      <c r="G26" s="93"/>
-      <c r="H26" s="93"/>
-      <c r="I26" s="93"/>
-      <c r="J26" s="93"/>
-      <c r="K26" s="95"/>
-      <c r="L26" s="95"/>
-      <c r="M26" s="96"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="101"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="103"/>
+      <c r="L26" s="103"/>
+      <c r="M26" s="104"/>
       <c r="N26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7782,18 +7783,18 @@
         <v>35</v>
       </c>
       <c r="E27" s="42"/>
-      <c r="F27" s="92" t="s">
+      <c r="F27" s="100" t="s">
         <v>235</v>
       </c>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="94"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="102"/>
       <c r="N27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7804,18 +7805,18 @@
         <v>35</v>
       </c>
       <c r="E28" s="42"/>
-      <c r="F28" s="92" t="s">
+      <c r="F28" s="100" t="s">
         <v>236</v>
       </c>
-      <c r="G28" s="93"/>
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="94"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="101"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="101"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="102"/>
       <c r="N28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7826,18 +7827,18 @@
         <v>35</v>
       </c>
       <c r="E29" s="42"/>
-      <c r="F29" s="92" t="s">
+      <c r="F29" s="100" t="s">
         <v>237</v>
       </c>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="94"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="101"/>
+      <c r="I29" s="101"/>
+      <c r="J29" s="101"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="102"/>
       <c r="N29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7850,14 +7851,14 @@
       <c r="E30" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F30" s="78"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="80"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="96"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="60" t="s">
@@ -7869,14 +7870,14 @@
       <c r="E31" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F31" s="78"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="79"/>
-      <c r="L31" s="79"/>
-      <c r="M31" s="80"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="96"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="60" t="s">
@@ -7888,18 +7889,18 @@
       <c r="E32" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F32" s="89" t="s">
+      <c r="F32" s="97" t="s">
         <v>238</v>
       </c>
-      <c r="G32" s="90"/>
-      <c r="H32" s="90"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="90"/>
-      <c r="K32" s="90"/>
-      <c r="L32" s="90"/>
-      <c r="M32" s="91"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="99"/>
       <c r="N32" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7912,18 +7913,18 @@
       <c r="E33" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F33" s="89" t="s">
+      <c r="F33" s="97" t="s">
         <v>239</v>
       </c>
-      <c r="G33" s="91"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="80"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="95"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="96"/>
       <c r="N33" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7936,18 +7937,18 @@
       <c r="E34" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F34" s="78"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="80"/>
-      <c r="K34" s="89" t="s">
+      <c r="F34" s="94"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="96"/>
+      <c r="K34" s="97" t="s">
         <v>240</v>
       </c>
-      <c r="L34" s="90"/>
-      <c r="M34" s="91"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="99"/>
       <c r="N34" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7960,18 +7961,18 @@
       <c r="E35" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F35" s="78"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
-      <c r="I35" s="80"/>
-      <c r="J35" s="89" t="s">
+      <c r="F35" s="94"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
+      <c r="I35" s="96"/>
+      <c r="J35" s="97" t="s">
         <v>241</v>
       </c>
-      <c r="K35" s="90"/>
-      <c r="L35" s="90"/>
-      <c r="M35" s="91"/>
+      <c r="K35" s="98"/>
+      <c r="L35" s="98"/>
+      <c r="M35" s="99"/>
       <c r="N35" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -7984,18 +7985,18 @@
       <c r="E36" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F36" s="78"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
-      <c r="I36" s="80"/>
-      <c r="J36" s="89" t="s">
+      <c r="F36" s="94"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="97" t="s">
         <v>242</v>
       </c>
-      <c r="K36" s="90"/>
-      <c r="L36" s="90"/>
-      <c r="M36" s="91"/>
+      <c r="K36" s="98"/>
+      <c r="L36" s="98"/>
+      <c r="M36" s="99"/>
       <c r="N36" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8008,18 +8009,18 @@
       <c r="E37" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F37" s="89" t="s">
+      <c r="F37" s="97" t="s">
         <v>243</v>
       </c>
-      <c r="G37" s="90"/>
-      <c r="H37" s="90"/>
-      <c r="I37" s="90"/>
-      <c r="J37" s="90"/>
-      <c r="K37" s="90"/>
-      <c r="L37" s="90"/>
-      <c r="M37" s="91"/>
+      <c r="G37" s="98"/>
+      <c r="H37" s="98"/>
+      <c r="I37" s="98"/>
+      <c r="J37" s="98"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="98"/>
+      <c r="M37" s="99"/>
       <c r="N37" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8032,14 +8033,14 @@
       <c r="E38" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F38" s="78"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
-      <c r="J38" s="79"/>
-      <c r="K38" s="79"/>
-      <c r="L38" s="79"/>
-      <c r="M38" s="80"/>
+      <c r="F38" s="94"/>
+      <c r="G38" s="95"/>
+      <c r="H38" s="95"/>
+      <c r="I38" s="95"/>
+      <c r="J38" s="95"/>
+      <c r="K38" s="95"/>
+      <c r="L38" s="95"/>
+      <c r="M38" s="96"/>
     </row>
     <row r="39" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="60" t="s">
@@ -8051,14 +8052,14 @@
       <c r="E39" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F39" s="78"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
-      <c r="I39" s="79"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="79"/>
-      <c r="L39" s="79"/>
-      <c r="M39" s="80"/>
+      <c r="F39" s="94"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="95"/>
+      <c r="J39" s="95"/>
+      <c r="K39" s="95"/>
+      <c r="L39" s="95"/>
+      <c r="M39" s="96"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="60" t="s">
@@ -8070,14 +8071,14 @@
       <c r="E40" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F40" s="78"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="79"/>
-      <c r="L40" s="79"/>
-      <c r="M40" s="80"/>
+      <c r="F40" s="94"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="95"/>
+      <c r="J40" s="95"/>
+      <c r="K40" s="95"/>
+      <c r="L40" s="95"/>
+      <c r="M40" s="96"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="60" t="s">
@@ -8089,14 +8090,14 @@
       <c r="E41" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F41" s="78"/>
-      <c r="G41" s="79"/>
-      <c r="H41" s="79"/>
-      <c r="I41" s="79"/>
-      <c r="J41" s="79"/>
-      <c r="K41" s="79"/>
-      <c r="L41" s="79"/>
-      <c r="M41" s="80"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="95"/>
+      <c r="H41" s="95"/>
+      <c r="I41" s="95"/>
+      <c r="J41" s="95"/>
+      <c r="K41" s="95"/>
+      <c r="L41" s="95"/>
+      <c r="M41" s="96"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="60" t="s">
@@ -8108,14 +8109,14 @@
       <c r="E42" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="F42" s="78"/>
-      <c r="G42" s="79"/>
-      <c r="H42" s="79"/>
-      <c r="I42" s="79"/>
-      <c r="J42" s="79"/>
-      <c r="K42" s="79"/>
-      <c r="L42" s="79"/>
-      <c r="M42" s="80"/>
+      <c r="F42" s="94"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="95"/>
+      <c r="I42" s="95"/>
+      <c r="J42" s="95"/>
+      <c r="K42" s="95"/>
+      <c r="L42" s="95"/>
+      <c r="M42" s="96"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="20" t="s">
@@ -8137,12 +8138,12 @@
       <c r="I43" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="81" t="s">
+      <c r="J43" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="82"/>
-      <c r="L43" s="82"/>
-      <c r="M43" s="83"/>
+      <c r="K43" s="86"/>
+      <c r="L43" s="86"/>
+      <c r="M43" s="87"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="19" t="s">
@@ -8152,18 +8153,18 @@
         <v>35</v>
       </c>
       <c r="E44" s="43"/>
-      <c r="F44" s="81" t="s">
+      <c r="F44" s="85" t="s">
         <v>252</v>
       </c>
-      <c r="G44" s="83"/>
-      <c r="H44" s="81" t="s">
+      <c r="G44" s="87"/>
+      <c r="H44" s="85" t="s">
         <v>111</v>
       </c>
-      <c r="I44" s="82"/>
-      <c r="J44" s="82"/>
-      <c r="K44" s="82"/>
-      <c r="L44" s="82"/>
-      <c r="M44" s="83"/>
+      <c r="I44" s="86"/>
+      <c r="J44" s="86"/>
+      <c r="K44" s="86"/>
+      <c r="L44" s="86"/>
+      <c r="M44" s="87"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="19" t="s">
@@ -8173,18 +8174,18 @@
         <v>35</v>
       </c>
       <c r="E45" s="43"/>
-      <c r="F45" s="98" t="s">
+      <c r="F45" s="82" t="s">
         <v>115</v>
       </c>
-      <c r="G45" s="99"/>
-      <c r="H45" s="99"/>
-      <c r="I45" s="100"/>
-      <c r="J45" s="81" t="s">
+      <c r="G45" s="83"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="84"/>
+      <c r="J45" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="K45" s="82"/>
-      <c r="L45" s="82"/>
-      <c r="M45" s="83"/>
+      <c r="K45" s="86"/>
+      <c r="L45" s="86"/>
+      <c r="M45" s="87"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="19" t="s">
@@ -8194,18 +8195,18 @@
         <v>35</v>
       </c>
       <c r="E46" s="6"/>
-      <c r="F46" s="81" t="s">
+      <c r="F46" s="85" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="82"/>
-      <c r="H46" s="82"/>
-      <c r="I46" s="83"/>
-      <c r="J46" s="101" t="s">
+      <c r="G46" s="86"/>
+      <c r="H46" s="86"/>
+      <c r="I46" s="87"/>
+      <c r="J46" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="K46" s="102"/>
-      <c r="L46" s="102"/>
-      <c r="M46" s="103"/>
+      <c r="K46" s="89"/>
+      <c r="L46" s="89"/>
+      <c r="M46" s="90"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="19" t="s">
@@ -8215,16 +8216,16 @@
         <v>35</v>
       </c>
       <c r="E47" s="6"/>
-      <c r="F47" s="86" t="s">
+      <c r="F47" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="G47" s="87"/>
-      <c r="H47" s="87"/>
-      <c r="I47" s="87"/>
-      <c r="J47" s="87"/>
-      <c r="K47" s="87"/>
-      <c r="L47" s="87"/>
-      <c r="M47" s="88"/>
+      <c r="G47" s="92"/>
+      <c r="H47" s="92"/>
+      <c r="I47" s="92"/>
+      <c r="J47" s="92"/>
+      <c r="K47" s="92"/>
+      <c r="L47" s="92"/>
+      <c r="M47" s="93"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="19" t="s">
@@ -8234,20 +8235,20 @@
         <v>35</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="77"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="81"/>
       <c r="H48" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="I48" s="86" t="s">
+      <c r="I48" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="J48" s="87"/>
-      <c r="K48" s="88"/>
-      <c r="L48" s="86" t="s">
+      <c r="J48" s="92"/>
+      <c r="K48" s="93"/>
+      <c r="L48" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="M48" s="88"/>
+      <c r="M48" s="93"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="19" t="s">
@@ -8290,15 +8291,15 @@
         <v>35</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="97"/>
-      <c r="H50" s="97"/>
-      <c r="I50" s="77"/>
-      <c r="J50" s="86" t="s">
+      <c r="F50" s="79"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="80"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="91" t="s">
         <v>112</v>
       </c>
-      <c r="K50" s="87"/>
-      <c r="L50" s="88"/>
+      <c r="K50" s="92"/>
+      <c r="L50" s="93"/>
       <c r="M50" s="13" t="s">
         <v>81</v>
       </c>
@@ -8313,135 +8314,135 @@
       <c r="E51" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F51" s="78"/>
-      <c r="G51" s="79"/>
-      <c r="H51" s="79"/>
-      <c r="I51" s="79"/>
-      <c r="J51" s="79"/>
-      <c r="K51" s="80"/>
-      <c r="L51" s="84" t="s">
+      <c r="F51" s="94"/>
+      <c r="G51" s="95"/>
+      <c r="H51" s="95"/>
+      <c r="I51" s="95"/>
+      <c r="J51" s="95"/>
+      <c r="K51" s="96"/>
+      <c r="L51" s="76" t="s">
         <v>257</v>
       </c>
-      <c r="M51" s="85"/>
+      <c r="M51" s="78"/>
     </row>
     <row r="52" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="F52" s="84" t="s">
+      <c r="F52" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G52" s="77"/>
+      <c r="H52" s="77"/>
+      <c r="I52" s="77"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="77"/>
+      <c r="L52" s="77"/>
+      <c r="M52" s="78"/>
+      <c r="N52" t="s">
         <v>334</v>
-      </c>
-      <c r="G52" s="104"/>
-      <c r="H52" s="104"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="104"/>
-      <c r="K52" s="104"/>
-      <c r="L52" s="104"/>
-      <c r="M52" s="85"/>
-      <c r="N52" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="53" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="F53" s="84" t="s">
+        <v>368</v>
+      </c>
+      <c r="F53" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G53" s="77"/>
+      <c r="H53" s="77"/>
+      <c r="I53" s="77"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="77"/>
+      <c r="L53" s="77"/>
+      <c r="M53" s="78"/>
+      <c r="N53" t="s">
         <v>334</v>
-      </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="104"/>
-      <c r="J53" s="104"/>
-      <c r="K53" s="104"/>
-      <c r="L53" s="104"/>
-      <c r="M53" s="85"/>
-      <c r="N53" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="54" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="19" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="F54" s="84" t="s">
+        <v>369</v>
+      </c>
+      <c r="F54" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G54" s="77"/>
+      <c r="H54" s="77"/>
+      <c r="I54" s="77"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="77"/>
+      <c r="L54" s="77"/>
+      <c r="M54" s="78"/>
+      <c r="N54" t="s">
         <v>334</v>
-      </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="104"/>
-      <c r="J54" s="104"/>
-      <c r="K54" s="104"/>
-      <c r="L54" s="104"/>
-      <c r="M54" s="85"/>
-      <c r="N54" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="55" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="19" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="F55" s="84" t="s">
+        <v>370</v>
+      </c>
+      <c r="F55" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G55" s="77"/>
+      <c r="H55" s="77"/>
+      <c r="I55" s="77"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="77"/>
+      <c r="L55" s="77"/>
+      <c r="M55" s="78"/>
+      <c r="N55" t="s">
         <v>334</v>
-      </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="104"/>
-      <c r="J55" s="104"/>
-      <c r="K55" s="104"/>
-      <c r="L55" s="104"/>
-      <c r="M55" s="85"/>
-      <c r="N55" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="56" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="19" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="F56" s="84" t="s">
+        <v>371</v>
+      </c>
+      <c r="F56" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G56" s="77"/>
+      <c r="H56" s="77"/>
+      <c r="I56" s="77"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="77"/>
+      <c r="L56" s="77"/>
+      <c r="M56" s="78"/>
+      <c r="N56" t="s">
         <v>334</v>
-      </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="104"/>
-      <c r="J56" s="104"/>
-      <c r="K56" s="104"/>
-      <c r="L56" s="104"/>
-      <c r="M56" s="85"/>
-      <c r="N56" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="57" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -8452,179 +8453,165 @@
         <v>35</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="F57" s="84" t="s">
+        <v>372</v>
+      </c>
+      <c r="F57" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G57" s="77"/>
+      <c r="H57" s="77"/>
+      <c r="I57" s="77"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="77"/>
+      <c r="L57" s="77"/>
+      <c r="M57" s="78"/>
+      <c r="N57" t="s">
         <v>334</v>
-      </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="104"/>
-      <c r="J57" s="104"/>
-      <c r="K57" s="104"/>
-      <c r="L57" s="104"/>
-      <c r="M57" s="85"/>
-      <c r="N57" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="58" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="F58" s="84" t="s">
+        <v>373</v>
+      </c>
+      <c r="F58" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G58" s="77"/>
+      <c r="H58" s="77"/>
+      <c r="I58" s="77"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="77"/>
+      <c r="L58" s="77"/>
+      <c r="M58" s="78"/>
+      <c r="N58" t="s">
         <v>334</v>
-      </c>
-      <c r="G58" s="104"/>
-      <c r="H58" s="104"/>
-      <c r="I58" s="104"/>
-      <c r="J58" s="104"/>
-      <c r="K58" s="104"/>
-      <c r="L58" s="104"/>
-      <c r="M58" s="85"/>
-      <c r="N58" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="59" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="F59" s="84" t="s">
+        <v>374</v>
+      </c>
+      <c r="F59" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G59" s="77"/>
+      <c r="H59" s="77"/>
+      <c r="I59" s="77"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="77"/>
+      <c r="L59" s="77"/>
+      <c r="M59" s="78"/>
+      <c r="N59" t="s">
         <v>334</v>
-      </c>
-      <c r="G59" s="104"/>
-      <c r="H59" s="104"/>
-      <c r="I59" s="104"/>
-      <c r="J59" s="104"/>
-      <c r="K59" s="104"/>
-      <c r="L59" s="104"/>
-      <c r="M59" s="85"/>
-      <c r="N59" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="60" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="F60" s="84" t="s">
+        <v>375</v>
+      </c>
+      <c r="F60" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G60" s="77"/>
+      <c r="H60" s="77"/>
+      <c r="I60" s="77"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="77"/>
+      <c r="L60" s="77"/>
+      <c r="M60" s="78"/>
+      <c r="N60" t="s">
         <v>334</v>
-      </c>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="104"/>
-      <c r="L60" s="104"/>
-      <c r="M60" s="85"/>
-      <c r="N60" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="61" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="F61" s="84" t="s">
+        <v>399</v>
+      </c>
+      <c r="F61" s="76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G61" s="77"/>
+      <c r="H61" s="77"/>
+      <c r="I61" s="77"/>
+      <c r="J61" s="77"/>
+      <c r="K61" s="77"/>
+      <c r="L61" s="77"/>
+      <c r="M61" s="78"/>
+      <c r="N61" t="s">
         <v>334</v>
-      </c>
-      <c r="G61" s="104"/>
-      <c r="H61" s="104"/>
-      <c r="I61" s="104"/>
-      <c r="J61" s="104"/>
-      <c r="K61" s="104"/>
-      <c r="L61" s="104"/>
-      <c r="M61" s="85"/>
-      <c r="N61" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="62" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="63" spans="3:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="53" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D63" t="s">
         <v>34</v>
       </c>
       <c r="F63" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="G63" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="G63" s="11" t="s">
+      <c r="H63" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="I63" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="I63" s="11" t="s">
+      <c r="J63" s="54" t="s">
+        <v>290</v>
+      </c>
+      <c r="K63" s="79"/>
+      <c r="L63" s="81"/>
+      <c r="M63" s="54" t="s">
         <v>289</v>
-      </c>
-      <c r="J63" s="54" t="s">
-        <v>291</v>
-      </c>
-      <c r="K63" s="76"/>
-      <c r="L63" s="77"/>
-      <c r="M63" s="54" t="s">
-        <v>290</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F59:M59"/>
-    <mergeCell ref="F60:M60"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F55:M55"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="F47:M47"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F23:M23"/>
-    <mergeCell ref="F20:M20"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="F11:M11"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="F61:M61"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="F51:K51"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="F16:M16"/>
     <mergeCell ref="F17:M17"/>
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="F26:M26"/>
@@ -8641,22 +8628,36 @@
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="F34:J34"/>
     <mergeCell ref="F21:M21"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="F11:M11"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="F61:M61"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="F51:K51"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="F20:M20"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="F47:M47"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F59:M59"/>
+    <mergeCell ref="F60:M60"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F55:M55"/>
+    <mergeCell ref="F56:M56"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8671,7 +8672,7 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -8687,7 +8688,7 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F743BA-ECE2-4927-8DE0-B43732771FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA28F09-917A-4058-990D-85DDA2634880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,14 @@
     <sheet name="OPL2+ADPCM" sheetId="5" r:id="rId5"/>
     <sheet name="SCC" sheetId="6" r:id="rId6"/>
     <sheet name="MIXIER" sheetId="7" r:id="rId7"/>
+    <sheet name="SerialSRAM Memory Map" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="430">
   <si>
     <t>OPL2 (YM3812) + ADPCM  [MSX-AUDIO(Y8950) Compatible]</t>
   </si>
@@ -701,529 +702,672 @@
     <t>MSX SLOT</t>
   </si>
   <si>
+    <t>7FF1h</t>
+  </si>
+  <si>
+    <t>SSG Register Write</t>
+  </si>
+  <si>
+    <t>7FF2h</t>
+  </si>
+  <si>
+    <t>7FF3h</t>
+  </si>
+  <si>
+    <t>OPL2 Register Data</t>
+  </si>
+  <si>
+    <t>7FF4h</t>
+  </si>
+  <si>
+    <t>OPLL Register Address</t>
+  </si>
+  <si>
+    <t>7FF5h</t>
+  </si>
+  <si>
+    <t>OPLL Register Value</t>
+  </si>
+  <si>
+    <t>OPLL Register Data</t>
+  </si>
+  <si>
+    <t>7FF6h</t>
+  </si>
+  <si>
+    <t>I/O Enabler1</t>
+  </si>
+  <si>
+    <t>7FF7h</t>
+  </si>
+  <si>
+    <t>SSG Volume</t>
+  </si>
+  <si>
+    <t>7FF8h</t>
+  </si>
+  <si>
+    <t>OPLL Volume</t>
+  </si>
+  <si>
+    <t>7FF9h</t>
+  </si>
+  <si>
+    <t>OPL2 Volume</t>
+  </si>
+  <si>
+    <t>7FFAh</t>
+  </si>
+  <si>
+    <t>SCC Volume</t>
+  </si>
+  <si>
+    <t>7FFBh</t>
+  </si>
+  <si>
+    <t>Reserved</t>
+  </si>
+  <si>
+    <t>7FFCh</t>
+  </si>
+  <si>
+    <t>7FFDh</t>
+  </si>
+  <si>
+    <t>7FFEh</t>
+  </si>
+  <si>
+    <t>7FFFh</t>
+  </si>
+  <si>
+    <t>I/O Enabler2</t>
+  </si>
+  <si>
+    <t>TIMER</t>
+  </si>
+  <si>
+    <t>9000-97FFh</t>
+  </si>
+  <si>
+    <t>B000-B7FFh</t>
+  </si>
+  <si>
+    <t>Dual SSG (YM2149) [PSG(AY-3-8910) Compatible]</t>
+  </si>
+  <si>
+    <t>A0h</t>
+  </si>
+  <si>
+    <t>Register Address</t>
+  </si>
+  <si>
+    <t>A1h</t>
+  </si>
+  <si>
+    <t>Write専用。Readすると 255。</t>
+  </si>
+  <si>
+    <t>A2h</t>
+  </si>
+  <si>
+    <t>Read専用。</t>
+  </si>
+  <si>
+    <t>Register(A0h にこの Address を書くと、A1h, A2h が Description の機能に切り替わる)</t>
+  </si>
+  <si>
+    <t>SSG1: Ch.A 分周比下位8bit</t>
+  </si>
+  <si>
+    <t>分周比下位</t>
+  </si>
+  <si>
+    <t>SSG1: Ch.A 分周比上位4bit</t>
+  </si>
+  <si>
+    <t>分周比上位</t>
+  </si>
+  <si>
+    <t>SSG1: Ch.B 分周比下位8bit</t>
+  </si>
+  <si>
+    <t>SSG1: Ch.B 分周比上位4bit</t>
+  </si>
+  <si>
+    <t>SSG1: Ch.C 分周比下位8bit</t>
+  </si>
+  <si>
+    <t>SSG1: Ch.C 分周比上位4bit</t>
+  </si>
+  <si>
+    <t>SSG1: ノイズ分周比</t>
+  </si>
+  <si>
+    <t>ノイズ分周比</t>
+  </si>
+  <si>
+    <t>SSG1: /ENABLE</t>
+  </si>
+  <si>
+    <t>IOB</t>
+  </si>
+  <si>
+    <t>IOA</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>NB</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>SSG1: Ch.A音量</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>音量</t>
+  </si>
+  <si>
+    <t>SSG1: Ch.B音量</t>
+  </si>
+  <si>
+    <t>SSG1: Ch.C音量</t>
+  </si>
+  <si>
+    <t>SSG1: エンベロープ周期 下位8bit</t>
+  </si>
+  <si>
+    <t>エンベロープ周期下位</t>
+  </si>
+  <si>
+    <t>SSG1: エンベロープ周期 上位8bit</t>
+  </si>
+  <si>
+    <t>エンベロープ周期下位周期上位</t>
+  </si>
+  <si>
+    <t>SSG1: エンベロープ波形</t>
+  </si>
+  <si>
+    <t>エンベロープ波形</t>
+  </si>
+  <si>
+    <t>SSG1: GPIO A 未接続</t>
+  </si>
+  <si>
+    <t>SSG1: GPIO B 未接続</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.A 分周比下位8bit</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.A 分周比上位4bit</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.B 分周比下位8bit</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.B 分周比上位4bit</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.C 分周比下位8bit</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.C 分周比上位4bit</t>
+  </si>
+  <si>
+    <t>SSG2: ノイズ分周比</t>
+  </si>
+  <si>
+    <t>SSG2: /ENABLE</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.A音量</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.B音量</t>
+  </si>
+  <si>
+    <t>SSG2: Ch.C音量</t>
+  </si>
+  <si>
+    <t>SSG2: エンベロープ周期 下位8bit</t>
+  </si>
+  <si>
+    <t>SSG2: エンベロープ周期 上位8bit</t>
+  </si>
+  <si>
+    <t>SSG2: エンベロープ波形</t>
+  </si>
+  <si>
+    <t>SSG2: GPIO A</t>
+  </si>
+  <si>
+    <t>SSG2: GPIO B 下位4bit は LED に接続</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SSG1 Ch.A 音量</t>
+  </si>
+  <si>
+    <t>0～128: 128が最大。デフォルト128。</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>SSG1 Ch.B 音量</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>SSG1 Ch.C 音量</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>未接続</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>SSG2 Ch.A 音量</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>SSG2 Ch.B 音量</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>SSG2 Ch.C 音量</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>SSG1 Ch.A ステレオ定位</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>SSG1 Ch.B ステレオ定位</t>
+  </si>
+  <si>
+    <t>2A</t>
+  </si>
+  <si>
+    <t>SSG1 Ch.C ステレオ定位</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>2C</t>
+  </si>
+  <si>
+    <t>SSG2 Ch.A ステレオ定位</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>SSG2 Ch.B ステレオ定位</t>
+  </si>
+  <si>
+    <t>2E</t>
+  </si>
+  <si>
+    <t>SSG2 Ch.C ステレオ定位</t>
+  </si>
+  <si>
+    <t>2F</t>
+  </si>
+  <si>
+    <t>20～EF</t>
+  </si>
+  <si>
+    <t>OPLL-EX (YM2413)</t>
+  </si>
+  <si>
+    <t>YM2413 に、OPLL/OPLL-X/OPLL-P/VRC7 のプリセット音色バンクを追加したもの。</t>
+  </si>
+  <si>
+    <t>7Ch</t>
+  </si>
+  <si>
+    <t>OPLL1 Register Address</t>
+  </si>
+  <si>
+    <t>7Dh</t>
+  </si>
+  <si>
+    <t>OPLL1 Register Value</t>
+  </si>
+  <si>
+    <t>OPLL1 Register Data</t>
+  </si>
+  <si>
+    <t>Register(7Ah にこの Address を書くと7Bh が Description の機能に切り替わる、7Ch にこの Address を書くと7Dh が Description の機能に切り替わる)</t>
+  </si>
+  <si>
+    <t>EGT</t>
+  </si>
+  <si>
+    <t>KS</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>08-0D</t>
+  </si>
+  <si>
+    <t>TESTレジスタ (常に 0)</t>
+  </si>
+  <si>
+    <t>19-1F</t>
+  </si>
+  <si>
+    <t>SUS</t>
+  </si>
+  <si>
+    <t>KEY</t>
+  </si>
+  <si>
+    <t>29-2F</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>INST</t>
+  </si>
+  <si>
+    <t>VOL</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39-3F</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>新設。ROM音色選択レジスタ。</t>
+  </si>
+  <si>
+    <t>BANK</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49-4F</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>新設。ステレオ定位。</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59-FF</t>
+  </si>
+  <si>
+    <t>SCCは、MemoryMappedI/Oのみ。</t>
+  </si>
+  <si>
+    <t>MIXIERは、MemoryMappedI/Oのみ。</t>
+  </si>
+  <si>
+    <t>Master Volume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#15) のときのみ利用可能</t>
   </si>
   <si>
-    <t>7FF1h</t>
-  </si>
-  <si>
-    <t>SSG Register Write</t>
-  </si>
-  <si>
-    <t>7FF2h</t>
-  </si>
-  <si>
-    <t>7FF3h</t>
-  </si>
-  <si>
-    <t>OPL2 Register Data</t>
-  </si>
-  <si>
-    <t>7FF4h</t>
-  </si>
-  <si>
-    <t>OPLL Register Address</t>
-  </si>
-  <si>
-    <t>7FF5h</t>
-  </si>
-  <si>
-    <t>OPLL Register Value</t>
-  </si>
-  <si>
-    <t>OPLL Register Data</t>
-  </si>
-  <si>
-    <t>7FF6h</t>
-  </si>
-  <si>
-    <t>I/O Enabler1</t>
-  </si>
-  <si>
-    <t>7FF7h</t>
-  </si>
-  <si>
-    <t>SSG Volume</t>
-  </si>
-  <si>
     <t>0: OFF,～128: MAX, RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#15) のときのみ利用可能</t>
   </si>
   <si>
-    <t>7FF8h</t>
-  </si>
-  <si>
-    <t>OPLL Volume</t>
-  </si>
-  <si>
-    <t>7FF9h</t>
-  </si>
-  <si>
-    <t>OPL2 Volume</t>
-  </si>
-  <si>
-    <t>7FFAh</t>
-  </si>
-  <si>
-    <t>SCC Volume</t>
-  </si>
-  <si>
-    <t>7FFBh</t>
-  </si>
-  <si>
-    <t>Reserved</t>
-  </si>
-  <si>
-    <t>7FFCh</t>
-  </si>
-  <si>
-    <t>7FFDh</t>
-  </si>
-  <si>
-    <t>7FFEh</t>
-  </si>
-  <si>
-    <t>7FFFh</t>
-  </si>
-  <si>
-    <t>I/O Enabler2</t>
-  </si>
-  <si>
-    <t>TIMER</t>
-  </si>
-  <si>
-    <t>9000-97FFh</t>
-  </si>
-  <si>
-    <t>B000-B7FFh</t>
-  </si>
-  <si>
-    <t>Dual SSG (YM2149) [PSG(AY-3-8910) Compatible]</t>
-  </si>
-  <si>
-    <t>A0h</t>
-  </si>
-  <si>
-    <t>Register Address</t>
-  </si>
-  <si>
-    <t>A1h</t>
-  </si>
-  <si>
-    <t>Write専用。Readすると 255。</t>
-  </si>
-  <si>
-    <t>A2h</t>
-  </si>
-  <si>
-    <t>Read専用。</t>
-  </si>
-  <si>
-    <t>Register(A0h にこの Address を書くと、A1h, A2h が Description の機能に切り替わる)</t>
-  </si>
-  <si>
-    <t>SSG1: Ch.A 分周比下位8bit</t>
-  </si>
-  <si>
-    <t>分周比下位</t>
-  </si>
-  <si>
-    <t>SSG1: Ch.A 分周比上位4bit</t>
-  </si>
-  <si>
-    <t>分周比上位</t>
-  </si>
-  <si>
-    <t>SSG1: Ch.B 分周比下位8bit</t>
-  </si>
-  <si>
-    <t>SSG1: Ch.B 分周比上位4bit</t>
-  </si>
-  <si>
-    <t>SSG1: Ch.C 分周比下位8bit</t>
-  </si>
-  <si>
-    <t>SSG1: Ch.C 分周比上位4bit</t>
-  </si>
-  <si>
-    <t>SSG1: ノイズ分周比</t>
-  </si>
-  <si>
-    <t>ノイズ分周比</t>
-  </si>
-  <si>
-    <t>SSG1: /ENABLE</t>
-  </si>
-  <si>
-    <t>IOB</t>
-  </si>
-  <si>
-    <t>IOA</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>NB</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>TA</t>
-  </si>
-  <si>
-    <t>SSG1: Ch.A音量</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>音量</t>
-  </si>
-  <si>
-    <t>SSG1: Ch.B音量</t>
-  </si>
-  <si>
-    <t>SSG1: Ch.C音量</t>
-  </si>
-  <si>
-    <t>SSG1: エンベロープ周期 下位8bit</t>
-  </si>
-  <si>
-    <t>エンベロープ周期下位</t>
-  </si>
-  <si>
-    <t>SSG1: エンベロープ周期 上位8bit</t>
-  </si>
-  <si>
-    <t>エンベロープ周期下位周期上位</t>
-  </si>
-  <si>
-    <t>SSG1: エンベロープ波形</t>
-  </si>
-  <si>
-    <t>エンベロープ波形</t>
-  </si>
-  <si>
-    <t>SSG1: GPIO A 未接続</t>
-  </si>
-  <si>
-    <t>SSG1: GPIO B 未接続</t>
-  </si>
-  <si>
-    <t>SSG2: Ch.A 分周比下位8bit</t>
-  </si>
-  <si>
-    <t>SSG2: Ch.A 分周比上位4bit</t>
-  </si>
-  <si>
-    <t>SSG2: Ch.B 分周比下位8bit</t>
-  </si>
-  <si>
-    <t>SSG2: Ch.B 分周比上位4bit</t>
-  </si>
-  <si>
-    <t>SSG2: Ch.C 分周比下位8bit</t>
-  </si>
-  <si>
-    <t>SSG2: Ch.C 分周比上位4bit</t>
-  </si>
-  <si>
-    <t>SSG2: ノイズ分周比</t>
-  </si>
-  <si>
-    <t>SSG2: /ENABLE</t>
-  </si>
-  <si>
-    <t>SSG2: Ch.A音量</t>
-  </si>
-  <si>
-    <t>SSG2: Ch.B音量</t>
-  </si>
-  <si>
-    <t>SSG2: Ch.C音量</t>
-  </si>
-  <si>
-    <t>SSG2: エンベロープ周期 下位8bit</t>
-  </si>
-  <si>
-    <t>SSG2: エンベロープ周期 上位8bit</t>
-  </si>
-  <si>
-    <t>SSG2: エンベロープ波形</t>
-  </si>
-  <si>
-    <t>SSG2: GPIO A</t>
-  </si>
-  <si>
-    <t>SSG2: GPIO B 下位4bit は LED に接続</t>
-  </si>
-  <si>
-    <t>LED</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>SSG1 Ch.A 音量</t>
-  </si>
-  <si>
-    <t>0～128: 128が最大。デフォルト128。</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>SSG1 Ch.B 音量</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>SSG1 Ch.C 音量</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>未接続</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>SSG2 Ch.A 音量</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>SSG2 Ch.B 音量</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>SSG2 Ch.C 音量</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>SSG1 Ch.A ステレオ定位</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>SSG1 Ch.B ステレオ定位</t>
-  </si>
-  <si>
-    <t>2A</t>
-  </si>
-  <si>
-    <t>SSG1 Ch.C ステレオ定位</t>
-  </si>
-  <si>
-    <t>2B</t>
-  </si>
-  <si>
-    <t>2C</t>
-  </si>
-  <si>
-    <t>SSG2 Ch.A ステレオ定位</t>
-  </si>
-  <si>
-    <t>2D</t>
-  </si>
-  <si>
-    <t>SSG2 Ch.B ステレオ定位</t>
-  </si>
-  <si>
-    <t>2E</t>
-  </si>
-  <si>
-    <t>SSG2 Ch.C ステレオ定位</t>
-  </si>
-  <si>
-    <t>2F</t>
-  </si>
-  <si>
-    <t>20～EF</t>
-  </si>
-  <si>
-    <t>OPLL-EX (YM2413)</t>
-  </si>
-  <si>
-    <t>YM2413 に、OPLL/OPLL-X/OPLL-P/VRC7 のプリセット音色バンクを追加したもの。</t>
-  </si>
-  <si>
-    <t>7Ch</t>
-  </si>
-  <si>
-    <t>OPLL1 Register Address</t>
-  </si>
-  <si>
-    <t>7Dh</t>
-  </si>
-  <si>
-    <t>OPLL1 Register Value</t>
-  </si>
-  <si>
-    <t>OPLL1 Register Data</t>
-  </si>
-  <si>
-    <t>Register(7Ah にこの Address を書くと7Bh が Description の機能に切り替わる、7Ch にこの Address を書くと7Dh が Description の機能に切り替わる)</t>
-  </si>
-  <si>
-    <t>EGT</t>
-  </si>
-  <si>
-    <t>KS</t>
-  </si>
-  <si>
-    <t>DC</t>
-  </si>
-  <si>
-    <t>DM</t>
-  </si>
-  <si>
-    <t>08-0D</t>
-  </si>
-  <si>
-    <t>TESTレジスタ (常に 0)</t>
-  </si>
-  <si>
-    <t>19-1F</t>
-  </si>
-  <si>
-    <t>SUS</t>
-  </si>
-  <si>
-    <t>KEY</t>
-  </si>
-  <si>
-    <t>29-2F</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>INST</t>
-  </si>
-  <si>
-    <t>VOL</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>39-3F</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>新設。ROM音色選択レジスタ。</t>
-  </si>
-  <si>
-    <t>BANK</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>49-4F</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>新設。ステレオ定位。</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>59-FF</t>
-  </si>
-  <si>
-    <t>SCCは、MemoryMappedI/Oのみ。</t>
-  </si>
-  <si>
-    <t>MIXIERは、MemoryMappedI/Oのみ。</t>
-  </si>
-  <si>
-    <t>Master Volume</t>
+    <t>#0～#15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BIOS ROM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#16～#31</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#32～#63</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADPCM RAM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>512KB の容量を、8KB単位に分割し、#0～#63 の番号を振ると、下記のような役割となる。</t>
+    <rPh sb="7" eb="9">
+      <t>ヨウリョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヤクワリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8KBの単位を BANK と呼び、#0～#31 は SCC のバンクレジスタで管理される。</t>
+    <rPh sb="4" eb="6">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A18</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A17</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A16</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A0</t>
+  </si>
+  <si>
+    <t>0=CPU Address, 1=ADPCM Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK内のアドレス</t>
+    <rPh sb="4" eb="5">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK番号</t>
+    <rPh sb="4" eb="6">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>:</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1357,7 +1501,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1719,6 +1863,109 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1728,7 +1975,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1967,56 +2214,92 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2662,13 +2945,13 @@
       <c r="F4" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G4" s="91"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="81"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="82"/>
       <c r="N4" s="66" t="s">
         <v>205</v>
       </c>
@@ -2689,16 +2972,16 @@
       <c r="F5" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G5" s="95" t="s">
+      <c r="G5" s="84" t="s">
         <v>209</v>
       </c>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="82"/>
       <c r="O5" s="49" t="s">
         <v>210</v>
       </c>
@@ -2716,16 +2999,16 @@
       <c r="F6" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G6" s="95" t="s">
+      <c r="G6" s="84" t="s">
         <v>209</v>
       </c>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="82"/>
       <c r="O6" s="49" t="s">
         <v>210</v>
       </c>
@@ -2743,16 +3026,16 @@
       <c r="F7" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="95" t="s">
+      <c r="G7" s="84" t="s">
         <v>209</v>
       </c>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="82"/>
       <c r="O7" s="49" t="s">
         <v>210</v>
       </c>
@@ -2770,16 +3053,16 @@
       <c r="F8" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G8" s="95" t="s">
+      <c r="G8" s="84" t="s">
         <v>209</v>
       </c>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="82"/>
       <c r="O8" s="49" t="s">
         <v>210</v>
       </c>
@@ -2797,16 +3080,16 @@
       <c r="F9" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G9" s="86" t="s">
+      <c r="G9" s="83" t="s">
         <v>218</v>
       </c>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="81"/>
+      <c r="N9" s="82"/>
       <c r="O9" s="49" t="s">
         <v>219</v>
       </c>
@@ -2824,16 +3107,16 @@
       <c r="F10" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G10" s="86" t="s">
+      <c r="G10" s="83" t="s">
         <v>218</v>
       </c>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="83"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="82"/>
       <c r="O10" s="49" t="s">
         <v>219</v>
       </c>
@@ -2851,50 +3134,50 @@
       <c r="F11" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G11" s="84" t="s">
+      <c r="G11" s="88" t="s">
         <v>222</v>
       </c>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="82"/>
       <c r="O11" s="50" t="s">
-        <v>224</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>225</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>226</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="84" t="s">
-        <v>226</v>
-      </c>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="81"/>
+      <c r="G12" s="88" t="s">
+        <v>225</v>
+      </c>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="82"/>
       <c r="O12" s="50" t="s">
-        <v>224</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="45" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D13" s="46" t="s">
         <v>19</v>
@@ -2905,23 +3188,23 @@
       <c r="F13" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G13" s="96" t="s">
+      <c r="G13" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="82"/>
       <c r="O13" s="50" t="s">
-        <v>224</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>19</v>
@@ -2932,185 +3215,185 @@
       <c r="F14" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G14" s="96" t="s">
-        <v>229</v>
-      </c>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="81"/>
+      <c r="G14" s="85" t="s">
+        <v>228</v>
+      </c>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="82"/>
       <c r="O14" s="50" t="s">
-        <v>224</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G15" s="80" t="s">
-        <v>231</v>
-      </c>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="83"/>
-      <c r="N15" s="81"/>
+      <c r="G15" s="87" t="s">
+        <v>230</v>
+      </c>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="82"/>
       <c r="O15" s="50" t="s">
-        <v>224</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G16" s="80" t="s">
-        <v>234</v>
-      </c>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="83"/>
-      <c r="N16" s="81"/>
+      <c r="G16" s="87" t="s">
+        <v>233</v>
+      </c>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="82"/>
       <c r="O16" s="50" t="s">
-        <v>224</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G17" s="97"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="81"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="82"/>
       <c r="N17" s="10" t="s">
         <v>176</v>
       </c>
       <c r="O17" s="50" t="s">
-        <v>224</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G18" s="96"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="83"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="83"/>
-      <c r="N18" s="81"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="82"/>
       <c r="O18" s="50" t="s">
-        <v>239</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="96"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="81"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="82"/>
       <c r="O19" s="50" t="s">
-        <v>239</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G20" s="96"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="83"/>
-      <c r="N20" s="81"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="81"/>
+      <c r="N20" s="82"/>
       <c r="O20" s="50" t="s">
-        <v>239</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>223</v>
@@ -3124,18 +3407,18 @@
       <c r="M21" s="72"/>
       <c r="N21" s="73"/>
       <c r="O21" s="50" t="s">
-        <v>239</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="75"/>
@@ -3150,13 +3433,13 @@
     </row>
     <row r="23" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="75"/>
@@ -3171,13 +3454,13 @@
     </row>
     <row r="24" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="75"/>
@@ -3192,13 +3475,13 @@
     </row>
     <row r="25" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>223</v>
@@ -3212,30 +3495,30 @@
       <c r="M25" s="72"/>
       <c r="N25" s="73"/>
       <c r="O25" s="50" t="s">
-        <v>239</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>223</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="H26" s="91"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="81"/>
+        <v>251</v>
+      </c>
+      <c r="H26" s="80"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="82"/>
       <c r="M26" s="32" t="s">
         <v>173</v>
       </c>
@@ -3243,12 +3526,12 @@
         <v>180</v>
       </c>
       <c r="O26" s="50" t="s">
-        <v>224</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="63" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>19</v>
@@ -3259,23 +3542,23 @@
       <c r="F27" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="86" t="s">
+      <c r="G27" s="83" t="s">
         <v>218</v>
       </c>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
+      <c r="M27" s="81"/>
+      <c r="N27" s="82"/>
       <c r="O27" s="49" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="28" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="65" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>19</v>
@@ -3286,16 +3569,16 @@
       <c r="F28" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="86" t="s">
+      <c r="G28" s="83" t="s">
         <v>218</v>
       </c>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
+      <c r="M28" s="81"/>
+      <c r="N28" s="82"/>
       <c r="O28" s="49" t="s">
         <v>219</v>
       </c>
@@ -3339,7 +3622,7 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
@@ -3360,40 +3643,40 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C6" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C8" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -3439,18 +3722,18 @@
         <v>19</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="F12" s="98" t="s">
-        <v>265</v>
-      </c>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="81"/>
+        <v>262</v>
+      </c>
+      <c r="F12" s="89" t="s">
+        <v>263</v>
+      </c>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="82"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -3460,18 +3743,18 @@
         <v>19</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F13" s="33"/>
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="98" t="s">
-        <v>267</v>
-      </c>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="81"/>
+      <c r="J13" s="89" t="s">
+        <v>265</v>
+      </c>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="82"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -3481,18 +3764,18 @@
         <v>19</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F14" s="98" t="s">
-        <v>265</v>
-      </c>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="81"/>
+        <v>266</v>
+      </c>
+      <c r="F14" s="89" t="s">
+        <v>263</v>
+      </c>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="82"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -3502,18 +3785,18 @@
         <v>19</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F15" s="33"/>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="35"/>
-      <c r="J15" s="98" t="s">
-        <v>267</v>
-      </c>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="81"/>
+      <c r="J15" s="89" t="s">
+        <v>265</v>
+      </c>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="82"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="18" t="s">
@@ -3523,18 +3806,18 @@
         <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="F16" s="98" t="s">
-        <v>265</v>
-      </c>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="81"/>
+        <v>268</v>
+      </c>
+      <c r="F16" s="89" t="s">
+        <v>263</v>
+      </c>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="82"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="18" t="s">
@@ -3544,18 +3827,18 @@
         <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F17" s="33"/>
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
       <c r="I17" s="35"/>
-      <c r="J17" s="98" t="s">
-        <v>267</v>
-      </c>
-      <c r="K17" s="83"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="81"/>
+      <c r="J17" s="89" t="s">
+        <v>265</v>
+      </c>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="82"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="18" t="s">
@@ -3565,18 +3848,18 @@
         <v>19</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F18" s="33"/>
       <c r="G18" s="34"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="98" t="s">
-        <v>273</v>
-      </c>
-      <c r="J18" s="83"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="81"/>
+      <c r="I18" s="89" t="s">
+        <v>271</v>
+      </c>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="82"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="18" t="s">
@@ -3586,31 +3869,31 @@
         <v>19</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="G19" s="37" t="s">
         <v>274</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="H19" s="36" t="s">
         <v>275</v>
       </c>
-      <c r="G19" s="37" t="s">
+      <c r="I19" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="H19" s="36" t="s">
+      <c r="J19" s="37" t="s">
         <v>277</v>
-      </c>
-      <c r="I19" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>279</v>
       </c>
       <c r="K19" s="39" t="s">
         <v>130</v>
       </c>
       <c r="L19" s="38" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="M19" s="37" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -3621,20 +3904,20 @@
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F20" s="33"/>
       <c r="G20" s="34"/>
       <c r="H20" s="35"/>
       <c r="I20" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="J20" s="98" t="s">
-        <v>284</v>
-      </c>
-      <c r="K20" s="83"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="81"/>
+        <v>281</v>
+      </c>
+      <c r="J20" s="89" t="s">
+        <v>282</v>
+      </c>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="82"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -3644,20 +3927,20 @@
         <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F21" s="33"/>
       <c r="G21" s="34"/>
       <c r="H21" s="35"/>
       <c r="I21" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="J21" s="98" t="s">
-        <v>284</v>
-      </c>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="81"/>
+        <v>281</v>
+      </c>
+      <c r="J21" s="89" t="s">
+        <v>282</v>
+      </c>
+      <c r="K21" s="81"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="82"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -3667,20 +3950,20 @@
         <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F22" s="33"/>
       <c r="G22" s="34"/>
       <c r="H22" s="35"/>
       <c r="I22" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="J22" s="98" t="s">
-        <v>284</v>
-      </c>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="81"/>
+        <v>281</v>
+      </c>
+      <c r="J22" s="89" t="s">
+        <v>282</v>
+      </c>
+      <c r="K22" s="81"/>
+      <c r="L22" s="81"/>
+      <c r="M22" s="82"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -3690,18 +3973,18 @@
         <v>19</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="F23" s="98" t="s">
-        <v>288</v>
-      </c>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="81"/>
+        <v>285</v>
+      </c>
+      <c r="F23" s="89" t="s">
+        <v>286</v>
+      </c>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="82"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -3711,18 +3994,18 @@
         <v>19</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="F24" s="98" t="s">
-        <v>290</v>
-      </c>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="81"/>
+        <v>287</v>
+      </c>
+      <c r="F24" s="89" t="s">
+        <v>288</v>
+      </c>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="81"/>
+      <c r="M24" s="82"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -3732,18 +4015,18 @@
         <v>19</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F25" s="33"/>
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="98" t="s">
-        <v>292</v>
-      </c>
-      <c r="K25" s="83"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="81"/>
+      <c r="J25" s="89" t="s">
+        <v>290</v>
+      </c>
+      <c r="K25" s="81"/>
+      <c r="L25" s="81"/>
+      <c r="M25" s="82"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -3753,7 +4036,7 @@
         <v>19</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="8"/>
@@ -3772,7 +4055,7 @@
         <v>19</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="8"/>
@@ -3791,18 +4074,18 @@
         <v>3</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>295</v>
-      </c>
-      <c r="F28" s="96" t="s">
-        <v>265</v>
-      </c>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="81"/>
+        <v>293</v>
+      </c>
+      <c r="F28" s="85" t="s">
+        <v>263</v>
+      </c>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
+      <c r="M28" s="82"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="18" t="s">
@@ -3812,18 +4095,18 @@
         <v>3</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F29" s="25"/>
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="27"/>
-      <c r="J29" s="96" t="s">
-        <v>267</v>
-      </c>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="81"/>
+      <c r="J29" s="85" t="s">
+        <v>265</v>
+      </c>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
+      <c r="M29" s="82"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -3833,18 +4116,18 @@
         <v>3</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="F30" s="96" t="s">
-        <v>265</v>
-      </c>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="81"/>
+        <v>295</v>
+      </c>
+      <c r="F30" s="85" t="s">
+        <v>263</v>
+      </c>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="81"/>
+      <c r="M30" s="82"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -3854,18 +4137,18 @@
         <v>3</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F31" s="25"/>
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="27"/>
-      <c r="J31" s="96" t="s">
-        <v>267</v>
-      </c>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="81"/>
+      <c r="J31" s="85" t="s">
+        <v>265</v>
+      </c>
+      <c r="K31" s="81"/>
+      <c r="L31" s="81"/>
+      <c r="M31" s="82"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -3875,18 +4158,18 @@
         <v>3</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="F32" s="96" t="s">
-        <v>265</v>
-      </c>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
-      <c r="M32" s="81"/>
+        <v>297</v>
+      </c>
+      <c r="F32" s="85" t="s">
+        <v>263</v>
+      </c>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="81"/>
+      <c r="M32" s="82"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -3896,18 +4179,18 @@
         <v>3</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F33" s="25"/>
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="27"/>
-      <c r="J33" s="96" t="s">
-        <v>267</v>
-      </c>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
-      <c r="M33" s="81"/>
+      <c r="J33" s="85" t="s">
+        <v>265</v>
+      </c>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="82"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -3917,18 +4200,18 @@
         <v>3</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F34" s="25"/>
       <c r="G34" s="26"/>
       <c r="H34" s="27"/>
-      <c r="I34" s="96" t="s">
-        <v>273</v>
-      </c>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="83"/>
-      <c r="M34" s="81"/>
+      <c r="I34" s="85" t="s">
+        <v>271</v>
+      </c>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="81"/>
+      <c r="M34" s="82"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -3938,31 +4221,31 @@
         <v>3</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F35" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="H35" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="G35" s="29" t="s">
+      <c r="I35" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="J35" s="29" t="s">
         <v>277</v>
-      </c>
-      <c r="I35" s="30" t="s">
-        <v>278</v>
-      </c>
-      <c r="J35" s="29" t="s">
-        <v>279</v>
       </c>
       <c r="K35" s="31" t="s">
         <v>130</v>
       </c>
       <c r="L35" s="30" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="M35" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -3973,20 +4256,20 @@
         <v>3</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F36" s="25"/>
       <c r="G36" s="26"/>
       <c r="H36" s="27"/>
       <c r="I36" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="J36" s="96" t="s">
-        <v>284</v>
-      </c>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
-      <c r="M36" s="81"/>
+        <v>281</v>
+      </c>
+      <c r="J36" s="85" t="s">
+        <v>282</v>
+      </c>
+      <c r="K36" s="81"/>
+      <c r="L36" s="81"/>
+      <c r="M36" s="82"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -3996,20 +4279,20 @@
         <v>3</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F37" s="25"/>
       <c r="G37" s="26"/>
       <c r="H37" s="27"/>
       <c r="I37" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="J37" s="96" t="s">
-        <v>284</v>
-      </c>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="81"/>
+        <v>281</v>
+      </c>
+      <c r="J37" s="85" t="s">
+        <v>282</v>
+      </c>
+      <c r="K37" s="81"/>
+      <c r="L37" s="81"/>
+      <c r="M37" s="82"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -4019,20 +4302,20 @@
         <v>3</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F38" s="25"/>
       <c r="G38" s="26"/>
       <c r="H38" s="27"/>
       <c r="I38" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="J38" s="96" t="s">
-        <v>284</v>
-      </c>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="81"/>
+        <v>281</v>
+      </c>
+      <c r="J38" s="85" t="s">
+        <v>282</v>
+      </c>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
+      <c r="M38" s="82"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -4042,18 +4325,18 @@
         <v>3</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="F39" s="96" t="s">
-        <v>288</v>
-      </c>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="83"/>
-      <c r="K39" s="83"/>
-      <c r="L39" s="83"/>
-      <c r="M39" s="81"/>
+        <v>304</v>
+      </c>
+      <c r="F39" s="85" t="s">
+        <v>286</v>
+      </c>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="81"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="81"/>
+      <c r="M39" s="82"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18" t="s">
@@ -4063,18 +4346,18 @@
         <v>3</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="F40" s="96" t="s">
-        <v>290</v>
-      </c>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="83"/>
-      <c r="M40" s="81"/>
+        <v>305</v>
+      </c>
+      <c r="F40" s="85" t="s">
+        <v>288</v>
+      </c>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="81"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="81"/>
+      <c r="L40" s="81"/>
+      <c r="M40" s="82"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18" t="s">
@@ -4084,18 +4367,18 @@
         <v>3</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F41" s="25"/>
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="27"/>
-      <c r="J41" s="96" t="s">
-        <v>292</v>
-      </c>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="81"/>
+      <c r="J41" s="85" t="s">
+        <v>290</v>
+      </c>
+      <c r="K41" s="81"/>
+      <c r="L41" s="81"/>
+      <c r="M41" s="82"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18" t="s">
@@ -4105,7 +4388,7 @@
         <v>3</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F42" s="25"/>
       <c r="G42" s="26"/>
@@ -4124,100 +4407,100 @@
         <v>3</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F43" s="68"/>
       <c r="G43" s="69"/>
       <c r="H43" s="69"/>
       <c r="I43" s="70"/>
-      <c r="J43" s="101" t="s">
-        <v>311</v>
-      </c>
-      <c r="K43" s="89"/>
-      <c r="L43" s="89"/>
-      <c r="M43" s="90"/>
+      <c r="J43" s="92" t="s">
+        <v>309</v>
+      </c>
+      <c r="K43" s="93"/>
+      <c r="L43" s="93"/>
+      <c r="M43" s="94"/>
     </row>
     <row r="44" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="F44" s="99" t="s">
-        <v>284</v>
-      </c>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="83"/>
-      <c r="M44" s="100"/>
+        <v>311</v>
+      </c>
+      <c r="F44" s="90" t="s">
+        <v>282</v>
+      </c>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
+      <c r="M44" s="91"/>
       <c r="O44" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="F45" s="99" t="s">
-        <v>284</v>
-      </c>
-      <c r="G45" s="83"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="83"/>
-      <c r="J45" s="83"/>
-      <c r="K45" s="83"/>
-      <c r="L45" s="83"/>
-      <c r="M45" s="100"/>
+        <v>314</v>
+      </c>
+      <c r="F45" s="90" t="s">
+        <v>282</v>
+      </c>
+      <c r="G45" s="81"/>
+      <c r="H45" s="81"/>
+      <c r="I45" s="81"/>
+      <c r="J45" s="81"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="81"/>
+      <c r="M45" s="91"/>
       <c r="O45" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="F46" s="99" t="s">
-        <v>284</v>
-      </c>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="83"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
-      <c r="L46" s="83"/>
-      <c r="M46" s="100"/>
+        <v>316</v>
+      </c>
+      <c r="F46" s="90" t="s">
+        <v>282</v>
+      </c>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="81"/>
+      <c r="M46" s="91"/>
       <c r="O46" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F47" s="60"/>
       <c r="G47" s="60"/>
@@ -4230,85 +4513,85 @@
     </row>
     <row r="48" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="F48" s="99" t="s">
-        <v>284</v>
-      </c>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-      <c r="L48" s="83"/>
-      <c r="M48" s="100"/>
+        <v>320</v>
+      </c>
+      <c r="F48" s="90" t="s">
+        <v>282</v>
+      </c>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="81"/>
+      <c r="M48" s="91"/>
       <c r="O48" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="F49" s="99" t="s">
-        <v>284</v>
-      </c>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83"/>
-      <c r="J49" s="83"/>
-      <c r="K49" s="83"/>
-      <c r="L49" s="83"/>
-      <c r="M49" s="100"/>
+        <v>322</v>
+      </c>
+      <c r="F49" s="90" t="s">
+        <v>282</v>
+      </c>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
+      <c r="M49" s="91"/>
       <c r="O49" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="F50" s="99" t="s">
-        <v>284</v>
-      </c>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="83"/>
-      <c r="L50" s="83"/>
-      <c r="M50" s="100"/>
+        <v>324</v>
+      </c>
+      <c r="F50" s="90" t="s">
+        <v>282</v>
+      </c>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="81"/>
+      <c r="M50" s="91"/>
       <c r="O50" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="18" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F51" s="60"/>
       <c r="G51" s="60"/>
@@ -4321,85 +4604,85 @@
     </row>
     <row r="52" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="F52" s="96" t="s">
+        <v>327</v>
+      </c>
+      <c r="F52" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="82"/>
       <c r="O52" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="53" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="F53" s="96" t="s">
+        <v>329</v>
+      </c>
+      <c r="F53" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="82"/>
       <c r="O53" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="54" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="F54" s="96" t="s">
+        <v>331</v>
+      </c>
+      <c r="F54" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="83"/>
-      <c r="J54" s="83"/>
-      <c r="K54" s="83"/>
-      <c r="L54" s="83"/>
-      <c r="M54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="82"/>
       <c r="O54" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="55" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F55" s="60"/>
       <c r="G55" s="60"/>
@@ -4412,85 +4695,85 @@
     </row>
     <row r="56" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="F56" s="96" t="s">
+        <v>334</v>
+      </c>
+      <c r="F56" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="83"/>
-      <c r="J56" s="83"/>
-      <c r="K56" s="83"/>
-      <c r="L56" s="83"/>
-      <c r="M56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
+      <c r="L56" s="81"/>
+      <c r="M56" s="82"/>
       <c r="O56" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="57" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="F57" s="96" t="s">
+        <v>336</v>
+      </c>
+      <c r="F57" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="83"/>
-      <c r="J57" s="83"/>
-      <c r="K57" s="83"/>
-      <c r="L57" s="83"/>
-      <c r="M57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
+      <c r="M57" s="82"/>
       <c r="O57" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="58" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="F58" s="96" t="s">
+        <v>338</v>
+      </c>
+      <c r="F58" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="83"/>
-      <c r="J58" s="83"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="81"/>
+      <c r="I58" s="81"/>
+      <c r="J58" s="81"/>
+      <c r="K58" s="81"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="82"/>
       <c r="O58" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="59" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C59" s="19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>3</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F59" s="60"/>
       <c r="G59" s="60"/>
@@ -4503,13 +4786,13 @@
     </row>
     <row r="60" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C60" s="18" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F60" s="60"/>
       <c r="G60" s="60"/>
@@ -4530,6 +4813,10 @@
     <mergeCell ref="F39:M39"/>
     <mergeCell ref="F49:M49"/>
     <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F53:M53"/>
     <mergeCell ref="F12:M12"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J17:M17"/>
@@ -4546,18 +4833,14 @@
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F54:M54"/>
     <mergeCell ref="F16:M16"/>
     <mergeCell ref="J21:M21"/>
     <mergeCell ref="J33:M33"/>
     <mergeCell ref="F40:M40"/>
     <mergeCell ref="F45:M45"/>
-    <mergeCell ref="F50:M50"/>
     <mergeCell ref="J41:M41"/>
-    <mergeCell ref="F46:M46"/>
     <mergeCell ref="I34:M34"/>
     <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F53:M53"/>
     <mergeCell ref="F44:M44"/>
     <mergeCell ref="J31:M31"/>
     <mergeCell ref="J43:M43"/>
@@ -4579,10 +4862,10 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
@@ -4627,49 +4910,49 @@
     </row>
     <row r="6" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F6" s="80" t="s">
-        <v>346</v>
-      </c>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="81"/>
+        <v>344</v>
+      </c>
+      <c r="F6" s="87" t="s">
+        <v>344</v>
+      </c>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="82"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F7" s="87" t="s">
         <v>347</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="F7" s="80" t="s">
-        <v>349</v>
-      </c>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="82"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4722,17 +5005,17 @@
         <v>106</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="80" t="s">
+      <c r="J19" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="82"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="18" t="s">
@@ -4749,17 +5032,17 @@
         <v>106</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="80" t="s">
+      <c r="J20" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="83"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="82"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -4769,18 +5052,18 @@
         <v>19</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="80" t="s">
-        <v>352</v>
-      </c>
-      <c r="G21" s="81"/>
-      <c r="H21" s="80" t="s">
+      <c r="F21" s="87" t="s">
+        <v>350</v>
+      </c>
+      <c r="G21" s="82"/>
+      <c r="H21" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="81"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="82"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -4790,22 +5073,22 @@
         <v>19</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="80" t="s">
-        <v>352</v>
-      </c>
-      <c r="G22" s="81"/>
+      <c r="F22" s="87" t="s">
+        <v>350</v>
+      </c>
+      <c r="G22" s="82"/>
       <c r="H22" s="17"/>
       <c r="I22" s="10" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="K22" s="80" t="s">
+        <v>352</v>
+      </c>
+      <c r="K22" s="87" t="s">
         <v>133</v>
       </c>
-      <c r="L22" s="83"/>
-      <c r="M22" s="81"/>
+      <c r="L22" s="81"/>
+      <c r="M22" s="82"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -4815,18 +5098,18 @@
         <v>19</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="80" t="s">
+      <c r="F23" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="80" t="s">
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="82"/>
+      <c r="J23" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="81"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="82"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -4836,18 +5119,18 @@
         <v>19</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="80" t="s">
+      <c r="F24" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="80" t="s">
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="81"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="81"/>
+      <c r="M24" s="82"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -4857,18 +5140,18 @@
         <v>19</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="80" t="s">
+      <c r="F25" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="80" t="s">
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="82"/>
+      <c r="J25" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="83"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="81"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="81"/>
+      <c r="M25" s="82"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -4878,25 +5161,25 @@
         <v>19</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="80" t="s">
+      <c r="F26" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="80" t="s">
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="81"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="81"/>
+      <c r="M26" s="82"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="18" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="7"/>
@@ -4941,18 +5224,18 @@
         <v>19</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="F29" s="80" t="s">
+        <v>354</v>
+      </c>
+      <c r="F29" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
+      <c r="M29" s="82"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -4962,16 +5245,16 @@
         <v>19</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="80" t="s">
+      <c r="F30" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="81"/>
+      <c r="M30" s="82"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -4981,16 +5264,16 @@
         <v>19</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="80" t="s">
+      <c r="F31" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="81"/>
+      <c r="M31" s="82"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -5000,16 +5283,16 @@
         <v>19</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="80" t="s">
+      <c r="F32" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
-      <c r="M32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="81"/>
+      <c r="M32" s="82"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -5019,16 +5302,16 @@
         <v>19</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="80" t="s">
+      <c r="F33" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
-      <c r="M33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="82"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -5038,16 +5321,16 @@
         <v>19</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="80" t="s">
+      <c r="F34" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="83"/>
-      <c r="M34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="81"/>
+      <c r="M34" s="82"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -5057,16 +5340,16 @@
         <v>19</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="80" t="s">
+      <c r="F35" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="83"/>
-      <c r="M35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="81"/>
+      <c r="L35" s="81"/>
+      <c r="M35" s="82"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="18" t="s">
@@ -5076,16 +5359,16 @@
         <v>19</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="80" t="s">
+      <c r="F36" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
-      <c r="M36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="81"/>
+      <c r="L36" s="81"/>
+      <c r="M36" s="82"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -5095,16 +5378,16 @@
         <v>19</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="80" t="s">
+      <c r="F37" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="81"/>
+      <c r="L37" s="81"/>
+      <c r="M37" s="82"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -5114,23 +5397,23 @@
         <v>19</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="80" t="s">
+      <c r="F38" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
+      <c r="M38" s="82"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="7"/>
@@ -5144,7 +5427,7 @@
     </row>
     <row r="40" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>19</v>
@@ -5153,23 +5436,23 @@
       <c r="F40" s="7"/>
       <c r="G40" s="9"/>
       <c r="H40" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J40" s="80" t="s">
+        <v>357</v>
+      </c>
+      <c r="J40" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="K40" s="83"/>
-      <c r="L40" s="81"/>
+      <c r="K40" s="81"/>
+      <c r="L40" s="82"/>
       <c r="M40" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="41" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>19</v>
@@ -5178,23 +5461,23 @@
       <c r="F41" s="7"/>
       <c r="G41" s="9"/>
       <c r="H41" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J41" s="80" t="s">
+        <v>357</v>
+      </c>
+      <c r="J41" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="K41" s="83"/>
-      <c r="L41" s="81"/>
+      <c r="K41" s="81"/>
+      <c r="L41" s="82"/>
       <c r="M41" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="42" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>19</v>
@@ -5203,23 +5486,23 @@
       <c r="F42" s="7"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J42" s="80" t="s">
+        <v>357</v>
+      </c>
+      <c r="J42" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="K42" s="83"/>
-      <c r="L42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="82"/>
       <c r="M42" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="43" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>19</v>
@@ -5228,23 +5511,23 @@
       <c r="F43" s="7"/>
       <c r="G43" s="9"/>
       <c r="H43" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J43" s="80" t="s">
+        <v>357</v>
+      </c>
+      <c r="J43" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="K43" s="83"/>
-      <c r="L43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="82"/>
       <c r="M43" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="44" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>19</v>
@@ -5253,23 +5536,23 @@
       <c r="F44" s="7"/>
       <c r="G44" s="9"/>
       <c r="H44" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J44" s="80" t="s">
+        <v>357</v>
+      </c>
+      <c r="J44" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="K44" s="83"/>
-      <c r="L44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="82"/>
       <c r="M44" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="45" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>19</v>
@@ -5278,23 +5561,23 @@
       <c r="F45" s="7"/>
       <c r="G45" s="9"/>
       <c r="H45" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J45" s="80" t="s">
+        <v>357</v>
+      </c>
+      <c r="J45" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="K45" s="83"/>
-      <c r="L45" s="81"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="82"/>
       <c r="M45" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="46" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>19</v>
@@ -5303,23 +5586,23 @@
       <c r="F46" s="7"/>
       <c r="G46" s="9"/>
       <c r="H46" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J46" s="80" t="s">
+        <v>357</v>
+      </c>
+      <c r="J46" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="K46" s="83"/>
-      <c r="L46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="82"/>
       <c r="M46" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="47" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>19</v>
@@ -5328,23 +5611,23 @@
       <c r="F47" s="7"/>
       <c r="G47" s="9"/>
       <c r="H47" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J47" s="80" t="s">
+        <v>357</v>
+      </c>
+      <c r="J47" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="K47" s="83"/>
-      <c r="L47" s="81"/>
+      <c r="K47" s="81"/>
+      <c r="L47" s="82"/>
       <c r="M47" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="48" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>19</v>
@@ -5353,26 +5636,26 @@
       <c r="F48" s="7"/>
       <c r="G48" s="9"/>
       <c r="H48" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J48" s="80" t="s">
+        <v>357</v>
+      </c>
+      <c r="J48" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="K48" s="83"/>
-      <c r="L48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="82"/>
       <c r="M48" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="49" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="7"/>
@@ -5386,199 +5669,199 @@
     </row>
     <row r="50" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="82"/>
+      <c r="J50" s="87" t="s">
         <v>361</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="80" t="s">
-        <v>362</v>
-      </c>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="K50" s="83"/>
-      <c r="L50" s="83"/>
-      <c r="M50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="81"/>
+      <c r="M50" s="82"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E51" s="11"/>
-      <c r="F51" s="80" t="s">
-        <v>362</v>
-      </c>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="K51" s="83"/>
-      <c r="L51" s="83"/>
-      <c r="M51" s="81"/>
+      <c r="F51" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="82"/>
+      <c r="J51" s="87" t="s">
+        <v>361</v>
+      </c>
+      <c r="K51" s="81"/>
+      <c r="L51" s="81"/>
+      <c r="M51" s="82"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="80" t="s">
-        <v>362</v>
-      </c>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="81"/>
-      <c r="J52" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="81"/>
+      <c r="F52" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="82"/>
+      <c r="J52" s="87" t="s">
+        <v>361</v>
+      </c>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="82"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="80" t="s">
-        <v>362</v>
-      </c>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="81"/>
+      <c r="F53" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="82"/>
+      <c r="J53" s="87" t="s">
+        <v>361</v>
+      </c>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="82"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="80" t="s">
-        <v>362</v>
-      </c>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="K54" s="83"/>
-      <c r="L54" s="83"/>
-      <c r="M54" s="81"/>
+      <c r="F54" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="82"/>
+      <c r="J54" s="87" t="s">
+        <v>361</v>
+      </c>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="82"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="80" t="s">
-        <v>362</v>
-      </c>
-      <c r="G55" s="83"/>
-      <c r="H55" s="83"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="K55" s="83"/>
-      <c r="L55" s="83"/>
-      <c r="M55" s="81"/>
+      <c r="F55" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="82"/>
+      <c r="J55" s="87" t="s">
+        <v>361</v>
+      </c>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
+      <c r="M55" s="82"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="80" t="s">
-        <v>362</v>
-      </c>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="K56" s="83"/>
-      <c r="L56" s="83"/>
-      <c r="M56" s="81"/>
+      <c r="F56" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="82"/>
+      <c r="J56" s="87" t="s">
+        <v>361</v>
+      </c>
+      <c r="K56" s="81"/>
+      <c r="L56" s="81"/>
+      <c r="M56" s="82"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="80" t="s">
-        <v>362</v>
-      </c>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="K57" s="83"/>
-      <c r="L57" s="83"/>
-      <c r="M57" s="81"/>
+      <c r="F57" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="82"/>
+      <c r="J57" s="87" t="s">
+        <v>361</v>
+      </c>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
+      <c r="M57" s="82"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="80" t="s">
-        <v>362</v>
-      </c>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="81"/>
-      <c r="J58" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="K58" s="83"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="81"/>
+      <c r="F58" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="G58" s="81"/>
+      <c r="H58" s="81"/>
+      <c r="I58" s="82"/>
+      <c r="J58" s="87" t="s">
+        <v>361</v>
+      </c>
+      <c r="K58" s="81"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="82"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="18" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="7"/>
@@ -5592,13 +5875,13 @@
     </row>
     <row r="60" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="18" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="8"/>
@@ -5606,20 +5889,20 @@
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="96" t="s">
-        <v>375</v>
-      </c>
-      <c r="M60" s="81"/>
+      <c r="L60" s="85" t="s">
+        <v>373</v>
+      </c>
+      <c r="M60" s="82"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="18" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="8"/>
@@ -5627,20 +5910,20 @@
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
       <c r="K61" s="9"/>
-      <c r="L61" s="84" t="s">
-        <v>375</v>
-      </c>
-      <c r="M61" s="81"/>
+      <c r="L61" s="88" t="s">
+        <v>373</v>
+      </c>
+      <c r="M61" s="82"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="18" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="8"/>
@@ -5648,20 +5931,20 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="9"/>
-      <c r="L62" s="84" t="s">
-        <v>375</v>
-      </c>
-      <c r="M62" s="81"/>
+      <c r="L62" s="88" t="s">
+        <v>373</v>
+      </c>
+      <c r="M62" s="82"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="18" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="8"/>
@@ -5669,20 +5952,20 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="9"/>
-      <c r="L63" s="84" t="s">
-        <v>375</v>
-      </c>
-      <c r="M63" s="81"/>
+      <c r="L63" s="88" t="s">
+        <v>373</v>
+      </c>
+      <c r="M63" s="82"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="18" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="8"/>
@@ -5690,20 +5973,20 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="9"/>
-      <c r="L64" s="84" t="s">
-        <v>375</v>
-      </c>
-      <c r="M64" s="81"/>
+      <c r="L64" s="88" t="s">
+        <v>373</v>
+      </c>
+      <c r="M64" s="82"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="18" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E65" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="8"/>
@@ -5711,20 +5994,20 @@
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="9"/>
-      <c r="L65" s="84" t="s">
-        <v>375</v>
-      </c>
-      <c r="M65" s="81"/>
+      <c r="L65" s="88" t="s">
+        <v>373</v>
+      </c>
+      <c r="M65" s="82"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="18" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="8"/>
@@ -5732,20 +6015,20 @@
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
       <c r="K66" s="9"/>
-      <c r="L66" s="84" t="s">
-        <v>375</v>
-      </c>
-      <c r="M66" s="81"/>
+      <c r="L66" s="88" t="s">
+        <v>373</v>
+      </c>
+      <c r="M66" s="82"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="8"/>
@@ -5753,20 +6036,20 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="9"/>
-      <c r="L67" s="84" t="s">
-        <v>375</v>
-      </c>
-      <c r="M67" s="81"/>
+      <c r="L67" s="88" t="s">
+        <v>373</v>
+      </c>
+      <c r="M67" s="82"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="18" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="8"/>
@@ -5774,17 +6057,17 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="9"/>
-      <c r="L68" s="84" t="s">
-        <v>375</v>
-      </c>
-      <c r="M68" s="81"/>
+      <c r="L68" s="88" t="s">
+        <v>373</v>
+      </c>
+      <c r="M68" s="82"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="7"/>
@@ -5798,226 +6081,226 @@
     </row>
     <row r="70" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="18" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="F70" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F70" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G70" s="83"/>
-      <c r="H70" s="83"/>
-      <c r="I70" s="83"/>
-      <c r="J70" s="83"/>
-      <c r="K70" s="83"/>
-      <c r="L70" s="83"/>
-      <c r="M70" s="81"/>
+      <c r="G70" s="81"/>
+      <c r="H70" s="81"/>
+      <c r="I70" s="81"/>
+      <c r="J70" s="81"/>
+      <c r="K70" s="81"/>
+      <c r="L70" s="81"/>
+      <c r="M70" s="82"/>
       <c r="O70" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="71" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="18" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="F71" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F71" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G71" s="83"/>
-      <c r="H71" s="83"/>
-      <c r="I71" s="83"/>
-      <c r="J71" s="83"/>
-      <c r="K71" s="83"/>
-      <c r="L71" s="83"/>
-      <c r="M71" s="81"/>
+      <c r="G71" s="81"/>
+      <c r="H71" s="81"/>
+      <c r="I71" s="81"/>
+      <c r="J71" s="81"/>
+      <c r="K71" s="81"/>
+      <c r="L71" s="81"/>
+      <c r="M71" s="82"/>
       <c r="O71" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="72" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C72" s="18" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="F72" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F72" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G72" s="83"/>
-      <c r="H72" s="83"/>
-      <c r="I72" s="83"/>
-      <c r="J72" s="83"/>
-      <c r="K72" s="83"/>
-      <c r="L72" s="83"/>
-      <c r="M72" s="81"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="81"/>
+      <c r="I72" s="81"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="81"/>
+      <c r="L72" s="81"/>
+      <c r="M72" s="82"/>
       <c r="O72" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="73" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C73" s="18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="F73" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F73" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="83"/>
-      <c r="H73" s="83"/>
-      <c r="I73" s="83"/>
-      <c r="J73" s="83"/>
-      <c r="K73" s="83"/>
-      <c r="L73" s="83"/>
-      <c r="M73" s="81"/>
+      <c r="G73" s="81"/>
+      <c r="H73" s="81"/>
+      <c r="I73" s="81"/>
+      <c r="J73" s="81"/>
+      <c r="K73" s="81"/>
+      <c r="L73" s="81"/>
+      <c r="M73" s="82"/>
       <c r="O73" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="74" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C74" s="18" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="F74" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F74" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G74" s="83"/>
-      <c r="H74" s="83"/>
-      <c r="I74" s="83"/>
-      <c r="J74" s="83"/>
-      <c r="K74" s="83"/>
-      <c r="L74" s="83"/>
-      <c r="M74" s="81"/>
+      <c r="G74" s="81"/>
+      <c r="H74" s="81"/>
+      <c r="I74" s="81"/>
+      <c r="J74" s="81"/>
+      <c r="K74" s="81"/>
+      <c r="L74" s="81"/>
+      <c r="M74" s="82"/>
       <c r="O74" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="75" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C75" s="18" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="F75" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F75" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G75" s="83"/>
-      <c r="H75" s="83"/>
-      <c r="I75" s="83"/>
-      <c r="J75" s="83"/>
-      <c r="K75" s="83"/>
-      <c r="L75" s="83"/>
-      <c r="M75" s="81"/>
+      <c r="G75" s="81"/>
+      <c r="H75" s="81"/>
+      <c r="I75" s="81"/>
+      <c r="J75" s="81"/>
+      <c r="K75" s="81"/>
+      <c r="L75" s="81"/>
+      <c r="M75" s="82"/>
       <c r="O75" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="76" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C76" s="18" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="F76" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F76" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G76" s="83"/>
-      <c r="H76" s="83"/>
-      <c r="I76" s="83"/>
-      <c r="J76" s="83"/>
-      <c r="K76" s="83"/>
-      <c r="L76" s="83"/>
-      <c r="M76" s="81"/>
+      <c r="G76" s="81"/>
+      <c r="H76" s="81"/>
+      <c r="I76" s="81"/>
+      <c r="J76" s="81"/>
+      <c r="K76" s="81"/>
+      <c r="L76" s="81"/>
+      <c r="M76" s="82"/>
       <c r="O76" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="77" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C77" s="18" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="F77" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F77" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G77" s="83"/>
-      <c r="H77" s="83"/>
-      <c r="I77" s="83"/>
-      <c r="J77" s="83"/>
-      <c r="K77" s="83"/>
-      <c r="L77" s="83"/>
-      <c r="M77" s="81"/>
+      <c r="G77" s="81"/>
+      <c r="H77" s="81"/>
+      <c r="I77" s="81"/>
+      <c r="J77" s="81"/>
+      <c r="K77" s="81"/>
+      <c r="L77" s="81"/>
+      <c r="M77" s="82"/>
       <c r="O77" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="78" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C78" s="18" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="F78" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F78" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="G78" s="83"/>
-      <c r="H78" s="83"/>
-      <c r="I78" s="83"/>
-      <c r="J78" s="83"/>
-      <c r="K78" s="83"/>
-      <c r="L78" s="83"/>
-      <c r="M78" s="81"/>
+      <c r="G78" s="81"/>
+      <c r="H78" s="81"/>
+      <c r="I78" s="81"/>
+      <c r="J78" s="81"/>
+      <c r="K78" s="81"/>
+      <c r="L78" s="81"/>
+      <c r="M78" s="82"/>
       <c r="O78" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="79" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C79" s="18" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="7"/>
@@ -6031,48 +6314,48 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="F77:M77"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J55:M55"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="L65:M65"/>
     <mergeCell ref="J54:M54"/>
     <mergeCell ref="J40:L40"/>
     <mergeCell ref="F23:I23"/>
     <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F71:M71"/>
     <mergeCell ref="L60:M60"/>
     <mergeCell ref="J44:L44"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="F26:I26"/>
     <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F76:M76"/>
-    <mergeCell ref="J43:L43"/>
     <mergeCell ref="F25:I25"/>
     <mergeCell ref="F70:M70"/>
     <mergeCell ref="J57:M57"/>
     <mergeCell ref="F35:M35"/>
     <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F75:M75"/>
-    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J55:M55"/>
     <mergeCell ref="J46:L46"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="L61:M61"/>
     <mergeCell ref="F72:M72"/>
     <mergeCell ref="F55:I55"/>
-    <mergeCell ref="F38:M38"/>
     <mergeCell ref="L63:M63"/>
     <mergeCell ref="J52:M52"/>
     <mergeCell ref="F57:I57"/>
     <mergeCell ref="L68:M68"/>
-    <mergeCell ref="J41:L41"/>
     <mergeCell ref="F53:I53"/>
     <mergeCell ref="L62:M62"/>
     <mergeCell ref="F54:I54"/>
     <mergeCell ref="J47:L47"/>
     <mergeCell ref="J48:L48"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="F71:M71"/>
     <mergeCell ref="F6:M6"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="F7:M7"/>
@@ -6087,21 +6370,21 @@
     <mergeCell ref="J24:M24"/>
     <mergeCell ref="F31:M31"/>
     <mergeCell ref="H21:M21"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="K22:M22"/>
     <mergeCell ref="F73:M73"/>
     <mergeCell ref="F56:I56"/>
     <mergeCell ref="F78:M78"/>
     <mergeCell ref="L67:M67"/>
     <mergeCell ref="J56:M56"/>
-    <mergeCell ref="F29:M29"/>
     <mergeCell ref="F58:I58"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J50:M50"/>
     <mergeCell ref="L66:M66"/>
-    <mergeCell ref="F34:M34"/>
     <mergeCell ref="F74:M74"/>
     <mergeCell ref="J58:M58"/>
+    <mergeCell ref="F75:M75"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="F77:M77"/>
+    <mergeCell ref="F76:M76"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6210,14 +6493,14 @@
       <c r="E11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="82"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="81"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="82"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="18" t="s">
@@ -6229,16 +6512,16 @@
       <c r="E12" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="86" t="s">
+      <c r="F12" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="82"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -6250,16 +6533,16 @@
       <c r="E13" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="86" t="s">
+      <c r="F13" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="82"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -6271,16 +6554,16 @@
       <c r="E14" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="86" t="s">
+      <c r="F14" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="82"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -6325,16 +6608,16 @@
       <c r="E16" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="87" t="s">
+      <c r="F16" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="82"/>
       <c r="N16" s="56" t="s">
         <v>38</v>
       </c>
@@ -6349,16 +6632,16 @@
       <c r="E17" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="87" t="s">
+      <c r="F17" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="81"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="82"/>
       <c r="N17" s="56" t="s">
         <v>38</v>
       </c>
@@ -6386,8 +6669,8 @@
       <c r="J18" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="82"/>
-      <c r="L18" s="81"/>
+      <c r="K18" s="95"/>
+      <c r="L18" s="82"/>
       <c r="M18" s="54" t="s">
         <v>47</v>
       </c>
@@ -6409,8 +6692,8 @@
       <c r="G19" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="82"/>
-      <c r="I19" s="81"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="82"/>
       <c r="J19" s="55" t="s">
         <v>52</v>
       </c>
@@ -6432,16 +6715,16 @@
         <v>19</v>
       </c>
       <c r="E20" s="42"/>
-      <c r="F20" s="85" t="s">
+      <c r="F20" s="96" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="82"/>
       <c r="N20" t="s">
         <v>58</v>
       </c>
@@ -6454,16 +6737,16 @@
         <v>19</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="85" t="s">
+      <c r="F21" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="81"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="82"/>
       <c r="N21" t="s">
         <v>61</v>
       </c>
@@ -6476,16 +6759,16 @@
         <v>19</v>
       </c>
       <c r="E22" s="41"/>
-      <c r="F22" s="85" t="s">
+      <c r="F22" s="96" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="83"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="83"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="81"/>
+      <c r="M22" s="82"/>
       <c r="N22" t="s">
         <v>64</v>
       </c>
@@ -6498,16 +6781,16 @@
         <v>19</v>
       </c>
       <c r="E23" s="41"/>
-      <c r="F23" s="85" t="s">
+      <c r="F23" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="82"/>
       <c r="N23" t="s">
         <v>67</v>
       </c>
@@ -6522,16 +6805,16 @@
       <c r="E24" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="87" t="s">
+      <c r="F24" s="97" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="81"/>
+      <c r="M24" s="82"/>
       <c r="N24" s="58" t="s">
         <v>38</v>
       </c>
@@ -6546,16 +6829,16 @@
       <c r="E25" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="82"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="81"/>
-      <c r="K25" s="87" t="s">
+      <c r="F25" s="95"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="82"/>
+      <c r="K25" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="L25" s="83"/>
-      <c r="M25" s="81"/>
+      <c r="L25" s="81"/>
+      <c r="M25" s="82"/>
       <c r="N25" s="56" t="s">
         <v>38</v>
       </c>
@@ -6568,16 +6851,16 @@
         <v>3</v>
       </c>
       <c r="E26" s="41"/>
-      <c r="F26" s="85" t="s">
+      <c r="F26" s="96" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="81"/>
+      <c r="M26" s="82"/>
       <c r="N26" t="s">
         <v>74</v>
       </c>
@@ -6590,16 +6873,16 @@
         <v>19</v>
       </c>
       <c r="E27" s="41"/>
-      <c r="F27" s="85" t="s">
+      <c r="F27" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
+      <c r="M27" s="82"/>
       <c r="N27" t="s">
         <v>77</v>
       </c>
@@ -6612,16 +6895,16 @@
         <v>19</v>
       </c>
       <c r="E28" s="41"/>
-      <c r="F28" s="85" t="s">
+      <c r="F28" s="96" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
+      <c r="M28" s="82"/>
       <c r="N28" t="s">
         <v>80</v>
       </c>
@@ -6634,16 +6917,16 @@
         <v>19</v>
       </c>
       <c r="E29" s="41"/>
-      <c r="F29" s="85" t="s">
+      <c r="F29" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
+      <c r="M29" s="82"/>
       <c r="N29" t="s">
         <v>83</v>
       </c>
@@ -6658,14 +6941,14 @@
       <c r="E30" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="82"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="81"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="81"/>
+      <c r="M30" s="82"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="59" t="s">
@@ -6677,14 +6960,14 @@
       <c r="E31" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="82"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="81"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="81"/>
+      <c r="M31" s="82"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="59" t="s">
@@ -6696,16 +6979,16 @@
       <c r="E32" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="87" t="s">
+      <c r="F32" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
-      <c r="M32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="81"/>
+      <c r="M32" s="82"/>
       <c r="N32" s="56" t="s">
         <v>38</v>
       </c>
@@ -6720,16 +7003,16 @@
       <c r="E33" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="87" t="s">
+      <c r="F33" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="81"/>
-      <c r="H33" s="82"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
-      <c r="M33" s="81"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="82"/>
       <c r="N33" s="56" t="s">
         <v>38</v>
       </c>
@@ -6744,16 +7027,16 @@
       <c r="E34" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="82"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="87" t="s">
+      <c r="F34" s="95"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="L34" s="83"/>
-      <c r="M34" s="81"/>
+      <c r="L34" s="81"/>
+      <c r="M34" s="82"/>
       <c r="N34" s="56" t="s">
         <v>38</v>
       </c>
@@ -6768,16 +7051,16 @@
       <c r="E35" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="82"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="87" t="s">
+      <c r="F35" s="95"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="82"/>
+      <c r="J35" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="K35" s="83"/>
-      <c r="L35" s="83"/>
-      <c r="M35" s="81"/>
+      <c r="K35" s="81"/>
+      <c r="L35" s="81"/>
+      <c r="M35" s="82"/>
       <c r="N35" s="56" t="s">
         <v>38</v>
       </c>
@@ -6792,16 +7075,16 @@
       <c r="E36" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="82"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="87" t="s">
+      <c r="F36" s="95"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="97" t="s">
         <v>95</v>
       </c>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
-      <c r="M36" s="81"/>
+      <c r="K36" s="81"/>
+      <c r="L36" s="81"/>
+      <c r="M36" s="82"/>
       <c r="N36" s="56" t="s">
         <v>38</v>
       </c>
@@ -6816,16 +7099,16 @@
       <c r="E37" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="87" t="s">
+      <c r="F37" s="97" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="81"/>
+      <c r="L37" s="81"/>
+      <c r="M37" s="82"/>
       <c r="N37" s="56" t="s">
         <v>38</v>
       </c>
@@ -6840,14 +7123,14 @@
       <c r="E38" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="82"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="81"/>
+      <c r="F38" s="95"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
+      <c r="M38" s="82"/>
       <c r="N38" t="s">
         <v>99</v>
       </c>
@@ -6862,14 +7145,14 @@
       <c r="E39" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="82"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="83"/>
-      <c r="K39" s="83"/>
-      <c r="L39" s="83"/>
-      <c r="M39" s="81"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="81"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="81"/>
+      <c r="M39" s="82"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="59" t="s">
@@ -6881,14 +7164,14 @@
       <c r="E40" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F40" s="82"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="83"/>
-      <c r="M40" s="81"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="81"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="81"/>
+      <c r="L40" s="81"/>
+      <c r="M40" s="82"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="59" t="s">
@@ -6900,14 +7183,14 @@
       <c r="E41" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F41" s="82"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="81"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="81"/>
+      <c r="J41" s="81"/>
+      <c r="K41" s="81"/>
+      <c r="L41" s="81"/>
+      <c r="M41" s="82"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="59" t="s">
@@ -6919,14 +7202,14 @@
       <c r="E42" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F42" s="82"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="83"/>
-      <c r="M42" s="81"/>
+      <c r="F42" s="95"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="81"/>
+      <c r="M42" s="82"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="19" t="s">
@@ -6948,12 +7231,12 @@
       <c r="I43" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="86" t="s">
+      <c r="J43" s="83" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="83"/>
-      <c r="L43" s="83"/>
-      <c r="M43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="81"/>
+      <c r="M43" s="82"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
@@ -6963,18 +7246,18 @@
         <v>19</v>
       </c>
       <c r="E44" s="42"/>
-      <c r="F44" s="86" t="s">
+      <c r="F44" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="G44" s="81"/>
-      <c r="H44" s="86" t="s">
+      <c r="G44" s="82"/>
+      <c r="H44" s="83" t="s">
         <v>112</v>
       </c>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="83"/>
-      <c r="M44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
+      <c r="M44" s="82"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
@@ -6984,18 +7267,18 @@
         <v>19</v>
       </c>
       <c r="E45" s="42"/>
-      <c r="F45" s="92" t="s">
+      <c r="F45" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="G45" s="93"/>
-      <c r="H45" s="93"/>
-      <c r="I45" s="94"/>
-      <c r="J45" s="86" t="s">
+      <c r="G45" s="100"/>
+      <c r="H45" s="100"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="K45" s="83"/>
-      <c r="L45" s="83"/>
-      <c r="M45" s="81"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="81"/>
+      <c r="M45" s="82"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
@@ -7005,18 +7288,18 @@
         <v>19</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="86" t="s">
+      <c r="F46" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="81"/>
-      <c r="J46" s="88" t="s">
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="82"/>
+      <c r="J46" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="K46" s="89"/>
-      <c r="L46" s="89"/>
-      <c r="M46" s="90"/>
+      <c r="K46" s="93"/>
+      <c r="L46" s="93"/>
+      <c r="M46" s="94"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18" t="s">
@@ -7026,16 +7309,16 @@
         <v>19</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="80" t="s">
+      <c r="F47" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G47" s="83"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="83"/>
-      <c r="J47" s="83"/>
-      <c r="K47" s="83"/>
-      <c r="L47" s="83"/>
-      <c r="M47" s="81"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="81"/>
+      <c r="L47" s="81"/>
+      <c r="M47" s="82"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
@@ -7045,20 +7328,20 @@
         <v>19</v>
       </c>
       <c r="E48" s="5"/>
-      <c r="F48" s="91"/>
-      <c r="G48" s="81"/>
+      <c r="F48" s="80"/>
+      <c r="G48" s="82"/>
       <c r="H48" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I48" s="80" t="s">
+      <c r="I48" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="J48" s="83"/>
-      <c r="K48" s="81"/>
-      <c r="L48" s="80" t="s">
+      <c r="J48" s="81"/>
+      <c r="K48" s="82"/>
+      <c r="L48" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="M48" s="81"/>
+      <c r="M48" s="82"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
@@ -7101,15 +7384,15 @@
         <v>19</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="91"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="80" t="s">
+      <c r="F50" s="80"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="82"/>
+      <c r="J50" s="87" t="s">
         <v>133</v>
       </c>
-      <c r="K50" s="83"/>
-      <c r="L50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="82"/>
       <c r="M50" s="12" t="s">
         <v>134</v>
       </c>
@@ -7124,16 +7407,16 @@
       <c r="E51" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F51" s="82"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
-      <c r="J51" s="83"/>
-      <c r="K51" s="81"/>
-      <c r="L51" s="84" t="s">
+      <c r="F51" s="95"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="82"/>
+      <c r="L51" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="M51" s="81"/>
+      <c r="M51" s="82"/>
     </row>
     <row r="52" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -7145,16 +7428,16 @@
       <c r="E52" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F52" s="84" t="s">
+      <c r="F52" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="82"/>
       <c r="N52" t="s">
         <v>141</v>
       </c>
@@ -7169,16 +7452,16 @@
       <c r="E53" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F53" s="84" t="s">
+      <c r="F53" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="82"/>
       <c r="N53" t="s">
         <v>141</v>
       </c>
@@ -7193,16 +7476,16 @@
       <c r="E54" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F54" s="84" t="s">
+      <c r="F54" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="83"/>
-      <c r="J54" s="83"/>
-      <c r="K54" s="83"/>
-      <c r="L54" s="83"/>
-      <c r="M54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="82"/>
       <c r="N54" t="s">
         <v>141</v>
       </c>
@@ -7217,16 +7500,16 @@
       <c r="E55" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="84" t="s">
+      <c r="F55" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G55" s="83"/>
-      <c r="H55" s="83"/>
-      <c r="I55" s="83"/>
-      <c r="J55" s="83"/>
-      <c r="K55" s="83"/>
-      <c r="L55" s="83"/>
-      <c r="M55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
+      <c r="M55" s="82"/>
       <c r="N55" t="s">
         <v>141</v>
       </c>
@@ -7241,16 +7524,16 @@
       <c r="E56" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="84" t="s">
+      <c r="F56" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="83"/>
-      <c r="J56" s="83"/>
-      <c r="K56" s="83"/>
-      <c r="L56" s="83"/>
-      <c r="M56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
+      <c r="L56" s="81"/>
+      <c r="M56" s="82"/>
       <c r="N56" t="s">
         <v>141</v>
       </c>
@@ -7265,16 +7548,16 @@
       <c r="E57" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F57" s="84" t="s">
+      <c r="F57" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="83"/>
-      <c r="J57" s="83"/>
-      <c r="K57" s="83"/>
-      <c r="L57" s="83"/>
-      <c r="M57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
+      <c r="M57" s="82"/>
       <c r="N57" t="s">
         <v>141</v>
       </c>
@@ -7289,16 +7572,16 @@
       <c r="E58" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F58" s="84" t="s">
+      <c r="F58" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="83"/>
-      <c r="J58" s="83"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="81"/>
+      <c r="I58" s="81"/>
+      <c r="J58" s="81"/>
+      <c r="K58" s="81"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="82"/>
       <c r="N58" t="s">
         <v>141</v>
       </c>
@@ -7313,16 +7596,16 @@
       <c r="E59" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="F59" s="84" t="s">
+      <c r="F59" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G59" s="83"/>
-      <c r="H59" s="83"/>
-      <c r="I59" s="83"/>
-      <c r="J59" s="83"/>
-      <c r="K59" s="83"/>
-      <c r="L59" s="83"/>
-      <c r="M59" s="81"/>
+      <c r="G59" s="81"/>
+      <c r="H59" s="81"/>
+      <c r="I59" s="81"/>
+      <c r="J59" s="81"/>
+      <c r="K59" s="81"/>
+      <c r="L59" s="81"/>
+      <c r="M59" s="82"/>
       <c r="N59" t="s">
         <v>141</v>
       </c>
@@ -7337,16 +7620,16 @@
       <c r="E60" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F60" s="84" t="s">
+      <c r="F60" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G60" s="83"/>
-      <c r="H60" s="83"/>
-      <c r="I60" s="83"/>
-      <c r="J60" s="83"/>
-      <c r="K60" s="83"/>
-      <c r="L60" s="83"/>
-      <c r="M60" s="81"/>
+      <c r="G60" s="81"/>
+      <c r="H60" s="81"/>
+      <c r="I60" s="81"/>
+      <c r="J60" s="81"/>
+      <c r="K60" s="81"/>
+      <c r="L60" s="81"/>
+      <c r="M60" s="82"/>
       <c r="N60" t="s">
         <v>141</v>
       </c>
@@ -7361,16 +7644,16 @@
       <c r="E61" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="F61" s="84" t="s">
+      <c r="F61" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="G61" s="83"/>
-      <c r="H61" s="83"/>
-      <c r="I61" s="83"/>
-      <c r="J61" s="83"/>
-      <c r="K61" s="83"/>
-      <c r="L61" s="83"/>
-      <c r="M61" s="81"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="81"/>
+      <c r="I61" s="81"/>
+      <c r="J61" s="81"/>
+      <c r="K61" s="81"/>
+      <c r="L61" s="81"/>
+      <c r="M61" s="82"/>
       <c r="N61" t="s">
         <v>141</v>
       </c>
@@ -7398,8 +7681,8 @@
       <c r="J63" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="K63" s="91"/>
-      <c r="L63" s="81"/>
+      <c r="K63" s="80"/>
+      <c r="L63" s="82"/>
       <c r="M63" s="53" t="s">
         <v>166</v>
       </c>
@@ -7412,6 +7695,16 @@
     <mergeCell ref="F57:M57"/>
     <mergeCell ref="F46:I46"/>
     <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F59:M59"/>
+    <mergeCell ref="F21:M21"/>
+    <mergeCell ref="F55:M55"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F20:M20"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="F23:M23"/>
     <mergeCell ref="K63:L63"/>
     <mergeCell ref="I48:K48"/>
     <mergeCell ref="F42:M42"/>
@@ -7428,17 +7721,6 @@
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="F61:M61"/>
     <mergeCell ref="H44:M44"/>
-    <mergeCell ref="F59:M59"/>
-    <mergeCell ref="F21:M21"/>
-    <mergeCell ref="F55:M55"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F20:M20"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="F23:M23"/>
-    <mergeCell ref="F38:M38"/>
     <mergeCell ref="F22:M22"/>
     <mergeCell ref="F28:M28"/>
     <mergeCell ref="K34:M34"/>
@@ -7468,6 +7750,7 @@
     <mergeCell ref="F39:M39"/>
     <mergeCell ref="F37:M37"/>
     <mergeCell ref="J35:M35"/>
+    <mergeCell ref="F38:M38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7482,7 +7765,7 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -7498,11 +7781,160 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35961C51-4C87-43E4-A01F-C0F08E028EB7}">
+  <dimension ref="B2:W11"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="23" width="4.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:23" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="3" spans="2:23" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.15">
+      <c r="B5" s="102" t="s">
+        <v>399</v>
+      </c>
+      <c r="C5" s="103" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.15">
+      <c r="B6" s="104" t="s">
+        <v>401</v>
+      </c>
+      <c r="C6" s="105" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="106" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="107" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="108" t="s">
+        <v>407</v>
+      </c>
+      <c r="F8" s="109" t="s">
+        <v>408</v>
+      </c>
+      <c r="G8" s="109" t="s">
+        <v>409</v>
+      </c>
+      <c r="H8" s="109" t="s">
+        <v>410</v>
+      </c>
+      <c r="I8" s="109" t="s">
+        <v>411</v>
+      </c>
+      <c r="J8" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="K8" s="109" t="s">
+        <v>413</v>
+      </c>
+      <c r="L8" s="109" t="s">
+        <v>414</v>
+      </c>
+      <c r="M8" s="109" t="s">
+        <v>415</v>
+      </c>
+      <c r="N8" s="109" t="s">
+        <v>416</v>
+      </c>
+      <c r="O8" s="109" t="s">
+        <v>417</v>
+      </c>
+      <c r="P8" s="109" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q8" s="109" t="s">
+        <v>419</v>
+      </c>
+      <c r="R8" s="109" t="s">
+        <v>420</v>
+      </c>
+      <c r="S8" s="109" t="s">
+        <v>421</v>
+      </c>
+      <c r="T8" s="109" t="s">
+        <v>422</v>
+      </c>
+      <c r="U8" s="109" t="s">
+        <v>423</v>
+      </c>
+      <c r="V8" s="109" t="s">
+        <v>424</v>
+      </c>
+      <c r="W8" s="110" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="111" t="s">
+        <v>428</v>
+      </c>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="111" t="s">
+        <v>427</v>
+      </c>
+      <c r="L9" s="112"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112"/>
+      <c r="Q9" s="112"/>
+      <c r="R9" s="112"/>
+      <c r="S9" s="112"/>
+      <c r="T9" s="112"/>
+      <c r="U9" s="112"/>
+      <c r="V9" s="112"/>
+      <c r="W9" s="113"/>
+    </row>
+    <row r="11" spans="2:23" x14ac:dyDescent="0.15">
+      <c r="E11" t="s">
+        <v>407</v>
+      </c>
+      <c r="F11" t="s">
+        <v>429</v>
+      </c>
+      <c r="G11" t="s">
+        <v>426</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="K9:W9"/>
+    <mergeCell ref="E9:J9"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA28F09-917A-4058-990D-85DDA2634880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612819BE-368A-4C5B-9E81-5526FE6B424C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="466">
   <si>
     <t>OPL2 (YM3812) + ADPCM  [MSX-AUDIO(Y8950) Compatible]</t>
   </si>
@@ -1368,6 +1368,153 @@
   </si>
   <si>
     <t>:</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCC BANK2-BANK#63</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9800h-981Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9820h-983Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9840h-985Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9860h-987Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9880h-9881h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9882h-9883h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9884h-9885h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9886h-9887h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9888h-9889h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Ah</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Bh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Ch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Dh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Eh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9890h-989Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>98A0h-98BFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>98C0h-98DFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>98E0h-98FFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9900h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCC Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9901h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9902h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9903h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9904h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCC Ch.A ステレオ定位</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCC Ch.B ステレオ定位</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCC Ch.C ステレオ定位</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCC Ch.D ステレオ定位</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCC Ch.E ステレオ定位</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>説明省略</t>
+    <rPh sb="0" eb="4">
+      <t>セツメイショウリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト128</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 の時のみ利用可能、1で左端、128で中央、255で右端。デフォルト128</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1501,7 +1648,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1966,6 +2113,62 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1975,7 +2178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2214,36 +2417,72 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2258,49 +2497,41 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2874,7 +3105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:O28"/>
+  <dimension ref="A2:O55"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.75" style="79" customWidth="1"/>
@@ -2945,13 +3176,13 @@
       <c r="F4" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G4" s="80"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
-      <c r="M4" s="82"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="94"/>
       <c r="N4" s="66" t="s">
         <v>205</v>
       </c>
@@ -2972,16 +3203,16 @@
       <c r="F5" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G5" s="84" t="s">
+      <c r="G5" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="82"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="94"/>
       <c r="O5" s="49" t="s">
         <v>210</v>
       </c>
@@ -2999,16 +3230,16 @@
       <c r="F6" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G6" s="84" t="s">
+      <c r="G6" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="82"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="94"/>
       <c r="O6" s="49" t="s">
         <v>210</v>
       </c>
@@ -3026,16 +3257,16 @@
       <c r="F7" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="84" t="s">
+      <c r="G7" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="82"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="94"/>
       <c r="O7" s="49" t="s">
         <v>210</v>
       </c>
@@ -3053,16 +3284,16 @@
       <c r="F8" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G8" s="84" t="s">
+      <c r="G8" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
-      <c r="L8" s="81"/>
-      <c r="M8" s="81"/>
-      <c r="N8" s="82"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="94"/>
       <c r="O8" s="49" t="s">
         <v>210</v>
       </c>
@@ -3080,16 +3311,16 @@
       <c r="F9" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G9" s="83" t="s">
+      <c r="G9" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="81"/>
-      <c r="N9" s="82"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="93"/>
+      <c r="K9" s="93"/>
+      <c r="L9" s="93"/>
+      <c r="M9" s="93"/>
+      <c r="N9" s="94"/>
       <c r="O9" s="49" t="s">
         <v>219</v>
       </c>
@@ -3107,16 +3338,16 @@
       <c r="F10" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G10" s="83" t="s">
+      <c r="G10" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
-      <c r="N10" s="82"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="93"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="94"/>
       <c r="O10" s="49" t="s">
         <v>219</v>
       </c>
@@ -3134,16 +3365,16 @@
       <c r="F11" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G11" s="88" t="s">
+      <c r="G11" s="100" t="s">
         <v>222</v>
       </c>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="82"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="93"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="94"/>
       <c r="O11" s="50" t="s">
         <v>397</v>
       </c>
@@ -3161,16 +3392,16 @@
       <c r="F12" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="88" t="s">
+      <c r="G12" s="100" t="s">
         <v>225</v>
       </c>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="81"/>
-      <c r="N12" s="82"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="94"/>
       <c r="O12" s="50" t="s">
         <v>397</v>
       </c>
@@ -3188,16 +3419,16 @@
       <c r="F13" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G13" s="85" t="s">
+      <c r="G13" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
-      <c r="N13" s="82"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="93"/>
+      <c r="N13" s="94"/>
       <c r="O13" s="50" t="s">
         <v>397</v>
       </c>
@@ -3215,16 +3446,16 @@
       <c r="F14" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G14" s="85" t="s">
+      <c r="G14" s="96" t="s">
         <v>228</v>
       </c>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="81"/>
-      <c r="N14" s="82"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="93"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="93"/>
+      <c r="N14" s="94"/>
       <c r="O14" s="50" t="s">
         <v>397</v>
       </c>
@@ -3242,16 +3473,16 @@
       <c r="F15" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G15" s="87" t="s">
+      <c r="G15" s="98" t="s">
         <v>230</v>
       </c>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="82"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="93"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="94"/>
       <c r="O15" s="50" t="s">
         <v>397</v>
       </c>
@@ -3269,21 +3500,21 @@
       <c r="F16" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G16" s="87" t="s">
+      <c r="G16" s="98" t="s">
         <v>233</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="82"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="93"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="93"/>
+      <c r="N16" s="94"/>
       <c r="O16" s="50" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="17" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="11" t="s">
         <v>234</v>
       </c>
@@ -3296,13 +3527,13 @@
       <c r="F17" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G17" s="86"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="82"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="93"/>
+      <c r="K17" s="93"/>
+      <c r="L17" s="93"/>
+      <c r="M17" s="94"/>
       <c r="N17" s="10" t="s">
         <v>176</v>
       </c>
@@ -3310,7 +3541,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="18" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="11" t="s">
         <v>236</v>
       </c>
@@ -3323,19 +3554,19 @@
       <c r="F18" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G18" s="85"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="82"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="93"/>
+      <c r="M18" s="93"/>
+      <c r="N18" s="94"/>
       <c r="O18" s="50" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="19" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="11" t="s">
         <v>238</v>
       </c>
@@ -3348,19 +3579,19 @@
       <c r="F19" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="85"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="82"/>
+      <c r="G19" s="96"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="93"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="93"/>
+      <c r="M19" s="93"/>
+      <c r="N19" s="94"/>
       <c r="O19" s="50" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="20" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="11" t="s">
         <v>240</v>
       </c>
@@ -3373,19 +3604,19 @@
       <c r="F20" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G20" s="85"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="81"/>
-      <c r="N20" s="82"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="93"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="93"/>
+      <c r="N20" s="94"/>
       <c r="O20" s="50" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="21" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="11" t="s">
         <v>242</v>
       </c>
@@ -3410,7 +3641,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="22" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="11" t="s">
         <v>244</v>
       </c>
@@ -3431,7 +3662,7 @@
       <c r="N22" s="77"/>
       <c r="O22" s="50"/>
     </row>
-    <row r="23" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="11" t="s">
         <v>246</v>
       </c>
@@ -3452,7 +3683,7 @@
       <c r="N23" s="77"/>
       <c r="O23" s="50"/>
     </row>
-    <row r="24" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="11" t="s">
         <v>247</v>
       </c>
@@ -3473,7 +3704,7 @@
       <c r="N24" s="77"/>
       <c r="O24" s="50"/>
     </row>
-    <row r="25" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="11" t="s">
         <v>248</v>
       </c>
@@ -3498,7 +3729,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="26" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>249</v>
       </c>
@@ -3514,11 +3745,11 @@
       <c r="G26" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="H26" s="80"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="81"/>
-      <c r="L26" s="82"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="93"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="94"/>
       <c r="M26" s="32" t="s">
         <v>173</v>
       </c>
@@ -3529,7 +3760,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="27" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="63" t="s">
         <v>252</v>
       </c>
@@ -3542,21 +3773,21 @@
       <c r="F27" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="83" t="s">
+      <c r="G27" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="81"/>
-      <c r="M27" s="81"/>
-      <c r="N27" s="82"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
+      <c r="M27" s="93"/>
+      <c r="N27" s="94"/>
       <c r="O27" s="49" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="28" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="65" t="s">
         <v>253</v>
       </c>
@@ -3569,22 +3800,734 @@
       <c r="F28" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="83" t="s">
+      <c r="G28" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="81"/>
-      <c r="L28" s="81"/>
-      <c r="M28" s="81"/>
-      <c r="N28" s="82"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="93"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="93"/>
+      <c r="M28" s="93"/>
+      <c r="N28" s="94"/>
       <c r="O28" s="49" t="s">
         <v>219</v>
       </c>
     </row>
+    <row r="30" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="79" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="115" t="s">
+        <v>252</v>
+      </c>
+      <c r="D31" s="116" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="116" t="s">
+        <v>214</v>
+      </c>
+      <c r="F31" s="121" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="122" t="s">
+        <v>218</v>
+      </c>
+      <c r="H31" s="123"/>
+      <c r="I31" s="123"/>
+      <c r="J31" s="123"/>
+      <c r="K31" s="123"/>
+      <c r="L31" s="123"/>
+      <c r="M31" s="123"/>
+      <c r="N31" s="124"/>
+      <c r="O31" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="117" t="s">
+        <v>431</v>
+      </c>
+      <c r="D32" s="114" t="s">
+        <v>435</v>
+      </c>
+      <c r="E32" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H32" s="123"/>
+      <c r="I32" s="123"/>
+      <c r="J32" s="123"/>
+      <c r="K32" s="123"/>
+      <c r="L32" s="123"/>
+      <c r="M32" s="123"/>
+      <c r="N32" s="124"/>
+      <c r="O32" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="117" t="s">
+        <v>432</v>
+      </c>
+      <c r="D33" s="114" t="s">
+        <v>435</v>
+      </c>
+      <c r="E33" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H33" s="123"/>
+      <c r="I33" s="123"/>
+      <c r="J33" s="123"/>
+      <c r="K33" s="123"/>
+      <c r="L33" s="123"/>
+      <c r="M33" s="123"/>
+      <c r="N33" s="124"/>
+      <c r="O33" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="117" t="s">
+        <v>433</v>
+      </c>
+      <c r="D34" s="114" t="s">
+        <v>435</v>
+      </c>
+      <c r="E34" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H34" s="123"/>
+      <c r="I34" s="123"/>
+      <c r="J34" s="123"/>
+      <c r="K34" s="123"/>
+      <c r="L34" s="123"/>
+      <c r="M34" s="123"/>
+      <c r="N34" s="124"/>
+      <c r="O34" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="117" t="s">
+        <v>434</v>
+      </c>
+      <c r="D35" s="114" t="s">
+        <v>435</v>
+      </c>
+      <c r="E35" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H35" s="123"/>
+      <c r="I35" s="123"/>
+      <c r="J35" s="123"/>
+      <c r="K35" s="123"/>
+      <c r="L35" s="123"/>
+      <c r="M35" s="123"/>
+      <c r="N35" s="124"/>
+      <c r="O35" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="117" t="s">
+        <v>436</v>
+      </c>
+      <c r="D36" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E36" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H36" s="123"/>
+      <c r="I36" s="123"/>
+      <c r="J36" s="123"/>
+      <c r="K36" s="123"/>
+      <c r="L36" s="123"/>
+      <c r="M36" s="123"/>
+      <c r="N36" s="124"/>
+      <c r="O36" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C37" s="117" t="s">
+        <v>437</v>
+      </c>
+      <c r="D37" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E37" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H37" s="123"/>
+      <c r="I37" s="123"/>
+      <c r="J37" s="123"/>
+      <c r="K37" s="123"/>
+      <c r="L37" s="123"/>
+      <c r="M37" s="123"/>
+      <c r="N37" s="124"/>
+      <c r="O37" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="117" t="s">
+        <v>438</v>
+      </c>
+      <c r="D38" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E38" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G38" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H38" s="123"/>
+      <c r="I38" s="123"/>
+      <c r="J38" s="123"/>
+      <c r="K38" s="123"/>
+      <c r="L38" s="123"/>
+      <c r="M38" s="123"/>
+      <c r="N38" s="124"/>
+      <c r="O38" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C39" s="117" t="s">
+        <v>439</v>
+      </c>
+      <c r="D39" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E39" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H39" s="123"/>
+      <c r="I39" s="123"/>
+      <c r="J39" s="123"/>
+      <c r="K39" s="123"/>
+      <c r="L39" s="123"/>
+      <c r="M39" s="123"/>
+      <c r="N39" s="124"/>
+      <c r="O39" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="40" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C40" s="117" t="s">
+        <v>440</v>
+      </c>
+      <c r="D40" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E40" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H40" s="123"/>
+      <c r="I40" s="123"/>
+      <c r="J40" s="123"/>
+      <c r="K40" s="123"/>
+      <c r="L40" s="123"/>
+      <c r="M40" s="123"/>
+      <c r="N40" s="124"/>
+      <c r="O40" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C41" s="117" t="s">
+        <v>441</v>
+      </c>
+      <c r="D41" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E41" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G41" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H41" s="123"/>
+      <c r="I41" s="123"/>
+      <c r="J41" s="123"/>
+      <c r="K41" s="123"/>
+      <c r="L41" s="123"/>
+      <c r="M41" s="123"/>
+      <c r="N41" s="124"/>
+      <c r="O41" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="42" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="117" t="s">
+        <v>442</v>
+      </c>
+      <c r="D42" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E42" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H42" s="123"/>
+      <c r="I42" s="123"/>
+      <c r="J42" s="123"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="123"/>
+      <c r="M42" s="123"/>
+      <c r="N42" s="124"/>
+      <c r="O42" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="117" t="s">
+        <v>443</v>
+      </c>
+      <c r="D43" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E43" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G43" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H43" s="123"/>
+      <c r="I43" s="123"/>
+      <c r="J43" s="123"/>
+      <c r="K43" s="123"/>
+      <c r="L43" s="123"/>
+      <c r="M43" s="123"/>
+      <c r="N43" s="124"/>
+      <c r="O43" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="44" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="117" t="s">
+        <v>444</v>
+      </c>
+      <c r="D44" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E44" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H44" s="123"/>
+      <c r="I44" s="123"/>
+      <c r="J44" s="123"/>
+      <c r="K44" s="123"/>
+      <c r="L44" s="123"/>
+      <c r="M44" s="123"/>
+      <c r="N44" s="124"/>
+      <c r="O44" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C45" s="117" t="s">
+        <v>445</v>
+      </c>
+      <c r="D45" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E45" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G45" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H45" s="123"/>
+      <c r="I45" s="123"/>
+      <c r="J45" s="123"/>
+      <c r="K45" s="123"/>
+      <c r="L45" s="123"/>
+      <c r="M45" s="123"/>
+      <c r="N45" s="124"/>
+      <c r="O45" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="46" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C46" s="117" t="s">
+        <v>446</v>
+      </c>
+      <c r="D46" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E46" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G46" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H46" s="123"/>
+      <c r="I46" s="123"/>
+      <c r="J46" s="123"/>
+      <c r="K46" s="123"/>
+      <c r="L46" s="123"/>
+      <c r="M46" s="123"/>
+      <c r="N46" s="124"/>
+      <c r="O46" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C47" s="117" t="s">
+        <v>448</v>
+      </c>
+      <c r="D47" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E47" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G47" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H47" s="123"/>
+      <c r="I47" s="123"/>
+      <c r="J47" s="123"/>
+      <c r="K47" s="123"/>
+      <c r="L47" s="123"/>
+      <c r="M47" s="123"/>
+      <c r="N47" s="124"/>
+      <c r="O47" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="48" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C48" s="117" t="s">
+        <v>449</v>
+      </c>
+      <c r="D48" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E48" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G48" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H48" s="123"/>
+      <c r="I48" s="123"/>
+      <c r="J48" s="123"/>
+      <c r="K48" s="123"/>
+      <c r="L48" s="123"/>
+      <c r="M48" s="123"/>
+      <c r="N48" s="124"/>
+      <c r="O48" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C49" s="117" t="s">
+        <v>450</v>
+      </c>
+      <c r="D49" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E49" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G49" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H49" s="123"/>
+      <c r="I49" s="123"/>
+      <c r="J49" s="123"/>
+      <c r="K49" s="123"/>
+      <c r="L49" s="123"/>
+      <c r="M49" s="123"/>
+      <c r="N49" s="124"/>
+      <c r="O49" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="117" t="s">
+        <v>451</v>
+      </c>
+      <c r="D50" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E50" s="114" t="s">
+        <v>453</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G50" s="122" t="s">
+        <v>463</v>
+      </c>
+      <c r="H50" s="123"/>
+      <c r="I50" s="123"/>
+      <c r="J50" s="123"/>
+      <c r="K50" s="123"/>
+      <c r="L50" s="123"/>
+      <c r="M50" s="123"/>
+      <c r="N50" s="124"/>
+      <c r="O50" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C51" s="117" t="s">
+        <v>452</v>
+      </c>
+      <c r="D51" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G51" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="H51" s="123"/>
+      <c r="I51" s="123"/>
+      <c r="J51" s="123"/>
+      <c r="K51" s="123"/>
+      <c r="L51" s="123"/>
+      <c r="M51" s="123"/>
+      <c r="N51" s="124"/>
+      <c r="O51" s="49" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="117" t="s">
+        <v>454</v>
+      </c>
+      <c r="D52" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G52" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="H52" s="123"/>
+      <c r="I52" s="123"/>
+      <c r="J52" s="123"/>
+      <c r="K52" s="123"/>
+      <c r="L52" s="123"/>
+      <c r="M52" s="123"/>
+      <c r="N52" s="124"/>
+      <c r="O52" s="49" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C53" s="117" t="s">
+        <v>455</v>
+      </c>
+      <c r="D53" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G53" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="H53" s="123"/>
+      <c r="I53" s="123"/>
+      <c r="J53" s="123"/>
+      <c r="K53" s="123"/>
+      <c r="L53" s="123"/>
+      <c r="M53" s="123"/>
+      <c r="N53" s="124"/>
+      <c r="O53" s="49" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C54" s="117" t="s">
+        <v>456</v>
+      </c>
+      <c r="D54" s="114" t="s">
+        <v>447</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G54" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="H54" s="123"/>
+      <c r="I54" s="123"/>
+      <c r="J54" s="123"/>
+      <c r="K54" s="123"/>
+      <c r="L54" s="123"/>
+      <c r="M54" s="123"/>
+      <c r="N54" s="124"/>
+      <c r="O54" s="49" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C55" s="118" t="s">
+        <v>457</v>
+      </c>
+      <c r="D55" s="119" t="s">
+        <v>447</v>
+      </c>
+      <c r="E55" s="120" t="s">
+        <v>462</v>
+      </c>
+      <c r="F55" s="125" t="s">
+        <v>187</v>
+      </c>
+      <c r="G55" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="H55" s="123"/>
+      <c r="I55" s="123"/>
+      <c r="J55" s="123"/>
+      <c r="K55" s="123"/>
+      <c r="L55" s="123"/>
+      <c r="M55" s="123"/>
+      <c r="N55" s="124"/>
+      <c r="O55" s="49" t="s">
+        <v>465</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="45">
+    <mergeCell ref="G55:N55"/>
+    <mergeCell ref="G51:N51"/>
+    <mergeCell ref="G52:N52"/>
+    <mergeCell ref="G53:N53"/>
+    <mergeCell ref="G54:N54"/>
+    <mergeCell ref="G46:N46"/>
+    <mergeCell ref="G47:N47"/>
+    <mergeCell ref="G48:N48"/>
+    <mergeCell ref="G49:N49"/>
+    <mergeCell ref="G50:N50"/>
+    <mergeCell ref="G41:N41"/>
+    <mergeCell ref="G42:N42"/>
+    <mergeCell ref="G43:N43"/>
+    <mergeCell ref="G44:N44"/>
+    <mergeCell ref="G45:N45"/>
+    <mergeCell ref="G36:N36"/>
+    <mergeCell ref="G37:N37"/>
+    <mergeCell ref="G38:N38"/>
+    <mergeCell ref="G39:N39"/>
+    <mergeCell ref="G40:N40"/>
+    <mergeCell ref="G31:N31"/>
+    <mergeCell ref="G32:N32"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G34:N34"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="G4:M4"/>
+    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="G8:N8"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="G19:N19"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="G5:N5"/>
     <mergeCell ref="G28:N28"/>
     <mergeCell ref="G6:N6"/>
     <mergeCell ref="G13:N13"/>
@@ -3598,13 +4541,6 @@
     <mergeCell ref="H26:L26"/>
     <mergeCell ref="G12:N12"/>
     <mergeCell ref="G11:N11"/>
-    <mergeCell ref="G4:M4"/>
-    <mergeCell ref="G27:N27"/>
-    <mergeCell ref="G8:N8"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="G5:N5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3724,16 +4660,16 @@
       <c r="E12" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F12" s="89" t="s">
+      <c r="F12" s="103" t="s">
         <v>263</v>
       </c>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="82"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="94"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -3749,12 +4685,12 @@
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="89" t="s">
+      <c r="J13" s="103" t="s">
         <v>265</v>
       </c>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="82"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="94"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -3766,16 +4702,16 @@
       <c r="E14" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F14" s="89" t="s">
+      <c r="F14" s="103" t="s">
         <v>263</v>
       </c>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="82"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="93"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="94"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -3791,12 +4727,12 @@
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="35"/>
-      <c r="J15" s="89" t="s">
+      <c r="J15" s="103" t="s">
         <v>265</v>
       </c>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="82"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="94"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="18" t="s">
@@ -3808,16 +4744,16 @@
       <c r="E16" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F16" s="89" t="s">
+      <c r="F16" s="103" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="82"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="93"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="94"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="18" t="s">
@@ -3833,12 +4769,12 @@
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
       <c r="I17" s="35"/>
-      <c r="J17" s="89" t="s">
+      <c r="J17" s="103" t="s">
         <v>265</v>
       </c>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="82"/>
+      <c r="K17" s="93"/>
+      <c r="L17" s="93"/>
+      <c r="M17" s="94"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="18" t="s">
@@ -3853,13 +4789,13 @@
       <c r="F18" s="33"/>
       <c r="G18" s="34"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="89" t="s">
+      <c r="I18" s="103" t="s">
         <v>271</v>
       </c>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="82"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="93"/>
+      <c r="M18" s="94"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="18" t="s">
@@ -3912,12 +4848,12 @@
       <c r="I20" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="J20" s="89" t="s">
+      <c r="J20" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="82"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="94"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -3935,12 +4871,12 @@
       <c r="I21" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="J21" s="89" t="s">
+      <c r="J21" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="82"/>
+      <c r="K21" s="93"/>
+      <c r="L21" s="93"/>
+      <c r="M21" s="94"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -3958,12 +4894,12 @@
       <c r="I22" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="J22" s="89" t="s">
+      <c r="J22" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="K22" s="81"/>
-      <c r="L22" s="81"/>
-      <c r="M22" s="82"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="94"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -3975,16 +4911,16 @@
       <c r="E23" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F23" s="89" t="s">
+      <c r="F23" s="103" t="s">
         <v>286</v>
       </c>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="81"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="82"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="94"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -3996,16 +4932,16 @@
       <c r="E24" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F24" s="89" t="s">
+      <c r="F24" s="103" t="s">
         <v>288</v>
       </c>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="81"/>
-      <c r="M24" s="82"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="94"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -4021,12 +4957,12 @@
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="89" t="s">
+      <c r="J25" s="103" t="s">
         <v>290</v>
       </c>
-      <c r="K25" s="81"/>
-      <c r="L25" s="81"/>
-      <c r="M25" s="82"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="94"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -4076,16 +5012,16 @@
       <c r="E28" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="F28" s="85" t="s">
+      <c r="F28" s="96" t="s">
         <v>263</v>
       </c>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="81"/>
-      <c r="L28" s="81"/>
-      <c r="M28" s="82"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="93"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="93"/>
+      <c r="M28" s="94"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="18" t="s">
@@ -4101,12 +5037,12 @@
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="27"/>
-      <c r="J29" s="85" t="s">
+      <c r="J29" s="96" t="s">
         <v>265</v>
       </c>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
-      <c r="M29" s="82"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="93"/>
+      <c r="M29" s="94"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -4118,16 +5054,16 @@
       <c r="E30" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="F30" s="85" t="s">
+      <c r="F30" s="96" t="s">
         <v>263</v>
       </c>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="81"/>
-      <c r="K30" s="81"/>
-      <c r="L30" s="81"/>
-      <c r="M30" s="82"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="94"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -4143,12 +5079,12 @@
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="27"/>
-      <c r="J31" s="85" t="s">
+      <c r="J31" s="96" t="s">
         <v>265</v>
       </c>
-      <c r="K31" s="81"/>
-      <c r="L31" s="81"/>
-      <c r="M31" s="82"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="94"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -4160,16 +5096,16 @@
       <c r="E32" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="F32" s="85" t="s">
+      <c r="F32" s="96" t="s">
         <v>263</v>
       </c>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="81"/>
-      <c r="M32" s="82"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="94"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -4185,12 +5121,12 @@
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="27"/>
-      <c r="J33" s="85" t="s">
+      <c r="J33" s="96" t="s">
         <v>265</v>
       </c>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
-      <c r="M33" s="82"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="94"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -4205,13 +5141,13 @@
       <c r="F34" s="25"/>
       <c r="G34" s="26"/>
       <c r="H34" s="27"/>
-      <c r="I34" s="85" t="s">
+      <c r="I34" s="96" t="s">
         <v>271</v>
       </c>
-      <c r="J34" s="81"/>
-      <c r="K34" s="81"/>
-      <c r="L34" s="81"/>
-      <c r="M34" s="82"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="93"/>
+      <c r="M34" s="94"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -4264,12 +5200,12 @@
       <c r="I36" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J36" s="85" t="s">
+      <c r="J36" s="96" t="s">
         <v>282</v>
       </c>
-      <c r="K36" s="81"/>
-      <c r="L36" s="81"/>
-      <c r="M36" s="82"/>
+      <c r="K36" s="93"/>
+      <c r="L36" s="93"/>
+      <c r="M36" s="94"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -4287,12 +5223,12 @@
       <c r="I37" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J37" s="85" t="s">
+      <c r="J37" s="96" t="s">
         <v>282</v>
       </c>
-      <c r="K37" s="81"/>
-      <c r="L37" s="81"/>
-      <c r="M37" s="82"/>
+      <c r="K37" s="93"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="94"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -4310,12 +5246,12 @@
       <c r="I38" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J38" s="85" t="s">
+      <c r="J38" s="96" t="s">
         <v>282</v>
       </c>
-      <c r="K38" s="81"/>
-      <c r="L38" s="81"/>
-      <c r="M38" s="82"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="94"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -4327,16 +5263,16 @@
       <c r="E39" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="F39" s="85" t="s">
+      <c r="F39" s="96" t="s">
         <v>286</v>
       </c>
-      <c r="G39" s="81"/>
-      <c r="H39" s="81"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="81"/>
-      <c r="K39" s="81"/>
-      <c r="L39" s="81"/>
-      <c r="M39" s="82"/>
+      <c r="G39" s="93"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93"/>
+      <c r="J39" s="93"/>
+      <c r="K39" s="93"/>
+      <c r="L39" s="93"/>
+      <c r="M39" s="94"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18" t="s">
@@ -4348,16 +5284,16 @@
       <c r="E40" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="F40" s="85" t="s">
+      <c r="F40" s="96" t="s">
         <v>288</v>
       </c>
-      <c r="G40" s="81"/>
-      <c r="H40" s="81"/>
-      <c r="I40" s="81"/>
-      <c r="J40" s="81"/>
-      <c r="K40" s="81"/>
-      <c r="L40" s="81"/>
-      <c r="M40" s="82"/>
+      <c r="G40" s="93"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93"/>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="93"/>
+      <c r="M40" s="94"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18" t="s">
@@ -4373,12 +5309,12 @@
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="27"/>
-      <c r="J41" s="85" t="s">
+      <c r="J41" s="96" t="s">
         <v>290</v>
       </c>
-      <c r="K41" s="81"/>
-      <c r="L41" s="81"/>
-      <c r="M41" s="82"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="94"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18" t="s">
@@ -4413,12 +5349,12 @@
       <c r="G43" s="69"/>
       <c r="H43" s="69"/>
       <c r="I43" s="70"/>
-      <c r="J43" s="92" t="s">
+      <c r="J43" s="104" t="s">
         <v>309</v>
       </c>
-      <c r="K43" s="93"/>
-      <c r="L43" s="93"/>
-      <c r="M43" s="94"/>
+      <c r="K43" s="105"/>
+      <c r="L43" s="105"/>
+      <c r="M43" s="106"/>
     </row>
     <row r="44" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
@@ -4430,16 +5366,16 @@
       <c r="E44" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="F44" s="90" t="s">
+      <c r="F44" s="101" t="s">
         <v>282</v>
       </c>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81"/>
-      <c r="L44" s="81"/>
-      <c r="M44" s="91"/>
+      <c r="G44" s="93"/>
+      <c r="H44" s="93"/>
+      <c r="I44" s="93"/>
+      <c r="J44" s="93"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="93"/>
+      <c r="M44" s="102"/>
       <c r="O44" t="s">
         <v>312</v>
       </c>
@@ -4454,16 +5390,16 @@
       <c r="E45" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="F45" s="90" t="s">
+      <c r="F45" s="101" t="s">
         <v>282</v>
       </c>
-      <c r="G45" s="81"/>
-      <c r="H45" s="81"/>
-      <c r="I45" s="81"/>
-      <c r="J45" s="81"/>
-      <c r="K45" s="81"/>
-      <c r="L45" s="81"/>
-      <c r="M45" s="91"/>
+      <c r="G45" s="93"/>
+      <c r="H45" s="93"/>
+      <c r="I45" s="93"/>
+      <c r="J45" s="93"/>
+      <c r="K45" s="93"/>
+      <c r="L45" s="93"/>
+      <c r="M45" s="102"/>
       <c r="O45" t="s">
         <v>312</v>
       </c>
@@ -4478,16 +5414,16 @@
       <c r="E46" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="F46" s="90" t="s">
+      <c r="F46" s="101" t="s">
         <v>282</v>
       </c>
-      <c r="G46" s="81"/>
-      <c r="H46" s="81"/>
-      <c r="I46" s="81"/>
-      <c r="J46" s="81"/>
-      <c r="K46" s="81"/>
-      <c r="L46" s="81"/>
-      <c r="M46" s="91"/>
+      <c r="G46" s="93"/>
+      <c r="H46" s="93"/>
+      <c r="I46" s="93"/>
+      <c r="J46" s="93"/>
+      <c r="K46" s="93"/>
+      <c r="L46" s="93"/>
+      <c r="M46" s="102"/>
       <c r="O46" t="s">
         <v>312</v>
       </c>
@@ -4521,16 +5457,16 @@
       <c r="E48" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="F48" s="90" t="s">
+      <c r="F48" s="101" t="s">
         <v>282</v>
       </c>
-      <c r="G48" s="81"/>
-      <c r="H48" s="81"/>
-      <c r="I48" s="81"/>
-      <c r="J48" s="81"/>
-      <c r="K48" s="81"/>
-      <c r="L48" s="81"/>
-      <c r="M48" s="91"/>
+      <c r="G48" s="93"/>
+      <c r="H48" s="93"/>
+      <c r="I48" s="93"/>
+      <c r="J48" s="93"/>
+      <c r="K48" s="93"/>
+      <c r="L48" s="93"/>
+      <c r="M48" s="102"/>
       <c r="O48" t="s">
         <v>312</v>
       </c>
@@ -4545,16 +5481,16 @@
       <c r="E49" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="F49" s="90" t="s">
+      <c r="F49" s="101" t="s">
         <v>282</v>
       </c>
-      <c r="G49" s="81"/>
-      <c r="H49" s="81"/>
-      <c r="I49" s="81"/>
-      <c r="J49" s="81"/>
-      <c r="K49" s="81"/>
-      <c r="L49" s="81"/>
-      <c r="M49" s="91"/>
+      <c r="G49" s="93"/>
+      <c r="H49" s="93"/>
+      <c r="I49" s="93"/>
+      <c r="J49" s="93"/>
+      <c r="K49" s="93"/>
+      <c r="L49" s="93"/>
+      <c r="M49" s="102"/>
       <c r="O49" t="s">
         <v>312</v>
       </c>
@@ -4569,16 +5505,16 @@
       <c r="E50" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="F50" s="90" t="s">
+      <c r="F50" s="101" t="s">
         <v>282</v>
       </c>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="81"/>
-      <c r="K50" s="81"/>
-      <c r="L50" s="81"/>
-      <c r="M50" s="91"/>
+      <c r="G50" s="93"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="93"/>
+      <c r="J50" s="93"/>
+      <c r="K50" s="93"/>
+      <c r="L50" s="93"/>
+      <c r="M50" s="102"/>
       <c r="O50" t="s">
         <v>312</v>
       </c>
@@ -4612,18 +5548,18 @@
       <c r="E52" s="22" t="s">
         <v>327</v>
       </c>
-      <c r="F52" s="85" t="s">
+      <c r="F52" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="81"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="81"/>
-      <c r="J52" s="81"/>
-      <c r="K52" s="81"/>
-      <c r="L52" s="81"/>
-      <c r="M52" s="82"/>
+      <c r="G52" s="93"/>
+      <c r="H52" s="93"/>
+      <c r="I52" s="93"/>
+      <c r="J52" s="93"/>
+      <c r="K52" s="93"/>
+      <c r="L52" s="93"/>
+      <c r="M52" s="94"/>
       <c r="O52" t="s">
-        <v>141</v>
+        <v>464</v>
       </c>
     </row>
     <row r="53" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4636,16 +5572,16 @@
       <c r="E53" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="F53" s="85" t="s">
+      <c r="F53" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81"/>
-      <c r="K53" s="81"/>
-      <c r="L53" s="81"/>
-      <c r="M53" s="82"/>
+      <c r="G53" s="93"/>
+      <c r="H53" s="93"/>
+      <c r="I53" s="93"/>
+      <c r="J53" s="93"/>
+      <c r="K53" s="93"/>
+      <c r="L53" s="93"/>
+      <c r="M53" s="94"/>
       <c r="O53" t="s">
         <v>141</v>
       </c>
@@ -4660,16 +5596,16 @@
       <c r="E54" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="F54" s="85" t="s">
+      <c r="F54" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="81"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="81"/>
-      <c r="K54" s="81"/>
-      <c r="L54" s="81"/>
-      <c r="M54" s="82"/>
+      <c r="G54" s="93"/>
+      <c r="H54" s="93"/>
+      <c r="I54" s="93"/>
+      <c r="J54" s="93"/>
+      <c r="K54" s="93"/>
+      <c r="L54" s="93"/>
+      <c r="M54" s="94"/>
       <c r="O54" t="s">
         <v>141</v>
       </c>
@@ -4703,16 +5639,16 @@
       <c r="E56" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="F56" s="85" t="s">
+      <c r="F56" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="81"/>
-      <c r="H56" s="81"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="81"/>
-      <c r="K56" s="81"/>
-      <c r="L56" s="81"/>
-      <c r="M56" s="82"/>
+      <c r="G56" s="93"/>
+      <c r="H56" s="93"/>
+      <c r="I56" s="93"/>
+      <c r="J56" s="93"/>
+      <c r="K56" s="93"/>
+      <c r="L56" s="93"/>
+      <c r="M56" s="94"/>
       <c r="O56" t="s">
         <v>141</v>
       </c>
@@ -4727,16 +5663,16 @@
       <c r="E57" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="F57" s="85" t="s">
+      <c r="F57" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="81"/>
-      <c r="K57" s="81"/>
-      <c r="L57" s="81"/>
-      <c r="M57" s="82"/>
+      <c r="G57" s="93"/>
+      <c r="H57" s="93"/>
+      <c r="I57" s="93"/>
+      <c r="J57" s="93"/>
+      <c r="K57" s="93"/>
+      <c r="L57" s="93"/>
+      <c r="M57" s="94"/>
       <c r="O57" t="s">
         <v>141</v>
       </c>
@@ -4751,16 +5687,16 @@
       <c r="E58" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="F58" s="85" t="s">
+      <c r="F58" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="81"/>
-      <c r="H58" s="81"/>
-      <c r="I58" s="81"/>
-      <c r="J58" s="81"/>
-      <c r="K58" s="81"/>
-      <c r="L58" s="81"/>
-      <c r="M58" s="82"/>
+      <c r="G58" s="93"/>
+      <c r="H58" s="93"/>
+      <c r="I58" s="93"/>
+      <c r="J58" s="93"/>
+      <c r="K58" s="93"/>
+      <c r="L58" s="93"/>
+      <c r="M58" s="94"/>
       <c r="O58" t="s">
         <v>141</v>
       </c>
@@ -4805,18 +5741,17 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:M48"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F50:M50"/>
-    <mergeCell ref="F46:M46"/>
-    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J43:M43"/>
     <mergeCell ref="F12:M12"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J17:M17"/>
@@ -4833,17 +5768,18 @@
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F45:M45"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:M48"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F53:M53"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4918,16 +5854,16 @@
       <c r="E6" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="F6" s="87" t="s">
+      <c r="F6" s="98" t="s">
         <v>344</v>
       </c>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="82"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="94"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
@@ -4939,16 +5875,16 @@
       <c r="E7" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F7" s="87" t="s">
+      <c r="F7" s="98" t="s">
         <v>347</v>
       </c>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="82"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="94"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
@@ -5010,12 +5946,12 @@
       <c r="I19" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="87" t="s">
+      <c r="J19" s="98" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="82"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="93"/>
+      <c r="M19" s="94"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="18" t="s">
@@ -5037,12 +5973,12 @@
       <c r="I20" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="87" t="s">
+      <c r="J20" s="98" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="82"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="94"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -5052,18 +5988,18 @@
         <v>19</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="87" t="s">
+      <c r="F21" s="98" t="s">
         <v>350</v>
       </c>
-      <c r="G21" s="82"/>
-      <c r="H21" s="87" t="s">
+      <c r="G21" s="94"/>
+      <c r="H21" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="82"/>
+      <c r="I21" s="93"/>
+      <c r="J21" s="93"/>
+      <c r="K21" s="93"/>
+      <c r="L21" s="93"/>
+      <c r="M21" s="94"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -5073,10 +6009,10 @@
         <v>19</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="87" t="s">
+      <c r="F22" s="98" t="s">
         <v>350</v>
       </c>
-      <c r="G22" s="82"/>
+      <c r="G22" s="94"/>
       <c r="H22" s="17"/>
       <c r="I22" s="10" t="s">
         <v>351</v>
@@ -5084,11 +6020,11 @@
       <c r="J22" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="K22" s="87" t="s">
+      <c r="K22" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="L22" s="81"/>
-      <c r="M22" s="82"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="94"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -5098,18 +6034,18 @@
         <v>19</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="87" t="s">
+      <c r="F23" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="82"/>
-      <c r="J23" s="87" t="s">
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="K23" s="81"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="82"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="94"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -5119,18 +6055,18 @@
         <v>19</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="87" t="s">
+      <c r="F24" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="82"/>
-      <c r="J24" s="87" t="s">
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="94"/>
+      <c r="J24" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="81"/>
-      <c r="L24" s="81"/>
-      <c r="M24" s="82"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="94"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -5140,18 +6076,18 @@
         <v>19</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="87" t="s">
+      <c r="F25" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="81"/>
-      <c r="H25" s="81"/>
-      <c r="I25" s="82"/>
-      <c r="J25" s="87" t="s">
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="94"/>
+      <c r="J25" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="81"/>
-      <c r="L25" s="81"/>
-      <c r="M25" s="82"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="94"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -5161,18 +6097,18 @@
         <v>19</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="87" t="s">
+      <c r="F26" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="82"/>
-      <c r="J26" s="87" t="s">
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="81"/>
-      <c r="L26" s="81"/>
-      <c r="M26" s="82"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
+      <c r="M26" s="94"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="18" t="s">
@@ -5226,16 +6162,16 @@
       <c r="E29" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="87" t="s">
+      <c r="F29" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="81"/>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
-      <c r="M29" s="82"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="93"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="93"/>
+      <c r="M29" s="94"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -5245,16 +6181,16 @@
         <v>19</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="87" t="s">
+      <c r="F30" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="81"/>
-      <c r="K30" s="81"/>
-      <c r="L30" s="81"/>
-      <c r="M30" s="82"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="94"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -5264,16 +6200,16 @@
         <v>19</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="87" t="s">
+      <c r="F31" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="81"/>
-      <c r="K31" s="81"/>
-      <c r="L31" s="81"/>
-      <c r="M31" s="82"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="94"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -5283,16 +6219,16 @@
         <v>19</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="87" t="s">
+      <c r="F32" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="81"/>
-      <c r="M32" s="82"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="94"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -5302,16 +6238,16 @@
         <v>19</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="87" t="s">
+      <c r="F33" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
-      <c r="M33" s="82"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="94"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -5321,16 +6257,16 @@
         <v>19</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="87" t="s">
+      <c r="F34" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="81"/>
-      <c r="L34" s="81"/>
-      <c r="M34" s="82"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="93"/>
+      <c r="M34" s="94"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -5340,16 +6276,16 @@
         <v>19</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="87" t="s">
+      <c r="F35" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="81"/>
-      <c r="K35" s="81"/>
-      <c r="L35" s="81"/>
-      <c r="M35" s="82"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93"/>
+      <c r="J35" s="93"/>
+      <c r="K35" s="93"/>
+      <c r="L35" s="93"/>
+      <c r="M35" s="94"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="18" t="s">
@@ -5359,16 +6295,16 @@
         <v>19</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="87" t="s">
+      <c r="F36" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
-      <c r="L36" s="81"/>
-      <c r="M36" s="82"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
+      <c r="J36" s="93"/>
+      <c r="K36" s="93"/>
+      <c r="L36" s="93"/>
+      <c r="M36" s="94"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -5378,16 +6314,16 @@
         <v>19</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="87" t="s">
+      <c r="F37" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="81"/>
-      <c r="K37" s="81"/>
-      <c r="L37" s="81"/>
-      <c r="M37" s="82"/>
+      <c r="G37" s="93"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93"/>
+      <c r="J37" s="93"/>
+      <c r="K37" s="93"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="94"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -5397,16 +6333,16 @@
         <v>19</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="87" t="s">
+      <c r="F38" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G38" s="81"/>
-      <c r="H38" s="81"/>
-      <c r="I38" s="81"/>
-      <c r="J38" s="81"/>
-      <c r="K38" s="81"/>
-      <c r="L38" s="81"/>
-      <c r="M38" s="82"/>
+      <c r="G38" s="93"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
+      <c r="J38" s="93"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="94"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -5441,11 +6377,11 @@
       <c r="I40" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J40" s="87" t="s">
+      <c r="J40" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="K40" s="81"/>
-      <c r="L40" s="82"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="94"/>
       <c r="M40" s="12" t="s">
         <v>120</v>
       </c>
@@ -5466,11 +6402,11 @@
       <c r="I41" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J41" s="87" t="s">
+      <c r="J41" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="K41" s="81"/>
-      <c r="L41" s="82"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="94"/>
       <c r="M41" s="12" t="s">
         <v>120</v>
       </c>
@@ -5491,11 +6427,11 @@
       <c r="I42" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J42" s="87" t="s">
+      <c r="J42" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="K42" s="81"/>
-      <c r="L42" s="82"/>
+      <c r="K42" s="93"/>
+      <c r="L42" s="94"/>
       <c r="M42" s="12" t="s">
         <v>120</v>
       </c>
@@ -5516,11 +6452,11 @@
       <c r="I43" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J43" s="87" t="s">
+      <c r="J43" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="K43" s="81"/>
-      <c r="L43" s="82"/>
+      <c r="K43" s="93"/>
+      <c r="L43" s="94"/>
       <c r="M43" s="12" t="s">
         <v>120</v>
       </c>
@@ -5541,11 +6477,11 @@
       <c r="I44" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J44" s="87" t="s">
+      <c r="J44" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="K44" s="81"/>
-      <c r="L44" s="82"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="94"/>
       <c r="M44" s="12" t="s">
         <v>120</v>
       </c>
@@ -5566,11 +6502,11 @@
       <c r="I45" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J45" s="87" t="s">
+      <c r="J45" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="K45" s="81"/>
-      <c r="L45" s="82"/>
+      <c r="K45" s="93"/>
+      <c r="L45" s="94"/>
       <c r="M45" s="12" t="s">
         <v>120</v>
       </c>
@@ -5591,11 +6527,11 @@
       <c r="I46" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J46" s="87" t="s">
+      <c r="J46" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="K46" s="81"/>
-      <c r="L46" s="82"/>
+      <c r="K46" s="93"/>
+      <c r="L46" s="94"/>
       <c r="M46" s="12" t="s">
         <v>120</v>
       </c>
@@ -5616,11 +6552,11 @@
       <c r="I47" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J47" s="87" t="s">
+      <c r="J47" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="K47" s="81"/>
-      <c r="L47" s="82"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="94"/>
       <c r="M47" s="12" t="s">
         <v>120</v>
       </c>
@@ -5641,11 +6577,11 @@
       <c r="I48" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J48" s="87" t="s">
+      <c r="J48" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="K48" s="81"/>
-      <c r="L48" s="82"/>
+      <c r="K48" s="93"/>
+      <c r="L48" s="94"/>
       <c r="M48" s="12" t="s">
         <v>120</v>
       </c>
@@ -5675,18 +6611,18 @@
         <v>19</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="87" t="s">
+      <c r="F50" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="82"/>
-      <c r="J50" s="87" t="s">
+      <c r="G50" s="93"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="94"/>
+      <c r="J50" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="K50" s="81"/>
-      <c r="L50" s="81"/>
-      <c r="M50" s="82"/>
+      <c r="K50" s="93"/>
+      <c r="L50" s="93"/>
+      <c r="M50" s="94"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
@@ -5696,18 +6632,18 @@
         <v>19</v>
       </c>
       <c r="E51" s="11"/>
-      <c r="F51" s="87" t="s">
+      <c r="F51" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="G51" s="81"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="82"/>
-      <c r="J51" s="87" t="s">
+      <c r="G51" s="93"/>
+      <c r="H51" s="93"/>
+      <c r="I51" s="94"/>
+      <c r="J51" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="K51" s="81"/>
-      <c r="L51" s="81"/>
-      <c r="M51" s="82"/>
+      <c r="K51" s="93"/>
+      <c r="L51" s="93"/>
+      <c r="M51" s="94"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -5717,18 +6653,18 @@
         <v>19</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="87" t="s">
+      <c r="F52" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="G52" s="81"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="82"/>
-      <c r="J52" s="87" t="s">
+      <c r="G52" s="93"/>
+      <c r="H52" s="93"/>
+      <c r="I52" s="94"/>
+      <c r="J52" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="K52" s="81"/>
-      <c r="L52" s="81"/>
-      <c r="M52" s="82"/>
+      <c r="K52" s="93"/>
+      <c r="L52" s="93"/>
+      <c r="M52" s="94"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18" t="s">
@@ -5738,18 +6674,18 @@
         <v>19</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="87" t="s">
+      <c r="F53" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="82"/>
-      <c r="J53" s="87" t="s">
+      <c r="G53" s="93"/>
+      <c r="H53" s="93"/>
+      <c r="I53" s="94"/>
+      <c r="J53" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="K53" s="81"/>
-      <c r="L53" s="81"/>
-      <c r="M53" s="82"/>
+      <c r="K53" s="93"/>
+      <c r="L53" s="93"/>
+      <c r="M53" s="94"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18" t="s">
@@ -5759,18 +6695,18 @@
         <v>19</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="87" t="s">
+      <c r="F54" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="G54" s="81"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="87" t="s">
+      <c r="G54" s="93"/>
+      <c r="H54" s="93"/>
+      <c r="I54" s="94"/>
+      <c r="J54" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="K54" s="81"/>
-      <c r="L54" s="81"/>
-      <c r="M54" s="82"/>
+      <c r="K54" s="93"/>
+      <c r="L54" s="93"/>
+      <c r="M54" s="94"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18" t="s">
@@ -5780,18 +6716,18 @@
         <v>19</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="87" t="s">
+      <c r="F55" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="G55" s="81"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="82"/>
-      <c r="J55" s="87" t="s">
+      <c r="G55" s="93"/>
+      <c r="H55" s="93"/>
+      <c r="I55" s="94"/>
+      <c r="J55" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="K55" s="81"/>
-      <c r="L55" s="81"/>
-      <c r="M55" s="82"/>
+      <c r="K55" s="93"/>
+      <c r="L55" s="93"/>
+      <c r="M55" s="94"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18" t="s">
@@ -5801,18 +6737,18 @@
         <v>19</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="87" t="s">
+      <c r="F56" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="G56" s="81"/>
-      <c r="H56" s="81"/>
-      <c r="I56" s="82"/>
-      <c r="J56" s="87" t="s">
+      <c r="G56" s="93"/>
+      <c r="H56" s="93"/>
+      <c r="I56" s="94"/>
+      <c r="J56" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="K56" s="81"/>
-      <c r="L56" s="81"/>
-      <c r="M56" s="82"/>
+      <c r="K56" s="93"/>
+      <c r="L56" s="93"/>
+      <c r="M56" s="94"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18" t="s">
@@ -5822,18 +6758,18 @@
         <v>19</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="87" t="s">
+      <c r="F57" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="82"/>
-      <c r="J57" s="87" t="s">
+      <c r="G57" s="93"/>
+      <c r="H57" s="93"/>
+      <c r="I57" s="94"/>
+      <c r="J57" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="K57" s="81"/>
-      <c r="L57" s="81"/>
-      <c r="M57" s="82"/>
+      <c r="K57" s="93"/>
+      <c r="L57" s="93"/>
+      <c r="M57" s="94"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18" t="s">
@@ -5843,18 +6779,18 @@
         <v>19</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="87" t="s">
+      <c r="F58" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="G58" s="81"/>
-      <c r="H58" s="81"/>
-      <c r="I58" s="82"/>
-      <c r="J58" s="87" t="s">
+      <c r="G58" s="93"/>
+      <c r="H58" s="93"/>
+      <c r="I58" s="94"/>
+      <c r="J58" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="K58" s="81"/>
-      <c r="L58" s="81"/>
-      <c r="M58" s="82"/>
+      <c r="K58" s="93"/>
+      <c r="L58" s="93"/>
+      <c r="M58" s="94"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="18" t="s">
@@ -5889,10 +6825,10 @@
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="85" t="s">
+      <c r="L60" s="96" t="s">
         <v>373</v>
       </c>
-      <c r="M60" s="82"/>
+      <c r="M60" s="94"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="18" t="s">
@@ -5910,10 +6846,10 @@
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
       <c r="K61" s="9"/>
-      <c r="L61" s="88" t="s">
+      <c r="L61" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="M61" s="82"/>
+      <c r="M61" s="94"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="18" t="s">
@@ -5931,10 +6867,10 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="9"/>
-      <c r="L62" s="88" t="s">
+      <c r="L62" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="M62" s="82"/>
+      <c r="M62" s="94"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="18" t="s">
@@ -5952,10 +6888,10 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="9"/>
-      <c r="L63" s="88" t="s">
+      <c r="L63" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="M63" s="82"/>
+      <c r="M63" s="94"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="18" t="s">
@@ -5973,10 +6909,10 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="9"/>
-      <c r="L64" s="88" t="s">
+      <c r="L64" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="M64" s="82"/>
+      <c r="M64" s="94"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="18" t="s">
@@ -5994,10 +6930,10 @@
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="9"/>
-      <c r="L65" s="88" t="s">
+      <c r="L65" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="M65" s="82"/>
+      <c r="M65" s="94"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="18" t="s">
@@ -6015,10 +6951,10 @@
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
       <c r="K66" s="9"/>
-      <c r="L66" s="88" t="s">
+      <c r="L66" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="M66" s="82"/>
+      <c r="M66" s="94"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="18" t="s">
@@ -6036,10 +6972,10 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="9"/>
-      <c r="L67" s="88" t="s">
+      <c r="L67" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="M67" s="82"/>
+      <c r="M67" s="94"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="18" t="s">
@@ -6057,10 +6993,10 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="9"/>
-      <c r="L68" s="88" t="s">
+      <c r="L68" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="M68" s="82"/>
+      <c r="M68" s="94"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="18" t="s">
@@ -6089,16 +7025,16 @@
       <c r="E70" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F70" s="85" t="s">
+      <c r="F70" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G70" s="81"/>
-      <c r="H70" s="81"/>
-      <c r="I70" s="81"/>
-      <c r="J70" s="81"/>
-      <c r="K70" s="81"/>
-      <c r="L70" s="81"/>
-      <c r="M70" s="82"/>
+      <c r="G70" s="93"/>
+      <c r="H70" s="93"/>
+      <c r="I70" s="93"/>
+      <c r="J70" s="93"/>
+      <c r="K70" s="93"/>
+      <c r="L70" s="93"/>
+      <c r="M70" s="94"/>
       <c r="O70" t="s">
         <v>141</v>
       </c>
@@ -6113,16 +7049,16 @@
       <c r="E71" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F71" s="85" t="s">
+      <c r="F71" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G71" s="81"/>
-      <c r="H71" s="81"/>
-      <c r="I71" s="81"/>
-      <c r="J71" s="81"/>
-      <c r="K71" s="81"/>
-      <c r="L71" s="81"/>
-      <c r="M71" s="82"/>
+      <c r="G71" s="93"/>
+      <c r="H71" s="93"/>
+      <c r="I71" s="93"/>
+      <c r="J71" s="93"/>
+      <c r="K71" s="93"/>
+      <c r="L71" s="93"/>
+      <c r="M71" s="94"/>
       <c r="O71" t="s">
         <v>141</v>
       </c>
@@ -6137,16 +7073,16 @@
       <c r="E72" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F72" s="85" t="s">
+      <c r="F72" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G72" s="81"/>
-      <c r="H72" s="81"/>
-      <c r="I72" s="81"/>
-      <c r="J72" s="81"/>
-      <c r="K72" s="81"/>
-      <c r="L72" s="81"/>
-      <c r="M72" s="82"/>
+      <c r="G72" s="93"/>
+      <c r="H72" s="93"/>
+      <c r="I72" s="93"/>
+      <c r="J72" s="93"/>
+      <c r="K72" s="93"/>
+      <c r="L72" s="93"/>
+      <c r="M72" s="94"/>
       <c r="O72" t="s">
         <v>141</v>
       </c>
@@ -6161,16 +7097,16 @@
       <c r="E73" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F73" s="85" t="s">
+      <c r="F73" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="81"/>
-      <c r="H73" s="81"/>
-      <c r="I73" s="81"/>
-      <c r="J73" s="81"/>
-      <c r="K73" s="81"/>
-      <c r="L73" s="81"/>
-      <c r="M73" s="82"/>
+      <c r="G73" s="93"/>
+      <c r="H73" s="93"/>
+      <c r="I73" s="93"/>
+      <c r="J73" s="93"/>
+      <c r="K73" s="93"/>
+      <c r="L73" s="93"/>
+      <c r="M73" s="94"/>
       <c r="O73" t="s">
         <v>141</v>
       </c>
@@ -6185,16 +7121,16 @@
       <c r="E74" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F74" s="85" t="s">
+      <c r="F74" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G74" s="81"/>
-      <c r="H74" s="81"/>
-      <c r="I74" s="81"/>
-      <c r="J74" s="81"/>
-      <c r="K74" s="81"/>
-      <c r="L74" s="81"/>
-      <c r="M74" s="82"/>
+      <c r="G74" s="93"/>
+      <c r="H74" s="93"/>
+      <c r="I74" s="93"/>
+      <c r="J74" s="93"/>
+      <c r="K74" s="93"/>
+      <c r="L74" s="93"/>
+      <c r="M74" s="94"/>
       <c r="O74" t="s">
         <v>141</v>
       </c>
@@ -6209,16 +7145,16 @@
       <c r="E75" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F75" s="85" t="s">
+      <c r="F75" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G75" s="81"/>
-      <c r="H75" s="81"/>
-      <c r="I75" s="81"/>
-      <c r="J75" s="81"/>
-      <c r="K75" s="81"/>
-      <c r="L75" s="81"/>
-      <c r="M75" s="82"/>
+      <c r="G75" s="93"/>
+      <c r="H75" s="93"/>
+      <c r="I75" s="93"/>
+      <c r="J75" s="93"/>
+      <c r="K75" s="93"/>
+      <c r="L75" s="93"/>
+      <c r="M75" s="94"/>
       <c r="O75" t="s">
         <v>141</v>
       </c>
@@ -6233,16 +7169,16 @@
       <c r="E76" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F76" s="85" t="s">
+      <c r="F76" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G76" s="81"/>
-      <c r="H76" s="81"/>
-      <c r="I76" s="81"/>
-      <c r="J76" s="81"/>
-      <c r="K76" s="81"/>
-      <c r="L76" s="81"/>
-      <c r="M76" s="82"/>
+      <c r="G76" s="93"/>
+      <c r="H76" s="93"/>
+      <c r="I76" s="93"/>
+      <c r="J76" s="93"/>
+      <c r="K76" s="93"/>
+      <c r="L76" s="93"/>
+      <c r="M76" s="94"/>
       <c r="O76" t="s">
         <v>141</v>
       </c>
@@ -6257,16 +7193,16 @@
       <c r="E77" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F77" s="85" t="s">
+      <c r="F77" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G77" s="81"/>
-      <c r="H77" s="81"/>
-      <c r="I77" s="81"/>
-      <c r="J77" s="81"/>
-      <c r="K77" s="81"/>
-      <c r="L77" s="81"/>
-      <c r="M77" s="82"/>
+      <c r="G77" s="93"/>
+      <c r="H77" s="93"/>
+      <c r="I77" s="93"/>
+      <c r="J77" s="93"/>
+      <c r="K77" s="93"/>
+      <c r="L77" s="93"/>
+      <c r="M77" s="94"/>
       <c r="O77" t="s">
         <v>141</v>
       </c>
@@ -6281,16 +7217,16 @@
       <c r="E78" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F78" s="85" t="s">
+      <c r="F78" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="G78" s="81"/>
-      <c r="H78" s="81"/>
-      <c r="I78" s="81"/>
-      <c r="J78" s="81"/>
-      <c r="K78" s="81"/>
-      <c r="L78" s="81"/>
-      <c r="M78" s="82"/>
+      <c r="G78" s="93"/>
+      <c r="H78" s="93"/>
+      <c r="I78" s="93"/>
+      <c r="J78" s="93"/>
+      <c r="K78" s="93"/>
+      <c r="L78" s="93"/>
+      <c r="M78" s="94"/>
       <c r="O78" t="s">
         <v>141</v>
       </c>
@@ -6314,18 +7250,45 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F73:M73"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F78:M78"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="F74:M74"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="F75:M75"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="F77:M77"/>
+    <mergeCell ref="F76:M76"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="F72:M72"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="F71:M71"/>
     <mergeCell ref="F70:M70"/>
     <mergeCell ref="J57:M57"/>
     <mergeCell ref="F35:M35"/>
@@ -6342,49 +7305,22 @@
     <mergeCell ref="J55:M55"/>
     <mergeCell ref="J46:L46"/>
     <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F25:I25"/>
     <mergeCell ref="L61:M61"/>
-    <mergeCell ref="F72:M72"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="F54:I54"/>
     <mergeCell ref="J47:L47"/>
     <mergeCell ref="J48:L48"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="F71:M71"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="F73:M73"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F78:M78"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="F74:M74"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="F75:M75"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="F77:M77"/>
-    <mergeCell ref="F76:M76"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6493,14 +7429,14 @@
       <c r="E11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="95"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="82"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="93"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="94"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="18" t="s">
@@ -6512,16 +7448,16 @@
       <c r="E12" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="83" t="s">
+      <c r="F12" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="82"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="94"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -6533,16 +7469,16 @@
       <c r="E13" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="83" t="s">
+      <c r="F13" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="82"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="94"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -6554,16 +7490,16 @@
       <c r="E14" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="83" t="s">
+      <c r="F14" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="82"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="93"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="94"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -6608,16 +7544,16 @@
       <c r="E16" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="97" t="s">
+      <c r="F16" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="82"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="93"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="94"/>
       <c r="N16" s="56" t="s">
         <v>38</v>
       </c>
@@ -6632,16 +7568,16 @@
       <c r="E17" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="97" t="s">
+      <c r="F17" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="82"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="93"/>
+      <c r="K17" s="93"/>
+      <c r="L17" s="93"/>
+      <c r="M17" s="94"/>
       <c r="N17" s="56" t="s">
         <v>38</v>
       </c>
@@ -6669,8 +7605,8 @@
       <c r="J18" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="95"/>
-      <c r="L18" s="82"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="94"/>
       <c r="M18" s="54" t="s">
         <v>47</v>
       </c>
@@ -6692,8 +7628,8 @@
       <c r="G19" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="95"/>
-      <c r="I19" s="82"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="94"/>
       <c r="J19" s="55" t="s">
         <v>52</v>
       </c>
@@ -6715,16 +7651,16 @@
         <v>19</v>
       </c>
       <c r="E20" s="42"/>
-      <c r="F20" s="96" t="s">
+      <c r="F20" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="82"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="93"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="94"/>
       <c r="N20" t="s">
         <v>58</v>
       </c>
@@ -6737,16 +7673,16 @@
         <v>19</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="96" t="s">
+      <c r="F21" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="82"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="93"/>
+      <c r="J21" s="93"/>
+      <c r="K21" s="93"/>
+      <c r="L21" s="93"/>
+      <c r="M21" s="94"/>
       <c r="N21" t="s">
         <v>61</v>
       </c>
@@ -6759,16 +7695,16 @@
         <v>19</v>
       </c>
       <c r="E22" s="41"/>
-      <c r="F22" s="96" t="s">
+      <c r="F22" s="108" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="81"/>
-      <c r="M22" s="82"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="93"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="94"/>
       <c r="N22" t="s">
         <v>64</v>
       </c>
@@ -6781,16 +7717,16 @@
         <v>19</v>
       </c>
       <c r="E23" s="41"/>
-      <c r="F23" s="96" t="s">
+      <c r="F23" s="108" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="81"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="82"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="94"/>
       <c r="N23" t="s">
         <v>67</v>
       </c>
@@ -6805,16 +7741,16 @@
       <c r="E24" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="97" t="s">
+      <c r="F24" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="81"/>
-      <c r="M24" s="82"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="94"/>
       <c r="N24" s="58" t="s">
         <v>38</v>
       </c>
@@ -6829,16 +7765,16 @@
       <c r="E25" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="95"/>
-      <c r="G25" s="81"/>
-      <c r="H25" s="81"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="82"/>
-      <c r="K25" s="97" t="s">
+      <c r="F25" s="107"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="94"/>
+      <c r="K25" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="L25" s="81"/>
-      <c r="M25" s="82"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="94"/>
       <c r="N25" s="56" t="s">
         <v>38</v>
       </c>
@@ -6851,16 +7787,16 @@
         <v>3</v>
       </c>
       <c r="E26" s="41"/>
-      <c r="F26" s="96" t="s">
+      <c r="F26" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="81"/>
-      <c r="L26" s="81"/>
-      <c r="M26" s="82"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="93"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
+      <c r="M26" s="94"/>
       <c r="N26" t="s">
         <v>74</v>
       </c>
@@ -6873,16 +7809,16 @@
         <v>19</v>
       </c>
       <c r="E27" s="41"/>
-      <c r="F27" s="96" t="s">
+      <c r="F27" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="81"/>
-      <c r="M27" s="82"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
+      <c r="M27" s="94"/>
       <c r="N27" t="s">
         <v>77</v>
       </c>
@@ -6895,16 +7831,16 @@
         <v>19</v>
       </c>
       <c r="E28" s="41"/>
-      <c r="F28" s="96" t="s">
+      <c r="F28" s="108" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="81"/>
-      <c r="L28" s="81"/>
-      <c r="M28" s="82"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="93"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="93"/>
+      <c r="M28" s="94"/>
       <c r="N28" t="s">
         <v>80</v>
       </c>
@@ -6917,16 +7853,16 @@
         <v>19</v>
       </c>
       <c r="E29" s="41"/>
-      <c r="F29" s="96" t="s">
+      <c r="F29" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="81"/>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
-      <c r="M29" s="82"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="93"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="93"/>
+      <c r="M29" s="94"/>
       <c r="N29" t="s">
         <v>83</v>
       </c>
@@ -6941,14 +7877,14 @@
       <c r="E30" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="95"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="81"/>
-      <c r="K30" s="81"/>
-      <c r="L30" s="81"/>
-      <c r="M30" s="82"/>
+      <c r="F30" s="107"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="94"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="59" t="s">
@@ -6960,14 +7896,14 @@
       <c r="E31" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="95"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="81"/>
-      <c r="K31" s="81"/>
-      <c r="L31" s="81"/>
-      <c r="M31" s="82"/>
+      <c r="F31" s="107"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="94"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="59" t="s">
@@ -6979,16 +7915,16 @@
       <c r="E32" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="97" t="s">
+      <c r="F32" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="81"/>
-      <c r="M32" s="82"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="94"/>
       <c r="N32" s="56" t="s">
         <v>38</v>
       </c>
@@ -7003,16 +7939,16 @@
       <c r="E33" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="97" t="s">
+      <c r="F33" s="109" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="82"/>
-      <c r="H33" s="95"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
-      <c r="M33" s="82"/>
+      <c r="G33" s="94"/>
+      <c r="H33" s="107"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="94"/>
       <c r="N33" s="56" t="s">
         <v>38</v>
       </c>
@@ -7027,16 +7963,16 @@
       <c r="E34" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="95"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="82"/>
-      <c r="K34" s="97" t="s">
+      <c r="F34" s="107"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="L34" s="81"/>
-      <c r="M34" s="82"/>
+      <c r="L34" s="93"/>
+      <c r="M34" s="94"/>
       <c r="N34" s="56" t="s">
         <v>38</v>
       </c>
@@ -7051,16 +7987,16 @@
       <c r="E35" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="95"/>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
-      <c r="I35" s="82"/>
-      <c r="J35" s="97" t="s">
+      <c r="F35" s="107"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="94"/>
+      <c r="J35" s="109" t="s">
         <v>93</v>
       </c>
-      <c r="K35" s="81"/>
-      <c r="L35" s="81"/>
-      <c r="M35" s="82"/>
+      <c r="K35" s="93"/>
+      <c r="L35" s="93"/>
+      <c r="M35" s="94"/>
       <c r="N35" s="56" t="s">
         <v>38</v>
       </c>
@@ -7075,16 +8011,16 @@
       <c r="E36" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="95"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-      <c r="I36" s="82"/>
-      <c r="J36" s="97" t="s">
+      <c r="F36" s="107"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="94"/>
+      <c r="J36" s="109" t="s">
         <v>95</v>
       </c>
-      <c r="K36" s="81"/>
-      <c r="L36" s="81"/>
-      <c r="M36" s="82"/>
+      <c r="K36" s="93"/>
+      <c r="L36" s="93"/>
+      <c r="M36" s="94"/>
       <c r="N36" s="56" t="s">
         <v>38</v>
       </c>
@@ -7099,16 +8035,16 @@
       <c r="E37" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="97" t="s">
+      <c r="F37" s="109" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="81"/>
-      <c r="K37" s="81"/>
-      <c r="L37" s="81"/>
-      <c r="M37" s="82"/>
+      <c r="G37" s="93"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93"/>
+      <c r="J37" s="93"/>
+      <c r="K37" s="93"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="94"/>
       <c r="N37" s="56" t="s">
         <v>38</v>
       </c>
@@ -7123,14 +8059,14 @@
       <c r="E38" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="95"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="81"/>
-      <c r="I38" s="81"/>
-      <c r="J38" s="81"/>
-      <c r="K38" s="81"/>
-      <c r="L38" s="81"/>
-      <c r="M38" s="82"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="93"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
+      <c r="J38" s="93"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="94"/>
       <c r="N38" t="s">
         <v>99</v>
       </c>
@@ -7145,14 +8081,14 @@
       <c r="E39" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="95"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="81"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="81"/>
-      <c r="K39" s="81"/>
-      <c r="L39" s="81"/>
-      <c r="M39" s="82"/>
+      <c r="F39" s="107"/>
+      <c r="G39" s="93"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93"/>
+      <c r="J39" s="93"/>
+      <c r="K39" s="93"/>
+      <c r="L39" s="93"/>
+      <c r="M39" s="94"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="59" t="s">
@@ -7164,14 +8100,14 @@
       <c r="E40" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F40" s="95"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="81"/>
-      <c r="I40" s="81"/>
-      <c r="J40" s="81"/>
-      <c r="K40" s="81"/>
-      <c r="L40" s="81"/>
-      <c r="M40" s="82"/>
+      <c r="F40" s="107"/>
+      <c r="G40" s="93"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93"/>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="93"/>
+      <c r="M40" s="94"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="59" t="s">
@@ -7183,14 +8119,14 @@
       <c r="E41" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F41" s="95"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="81"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="81"/>
-      <c r="K41" s="81"/>
-      <c r="L41" s="81"/>
-      <c r="M41" s="82"/>
+      <c r="F41" s="107"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="94"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="59" t="s">
@@ -7202,14 +8138,14 @@
       <c r="E42" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F42" s="95"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="81"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="81"/>
-      <c r="M42" s="82"/>
+      <c r="F42" s="107"/>
+      <c r="G42" s="93"/>
+      <c r="H42" s="93"/>
+      <c r="I42" s="93"/>
+      <c r="J42" s="93"/>
+      <c r="K42" s="93"/>
+      <c r="L42" s="93"/>
+      <c r="M42" s="94"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="19" t="s">
@@ -7231,12 +8167,12 @@
       <c r="I43" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="83" t="s">
+      <c r="J43" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="81"/>
-      <c r="L43" s="81"/>
-      <c r="M43" s="82"/>
+      <c r="K43" s="93"/>
+      <c r="L43" s="93"/>
+      <c r="M43" s="94"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
@@ -7246,18 +8182,18 @@
         <v>19</v>
       </c>
       <c r="E44" s="42"/>
-      <c r="F44" s="83" t="s">
+      <c r="F44" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="G44" s="82"/>
-      <c r="H44" s="83" t="s">
+      <c r="G44" s="94"/>
+      <c r="H44" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81"/>
-      <c r="L44" s="81"/>
-      <c r="M44" s="82"/>
+      <c r="I44" s="93"/>
+      <c r="J44" s="93"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="93"/>
+      <c r="M44" s="94"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
@@ -7267,18 +8203,18 @@
         <v>19</v>
       </c>
       <c r="E45" s="42"/>
-      <c r="F45" s="99" t="s">
+      <c r="F45" s="110" t="s">
         <v>114</v>
       </c>
-      <c r="G45" s="100"/>
-      <c r="H45" s="100"/>
-      <c r="I45" s="101"/>
-      <c r="J45" s="83" t="s">
+      <c r="G45" s="111"/>
+      <c r="H45" s="111"/>
+      <c r="I45" s="112"/>
+      <c r="J45" s="92" t="s">
         <v>115</v>
       </c>
-      <c r="K45" s="81"/>
-      <c r="L45" s="81"/>
-      <c r="M45" s="82"/>
+      <c r="K45" s="93"/>
+      <c r="L45" s="93"/>
+      <c r="M45" s="94"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
@@ -7288,18 +8224,18 @@
         <v>19</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="83" t="s">
+      <c r="F46" s="92" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="81"/>
-      <c r="H46" s="81"/>
-      <c r="I46" s="82"/>
-      <c r="J46" s="98" t="s">
+      <c r="G46" s="93"/>
+      <c r="H46" s="93"/>
+      <c r="I46" s="94"/>
+      <c r="J46" s="113" t="s">
         <v>118</v>
       </c>
-      <c r="K46" s="93"/>
-      <c r="L46" s="93"/>
-      <c r="M46" s="94"/>
+      <c r="K46" s="105"/>
+      <c r="L46" s="105"/>
+      <c r="M46" s="106"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18" t="s">
@@ -7309,16 +8245,16 @@
         <v>19</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="87" t="s">
+      <c r="F47" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="G47" s="81"/>
-      <c r="H47" s="81"/>
-      <c r="I47" s="81"/>
-      <c r="J47" s="81"/>
-      <c r="K47" s="81"/>
-      <c r="L47" s="81"/>
-      <c r="M47" s="82"/>
+      <c r="G47" s="93"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="93"/>
+      <c r="J47" s="93"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="93"/>
+      <c r="M47" s="94"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
@@ -7328,20 +8264,20 @@
         <v>19</v>
       </c>
       <c r="E48" s="5"/>
-      <c r="F48" s="80"/>
-      <c r="G48" s="82"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="94"/>
       <c r="H48" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I48" s="87" t="s">
+      <c r="I48" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="J48" s="81"/>
-      <c r="K48" s="82"/>
-      <c r="L48" s="87" t="s">
+      <c r="J48" s="93"/>
+      <c r="K48" s="94"/>
+      <c r="L48" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="M48" s="82"/>
+      <c r="M48" s="94"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
@@ -7384,15 +8320,15 @@
         <v>19</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="80"/>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="82"/>
-      <c r="J50" s="87" t="s">
+      <c r="F50" s="99"/>
+      <c r="G50" s="93"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="94"/>
+      <c r="J50" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="K50" s="81"/>
-      <c r="L50" s="82"/>
+      <c r="K50" s="93"/>
+      <c r="L50" s="94"/>
       <c r="M50" s="12" t="s">
         <v>134</v>
       </c>
@@ -7407,16 +8343,16 @@
       <c r="E51" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F51" s="95"/>
-      <c r="G51" s="81"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="82"/>
-      <c r="L51" s="88" t="s">
+      <c r="F51" s="107"/>
+      <c r="G51" s="93"/>
+      <c r="H51" s="93"/>
+      <c r="I51" s="93"/>
+      <c r="J51" s="93"/>
+      <c r="K51" s="94"/>
+      <c r="L51" s="100" t="s">
         <v>137</v>
       </c>
-      <c r="M51" s="82"/>
+      <c r="M51" s="94"/>
     </row>
     <row r="52" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -7428,16 +8364,16 @@
       <c r="E52" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F52" s="88" t="s">
+      <c r="F52" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="81"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="81"/>
-      <c r="J52" s="81"/>
-      <c r="K52" s="81"/>
-      <c r="L52" s="81"/>
-      <c r="M52" s="82"/>
+      <c r="G52" s="93"/>
+      <c r="H52" s="93"/>
+      <c r="I52" s="93"/>
+      <c r="J52" s="93"/>
+      <c r="K52" s="93"/>
+      <c r="L52" s="93"/>
+      <c r="M52" s="94"/>
       <c r="N52" t="s">
         <v>141</v>
       </c>
@@ -7452,16 +8388,16 @@
       <c r="E53" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F53" s="88" t="s">
+      <c r="F53" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81"/>
-      <c r="K53" s="81"/>
-      <c r="L53" s="81"/>
-      <c r="M53" s="82"/>
+      <c r="G53" s="93"/>
+      <c r="H53" s="93"/>
+      <c r="I53" s="93"/>
+      <c r="J53" s="93"/>
+      <c r="K53" s="93"/>
+      <c r="L53" s="93"/>
+      <c r="M53" s="94"/>
       <c r="N53" t="s">
         <v>141</v>
       </c>
@@ -7476,16 +8412,16 @@
       <c r="E54" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F54" s="88" t="s">
+      <c r="F54" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="81"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="81"/>
-      <c r="K54" s="81"/>
-      <c r="L54" s="81"/>
-      <c r="M54" s="82"/>
+      <c r="G54" s="93"/>
+      <c r="H54" s="93"/>
+      <c r="I54" s="93"/>
+      <c r="J54" s="93"/>
+      <c r="K54" s="93"/>
+      <c r="L54" s="93"/>
+      <c r="M54" s="94"/>
       <c r="N54" t="s">
         <v>141</v>
       </c>
@@ -7500,16 +8436,16 @@
       <c r="E55" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="88" t="s">
+      <c r="F55" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G55" s="81"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="81"/>
-      <c r="K55" s="81"/>
-      <c r="L55" s="81"/>
-      <c r="M55" s="82"/>
+      <c r="G55" s="93"/>
+      <c r="H55" s="93"/>
+      <c r="I55" s="93"/>
+      <c r="J55" s="93"/>
+      <c r="K55" s="93"/>
+      <c r="L55" s="93"/>
+      <c r="M55" s="94"/>
       <c r="N55" t="s">
         <v>141</v>
       </c>
@@ -7524,16 +8460,16 @@
       <c r="E56" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="88" t="s">
+      <c r="F56" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="81"/>
-      <c r="H56" s="81"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="81"/>
-      <c r="K56" s="81"/>
-      <c r="L56" s="81"/>
-      <c r="M56" s="82"/>
+      <c r="G56" s="93"/>
+      <c r="H56" s="93"/>
+      <c r="I56" s="93"/>
+      <c r="J56" s="93"/>
+      <c r="K56" s="93"/>
+      <c r="L56" s="93"/>
+      <c r="M56" s="94"/>
       <c r="N56" t="s">
         <v>141</v>
       </c>
@@ -7548,16 +8484,16 @@
       <c r="E57" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F57" s="88" t="s">
+      <c r="F57" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="81"/>
-      <c r="K57" s="81"/>
-      <c r="L57" s="81"/>
-      <c r="M57" s="82"/>
+      <c r="G57" s="93"/>
+      <c r="H57" s="93"/>
+      <c r="I57" s="93"/>
+      <c r="J57" s="93"/>
+      <c r="K57" s="93"/>
+      <c r="L57" s="93"/>
+      <c r="M57" s="94"/>
       <c r="N57" t="s">
         <v>141</v>
       </c>
@@ -7572,16 +8508,16 @@
       <c r="E58" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F58" s="88" t="s">
+      <c r="F58" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="81"/>
-      <c r="H58" s="81"/>
-      <c r="I58" s="81"/>
-      <c r="J58" s="81"/>
-      <c r="K58" s="81"/>
-      <c r="L58" s="81"/>
-      <c r="M58" s="82"/>
+      <c r="G58" s="93"/>
+      <c r="H58" s="93"/>
+      <c r="I58" s="93"/>
+      <c r="J58" s="93"/>
+      <c r="K58" s="93"/>
+      <c r="L58" s="93"/>
+      <c r="M58" s="94"/>
       <c r="N58" t="s">
         <v>141</v>
       </c>
@@ -7596,16 +8532,16 @@
       <c r="E59" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="F59" s="88" t="s">
+      <c r="F59" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G59" s="81"/>
-      <c r="H59" s="81"/>
-      <c r="I59" s="81"/>
-      <c r="J59" s="81"/>
-      <c r="K59" s="81"/>
-      <c r="L59" s="81"/>
-      <c r="M59" s="82"/>
+      <c r="G59" s="93"/>
+      <c r="H59" s="93"/>
+      <c r="I59" s="93"/>
+      <c r="J59" s="93"/>
+      <c r="K59" s="93"/>
+      <c r="L59" s="93"/>
+      <c r="M59" s="94"/>
       <c r="N59" t="s">
         <v>141</v>
       </c>
@@ -7620,16 +8556,16 @@
       <c r="E60" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F60" s="88" t="s">
+      <c r="F60" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G60" s="81"/>
-      <c r="H60" s="81"/>
-      <c r="I60" s="81"/>
-      <c r="J60" s="81"/>
-      <c r="K60" s="81"/>
-      <c r="L60" s="81"/>
-      <c r="M60" s="82"/>
+      <c r="G60" s="93"/>
+      <c r="H60" s="93"/>
+      <c r="I60" s="93"/>
+      <c r="J60" s="93"/>
+      <c r="K60" s="93"/>
+      <c r="L60" s="93"/>
+      <c r="M60" s="94"/>
       <c r="N60" t="s">
         <v>141</v>
       </c>
@@ -7644,16 +8580,16 @@
       <c r="E61" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="F61" s="88" t="s">
+      <c r="F61" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G61" s="81"/>
-      <c r="H61" s="81"/>
-      <c r="I61" s="81"/>
-      <c r="J61" s="81"/>
-      <c r="K61" s="81"/>
-      <c r="L61" s="81"/>
-      <c r="M61" s="82"/>
+      <c r="G61" s="93"/>
+      <c r="H61" s="93"/>
+      <c r="I61" s="93"/>
+      <c r="J61" s="93"/>
+      <c r="K61" s="93"/>
+      <c r="L61" s="93"/>
+      <c r="M61" s="94"/>
       <c r="N61" t="s">
         <v>141</v>
       </c>
@@ -7681,14 +8617,60 @@
       <c r="J63" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="K63" s="80"/>
-      <c r="L63" s="82"/>
+      <c r="K63" s="99"/>
+      <c r="L63" s="94"/>
       <c r="M63" s="53" t="s">
         <v>166</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="F51:K51"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F11:M11"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F17:M17"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="F47:M47"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F61:M61"/>
+    <mergeCell ref="H44:M44"/>
     <mergeCell ref="F60:M60"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="K18:L18"/>
@@ -7705,52 +8687,6 @@
     <mergeCell ref="F26:M26"/>
     <mergeCell ref="H33:M33"/>
     <mergeCell ref="F23:M23"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="F47:M47"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F61:M61"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="F11:M11"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F17:M17"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="F51:K51"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="F38:M38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7811,112 +8747,112 @@
     </row>
     <row r="4" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:23" x14ac:dyDescent="0.15">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="80" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="103" t="s">
+      <c r="C5" s="81" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="6" spans="2:23" x14ac:dyDescent="0.15">
-      <c r="B6" s="104" t="s">
+      <c r="B6" s="82" t="s">
         <v>401</v>
       </c>
-      <c r="C6" s="105" t="s">
+      <c r="C6" s="83" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="7" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="106" t="s">
+      <c r="B7" s="84" t="s">
         <v>403</v>
       </c>
-      <c r="C7" s="107" t="s">
+      <c r="C7" s="85" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="8" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="E8" s="108" t="s">
+      <c r="E8" s="86" t="s">
         <v>407</v>
       </c>
-      <c r="F8" s="109" t="s">
+      <c r="F8" s="87" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="109" t="s">
+      <c r="G8" s="87" t="s">
         <v>409</v>
       </c>
-      <c r="H8" s="109" t="s">
+      <c r="H8" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="I8" s="109" t="s">
+      <c r="I8" s="87" t="s">
         <v>411</v>
       </c>
-      <c r="J8" s="109" t="s">
+      <c r="J8" s="87" t="s">
         <v>412</v>
       </c>
-      <c r="K8" s="109" t="s">
+      <c r="K8" s="87" t="s">
         <v>413</v>
       </c>
-      <c r="L8" s="109" t="s">
+      <c r="L8" s="87" t="s">
         <v>414</v>
       </c>
-      <c r="M8" s="109" t="s">
+      <c r="M8" s="87" t="s">
         <v>415</v>
       </c>
-      <c r="N8" s="109" t="s">
+      <c r="N8" s="87" t="s">
         <v>416</v>
       </c>
-      <c r="O8" s="109" t="s">
+      <c r="O8" s="87" t="s">
         <v>417</v>
       </c>
-      <c r="P8" s="109" t="s">
+      <c r="P8" s="87" t="s">
         <v>418</v>
       </c>
-      <c r="Q8" s="109" t="s">
+      <c r="Q8" s="87" t="s">
         <v>419</v>
       </c>
-      <c r="R8" s="109" t="s">
+      <c r="R8" s="87" t="s">
         <v>420</v>
       </c>
-      <c r="S8" s="109" t="s">
+      <c r="S8" s="87" t="s">
         <v>421</v>
       </c>
-      <c r="T8" s="109" t="s">
+      <c r="T8" s="87" t="s">
         <v>422</v>
       </c>
-      <c r="U8" s="109" t="s">
+      <c r="U8" s="87" t="s">
         <v>423</v>
       </c>
-      <c r="V8" s="109" t="s">
+      <c r="V8" s="87" t="s">
         <v>424</v>
       </c>
-      <c r="W8" s="110" t="s">
+      <c r="W8" s="88" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="9" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="E9" s="111" t="s">
+      <c r="E9" s="89" t="s">
         <v>428</v>
       </c>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="111" t="s">
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="91"/>
+      <c r="K9" s="89" t="s">
         <v>427</v>
       </c>
-      <c r="L9" s="112"/>
-      <c r="M9" s="112"/>
-      <c r="N9" s="112"/>
-      <c r="O9" s="112"/>
-      <c r="P9" s="112"/>
-      <c r="Q9" s="112"/>
-      <c r="R9" s="112"/>
-      <c r="S9" s="112"/>
-      <c r="T9" s="112"/>
-      <c r="U9" s="112"/>
-      <c r="V9" s="112"/>
-      <c r="W9" s="113"/>
+      <c r="L9" s="90"/>
+      <c r="M9" s="90"/>
+      <c r="N9" s="90"/>
+      <c r="O9" s="90"/>
+      <c r="P9" s="90"/>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="90"/>
+      <c r="U9" s="90"/>
+      <c r="V9" s="90"/>
+      <c r="W9" s="91"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.15">
       <c r="E11" t="s">

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612819BE-368A-4C5B-9E81-5526FE6B424C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119C2E0D-8783-41D7-A8B4-2D6E87857A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="75" windowWidth="20025" windowHeight="15975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="534">
   <si>
     <t>OPL2 (YM3812) + ADPCM  [MSX-AUDIO(Y8950) Compatible]</t>
   </si>
@@ -1371,118 +1371,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>SCC BANK2-BANK#63</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9800h-981Fh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9820h-983Fh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9840h-985Fh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9860h-987Fh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>RW</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>9880h-9881h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9882h-9883h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9884h-9885h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9886h-9887h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9888h-9889h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>988Ah</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>988Bh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>988Ch</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>988Dh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>988Eh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>988Fh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>WO</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>9890h-989Fh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>98A0h-98BFh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>98C0h-98DFh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>98E0h-98FFh</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9900h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>SCC Register</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>9901h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9902h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9903h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9904h</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>SCC Ch.A ステレオ定位</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1503,18 +1403,657 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>説明省略</t>
-    <rPh sb="0" eb="4">
-      <t>セツメイショウリャク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1で左端、128で中央、255で右端。デフォルト128</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>RAM Mode=0 の時のみ利用可能、1で左端、128で中央、255で右端。デフォルト128</t>
+    <t>SCC BANK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4000h-5FFFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6000h-7FFFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8000h-9FFFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A000h-BFFFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK0～BANK3 には、バンクレジスタがある。、バンクレジスタに値nを書き込むことによって、対応する BANK#n が出現する。</t>
+    <rPh sb="35" eb="36">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>シュツゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中略</t>
+    <rPh sb="0" eb="2">
+      <t>チュウリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SerialSRAM 0x02000-0x03FFF に対応し、ROM の扱い</t>
+    <rPh sb="28" eb="30">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SerialSRAM 0x00000-0x01FFF に対応し、ROM の扱い</t>
+    <rPh sb="28" eb="30">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SerialSRAM 0x1E000-0x1FFFF に対応し、ROM の扱い</t>
+    <rPh sb="28" eb="30">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#16</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SerialSRAM 0x20000-0x21FFF に対応し、RAM の扱い</t>
+    <rPh sb="28" eb="30">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#17</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#31</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SerialSRAM 0x3E000-0x3FFFF に対応し、RAM の扱い</t>
+    <rPh sb="28" eb="30">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SerialSRAM 0x22000-0x23FFF に対応し、RAM の扱い</t>
+    <rPh sb="28" eb="30">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK0 に RAM である BANK#16～31 を出現させても、その BANK# へ書き込むことはできない。BANK0 は基本的にリードオンリーである。ただし、4XFBh への書き込みは、RAM Mode への書き込みとなる。</t>
+    <rPh sb="28" eb="30">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="64" eb="67">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="91" eb="92">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="108" eb="109">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="110" eb="111">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>読み出しは、選択されている BANK# の値になることに注意。</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>チュウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode = 1 の場合、さらに 4XFC～4XFFh は、バンクレジスタになる。これも書き込みのみで、読み出すと BANK# の値になる。</t>
+    <rPh sb="14" eb="16">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode への書き込み、並びにバンクレジスタへの書き込みは、BANK# へ書き込まれない。</t>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#32</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未接続</t>
+    <rPh sb="0" eb="3">
+      <t>ミセツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#62</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#63</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#64</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#255</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode = 0 にすると、バンクレジスタのアドレスが変化する。</t>
+    <rPh sb="31" eb="33">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9800h-981Fh, 7800h-781Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9820h-983Fh, 7820h-783Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9840h-985Fh, 7840h-785Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9860h-987Fh, 7860h-787Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9880h-9881h, 7880h-7881h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9882h-9883h, 7882h-7883h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9884h-9885h, 7884h-7885h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9886h-9887h, 7886h-7887h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9888h-9889h, 7888h-7889h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Ah, 788Ah</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Bh, 788Bh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Ch, 788Ch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Dh, 788Dh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Eh, 788Eh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>988Fh, 788Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9890h-989Fh, 7890h-789Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>98C0h-98DFh, 78C0h-78DFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>98A0h-98BFh, 78A0h-78BFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>98E0h-98FFh, 78E0h-78FFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9900h, 7900h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9901h, 7901h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9903h, 7903h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9904h, 7904h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCCレジスタ ( RAM Mode = 0 で BANK2-BANK#63, または RAM Mode = 1 で BANK1-BANK#63  ), 9xxxhはBANK2に出現した場合、7xxxh は BANK1に出現した場合のアドレス。</t>
+    <rPh sb="89" eb="91">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9880h-988Fh のミラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未使用</t>
+    <rPh sb="0" eb="3">
+      <t>ミシヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モードレジスタ、実体は 1byte</t>
+    <rPh sb="8" eb="10">
+      <t>ジッタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力スイッチ</t>
+    <rPh sb="0" eb="2">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.A 音量</t>
+    <rPh sb="5" eb="7">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.B 音量</t>
+    <rPh sb="5" eb="7">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.C 音量</t>
+    <rPh sb="5" eb="7">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.D 音量</t>
+    <rPh sb="5" eb="7">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.E 音量</t>
+    <rPh sb="5" eb="7">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.A 波形メモリ</t>
+    <rPh sb="5" eb="7">
+      <t>ハケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.B 波形メモリ</t>
+    <rPh sb="5" eb="7">
+      <t>ハケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.C 波形メモリ</t>
+    <rPh sb="5" eb="7">
+      <t>ハケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.D/E 波形メモリ</t>
+    <rPh sb="7" eb="9">
+      <t>ハケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.A 周波数レジスタ</t>
+    <rPh sb="5" eb="8">
+      <t>シュウハスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.B 周波数レジスタ</t>
+    <rPh sb="5" eb="8">
+      <t>シュウハスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.C 周波数レジスタ</t>
+    <rPh sb="5" eb="8">
+      <t>シュウハスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.D 周波数レジスタ</t>
+    <rPh sb="5" eb="8">
+      <t>シュウハスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ch.E 周波数レジスタ</t>
+    <rPh sb="5" eb="8">
+      <t>シュウハスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9902h, 7902h</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9000h-97FFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK2(8000-9FFFh) Bank Register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1で左端、128で中央、255で右端。デフォルト128、読み出し結果は未定義</t>
+    <rPh sb="28" eb="29">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>ミテイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>読み出し結果は未定義</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ミテイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9905h-9FFFh, 7905h-7FEFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7FF0h-7FFFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Memory Mapped I/O</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上の表に記載の動作を継承</t>
+    <rPh sb="0" eb="1">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ケイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6000h-77FFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8000h-8FFFh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>読み出し結果は未定義</t>
+  </si>
+  <si>
+    <t>アクセス禁止。読み書き結果は未定義。将来予約。</t>
+    <rPh sb="4" eb="6">
+      <t>キンシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ミテイギ</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>ショウライヨヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセス禁止</t>
+    <rPh sb="4" eb="6">
+      <t>キンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#0 のミラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BANK#30 のミラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode = 0 で BANK2 の場合、または、RAM Mode = 1 で BANK1 の場合にのみ SCCレジスタになる。
+それ以外では BANK#31 のミラー。</t>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>イガイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1648,7 +2187,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -2143,32 +2682,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2178,7 +2691,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2444,20 +2957,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2467,22 +3013,19 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2497,41 +3040,22 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3105,14 +3629,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:O55"/>
+  <dimension ref="A2:O94"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.75" style="79" customWidth="1"/>
     <col min="2" max="2" width="3.25" style="79" customWidth="1"/>
-    <col min="3" max="3" width="15.25" style="79" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.875" style="79" customWidth="1"/>
     <col min="4" max="4" width="4" style="79" customWidth="1"/>
-    <col min="5" max="5" width="30" style="79" customWidth="1"/>
+    <col min="5" max="5" width="45" style="79" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="79" customWidth="1"/>
     <col min="15" max="15" width="90.875" style="79" bestFit="1" customWidth="1"/>
   </cols>
@@ -3176,13 +3700,13 @@
       <c r="F4" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G4" s="99"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="94"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="112"/>
       <c r="N4" s="66" t="s">
         <v>205</v>
       </c>
@@ -3203,16 +3727,16 @@
       <c r="F5" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G5" s="95" t="s">
+      <c r="G5" s="114" t="s">
         <v>209</v>
       </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="94"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="111"/>
+      <c r="N5" s="112"/>
       <c r="O5" s="49" t="s">
         <v>210</v>
       </c>
@@ -3230,16 +3754,16 @@
       <c r="F6" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G6" s="95" t="s">
+      <c r="G6" s="114" t="s">
         <v>209</v>
       </c>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="94"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="112"/>
       <c r="O6" s="49" t="s">
         <v>210</v>
       </c>
@@ -3257,16 +3781,16 @@
       <c r="F7" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="95" t="s">
+      <c r="G7" s="114" t="s">
         <v>209</v>
       </c>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="94"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="111"/>
+      <c r="N7" s="112"/>
       <c r="O7" s="49" t="s">
         <v>210</v>
       </c>
@@ -3284,16 +3808,16 @@
       <c r="F8" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G8" s="95" t="s">
+      <c r="G8" s="114" t="s">
         <v>209</v>
       </c>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
-      <c r="N8" s="94"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="112"/>
       <c r="O8" s="49" t="s">
         <v>210</v>
       </c>
@@ -3311,16 +3835,16 @@
       <c r="F9" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G9" s="92" t="s">
+      <c r="G9" s="113" t="s">
         <v>218</v>
       </c>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="94"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="111"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="111"/>
+      <c r="N9" s="112"/>
       <c r="O9" s="49" t="s">
         <v>219</v>
       </c>
@@ -3338,16 +3862,16 @@
       <c r="F10" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G10" s="92" t="s">
+      <c r="G10" s="113" t="s">
         <v>218</v>
       </c>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="93"/>
-      <c r="N10" s="94"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="112"/>
       <c r="O10" s="49" t="s">
         <v>219</v>
       </c>
@@ -3365,16 +3889,16 @@
       <c r="F11" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G11" s="100" t="s">
+      <c r="G11" s="117" t="s">
         <v>222</v>
       </c>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
-      <c r="M11" s="93"/>
-      <c r="N11" s="94"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="111"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="111"/>
+      <c r="N11" s="112"/>
       <c r="O11" s="50" t="s">
         <v>397</v>
       </c>
@@ -3392,16 +3916,16 @@
       <c r="F12" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="100" t="s">
+      <c r="G12" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="94"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="112"/>
       <c r="O12" s="50" t="s">
         <v>397</v>
       </c>
@@ -3419,16 +3943,16 @@
       <c r="F13" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G13" s="96" t="s">
+      <c r="G13" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="93"/>
-      <c r="K13" s="93"/>
-      <c r="L13" s="93"/>
-      <c r="M13" s="93"/>
-      <c r="N13" s="94"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="112"/>
       <c r="O13" s="50" t="s">
         <v>397</v>
       </c>
@@ -3446,16 +3970,16 @@
       <c r="F14" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G14" s="96" t="s">
+      <c r="G14" s="115" t="s">
         <v>228</v>
       </c>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="93"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="93"/>
-      <c r="N14" s="94"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="112"/>
       <c r="O14" s="50" t="s">
         <v>397</v>
       </c>
@@ -3473,16 +3997,16 @@
       <c r="F15" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G15" s="98" t="s">
+      <c r="G15" s="118" t="s">
         <v>230</v>
       </c>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="93"/>
-      <c r="K15" s="93"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="94"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="112"/>
       <c r="O15" s="50" t="s">
         <v>397</v>
       </c>
@@ -3500,16 +4024,16 @@
       <c r="F16" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G16" s="98" t="s">
+      <c r="G16" s="118" t="s">
         <v>233</v>
       </c>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="93"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="94"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="112"/>
       <c r="O16" s="50" t="s">
         <v>397</v>
       </c>
@@ -3527,13 +4051,13 @@
       <c r="F17" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G17" s="97"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="94"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="112"/>
       <c r="N17" s="10" t="s">
         <v>176</v>
       </c>
@@ -3554,14 +4078,14 @@
       <c r="F18" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G18" s="96"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="93"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="94"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="111"/>
+      <c r="N18" s="112"/>
       <c r="O18" s="50" t="s">
         <v>398</v>
       </c>
@@ -3579,14 +4103,14 @@
       <c r="F19" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="96"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="94"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="111"/>
+      <c r="N19" s="112"/>
       <c r="O19" s="50" t="s">
         <v>398</v>
       </c>
@@ -3604,14 +4128,14 @@
       <c r="F20" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G20" s="96"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="93"/>
-      <c r="J20" s="93"/>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="93"/>
-      <c r="N20" s="94"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="112"/>
       <c r="O20" s="50" t="s">
         <v>398</v>
       </c>
@@ -3745,11 +4269,11 @@
       <c r="G26" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="H26" s="99"/>
-      <c r="I26" s="93"/>
-      <c r="J26" s="93"/>
-      <c r="K26" s="93"/>
-      <c r="L26" s="94"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="112"/>
       <c r="M26" s="32" t="s">
         <v>173</v>
       </c>
@@ -3773,16 +4297,16 @@
       <c r="F27" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="92" t="s">
+      <c r="G27" s="113" t="s">
         <v>218</v>
       </c>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="94"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="111"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="111"/>
+      <c r="N27" s="112"/>
       <c r="O27" s="49" t="s">
         <v>219</v>
       </c>
@@ -3800,727 +4324,1018 @@
       <c r="F28" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="92" t="s">
+      <c r="G28" s="113" t="s">
         <v>218</v>
       </c>
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="94"/>
+      <c r="H28" s="111"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="112"/>
       <c r="O28" s="49" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="30" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B30" s="79" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="C31" s="93" t="s">
+        <v>526</v>
+      </c>
+      <c r="D31" s="100" t="s">
+        <v>448</v>
+      </c>
+      <c r="E31" s="100" t="s">
+        <v>499</v>
+      </c>
+      <c r="F31" s="101" t="s">
+        <v>519</v>
+      </c>
+      <c r="G31" s="105" t="s">
+        <v>499</v>
+      </c>
+      <c r="H31" s="106"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="106"/>
+      <c r="L31" s="106"/>
+      <c r="M31" s="106"/>
+      <c r="N31" s="106"/>
+      <c r="O31" s="81" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="C32" s="89" t="s">
+        <v>527</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="G32" s="103" t="s">
+        <v>499</v>
+      </c>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="104"/>
+      <c r="N32" s="104"/>
+      <c r="O32" s="83" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="33" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C33" s="89" t="s">
+        <v>517</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="G33" s="103" t="s">
+        <v>218</v>
+      </c>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="104"/>
+      <c r="M33" s="104"/>
+      <c r="N33" s="104"/>
+      <c r="O33" s="83" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C34" s="89" t="s">
+        <v>474</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="31" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C31" s="115" t="s">
-        <v>252</v>
-      </c>
-      <c r="D31" s="116" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="116" t="s">
-        <v>214</v>
-      </c>
-      <c r="F31" s="121" t="s">
+      <c r="E34" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F34" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G31" s="122" t="s">
-        <v>218</v>
-      </c>
-      <c r="H31" s="123"/>
-      <c r="I31" s="123"/>
-      <c r="J31" s="123"/>
-      <c r="K31" s="123"/>
-      <c r="L31" s="123"/>
-      <c r="M31" s="123"/>
-      <c r="N31" s="124"/>
-      <c r="O31" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C32" s="117" t="s">
+      <c r="G34" s="103" t="s">
+        <v>507</v>
+      </c>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="104"/>
+      <c r="K34" s="104"/>
+      <c r="L34" s="104"/>
+      <c r="M34" s="104"/>
+      <c r="N34" s="104"/>
+      <c r="O34" s="83"/>
+    </row>
+    <row r="35" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C35" s="89" t="s">
+        <v>475</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" s="103" t="s">
+        <v>508</v>
+      </c>
+      <c r="H35" s="104"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="104"/>
+      <c r="K35" s="104"/>
+      <c r="L35" s="104"/>
+      <c r="M35" s="104"/>
+      <c r="N35" s="104"/>
+      <c r="O35" s="83"/>
+    </row>
+    <row r="36" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C36" s="89" t="s">
+        <v>476</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="103" t="s">
+        <v>509</v>
+      </c>
+      <c r="H36" s="104"/>
+      <c r="I36" s="104"/>
+      <c r="J36" s="104"/>
+      <c r="K36" s="104"/>
+      <c r="L36" s="104"/>
+      <c r="M36" s="104"/>
+      <c r="N36" s="104"/>
+      <c r="O36" s="83"/>
+    </row>
+    <row r="37" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C37" s="89" t="s">
+        <v>477</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="103" t="s">
+        <v>510</v>
+      </c>
+      <c r="H37" s="104"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="104"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="104"/>
+      <c r="M37" s="104"/>
+      <c r="N37" s="104"/>
+      <c r="O37" s="83"/>
+    </row>
+    <row r="38" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C38" s="89" t="s">
+        <v>478</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D32" s="114" t="s">
+      <c r="E38" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G38" s="103" t="s">
+        <v>511</v>
+      </c>
+      <c r="H38" s="104"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="104"/>
+      <c r="K38" s="104"/>
+      <c r="L38" s="104"/>
+      <c r="M38" s="104"/>
+      <c r="N38" s="104"/>
+      <c r="O38" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="39" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C39" s="89" t="s">
+        <v>479</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="103" t="s">
+        <v>512</v>
+      </c>
+      <c r="H39" s="104"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="104"/>
+      <c r="L39" s="104"/>
+      <c r="M39" s="104"/>
+      <c r="N39" s="104"/>
+      <c r="O39" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="40" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C40" s="89" t="s">
+        <v>480</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="103" t="s">
+        <v>513</v>
+      </c>
+      <c r="H40" s="104"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="104"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="104"/>
+      <c r="M40" s="104"/>
+      <c r="N40" s="104"/>
+      <c r="O40" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="41" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C41" s="89" t="s">
+        <v>481</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G41" s="103" t="s">
+        <v>514</v>
+      </c>
+      <c r="H41" s="104"/>
+      <c r="I41" s="104"/>
+      <c r="J41" s="104"/>
+      <c r="K41" s="104"/>
+      <c r="L41" s="104"/>
+      <c r="M41" s="104"/>
+      <c r="N41" s="104"/>
+      <c r="O41" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="42" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C42" s="89" t="s">
+        <v>482</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" s="103" t="s">
+        <v>515</v>
+      </c>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="104"/>
+      <c r="M42" s="104"/>
+      <c r="N42" s="104"/>
+      <c r="O42" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="43" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C43" s="89" t="s">
+        <v>483</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G43" s="103" t="s">
+        <v>502</v>
+      </c>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="104"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="104"/>
+      <c r="M43" s="104"/>
+      <c r="N43" s="104"/>
+      <c r="O43" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="44" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C44" s="89" t="s">
+        <v>484</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="103" t="s">
+        <v>503</v>
+      </c>
+      <c r="H44" s="104"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="104"/>
+      <c r="K44" s="104"/>
+      <c r="L44" s="104"/>
+      <c r="M44" s="104"/>
+      <c r="N44" s="104"/>
+      <c r="O44" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="45" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C45" s="89" t="s">
+        <v>485</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G45" s="103" t="s">
+        <v>504</v>
+      </c>
+      <c r="H45" s="104"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="104"/>
+      <c r="K45" s="104"/>
+      <c r="L45" s="104"/>
+      <c r="M45" s="104"/>
+      <c r="N45" s="104"/>
+      <c r="O45" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="46" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C46" s="89" t="s">
+        <v>486</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G46" s="103" t="s">
+        <v>505</v>
+      </c>
+      <c r="H46" s="104"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="104"/>
+      <c r="K46" s="104"/>
+      <c r="L46" s="104"/>
+      <c r="M46" s="104"/>
+      <c r="N46" s="104"/>
+      <c r="O46" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="47" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C47" s="89" t="s">
+        <v>487</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G47" s="103" t="s">
+        <v>506</v>
+      </c>
+      <c r="H47" s="104"/>
+      <c r="I47" s="104"/>
+      <c r="J47" s="104"/>
+      <c r="K47" s="104"/>
+      <c r="L47" s="104"/>
+      <c r="M47" s="104"/>
+      <c r="N47" s="104"/>
+      <c r="O47" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="48" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C48" s="89" t="s">
+        <v>488</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G48" s="103" t="s">
+        <v>501</v>
+      </c>
+      <c r="H48" s="104"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="104"/>
+      <c r="K48" s="104"/>
+      <c r="L48" s="104"/>
+      <c r="M48" s="104"/>
+      <c r="N48" s="104"/>
+      <c r="O48" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C49" s="89" t="s">
+        <v>489</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G49" s="103" t="s">
+        <v>498</v>
+      </c>
+      <c r="H49" s="104"/>
+      <c r="I49" s="104"/>
+      <c r="J49" s="104"/>
+      <c r="K49" s="104"/>
+      <c r="L49" s="104"/>
+      <c r="M49" s="104"/>
+      <c r="N49" s="104"/>
+      <c r="O49" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C50" s="89" t="s">
+        <v>491</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G50" s="103" t="s">
+        <v>530</v>
+      </c>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="104"/>
+      <c r="K50" s="104"/>
+      <c r="L50" s="104"/>
+      <c r="M50" s="104"/>
+      <c r="N50" s="104"/>
+      <c r="O50" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C51" s="89" t="s">
+        <v>490</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G51" s="103" t="s">
+        <v>530</v>
+      </c>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="104"/>
+      <c r="K51" s="104"/>
+      <c r="L51" s="104"/>
+      <c r="M51" s="104"/>
+      <c r="N51" s="104"/>
+      <c r="O51" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C52" s="89" t="s">
+        <v>492</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G52" s="103" t="s">
+        <v>500</v>
+      </c>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="104"/>
+      <c r="M52" s="104"/>
+      <c r="N52" s="104"/>
+      <c r="O52" s="83" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C53" s="89" t="s">
+        <v>493</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G53" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="104"/>
+      <c r="M53" s="104"/>
+      <c r="N53" s="104"/>
+      <c r="O53" s="83" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C54" s="89" t="s">
+        <v>494</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G54" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="104"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="104"/>
+      <c r="M54" s="104"/>
+      <c r="N54" s="104"/>
+      <c r="O54" s="83" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C55" s="89" t="s">
+        <v>516</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E55" s="22" t="s">
         <v>435</v>
       </c>
-      <c r="E32" s="114" t="s">
+      <c r="F55" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G55" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="104"/>
+      <c r="K55" s="104"/>
+      <c r="L55" s="104"/>
+      <c r="M55" s="104"/>
+      <c r="N55" s="104"/>
+      <c r="O55" s="83" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C56" s="89" t="s">
+        <v>495</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="F56" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G56" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="104"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="104"/>
+      <c r="M56" s="104"/>
+      <c r="N56" s="104"/>
+      <c r="O56" s="83" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C57" s="89" t="s">
+        <v>496</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="F57" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G57" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="104"/>
+      <c r="K57" s="104"/>
+      <c r="L57" s="104"/>
+      <c r="M57" s="104"/>
+      <c r="N57" s="104"/>
+      <c r="O57" s="83" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C58" s="89" t="s">
+        <v>522</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F58" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="G58" s="103" t="s">
+        <v>530</v>
+      </c>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="104"/>
+      <c r="K58" s="104"/>
+      <c r="L58" s="104"/>
+      <c r="M58" s="104"/>
+      <c r="N58" s="104"/>
+      <c r="O58" s="83" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="90" t="s">
+        <v>523</v>
+      </c>
+      <c r="D59" s="102" t="s">
+        <v>431</v>
+      </c>
+      <c r="E59" s="91" t="s">
+        <v>524</v>
+      </c>
+      <c r="F59" s="91"/>
+      <c r="G59" s="107" t="s">
+        <v>525</v>
+      </c>
+      <c r="H59" s="108"/>
+      <c r="I59" s="108"/>
+      <c r="J59" s="108"/>
+      <c r="K59" s="108"/>
+      <c r="L59" s="108"/>
+      <c r="M59" s="108"/>
+      <c r="N59" s="108"/>
+      <c r="O59" s="85"/>
+    </row>
+    <row r="61" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C62" s="93" t="s">
+        <v>439</v>
+      </c>
+      <c r="D62" s="94"/>
+      <c r="E62" s="95"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C63" s="89" t="s">
+        <v>440</v>
+      </c>
+      <c r="D63" s="92" t="s">
+        <v>448</v>
+      </c>
+      <c r="E63" s="96" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C64" s="89" t="s">
+        <v>441</v>
+      </c>
+      <c r="D64" s="92" t="s">
+        <v>448</v>
+      </c>
+      <c r="E64" s="96" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C65" s="89" t="s">
+        <v>442</v>
+      </c>
+      <c r="D65" s="92" t="s">
+        <v>448</v>
+      </c>
+      <c r="E65" s="96" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C66" s="90" t="s">
+        <v>443</v>
+      </c>
+      <c r="D66" s="97" t="s">
+        <v>448</v>
+      </c>
+      <c r="E66" s="98" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C68" s="79" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="69" spans="3:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C70" s="93" t="s">
+        <v>450</v>
+      </c>
+      <c r="D70" s="94"/>
+      <c r="E70" s="95" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C71" s="89" t="s">
+        <v>451</v>
+      </c>
+      <c r="D71" s="92"/>
+      <c r="E71" s="96" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C72" s="89" t="s">
+        <v>452</v>
+      </c>
+      <c r="D72" s="92"/>
+      <c r="E72" s="96"/>
+    </row>
+    <row r="73" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C73" s="89" t="s">
         <v>453</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G32" s="122" t="s">
+      <c r="D73" s="92"/>
+      <c r="E73" s="96" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C74" s="89" t="s">
+        <v>457</v>
+      </c>
+      <c r="D74" s="92"/>
+      <c r="E74" s="96" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C75" s="89" t="s">
+        <v>459</v>
+      </c>
+      <c r="D75" s="92"/>
+      <c r="E75" s="96" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="76" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C76" s="89" t="s">
+        <v>452</v>
+      </c>
+      <c r="D76" s="92"/>
+      <c r="E76" s="96"/>
+    </row>
+    <row r="77" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C77" s="89" t="s">
+        <v>460</v>
+      </c>
+      <c r="D77" s="92"/>
+      <c r="E77" s="96" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C78" s="89" t="s">
+        <v>467</v>
+      </c>
+      <c r="D78" s="92"/>
+      <c r="E78" s="96" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C79" s="89" t="s">
+        <v>452</v>
+      </c>
+      <c r="D79" s="92"/>
+      <c r="E79" s="96"/>
+    </row>
+    <row r="80" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C80" s="89" t="s">
+        <v>469</v>
+      </c>
+      <c r="D80" s="92"/>
+      <c r="E80" s="96" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="C81" s="89" t="s">
+        <v>470</v>
+      </c>
+      <c r="D81" s="92"/>
+      <c r="E81" s="99" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C82" s="89" t="s">
+        <v>471</v>
+      </c>
+      <c r="D82" s="92"/>
+      <c r="E82" s="96" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C83" s="89" t="s">
+        <v>452</v>
+      </c>
+      <c r="D83" s="92"/>
+      <c r="E83" s="96"/>
+    </row>
+    <row r="84" spans="3:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C84" s="90" t="s">
+        <v>472</v>
+      </c>
+      <c r="D84" s="97"/>
+      <c r="E84" s="98" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C87" s="79" t="s">
         <v>463</v>
       </c>
-      <c r="H32" s="123"/>
-      <c r="I32" s="123"/>
-      <c r="J32" s="123"/>
-      <c r="K32" s="123"/>
-      <c r="L32" s="123"/>
-      <c r="M32" s="123"/>
-      <c r="N32" s="124"/>
-      <c r="O32" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="33" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="117" t="s">
-        <v>432</v>
-      </c>
-      <c r="D33" s="114" t="s">
-        <v>435</v>
-      </c>
-      <c r="E33" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G33" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H33" s="123"/>
-      <c r="I33" s="123"/>
-      <c r="J33" s="123"/>
-      <c r="K33" s="123"/>
-      <c r="L33" s="123"/>
-      <c r="M33" s="123"/>
-      <c r="N33" s="124"/>
-      <c r="O33" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="34" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C34" s="117" t="s">
-        <v>433</v>
-      </c>
-      <c r="D34" s="114" t="s">
-        <v>435</v>
-      </c>
-      <c r="E34" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G34" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H34" s="123"/>
-      <c r="I34" s="123"/>
-      <c r="J34" s="123"/>
-      <c r="K34" s="123"/>
-      <c r="L34" s="123"/>
-      <c r="M34" s="123"/>
-      <c r="N34" s="124"/>
-      <c r="O34" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="35" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C35" s="117" t="s">
-        <v>434</v>
-      </c>
-      <c r="D35" s="114" t="s">
-        <v>435</v>
-      </c>
-      <c r="E35" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G35" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H35" s="123"/>
-      <c r="I35" s="123"/>
-      <c r="J35" s="123"/>
-      <c r="K35" s="123"/>
-      <c r="L35" s="123"/>
-      <c r="M35" s="123"/>
-      <c r="N35" s="124"/>
-      <c r="O35" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="36" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C36" s="117" t="s">
-        <v>436</v>
-      </c>
-      <c r="D36" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E36" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G36" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H36" s="123"/>
-      <c r="I36" s="123"/>
-      <c r="J36" s="123"/>
-      <c r="K36" s="123"/>
-      <c r="L36" s="123"/>
-      <c r="M36" s="123"/>
-      <c r="N36" s="124"/>
-      <c r="O36" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="37" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C37" s="117" t="s">
-        <v>437</v>
-      </c>
-      <c r="D37" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E37" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G37" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H37" s="123"/>
-      <c r="I37" s="123"/>
-      <c r="J37" s="123"/>
-      <c r="K37" s="123"/>
-      <c r="L37" s="123"/>
-      <c r="M37" s="123"/>
-      <c r="N37" s="124"/>
-      <c r="O37" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="38" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="117" t="s">
-        <v>438</v>
-      </c>
-      <c r="D38" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E38" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G38" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H38" s="123"/>
-      <c r="I38" s="123"/>
-      <c r="J38" s="123"/>
-      <c r="K38" s="123"/>
-      <c r="L38" s="123"/>
-      <c r="M38" s="123"/>
-      <c r="N38" s="124"/>
-      <c r="O38" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="39" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C39" s="117" t="s">
-        <v>439</v>
-      </c>
-      <c r="D39" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E39" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G39" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H39" s="123"/>
-      <c r="I39" s="123"/>
-      <c r="J39" s="123"/>
-      <c r="K39" s="123"/>
-      <c r="L39" s="123"/>
-      <c r="M39" s="123"/>
-      <c r="N39" s="124"/>
-      <c r="O39" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="40" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C40" s="117" t="s">
-        <v>440</v>
-      </c>
-      <c r="D40" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E40" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F40" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G40" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H40" s="123"/>
-      <c r="I40" s="123"/>
-      <c r="J40" s="123"/>
-      <c r="K40" s="123"/>
-      <c r="L40" s="123"/>
-      <c r="M40" s="123"/>
-      <c r="N40" s="124"/>
-      <c r="O40" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="41" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C41" s="117" t="s">
-        <v>441</v>
-      </c>
-      <c r="D41" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E41" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G41" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H41" s="123"/>
-      <c r="I41" s="123"/>
-      <c r="J41" s="123"/>
-      <c r="K41" s="123"/>
-      <c r="L41" s="123"/>
-      <c r="M41" s="123"/>
-      <c r="N41" s="124"/>
-      <c r="O41" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="42" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C42" s="117" t="s">
-        <v>442</v>
-      </c>
-      <c r="D42" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E42" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G42" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H42" s="123"/>
-      <c r="I42" s="123"/>
-      <c r="J42" s="123"/>
-      <c r="K42" s="123"/>
-      <c r="L42" s="123"/>
-      <c r="M42" s="123"/>
-      <c r="N42" s="124"/>
-      <c r="O42" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="43" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C43" s="117" t="s">
-        <v>443</v>
-      </c>
-      <c r="D43" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E43" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G43" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H43" s="123"/>
-      <c r="I43" s="123"/>
-      <c r="J43" s="123"/>
-      <c r="K43" s="123"/>
-      <c r="L43" s="123"/>
-      <c r="M43" s="123"/>
-      <c r="N43" s="124"/>
-      <c r="O43" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="44" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C44" s="117" t="s">
-        <v>444</v>
-      </c>
-      <c r="D44" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E44" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G44" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H44" s="123"/>
-      <c r="I44" s="123"/>
-      <c r="J44" s="123"/>
-      <c r="K44" s="123"/>
-      <c r="L44" s="123"/>
-      <c r="M44" s="123"/>
-      <c r="N44" s="124"/>
-      <c r="O44" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="45" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="117" t="s">
-        <v>445</v>
-      </c>
-      <c r="D45" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E45" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G45" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H45" s="123"/>
-      <c r="I45" s="123"/>
-      <c r="J45" s="123"/>
-      <c r="K45" s="123"/>
-      <c r="L45" s="123"/>
-      <c r="M45" s="123"/>
-      <c r="N45" s="124"/>
-      <c r="O45" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="46" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C46" s="117" t="s">
-        <v>446</v>
-      </c>
-      <c r="D46" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E46" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F46" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G46" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H46" s="123"/>
-      <c r="I46" s="123"/>
-      <c r="J46" s="123"/>
-      <c r="K46" s="123"/>
-      <c r="L46" s="123"/>
-      <c r="M46" s="123"/>
-      <c r="N46" s="124"/>
-      <c r="O46" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="47" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C47" s="117" t="s">
-        <v>448</v>
-      </c>
-      <c r="D47" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E47" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G47" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H47" s="123"/>
-      <c r="I47" s="123"/>
-      <c r="J47" s="123"/>
-      <c r="K47" s="123"/>
-      <c r="L47" s="123"/>
-      <c r="M47" s="123"/>
-      <c r="N47" s="124"/>
-      <c r="O47" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="48" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C48" s="117" t="s">
-        <v>449</v>
-      </c>
-      <c r="D48" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E48" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G48" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H48" s="123"/>
-      <c r="I48" s="123"/>
-      <c r="J48" s="123"/>
-      <c r="K48" s="123"/>
-      <c r="L48" s="123"/>
-      <c r="M48" s="123"/>
-      <c r="N48" s="124"/>
-      <c r="O48" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="49" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C49" s="117" t="s">
-        <v>450</v>
-      </c>
-      <c r="D49" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E49" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G49" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H49" s="123"/>
-      <c r="I49" s="123"/>
-      <c r="J49" s="123"/>
-      <c r="K49" s="123"/>
-      <c r="L49" s="123"/>
-      <c r="M49" s="123"/>
-      <c r="N49" s="124"/>
-      <c r="O49" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="50" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="117" t="s">
-        <v>451</v>
-      </c>
-      <c r="D50" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E50" s="114" t="s">
-        <v>453</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G50" s="122" t="s">
-        <v>463</v>
-      </c>
-      <c r="H50" s="123"/>
-      <c r="I50" s="123"/>
-      <c r="J50" s="123"/>
-      <c r="K50" s="123"/>
-      <c r="L50" s="123"/>
-      <c r="M50" s="123"/>
-      <c r="N50" s="124"/>
-      <c r="O50" s="49" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="51" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C51" s="117" t="s">
-        <v>452</v>
-      </c>
-      <c r="D51" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>458</v>
-      </c>
-      <c r="F51" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G51" s="101" t="s">
-        <v>140</v>
-      </c>
-      <c r="H51" s="123"/>
-      <c r="I51" s="123"/>
-      <c r="J51" s="123"/>
-      <c r="K51" s="123"/>
-      <c r="L51" s="123"/>
-      <c r="M51" s="123"/>
-      <c r="N51" s="124"/>
-      <c r="O51" s="49" t="s">
+    </row>
+    <row r="88" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C88" s="79" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="90" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C90" s="79" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="52" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C52" s="117" t="s">
-        <v>454</v>
-      </c>
-      <c r="D52" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>459</v>
-      </c>
-      <c r="F52" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G52" s="101" t="s">
-        <v>140</v>
-      </c>
-      <c r="H52" s="123"/>
-      <c r="I52" s="123"/>
-      <c r="J52" s="123"/>
-      <c r="K52" s="123"/>
-      <c r="L52" s="123"/>
-      <c r="M52" s="123"/>
-      <c r="N52" s="124"/>
-      <c r="O52" s="49" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C53" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="D53" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>460</v>
-      </c>
-      <c r="F53" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G53" s="101" t="s">
-        <v>140</v>
-      </c>
-      <c r="H53" s="123"/>
-      <c r="I53" s="123"/>
-      <c r="J53" s="123"/>
-      <c r="K53" s="123"/>
-      <c r="L53" s="123"/>
-      <c r="M53" s="123"/>
-      <c r="N53" s="124"/>
-      <c r="O53" s="49" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="54" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="117" t="s">
-        <v>456</v>
-      </c>
-      <c r="D54" s="114" t="s">
-        <v>447</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G54" s="101" t="s">
-        <v>140</v>
-      </c>
-      <c r="H54" s="123"/>
-      <c r="I54" s="123"/>
-      <c r="J54" s="123"/>
-      <c r="K54" s="123"/>
-      <c r="L54" s="123"/>
-      <c r="M54" s="123"/>
-      <c r="N54" s="124"/>
-      <c r="O54" s="49" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C55" s="118" t="s">
-        <v>457</v>
-      </c>
-      <c r="D55" s="119" t="s">
-        <v>447</v>
-      </c>
-      <c r="E55" s="120" t="s">
-        <v>462</v>
-      </c>
-      <c r="F55" s="125" t="s">
-        <v>187</v>
-      </c>
-      <c r="G55" s="101" t="s">
-        <v>140</v>
-      </c>
-      <c r="H55" s="123"/>
-      <c r="I55" s="123"/>
-      <c r="J55" s="123"/>
-      <c r="K55" s="123"/>
-      <c r="L55" s="123"/>
-      <c r="M55" s="123"/>
-      <c r="N55" s="124"/>
-      <c r="O55" s="49" t="s">
-        <v>465</v>
+    <row r="92" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C92" s="79" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="94" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C94" s="79" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="G55:N55"/>
-    <mergeCell ref="G51:N51"/>
-    <mergeCell ref="G52:N52"/>
-    <mergeCell ref="G53:N53"/>
-    <mergeCell ref="G54:N54"/>
-    <mergeCell ref="G46:N46"/>
-    <mergeCell ref="G47:N47"/>
-    <mergeCell ref="G48:N48"/>
-    <mergeCell ref="G49:N49"/>
-    <mergeCell ref="G50:N50"/>
-    <mergeCell ref="G41:N41"/>
-    <mergeCell ref="G42:N42"/>
-    <mergeCell ref="G43:N43"/>
-    <mergeCell ref="G44:N44"/>
-    <mergeCell ref="G45:N45"/>
+  <mergeCells count="49">
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G16:N16"/>
+    <mergeCell ref="G32:N32"/>
+    <mergeCell ref="G34:N34"/>
+    <mergeCell ref="G35:N35"/>
     <mergeCell ref="G36:N36"/>
     <mergeCell ref="G37:N37"/>
-    <mergeCell ref="G38:N38"/>
-    <mergeCell ref="G39:N39"/>
-    <mergeCell ref="G40:N40"/>
-    <mergeCell ref="G31:N31"/>
-    <mergeCell ref="G32:N32"/>
+    <mergeCell ref="G28:N28"/>
     <mergeCell ref="G33:N33"/>
-    <mergeCell ref="G34:N34"/>
-    <mergeCell ref="G35:N35"/>
     <mergeCell ref="G4:M4"/>
     <mergeCell ref="G27:N27"/>
     <mergeCell ref="G8:N8"/>
@@ -4528,19 +5343,38 @@
     <mergeCell ref="G19:N19"/>
     <mergeCell ref="G10:N10"/>
     <mergeCell ref="G5:N5"/>
-    <mergeCell ref="G28:N28"/>
     <mergeCell ref="G6:N6"/>
     <mergeCell ref="G13:N13"/>
     <mergeCell ref="G18:N18"/>
     <mergeCell ref="G17:M17"/>
-    <mergeCell ref="G15:N15"/>
-    <mergeCell ref="G14:N14"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="G16:N16"/>
     <mergeCell ref="G9:N9"/>
     <mergeCell ref="H26:L26"/>
     <mergeCell ref="G12:N12"/>
     <mergeCell ref="G11:N11"/>
+    <mergeCell ref="G15:N15"/>
+    <mergeCell ref="G46:N46"/>
+    <mergeCell ref="G47:N47"/>
+    <mergeCell ref="G38:N38"/>
+    <mergeCell ref="G39:N39"/>
+    <mergeCell ref="G40:N40"/>
+    <mergeCell ref="G41:N41"/>
+    <mergeCell ref="G42:N42"/>
+    <mergeCell ref="G58:N58"/>
+    <mergeCell ref="G31:N31"/>
+    <mergeCell ref="G59:N59"/>
+    <mergeCell ref="G57:N57"/>
+    <mergeCell ref="G53:N53"/>
+    <mergeCell ref="G54:N54"/>
+    <mergeCell ref="G55:N55"/>
+    <mergeCell ref="G56:N56"/>
+    <mergeCell ref="G48:N48"/>
+    <mergeCell ref="G49:N49"/>
+    <mergeCell ref="G50:N50"/>
+    <mergeCell ref="G51:N51"/>
+    <mergeCell ref="G52:N52"/>
+    <mergeCell ref="G43:N43"/>
+    <mergeCell ref="G44:N44"/>
+    <mergeCell ref="G45:N45"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4660,16 +5494,16 @@
       <c r="E12" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F12" s="103" t="s">
+      <c r="F12" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="94"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="112"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -4685,12 +5519,12 @@
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="103" t="s">
+      <c r="J13" s="119" t="s">
         <v>265</v>
       </c>
-      <c r="K13" s="93"/>
-      <c r="L13" s="93"/>
-      <c r="M13" s="94"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="112"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -4702,16 +5536,16 @@
       <c r="E14" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F14" s="103" t="s">
+      <c r="F14" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="93"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="94"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="112"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -4727,12 +5561,12 @@
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="35"/>
-      <c r="J15" s="103" t="s">
+      <c r="J15" s="119" t="s">
         <v>265</v>
       </c>
-      <c r="K15" s="93"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="94"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="112"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="18" t="s">
@@ -4744,16 +5578,16 @@
       <c r="E16" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F16" s="103" t="s">
+      <c r="F16" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="93"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="94"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="112"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="18" t="s">
@@ -4769,12 +5603,12 @@
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
       <c r="I17" s="35"/>
-      <c r="J17" s="103" t="s">
+      <c r="J17" s="119" t="s">
         <v>265</v>
       </c>
-      <c r="K17" s="93"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="94"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="112"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="18" t="s">
@@ -4789,13 +5623,13 @@
       <c r="F18" s="33"/>
       <c r="G18" s="34"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="103" t="s">
+      <c r="I18" s="119" t="s">
         <v>271</v>
       </c>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="93"/>
-      <c r="M18" s="94"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="112"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="18" t="s">
@@ -4848,12 +5682,12 @@
       <c r="I20" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="J20" s="103" t="s">
+      <c r="J20" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="94"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="112"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -4871,12 +5705,12 @@
       <c r="I21" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="J21" s="103" t="s">
+      <c r="J21" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="94"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="112"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -4894,12 +5728,12 @@
       <c r="I22" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="J22" s="103" t="s">
+      <c r="J22" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="K22" s="93"/>
-      <c r="L22" s="93"/>
-      <c r="M22" s="94"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="112"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -4911,16 +5745,16 @@
       <c r="E23" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F23" s="103" t="s">
+      <c r="F23" s="119" t="s">
         <v>286</v>
       </c>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="93"/>
-      <c r="L23" s="93"/>
-      <c r="M23" s="94"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="112"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -4932,16 +5766,16 @@
       <c r="E24" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F24" s="103" t="s">
+      <c r="F24" s="119" t="s">
         <v>288</v>
       </c>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="93"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="93"/>
-      <c r="L24" s="93"/>
-      <c r="M24" s="94"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="112"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -4957,12 +5791,12 @@
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="103" t="s">
+      <c r="J25" s="119" t="s">
         <v>290</v>
       </c>
-      <c r="K25" s="93"/>
-      <c r="L25" s="93"/>
-      <c r="M25" s="94"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="112"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -5012,16 +5846,16 @@
       <c r="E28" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="F28" s="96" t="s">
+      <c r="F28" s="115" t="s">
         <v>263</v>
       </c>
-      <c r="G28" s="93"/>
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="94"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="111"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="112"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="18" t="s">
@@ -5037,12 +5871,12 @@
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="27"/>
-      <c r="J29" s="96" t="s">
+      <c r="J29" s="115" t="s">
         <v>265</v>
       </c>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="94"/>
+      <c r="K29" s="111"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="112"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -5054,16 +5888,16 @@
       <c r="E30" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="F30" s="96" t="s">
+      <c r="F30" s="115" t="s">
         <v>263</v>
       </c>
-      <c r="G30" s="93"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="94"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="111"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="112"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -5079,12 +5913,12 @@
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="27"/>
-      <c r="J31" s="96" t="s">
+      <c r="J31" s="115" t="s">
         <v>265</v>
       </c>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="94"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="112"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -5096,16 +5930,16 @@
       <c r="E32" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="F32" s="96" t="s">
+      <c r="F32" s="115" t="s">
         <v>263</v>
       </c>
-      <c r="G32" s="93"/>
-      <c r="H32" s="93"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="93"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="94"/>
+      <c r="G32" s="111"/>
+      <c r="H32" s="111"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="111"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="112"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -5121,12 +5955,12 @@
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="27"/>
-      <c r="J33" s="96" t="s">
+      <c r="J33" s="115" t="s">
         <v>265</v>
       </c>
-      <c r="K33" s="93"/>
-      <c r="L33" s="93"/>
-      <c r="M33" s="94"/>
+      <c r="K33" s="111"/>
+      <c r="L33" s="111"/>
+      <c r="M33" s="112"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -5141,13 +5975,13 @@
       <c r="F34" s="25"/>
       <c r="G34" s="26"/>
       <c r="H34" s="27"/>
-      <c r="I34" s="96" t="s">
+      <c r="I34" s="115" t="s">
         <v>271</v>
       </c>
-      <c r="J34" s="93"/>
-      <c r="K34" s="93"/>
-      <c r="L34" s="93"/>
-      <c r="M34" s="94"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="111"/>
+      <c r="L34" s="111"/>
+      <c r="M34" s="112"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -5200,12 +6034,12 @@
       <c r="I36" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J36" s="96" t="s">
+      <c r="J36" s="115" t="s">
         <v>282</v>
       </c>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="94"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="111"/>
+      <c r="M36" s="112"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -5223,12 +6057,12 @@
       <c r="I37" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J37" s="96" t="s">
+      <c r="J37" s="115" t="s">
         <v>282</v>
       </c>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="94"/>
+      <c r="K37" s="111"/>
+      <c r="L37" s="111"/>
+      <c r="M37" s="112"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -5246,12 +6080,12 @@
       <c r="I38" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J38" s="96" t="s">
+      <c r="J38" s="115" t="s">
         <v>282</v>
       </c>
-      <c r="K38" s="93"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="94"/>
+      <c r="K38" s="111"/>
+      <c r="L38" s="111"/>
+      <c r="M38" s="112"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -5263,16 +6097,16 @@
       <c r="E39" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="F39" s="96" t="s">
+      <c r="F39" s="115" t="s">
         <v>286</v>
       </c>
-      <c r="G39" s="93"/>
-      <c r="H39" s="93"/>
-      <c r="I39" s="93"/>
-      <c r="J39" s="93"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="93"/>
-      <c r="M39" s="94"/>
+      <c r="G39" s="111"/>
+      <c r="H39" s="111"/>
+      <c r="I39" s="111"/>
+      <c r="J39" s="111"/>
+      <c r="K39" s="111"/>
+      <c r="L39" s="111"/>
+      <c r="M39" s="112"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18" t="s">
@@ -5284,16 +6118,16 @@
       <c r="E40" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="F40" s="96" t="s">
+      <c r="F40" s="115" t="s">
         <v>288</v>
       </c>
-      <c r="G40" s="93"/>
-      <c r="H40" s="93"/>
-      <c r="I40" s="93"/>
-      <c r="J40" s="93"/>
-      <c r="K40" s="93"/>
-      <c r="L40" s="93"/>
-      <c r="M40" s="94"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="111"/>
+      <c r="I40" s="111"/>
+      <c r="J40" s="111"/>
+      <c r="K40" s="111"/>
+      <c r="L40" s="111"/>
+      <c r="M40" s="112"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18" t="s">
@@ -5309,12 +6143,12 @@
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="27"/>
-      <c r="J41" s="96" t="s">
+      <c r="J41" s="115" t="s">
         <v>290</v>
       </c>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="94"/>
+      <c r="K41" s="111"/>
+      <c r="L41" s="111"/>
+      <c r="M41" s="112"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18" t="s">
@@ -5349,12 +6183,12 @@
       <c r="G43" s="69"/>
       <c r="H43" s="69"/>
       <c r="I43" s="70"/>
-      <c r="J43" s="104" t="s">
+      <c r="J43" s="122" t="s">
         <v>309</v>
       </c>
-      <c r="K43" s="105"/>
-      <c r="L43" s="105"/>
-      <c r="M43" s="106"/>
+      <c r="K43" s="123"/>
+      <c r="L43" s="123"/>
+      <c r="M43" s="124"/>
     </row>
     <row r="44" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
@@ -5366,16 +6200,16 @@
       <c r="E44" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="F44" s="101" t="s">
+      <c r="F44" s="120" t="s">
         <v>282</v>
       </c>
-      <c r="G44" s="93"/>
-      <c r="H44" s="93"/>
-      <c r="I44" s="93"/>
-      <c r="J44" s="93"/>
-      <c r="K44" s="93"/>
-      <c r="L44" s="93"/>
-      <c r="M44" s="102"/>
+      <c r="G44" s="111"/>
+      <c r="H44" s="111"/>
+      <c r="I44" s="111"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="111"/>
+      <c r="L44" s="111"/>
+      <c r="M44" s="121"/>
       <c r="O44" t="s">
         <v>312</v>
       </c>
@@ -5390,16 +6224,16 @@
       <c r="E45" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="F45" s="101" t="s">
+      <c r="F45" s="120" t="s">
         <v>282</v>
       </c>
-      <c r="G45" s="93"/>
-      <c r="H45" s="93"/>
-      <c r="I45" s="93"/>
-      <c r="J45" s="93"/>
-      <c r="K45" s="93"/>
-      <c r="L45" s="93"/>
-      <c r="M45" s="102"/>
+      <c r="G45" s="111"/>
+      <c r="H45" s="111"/>
+      <c r="I45" s="111"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="111"/>
+      <c r="L45" s="111"/>
+      <c r="M45" s="121"/>
       <c r="O45" t="s">
         <v>312</v>
       </c>
@@ -5414,16 +6248,16 @@
       <c r="E46" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="F46" s="101" t="s">
+      <c r="F46" s="120" t="s">
         <v>282</v>
       </c>
-      <c r="G46" s="93"/>
-      <c r="H46" s="93"/>
-      <c r="I46" s="93"/>
-      <c r="J46" s="93"/>
-      <c r="K46" s="93"/>
-      <c r="L46" s="93"/>
-      <c r="M46" s="102"/>
+      <c r="G46" s="111"/>
+      <c r="H46" s="111"/>
+      <c r="I46" s="111"/>
+      <c r="J46" s="111"/>
+      <c r="K46" s="111"/>
+      <c r="L46" s="111"/>
+      <c r="M46" s="121"/>
       <c r="O46" t="s">
         <v>312</v>
       </c>
@@ -5457,16 +6291,16 @@
       <c r="E48" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="F48" s="101" t="s">
+      <c r="F48" s="120" t="s">
         <v>282</v>
       </c>
-      <c r="G48" s="93"/>
-      <c r="H48" s="93"/>
-      <c r="I48" s="93"/>
-      <c r="J48" s="93"/>
-      <c r="K48" s="93"/>
-      <c r="L48" s="93"/>
-      <c r="M48" s="102"/>
+      <c r="G48" s="111"/>
+      <c r="H48" s="111"/>
+      <c r="I48" s="111"/>
+      <c r="J48" s="111"/>
+      <c r="K48" s="111"/>
+      <c r="L48" s="111"/>
+      <c r="M48" s="121"/>
       <c r="O48" t="s">
         <v>312</v>
       </c>
@@ -5481,16 +6315,16 @@
       <c r="E49" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="F49" s="101" t="s">
+      <c r="F49" s="120" t="s">
         <v>282</v>
       </c>
-      <c r="G49" s="93"/>
-      <c r="H49" s="93"/>
-      <c r="I49" s="93"/>
-      <c r="J49" s="93"/>
-      <c r="K49" s="93"/>
-      <c r="L49" s="93"/>
-      <c r="M49" s="102"/>
+      <c r="G49" s="111"/>
+      <c r="H49" s="111"/>
+      <c r="I49" s="111"/>
+      <c r="J49" s="111"/>
+      <c r="K49" s="111"/>
+      <c r="L49" s="111"/>
+      <c r="M49" s="121"/>
       <c r="O49" t="s">
         <v>312</v>
       </c>
@@ -5505,16 +6339,16 @@
       <c r="E50" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="F50" s="101" t="s">
+      <c r="F50" s="120" t="s">
         <v>282</v>
       </c>
-      <c r="G50" s="93"/>
-      <c r="H50" s="93"/>
-      <c r="I50" s="93"/>
-      <c r="J50" s="93"/>
-      <c r="K50" s="93"/>
-      <c r="L50" s="93"/>
-      <c r="M50" s="102"/>
+      <c r="G50" s="111"/>
+      <c r="H50" s="111"/>
+      <c r="I50" s="111"/>
+      <c r="J50" s="111"/>
+      <c r="K50" s="111"/>
+      <c r="L50" s="111"/>
+      <c r="M50" s="121"/>
       <c r="O50" t="s">
         <v>312</v>
       </c>
@@ -5548,18 +6382,18 @@
       <c r="E52" s="22" t="s">
         <v>327</v>
       </c>
-      <c r="F52" s="96" t="s">
+      <c r="F52" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="93"/>
-      <c r="H52" s="93"/>
-      <c r="I52" s="93"/>
-      <c r="J52" s="93"/>
-      <c r="K52" s="93"/>
-      <c r="L52" s="93"/>
-      <c r="M52" s="94"/>
+      <c r="G52" s="111"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="111"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="111"/>
+      <c r="L52" s="111"/>
+      <c r="M52" s="112"/>
       <c r="O52" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
     </row>
     <row r="53" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -5572,16 +6406,16 @@
       <c r="E53" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="F53" s="96" t="s">
+      <c r="F53" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="93"/>
-      <c r="H53" s="93"/>
-      <c r="I53" s="93"/>
-      <c r="J53" s="93"/>
-      <c r="K53" s="93"/>
-      <c r="L53" s="93"/>
-      <c r="M53" s="94"/>
+      <c r="G53" s="111"/>
+      <c r="H53" s="111"/>
+      <c r="I53" s="111"/>
+      <c r="J53" s="111"/>
+      <c r="K53" s="111"/>
+      <c r="L53" s="111"/>
+      <c r="M53" s="112"/>
       <c r="O53" t="s">
         <v>141</v>
       </c>
@@ -5596,16 +6430,16 @@
       <c r="E54" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="F54" s="96" t="s">
+      <c r="F54" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="93"/>
-      <c r="H54" s="93"/>
-      <c r="I54" s="93"/>
-      <c r="J54" s="93"/>
-      <c r="K54" s="93"/>
-      <c r="L54" s="93"/>
-      <c r="M54" s="94"/>
+      <c r="G54" s="111"/>
+      <c r="H54" s="111"/>
+      <c r="I54" s="111"/>
+      <c r="J54" s="111"/>
+      <c r="K54" s="111"/>
+      <c r="L54" s="111"/>
+      <c r="M54" s="112"/>
       <c r="O54" t="s">
         <v>141</v>
       </c>
@@ -5639,16 +6473,16 @@
       <c r="E56" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="F56" s="96" t="s">
+      <c r="F56" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="93"/>
-      <c r="H56" s="93"/>
-      <c r="I56" s="93"/>
-      <c r="J56" s="93"/>
-      <c r="K56" s="93"/>
-      <c r="L56" s="93"/>
-      <c r="M56" s="94"/>
+      <c r="G56" s="111"/>
+      <c r="H56" s="111"/>
+      <c r="I56" s="111"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="111"/>
+      <c r="L56" s="111"/>
+      <c r="M56" s="112"/>
       <c r="O56" t="s">
         <v>141</v>
       </c>
@@ -5663,16 +6497,16 @@
       <c r="E57" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="F57" s="96" t="s">
+      <c r="F57" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="93"/>
-      <c r="H57" s="93"/>
-      <c r="I57" s="93"/>
-      <c r="J57" s="93"/>
-      <c r="K57" s="93"/>
-      <c r="L57" s="93"/>
-      <c r="M57" s="94"/>
+      <c r="G57" s="111"/>
+      <c r="H57" s="111"/>
+      <c r="I57" s="111"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="111"/>
+      <c r="L57" s="111"/>
+      <c r="M57" s="112"/>
       <c r="O57" t="s">
         <v>141</v>
       </c>
@@ -5687,16 +6521,16 @@
       <c r="E58" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="F58" s="96" t="s">
+      <c r="F58" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="93"/>
-      <c r="H58" s="93"/>
-      <c r="I58" s="93"/>
-      <c r="J58" s="93"/>
-      <c r="K58" s="93"/>
-      <c r="L58" s="93"/>
-      <c r="M58" s="94"/>
+      <c r="G58" s="111"/>
+      <c r="H58" s="111"/>
+      <c r="I58" s="111"/>
+      <c r="J58" s="111"/>
+      <c r="K58" s="111"/>
+      <c r="L58" s="111"/>
+      <c r="M58" s="112"/>
       <c r="O58" t="s">
         <v>141</v>
       </c>
@@ -5741,17 +6575,18 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F45:M45"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:M48"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F53:M53"/>
     <mergeCell ref="F12:M12"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J17:M17"/>
@@ -5768,18 +6603,17 @@
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:M48"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F50:M50"/>
-    <mergeCell ref="F46:M46"/>
-    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J43:M43"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5854,16 +6688,16 @@
       <c r="E6" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="F6" s="98" t="s">
+      <c r="F6" s="118" t="s">
         <v>344</v>
       </c>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="94"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="112"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
@@ -5875,16 +6709,16 @@
       <c r="E7" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F7" s="98" t="s">
+      <c r="F7" s="118" t="s">
         <v>347</v>
       </c>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="94"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="112"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
@@ -5946,12 +6780,12 @@
       <c r="I19" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="98" t="s">
+      <c r="J19" s="118" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="93"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="94"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="112"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="18" t="s">
@@ -5973,12 +6807,12 @@
       <c r="I20" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="98" t="s">
+      <c r="J20" s="118" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="94"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="112"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -5988,18 +6822,18 @@
         <v>19</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="98" t="s">
+      <c r="F21" s="118" t="s">
         <v>350</v>
       </c>
-      <c r="G21" s="94"/>
-      <c r="H21" s="98" t="s">
+      <c r="G21" s="112"/>
+      <c r="H21" s="118" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="93"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="94"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="112"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -6009,10 +6843,10 @@
         <v>19</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="98" t="s">
+      <c r="F22" s="118" t="s">
         <v>350</v>
       </c>
-      <c r="G22" s="94"/>
+      <c r="G22" s="112"/>
       <c r="H22" s="17"/>
       <c r="I22" s="10" t="s">
         <v>351</v>
@@ -6020,11 +6854,11 @@
       <c r="J22" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="K22" s="98" t="s">
+      <c r="K22" s="118" t="s">
         <v>133</v>
       </c>
-      <c r="L22" s="93"/>
-      <c r="M22" s="94"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="112"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -6034,18 +6868,18 @@
         <v>19</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="98" t="s">
+      <c r="F23" s="118" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="98" t="s">
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="118" t="s">
         <v>115</v>
       </c>
-      <c r="K23" s="93"/>
-      <c r="L23" s="93"/>
-      <c r="M23" s="94"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="112"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -6055,18 +6889,18 @@
         <v>19</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="98" t="s">
+      <c r="F24" s="118" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="98" t="s">
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="118" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="93"/>
-      <c r="L24" s="93"/>
-      <c r="M24" s="94"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="112"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -6076,18 +6910,18 @@
         <v>19</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="98" t="s">
+      <c r="F25" s="118" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="93"/>
-      <c r="H25" s="93"/>
-      <c r="I25" s="94"/>
-      <c r="J25" s="98" t="s">
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="118" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="93"/>
-      <c r="L25" s="93"/>
-      <c r="M25" s="94"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="112"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -6097,18 +6931,18 @@
         <v>19</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="98" t="s">
+      <c r="F26" s="118" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="93"/>
-      <c r="H26" s="93"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="98" t="s">
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="118" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="93"/>
-      <c r="L26" s="93"/>
-      <c r="M26" s="94"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="112"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="18" t="s">
@@ -6162,16 +6996,16 @@
       <c r="E29" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="98" t="s">
+      <c r="F29" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="94"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="111"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="111"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="112"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -6181,16 +7015,16 @@
         <v>19</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="98" t="s">
+      <c r="F30" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="93"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="94"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="111"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="112"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -6200,16 +7034,16 @@
         <v>19</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="98" t="s">
+      <c r="F31" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="94"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="111"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="112"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -6219,16 +7053,16 @@
         <v>19</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="98" t="s">
+      <c r="F32" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="93"/>
-      <c r="H32" s="93"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="93"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="94"/>
+      <c r="G32" s="111"/>
+      <c r="H32" s="111"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="111"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="112"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -6238,16 +7072,16 @@
         <v>19</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="98" t="s">
+      <c r="F33" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="93"/>
-      <c r="H33" s="93"/>
-      <c r="I33" s="93"/>
-      <c r="J33" s="93"/>
-      <c r="K33" s="93"/>
-      <c r="L33" s="93"/>
-      <c r="M33" s="94"/>
+      <c r="G33" s="111"/>
+      <c r="H33" s="111"/>
+      <c r="I33" s="111"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="111"/>
+      <c r="L33" s="111"/>
+      <c r="M33" s="112"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -6257,16 +7091,16 @@
         <v>19</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="98" t="s">
+      <c r="F34" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="93"/>
-      <c r="H34" s="93"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="93"/>
-      <c r="K34" s="93"/>
-      <c r="L34" s="93"/>
-      <c r="M34" s="94"/>
+      <c r="G34" s="111"/>
+      <c r="H34" s="111"/>
+      <c r="I34" s="111"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="111"/>
+      <c r="L34" s="111"/>
+      <c r="M34" s="112"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -6276,16 +7110,16 @@
         <v>19</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="98" t="s">
+      <c r="F35" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="93"/>
-      <c r="H35" s="93"/>
-      <c r="I35" s="93"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="93"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="94"/>
+      <c r="G35" s="111"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="111"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="111"/>
+      <c r="L35" s="111"/>
+      <c r="M35" s="112"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="18" t="s">
@@ -6295,16 +7129,16 @@
         <v>19</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="98" t="s">
+      <c r="F36" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="93"/>
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="94"/>
+      <c r="G36" s="111"/>
+      <c r="H36" s="111"/>
+      <c r="I36" s="111"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="111"/>
+      <c r="M36" s="112"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -6314,16 +7148,16 @@
         <v>19</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="98" t="s">
+      <c r="F37" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="93"/>
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="94"/>
+      <c r="G37" s="111"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="111"/>
+      <c r="J37" s="111"/>
+      <c r="K37" s="111"/>
+      <c r="L37" s="111"/>
+      <c r="M37" s="112"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -6333,16 +7167,16 @@
         <v>19</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="98" t="s">
+      <c r="F38" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G38" s="93"/>
-      <c r="H38" s="93"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="94"/>
+      <c r="G38" s="111"/>
+      <c r="H38" s="111"/>
+      <c r="I38" s="111"/>
+      <c r="J38" s="111"/>
+      <c r="K38" s="111"/>
+      <c r="L38" s="111"/>
+      <c r="M38" s="112"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -6377,11 +7211,11 @@
       <c r="I40" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J40" s="98" t="s">
+      <c r="J40" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="K40" s="93"/>
-      <c r="L40" s="94"/>
+      <c r="K40" s="111"/>
+      <c r="L40" s="112"/>
       <c r="M40" s="12" t="s">
         <v>120</v>
       </c>
@@ -6402,11 +7236,11 @@
       <c r="I41" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J41" s="98" t="s">
+      <c r="J41" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="K41" s="93"/>
-      <c r="L41" s="94"/>
+      <c r="K41" s="111"/>
+      <c r="L41" s="112"/>
       <c r="M41" s="12" t="s">
         <v>120</v>
       </c>
@@ -6427,11 +7261,11 @@
       <c r="I42" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J42" s="98" t="s">
+      <c r="J42" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="K42" s="93"/>
-      <c r="L42" s="94"/>
+      <c r="K42" s="111"/>
+      <c r="L42" s="112"/>
       <c r="M42" s="12" t="s">
         <v>120</v>
       </c>
@@ -6452,11 +7286,11 @@
       <c r="I43" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J43" s="98" t="s">
+      <c r="J43" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="K43" s="93"/>
-      <c r="L43" s="94"/>
+      <c r="K43" s="111"/>
+      <c r="L43" s="112"/>
       <c r="M43" s="12" t="s">
         <v>120</v>
       </c>
@@ -6477,11 +7311,11 @@
       <c r="I44" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J44" s="98" t="s">
+      <c r="J44" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="K44" s="93"/>
-      <c r="L44" s="94"/>
+      <c r="K44" s="111"/>
+      <c r="L44" s="112"/>
       <c r="M44" s="12" t="s">
         <v>120</v>
       </c>
@@ -6502,11 +7336,11 @@
       <c r="I45" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J45" s="98" t="s">
+      <c r="J45" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="K45" s="93"/>
-      <c r="L45" s="94"/>
+      <c r="K45" s="111"/>
+      <c r="L45" s="112"/>
       <c r="M45" s="12" t="s">
         <v>120</v>
       </c>
@@ -6527,11 +7361,11 @@
       <c r="I46" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J46" s="98" t="s">
+      <c r="J46" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="K46" s="93"/>
-      <c r="L46" s="94"/>
+      <c r="K46" s="111"/>
+      <c r="L46" s="112"/>
       <c r="M46" s="12" t="s">
         <v>120</v>
       </c>
@@ -6552,11 +7386,11 @@
       <c r="I47" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J47" s="98" t="s">
+      <c r="J47" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="K47" s="93"/>
-      <c r="L47" s="94"/>
+      <c r="K47" s="111"/>
+      <c r="L47" s="112"/>
       <c r="M47" s="12" t="s">
         <v>120</v>
       </c>
@@ -6577,11 +7411,11 @@
       <c r="I48" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J48" s="98" t="s">
+      <c r="J48" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="K48" s="93"/>
-      <c r="L48" s="94"/>
+      <c r="K48" s="111"/>
+      <c r="L48" s="112"/>
       <c r="M48" s="12" t="s">
         <v>120</v>
       </c>
@@ -6611,18 +7445,18 @@
         <v>19</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="98" t="s">
+      <c r="F50" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="G50" s="93"/>
-      <c r="H50" s="93"/>
-      <c r="I50" s="94"/>
-      <c r="J50" s="98" t="s">
+      <c r="G50" s="111"/>
+      <c r="H50" s="111"/>
+      <c r="I50" s="112"/>
+      <c r="J50" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="K50" s="93"/>
-      <c r="L50" s="93"/>
-      <c r="M50" s="94"/>
+      <c r="K50" s="111"/>
+      <c r="L50" s="111"/>
+      <c r="M50" s="112"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
@@ -6632,18 +7466,18 @@
         <v>19</v>
       </c>
       <c r="E51" s="11"/>
-      <c r="F51" s="98" t="s">
+      <c r="F51" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="G51" s="93"/>
-      <c r="H51" s="93"/>
-      <c r="I51" s="94"/>
-      <c r="J51" s="98" t="s">
+      <c r="G51" s="111"/>
+      <c r="H51" s="111"/>
+      <c r="I51" s="112"/>
+      <c r="J51" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="K51" s="93"/>
-      <c r="L51" s="93"/>
-      <c r="M51" s="94"/>
+      <c r="K51" s="111"/>
+      <c r="L51" s="111"/>
+      <c r="M51" s="112"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -6653,18 +7487,18 @@
         <v>19</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="98" t="s">
+      <c r="F52" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="G52" s="93"/>
-      <c r="H52" s="93"/>
-      <c r="I52" s="94"/>
-      <c r="J52" s="98" t="s">
+      <c r="G52" s="111"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="112"/>
+      <c r="J52" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="K52" s="93"/>
-      <c r="L52" s="93"/>
-      <c r="M52" s="94"/>
+      <c r="K52" s="111"/>
+      <c r="L52" s="111"/>
+      <c r="M52" s="112"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18" t="s">
@@ -6674,18 +7508,18 @@
         <v>19</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="98" t="s">
+      <c r="F53" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="G53" s="93"/>
-      <c r="H53" s="93"/>
-      <c r="I53" s="94"/>
-      <c r="J53" s="98" t="s">
+      <c r="G53" s="111"/>
+      <c r="H53" s="111"/>
+      <c r="I53" s="112"/>
+      <c r="J53" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="K53" s="93"/>
-      <c r="L53" s="93"/>
-      <c r="M53" s="94"/>
+      <c r="K53" s="111"/>
+      <c r="L53" s="111"/>
+      <c r="M53" s="112"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18" t="s">
@@ -6695,18 +7529,18 @@
         <v>19</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="98" t="s">
+      <c r="F54" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="G54" s="93"/>
-      <c r="H54" s="93"/>
-      <c r="I54" s="94"/>
-      <c r="J54" s="98" t="s">
+      <c r="G54" s="111"/>
+      <c r="H54" s="111"/>
+      <c r="I54" s="112"/>
+      <c r="J54" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="K54" s="93"/>
-      <c r="L54" s="93"/>
-      <c r="M54" s="94"/>
+      <c r="K54" s="111"/>
+      <c r="L54" s="111"/>
+      <c r="M54" s="112"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18" t="s">
@@ -6716,18 +7550,18 @@
         <v>19</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="98" t="s">
+      <c r="F55" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="G55" s="93"/>
-      <c r="H55" s="93"/>
-      <c r="I55" s="94"/>
-      <c r="J55" s="98" t="s">
+      <c r="G55" s="111"/>
+      <c r="H55" s="111"/>
+      <c r="I55" s="112"/>
+      <c r="J55" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="K55" s="93"/>
-      <c r="L55" s="93"/>
-      <c r="M55" s="94"/>
+      <c r="K55" s="111"/>
+      <c r="L55" s="111"/>
+      <c r="M55" s="112"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18" t="s">
@@ -6737,18 +7571,18 @@
         <v>19</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="98" t="s">
+      <c r="F56" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="G56" s="93"/>
-      <c r="H56" s="93"/>
-      <c r="I56" s="94"/>
-      <c r="J56" s="98" t="s">
+      <c r="G56" s="111"/>
+      <c r="H56" s="111"/>
+      <c r="I56" s="112"/>
+      <c r="J56" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="K56" s="93"/>
-      <c r="L56" s="93"/>
-      <c r="M56" s="94"/>
+      <c r="K56" s="111"/>
+      <c r="L56" s="111"/>
+      <c r="M56" s="112"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18" t="s">
@@ -6758,18 +7592,18 @@
         <v>19</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="98" t="s">
+      <c r="F57" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="G57" s="93"/>
-      <c r="H57" s="93"/>
-      <c r="I57" s="94"/>
-      <c r="J57" s="98" t="s">
+      <c r="G57" s="111"/>
+      <c r="H57" s="111"/>
+      <c r="I57" s="112"/>
+      <c r="J57" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="K57" s="93"/>
-      <c r="L57" s="93"/>
-      <c r="M57" s="94"/>
+      <c r="K57" s="111"/>
+      <c r="L57" s="111"/>
+      <c r="M57" s="112"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18" t="s">
@@ -6779,18 +7613,18 @@
         <v>19</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="98" t="s">
+      <c r="F58" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="G58" s="93"/>
-      <c r="H58" s="93"/>
-      <c r="I58" s="94"/>
-      <c r="J58" s="98" t="s">
+      <c r="G58" s="111"/>
+      <c r="H58" s="111"/>
+      <c r="I58" s="112"/>
+      <c r="J58" s="118" t="s">
         <v>361</v>
       </c>
-      <c r="K58" s="93"/>
-      <c r="L58" s="93"/>
-      <c r="M58" s="94"/>
+      <c r="K58" s="111"/>
+      <c r="L58" s="111"/>
+      <c r="M58" s="112"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="18" t="s">
@@ -6825,10 +7659,10 @@
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="96" t="s">
+      <c r="L60" s="115" t="s">
         <v>373</v>
       </c>
-      <c r="M60" s="94"/>
+      <c r="M60" s="112"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="18" t="s">
@@ -6846,10 +7680,10 @@
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
       <c r="K61" s="9"/>
-      <c r="L61" s="100" t="s">
+      <c r="L61" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="M61" s="94"/>
+      <c r="M61" s="112"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="18" t="s">
@@ -6867,10 +7701,10 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="9"/>
-      <c r="L62" s="100" t="s">
+      <c r="L62" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="M62" s="94"/>
+      <c r="M62" s="112"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="18" t="s">
@@ -6888,10 +7722,10 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="9"/>
-      <c r="L63" s="100" t="s">
+      <c r="L63" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="M63" s="94"/>
+      <c r="M63" s="112"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="18" t="s">
@@ -6909,10 +7743,10 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="9"/>
-      <c r="L64" s="100" t="s">
+      <c r="L64" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="M64" s="94"/>
+      <c r="M64" s="112"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="18" t="s">
@@ -6930,10 +7764,10 @@
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="9"/>
-      <c r="L65" s="100" t="s">
+      <c r="L65" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="M65" s="94"/>
+      <c r="M65" s="112"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="18" t="s">
@@ -6951,10 +7785,10 @@
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
       <c r="K66" s="9"/>
-      <c r="L66" s="100" t="s">
+      <c r="L66" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="M66" s="94"/>
+      <c r="M66" s="112"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="18" t="s">
@@ -6972,10 +7806,10 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="9"/>
-      <c r="L67" s="100" t="s">
+      <c r="L67" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="M67" s="94"/>
+      <c r="M67" s="112"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="18" t="s">
@@ -6993,10 +7827,10 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="9"/>
-      <c r="L68" s="100" t="s">
+      <c r="L68" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="M68" s="94"/>
+      <c r="M68" s="112"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="18" t="s">
@@ -7025,16 +7859,16 @@
       <c r="E70" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F70" s="96" t="s">
+      <c r="F70" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G70" s="93"/>
-      <c r="H70" s="93"/>
-      <c r="I70" s="93"/>
-      <c r="J70" s="93"/>
-      <c r="K70" s="93"/>
-      <c r="L70" s="93"/>
-      <c r="M70" s="94"/>
+      <c r="G70" s="111"/>
+      <c r="H70" s="111"/>
+      <c r="I70" s="111"/>
+      <c r="J70" s="111"/>
+      <c r="K70" s="111"/>
+      <c r="L70" s="111"/>
+      <c r="M70" s="112"/>
       <c r="O70" t="s">
         <v>141</v>
       </c>
@@ -7049,16 +7883,16 @@
       <c r="E71" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F71" s="96" t="s">
+      <c r="F71" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G71" s="93"/>
-      <c r="H71" s="93"/>
-      <c r="I71" s="93"/>
-      <c r="J71" s="93"/>
-      <c r="K71" s="93"/>
-      <c r="L71" s="93"/>
-      <c r="M71" s="94"/>
+      <c r="G71" s="111"/>
+      <c r="H71" s="111"/>
+      <c r="I71" s="111"/>
+      <c r="J71" s="111"/>
+      <c r="K71" s="111"/>
+      <c r="L71" s="111"/>
+      <c r="M71" s="112"/>
       <c r="O71" t="s">
         <v>141</v>
       </c>
@@ -7073,16 +7907,16 @@
       <c r="E72" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F72" s="96" t="s">
+      <c r="F72" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G72" s="93"/>
-      <c r="H72" s="93"/>
-      <c r="I72" s="93"/>
-      <c r="J72" s="93"/>
-      <c r="K72" s="93"/>
-      <c r="L72" s="93"/>
-      <c r="M72" s="94"/>
+      <c r="G72" s="111"/>
+      <c r="H72" s="111"/>
+      <c r="I72" s="111"/>
+      <c r="J72" s="111"/>
+      <c r="K72" s="111"/>
+      <c r="L72" s="111"/>
+      <c r="M72" s="112"/>
       <c r="O72" t="s">
         <v>141</v>
       </c>
@@ -7097,16 +7931,16 @@
       <c r="E73" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F73" s="96" t="s">
+      <c r="F73" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="93"/>
-      <c r="H73" s="93"/>
-      <c r="I73" s="93"/>
-      <c r="J73" s="93"/>
-      <c r="K73" s="93"/>
-      <c r="L73" s="93"/>
-      <c r="M73" s="94"/>
+      <c r="G73" s="111"/>
+      <c r="H73" s="111"/>
+      <c r="I73" s="111"/>
+      <c r="J73" s="111"/>
+      <c r="K73" s="111"/>
+      <c r="L73" s="111"/>
+      <c r="M73" s="112"/>
       <c r="O73" t="s">
         <v>141</v>
       </c>
@@ -7121,16 +7955,16 @@
       <c r="E74" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F74" s="96" t="s">
+      <c r="F74" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G74" s="93"/>
-      <c r="H74" s="93"/>
-      <c r="I74" s="93"/>
-      <c r="J74" s="93"/>
-      <c r="K74" s="93"/>
-      <c r="L74" s="93"/>
-      <c r="M74" s="94"/>
+      <c r="G74" s="111"/>
+      <c r="H74" s="111"/>
+      <c r="I74" s="111"/>
+      <c r="J74" s="111"/>
+      <c r="K74" s="111"/>
+      <c r="L74" s="111"/>
+      <c r="M74" s="112"/>
       <c r="O74" t="s">
         <v>141</v>
       </c>
@@ -7145,16 +7979,16 @@
       <c r="E75" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F75" s="96" t="s">
+      <c r="F75" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G75" s="93"/>
-      <c r="H75" s="93"/>
-      <c r="I75" s="93"/>
-      <c r="J75" s="93"/>
-      <c r="K75" s="93"/>
-      <c r="L75" s="93"/>
-      <c r="M75" s="94"/>
+      <c r="G75" s="111"/>
+      <c r="H75" s="111"/>
+      <c r="I75" s="111"/>
+      <c r="J75" s="111"/>
+      <c r="K75" s="111"/>
+      <c r="L75" s="111"/>
+      <c r="M75" s="112"/>
       <c r="O75" t="s">
         <v>141</v>
       </c>
@@ -7169,16 +8003,16 @@
       <c r="E76" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F76" s="96" t="s">
+      <c r="F76" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G76" s="93"/>
-      <c r="H76" s="93"/>
-      <c r="I76" s="93"/>
-      <c r="J76" s="93"/>
-      <c r="K76" s="93"/>
-      <c r="L76" s="93"/>
-      <c r="M76" s="94"/>
+      <c r="G76" s="111"/>
+      <c r="H76" s="111"/>
+      <c r="I76" s="111"/>
+      <c r="J76" s="111"/>
+      <c r="K76" s="111"/>
+      <c r="L76" s="111"/>
+      <c r="M76" s="112"/>
       <c r="O76" t="s">
         <v>141</v>
       </c>
@@ -7193,16 +8027,16 @@
       <c r="E77" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F77" s="96" t="s">
+      <c r="F77" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G77" s="93"/>
-      <c r="H77" s="93"/>
-      <c r="I77" s="93"/>
-      <c r="J77" s="93"/>
-      <c r="K77" s="93"/>
-      <c r="L77" s="93"/>
-      <c r="M77" s="94"/>
+      <c r="G77" s="111"/>
+      <c r="H77" s="111"/>
+      <c r="I77" s="111"/>
+      <c r="J77" s="111"/>
+      <c r="K77" s="111"/>
+      <c r="L77" s="111"/>
+      <c r="M77" s="112"/>
       <c r="O77" t="s">
         <v>141</v>
       </c>
@@ -7217,16 +8051,16 @@
       <c r="E78" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F78" s="96" t="s">
+      <c r="F78" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="G78" s="93"/>
-      <c r="H78" s="93"/>
-      <c r="I78" s="93"/>
-      <c r="J78" s="93"/>
-      <c r="K78" s="93"/>
-      <c r="L78" s="93"/>
-      <c r="M78" s="94"/>
+      <c r="G78" s="111"/>
+      <c r="H78" s="111"/>
+      <c r="I78" s="111"/>
+      <c r="J78" s="111"/>
+      <c r="K78" s="111"/>
+      <c r="L78" s="111"/>
+      <c r="M78" s="112"/>
       <c r="O78" t="s">
         <v>141</v>
       </c>
@@ -7250,19 +8084,45 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="F73:M73"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F78:M78"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="F74:M74"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="F75:M75"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="F77:M77"/>
-    <mergeCell ref="F76:M76"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="J55:M55"/>
     <mergeCell ref="F6:M6"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="F7:M7"/>
@@ -7279,48 +8139,22 @@
     <mergeCell ref="H21:M21"/>
     <mergeCell ref="F29:M29"/>
     <mergeCell ref="K22:M22"/>
+    <mergeCell ref="F73:M73"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F78:M78"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="F74:M74"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="F75:M75"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="F77:M77"/>
+    <mergeCell ref="F76:M76"/>
     <mergeCell ref="F72:M72"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="F54:I54"/>
     <mergeCell ref="F71:M71"/>
     <mergeCell ref="F70:M70"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="J43:L43"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7429,14 +8263,14 @@
       <c r="E11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="107"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
-      <c r="M11" s="94"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="111"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="112"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="18" t="s">
@@ -7448,16 +8282,16 @@
       <c r="E12" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="92" t="s">
+      <c r="F12" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="94"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="112"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -7469,16 +8303,16 @@
       <c r="E13" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="92" t="s">
+      <c r="F13" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="93"/>
-      <c r="K13" s="93"/>
-      <c r="L13" s="93"/>
-      <c r="M13" s="94"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="112"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -7490,16 +8324,16 @@
       <c r="E14" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="92" t="s">
+      <c r="F14" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="93"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="94"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="112"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -7544,16 +8378,16 @@
       <c r="E16" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="109" t="s">
+      <c r="F16" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="93"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="94"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="112"/>
       <c r="N16" s="56" t="s">
         <v>38</v>
       </c>
@@ -7568,16 +8402,16 @@
       <c r="E17" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="109" t="s">
+      <c r="F17" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="94"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="112"/>
       <c r="N17" s="56" t="s">
         <v>38</v>
       </c>
@@ -7605,8 +8439,8 @@
       <c r="J18" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="107"/>
-      <c r="L18" s="94"/>
+      <c r="K18" s="125"/>
+      <c r="L18" s="112"/>
       <c r="M18" s="54" t="s">
         <v>47</v>
       </c>
@@ -7628,8 +8462,8 @@
       <c r="G19" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="107"/>
-      <c r="I19" s="94"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="112"/>
       <c r="J19" s="55" t="s">
         <v>52</v>
       </c>
@@ -7651,16 +8485,16 @@
         <v>19</v>
       </c>
       <c r="E20" s="42"/>
-      <c r="F20" s="108" t="s">
+      <c r="F20" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="93"/>
-      <c r="J20" s="93"/>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="94"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="112"/>
       <c r="N20" t="s">
         <v>58</v>
       </c>
@@ -7673,16 +8507,16 @@
         <v>19</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="108" t="s">
+      <c r="F21" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="93"/>
-      <c r="H21" s="93"/>
-      <c r="I21" s="93"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="94"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="112"/>
       <c r="N21" t="s">
         <v>61</v>
       </c>
@@ -7695,16 +8529,16 @@
         <v>19</v>
       </c>
       <c r="E22" s="41"/>
-      <c r="F22" s="108" t="s">
+      <c r="F22" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="93"/>
-      <c r="H22" s="93"/>
-      <c r="I22" s="93"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="93"/>
-      <c r="L22" s="93"/>
-      <c r="M22" s="94"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="112"/>
       <c r="N22" t="s">
         <v>64</v>
       </c>
@@ -7717,16 +8551,16 @@
         <v>19</v>
       </c>
       <c r="E23" s="41"/>
-      <c r="F23" s="108" t="s">
+      <c r="F23" s="126" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="93"/>
-      <c r="L23" s="93"/>
-      <c r="M23" s="94"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="112"/>
       <c r="N23" t="s">
         <v>67</v>
       </c>
@@ -7741,16 +8575,16 @@
       <c r="E24" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="109" t="s">
+      <c r="F24" s="127" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="93"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="93"/>
-      <c r="L24" s="93"/>
-      <c r="M24" s="94"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="112"/>
       <c r="N24" s="58" t="s">
         <v>38</v>
       </c>
@@ -7765,16 +8599,16 @@
       <c r="E25" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="107"/>
-      <c r="G25" s="93"/>
-      <c r="H25" s="93"/>
-      <c r="I25" s="93"/>
-      <c r="J25" s="94"/>
-      <c r="K25" s="109" t="s">
+      <c r="F25" s="125"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="127" t="s">
         <v>71</v>
       </c>
-      <c r="L25" s="93"/>
-      <c r="M25" s="94"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="112"/>
       <c r="N25" s="56" t="s">
         <v>38</v>
       </c>
@@ -7787,16 +8621,16 @@
         <v>3</v>
       </c>
       <c r="E26" s="41"/>
-      <c r="F26" s="108" t="s">
+      <c r="F26" s="126" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="93"/>
-      <c r="H26" s="93"/>
-      <c r="I26" s="93"/>
-      <c r="J26" s="93"/>
-      <c r="K26" s="93"/>
-      <c r="L26" s="93"/>
-      <c r="M26" s="94"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="112"/>
       <c r="N26" t="s">
         <v>74</v>
       </c>
@@ -7809,16 +8643,16 @@
         <v>19</v>
       </c>
       <c r="E27" s="41"/>
-      <c r="F27" s="108" t="s">
+      <c r="F27" s="126" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="94"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="111"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="112"/>
       <c r="N27" t="s">
         <v>77</v>
       </c>
@@ -7831,16 +8665,16 @@
         <v>19</v>
       </c>
       <c r="E28" s="41"/>
-      <c r="F28" s="108" t="s">
+      <c r="F28" s="126" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="93"/>
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="94"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="111"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="112"/>
       <c r="N28" t="s">
         <v>80</v>
       </c>
@@ -7853,16 +8687,16 @@
         <v>19</v>
       </c>
       <c r="E29" s="41"/>
-      <c r="F29" s="108" t="s">
+      <c r="F29" s="126" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="94"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="111"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="111"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="112"/>
       <c r="N29" t="s">
         <v>83</v>
       </c>
@@ -7877,14 +8711,14 @@
       <c r="E30" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="107"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="94"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="111"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="112"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="59" t="s">
@@ -7896,14 +8730,14 @@
       <c r="E31" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="107"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="94"/>
+      <c r="F31" s="125"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="111"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="112"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="59" t="s">
@@ -7915,16 +8749,16 @@
       <c r="E32" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="109" t="s">
+      <c r="F32" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="93"/>
-      <c r="H32" s="93"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="93"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="94"/>
+      <c r="G32" s="111"/>
+      <c r="H32" s="111"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="111"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="112"/>
       <c r="N32" s="56" t="s">
         <v>38</v>
       </c>
@@ -7939,16 +8773,16 @@
       <c r="E33" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="109" t="s">
+      <c r="F33" s="127" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="94"/>
-      <c r="H33" s="107"/>
-      <c r="I33" s="93"/>
-      <c r="J33" s="93"/>
-      <c r="K33" s="93"/>
-      <c r="L33" s="93"/>
-      <c r="M33" s="94"/>
+      <c r="G33" s="112"/>
+      <c r="H33" s="125"/>
+      <c r="I33" s="111"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="111"/>
+      <c r="L33" s="111"/>
+      <c r="M33" s="112"/>
       <c r="N33" s="56" t="s">
         <v>38</v>
       </c>
@@ -7963,16 +8797,16 @@
       <c r="E34" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="107"/>
-      <c r="G34" s="93"/>
-      <c r="H34" s="93"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="109" t="s">
+      <c r="F34" s="125"/>
+      <c r="G34" s="111"/>
+      <c r="H34" s="111"/>
+      <c r="I34" s="111"/>
+      <c r="J34" s="112"/>
+      <c r="K34" s="127" t="s">
         <v>91</v>
       </c>
-      <c r="L34" s="93"/>
-      <c r="M34" s="94"/>
+      <c r="L34" s="111"/>
+      <c r="M34" s="112"/>
       <c r="N34" s="56" t="s">
         <v>38</v>
       </c>
@@ -7987,16 +8821,16 @@
       <c r="E35" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="107"/>
-      <c r="G35" s="93"/>
-      <c r="H35" s="93"/>
-      <c r="I35" s="94"/>
-      <c r="J35" s="109" t="s">
+      <c r="F35" s="125"/>
+      <c r="G35" s="111"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="112"/>
+      <c r="J35" s="127" t="s">
         <v>93</v>
       </c>
-      <c r="K35" s="93"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="94"/>
+      <c r="K35" s="111"/>
+      <c r="L35" s="111"/>
+      <c r="M35" s="112"/>
       <c r="N35" s="56" t="s">
         <v>38</v>
       </c>
@@ -8011,16 +8845,16 @@
       <c r="E36" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="107"/>
-      <c r="G36" s="93"/>
-      <c r="H36" s="93"/>
-      <c r="I36" s="94"/>
-      <c r="J36" s="109" t="s">
+      <c r="F36" s="125"/>
+      <c r="G36" s="111"/>
+      <c r="H36" s="111"/>
+      <c r="I36" s="112"/>
+      <c r="J36" s="127" t="s">
         <v>95</v>
       </c>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="94"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="111"/>
+      <c r="M36" s="112"/>
       <c r="N36" s="56" t="s">
         <v>38</v>
       </c>
@@ -8035,16 +8869,16 @@
       <c r="E37" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="109" t="s">
+      <c r="F37" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="93"/>
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="94"/>
+      <c r="G37" s="111"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="111"/>
+      <c r="J37" s="111"/>
+      <c r="K37" s="111"/>
+      <c r="L37" s="111"/>
+      <c r="M37" s="112"/>
       <c r="N37" s="56" t="s">
         <v>38</v>
       </c>
@@ -8059,14 +8893,14 @@
       <c r="E38" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="107"/>
-      <c r="G38" s="93"/>
-      <c r="H38" s="93"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="94"/>
+      <c r="F38" s="125"/>
+      <c r="G38" s="111"/>
+      <c r="H38" s="111"/>
+      <c r="I38" s="111"/>
+      <c r="J38" s="111"/>
+      <c r="K38" s="111"/>
+      <c r="L38" s="111"/>
+      <c r="M38" s="112"/>
       <c r="N38" t="s">
         <v>99</v>
       </c>
@@ -8081,14 +8915,14 @@
       <c r="E39" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="107"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="93"/>
-      <c r="I39" s="93"/>
-      <c r="J39" s="93"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="93"/>
-      <c r="M39" s="94"/>
+      <c r="F39" s="125"/>
+      <c r="G39" s="111"/>
+      <c r="H39" s="111"/>
+      <c r="I39" s="111"/>
+      <c r="J39" s="111"/>
+      <c r="K39" s="111"/>
+      <c r="L39" s="111"/>
+      <c r="M39" s="112"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="59" t="s">
@@ -8100,14 +8934,14 @@
       <c r="E40" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F40" s="107"/>
-      <c r="G40" s="93"/>
-      <c r="H40" s="93"/>
-      <c r="I40" s="93"/>
-      <c r="J40" s="93"/>
-      <c r="K40" s="93"/>
-      <c r="L40" s="93"/>
-      <c r="M40" s="94"/>
+      <c r="F40" s="125"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="111"/>
+      <c r="I40" s="111"/>
+      <c r="J40" s="111"/>
+      <c r="K40" s="111"/>
+      <c r="L40" s="111"/>
+      <c r="M40" s="112"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="59" t="s">
@@ -8119,14 +8953,14 @@
       <c r="E41" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F41" s="107"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="93"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="93"/>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="94"/>
+      <c r="F41" s="125"/>
+      <c r="G41" s="111"/>
+      <c r="H41" s="111"/>
+      <c r="I41" s="111"/>
+      <c r="J41" s="111"/>
+      <c r="K41" s="111"/>
+      <c r="L41" s="111"/>
+      <c r="M41" s="112"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="59" t="s">
@@ -8138,14 +8972,14 @@
       <c r="E42" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F42" s="107"/>
-      <c r="G42" s="93"/>
-      <c r="H42" s="93"/>
-      <c r="I42" s="93"/>
-      <c r="J42" s="93"/>
-      <c r="K42" s="93"/>
-      <c r="L42" s="93"/>
-      <c r="M42" s="94"/>
+      <c r="F42" s="125"/>
+      <c r="G42" s="111"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="111"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="111"/>
+      <c r="L42" s="111"/>
+      <c r="M42" s="112"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="19" t="s">
@@ -8167,12 +9001,12 @@
       <c r="I43" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="92" t="s">
+      <c r="J43" s="113" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="93"/>
-      <c r="L43" s="93"/>
-      <c r="M43" s="94"/>
+      <c r="K43" s="111"/>
+      <c r="L43" s="111"/>
+      <c r="M43" s="112"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
@@ -8182,18 +9016,18 @@
         <v>19</v>
       </c>
       <c r="E44" s="42"/>
-      <c r="F44" s="92" t="s">
+      <c r="F44" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="G44" s="94"/>
-      <c r="H44" s="92" t="s">
+      <c r="G44" s="112"/>
+      <c r="H44" s="113" t="s">
         <v>112</v>
       </c>
-      <c r="I44" s="93"/>
-      <c r="J44" s="93"/>
-      <c r="K44" s="93"/>
-      <c r="L44" s="93"/>
-      <c r="M44" s="94"/>
+      <c r="I44" s="111"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="111"/>
+      <c r="L44" s="111"/>
+      <c r="M44" s="112"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
@@ -8203,18 +9037,18 @@
         <v>19</v>
       </c>
       <c r="E45" s="42"/>
-      <c r="F45" s="110" t="s">
+      <c r="F45" s="129" t="s">
         <v>114</v>
       </c>
-      <c r="G45" s="111"/>
-      <c r="H45" s="111"/>
-      <c r="I45" s="112"/>
-      <c r="J45" s="92" t="s">
+      <c r="G45" s="130"/>
+      <c r="H45" s="130"/>
+      <c r="I45" s="131"/>
+      <c r="J45" s="113" t="s">
         <v>115</v>
       </c>
-      <c r="K45" s="93"/>
-      <c r="L45" s="93"/>
-      <c r="M45" s="94"/>
+      <c r="K45" s="111"/>
+      <c r="L45" s="111"/>
+      <c r="M45" s="112"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
@@ -8224,18 +9058,18 @@
         <v>19</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="92" t="s">
+      <c r="F46" s="113" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="93"/>
-      <c r="H46" s="93"/>
-      <c r="I46" s="94"/>
-      <c r="J46" s="113" t="s">
+      <c r="G46" s="111"/>
+      <c r="H46" s="111"/>
+      <c r="I46" s="112"/>
+      <c r="J46" s="128" t="s">
         <v>118</v>
       </c>
-      <c r="K46" s="105"/>
-      <c r="L46" s="105"/>
-      <c r="M46" s="106"/>
+      <c r="K46" s="123"/>
+      <c r="L46" s="123"/>
+      <c r="M46" s="124"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18" t="s">
@@ -8245,16 +9079,16 @@
         <v>19</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="98" t="s">
+      <c r="F47" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="G47" s="93"/>
-      <c r="H47" s="93"/>
-      <c r="I47" s="93"/>
-      <c r="J47" s="93"/>
-      <c r="K47" s="93"/>
-      <c r="L47" s="93"/>
-      <c r="M47" s="94"/>
+      <c r="G47" s="111"/>
+      <c r="H47" s="111"/>
+      <c r="I47" s="111"/>
+      <c r="J47" s="111"/>
+      <c r="K47" s="111"/>
+      <c r="L47" s="111"/>
+      <c r="M47" s="112"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
@@ -8264,20 +9098,20 @@
         <v>19</v>
       </c>
       <c r="E48" s="5"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="94"/>
+      <c r="F48" s="110"/>
+      <c r="G48" s="112"/>
       <c r="H48" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I48" s="98" t="s">
+      <c r="I48" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="J48" s="93"/>
-      <c r="K48" s="94"/>
-      <c r="L48" s="98" t="s">
+      <c r="J48" s="111"/>
+      <c r="K48" s="112"/>
+      <c r="L48" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="M48" s="94"/>
+      <c r="M48" s="112"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
@@ -8320,15 +9154,15 @@
         <v>19</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="99"/>
-      <c r="G50" s="93"/>
-      <c r="H50" s="93"/>
-      <c r="I50" s="94"/>
-      <c r="J50" s="98" t="s">
+      <c r="F50" s="110"/>
+      <c r="G50" s="111"/>
+      <c r="H50" s="111"/>
+      <c r="I50" s="112"/>
+      <c r="J50" s="118" t="s">
         <v>133</v>
       </c>
-      <c r="K50" s="93"/>
-      <c r="L50" s="94"/>
+      <c r="K50" s="111"/>
+      <c r="L50" s="112"/>
       <c r="M50" s="12" t="s">
         <v>134</v>
       </c>
@@ -8343,16 +9177,16 @@
       <c r="E51" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F51" s="107"/>
-      <c r="G51" s="93"/>
-      <c r="H51" s="93"/>
-      <c r="I51" s="93"/>
-      <c r="J51" s="93"/>
-      <c r="K51" s="94"/>
-      <c r="L51" s="100" t="s">
+      <c r="F51" s="125"/>
+      <c r="G51" s="111"/>
+      <c r="H51" s="111"/>
+      <c r="I51" s="111"/>
+      <c r="J51" s="111"/>
+      <c r="K51" s="112"/>
+      <c r="L51" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="M51" s="94"/>
+      <c r="M51" s="112"/>
     </row>
     <row r="52" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -8364,16 +9198,16 @@
       <c r="E52" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F52" s="100" t="s">
+      <c r="F52" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="93"/>
-      <c r="H52" s="93"/>
-      <c r="I52" s="93"/>
-      <c r="J52" s="93"/>
-      <c r="K52" s="93"/>
-      <c r="L52" s="93"/>
-      <c r="M52" s="94"/>
+      <c r="G52" s="111"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="111"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="111"/>
+      <c r="L52" s="111"/>
+      <c r="M52" s="112"/>
       <c r="N52" t="s">
         <v>141</v>
       </c>
@@ -8388,16 +9222,16 @@
       <c r="E53" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F53" s="100" t="s">
+      <c r="F53" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="93"/>
-      <c r="H53" s="93"/>
-      <c r="I53" s="93"/>
-      <c r="J53" s="93"/>
-      <c r="K53" s="93"/>
-      <c r="L53" s="93"/>
-      <c r="M53" s="94"/>
+      <c r="G53" s="111"/>
+      <c r="H53" s="111"/>
+      <c r="I53" s="111"/>
+      <c r="J53" s="111"/>
+      <c r="K53" s="111"/>
+      <c r="L53" s="111"/>
+      <c r="M53" s="112"/>
       <c r="N53" t="s">
         <v>141</v>
       </c>
@@ -8412,16 +9246,16 @@
       <c r="E54" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F54" s="100" t="s">
+      <c r="F54" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="93"/>
-      <c r="H54" s="93"/>
-      <c r="I54" s="93"/>
-      <c r="J54" s="93"/>
-      <c r="K54" s="93"/>
-      <c r="L54" s="93"/>
-      <c r="M54" s="94"/>
+      <c r="G54" s="111"/>
+      <c r="H54" s="111"/>
+      <c r="I54" s="111"/>
+      <c r="J54" s="111"/>
+      <c r="K54" s="111"/>
+      <c r="L54" s="111"/>
+      <c r="M54" s="112"/>
       <c r="N54" t="s">
         <v>141</v>
       </c>
@@ -8436,16 +9270,16 @@
       <c r="E55" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="100" t="s">
+      <c r="F55" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G55" s="93"/>
-      <c r="H55" s="93"/>
-      <c r="I55" s="93"/>
-      <c r="J55" s="93"/>
-      <c r="K55" s="93"/>
-      <c r="L55" s="93"/>
-      <c r="M55" s="94"/>
+      <c r="G55" s="111"/>
+      <c r="H55" s="111"/>
+      <c r="I55" s="111"/>
+      <c r="J55" s="111"/>
+      <c r="K55" s="111"/>
+      <c r="L55" s="111"/>
+      <c r="M55" s="112"/>
       <c r="N55" t="s">
         <v>141</v>
       </c>
@@ -8460,16 +9294,16 @@
       <c r="E56" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="100" t="s">
+      <c r="F56" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="93"/>
-      <c r="H56" s="93"/>
-      <c r="I56" s="93"/>
-      <c r="J56" s="93"/>
-      <c r="K56" s="93"/>
-      <c r="L56" s="93"/>
-      <c r="M56" s="94"/>
+      <c r="G56" s="111"/>
+      <c r="H56" s="111"/>
+      <c r="I56" s="111"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="111"/>
+      <c r="L56" s="111"/>
+      <c r="M56" s="112"/>
       <c r="N56" t="s">
         <v>141</v>
       </c>
@@ -8484,16 +9318,16 @@
       <c r="E57" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F57" s="100" t="s">
+      <c r="F57" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="93"/>
-      <c r="H57" s="93"/>
-      <c r="I57" s="93"/>
-      <c r="J57" s="93"/>
-      <c r="K57" s="93"/>
-      <c r="L57" s="93"/>
-      <c r="M57" s="94"/>
+      <c r="G57" s="111"/>
+      <c r="H57" s="111"/>
+      <c r="I57" s="111"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="111"/>
+      <c r="L57" s="111"/>
+      <c r="M57" s="112"/>
       <c r="N57" t="s">
         <v>141</v>
       </c>
@@ -8508,16 +9342,16 @@
       <c r="E58" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F58" s="100" t="s">
+      <c r="F58" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="93"/>
-      <c r="H58" s="93"/>
-      <c r="I58" s="93"/>
-      <c r="J58" s="93"/>
-      <c r="K58" s="93"/>
-      <c r="L58" s="93"/>
-      <c r="M58" s="94"/>
+      <c r="G58" s="111"/>
+      <c r="H58" s="111"/>
+      <c r="I58" s="111"/>
+      <c r="J58" s="111"/>
+      <c r="K58" s="111"/>
+      <c r="L58" s="111"/>
+      <c r="M58" s="112"/>
       <c r="N58" t="s">
         <v>141</v>
       </c>
@@ -8532,16 +9366,16 @@
       <c r="E59" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="F59" s="100" t="s">
+      <c r="F59" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G59" s="93"/>
-      <c r="H59" s="93"/>
-      <c r="I59" s="93"/>
-      <c r="J59" s="93"/>
-      <c r="K59" s="93"/>
-      <c r="L59" s="93"/>
-      <c r="M59" s="94"/>
+      <c r="G59" s="111"/>
+      <c r="H59" s="111"/>
+      <c r="I59" s="111"/>
+      <c r="J59" s="111"/>
+      <c r="K59" s="111"/>
+      <c r="L59" s="111"/>
+      <c r="M59" s="112"/>
       <c r="N59" t="s">
         <v>141</v>
       </c>
@@ -8556,16 +9390,16 @@
       <c r="E60" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F60" s="100" t="s">
+      <c r="F60" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G60" s="93"/>
-      <c r="H60" s="93"/>
-      <c r="I60" s="93"/>
-      <c r="J60" s="93"/>
-      <c r="K60" s="93"/>
-      <c r="L60" s="93"/>
-      <c r="M60" s="94"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="111"/>
+      <c r="L60" s="111"/>
+      <c r="M60" s="112"/>
       <c r="N60" t="s">
         <v>141</v>
       </c>
@@ -8580,16 +9414,16 @@
       <c r="E61" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="F61" s="100" t="s">
+      <c r="F61" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="G61" s="93"/>
-      <c r="H61" s="93"/>
-      <c r="I61" s="93"/>
-      <c r="J61" s="93"/>
-      <c r="K61" s="93"/>
-      <c r="L61" s="93"/>
-      <c r="M61" s="94"/>
+      <c r="G61" s="111"/>
+      <c r="H61" s="111"/>
+      <c r="I61" s="111"/>
+      <c r="J61" s="111"/>
+      <c r="K61" s="111"/>
+      <c r="L61" s="111"/>
+      <c r="M61" s="112"/>
       <c r="N61" t="s">
         <v>141</v>
       </c>
@@ -8617,23 +9451,51 @@
       <c r="J63" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="K63" s="99"/>
-      <c r="L63" s="94"/>
+      <c r="K63" s="110"/>
+      <c r="L63" s="112"/>
       <c r="M63" s="53" t="s">
         <v>166</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="F51:K51"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F60:M60"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F59:M59"/>
+    <mergeCell ref="F21:M21"/>
+    <mergeCell ref="F55:M55"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F20:M20"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="F47:M47"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F61:M61"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F27:M27"/>
     <mergeCell ref="F11:M11"/>
     <mergeCell ref="J43:M43"/>
     <mergeCell ref="F54:M54"/>
@@ -8650,43 +9512,15 @@
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="J36:M36"/>
     <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="F47:M47"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F61:M61"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="F60:M60"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F59:M59"/>
-    <mergeCell ref="F21:M21"/>
-    <mergeCell ref="F55:M55"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F20:M20"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="F51:K51"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="F38:M38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8830,29 +9664,29 @@
       </c>
     </row>
     <row r="9" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="E9" s="89" t="s">
+      <c r="E9" s="132" t="s">
         <v>428</v>
       </c>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="91"/>
-      <c r="K9" s="89" t="s">
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="132" t="s">
         <v>427</v>
       </c>
-      <c r="L9" s="90"/>
-      <c r="M9" s="90"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="90"/>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="90"/>
-      <c r="R9" s="90"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="90"/>
-      <c r="U9" s="90"/>
-      <c r="V9" s="90"/>
-      <c r="W9" s="91"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="133"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="133"/>
+      <c r="T9" s="133"/>
+      <c r="U9" s="133"/>
+      <c r="V9" s="133"/>
+      <c r="W9" s="134"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.15">
       <c r="E11" t="s">

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119C2E0D-8783-41D7-A8B4-2D6E87857A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8DE791-AEF2-46D4-A4DB-E5DAEFAE58D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="75" windowWidth="20025" windowHeight="15975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modules" sheetId="1" r:id="rId1"/>
@@ -1777,22 +1777,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>SCCレジスタ ( RAM Mode = 0 で BANK2-BANK#63, または RAM Mode = 1 で BANK1-BANK#63  ), 9xxxhはBANK2に出現した場合、7xxxh は BANK1に出現した場合のアドレス。</t>
-    <rPh sb="89" eb="91">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>9880h-988Fh のミラー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2053,6 +2037,28 @@
     </rPh>
     <rPh sb="71" eb="73">
       <t>イガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SCCレジスタ ( 「RAM Mode = 0 で BANK2-BANK#63」, または RAM Mode = 1 のときは「BANK1 または BANK1 に BANK#63 を出現」させると利用できる  ), 9xxxhはBANK2に出現した場合、7xxxh は BANK1に出現した場合のアドレス。</t>
+    <rPh sb="91" eb="93">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="141" eb="143">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2981,10 +2987,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2996,36 +3025,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3040,14 +3046,14 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3701,12 +3707,12 @@
         <v>187</v>
       </c>
       <c r="G4" s="110"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="112"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="105"/>
       <c r="N4" s="66" t="s">
         <v>205</v>
       </c>
@@ -3727,16 +3733,16 @@
       <c r="F5" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G5" s="114" t="s">
+      <c r="G5" s="111" t="s">
         <v>209</v>
       </c>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="112"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="105"/>
       <c r="O5" s="49" t="s">
         <v>210</v>
       </c>
@@ -3754,16 +3760,16 @@
       <c r="F6" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G6" s="114" t="s">
+      <c r="G6" s="111" t="s">
         <v>209</v>
       </c>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="111"/>
-      <c r="L6" s="111"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="112"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="105"/>
       <c r="O6" s="49" t="s">
         <v>210</v>
       </c>
@@ -3781,16 +3787,16 @@
       <c r="F7" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="114" t="s">
+      <c r="G7" s="111" t="s">
         <v>209</v>
       </c>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
-      <c r="N7" s="112"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="105"/>
       <c r="O7" s="49" t="s">
         <v>210</v>
       </c>
@@ -3808,16 +3814,16 @@
       <c r="F8" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G8" s="114" t="s">
+      <c r="G8" s="111" t="s">
         <v>209</v>
       </c>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="111"/>
-      <c r="L8" s="111"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="112"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="105"/>
       <c r="O8" s="49" t="s">
         <v>210</v>
       </c>
@@ -3835,16 +3841,16 @@
       <c r="F9" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G9" s="113" t="s">
+      <c r="G9" s="109" t="s">
         <v>218</v>
       </c>
-      <c r="H9" s="111"/>
-      <c r="I9" s="111"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="112"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="104"/>
+      <c r="K9" s="104"/>
+      <c r="L9" s="104"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="105"/>
       <c r="O9" s="49" t="s">
         <v>219</v>
       </c>
@@ -3862,16 +3868,16 @@
       <c r="F10" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G10" s="113" t="s">
+      <c r="G10" s="109" t="s">
         <v>218</v>
       </c>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="111"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="112"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="104"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="105"/>
       <c r="O10" s="49" t="s">
         <v>219</v>
       </c>
@@ -3889,16 +3895,16 @@
       <c r="F11" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G11" s="117" t="s">
+      <c r="G11" s="113" t="s">
         <v>222</v>
       </c>
-      <c r="H11" s="111"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="111"/>
-      <c r="K11" s="111"/>
-      <c r="L11" s="111"/>
-      <c r="M11" s="111"/>
-      <c r="N11" s="112"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="104"/>
+      <c r="N11" s="105"/>
       <c r="O11" s="50" t="s">
         <v>397</v>
       </c>
@@ -3916,16 +3922,16 @@
       <c r="F12" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="117" t="s">
+      <c r="G12" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="111"/>
-      <c r="N12" s="112"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="104"/>
+      <c r="N12" s="105"/>
       <c r="O12" s="50" t="s">
         <v>397</v>
       </c>
@@ -3943,16 +3949,16 @@
       <c r="F13" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G13" s="115" t="s">
+      <c r="G13" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="112"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="105"/>
       <c r="O13" s="50" t="s">
         <v>397</v>
       </c>
@@ -3970,16 +3976,16 @@
       <c r="F14" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G14" s="115" t="s">
+      <c r="G14" s="103" t="s">
         <v>228</v>
       </c>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="111"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="112"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="105"/>
       <c r="O14" s="50" t="s">
         <v>397</v>
       </c>
@@ -3997,16 +4003,16 @@
       <c r="F15" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G15" s="118" t="s">
+      <c r="G15" s="106" t="s">
         <v>230</v>
       </c>
-      <c r="H15" s="111"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="112"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="104"/>
+      <c r="N15" s="105"/>
       <c r="O15" s="50" t="s">
         <v>397</v>
       </c>
@@ -4024,16 +4030,16 @@
       <c r="F16" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G16" s="118" t="s">
+      <c r="G16" s="106" t="s">
         <v>233</v>
       </c>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="112"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="105"/>
       <c r="O16" s="50" t="s">
         <v>397</v>
       </c>
@@ -4051,13 +4057,13 @@
       <c r="F17" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G17" s="116"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="112"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="104"/>
+      <c r="L17" s="104"/>
+      <c r="M17" s="105"/>
       <c r="N17" s="10" t="s">
         <v>176</v>
       </c>
@@ -4078,14 +4084,14 @@
       <c r="F18" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G18" s="115"/>
-      <c r="H18" s="111"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="111"/>
-      <c r="M18" s="111"/>
-      <c r="N18" s="112"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="104"/>
+      <c r="N18" s="105"/>
       <c r="O18" s="50" t="s">
         <v>398</v>
       </c>
@@ -4103,14 +4109,14 @@
       <c r="F19" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="115"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="111"/>
-      <c r="N19" s="112"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="104"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="105"/>
       <c r="O19" s="50" t="s">
         <v>398</v>
       </c>
@@ -4128,14 +4134,14 @@
       <c r="F20" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G20" s="115"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="111"/>
-      <c r="N20" s="112"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="105"/>
       <c r="O20" s="50" t="s">
         <v>398</v>
       </c>
@@ -4270,10 +4276,10 @@
         <v>251</v>
       </c>
       <c r="H26" s="110"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="111"/>
-      <c r="L26" s="112"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="105"/>
       <c r="M26" s="32" t="s">
         <v>173</v>
       </c>
@@ -4297,16 +4303,16 @@
       <c r="F27" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="113" t="s">
+      <c r="G27" s="109" t="s">
         <v>218</v>
       </c>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="111"/>
-      <c r="N27" s="112"/>
+      <c r="H27" s="104"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="105"/>
       <c r="O27" s="49" t="s">
         <v>219</v>
       </c>
@@ -4324,102 +4330,102 @@
       <c r="F28" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="113" t="s">
+      <c r="G28" s="109" t="s">
         <v>218</v>
       </c>
-      <c r="H28" s="111"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="112"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="105"/>
       <c r="O28" s="49" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="30" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B30" s="79" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.15">
       <c r="C31" s="93" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D31" s="100" t="s">
         <v>448</v>
       </c>
       <c r="E31" s="100" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F31" s="101" t="s">
-        <v>519</v>
-      </c>
-      <c r="G31" s="105" t="s">
-        <v>499</v>
-      </c>
-      <c r="H31" s="106"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="106"/>
-      <c r="M31" s="106"/>
-      <c r="N31" s="106"/>
+        <v>518</v>
+      </c>
+      <c r="G31" s="114" t="s">
+        <v>498</v>
+      </c>
+      <c r="H31" s="115"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="115"/>
+      <c r="N31" s="115"/>
       <c r="O31" s="81" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.15">
       <c r="C32" s="89" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>448</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>519</v>
-      </c>
-      <c r="G32" s="103" t="s">
-        <v>499</v>
-      </c>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="104"/>
+        <v>518</v>
+      </c>
+      <c r="G32" s="107" t="s">
+        <v>498</v>
+      </c>
+      <c r="H32" s="108"/>
+      <c r="I32" s="108"/>
+      <c r="J32" s="108"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="108"/>
+      <c r="M32" s="108"/>
+      <c r="N32" s="108"/>
       <c r="O32" s="83" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="33" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C33" s="89" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>431</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F33" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="F33" s="22" t="s">
-        <v>519</v>
-      </c>
-      <c r="G33" s="103" t="s">
+      <c r="G33" s="107" t="s">
         <v>218</v>
       </c>
-      <c r="H33" s="104"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="104"/>
-      <c r="N33" s="104"/>
+      <c r="H33" s="108"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="108"/>
+      <c r="K33" s="108"/>
+      <c r="L33" s="108"/>
+      <c r="M33" s="108"/>
+      <c r="N33" s="108"/>
       <c r="O33" s="83" t="s">
         <v>219</v>
       </c>
@@ -4437,16 +4443,16 @@
       <c r="F34" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G34" s="103" t="s">
-        <v>507</v>
-      </c>
-      <c r="H34" s="104"/>
-      <c r="I34" s="104"/>
-      <c r="J34" s="104"/>
-      <c r="K34" s="104"/>
-      <c r="L34" s="104"/>
-      <c r="M34" s="104"/>
-      <c r="N34" s="104"/>
+      <c r="G34" s="107" t="s">
+        <v>506</v>
+      </c>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="108"/>
+      <c r="N34" s="108"/>
       <c r="O34" s="83"/>
     </row>
     <row r="35" spans="3:15" x14ac:dyDescent="0.15">
@@ -4462,16 +4468,16 @@
       <c r="F35" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G35" s="103" t="s">
-        <v>508</v>
-      </c>
-      <c r="H35" s="104"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="104"/>
-      <c r="K35" s="104"/>
-      <c r="L35" s="104"/>
-      <c r="M35" s="104"/>
-      <c r="N35" s="104"/>
+      <c r="G35" s="107" t="s">
+        <v>507</v>
+      </c>
+      <c r="H35" s="108"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="108"/>
+      <c r="K35" s="108"/>
+      <c r="L35" s="108"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
       <c r="O35" s="83"/>
     </row>
     <row r="36" spans="3:15" x14ac:dyDescent="0.15">
@@ -4487,16 +4493,16 @@
       <c r="F36" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G36" s="103" t="s">
-        <v>509</v>
-      </c>
-      <c r="H36" s="104"/>
-      <c r="I36" s="104"/>
-      <c r="J36" s="104"/>
-      <c r="K36" s="104"/>
-      <c r="L36" s="104"/>
-      <c r="M36" s="104"/>
-      <c r="N36" s="104"/>
+      <c r="G36" s="107" t="s">
+        <v>508</v>
+      </c>
+      <c r="H36" s="108"/>
+      <c r="I36" s="108"/>
+      <c r="J36" s="108"/>
+      <c r="K36" s="108"/>
+      <c r="L36" s="108"/>
+      <c r="M36" s="108"/>
+      <c r="N36" s="108"/>
       <c r="O36" s="83"/>
     </row>
     <row r="37" spans="3:15" x14ac:dyDescent="0.15">
@@ -4512,16 +4518,16 @@
       <c r="F37" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G37" s="103" t="s">
-        <v>510</v>
-      </c>
-      <c r="H37" s="104"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="104"/>
-      <c r="N37" s="104"/>
+      <c r="G37" s="107" t="s">
+        <v>509</v>
+      </c>
+      <c r="H37" s="108"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="108"/>
+      <c r="K37" s="108"/>
+      <c r="L37" s="108"/>
+      <c r="M37" s="108"/>
+      <c r="N37" s="108"/>
       <c r="O37" s="83"/>
     </row>
     <row r="38" spans="3:15" x14ac:dyDescent="0.15">
@@ -4537,18 +4543,18 @@
       <c r="F38" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G38" s="103" t="s">
-        <v>511</v>
-      </c>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="104"/>
-      <c r="N38" s="104"/>
+      <c r="G38" s="107" t="s">
+        <v>510</v>
+      </c>
+      <c r="H38" s="108"/>
+      <c r="I38" s="108"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="M38" s="108"/>
+      <c r="N38" s="108"/>
       <c r="O38" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="3:15" x14ac:dyDescent="0.15">
@@ -4564,18 +4570,18 @@
       <c r="F39" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G39" s="103" t="s">
-        <v>512</v>
-      </c>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="104"/>
-      <c r="K39" s="104"/>
-      <c r="L39" s="104"/>
-      <c r="M39" s="104"/>
-      <c r="N39" s="104"/>
+      <c r="G39" s="107" t="s">
+        <v>511</v>
+      </c>
+      <c r="H39" s="108"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
+      <c r="K39" s="108"/>
+      <c r="L39" s="108"/>
+      <c r="M39" s="108"/>
+      <c r="N39" s="108"/>
       <c r="O39" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="40" spans="3:15" x14ac:dyDescent="0.15">
@@ -4591,18 +4597,18 @@
       <c r="F40" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G40" s="103" t="s">
-        <v>513</v>
-      </c>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="104"/>
-      <c r="N40" s="104"/>
+      <c r="G40" s="107" t="s">
+        <v>512</v>
+      </c>
+      <c r="H40" s="108"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="108"/>
+      <c r="K40" s="108"/>
+      <c r="L40" s="108"/>
+      <c r="M40" s="108"/>
+      <c r="N40" s="108"/>
       <c r="O40" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="41" spans="3:15" x14ac:dyDescent="0.15">
@@ -4618,18 +4624,18 @@
       <c r="F41" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G41" s="103" t="s">
-        <v>514</v>
-      </c>
-      <c r="H41" s="104"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="104"/>
-      <c r="K41" s="104"/>
-      <c r="L41" s="104"/>
-      <c r="M41" s="104"/>
-      <c r="N41" s="104"/>
+      <c r="G41" s="107" t="s">
+        <v>513</v>
+      </c>
+      <c r="H41" s="108"/>
+      <c r="I41" s="108"/>
+      <c r="J41" s="108"/>
+      <c r="K41" s="108"/>
+      <c r="L41" s="108"/>
+      <c r="M41" s="108"/>
+      <c r="N41" s="108"/>
       <c r="O41" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="42" spans="3:15" x14ac:dyDescent="0.15">
@@ -4645,18 +4651,18 @@
       <c r="F42" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G42" s="103" t="s">
-        <v>515</v>
-      </c>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="104"/>
-      <c r="L42" s="104"/>
-      <c r="M42" s="104"/>
-      <c r="N42" s="104"/>
+      <c r="G42" s="107" t="s">
+        <v>514</v>
+      </c>
+      <c r="H42" s="108"/>
+      <c r="I42" s="108"/>
+      <c r="J42" s="108"/>
+      <c r="K42" s="108"/>
+      <c r="L42" s="108"/>
+      <c r="M42" s="108"/>
+      <c r="N42" s="108"/>
       <c r="O42" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="43" spans="3:15" x14ac:dyDescent="0.15">
@@ -4672,18 +4678,18 @@
       <c r="F43" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G43" s="103" t="s">
-        <v>502</v>
-      </c>
-      <c r="H43" s="104"/>
-      <c r="I43" s="104"/>
-      <c r="J43" s="104"/>
-      <c r="K43" s="104"/>
-      <c r="L43" s="104"/>
-      <c r="M43" s="104"/>
-      <c r="N43" s="104"/>
+      <c r="G43" s="107" t="s">
+        <v>501</v>
+      </c>
+      <c r="H43" s="108"/>
+      <c r="I43" s="108"/>
+      <c r="J43" s="108"/>
+      <c r="K43" s="108"/>
+      <c r="L43" s="108"/>
+      <c r="M43" s="108"/>
+      <c r="N43" s="108"/>
       <c r="O43" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.15">
@@ -4699,18 +4705,18 @@
       <c r="F44" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G44" s="103" t="s">
-        <v>503</v>
-      </c>
-      <c r="H44" s="104"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="104"/>
-      <c r="K44" s="104"/>
-      <c r="L44" s="104"/>
-      <c r="M44" s="104"/>
-      <c r="N44" s="104"/>
+      <c r="G44" s="107" t="s">
+        <v>502</v>
+      </c>
+      <c r="H44" s="108"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="108"/>
+      <c r="K44" s="108"/>
+      <c r="L44" s="108"/>
+      <c r="M44" s="108"/>
+      <c r="N44" s="108"/>
       <c r="O44" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="45" spans="3:15" x14ac:dyDescent="0.15">
@@ -4726,18 +4732,18 @@
       <c r="F45" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G45" s="103" t="s">
-        <v>504</v>
-      </c>
-      <c r="H45" s="104"/>
-      <c r="I45" s="104"/>
-      <c r="J45" s="104"/>
-      <c r="K45" s="104"/>
-      <c r="L45" s="104"/>
-      <c r="M45" s="104"/>
-      <c r="N45" s="104"/>
+      <c r="G45" s="107" t="s">
+        <v>503</v>
+      </c>
+      <c r="H45" s="108"/>
+      <c r="I45" s="108"/>
+      <c r="J45" s="108"/>
+      <c r="K45" s="108"/>
+      <c r="L45" s="108"/>
+      <c r="M45" s="108"/>
+      <c r="N45" s="108"/>
       <c r="O45" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="46" spans="3:15" x14ac:dyDescent="0.15">
@@ -4753,18 +4759,18 @@
       <c r="F46" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G46" s="103" t="s">
-        <v>505</v>
-      </c>
-      <c r="H46" s="104"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="104"/>
-      <c r="K46" s="104"/>
-      <c r="L46" s="104"/>
-      <c r="M46" s="104"/>
-      <c r="N46" s="104"/>
+      <c r="G46" s="107" t="s">
+        <v>504</v>
+      </c>
+      <c r="H46" s="108"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="108"/>
+      <c r="K46" s="108"/>
+      <c r="L46" s="108"/>
+      <c r="M46" s="108"/>
+      <c r="N46" s="108"/>
       <c r="O46" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" spans="3:15" x14ac:dyDescent="0.15">
@@ -4780,18 +4786,18 @@
       <c r="F47" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G47" s="103" t="s">
-        <v>506</v>
-      </c>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="104"/>
-      <c r="L47" s="104"/>
-      <c r="M47" s="104"/>
-      <c r="N47" s="104"/>
+      <c r="G47" s="107" t="s">
+        <v>505</v>
+      </c>
+      <c r="H47" s="108"/>
+      <c r="I47" s="108"/>
+      <c r="J47" s="108"/>
+      <c r="K47" s="108"/>
+      <c r="L47" s="108"/>
+      <c r="M47" s="108"/>
+      <c r="N47" s="108"/>
       <c r="O47" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="48" spans="3:15" x14ac:dyDescent="0.15">
@@ -4807,18 +4813,18 @@
       <c r="F48" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G48" s="103" t="s">
-        <v>501</v>
-      </c>
-      <c r="H48" s="104"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="104"/>
-      <c r="K48" s="104"/>
-      <c r="L48" s="104"/>
-      <c r="M48" s="104"/>
-      <c r="N48" s="104"/>
+      <c r="G48" s="107" t="s">
+        <v>500</v>
+      </c>
+      <c r="H48" s="108"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="108"/>
+      <c r="K48" s="108"/>
+      <c r="L48" s="108"/>
+      <c r="M48" s="108"/>
+      <c r="N48" s="108"/>
       <c r="O48" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" spans="3:15" x14ac:dyDescent="0.15">
@@ -4834,18 +4840,18 @@
       <c r="F49" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G49" s="103" t="s">
-        <v>498</v>
-      </c>
-      <c r="H49" s="104"/>
-      <c r="I49" s="104"/>
-      <c r="J49" s="104"/>
-      <c r="K49" s="104"/>
-      <c r="L49" s="104"/>
-      <c r="M49" s="104"/>
-      <c r="N49" s="104"/>
+      <c r="G49" s="107" t="s">
+        <v>497</v>
+      </c>
+      <c r="H49" s="108"/>
+      <c r="I49" s="108"/>
+      <c r="J49" s="108"/>
+      <c r="K49" s="108"/>
+      <c r="L49" s="108"/>
+      <c r="M49" s="108"/>
+      <c r="N49" s="108"/>
       <c r="O49" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="50" spans="3:15" x14ac:dyDescent="0.15">
@@ -4856,23 +4862,23 @@
         <v>448</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F50" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G50" s="103" t="s">
-        <v>530</v>
-      </c>
-      <c r="H50" s="104"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="104"/>
-      <c r="K50" s="104"/>
-      <c r="L50" s="104"/>
-      <c r="M50" s="104"/>
-      <c r="N50" s="104"/>
+      <c r="G50" s="107" t="s">
+        <v>529</v>
+      </c>
+      <c r="H50" s="108"/>
+      <c r="I50" s="108"/>
+      <c r="J50" s="108"/>
+      <c r="K50" s="108"/>
+      <c r="L50" s="108"/>
+      <c r="M50" s="108"/>
+      <c r="N50" s="108"/>
       <c r="O50" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="51" spans="3:15" x14ac:dyDescent="0.15">
@@ -4883,23 +4889,23 @@
         <v>448</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F51" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G51" s="103" t="s">
-        <v>530</v>
-      </c>
-      <c r="H51" s="104"/>
-      <c r="I51" s="104"/>
-      <c r="J51" s="104"/>
-      <c r="K51" s="104"/>
-      <c r="L51" s="104"/>
-      <c r="M51" s="104"/>
-      <c r="N51" s="104"/>
+      <c r="G51" s="107" t="s">
+        <v>529</v>
+      </c>
+      <c r="H51" s="108"/>
+      <c r="I51" s="108"/>
+      <c r="J51" s="108"/>
+      <c r="K51" s="108"/>
+      <c r="L51" s="108"/>
+      <c r="M51" s="108"/>
+      <c r="N51" s="108"/>
       <c r="O51" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="52" spans="3:15" x14ac:dyDescent="0.15">
@@ -4915,18 +4921,18 @@
       <c r="F52" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G52" s="103" t="s">
-        <v>500</v>
-      </c>
-      <c r="H52" s="104"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="104"/>
-      <c r="K52" s="104"/>
-      <c r="L52" s="104"/>
-      <c r="M52" s="104"/>
-      <c r="N52" s="104"/>
+      <c r="G52" s="107" t="s">
+        <v>499</v>
+      </c>
+      <c r="H52" s="108"/>
+      <c r="I52" s="108"/>
+      <c r="J52" s="108"/>
+      <c r="K52" s="108"/>
+      <c r="L52" s="108"/>
+      <c r="M52" s="108"/>
+      <c r="N52" s="108"/>
       <c r="O52" s="83" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="53" spans="3:15" x14ac:dyDescent="0.15">
@@ -4942,18 +4948,18 @@
       <c r="F53" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G53" s="109" t="s">
+      <c r="G53" s="118" t="s">
         <v>140</v>
       </c>
-      <c r="H53" s="104"/>
-      <c r="I53" s="104"/>
-      <c r="J53" s="104"/>
-      <c r="K53" s="104"/>
-      <c r="L53" s="104"/>
-      <c r="M53" s="104"/>
-      <c r="N53" s="104"/>
+      <c r="H53" s="108"/>
+      <c r="I53" s="108"/>
+      <c r="J53" s="108"/>
+      <c r="K53" s="108"/>
+      <c r="L53" s="108"/>
+      <c r="M53" s="108"/>
+      <c r="N53" s="108"/>
       <c r="O53" s="83" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="54" spans="3:15" x14ac:dyDescent="0.15">
@@ -4969,23 +4975,23 @@
       <c r="F54" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G54" s="109" t="s">
+      <c r="G54" s="118" t="s">
         <v>140</v>
       </c>
-      <c r="H54" s="104"/>
-      <c r="I54" s="104"/>
-      <c r="J54" s="104"/>
-      <c r="K54" s="104"/>
-      <c r="L54" s="104"/>
-      <c r="M54" s="104"/>
-      <c r="N54" s="104"/>
+      <c r="H54" s="108"/>
+      <c r="I54" s="108"/>
+      <c r="J54" s="108"/>
+      <c r="K54" s="108"/>
+      <c r="L54" s="108"/>
+      <c r="M54" s="108"/>
+      <c r="N54" s="108"/>
       <c r="O54" s="83" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="55" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C55" s="89" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>431</v>
@@ -4996,18 +5002,18 @@
       <c r="F55" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G55" s="109" t="s">
+      <c r="G55" s="118" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="104"/>
-      <c r="I55" s="104"/>
-      <c r="J55" s="104"/>
-      <c r="K55" s="104"/>
-      <c r="L55" s="104"/>
-      <c r="M55" s="104"/>
-      <c r="N55" s="104"/>
+      <c r="H55" s="108"/>
+      <c r="I55" s="108"/>
+      <c r="J55" s="108"/>
+      <c r="K55" s="108"/>
+      <c r="L55" s="108"/>
+      <c r="M55" s="108"/>
+      <c r="N55" s="108"/>
       <c r="O55" s="83" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="56" spans="3:15" x14ac:dyDescent="0.15">
@@ -5023,18 +5029,18 @@
       <c r="F56" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G56" s="109" t="s">
+      <c r="G56" s="118" t="s">
         <v>140</v>
       </c>
-      <c r="H56" s="104"/>
-      <c r="I56" s="104"/>
-      <c r="J56" s="104"/>
-      <c r="K56" s="104"/>
-      <c r="L56" s="104"/>
-      <c r="M56" s="104"/>
-      <c r="N56" s="104"/>
+      <c r="H56" s="108"/>
+      <c r="I56" s="108"/>
+      <c r="J56" s="108"/>
+      <c r="K56" s="108"/>
+      <c r="L56" s="108"/>
+      <c r="M56" s="108"/>
+      <c r="N56" s="108"/>
       <c r="O56" s="83" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="57" spans="3:15" x14ac:dyDescent="0.15">
@@ -5050,68 +5056,68 @@
       <c r="F57" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G57" s="109" t="s">
+      <c r="G57" s="118" t="s">
         <v>140</v>
       </c>
-      <c r="H57" s="104"/>
-      <c r="I57" s="104"/>
-      <c r="J57" s="104"/>
-      <c r="K57" s="104"/>
-      <c r="L57" s="104"/>
-      <c r="M57" s="104"/>
-      <c r="N57" s="104"/>
+      <c r="H57" s="108"/>
+      <c r="I57" s="108"/>
+      <c r="J57" s="108"/>
+      <c r="K57" s="108"/>
+      <c r="L57" s="108"/>
+      <c r="M57" s="108"/>
+      <c r="N57" s="108"/>
       <c r="O57" s="83" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="58" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C58" s="89" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>448</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>519</v>
-      </c>
-      <c r="G58" s="103" t="s">
-        <v>530</v>
-      </c>
-      <c r="H58" s="104"/>
-      <c r="I58" s="104"/>
-      <c r="J58" s="104"/>
-      <c r="K58" s="104"/>
-      <c r="L58" s="104"/>
-      <c r="M58" s="104"/>
-      <c r="N58" s="104"/>
+        <v>518</v>
+      </c>
+      <c r="G58" s="107" t="s">
+        <v>529</v>
+      </c>
+      <c r="H58" s="108"/>
+      <c r="I58" s="108"/>
+      <c r="J58" s="108"/>
+      <c r="K58" s="108"/>
+      <c r="L58" s="108"/>
+      <c r="M58" s="108"/>
+      <c r="N58" s="108"/>
       <c r="O58" s="83" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="59" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="90" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D59" s="102" t="s">
         <v>431</v>
       </c>
       <c r="E59" s="91" t="s">
+        <v>523</v>
+      </c>
+      <c r="F59" s="91"/>
+      <c r="G59" s="116" t="s">
         <v>524</v>
       </c>
-      <c r="F59" s="91"/>
-      <c r="G59" s="107" t="s">
-        <v>525</v>
-      </c>
-      <c r="H59" s="108"/>
-      <c r="I59" s="108"/>
-      <c r="J59" s="108"/>
-      <c r="K59" s="108"/>
-      <c r="L59" s="108"/>
-      <c r="M59" s="108"/>
-      <c r="N59" s="108"/>
+      <c r="H59" s="117"/>
+      <c r="I59" s="117"/>
+      <c r="J59" s="117"/>
+      <c r="K59" s="117"/>
+      <c r="L59" s="117"/>
+      <c r="M59" s="117"/>
+      <c r="N59" s="117"/>
       <c r="O59" s="85"/>
     </row>
     <row r="61" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -5246,7 +5252,7 @@
       </c>
       <c r="D78" s="92"/>
       <c r="E78" s="96" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="79" spans="3:5" x14ac:dyDescent="0.15">
@@ -5262,7 +5268,7 @@
       </c>
       <c r="D80" s="92"/>
       <c r="E80" s="96" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="81" spans="3:5" ht="40.5" x14ac:dyDescent="0.15">
@@ -5271,7 +5277,7 @@
       </c>
       <c r="D81" s="92"/>
       <c r="E81" s="99" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="82" spans="3:5" x14ac:dyDescent="0.15">
@@ -5326,16 +5332,29 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="G14:N14"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="G16:N16"/>
-    <mergeCell ref="G32:N32"/>
-    <mergeCell ref="G34:N34"/>
-    <mergeCell ref="G35:N35"/>
-    <mergeCell ref="G36:N36"/>
-    <mergeCell ref="G37:N37"/>
-    <mergeCell ref="G28:N28"/>
-    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G58:N58"/>
+    <mergeCell ref="G31:N31"/>
+    <mergeCell ref="G59:N59"/>
+    <mergeCell ref="G57:N57"/>
+    <mergeCell ref="G53:N53"/>
+    <mergeCell ref="G54:N54"/>
+    <mergeCell ref="G55:N55"/>
+    <mergeCell ref="G56:N56"/>
+    <mergeCell ref="G48:N48"/>
+    <mergeCell ref="G49:N49"/>
+    <mergeCell ref="G50:N50"/>
+    <mergeCell ref="G51:N51"/>
+    <mergeCell ref="G52:N52"/>
+    <mergeCell ref="G43:N43"/>
+    <mergeCell ref="G44:N44"/>
+    <mergeCell ref="G45:N45"/>
+    <mergeCell ref="G46:N46"/>
+    <mergeCell ref="G47:N47"/>
+    <mergeCell ref="G38:N38"/>
+    <mergeCell ref="G39:N39"/>
+    <mergeCell ref="G40:N40"/>
+    <mergeCell ref="G41:N41"/>
+    <mergeCell ref="G42:N42"/>
     <mergeCell ref="G4:M4"/>
     <mergeCell ref="G27:N27"/>
     <mergeCell ref="G8:N8"/>
@@ -5352,29 +5371,16 @@
     <mergeCell ref="G12:N12"/>
     <mergeCell ref="G11:N11"/>
     <mergeCell ref="G15:N15"/>
-    <mergeCell ref="G46:N46"/>
-    <mergeCell ref="G47:N47"/>
-    <mergeCell ref="G38:N38"/>
-    <mergeCell ref="G39:N39"/>
-    <mergeCell ref="G40:N40"/>
-    <mergeCell ref="G41:N41"/>
-    <mergeCell ref="G42:N42"/>
-    <mergeCell ref="G58:N58"/>
-    <mergeCell ref="G31:N31"/>
-    <mergeCell ref="G59:N59"/>
-    <mergeCell ref="G57:N57"/>
-    <mergeCell ref="G53:N53"/>
-    <mergeCell ref="G54:N54"/>
-    <mergeCell ref="G55:N55"/>
-    <mergeCell ref="G56:N56"/>
-    <mergeCell ref="G48:N48"/>
-    <mergeCell ref="G49:N49"/>
-    <mergeCell ref="G50:N50"/>
-    <mergeCell ref="G51:N51"/>
-    <mergeCell ref="G52:N52"/>
-    <mergeCell ref="G43:N43"/>
-    <mergeCell ref="G44:N44"/>
-    <mergeCell ref="G45:N45"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="G36:N36"/>
+    <mergeCell ref="G37:N37"/>
+    <mergeCell ref="G28:N28"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G16:N16"/>
+    <mergeCell ref="G32:N32"/>
+    <mergeCell ref="G34:N34"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5494,16 +5500,16 @@
       <c r="E12" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F12" s="119" t="s">
+      <c r="F12" s="121" t="s">
         <v>263</v>
       </c>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="112"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="105"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -5519,12 +5525,12 @@
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="119" t="s">
+      <c r="J13" s="121" t="s">
         <v>265</v>
       </c>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="112"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="105"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -5536,16 +5542,16 @@
       <c r="E14" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F14" s="119" t="s">
+      <c r="F14" s="121" t="s">
         <v>263</v>
       </c>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="111"/>
-      <c r="M14" s="112"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="105"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -5561,12 +5567,12 @@
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="35"/>
-      <c r="J15" s="119" t="s">
+      <c r="J15" s="121" t="s">
         <v>265</v>
       </c>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="112"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="105"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="18" t="s">
@@ -5578,16 +5584,16 @@
       <c r="E16" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F16" s="119" t="s">
+      <c r="F16" s="121" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="112"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="105"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="18" t="s">
@@ -5603,12 +5609,12 @@
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
       <c r="I17" s="35"/>
-      <c r="J17" s="119" t="s">
+      <c r="J17" s="121" t="s">
         <v>265</v>
       </c>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="112"/>
+      <c r="K17" s="104"/>
+      <c r="L17" s="104"/>
+      <c r="M17" s="105"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="18" t="s">
@@ -5623,13 +5629,13 @@
       <c r="F18" s="33"/>
       <c r="G18" s="34"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="119" t="s">
+      <c r="I18" s="121" t="s">
         <v>271</v>
       </c>
-      <c r="J18" s="111"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="111"/>
-      <c r="M18" s="112"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="105"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="18" t="s">
@@ -5682,12 +5688,12 @@
       <c r="I20" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="J20" s="119" t="s">
+      <c r="J20" s="121" t="s">
         <v>282</v>
       </c>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="112"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="105"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -5705,12 +5711,12 @@
       <c r="I21" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="J21" s="119" t="s">
+      <c r="J21" s="121" t="s">
         <v>282</v>
       </c>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="112"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="105"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -5728,12 +5734,12 @@
       <c r="I22" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="J22" s="119" t="s">
+      <c r="J22" s="121" t="s">
         <v>282</v>
       </c>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="112"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="105"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -5745,16 +5751,16 @@
       <c r="E23" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F23" s="119" t="s">
+      <c r="F23" s="121" t="s">
         <v>286</v>
       </c>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="112"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="105"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -5766,16 +5772,16 @@
       <c r="E24" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F24" s="119" t="s">
+      <c r="F24" s="121" t="s">
         <v>288</v>
       </c>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="112"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="105"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -5791,12 +5797,12 @@
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="119" t="s">
+      <c r="J25" s="121" t="s">
         <v>290</v>
       </c>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="112"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="105"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -5846,16 +5852,16 @@
       <c r="E28" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="F28" s="115" t="s">
+      <c r="F28" s="103" t="s">
         <v>263</v>
       </c>
-      <c r="G28" s="111"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="112"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="105"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="18" t="s">
@@ -5871,12 +5877,12 @@
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="27"/>
-      <c r="J29" s="115" t="s">
+      <c r="J29" s="103" t="s">
         <v>265</v>
       </c>
-      <c r="K29" s="111"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="112"/>
+      <c r="K29" s="104"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="105"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -5888,16 +5894,16 @@
       <c r="E30" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="F30" s="115" t="s">
+      <c r="F30" s="103" t="s">
         <v>263</v>
       </c>
-      <c r="G30" s="111"/>
-      <c r="H30" s="111"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="112"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="105"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -5913,12 +5919,12 @@
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="27"/>
-      <c r="J31" s="115" t="s">
+      <c r="J31" s="103" t="s">
         <v>265</v>
       </c>
-      <c r="K31" s="111"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="112"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="105"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -5930,16 +5936,16 @@
       <c r="E32" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="F32" s="115" t="s">
+      <c r="F32" s="103" t="s">
         <v>263</v>
       </c>
-      <c r="G32" s="111"/>
-      <c r="H32" s="111"/>
-      <c r="I32" s="111"/>
-      <c r="J32" s="111"/>
-      <c r="K32" s="111"/>
-      <c r="L32" s="111"/>
-      <c r="M32" s="112"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="105"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -5955,12 +5961,12 @@
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="27"/>
-      <c r="J33" s="115" t="s">
+      <c r="J33" s="103" t="s">
         <v>265</v>
       </c>
-      <c r="K33" s="111"/>
-      <c r="L33" s="111"/>
-      <c r="M33" s="112"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="104"/>
+      <c r="M33" s="105"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -5975,13 +5981,13 @@
       <c r="F34" s="25"/>
       <c r="G34" s="26"/>
       <c r="H34" s="27"/>
-      <c r="I34" s="115" t="s">
+      <c r="I34" s="103" t="s">
         <v>271</v>
       </c>
-      <c r="J34" s="111"/>
-      <c r="K34" s="111"/>
-      <c r="L34" s="111"/>
-      <c r="M34" s="112"/>
+      <c r="J34" s="104"/>
+      <c r="K34" s="104"/>
+      <c r="L34" s="104"/>
+      <c r="M34" s="105"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -6034,12 +6040,12 @@
       <c r="I36" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J36" s="115" t="s">
+      <c r="J36" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="112"/>
+      <c r="K36" s="104"/>
+      <c r="L36" s="104"/>
+      <c r="M36" s="105"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -6057,12 +6063,12 @@
       <c r="I37" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J37" s="115" t="s">
+      <c r="J37" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="K37" s="111"/>
-      <c r="L37" s="111"/>
-      <c r="M37" s="112"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="104"/>
+      <c r="M37" s="105"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -6080,12 +6086,12 @@
       <c r="I38" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J38" s="115" t="s">
+      <c r="J38" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="K38" s="111"/>
-      <c r="L38" s="111"/>
-      <c r="M38" s="112"/>
+      <c r="K38" s="104"/>
+      <c r="L38" s="104"/>
+      <c r="M38" s="105"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -6097,16 +6103,16 @@
       <c r="E39" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="F39" s="115" t="s">
+      <c r="F39" s="103" t="s">
         <v>286</v>
       </c>
-      <c r="G39" s="111"/>
-      <c r="H39" s="111"/>
-      <c r="I39" s="111"/>
-      <c r="J39" s="111"/>
-      <c r="K39" s="111"/>
-      <c r="L39" s="111"/>
-      <c r="M39" s="112"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="104"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="104"/>
+      <c r="L39" s="104"/>
+      <c r="M39" s="105"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18" t="s">
@@ -6118,16 +6124,16 @@
       <c r="E40" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="F40" s="115" t="s">
+      <c r="F40" s="103" t="s">
         <v>288</v>
       </c>
-      <c r="G40" s="111"/>
-      <c r="H40" s="111"/>
-      <c r="I40" s="111"/>
-      <c r="J40" s="111"/>
-      <c r="K40" s="111"/>
-      <c r="L40" s="111"/>
-      <c r="M40" s="112"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="104"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="104"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="104"/>
+      <c r="M40" s="105"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18" t="s">
@@ -6143,12 +6149,12 @@
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="27"/>
-      <c r="J41" s="115" t="s">
+      <c r="J41" s="103" t="s">
         <v>290</v>
       </c>
-      <c r="K41" s="111"/>
-      <c r="L41" s="111"/>
-      <c r="M41" s="112"/>
+      <c r="K41" s="104"/>
+      <c r="L41" s="104"/>
+      <c r="M41" s="105"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18" t="s">
@@ -6200,16 +6206,16 @@
       <c r="E44" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="F44" s="120" t="s">
+      <c r="F44" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="G44" s="111"/>
-      <c r="H44" s="111"/>
-      <c r="I44" s="111"/>
-      <c r="J44" s="111"/>
-      <c r="K44" s="111"/>
-      <c r="L44" s="111"/>
-      <c r="M44" s="121"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="104"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="104"/>
+      <c r="K44" s="104"/>
+      <c r="L44" s="104"/>
+      <c r="M44" s="120"/>
       <c r="O44" t="s">
         <v>312</v>
       </c>
@@ -6224,16 +6230,16 @@
       <c r="E45" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="F45" s="120" t="s">
+      <c r="F45" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="G45" s="111"/>
-      <c r="H45" s="111"/>
-      <c r="I45" s="111"/>
-      <c r="J45" s="111"/>
-      <c r="K45" s="111"/>
-      <c r="L45" s="111"/>
-      <c r="M45" s="121"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="104"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="104"/>
+      <c r="K45" s="104"/>
+      <c r="L45" s="104"/>
+      <c r="M45" s="120"/>
       <c r="O45" t="s">
         <v>312</v>
       </c>
@@ -6248,16 +6254,16 @@
       <c r="E46" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="F46" s="120" t="s">
+      <c r="F46" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="G46" s="111"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="111"/>
-      <c r="J46" s="111"/>
-      <c r="K46" s="111"/>
-      <c r="L46" s="111"/>
-      <c r="M46" s="121"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="104"/>
+      <c r="K46" s="104"/>
+      <c r="L46" s="104"/>
+      <c r="M46" s="120"/>
       <c r="O46" t="s">
         <v>312</v>
       </c>
@@ -6291,16 +6297,16 @@
       <c r="E48" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="F48" s="120" t="s">
+      <c r="F48" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="G48" s="111"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="111"/>
-      <c r="L48" s="111"/>
-      <c r="M48" s="121"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="104"/>
+      <c r="K48" s="104"/>
+      <c r="L48" s="104"/>
+      <c r="M48" s="120"/>
       <c r="O48" t="s">
         <v>312</v>
       </c>
@@ -6315,16 +6321,16 @@
       <c r="E49" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="F49" s="120" t="s">
+      <c r="F49" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="G49" s="111"/>
-      <c r="H49" s="111"/>
-      <c r="I49" s="111"/>
-      <c r="J49" s="111"/>
-      <c r="K49" s="111"/>
-      <c r="L49" s="111"/>
-      <c r="M49" s="121"/>
+      <c r="G49" s="104"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="104"/>
+      <c r="J49" s="104"/>
+      <c r="K49" s="104"/>
+      <c r="L49" s="104"/>
+      <c r="M49" s="120"/>
       <c r="O49" t="s">
         <v>312</v>
       </c>
@@ -6339,16 +6345,16 @@
       <c r="E50" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="F50" s="120" t="s">
+      <c r="F50" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="G50" s="111"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="111"/>
-      <c r="J50" s="111"/>
-      <c r="K50" s="111"/>
-      <c r="L50" s="111"/>
-      <c r="M50" s="121"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="104"/>
+      <c r="K50" s="104"/>
+      <c r="L50" s="104"/>
+      <c r="M50" s="120"/>
       <c r="O50" t="s">
         <v>312</v>
       </c>
@@ -6382,16 +6388,16 @@
       <c r="E52" s="22" t="s">
         <v>327</v>
       </c>
-      <c r="F52" s="115" t="s">
+      <c r="F52" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="111"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="111"/>
-      <c r="J52" s="111"/>
-      <c r="K52" s="111"/>
-      <c r="L52" s="111"/>
-      <c r="M52" s="112"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="104"/>
+      <c r="M52" s="105"/>
       <c r="O52" t="s">
         <v>438</v>
       </c>
@@ -6406,16 +6412,16 @@
       <c r="E53" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="F53" s="115" t="s">
+      <c r="F53" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="111"/>
-      <c r="H53" s="111"/>
-      <c r="I53" s="111"/>
-      <c r="J53" s="111"/>
-      <c r="K53" s="111"/>
-      <c r="L53" s="111"/>
-      <c r="M53" s="112"/>
+      <c r="G53" s="104"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="104"/>
+      <c r="M53" s="105"/>
       <c r="O53" t="s">
         <v>141</v>
       </c>
@@ -6430,16 +6436,16 @@
       <c r="E54" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="F54" s="115" t="s">
+      <c r="F54" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="111"/>
-      <c r="H54" s="111"/>
-      <c r="I54" s="111"/>
-      <c r="J54" s="111"/>
-      <c r="K54" s="111"/>
-      <c r="L54" s="111"/>
-      <c r="M54" s="112"/>
+      <c r="G54" s="104"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="104"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="104"/>
+      <c r="M54" s="105"/>
       <c r="O54" t="s">
         <v>141</v>
       </c>
@@ -6473,16 +6479,16 @@
       <c r="E56" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="F56" s="115" t="s">
+      <c r="F56" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="111"/>
-      <c r="H56" s="111"/>
-      <c r="I56" s="111"/>
-      <c r="J56" s="111"/>
-      <c r="K56" s="111"/>
-      <c r="L56" s="111"/>
-      <c r="M56" s="112"/>
+      <c r="G56" s="104"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="104"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="104"/>
+      <c r="M56" s="105"/>
       <c r="O56" t="s">
         <v>141</v>
       </c>
@@ -6497,16 +6503,16 @@
       <c r="E57" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="F57" s="115" t="s">
+      <c r="F57" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="111"/>
-      <c r="H57" s="111"/>
-      <c r="I57" s="111"/>
-      <c r="J57" s="111"/>
-      <c r="K57" s="111"/>
-      <c r="L57" s="111"/>
-      <c r="M57" s="112"/>
+      <c r="G57" s="104"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="104"/>
+      <c r="K57" s="104"/>
+      <c r="L57" s="104"/>
+      <c r="M57" s="105"/>
       <c r="O57" t="s">
         <v>141</v>
       </c>
@@ -6521,16 +6527,16 @@
       <c r="E58" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="F58" s="115" t="s">
+      <c r="F58" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="111"/>
-      <c r="H58" s="111"/>
-      <c r="I58" s="111"/>
-      <c r="J58" s="111"/>
-      <c r="K58" s="111"/>
-      <c r="L58" s="111"/>
-      <c r="M58" s="112"/>
+      <c r="G58" s="104"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="104"/>
+      <c r="K58" s="104"/>
+      <c r="L58" s="104"/>
+      <c r="M58" s="105"/>
       <c r="O58" t="s">
         <v>141</v>
       </c>
@@ -6575,18 +6581,17 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:M48"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F50:M50"/>
-    <mergeCell ref="F46:M46"/>
-    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J43:M43"/>
     <mergeCell ref="F12:M12"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J17:M17"/>
@@ -6603,17 +6608,18 @@
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F45:M45"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:M48"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F53:M53"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6688,16 +6694,16 @@
       <c r="E6" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="F6" s="118" t="s">
+      <c r="F6" s="106" t="s">
         <v>344</v>
       </c>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="111"/>
-      <c r="L6" s="111"/>
-      <c r="M6" s="112"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="105"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
@@ -6709,16 +6715,16 @@
       <c r="E7" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F7" s="118" t="s">
+      <c r="F7" s="106" t="s">
         <v>347</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="112"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="105"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
@@ -6780,12 +6786,12 @@
       <c r="I19" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="118" t="s">
+      <c r="J19" s="106" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="111"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="112"/>
+      <c r="K19" s="104"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="105"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="18" t="s">
@@ -6807,12 +6813,12 @@
       <c r="I20" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="118" t="s">
+      <c r="J20" s="106" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="112"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="105"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -6822,18 +6828,18 @@
         <v>19</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="118" t="s">
+      <c r="F21" s="106" t="s">
         <v>350</v>
       </c>
-      <c r="G21" s="112"/>
-      <c r="H21" s="118" t="s">
+      <c r="G21" s="105"/>
+      <c r="H21" s="106" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="111"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="112"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="105"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -6843,10 +6849,10 @@
         <v>19</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="118" t="s">
+      <c r="F22" s="106" t="s">
         <v>350</v>
       </c>
-      <c r="G22" s="112"/>
+      <c r="G22" s="105"/>
       <c r="H22" s="17"/>
       <c r="I22" s="10" t="s">
         <v>351</v>
@@ -6854,11 +6860,11 @@
       <c r="J22" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="K22" s="118" t="s">
+      <c r="K22" s="106" t="s">
         <v>133</v>
       </c>
-      <c r="L22" s="111"/>
-      <c r="M22" s="112"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="105"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -6868,18 +6874,18 @@
         <v>19</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="118" t="s">
+      <c r="F23" s="106" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="112"/>
-      <c r="J23" s="118" t="s">
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="106" t="s">
         <v>115</v>
       </c>
-      <c r="K23" s="111"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="112"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="105"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -6889,18 +6895,18 @@
         <v>19</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="118" t="s">
+      <c r="F24" s="106" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="112"/>
-      <c r="J24" s="118" t="s">
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="106" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="112"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="105"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -6910,18 +6916,18 @@
         <v>19</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="118" t="s">
+      <c r="F25" s="106" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="118" t="s">
+      <c r="G25" s="104"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="106" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="112"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="105"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -6931,18 +6937,18 @@
         <v>19</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="118" t="s">
+      <c r="F26" s="106" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="118" t="s">
+      <c r="G26" s="104"/>
+      <c r="H26" s="104"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="106" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="111"/>
-      <c r="L26" s="111"/>
-      <c r="M26" s="112"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="105"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="18" t="s">
@@ -6996,16 +7002,16 @@
       <c r="E29" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="118" t="s">
+      <c r="F29" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="111"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="112"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="104"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="105"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -7015,16 +7021,16 @@
         <v>19</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="118" t="s">
+      <c r="F30" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="111"/>
-      <c r="H30" s="111"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="112"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="105"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -7034,16 +7040,16 @@
         <v>19</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="118" t="s">
+      <c r="F31" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="111"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="111"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="111"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="112"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="105"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -7053,16 +7059,16 @@
         <v>19</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="118" t="s">
+      <c r="F32" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="111"/>
-      <c r="H32" s="111"/>
-      <c r="I32" s="111"/>
-      <c r="J32" s="111"/>
-      <c r="K32" s="111"/>
-      <c r="L32" s="111"/>
-      <c r="M32" s="112"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="105"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -7072,16 +7078,16 @@
         <v>19</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="118" t="s">
+      <c r="F33" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="111"/>
-      <c r="H33" s="111"/>
-      <c r="I33" s="111"/>
-      <c r="J33" s="111"/>
-      <c r="K33" s="111"/>
-      <c r="L33" s="111"/>
-      <c r="M33" s="112"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="104"/>
+      <c r="M33" s="105"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -7091,16 +7097,16 @@
         <v>19</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="118" t="s">
+      <c r="F34" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="111"/>
-      <c r="H34" s="111"/>
-      <c r="I34" s="111"/>
-      <c r="J34" s="111"/>
-      <c r="K34" s="111"/>
-      <c r="L34" s="111"/>
-      <c r="M34" s="112"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="104"/>
+      <c r="K34" s="104"/>
+      <c r="L34" s="104"/>
+      <c r="M34" s="105"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -7110,16 +7116,16 @@
         <v>19</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="118" t="s">
+      <c r="F35" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="112"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="104"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="104"/>
+      <c r="K35" s="104"/>
+      <c r="L35" s="104"/>
+      <c r="M35" s="105"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="18" t="s">
@@ -7129,16 +7135,16 @@
         <v>19</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="118" t="s">
+      <c r="F36" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="112"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="104"/>
+      <c r="I36" s="104"/>
+      <c r="J36" s="104"/>
+      <c r="K36" s="104"/>
+      <c r="L36" s="104"/>
+      <c r="M36" s="105"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -7148,16 +7154,16 @@
         <v>19</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="118" t="s">
+      <c r="F37" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="111"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="111"/>
-      <c r="J37" s="111"/>
-      <c r="K37" s="111"/>
-      <c r="L37" s="111"/>
-      <c r="M37" s="112"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="104"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="104"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="104"/>
+      <c r="M37" s="105"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -7167,16 +7173,16 @@
         <v>19</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="118" t="s">
+      <c r="F38" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G38" s="111"/>
-      <c r="H38" s="111"/>
-      <c r="I38" s="111"/>
-      <c r="J38" s="111"/>
-      <c r="K38" s="111"/>
-      <c r="L38" s="111"/>
-      <c r="M38" s="112"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="104"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="104"/>
+      <c r="K38" s="104"/>
+      <c r="L38" s="104"/>
+      <c r="M38" s="105"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -7211,11 +7217,11 @@
       <c r="I40" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J40" s="118" t="s">
+      <c r="J40" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="K40" s="111"/>
-      <c r="L40" s="112"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="105"/>
       <c r="M40" s="12" t="s">
         <v>120</v>
       </c>
@@ -7236,11 +7242,11 @@
       <c r="I41" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J41" s="118" t="s">
+      <c r="J41" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="K41" s="111"/>
-      <c r="L41" s="112"/>
+      <c r="K41" s="104"/>
+      <c r="L41" s="105"/>
       <c r="M41" s="12" t="s">
         <v>120</v>
       </c>
@@ -7261,11 +7267,11 @@
       <c r="I42" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J42" s="118" t="s">
+      <c r="J42" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="K42" s="111"/>
-      <c r="L42" s="112"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="105"/>
       <c r="M42" s="12" t="s">
         <v>120</v>
       </c>
@@ -7286,11 +7292,11 @@
       <c r="I43" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J43" s="118" t="s">
+      <c r="J43" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="K43" s="111"/>
-      <c r="L43" s="112"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="105"/>
       <c r="M43" s="12" t="s">
         <v>120</v>
       </c>
@@ -7311,11 +7317,11 @@
       <c r="I44" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J44" s="118" t="s">
+      <c r="J44" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="K44" s="111"/>
-      <c r="L44" s="112"/>
+      <c r="K44" s="104"/>
+      <c r="L44" s="105"/>
       <c r="M44" s="12" t="s">
         <v>120</v>
       </c>
@@ -7336,11 +7342,11 @@
       <c r="I45" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J45" s="118" t="s">
+      <c r="J45" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="K45" s="111"/>
-      <c r="L45" s="112"/>
+      <c r="K45" s="104"/>
+      <c r="L45" s="105"/>
       <c r="M45" s="12" t="s">
         <v>120</v>
       </c>
@@ -7361,11 +7367,11 @@
       <c r="I46" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J46" s="118" t="s">
+      <c r="J46" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="K46" s="111"/>
-      <c r="L46" s="112"/>
+      <c r="K46" s="104"/>
+      <c r="L46" s="105"/>
       <c r="M46" s="12" t="s">
         <v>120</v>
       </c>
@@ -7386,11 +7392,11 @@
       <c r="I47" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J47" s="118" t="s">
+      <c r="J47" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="K47" s="111"/>
-      <c r="L47" s="112"/>
+      <c r="K47" s="104"/>
+      <c r="L47" s="105"/>
       <c r="M47" s="12" t="s">
         <v>120</v>
       </c>
@@ -7411,11 +7417,11 @@
       <c r="I48" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J48" s="118" t="s">
+      <c r="J48" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="K48" s="111"/>
-      <c r="L48" s="112"/>
+      <c r="K48" s="104"/>
+      <c r="L48" s="105"/>
       <c r="M48" s="12" t="s">
         <v>120</v>
       </c>
@@ -7445,18 +7451,18 @@
         <v>19</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="118" t="s">
+      <c r="F50" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="G50" s="111"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="112"/>
-      <c r="J50" s="118" t="s">
+      <c r="G50" s="104"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="105"/>
+      <c r="J50" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K50" s="111"/>
-      <c r="L50" s="111"/>
-      <c r="M50" s="112"/>
+      <c r="K50" s="104"/>
+      <c r="L50" s="104"/>
+      <c r="M50" s="105"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
@@ -7466,18 +7472,18 @@
         <v>19</v>
       </c>
       <c r="E51" s="11"/>
-      <c r="F51" s="118" t="s">
+      <c r="F51" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="G51" s="111"/>
-      <c r="H51" s="111"/>
-      <c r="I51" s="112"/>
-      <c r="J51" s="118" t="s">
+      <c r="G51" s="104"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="105"/>
+      <c r="J51" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K51" s="111"/>
-      <c r="L51" s="111"/>
-      <c r="M51" s="112"/>
+      <c r="K51" s="104"/>
+      <c r="L51" s="104"/>
+      <c r="M51" s="105"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -7487,18 +7493,18 @@
         <v>19</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="118" t="s">
+      <c r="F52" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="G52" s="111"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="112"/>
-      <c r="J52" s="118" t="s">
+      <c r="G52" s="104"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="105"/>
+      <c r="J52" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K52" s="111"/>
-      <c r="L52" s="111"/>
-      <c r="M52" s="112"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="104"/>
+      <c r="M52" s="105"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18" t="s">
@@ -7508,18 +7514,18 @@
         <v>19</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="118" t="s">
+      <c r="F53" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="G53" s="111"/>
-      <c r="H53" s="111"/>
-      <c r="I53" s="112"/>
-      <c r="J53" s="118" t="s">
+      <c r="G53" s="104"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="105"/>
+      <c r="J53" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K53" s="111"/>
-      <c r="L53" s="111"/>
-      <c r="M53" s="112"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="104"/>
+      <c r="M53" s="105"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18" t="s">
@@ -7529,18 +7535,18 @@
         <v>19</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="118" t="s">
+      <c r="F54" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="G54" s="111"/>
-      <c r="H54" s="111"/>
-      <c r="I54" s="112"/>
-      <c r="J54" s="118" t="s">
+      <c r="G54" s="104"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="105"/>
+      <c r="J54" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K54" s="111"/>
-      <c r="L54" s="111"/>
-      <c r="M54" s="112"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="104"/>
+      <c r="M54" s="105"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18" t="s">
@@ -7550,18 +7556,18 @@
         <v>19</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="118" t="s">
+      <c r="F55" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="G55" s="111"/>
-      <c r="H55" s="111"/>
-      <c r="I55" s="112"/>
-      <c r="J55" s="118" t="s">
+      <c r="G55" s="104"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K55" s="111"/>
-      <c r="L55" s="111"/>
-      <c r="M55" s="112"/>
+      <c r="K55" s="104"/>
+      <c r="L55" s="104"/>
+      <c r="M55" s="105"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18" t="s">
@@ -7571,18 +7577,18 @@
         <v>19</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="118" t="s">
+      <c r="F56" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="G56" s="111"/>
-      <c r="H56" s="111"/>
-      <c r="I56" s="112"/>
-      <c r="J56" s="118" t="s">
+      <c r="G56" s="104"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="105"/>
+      <c r="J56" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K56" s="111"/>
-      <c r="L56" s="111"/>
-      <c r="M56" s="112"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="104"/>
+      <c r="M56" s="105"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18" t="s">
@@ -7592,18 +7598,18 @@
         <v>19</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="118" t="s">
+      <c r="F57" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="G57" s="111"/>
-      <c r="H57" s="111"/>
-      <c r="I57" s="112"/>
-      <c r="J57" s="118" t="s">
+      <c r="G57" s="104"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="105"/>
+      <c r="J57" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K57" s="111"/>
-      <c r="L57" s="111"/>
-      <c r="M57" s="112"/>
+      <c r="K57" s="104"/>
+      <c r="L57" s="104"/>
+      <c r="M57" s="105"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18" t="s">
@@ -7613,18 +7619,18 @@
         <v>19</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="118" t="s">
+      <c r="F58" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="G58" s="111"/>
-      <c r="H58" s="111"/>
-      <c r="I58" s="112"/>
-      <c r="J58" s="118" t="s">
+      <c r="G58" s="104"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="105"/>
+      <c r="J58" s="106" t="s">
         <v>361</v>
       </c>
-      <c r="K58" s="111"/>
-      <c r="L58" s="111"/>
-      <c r="M58" s="112"/>
+      <c r="K58" s="104"/>
+      <c r="L58" s="104"/>
+      <c r="M58" s="105"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="18" t="s">
@@ -7659,10 +7665,10 @@
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="115" t="s">
+      <c r="L60" s="103" t="s">
         <v>373</v>
       </c>
-      <c r="M60" s="112"/>
+      <c r="M60" s="105"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="18" t="s">
@@ -7680,10 +7686,10 @@
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
       <c r="K61" s="9"/>
-      <c r="L61" s="117" t="s">
+      <c r="L61" s="113" t="s">
         <v>373</v>
       </c>
-      <c r="M61" s="112"/>
+      <c r="M61" s="105"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="18" t="s">
@@ -7701,10 +7707,10 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="9"/>
-      <c r="L62" s="117" t="s">
+      <c r="L62" s="113" t="s">
         <v>373</v>
       </c>
-      <c r="M62" s="112"/>
+      <c r="M62" s="105"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="18" t="s">
@@ -7722,10 +7728,10 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="9"/>
-      <c r="L63" s="117" t="s">
+      <c r="L63" s="113" t="s">
         <v>373</v>
       </c>
-      <c r="M63" s="112"/>
+      <c r="M63" s="105"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="18" t="s">
@@ -7743,10 +7749,10 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="9"/>
-      <c r="L64" s="117" t="s">
+      <c r="L64" s="113" t="s">
         <v>373</v>
       </c>
-      <c r="M64" s="112"/>
+      <c r="M64" s="105"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="18" t="s">
@@ -7764,10 +7770,10 @@
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="9"/>
-      <c r="L65" s="117" t="s">
+      <c r="L65" s="113" t="s">
         <v>373</v>
       </c>
-      <c r="M65" s="112"/>
+      <c r="M65" s="105"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="18" t="s">
@@ -7785,10 +7791,10 @@
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
       <c r="K66" s="9"/>
-      <c r="L66" s="117" t="s">
+      <c r="L66" s="113" t="s">
         <v>373</v>
       </c>
-      <c r="M66" s="112"/>
+      <c r="M66" s="105"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="18" t="s">
@@ -7806,10 +7812,10 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="9"/>
-      <c r="L67" s="117" t="s">
+      <c r="L67" s="113" t="s">
         <v>373</v>
       </c>
-      <c r="M67" s="112"/>
+      <c r="M67" s="105"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="18" t="s">
@@ -7827,10 +7833,10 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="9"/>
-      <c r="L68" s="117" t="s">
+      <c r="L68" s="113" t="s">
         <v>373</v>
       </c>
-      <c r="M68" s="112"/>
+      <c r="M68" s="105"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="18" t="s">
@@ -7859,16 +7865,16 @@
       <c r="E70" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F70" s="115" t="s">
+      <c r="F70" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G70" s="111"/>
-      <c r="H70" s="111"/>
-      <c r="I70" s="111"/>
-      <c r="J70" s="111"/>
-      <c r="K70" s="111"/>
-      <c r="L70" s="111"/>
-      <c r="M70" s="112"/>
+      <c r="G70" s="104"/>
+      <c r="H70" s="104"/>
+      <c r="I70" s="104"/>
+      <c r="J70" s="104"/>
+      <c r="K70" s="104"/>
+      <c r="L70" s="104"/>
+      <c r="M70" s="105"/>
       <c r="O70" t="s">
         <v>141</v>
       </c>
@@ -7883,16 +7889,16 @@
       <c r="E71" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F71" s="115" t="s">
+      <c r="F71" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G71" s="111"/>
-      <c r="H71" s="111"/>
-      <c r="I71" s="111"/>
-      <c r="J71" s="111"/>
-      <c r="K71" s="111"/>
-      <c r="L71" s="111"/>
-      <c r="M71" s="112"/>
+      <c r="G71" s="104"/>
+      <c r="H71" s="104"/>
+      <c r="I71" s="104"/>
+      <c r="J71" s="104"/>
+      <c r="K71" s="104"/>
+      <c r="L71" s="104"/>
+      <c r="M71" s="105"/>
       <c r="O71" t="s">
         <v>141</v>
       </c>
@@ -7907,16 +7913,16 @@
       <c r="E72" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F72" s="115" t="s">
+      <c r="F72" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G72" s="111"/>
-      <c r="H72" s="111"/>
-      <c r="I72" s="111"/>
-      <c r="J72" s="111"/>
-      <c r="K72" s="111"/>
-      <c r="L72" s="111"/>
-      <c r="M72" s="112"/>
+      <c r="G72" s="104"/>
+      <c r="H72" s="104"/>
+      <c r="I72" s="104"/>
+      <c r="J72" s="104"/>
+      <c r="K72" s="104"/>
+      <c r="L72" s="104"/>
+      <c r="M72" s="105"/>
       <c r="O72" t="s">
         <v>141</v>
       </c>
@@ -7931,16 +7937,16 @@
       <c r="E73" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F73" s="115" t="s">
+      <c r="F73" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="111"/>
-      <c r="H73" s="111"/>
-      <c r="I73" s="111"/>
-      <c r="J73" s="111"/>
-      <c r="K73" s="111"/>
-      <c r="L73" s="111"/>
-      <c r="M73" s="112"/>
+      <c r="G73" s="104"/>
+      <c r="H73" s="104"/>
+      <c r="I73" s="104"/>
+      <c r="J73" s="104"/>
+      <c r="K73" s="104"/>
+      <c r="L73" s="104"/>
+      <c r="M73" s="105"/>
       <c r="O73" t="s">
         <v>141</v>
       </c>
@@ -7955,16 +7961,16 @@
       <c r="E74" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F74" s="115" t="s">
+      <c r="F74" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G74" s="111"/>
-      <c r="H74" s="111"/>
-      <c r="I74" s="111"/>
-      <c r="J74" s="111"/>
-      <c r="K74" s="111"/>
-      <c r="L74" s="111"/>
-      <c r="M74" s="112"/>
+      <c r="G74" s="104"/>
+      <c r="H74" s="104"/>
+      <c r="I74" s="104"/>
+      <c r="J74" s="104"/>
+      <c r="K74" s="104"/>
+      <c r="L74" s="104"/>
+      <c r="M74" s="105"/>
       <c r="O74" t="s">
         <v>141</v>
       </c>
@@ -7979,16 +7985,16 @@
       <c r="E75" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F75" s="115" t="s">
+      <c r="F75" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G75" s="111"/>
-      <c r="H75" s="111"/>
-      <c r="I75" s="111"/>
-      <c r="J75" s="111"/>
-      <c r="K75" s="111"/>
-      <c r="L75" s="111"/>
-      <c r="M75" s="112"/>
+      <c r="G75" s="104"/>
+      <c r="H75" s="104"/>
+      <c r="I75" s="104"/>
+      <c r="J75" s="104"/>
+      <c r="K75" s="104"/>
+      <c r="L75" s="104"/>
+      <c r="M75" s="105"/>
       <c r="O75" t="s">
         <v>141</v>
       </c>
@@ -8003,16 +8009,16 @@
       <c r="E76" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F76" s="115" t="s">
+      <c r="F76" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G76" s="111"/>
-      <c r="H76" s="111"/>
-      <c r="I76" s="111"/>
-      <c r="J76" s="111"/>
-      <c r="K76" s="111"/>
-      <c r="L76" s="111"/>
-      <c r="M76" s="112"/>
+      <c r="G76" s="104"/>
+      <c r="H76" s="104"/>
+      <c r="I76" s="104"/>
+      <c r="J76" s="104"/>
+      <c r="K76" s="104"/>
+      <c r="L76" s="104"/>
+      <c r="M76" s="105"/>
       <c r="O76" t="s">
         <v>141</v>
       </c>
@@ -8027,16 +8033,16 @@
       <c r="E77" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F77" s="115" t="s">
+      <c r="F77" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G77" s="111"/>
-      <c r="H77" s="111"/>
-      <c r="I77" s="111"/>
-      <c r="J77" s="111"/>
-      <c r="K77" s="111"/>
-      <c r="L77" s="111"/>
-      <c r="M77" s="112"/>
+      <c r="G77" s="104"/>
+      <c r="H77" s="104"/>
+      <c r="I77" s="104"/>
+      <c r="J77" s="104"/>
+      <c r="K77" s="104"/>
+      <c r="L77" s="104"/>
+      <c r="M77" s="105"/>
       <c r="O77" t="s">
         <v>141</v>
       </c>
@@ -8051,16 +8057,16 @@
       <c r="E78" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F78" s="115" t="s">
+      <c r="F78" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="G78" s="111"/>
-      <c r="H78" s="111"/>
-      <c r="I78" s="111"/>
-      <c r="J78" s="111"/>
-      <c r="K78" s="111"/>
-      <c r="L78" s="111"/>
-      <c r="M78" s="112"/>
+      <c r="G78" s="104"/>
+      <c r="H78" s="104"/>
+      <c r="I78" s="104"/>
+      <c r="J78" s="104"/>
+      <c r="K78" s="104"/>
+      <c r="L78" s="104"/>
+      <c r="M78" s="105"/>
       <c r="O78" t="s">
         <v>141</v>
       </c>
@@ -8084,6 +8090,61 @@
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="F73:M73"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F78:M78"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="F74:M74"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="F75:M75"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="F77:M77"/>
+    <mergeCell ref="F76:M76"/>
+    <mergeCell ref="F72:M72"/>
+    <mergeCell ref="F71:M71"/>
+    <mergeCell ref="F70:M70"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J42:L42"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="L65:M65"/>
     <mergeCell ref="J54:M54"/>
@@ -8100,61 +8161,6 @@
     <mergeCell ref="J47:L47"/>
     <mergeCell ref="J48:L48"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="F73:M73"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F78:M78"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="F74:M74"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="F75:M75"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="F77:M77"/>
-    <mergeCell ref="F76:M76"/>
-    <mergeCell ref="F72:M72"/>
-    <mergeCell ref="F71:M71"/>
-    <mergeCell ref="F70:M70"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8264,13 +8270,13 @@
         <v>20</v>
       </c>
       <c r="F11" s="125"/>
-      <c r="G11" s="111"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="111"/>
-      <c r="K11" s="111"/>
-      <c r="L11" s="111"/>
-      <c r="M11" s="112"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="105"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="18" t="s">
@@ -8282,16 +8288,16 @@
       <c r="E12" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="113" t="s">
+      <c r="F12" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="112"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="105"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -8303,16 +8309,16 @@
       <c r="E13" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="113" t="s">
+      <c r="F13" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="112"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="105"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -8324,16 +8330,16 @@
       <c r="E14" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="113" t="s">
+      <c r="F14" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="111"/>
-      <c r="M14" s="112"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="105"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -8381,13 +8387,13 @@
       <c r="F16" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="112"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="105"/>
       <c r="N16" s="56" t="s">
         <v>38</v>
       </c>
@@ -8405,13 +8411,13 @@
       <c r="F17" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="112"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="104"/>
+      <c r="L17" s="104"/>
+      <c r="M17" s="105"/>
       <c r="N17" s="56" t="s">
         <v>38</v>
       </c>
@@ -8440,7 +8446,7 @@
         <v>46</v>
       </c>
       <c r="K18" s="125"/>
-      <c r="L18" s="112"/>
+      <c r="L18" s="105"/>
       <c r="M18" s="54" t="s">
         <v>47</v>
       </c>
@@ -8463,7 +8469,7 @@
         <v>51</v>
       </c>
       <c r="H19" s="125"/>
-      <c r="I19" s="112"/>
+      <c r="I19" s="105"/>
       <c r="J19" s="55" t="s">
         <v>52</v>
       </c>
@@ -8488,13 +8494,13 @@
       <c r="F20" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="111"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="112"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="105"/>
       <c r="N20" t="s">
         <v>58</v>
       </c>
@@ -8510,13 +8516,13 @@
       <c r="F21" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="112"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="105"/>
       <c r="N21" t="s">
         <v>61</v>
       </c>
@@ -8532,13 +8538,13 @@
       <c r="F22" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="112"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="104"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="105"/>
       <c r="N22" t="s">
         <v>64</v>
       </c>
@@ -8554,13 +8560,13 @@
       <c r="F23" s="126" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="112"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="105"/>
       <c r="N23" t="s">
         <v>67</v>
       </c>
@@ -8578,13 +8584,13 @@
       <c r="F24" s="127" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="112"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="105"/>
       <c r="N24" s="58" t="s">
         <v>38</v>
       </c>
@@ -8600,15 +8606,15 @@
         <v>20</v>
       </c>
       <c r="F25" s="125"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="112"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="105"/>
       <c r="K25" s="127" t="s">
         <v>71</v>
       </c>
-      <c r="L25" s="111"/>
-      <c r="M25" s="112"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="105"/>
       <c r="N25" s="56" t="s">
         <v>38</v>
       </c>
@@ -8624,13 +8630,13 @@
       <c r="F26" s="126" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="111"/>
-      <c r="L26" s="111"/>
-      <c r="M26" s="112"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="104"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="105"/>
       <c r="N26" t="s">
         <v>74</v>
       </c>
@@ -8646,13 +8652,13 @@
       <c r="F27" s="126" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="112"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="104"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="105"/>
       <c r="N27" t="s">
         <v>77</v>
       </c>
@@ -8668,13 +8674,13 @@
       <c r="F28" s="126" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="111"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="112"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="105"/>
       <c r="N28" t="s">
         <v>80</v>
       </c>
@@ -8690,13 +8696,13 @@
       <c r="F29" s="126" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="111"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="112"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="104"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="105"/>
       <c r="N29" t="s">
         <v>83</v>
       </c>
@@ -8712,13 +8718,13 @@
         <v>20</v>
       </c>
       <c r="F30" s="125"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="111"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="112"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="105"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="59" t="s">
@@ -8731,13 +8737,13 @@
         <v>20</v>
       </c>
       <c r="F31" s="125"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="111"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="111"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="112"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="105"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="59" t="s">
@@ -8752,13 +8758,13 @@
       <c r="F32" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="111"/>
-      <c r="H32" s="111"/>
-      <c r="I32" s="111"/>
-      <c r="J32" s="111"/>
-      <c r="K32" s="111"/>
-      <c r="L32" s="111"/>
-      <c r="M32" s="112"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="105"/>
       <c r="N32" s="56" t="s">
         <v>38</v>
       </c>
@@ -8776,13 +8782,13 @@
       <c r="F33" s="127" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="112"/>
+      <c r="G33" s="105"/>
       <c r="H33" s="125"/>
-      <c r="I33" s="111"/>
-      <c r="J33" s="111"/>
-      <c r="K33" s="111"/>
-      <c r="L33" s="111"/>
-      <c r="M33" s="112"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="104"/>
+      <c r="M33" s="105"/>
       <c r="N33" s="56" t="s">
         <v>38</v>
       </c>
@@ -8798,15 +8804,15 @@
         <v>20</v>
       </c>
       <c r="F34" s="125"/>
-      <c r="G34" s="111"/>
-      <c r="H34" s="111"/>
-      <c r="I34" s="111"/>
-      <c r="J34" s="112"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="105"/>
       <c r="K34" s="127" t="s">
         <v>91</v>
       </c>
-      <c r="L34" s="111"/>
-      <c r="M34" s="112"/>
+      <c r="L34" s="104"/>
+      <c r="M34" s="105"/>
       <c r="N34" s="56" t="s">
         <v>38</v>
       </c>
@@ -8822,15 +8828,15 @@
         <v>20</v>
       </c>
       <c r="F35" s="125"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="112"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="104"/>
+      <c r="I35" s="105"/>
       <c r="J35" s="127" t="s">
         <v>93</v>
       </c>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="112"/>
+      <c r="K35" s="104"/>
+      <c r="L35" s="104"/>
+      <c r="M35" s="105"/>
       <c r="N35" s="56" t="s">
         <v>38</v>
       </c>
@@ -8846,15 +8852,15 @@
         <v>20</v>
       </c>
       <c r="F36" s="125"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="112"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="104"/>
+      <c r="I36" s="105"/>
       <c r="J36" s="127" t="s">
         <v>95</v>
       </c>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="112"/>
+      <c r="K36" s="104"/>
+      <c r="L36" s="104"/>
+      <c r="M36" s="105"/>
       <c r="N36" s="56" t="s">
         <v>38</v>
       </c>
@@ -8872,13 +8878,13 @@
       <c r="F37" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="111"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="111"/>
-      <c r="J37" s="111"/>
-      <c r="K37" s="111"/>
-      <c r="L37" s="111"/>
-      <c r="M37" s="112"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="104"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="104"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="104"/>
+      <c r="M37" s="105"/>
       <c r="N37" s="56" t="s">
         <v>38</v>
       </c>
@@ -8894,13 +8900,13 @@
         <v>20</v>
       </c>
       <c r="F38" s="125"/>
-      <c r="G38" s="111"/>
-      <c r="H38" s="111"/>
-      <c r="I38" s="111"/>
-      <c r="J38" s="111"/>
-      <c r="K38" s="111"/>
-      <c r="L38" s="111"/>
-      <c r="M38" s="112"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="104"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="104"/>
+      <c r="K38" s="104"/>
+      <c r="L38" s="104"/>
+      <c r="M38" s="105"/>
       <c r="N38" t="s">
         <v>99</v>
       </c>
@@ -8916,13 +8922,13 @@
         <v>20</v>
       </c>
       <c r="F39" s="125"/>
-      <c r="G39" s="111"/>
-      <c r="H39" s="111"/>
-      <c r="I39" s="111"/>
-      <c r="J39" s="111"/>
-      <c r="K39" s="111"/>
-      <c r="L39" s="111"/>
-      <c r="M39" s="112"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="104"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="104"/>
+      <c r="L39" s="104"/>
+      <c r="M39" s="105"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="59" t="s">
@@ -8935,13 +8941,13 @@
         <v>20</v>
       </c>
       <c r="F40" s="125"/>
-      <c r="G40" s="111"/>
-      <c r="H40" s="111"/>
-      <c r="I40" s="111"/>
-      <c r="J40" s="111"/>
-      <c r="K40" s="111"/>
-      <c r="L40" s="111"/>
-      <c r="M40" s="112"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="104"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="104"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="104"/>
+      <c r="M40" s="105"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="59" t="s">
@@ -8954,13 +8960,13 @@
         <v>20</v>
       </c>
       <c r="F41" s="125"/>
-      <c r="G41" s="111"/>
-      <c r="H41" s="111"/>
-      <c r="I41" s="111"/>
-      <c r="J41" s="111"/>
-      <c r="K41" s="111"/>
-      <c r="L41" s="111"/>
-      <c r="M41" s="112"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="104"/>
+      <c r="I41" s="104"/>
+      <c r="J41" s="104"/>
+      <c r="K41" s="104"/>
+      <c r="L41" s="104"/>
+      <c r="M41" s="105"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="59" t="s">
@@ -8973,13 +8979,13 @@
         <v>20</v>
       </c>
       <c r="F42" s="125"/>
-      <c r="G42" s="111"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="111"/>
-      <c r="J42" s="111"/>
-      <c r="K42" s="111"/>
-      <c r="L42" s="111"/>
-      <c r="M42" s="112"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="104"/>
+      <c r="M42" s="105"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="19" t="s">
@@ -9001,12 +9007,12 @@
       <c r="I43" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="113" t="s">
+      <c r="J43" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="111"/>
-      <c r="L43" s="111"/>
-      <c r="M43" s="112"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="104"/>
+      <c r="M43" s="105"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
@@ -9016,18 +9022,18 @@
         <v>19</v>
       </c>
       <c r="E44" s="42"/>
-      <c r="F44" s="113" t="s">
+      <c r="F44" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="G44" s="112"/>
-      <c r="H44" s="113" t="s">
+      <c r="G44" s="105"/>
+      <c r="H44" s="109" t="s">
         <v>112</v>
       </c>
-      <c r="I44" s="111"/>
-      <c r="J44" s="111"/>
-      <c r="K44" s="111"/>
-      <c r="L44" s="111"/>
-      <c r="M44" s="112"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="104"/>
+      <c r="K44" s="104"/>
+      <c r="L44" s="104"/>
+      <c r="M44" s="105"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
@@ -9037,18 +9043,18 @@
         <v>19</v>
       </c>
       <c r="E45" s="42"/>
-      <c r="F45" s="129" t="s">
+      <c r="F45" s="128" t="s">
         <v>114</v>
       </c>
-      <c r="G45" s="130"/>
-      <c r="H45" s="130"/>
-      <c r="I45" s="131"/>
-      <c r="J45" s="113" t="s">
+      <c r="G45" s="129"/>
+      <c r="H45" s="129"/>
+      <c r="I45" s="130"/>
+      <c r="J45" s="109" t="s">
         <v>115</v>
       </c>
-      <c r="K45" s="111"/>
-      <c r="L45" s="111"/>
-      <c r="M45" s="112"/>
+      <c r="K45" s="104"/>
+      <c r="L45" s="104"/>
+      <c r="M45" s="105"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
@@ -9058,13 +9064,13 @@
         <v>19</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="113" t="s">
+      <c r="F46" s="109" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="111"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="112"/>
-      <c r="J46" s="128" t="s">
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="131" t="s">
         <v>118</v>
       </c>
       <c r="K46" s="123"/>
@@ -9079,16 +9085,16 @@
         <v>19</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="118" t="s">
+      <c r="F47" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
-      <c r="M47" s="112"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="104"/>
+      <c r="J47" s="104"/>
+      <c r="K47" s="104"/>
+      <c r="L47" s="104"/>
+      <c r="M47" s="105"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
@@ -9099,19 +9105,19 @@
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="110"/>
-      <c r="G48" s="112"/>
+      <c r="G48" s="105"/>
       <c r="H48" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I48" s="118" t="s">
+      <c r="I48" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="J48" s="111"/>
-      <c r="K48" s="112"/>
-      <c r="L48" s="118" t="s">
+      <c r="J48" s="104"/>
+      <c r="K48" s="105"/>
+      <c r="L48" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="M48" s="112"/>
+      <c r="M48" s="105"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
@@ -9155,14 +9161,14 @@
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="110"/>
-      <c r="G50" s="111"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="112"/>
-      <c r="J50" s="118" t="s">
+      <c r="G50" s="104"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="105"/>
+      <c r="J50" s="106" t="s">
         <v>133</v>
       </c>
-      <c r="K50" s="111"/>
-      <c r="L50" s="112"/>
+      <c r="K50" s="104"/>
+      <c r="L50" s="105"/>
       <c r="M50" s="12" t="s">
         <v>134</v>
       </c>
@@ -9178,15 +9184,15 @@
         <v>136</v>
       </c>
       <c r="F51" s="125"/>
-      <c r="G51" s="111"/>
-      <c r="H51" s="111"/>
-      <c r="I51" s="111"/>
-      <c r="J51" s="111"/>
-      <c r="K51" s="112"/>
-      <c r="L51" s="117" t="s">
+      <c r="G51" s="104"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="104"/>
+      <c r="K51" s="105"/>
+      <c r="L51" s="113" t="s">
         <v>137</v>
       </c>
-      <c r="M51" s="112"/>
+      <c r="M51" s="105"/>
     </row>
     <row r="52" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -9198,16 +9204,16 @@
       <c r="E52" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F52" s="117" t="s">
+      <c r="F52" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="111"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="111"/>
-      <c r="J52" s="111"/>
-      <c r="K52" s="111"/>
-      <c r="L52" s="111"/>
-      <c r="M52" s="112"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="104"/>
+      <c r="M52" s="105"/>
       <c r="N52" t="s">
         <v>141</v>
       </c>
@@ -9222,16 +9228,16 @@
       <c r="E53" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F53" s="117" t="s">
+      <c r="F53" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="111"/>
-      <c r="H53" s="111"/>
-      <c r="I53" s="111"/>
-      <c r="J53" s="111"/>
-      <c r="K53" s="111"/>
-      <c r="L53" s="111"/>
-      <c r="M53" s="112"/>
+      <c r="G53" s="104"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="104"/>
+      <c r="M53" s="105"/>
       <c r="N53" t="s">
         <v>141</v>
       </c>
@@ -9246,16 +9252,16 @@
       <c r="E54" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F54" s="117" t="s">
+      <c r="F54" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="111"/>
-      <c r="H54" s="111"/>
-      <c r="I54" s="111"/>
-      <c r="J54" s="111"/>
-      <c r="K54" s="111"/>
-      <c r="L54" s="111"/>
-      <c r="M54" s="112"/>
+      <c r="G54" s="104"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="104"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="104"/>
+      <c r="M54" s="105"/>
       <c r="N54" t="s">
         <v>141</v>
       </c>
@@ -9270,16 +9276,16 @@
       <c r="E55" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="117" t="s">
+      <c r="F55" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G55" s="111"/>
-      <c r="H55" s="111"/>
-      <c r="I55" s="111"/>
-      <c r="J55" s="111"/>
-      <c r="K55" s="111"/>
-      <c r="L55" s="111"/>
-      <c r="M55" s="112"/>
+      <c r="G55" s="104"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="104"/>
+      <c r="K55" s="104"/>
+      <c r="L55" s="104"/>
+      <c r="M55" s="105"/>
       <c r="N55" t="s">
         <v>141</v>
       </c>
@@ -9294,16 +9300,16 @@
       <c r="E56" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="117" t="s">
+      <c r="F56" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="111"/>
-      <c r="H56" s="111"/>
-      <c r="I56" s="111"/>
-      <c r="J56" s="111"/>
-      <c r="K56" s="111"/>
-      <c r="L56" s="111"/>
-      <c r="M56" s="112"/>
+      <c r="G56" s="104"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="104"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="104"/>
+      <c r="M56" s="105"/>
       <c r="N56" t="s">
         <v>141</v>
       </c>
@@ -9318,16 +9324,16 @@
       <c r="E57" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F57" s="117" t="s">
+      <c r="F57" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="111"/>
-      <c r="H57" s="111"/>
-      <c r="I57" s="111"/>
-      <c r="J57" s="111"/>
-      <c r="K57" s="111"/>
-      <c r="L57" s="111"/>
-      <c r="M57" s="112"/>
+      <c r="G57" s="104"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="104"/>
+      <c r="K57" s="104"/>
+      <c r="L57" s="104"/>
+      <c r="M57" s="105"/>
       <c r="N57" t="s">
         <v>141</v>
       </c>
@@ -9342,16 +9348,16 @@
       <c r="E58" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F58" s="117" t="s">
+      <c r="F58" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="111"/>
-      <c r="H58" s="111"/>
-      <c r="I58" s="111"/>
-      <c r="J58" s="111"/>
-      <c r="K58" s="111"/>
-      <c r="L58" s="111"/>
-      <c r="M58" s="112"/>
+      <c r="G58" s="104"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="104"/>
+      <c r="K58" s="104"/>
+      <c r="L58" s="104"/>
+      <c r="M58" s="105"/>
       <c r="N58" t="s">
         <v>141</v>
       </c>
@@ -9366,16 +9372,16 @@
       <c r="E59" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="F59" s="117" t="s">
+      <c r="F59" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G59" s="111"/>
-      <c r="H59" s="111"/>
-      <c r="I59" s="111"/>
-      <c r="J59" s="111"/>
-      <c r="K59" s="111"/>
-      <c r="L59" s="111"/>
-      <c r="M59" s="112"/>
+      <c r="G59" s="104"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="104"/>
+      <c r="K59" s="104"/>
+      <c r="L59" s="104"/>
+      <c r="M59" s="105"/>
       <c r="N59" t="s">
         <v>141</v>
       </c>
@@ -9390,16 +9396,16 @@
       <c r="E60" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F60" s="117" t="s">
+      <c r="F60" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="111"/>
-      <c r="L60" s="111"/>
-      <c r="M60" s="112"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="104"/>
+      <c r="L60" s="104"/>
+      <c r="M60" s="105"/>
       <c r="N60" t="s">
         <v>141</v>
       </c>
@@ -9414,16 +9420,16 @@
       <c r="E61" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="F61" s="117" t="s">
+      <c r="F61" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="G61" s="111"/>
-      <c r="H61" s="111"/>
-      <c r="I61" s="111"/>
-      <c r="J61" s="111"/>
-      <c r="K61" s="111"/>
-      <c r="L61" s="111"/>
-      <c r="M61" s="112"/>
+      <c r="G61" s="104"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="104"/>
+      <c r="K61" s="104"/>
+      <c r="L61" s="104"/>
+      <c r="M61" s="105"/>
       <c r="N61" t="s">
         <v>141</v>
       </c>
@@ -9452,13 +9458,59 @@
         <v>165</v>
       </c>
       <c r="K63" s="110"/>
-      <c r="L63" s="112"/>
+      <c r="L63" s="105"/>
       <c r="M63" s="53" t="s">
         <v>166</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="F51:K51"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F11:M11"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F17:M17"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="F47:M47"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F61:M61"/>
+    <mergeCell ref="H44:M44"/>
     <mergeCell ref="F60:M60"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="K18:L18"/>
@@ -9475,52 +9527,6 @@
     <mergeCell ref="F26:M26"/>
     <mergeCell ref="H33:M33"/>
     <mergeCell ref="F23:M23"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="F47:M47"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F61:M61"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="F11:M11"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F17:M17"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="F51:K51"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="F38:M38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8DE791-AEF2-46D4-A4DB-E5DAEFAE58D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4649F2A9-B8E7-4B9B-B802-B24B97690E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,15 +19,16 @@
     <sheet name="OPLL-EX" sheetId="4" r:id="rId4"/>
     <sheet name="OPL2+ADPCM" sheetId="5" r:id="rId5"/>
     <sheet name="SCC" sheetId="6" r:id="rId6"/>
-    <sheet name="MIXIER" sheetId="7" r:id="rId7"/>
-    <sheet name="SerialSRAM Memory Map" sheetId="8" r:id="rId8"/>
+    <sheet name="OPM" sheetId="9" r:id="rId7"/>
+    <sheet name="MIXIER" sheetId="7" r:id="rId8"/>
+    <sheet name="SerialSRAM Memory Map" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="542">
   <si>
     <t>OPL2 (YM3812) + ADPCM  [MSX-AUDIO(Y8950) Compatible]</t>
   </si>
@@ -765,9 +766,6 @@
     <t>7FFBh</t>
   </si>
   <si>
-    <t>Reserved</t>
-  </si>
-  <si>
     <t>7FFCh</t>
   </si>
   <si>
@@ -1062,16 +1060,7 @@
     <t>7Ch</t>
   </si>
   <si>
-    <t>OPLL1 Register Address</t>
-  </si>
-  <si>
     <t>7Dh</t>
-  </si>
-  <si>
-    <t>OPLL1 Register Value</t>
-  </si>
-  <si>
-    <t>OPLL1 Register Data</t>
   </si>
   <si>
     <t>Register(7Ah にこの Address を書くと7Bh が Description の機能に切り替わる、7Ch にこの Address を書くと7Dh が Description の機能に切り替わる)</t>
@@ -2060,6 +2049,54 @@
     <rPh sb="145" eb="147">
       <t>バアイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPM Register Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPM Register Value</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPM Volume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPM Register Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAM Mode=0 か、あるいは BANK1 が ROMバンク (#0～#15) のときのみ利用可能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPM (YM2151)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7Eh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7Fh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL Register Value</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL Register Address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPLL Register Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OPM</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2697,7 +2734,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2921,18 +2958,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -2987,33 +3012,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3025,13 +3032,31 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3046,14 +3071,14 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3063,6 +3088,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -3402,10 +3434,10 @@
   <dimension ref="A2:F16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.75" style="79" customWidth="1"/>
-    <col min="3" max="3" width="29.25" style="79" customWidth="1"/>
-    <col min="4" max="5" width="33.75" style="79" customWidth="1"/>
-    <col min="6" max="6" width="91" style="79" customWidth="1"/>
+    <col min="1" max="1" width="2.75" style="75" customWidth="1"/>
+    <col min="3" max="3" width="29.25" style="75" customWidth="1"/>
+    <col min="4" max="5" width="33.75" style="75" customWidth="1"/>
+    <col min="6" max="6" width="91" style="75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.15">
@@ -3638,13 +3670,13 @@
   <dimension ref="A2:O94"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.75" style="79" customWidth="1"/>
-    <col min="2" max="2" width="3.25" style="79" customWidth="1"/>
-    <col min="3" max="3" width="26.875" style="79" customWidth="1"/>
-    <col min="4" max="4" width="4" style="79" customWidth="1"/>
-    <col min="5" max="5" width="45" style="79" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="79" customWidth="1"/>
-    <col min="15" max="15" width="90.875" style="79" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.75" style="75" customWidth="1"/>
+    <col min="2" max="2" width="3.25" style="75" customWidth="1"/>
+    <col min="3" max="3" width="26.875" style="75" customWidth="1"/>
+    <col min="4" max="4" width="4" style="75" customWidth="1"/>
+    <col min="5" max="5" width="45" style="75" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="75" customWidth="1"/>
+    <col min="15" max="15" width="90.875" style="75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.15">
@@ -3706,13 +3738,13 @@
       <c r="F4" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G4" s="110"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="105"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="101"/>
       <c r="N4" s="66" t="s">
         <v>205</v>
       </c>
@@ -3736,13 +3768,13 @@
       <c r="G5" s="111" t="s">
         <v>209</v>
       </c>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="105"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="101"/>
       <c r="O5" s="49" t="s">
         <v>210</v>
       </c>
@@ -3763,13 +3795,13 @@
       <c r="G6" s="111" t="s">
         <v>209</v>
       </c>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="105"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="100"/>
+      <c r="N6" s="101"/>
       <c r="O6" s="49" t="s">
         <v>210</v>
       </c>
@@ -3790,13 +3822,13 @@
       <c r="G7" s="111" t="s">
         <v>209</v>
       </c>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="105"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="100"/>
+      <c r="N7" s="101"/>
       <c r="O7" s="49" t="s">
         <v>210</v>
       </c>
@@ -3817,13 +3849,13 @@
       <c r="G8" s="111" t="s">
         <v>209</v>
       </c>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="105"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="100"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="100"/>
+      <c r="N8" s="101"/>
       <c r="O8" s="49" t="s">
         <v>210</v>
       </c>
@@ -3841,16 +3873,16 @@
       <c r="F9" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G9" s="109" t="s">
+      <c r="G9" s="110" t="s">
         <v>218</v>
       </c>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="104"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="105"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
+      <c r="L9" s="100"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="101"/>
       <c r="O9" s="49" t="s">
         <v>219</v>
       </c>
@@ -3868,16 +3900,16 @@
       <c r="F10" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G10" s="109" t="s">
+      <c r="G10" s="110" t="s">
         <v>218</v>
       </c>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="104"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="105"/>
+      <c r="H10" s="100"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="101"/>
       <c r="O10" s="49" t="s">
         <v>219</v>
       </c>
@@ -3895,18 +3927,18 @@
       <c r="F11" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G11" s="113" t="s">
+      <c r="G11" s="114" t="s">
         <v>222</v>
       </c>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="104"/>
-      <c r="N11" s="105"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="101"/>
       <c r="O11" s="50" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -3922,18 +3954,18 @@
       <c r="F12" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="113" t="s">
+      <c r="G12" s="114" t="s">
         <v>225</v>
       </c>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="104"/>
-      <c r="N12" s="105"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="100"/>
+      <c r="N12" s="101"/>
       <c r="O12" s="50" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -3949,18 +3981,18 @@
       <c r="F13" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G13" s="103" t="s">
+      <c r="G13" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="105"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="100"/>
+      <c r="N13" s="101"/>
       <c r="O13" s="50" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -3976,18 +4008,18 @@
       <c r="F14" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G14" s="103" t="s">
+      <c r="G14" s="112" t="s">
         <v>228</v>
       </c>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="104"/>
-      <c r="N14" s="105"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="100"/>
+      <c r="K14" s="100"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="100"/>
+      <c r="N14" s="101"/>
       <c r="O14" s="50" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4003,18 +4035,18 @@
       <c r="F15" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G15" s="106" t="s">
+      <c r="G15" s="99" t="s">
         <v>230</v>
       </c>
-      <c r="H15" s="104"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="104"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="104"/>
-      <c r="M15" s="104"/>
-      <c r="N15" s="105"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="100"/>
+      <c r="K15" s="100"/>
+      <c r="L15" s="100"/>
+      <c r="M15" s="100"/>
+      <c r="N15" s="101"/>
       <c r="O15" s="50" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4030,18 +4062,18 @@
       <c r="F16" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G16" s="106" t="s">
+      <c r="G16" s="99" t="s">
         <v>233</v>
       </c>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="104"/>
-      <c r="M16" s="104"/>
-      <c r="N16" s="105"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="100"/>
+      <c r="K16" s="100"/>
+      <c r="L16" s="100"/>
+      <c r="M16" s="100"/>
+      <c r="N16" s="101"/>
       <c r="O16" s="50" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4057,18 +4089,18 @@
       <c r="F17" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G17" s="112"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="104"/>
-      <c r="M17" s="105"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="101"/>
       <c r="N17" s="10" t="s">
         <v>176</v>
       </c>
       <c r="O17" s="50" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4084,16 +4116,16 @@
       <c r="F18" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G18" s="103"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="104"/>
-      <c r="N18" s="105"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="101"/>
       <c r="O18" s="50" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4109,16 +4141,16 @@
       <c r="F19" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="103"/>
-      <c r="H19" s="104"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="104"/>
-      <c r="K19" s="104"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="104"/>
-      <c r="N19" s="105"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="101"/>
       <c r="O19" s="50" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4134,16 +4166,16 @@
       <c r="F20" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G20" s="103"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="105"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="100"/>
+      <c r="N20" s="101"/>
       <c r="O20" s="50" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4168,7 +4200,7 @@
       <c r="M21" s="72"/>
       <c r="N21" s="73"/>
       <c r="O21" s="50" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -4179,70 +4211,86 @@
         <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="50"/>
+        <v>530</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="G22" s="99" t="s">
+        <v>530</v>
+      </c>
+      <c r="H22" s="100"/>
+      <c r="I22" s="100"/>
+      <c r="J22" s="100"/>
+      <c r="K22" s="100"/>
+      <c r="L22" s="100"/>
+      <c r="M22" s="100"/>
+      <c r="N22" s="101"/>
+      <c r="O22" s="50" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="23" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="77"/>
-      <c r="O23" s="50"/>
+        <v>531</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="G23" s="99" t="s">
+        <v>533</v>
+      </c>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="100"/>
+      <c r="N23" s="101"/>
+      <c r="O23" s="50" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="24" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="77"/>
-      <c r="O24" s="50"/>
+        <v>532</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" s="71"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="73"/>
+      <c r="O24" s="50" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="25" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>223</v>
@@ -4256,30 +4304,32 @@
       <c r="M25" s="72"/>
       <c r="N25" s="73"/>
       <c r="O25" s="50" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>223</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="H26" s="110"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="104"/>
-      <c r="L26" s="105"/>
+        <v>250</v>
+      </c>
+      <c r="H26" s="131"/>
+      <c r="I26" s="132"/>
+      <c r="J26" s="132"/>
+      <c r="K26" s="132"/>
+      <c r="L26" s="133" t="s">
+        <v>541</v>
+      </c>
       <c r="M26" s="32" t="s">
         <v>173</v>
       </c>
@@ -4287,12 +4337,12 @@
         <v>180</v>
       </c>
       <c r="O26" s="50" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="63" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>19</v>
@@ -4303,23 +4353,23 @@
       <c r="F27" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="109" t="s">
+      <c r="G27" s="110" t="s">
         <v>218</v>
       </c>
-      <c r="H27" s="104"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="104"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="104"/>
-      <c r="N27" s="105"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="100"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="100"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="100"/>
+      <c r="N27" s="101"/>
       <c r="O27" s="49" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="28" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C28" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>19</v>
@@ -4330,1008 +4380,1043 @@
       <c r="F28" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="109" t="s">
+      <c r="G28" s="110" t="s">
         <v>218</v>
       </c>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="105"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="100"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="100"/>
+      <c r="L28" s="100"/>
+      <c r="M28" s="100"/>
+      <c r="N28" s="101"/>
       <c r="O28" s="49" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="30" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="79" t="s">
-        <v>533</v>
+      <c r="B30" s="75" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C31" s="93" t="s">
-        <v>525</v>
-      </c>
-      <c r="D31" s="100" t="s">
-        <v>448</v>
-      </c>
-      <c r="E31" s="100" t="s">
-        <v>498</v>
-      </c>
-      <c r="F31" s="101" t="s">
-        <v>518</v>
-      </c>
-      <c r="G31" s="114" t="s">
-        <v>498</v>
-      </c>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="115"/>
-      <c r="N31" s="115"/>
-      <c r="O31" s="81" t="s">
-        <v>520</v>
+      <c r="C31" s="89" t="s">
+        <v>521</v>
+      </c>
+      <c r="D31" s="96" t="s">
+        <v>444</v>
+      </c>
+      <c r="E31" s="96" t="s">
+        <v>494</v>
+      </c>
+      <c r="F31" s="97" t="s">
+        <v>514</v>
+      </c>
+      <c r="G31" s="104" t="s">
+        <v>494</v>
+      </c>
+      <c r="H31" s="105"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="105"/>
+      <c r="K31" s="105"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="105"/>
+      <c r="N31" s="105"/>
+      <c r="O31" s="77" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C32" s="89" t="s">
-        <v>526</v>
+      <c r="C32" s="85" t="s">
+        <v>522</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>518</v>
-      </c>
-      <c r="G32" s="107" t="s">
-        <v>498</v>
-      </c>
-      <c r="H32" s="108"/>
-      <c r="I32" s="108"/>
-      <c r="J32" s="108"/>
-      <c r="K32" s="108"/>
-      <c r="L32" s="108"/>
-      <c r="M32" s="108"/>
-      <c r="N32" s="108"/>
-      <c r="O32" s="83" t="s">
-        <v>527</v>
+        <v>514</v>
+      </c>
+      <c r="G32" s="102" t="s">
+        <v>494</v>
+      </c>
+      <c r="H32" s="103"/>
+      <c r="I32" s="103"/>
+      <c r="J32" s="103"/>
+      <c r="K32" s="103"/>
+      <c r="L32" s="103"/>
+      <c r="M32" s="103"/>
+      <c r="N32" s="103"/>
+      <c r="O32" s="79" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="33" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C33" s="89" t="s">
-        <v>516</v>
+      <c r="C33" s="85" t="s">
+        <v>512</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>518</v>
-      </c>
-      <c r="G33" s="107" t="s">
+        <v>514</v>
+      </c>
+      <c r="G33" s="102" t="s">
         <v>218</v>
       </c>
-      <c r="H33" s="108"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="108"/>
-      <c r="K33" s="108"/>
-      <c r="L33" s="108"/>
-      <c r="M33" s="108"/>
-      <c r="N33" s="108"/>
-      <c r="O33" s="83" t="s">
+      <c r="H33" s="103"/>
+      <c r="I33" s="103"/>
+      <c r="J33" s="103"/>
+      <c r="K33" s="103"/>
+      <c r="L33" s="103"/>
+      <c r="M33" s="103"/>
+      <c r="N33" s="103"/>
+      <c r="O33" s="79" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="34" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C34" s="89" t="s">
-        <v>474</v>
+      <c r="C34" s="85" t="s">
+        <v>470</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F34" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G34" s="107" t="s">
-        <v>506</v>
-      </c>
-      <c r="H34" s="108"/>
-      <c r="I34" s="108"/>
-      <c r="J34" s="108"/>
-      <c r="K34" s="108"/>
-      <c r="L34" s="108"/>
-      <c r="M34" s="108"/>
-      <c r="N34" s="108"/>
-      <c r="O34" s="83"/>
+      <c r="G34" s="102" t="s">
+        <v>502</v>
+      </c>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="103"/>
+      <c r="M34" s="103"/>
+      <c r="N34" s="103"/>
+      <c r="O34" s="79"/>
     </row>
     <row r="35" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C35" s="89" t="s">
-        <v>475</v>
+      <c r="C35" s="85" t="s">
+        <v>471</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F35" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G35" s="107" t="s">
-        <v>507</v>
-      </c>
-      <c r="H35" s="108"/>
-      <c r="I35" s="108"/>
-      <c r="J35" s="108"/>
-      <c r="K35" s="108"/>
-      <c r="L35" s="108"/>
-      <c r="M35" s="108"/>
-      <c r="N35" s="108"/>
-      <c r="O35" s="83"/>
+      <c r="G35" s="102" t="s">
+        <v>503</v>
+      </c>
+      <c r="H35" s="103"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="103"/>
+      <c r="K35" s="103"/>
+      <c r="L35" s="103"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="79"/>
     </row>
     <row r="36" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C36" s="89" t="s">
-        <v>476</v>
+      <c r="C36" s="85" t="s">
+        <v>472</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F36" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G36" s="107" t="s">
-        <v>508</v>
-      </c>
-      <c r="H36" s="108"/>
-      <c r="I36" s="108"/>
-      <c r="J36" s="108"/>
-      <c r="K36" s="108"/>
-      <c r="L36" s="108"/>
-      <c r="M36" s="108"/>
-      <c r="N36" s="108"/>
-      <c r="O36" s="83"/>
+      <c r="G36" s="102" t="s">
+        <v>504</v>
+      </c>
+      <c r="H36" s="103"/>
+      <c r="I36" s="103"/>
+      <c r="J36" s="103"/>
+      <c r="K36" s="103"/>
+      <c r="L36" s="103"/>
+      <c r="M36" s="103"/>
+      <c r="N36" s="103"/>
+      <c r="O36" s="79"/>
     </row>
     <row r="37" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C37" s="89" t="s">
-        <v>477</v>
+      <c r="C37" s="85" t="s">
+        <v>473</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F37" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G37" s="107" t="s">
-        <v>509</v>
-      </c>
-      <c r="H37" s="108"/>
-      <c r="I37" s="108"/>
-      <c r="J37" s="108"/>
-      <c r="K37" s="108"/>
-      <c r="L37" s="108"/>
-      <c r="M37" s="108"/>
-      <c r="N37" s="108"/>
-      <c r="O37" s="83"/>
+      <c r="G37" s="102" t="s">
+        <v>505</v>
+      </c>
+      <c r="H37" s="103"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="103"/>
+      <c r="K37" s="103"/>
+      <c r="L37" s="103"/>
+      <c r="M37" s="103"/>
+      <c r="N37" s="103"/>
+      <c r="O37" s="79"/>
     </row>
     <row r="38" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C38" s="89" t="s">
-        <v>478</v>
+      <c r="C38" s="85" t="s">
+        <v>474</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F38" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G38" s="107" t="s">
-        <v>510</v>
-      </c>
-      <c r="H38" s="108"/>
-      <c r="I38" s="108"/>
-      <c r="J38" s="108"/>
-      <c r="K38" s="108"/>
-      <c r="L38" s="108"/>
-      <c r="M38" s="108"/>
-      <c r="N38" s="108"/>
-      <c r="O38" s="83" t="s">
-        <v>520</v>
+      <c r="G38" s="102" t="s">
+        <v>506</v>
+      </c>
+      <c r="H38" s="103"/>
+      <c r="I38" s="103"/>
+      <c r="J38" s="103"/>
+      <c r="K38" s="103"/>
+      <c r="L38" s="103"/>
+      <c r="M38" s="103"/>
+      <c r="N38" s="103"/>
+      <c r="O38" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="39" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C39" s="89" t="s">
-        <v>479</v>
+      <c r="C39" s="85" t="s">
+        <v>475</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F39" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G39" s="107" t="s">
-        <v>511</v>
-      </c>
-      <c r="H39" s="108"/>
-      <c r="I39" s="108"/>
-      <c r="J39" s="108"/>
-      <c r="K39" s="108"/>
-      <c r="L39" s="108"/>
-      <c r="M39" s="108"/>
-      <c r="N39" s="108"/>
-      <c r="O39" s="83" t="s">
-        <v>520</v>
+      <c r="G39" s="102" t="s">
+        <v>507</v>
+      </c>
+      <c r="H39" s="103"/>
+      <c r="I39" s="103"/>
+      <c r="J39" s="103"/>
+      <c r="K39" s="103"/>
+      <c r="L39" s="103"/>
+      <c r="M39" s="103"/>
+      <c r="N39" s="103"/>
+      <c r="O39" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="40" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C40" s="89" t="s">
-        <v>480</v>
+      <c r="C40" s="85" t="s">
+        <v>476</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F40" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G40" s="107" t="s">
-        <v>512</v>
-      </c>
-      <c r="H40" s="108"/>
-      <c r="I40" s="108"/>
-      <c r="J40" s="108"/>
-      <c r="K40" s="108"/>
-      <c r="L40" s="108"/>
-      <c r="M40" s="108"/>
-      <c r="N40" s="108"/>
-      <c r="O40" s="83" t="s">
-        <v>520</v>
+      <c r="G40" s="102" t="s">
+        <v>508</v>
+      </c>
+      <c r="H40" s="103"/>
+      <c r="I40" s="103"/>
+      <c r="J40" s="103"/>
+      <c r="K40" s="103"/>
+      <c r="L40" s="103"/>
+      <c r="M40" s="103"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="41" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C41" s="89" t="s">
-        <v>481</v>
+      <c r="C41" s="85" t="s">
+        <v>477</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F41" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G41" s="107" t="s">
-        <v>513</v>
-      </c>
-      <c r="H41" s="108"/>
-      <c r="I41" s="108"/>
-      <c r="J41" s="108"/>
-      <c r="K41" s="108"/>
-      <c r="L41" s="108"/>
-      <c r="M41" s="108"/>
-      <c r="N41" s="108"/>
-      <c r="O41" s="83" t="s">
-        <v>520</v>
+      <c r="G41" s="102" t="s">
+        <v>509</v>
+      </c>
+      <c r="H41" s="103"/>
+      <c r="I41" s="103"/>
+      <c r="J41" s="103"/>
+      <c r="K41" s="103"/>
+      <c r="L41" s="103"/>
+      <c r="M41" s="103"/>
+      <c r="N41" s="103"/>
+      <c r="O41" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="42" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C42" s="89" t="s">
-        <v>482</v>
+      <c r="C42" s="85" t="s">
+        <v>478</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F42" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G42" s="107" t="s">
-        <v>514</v>
-      </c>
-      <c r="H42" s="108"/>
-      <c r="I42" s="108"/>
-      <c r="J42" s="108"/>
-      <c r="K42" s="108"/>
-      <c r="L42" s="108"/>
-      <c r="M42" s="108"/>
-      <c r="N42" s="108"/>
-      <c r="O42" s="83" t="s">
-        <v>520</v>
+      <c r="G42" s="102" t="s">
+        <v>510</v>
+      </c>
+      <c r="H42" s="103"/>
+      <c r="I42" s="103"/>
+      <c r="J42" s="103"/>
+      <c r="K42" s="103"/>
+      <c r="L42" s="103"/>
+      <c r="M42" s="103"/>
+      <c r="N42" s="103"/>
+      <c r="O42" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="43" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C43" s="89" t="s">
-        <v>483</v>
+      <c r="C43" s="85" t="s">
+        <v>479</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F43" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G43" s="107" t="s">
-        <v>501</v>
-      </c>
-      <c r="H43" s="108"/>
-      <c r="I43" s="108"/>
-      <c r="J43" s="108"/>
-      <c r="K43" s="108"/>
-      <c r="L43" s="108"/>
-      <c r="M43" s="108"/>
-      <c r="N43" s="108"/>
-      <c r="O43" s="83" t="s">
-        <v>520</v>
+      <c r="G43" s="102" t="s">
+        <v>497</v>
+      </c>
+      <c r="H43" s="103"/>
+      <c r="I43" s="103"/>
+      <c r="J43" s="103"/>
+      <c r="K43" s="103"/>
+      <c r="L43" s="103"/>
+      <c r="M43" s="103"/>
+      <c r="N43" s="103"/>
+      <c r="O43" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C44" s="89" t="s">
-        <v>484</v>
+      <c r="C44" s="85" t="s">
+        <v>480</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F44" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G44" s="107" t="s">
-        <v>502</v>
-      </c>
-      <c r="H44" s="108"/>
-      <c r="I44" s="108"/>
-      <c r="J44" s="108"/>
-      <c r="K44" s="108"/>
-      <c r="L44" s="108"/>
-      <c r="M44" s="108"/>
-      <c r="N44" s="108"/>
-      <c r="O44" s="83" t="s">
-        <v>520</v>
+      <c r="G44" s="102" t="s">
+        <v>498</v>
+      </c>
+      <c r="H44" s="103"/>
+      <c r="I44" s="103"/>
+      <c r="J44" s="103"/>
+      <c r="K44" s="103"/>
+      <c r="L44" s="103"/>
+      <c r="M44" s="103"/>
+      <c r="N44" s="103"/>
+      <c r="O44" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="45" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C45" s="89" t="s">
-        <v>485</v>
+      <c r="C45" s="85" t="s">
+        <v>481</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F45" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G45" s="107" t="s">
-        <v>503</v>
-      </c>
-      <c r="H45" s="108"/>
-      <c r="I45" s="108"/>
-      <c r="J45" s="108"/>
-      <c r="K45" s="108"/>
-      <c r="L45" s="108"/>
-      <c r="M45" s="108"/>
-      <c r="N45" s="108"/>
-      <c r="O45" s="83" t="s">
-        <v>520</v>
+      <c r="G45" s="102" t="s">
+        <v>499</v>
+      </c>
+      <c r="H45" s="103"/>
+      <c r="I45" s="103"/>
+      <c r="J45" s="103"/>
+      <c r="K45" s="103"/>
+      <c r="L45" s="103"/>
+      <c r="M45" s="103"/>
+      <c r="N45" s="103"/>
+      <c r="O45" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="46" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C46" s="89" t="s">
-        <v>486</v>
+      <c r="C46" s="85" t="s">
+        <v>482</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F46" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G46" s="107" t="s">
-        <v>504</v>
-      </c>
-      <c r="H46" s="108"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="108"/>
-      <c r="K46" s="108"/>
-      <c r="L46" s="108"/>
-      <c r="M46" s="108"/>
-      <c r="N46" s="108"/>
-      <c r="O46" s="83" t="s">
-        <v>520</v>
+      <c r="G46" s="102" t="s">
+        <v>500</v>
+      </c>
+      <c r="H46" s="103"/>
+      <c r="I46" s="103"/>
+      <c r="J46" s="103"/>
+      <c r="K46" s="103"/>
+      <c r="L46" s="103"/>
+      <c r="M46" s="103"/>
+      <c r="N46" s="103"/>
+      <c r="O46" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="47" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C47" s="89" t="s">
-        <v>487</v>
+      <c r="C47" s="85" t="s">
+        <v>483</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G47" s="107" t="s">
-        <v>505</v>
-      </c>
-      <c r="H47" s="108"/>
-      <c r="I47" s="108"/>
-      <c r="J47" s="108"/>
-      <c r="K47" s="108"/>
-      <c r="L47" s="108"/>
-      <c r="M47" s="108"/>
-      <c r="N47" s="108"/>
-      <c r="O47" s="83" t="s">
-        <v>520</v>
+      <c r="G47" s="102" t="s">
+        <v>501</v>
+      </c>
+      <c r="H47" s="103"/>
+      <c r="I47" s="103"/>
+      <c r="J47" s="103"/>
+      <c r="K47" s="103"/>
+      <c r="L47" s="103"/>
+      <c r="M47" s="103"/>
+      <c r="N47" s="103"/>
+      <c r="O47" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="48" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C48" s="89" t="s">
-        <v>488</v>
+      <c r="C48" s="85" t="s">
+        <v>484</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F48" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G48" s="107" t="s">
-        <v>500</v>
-      </c>
-      <c r="H48" s="108"/>
-      <c r="I48" s="108"/>
-      <c r="J48" s="108"/>
-      <c r="K48" s="108"/>
-      <c r="L48" s="108"/>
-      <c r="M48" s="108"/>
-      <c r="N48" s="108"/>
-      <c r="O48" s="83" t="s">
-        <v>520</v>
+      <c r="G48" s="102" t="s">
+        <v>496</v>
+      </c>
+      <c r="H48" s="103"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="103"/>
+      <c r="K48" s="103"/>
+      <c r="L48" s="103"/>
+      <c r="M48" s="103"/>
+      <c r="N48" s="103"/>
+      <c r="O48" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="49" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C49" s="89" t="s">
-        <v>489</v>
+      <c r="C49" s="85" t="s">
+        <v>485</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F49" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G49" s="107" t="s">
-        <v>497</v>
-      </c>
-      <c r="H49" s="108"/>
-      <c r="I49" s="108"/>
-      <c r="J49" s="108"/>
-      <c r="K49" s="108"/>
-      <c r="L49" s="108"/>
-      <c r="M49" s="108"/>
-      <c r="N49" s="108"/>
-      <c r="O49" s="83" t="s">
-        <v>520</v>
+      <c r="G49" s="102" t="s">
+        <v>493</v>
+      </c>
+      <c r="H49" s="103"/>
+      <c r="I49" s="103"/>
+      <c r="J49" s="103"/>
+      <c r="K49" s="103"/>
+      <c r="L49" s="103"/>
+      <c r="M49" s="103"/>
+      <c r="N49" s="103"/>
+      <c r="O49" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="50" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C50" s="89" t="s">
-        <v>491</v>
+      <c r="C50" s="85" t="s">
+        <v>487</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F50" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G50" s="107" t="s">
-        <v>529</v>
-      </c>
-      <c r="H50" s="108"/>
-      <c r="I50" s="108"/>
-      <c r="J50" s="108"/>
-      <c r="K50" s="108"/>
-      <c r="L50" s="108"/>
-      <c r="M50" s="108"/>
-      <c r="N50" s="108"/>
-      <c r="O50" s="83" t="s">
-        <v>520</v>
+      <c r="G50" s="102" t="s">
+        <v>525</v>
+      </c>
+      <c r="H50" s="103"/>
+      <c r="I50" s="103"/>
+      <c r="J50" s="103"/>
+      <c r="K50" s="103"/>
+      <c r="L50" s="103"/>
+      <c r="M50" s="103"/>
+      <c r="N50" s="103"/>
+      <c r="O50" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="51" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C51" s="89" t="s">
-        <v>490</v>
+      <c r="C51" s="85" t="s">
+        <v>486</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F51" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G51" s="107" t="s">
-        <v>529</v>
-      </c>
-      <c r="H51" s="108"/>
-      <c r="I51" s="108"/>
-      <c r="J51" s="108"/>
-      <c r="K51" s="108"/>
-      <c r="L51" s="108"/>
-      <c r="M51" s="108"/>
-      <c r="N51" s="108"/>
-      <c r="O51" s="83" t="s">
-        <v>520</v>
+      <c r="G51" s="102" t="s">
+        <v>525</v>
+      </c>
+      <c r="H51" s="103"/>
+      <c r="I51" s="103"/>
+      <c r="J51" s="103"/>
+      <c r="K51" s="103"/>
+      <c r="L51" s="103"/>
+      <c r="M51" s="103"/>
+      <c r="N51" s="103"/>
+      <c r="O51" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="52" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C52" s="89" t="s">
-        <v>492</v>
+      <c r="C52" s="85" t="s">
+        <v>488</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F52" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G52" s="107" t="s">
-        <v>499</v>
-      </c>
-      <c r="H52" s="108"/>
-      <c r="I52" s="108"/>
-      <c r="J52" s="108"/>
-      <c r="K52" s="108"/>
-      <c r="L52" s="108"/>
-      <c r="M52" s="108"/>
-      <c r="N52" s="108"/>
-      <c r="O52" s="83" t="s">
-        <v>520</v>
+      <c r="G52" s="102" t="s">
+        <v>495</v>
+      </c>
+      <c r="H52" s="103"/>
+      <c r="I52" s="103"/>
+      <c r="J52" s="103"/>
+      <c r="K52" s="103"/>
+      <c r="L52" s="103"/>
+      <c r="M52" s="103"/>
+      <c r="N52" s="103"/>
+      <c r="O52" s="79" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="53" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C53" s="89" t="s">
-        <v>493</v>
+      <c r="C53" s="85" t="s">
+        <v>489</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="F53" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G53" s="118" t="s">
+      <c r="G53" s="108" t="s">
         <v>140</v>
       </c>
-      <c r="H53" s="108"/>
-      <c r="I53" s="108"/>
-      <c r="J53" s="108"/>
-      <c r="K53" s="108"/>
-      <c r="L53" s="108"/>
-      <c r="M53" s="108"/>
-      <c r="N53" s="108"/>
-      <c r="O53" s="83" t="s">
-        <v>519</v>
+      <c r="H53" s="103"/>
+      <c r="I53" s="103"/>
+      <c r="J53" s="103"/>
+      <c r="K53" s="103"/>
+      <c r="L53" s="103"/>
+      <c r="M53" s="103"/>
+      <c r="N53" s="103"/>
+      <c r="O53" s="79" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="54" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C54" s="89" t="s">
-        <v>494</v>
+      <c r="C54" s="85" t="s">
+        <v>490</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F54" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G54" s="118" t="s">
+      <c r="G54" s="108" t="s">
         <v>140</v>
       </c>
-      <c r="H54" s="108"/>
-      <c r="I54" s="108"/>
-      <c r="J54" s="108"/>
-      <c r="K54" s="108"/>
-      <c r="L54" s="108"/>
-      <c r="M54" s="108"/>
-      <c r="N54" s="108"/>
-      <c r="O54" s="83" t="s">
-        <v>519</v>
+      <c r="H54" s="103"/>
+      <c r="I54" s="103"/>
+      <c r="J54" s="103"/>
+      <c r="K54" s="103"/>
+      <c r="L54" s="103"/>
+      <c r="M54" s="103"/>
+      <c r="N54" s="103"/>
+      <c r="O54" s="79" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="55" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C55" s="89" t="s">
-        <v>515</v>
+      <c r="C55" s="85" t="s">
+        <v>511</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E55" s="22" t="s">
         <v>431</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>435</v>
       </c>
       <c r="F55" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G55" s="118" t="s">
+      <c r="G55" s="108" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="108"/>
-      <c r="I55" s="108"/>
-      <c r="J55" s="108"/>
-      <c r="K55" s="108"/>
-      <c r="L55" s="108"/>
-      <c r="M55" s="108"/>
-      <c r="N55" s="108"/>
-      <c r="O55" s="83" t="s">
-        <v>519</v>
+      <c r="H55" s="103"/>
+      <c r="I55" s="103"/>
+      <c r="J55" s="103"/>
+      <c r="K55" s="103"/>
+      <c r="L55" s="103"/>
+      <c r="M55" s="103"/>
+      <c r="N55" s="103"/>
+      <c r="O55" s="79" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="56" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C56" s="89" t="s">
-        <v>495</v>
+      <c r="C56" s="85" t="s">
+        <v>491</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F56" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G56" s="118" t="s">
+      <c r="G56" s="108" t="s">
         <v>140</v>
       </c>
-      <c r="H56" s="108"/>
-      <c r="I56" s="108"/>
-      <c r="J56" s="108"/>
-      <c r="K56" s="108"/>
-      <c r="L56" s="108"/>
-      <c r="M56" s="108"/>
-      <c r="N56" s="108"/>
-      <c r="O56" s="83" t="s">
-        <v>519</v>
+      <c r="H56" s="103"/>
+      <c r="I56" s="103"/>
+      <c r="J56" s="103"/>
+      <c r="K56" s="103"/>
+      <c r="L56" s="103"/>
+      <c r="M56" s="103"/>
+      <c r="N56" s="103"/>
+      <c r="O56" s="79" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="57" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C57" s="89" t="s">
-        <v>496</v>
+      <c r="C57" s="85" t="s">
+        <v>492</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F57" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G57" s="118" t="s">
+      <c r="G57" s="108" t="s">
         <v>140</v>
       </c>
-      <c r="H57" s="108"/>
-      <c r="I57" s="108"/>
-      <c r="J57" s="108"/>
-      <c r="K57" s="108"/>
-      <c r="L57" s="108"/>
-      <c r="M57" s="108"/>
-      <c r="N57" s="108"/>
-      <c r="O57" s="83" t="s">
+      <c r="H57" s="103"/>
+      <c r="I57" s="103"/>
+      <c r="J57" s="103"/>
+      <c r="K57" s="103"/>
+      <c r="L57" s="103"/>
+      <c r="M57" s="103"/>
+      <c r="N57" s="103"/>
+      <c r="O57" s="79" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C58" s="85" t="s">
+        <v>517</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F58" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="G58" s="102" t="s">
+        <v>525</v>
+      </c>
+      <c r="H58" s="103"/>
+      <c r="I58" s="103"/>
+      <c r="J58" s="103"/>
+      <c r="K58" s="103"/>
+      <c r="L58" s="103"/>
+      <c r="M58" s="103"/>
+      <c r="N58" s="103"/>
+      <c r="O58" s="79" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="86" t="s">
+        <v>518</v>
+      </c>
+      <c r="D59" s="98" t="s">
+        <v>427</v>
+      </c>
+      <c r="E59" s="87" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C58" s="89" t="s">
-        <v>521</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="F58" s="22" t="s">
-        <v>518</v>
-      </c>
-      <c r="G58" s="107" t="s">
-        <v>529</v>
-      </c>
-      <c r="H58" s="108"/>
-      <c r="I58" s="108"/>
-      <c r="J58" s="108"/>
-      <c r="K58" s="108"/>
-      <c r="L58" s="108"/>
-      <c r="M58" s="108"/>
-      <c r="N58" s="108"/>
-      <c r="O58" s="83" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C59" s="90" t="s">
-        <v>522</v>
-      </c>
-      <c r="D59" s="102" t="s">
-        <v>431</v>
-      </c>
-      <c r="E59" s="91" t="s">
-        <v>523</v>
-      </c>
-      <c r="F59" s="91"/>
-      <c r="G59" s="116" t="s">
-        <v>524</v>
-      </c>
-      <c r="H59" s="117"/>
-      <c r="I59" s="117"/>
-      <c r="J59" s="117"/>
-      <c r="K59" s="117"/>
-      <c r="L59" s="117"/>
-      <c r="M59" s="117"/>
-      <c r="N59" s="117"/>
-      <c r="O59" s="85"/>
+      <c r="F59" s="87"/>
+      <c r="G59" s="106" t="s">
+        <v>520</v>
+      </c>
+      <c r="H59" s="107"/>
+      <c r="I59" s="107"/>
+      <c r="J59" s="107"/>
+      <c r="K59" s="107"/>
+      <c r="L59" s="107"/>
+      <c r="M59" s="107"/>
+      <c r="N59" s="107"/>
+      <c r="O59" s="81"/>
     </row>
     <row r="61" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="62" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C62" s="93" t="s">
+      <c r="C62" s="89" t="s">
+        <v>435</v>
+      </c>
+      <c r="D62" s="90"/>
+      <c r="E62" s="91"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C63" s="85" t="s">
+        <v>436</v>
+      </c>
+      <c r="D63" s="88" t="s">
+        <v>444</v>
+      </c>
+      <c r="E63" s="92" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.15">
+      <c r="C64" s="85" t="s">
+        <v>437</v>
+      </c>
+      <c r="D64" s="88" t="s">
+        <v>444</v>
+      </c>
+      <c r="E64" s="92" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C65" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="D65" s="88" t="s">
+        <v>444</v>
+      </c>
+      <c r="E65" s="92" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C66" s="86" t="s">
         <v>439</v>
       </c>
-      <c r="D62" s="94"/>
-      <c r="E62" s="95"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C63" s="89" t="s">
-        <v>440</v>
-      </c>
-      <c r="D63" s="92" t="s">
-        <v>448</v>
-      </c>
-      <c r="E63" s="96" t="s">
+      <c r="D66" s="93" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.15">
-      <c r="C64" s="89" t="s">
-        <v>441</v>
-      </c>
-      <c r="D64" s="92" t="s">
-        <v>448</v>
-      </c>
-      <c r="E64" s="96" t="s">
+      <c r="E66" s="94" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C68" s="75" t="s">
         <v>445</v>
-      </c>
-    </row>
-    <row r="65" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C65" s="89" t="s">
-        <v>442</v>
-      </c>
-      <c r="D65" s="92" t="s">
-        <v>448</v>
-      </c>
-      <c r="E65" s="96" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="66" spans="3:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C66" s="90" t="s">
-        <v>443</v>
-      </c>
-      <c r="D66" s="97" t="s">
-        <v>448</v>
-      </c>
-      <c r="E66" s="98" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="68" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C68" s="79" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="69" spans="3:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C70" s="93" t="s">
+      <c r="C70" s="89" t="s">
+        <v>446</v>
+      </c>
+      <c r="D70" s="90"/>
+      <c r="E70" s="91" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C71" s="85" t="s">
+        <v>447</v>
+      </c>
+      <c r="D71" s="88"/>
+      <c r="E71" s="92" t="s">
         <v>450</v>
       </c>
-      <c r="D70" s="94"/>
-      <c r="E70" s="95" t="s">
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C72" s="85" t="s">
+        <v>448</v>
+      </c>
+      <c r="D72" s="88"/>
+      <c r="E72" s="92"/>
+    </row>
+    <row r="73" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C73" s="85" t="s">
+        <v>449</v>
+      </c>
+      <c r="D73" s="88"/>
+      <c r="E73" s="92" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C74" s="85" t="s">
+        <v>453</v>
+      </c>
+      <c r="D74" s="88"/>
+      <c r="E74" s="92" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C75" s="85" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="71" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C71" s="89" t="s">
-        <v>451</v>
-      </c>
-      <c r="D71" s="92"/>
-      <c r="E71" s="96" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="72" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C72" s="89" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="92"/>
-      <c r="E72" s="96"/>
-    </row>
-    <row r="73" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C73" s="89" t="s">
-        <v>453</v>
-      </c>
-      <c r="D73" s="92"/>
-      <c r="E73" s="96" t="s">
+      <c r="D75" s="88"/>
+      <c r="E75" s="92" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="76" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C76" s="85" t="s">
+        <v>448</v>
+      </c>
+      <c r="D76" s="88"/>
+      <c r="E76" s="92"/>
+    </row>
+    <row r="77" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C77" s="85" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="74" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C74" s="89" t="s">
+      <c r="D77" s="88"/>
+      <c r="E77" s="92" t="s">
         <v>457</v>
       </c>
-      <c r="D74" s="92"/>
-      <c r="E74" s="96" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="75" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C75" s="89" t="s">
+    </row>
+    <row r="78" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C78" s="85" t="s">
+        <v>463</v>
+      </c>
+      <c r="D78" s="88"/>
+      <c r="E78" s="92" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C79" s="85" t="s">
+        <v>448</v>
+      </c>
+      <c r="D79" s="88"/>
+      <c r="E79" s="92"/>
+    </row>
+    <row r="80" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C80" s="85" t="s">
+        <v>465</v>
+      </c>
+      <c r="D80" s="88"/>
+      <c r="E80" s="92" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="C81" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="D81" s="88"/>
+      <c r="E81" s="95" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C82" s="85" t="s">
+        <v>467</v>
+      </c>
+      <c r="D82" s="88"/>
+      <c r="E82" s="92" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C83" s="85" t="s">
+        <v>448</v>
+      </c>
+      <c r="D83" s="88"/>
+      <c r="E83" s="92"/>
+    </row>
+    <row r="84" spans="3:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C84" s="86" t="s">
+        <v>468</v>
+      </c>
+      <c r="D84" s="93"/>
+      <c r="E84" s="94" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C87" s="75" t="s">
         <v>459</v>
       </c>
-      <c r="D75" s="92"/>
-      <c r="E75" s="96" t="s">
+    </row>
+    <row r="88" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C88" s="75" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="90" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C90" s="75" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="92" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C92" s="75" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="76" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C76" s="89" t="s">
-        <v>452</v>
-      </c>
-      <c r="D76" s="92"/>
-      <c r="E76" s="96"/>
-    </row>
-    <row r="77" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C77" s="89" t="s">
-        <v>460</v>
-      </c>
-      <c r="D77" s="92"/>
-      <c r="E77" s="96" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="78" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C78" s="89" t="s">
-        <v>467</v>
-      </c>
-      <c r="D78" s="92"/>
-      <c r="E78" s="96" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="79" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C79" s="89" t="s">
-        <v>452</v>
-      </c>
-      <c r="D79" s="92"/>
-      <c r="E79" s="96"/>
-    </row>
-    <row r="80" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C80" s="89" t="s">
+    <row r="94" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C94" s="75" t="s">
         <v>469</v>
       </c>
-      <c r="D80" s="92"/>
-      <c r="E80" s="96" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="81" spans="3:5" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="C81" s="89" t="s">
-        <v>470</v>
-      </c>
-      <c r="D81" s="92"/>
-      <c r="E81" s="99" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="82" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C82" s="89" t="s">
-        <v>471</v>
-      </c>
-      <c r="D82" s="92"/>
-      <c r="E82" s="96" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="83" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C83" s="89" t="s">
-        <v>452</v>
-      </c>
-      <c r="D83" s="92"/>
-      <c r="E83" s="96"/>
-    </row>
-    <row r="84" spans="3:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C84" s="90" t="s">
-        <v>472</v>
-      </c>
-      <c r="D84" s="97"/>
-      <c r="E84" s="98" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="87" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C87" s="79" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="88" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C88" s="79" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="90" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C90" s="79" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="92" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C92" s="79" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="94" spans="3:5" x14ac:dyDescent="0.15">
-      <c r="C94" s="79" t="s">
-        <v>473</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="51">
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G16:N16"/>
+    <mergeCell ref="G32:N32"/>
+    <mergeCell ref="G34:N34"/>
+    <mergeCell ref="G22:N22"/>
+    <mergeCell ref="G23:N23"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="G36:N36"/>
+    <mergeCell ref="G37:N37"/>
+    <mergeCell ref="G28:N28"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G4:M4"/>
+    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="G8:N8"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="G19:N19"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="G6:N6"/>
+    <mergeCell ref="G13:N13"/>
+    <mergeCell ref="G18:N18"/>
+    <mergeCell ref="G17:M17"/>
+    <mergeCell ref="G9:N9"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="G11:N11"/>
+    <mergeCell ref="G15:N15"/>
+    <mergeCell ref="G46:N46"/>
+    <mergeCell ref="G47:N47"/>
+    <mergeCell ref="G38:N38"/>
+    <mergeCell ref="G39:N39"/>
+    <mergeCell ref="G40:N40"/>
+    <mergeCell ref="G41:N41"/>
+    <mergeCell ref="G42:N42"/>
     <mergeCell ref="G58:N58"/>
     <mergeCell ref="G31:N31"/>
     <mergeCell ref="G59:N59"/>
@@ -5348,39 +5433,6 @@
     <mergeCell ref="G43:N43"/>
     <mergeCell ref="G44:N44"/>
     <mergeCell ref="G45:N45"/>
-    <mergeCell ref="G46:N46"/>
-    <mergeCell ref="G47:N47"/>
-    <mergeCell ref="G38:N38"/>
-    <mergeCell ref="G39:N39"/>
-    <mergeCell ref="G40:N40"/>
-    <mergeCell ref="G41:N41"/>
-    <mergeCell ref="G42:N42"/>
-    <mergeCell ref="G4:M4"/>
-    <mergeCell ref="G27:N27"/>
-    <mergeCell ref="G8:N8"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="G5:N5"/>
-    <mergeCell ref="G6:N6"/>
-    <mergeCell ref="G13:N13"/>
-    <mergeCell ref="G18:N18"/>
-    <mergeCell ref="G17:M17"/>
-    <mergeCell ref="G9:N9"/>
-    <mergeCell ref="H26:L26"/>
-    <mergeCell ref="G12:N12"/>
-    <mergeCell ref="G11:N11"/>
-    <mergeCell ref="G15:N15"/>
-    <mergeCell ref="G35:N35"/>
-    <mergeCell ref="G36:N36"/>
-    <mergeCell ref="G37:N37"/>
-    <mergeCell ref="G28:N28"/>
-    <mergeCell ref="G33:N33"/>
-    <mergeCell ref="G14:N14"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="G16:N16"/>
-    <mergeCell ref="G32:N32"/>
-    <mergeCell ref="G34:N34"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5392,13 +5444,13 @@
   <dimension ref="B2:O60"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="5" max="5" width="39.75" style="79" customWidth="1"/>
-    <col min="6" max="13" width="4.75" style="79" customWidth="1"/>
+    <col min="5" max="5" width="39.75" style="75" customWidth="1"/>
+    <col min="6" max="13" width="4.75" style="75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
@@ -5419,40 +5471,40 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C6" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C8" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -5498,18 +5550,18 @@
         <v>19</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F12" s="115" t="s">
         <v>262</v>
       </c>
-      <c r="F12" s="121" t="s">
-        <v>263</v>
-      </c>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="105"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="101"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -5519,18 +5571,18 @@
         <v>19</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F13" s="33"/>
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="121" t="s">
-        <v>265</v>
-      </c>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="105"/>
+      <c r="J13" s="115" t="s">
+        <v>264</v>
+      </c>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="101"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -5540,18 +5592,18 @@
         <v>19</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F14" s="121" t="s">
-        <v>263</v>
-      </c>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="105"/>
+        <v>265</v>
+      </c>
+      <c r="F14" s="115" t="s">
+        <v>262</v>
+      </c>
+      <c r="G14" s="100"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="100"/>
+      <c r="K14" s="100"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="101"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -5561,18 +5613,18 @@
         <v>19</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F15" s="33"/>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="35"/>
-      <c r="J15" s="121" t="s">
-        <v>265</v>
-      </c>
-      <c r="K15" s="104"/>
-      <c r="L15" s="104"/>
-      <c r="M15" s="105"/>
+      <c r="J15" s="115" t="s">
+        <v>264</v>
+      </c>
+      <c r="K15" s="100"/>
+      <c r="L15" s="100"/>
+      <c r="M15" s="101"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="18" t="s">
@@ -5582,18 +5634,18 @@
         <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F16" s="121" t="s">
-        <v>263</v>
-      </c>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="104"/>
-      <c r="M16" s="105"/>
+        <v>267</v>
+      </c>
+      <c r="F16" s="115" t="s">
+        <v>262</v>
+      </c>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="100"/>
+      <c r="K16" s="100"/>
+      <c r="L16" s="100"/>
+      <c r="M16" s="101"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="18" t="s">
@@ -5603,18 +5655,18 @@
         <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F17" s="33"/>
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
       <c r="I17" s="35"/>
-      <c r="J17" s="121" t="s">
-        <v>265</v>
-      </c>
-      <c r="K17" s="104"/>
-      <c r="L17" s="104"/>
-      <c r="M17" s="105"/>
+      <c r="J17" s="115" t="s">
+        <v>264</v>
+      </c>
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="101"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="18" t="s">
@@ -5624,18 +5676,18 @@
         <v>19</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F18" s="33"/>
       <c r="G18" s="34"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="121" t="s">
-        <v>271</v>
-      </c>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="105"/>
+      <c r="I18" s="115" t="s">
+        <v>270</v>
+      </c>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="101"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="18" t="s">
@@ -5645,31 +5697,31 @@
         <v>19</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F19" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="G19" s="37" t="s">
         <v>273</v>
       </c>
-      <c r="G19" s="37" t="s">
+      <c r="H19" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="H19" s="36" t="s">
+      <c r="I19" s="38" t="s">
         <v>275</v>
       </c>
-      <c r="I19" s="38" t="s">
+      <c r="J19" s="37" t="s">
         <v>276</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>277</v>
       </c>
       <c r="K19" s="39" t="s">
         <v>130</v>
       </c>
       <c r="L19" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>278</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="20" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -5680,20 +5732,20 @@
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F20" s="33"/>
       <c r="G20" s="34"/>
       <c r="H20" s="35"/>
       <c r="I20" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="J20" s="115" t="s">
         <v>281</v>
       </c>
-      <c r="J20" s="121" t="s">
-        <v>282</v>
-      </c>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="105"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="101"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -5703,20 +5755,20 @@
         <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F21" s="33"/>
       <c r="G21" s="34"/>
       <c r="H21" s="35"/>
       <c r="I21" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="J21" s="115" t="s">
         <v>281</v>
       </c>
-      <c r="J21" s="121" t="s">
-        <v>282</v>
-      </c>
-      <c r="K21" s="104"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="105"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="101"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -5726,20 +5778,20 @@
         <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F22" s="33"/>
       <c r="G22" s="34"/>
       <c r="H22" s="35"/>
       <c r="I22" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="J22" s="115" t="s">
         <v>281</v>
       </c>
-      <c r="J22" s="121" t="s">
-        <v>282</v>
-      </c>
-      <c r="K22" s="104"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="105"/>
+      <c r="K22" s="100"/>
+      <c r="L22" s="100"/>
+      <c r="M22" s="101"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -5749,18 +5801,18 @@
         <v>19</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F23" s="115" t="s">
         <v>285</v>
       </c>
-      <c r="F23" s="121" t="s">
-        <v>286</v>
-      </c>
-      <c r="G23" s="104"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="105"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="101"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -5770,18 +5822,18 @@
         <v>19</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F24" s="115" t="s">
         <v>287</v>
       </c>
-      <c r="F24" s="121" t="s">
-        <v>288</v>
-      </c>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="105"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="101"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -5791,18 +5843,18 @@
         <v>19</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F25" s="33"/>
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="121" t="s">
-        <v>290</v>
-      </c>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="105"/>
+      <c r="J25" s="115" t="s">
+        <v>289</v>
+      </c>
+      <c r="K25" s="100"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="101"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -5812,7 +5864,7 @@
         <v>19</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="8"/>
@@ -5831,7 +5883,7 @@
         <v>19</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="8"/>
@@ -5850,18 +5902,18 @@
         <v>3</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>293</v>
-      </c>
-      <c r="F28" s="103" t="s">
-        <v>263</v>
-      </c>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="105"/>
+        <v>292</v>
+      </c>
+      <c r="F28" s="112" t="s">
+        <v>262</v>
+      </c>
+      <c r="G28" s="100"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="100"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="100"/>
+      <c r="L28" s="100"/>
+      <c r="M28" s="101"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="18" t="s">
@@ -5871,18 +5923,18 @@
         <v>3</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F29" s="25"/>
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="27"/>
-      <c r="J29" s="103" t="s">
-        <v>265</v>
-      </c>
-      <c r="K29" s="104"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="105"/>
+      <c r="J29" s="112" t="s">
+        <v>264</v>
+      </c>
+      <c r="K29" s="100"/>
+      <c r="L29" s="100"/>
+      <c r="M29" s="101"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -5892,18 +5944,18 @@
         <v>3</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="F30" s="103" t="s">
-        <v>263</v>
-      </c>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="105"/>
+        <v>294</v>
+      </c>
+      <c r="F30" s="112" t="s">
+        <v>262</v>
+      </c>
+      <c r="G30" s="100"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="100"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="100"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="101"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -5913,18 +5965,18 @@
         <v>3</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F31" s="25"/>
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="27"/>
-      <c r="J31" s="103" t="s">
-        <v>265</v>
-      </c>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="105"/>
+      <c r="J31" s="112" t="s">
+        <v>264</v>
+      </c>
+      <c r="K31" s="100"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="101"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -5934,18 +5986,18 @@
         <v>3</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="F32" s="103" t="s">
-        <v>263</v>
-      </c>
-      <c r="G32" s="104"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="105"/>
+        <v>296</v>
+      </c>
+      <c r="F32" s="112" t="s">
+        <v>262</v>
+      </c>
+      <c r="G32" s="100"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="100"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="100"/>
+      <c r="M32" s="101"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -5955,18 +6007,18 @@
         <v>3</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F33" s="25"/>
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="27"/>
-      <c r="J33" s="103" t="s">
-        <v>265</v>
-      </c>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="105"/>
+      <c r="J33" s="112" t="s">
+        <v>264</v>
+      </c>
+      <c r="K33" s="100"/>
+      <c r="L33" s="100"/>
+      <c r="M33" s="101"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -5976,18 +6028,18 @@
         <v>3</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F34" s="25"/>
       <c r="G34" s="26"/>
       <c r="H34" s="27"/>
-      <c r="I34" s="103" t="s">
-        <v>271</v>
-      </c>
-      <c r="J34" s="104"/>
-      <c r="K34" s="104"/>
-      <c r="L34" s="104"/>
-      <c r="M34" s="105"/>
+      <c r="I34" s="112" t="s">
+        <v>270</v>
+      </c>
+      <c r="J34" s="100"/>
+      <c r="K34" s="100"/>
+      <c r="L34" s="100"/>
+      <c r="M34" s="101"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -5997,31 +6049,31 @@
         <v>3</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F35" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="G35" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="G35" s="29" t="s">
+      <c r="H35" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="I35" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="I35" s="30" t="s">
+      <c r="J35" s="29" t="s">
         <v>276</v>
-      </c>
-      <c r="J35" s="29" t="s">
-        <v>277</v>
       </c>
       <c r="K35" s="31" t="s">
         <v>130</v>
       </c>
       <c r="L35" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="M35" s="29" t="s">
         <v>278</v>
-      </c>
-      <c r="M35" s="29" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="36" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -6032,20 +6084,20 @@
         <v>3</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F36" s="25"/>
       <c r="G36" s="26"/>
       <c r="H36" s="27"/>
       <c r="I36" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="J36" s="112" t="s">
         <v>281</v>
       </c>
-      <c r="J36" s="103" t="s">
-        <v>282</v>
-      </c>
-      <c r="K36" s="104"/>
-      <c r="L36" s="104"/>
-      <c r="M36" s="105"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="101"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -6055,20 +6107,20 @@
         <v>3</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F37" s="25"/>
       <c r="G37" s="26"/>
       <c r="H37" s="27"/>
       <c r="I37" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="J37" s="112" t="s">
         <v>281</v>
       </c>
-      <c r="J37" s="103" t="s">
-        <v>282</v>
-      </c>
-      <c r="K37" s="104"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="105"/>
+      <c r="K37" s="100"/>
+      <c r="L37" s="100"/>
+      <c r="M37" s="101"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -6078,20 +6130,20 @@
         <v>3</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F38" s="25"/>
       <c r="G38" s="26"/>
       <c r="H38" s="27"/>
       <c r="I38" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="J38" s="112" t="s">
         <v>281</v>
       </c>
-      <c r="J38" s="103" t="s">
-        <v>282</v>
-      </c>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="105"/>
+      <c r="K38" s="100"/>
+      <c r="L38" s="100"/>
+      <c r="M38" s="101"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -6101,18 +6153,18 @@
         <v>3</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="F39" s="103" t="s">
-        <v>286</v>
-      </c>
-      <c r="G39" s="104"/>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="104"/>
-      <c r="K39" s="104"/>
-      <c r="L39" s="104"/>
-      <c r="M39" s="105"/>
+        <v>303</v>
+      </c>
+      <c r="F39" s="112" t="s">
+        <v>285</v>
+      </c>
+      <c r="G39" s="100"/>
+      <c r="H39" s="100"/>
+      <c r="I39" s="100"/>
+      <c r="J39" s="100"/>
+      <c r="K39" s="100"/>
+      <c r="L39" s="100"/>
+      <c r="M39" s="101"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18" t="s">
@@ -6122,18 +6174,18 @@
         <v>3</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="F40" s="103" t="s">
-        <v>288</v>
-      </c>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="105"/>
+        <v>304</v>
+      </c>
+      <c r="F40" s="112" t="s">
+        <v>287</v>
+      </c>
+      <c r="G40" s="100"/>
+      <c r="H40" s="100"/>
+      <c r="I40" s="100"/>
+      <c r="J40" s="100"/>
+      <c r="K40" s="100"/>
+      <c r="L40" s="100"/>
+      <c r="M40" s="101"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18" t="s">
@@ -6143,18 +6195,18 @@
         <v>3</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F41" s="25"/>
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="27"/>
-      <c r="J41" s="103" t="s">
-        <v>290</v>
-      </c>
-      <c r="K41" s="104"/>
-      <c r="L41" s="104"/>
-      <c r="M41" s="105"/>
+      <c r="J41" s="112" t="s">
+        <v>289</v>
+      </c>
+      <c r="K41" s="100"/>
+      <c r="L41" s="100"/>
+      <c r="M41" s="101"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18" t="s">
@@ -6164,7 +6216,7 @@
         <v>3</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F42" s="25"/>
       <c r="G42" s="26"/>
@@ -6183,100 +6235,100 @@
         <v>3</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F43" s="68"/>
       <c r="G43" s="69"/>
       <c r="H43" s="69"/>
       <c r="I43" s="70"/>
-      <c r="J43" s="122" t="s">
-        <v>309</v>
-      </c>
-      <c r="K43" s="123"/>
-      <c r="L43" s="123"/>
-      <c r="M43" s="124"/>
+      <c r="J43" s="118" t="s">
+        <v>308</v>
+      </c>
+      <c r="K43" s="119"/>
+      <c r="L43" s="119"/>
+      <c r="M43" s="120"/>
     </row>
     <row r="44" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E44" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="F44" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="G44" s="100"/>
+      <c r="H44" s="100"/>
+      <c r="I44" s="100"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="100"/>
+      <c r="M44" s="117"/>
+      <c r="O44" t="s">
         <v>311</v>
-      </c>
-      <c r="F44" s="119" t="s">
-        <v>282</v>
-      </c>
-      <c r="G44" s="104"/>
-      <c r="H44" s="104"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="104"/>
-      <c r="K44" s="104"/>
-      <c r="L44" s="104"/>
-      <c r="M44" s="120"/>
-      <c r="O44" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="45" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F45" s="119" t="s">
-        <v>282</v>
-      </c>
-      <c r="G45" s="104"/>
-      <c r="H45" s="104"/>
-      <c r="I45" s="104"/>
-      <c r="J45" s="104"/>
-      <c r="K45" s="104"/>
-      <c r="L45" s="104"/>
-      <c r="M45" s="120"/>
+        <v>313</v>
+      </c>
+      <c r="F45" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="G45" s="100"/>
+      <c r="H45" s="100"/>
+      <c r="I45" s="100"/>
+      <c r="J45" s="100"/>
+      <c r="K45" s="100"/>
+      <c r="L45" s="100"/>
+      <c r="M45" s="117"/>
       <c r="O45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="F46" s="119" t="s">
-        <v>282</v>
-      </c>
-      <c r="G46" s="104"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="104"/>
-      <c r="K46" s="104"/>
-      <c r="L46" s="104"/>
-      <c r="M46" s="120"/>
+        <v>315</v>
+      </c>
+      <c r="F46" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="G46" s="100"/>
+      <c r="H46" s="100"/>
+      <c r="I46" s="100"/>
+      <c r="J46" s="100"/>
+      <c r="K46" s="100"/>
+      <c r="L46" s="100"/>
+      <c r="M46" s="117"/>
       <c r="O46" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F47" s="60"/>
       <c r="G47" s="60"/>
@@ -6289,85 +6341,85 @@
     </row>
     <row r="48" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="F48" s="119" t="s">
-        <v>282</v>
-      </c>
-      <c r="G48" s="104"/>
-      <c r="H48" s="104"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="104"/>
-      <c r="K48" s="104"/>
-      <c r="L48" s="104"/>
-      <c r="M48" s="120"/>
+        <v>319</v>
+      </c>
+      <c r="F48" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="G48" s="100"/>
+      <c r="H48" s="100"/>
+      <c r="I48" s="100"/>
+      <c r="J48" s="100"/>
+      <c r="K48" s="100"/>
+      <c r="L48" s="100"/>
+      <c r="M48" s="117"/>
       <c r="O48" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="F49" s="119" t="s">
-        <v>282</v>
-      </c>
-      <c r="G49" s="104"/>
-      <c r="H49" s="104"/>
-      <c r="I49" s="104"/>
-      <c r="J49" s="104"/>
-      <c r="K49" s="104"/>
-      <c r="L49" s="104"/>
-      <c r="M49" s="120"/>
+        <v>321</v>
+      </c>
+      <c r="F49" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="G49" s="100"/>
+      <c r="H49" s="100"/>
+      <c r="I49" s="100"/>
+      <c r="J49" s="100"/>
+      <c r="K49" s="100"/>
+      <c r="L49" s="100"/>
+      <c r="M49" s="117"/>
       <c r="O49" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="F50" s="119" t="s">
-        <v>282</v>
-      </c>
-      <c r="G50" s="104"/>
-      <c r="H50" s="104"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="104"/>
-      <c r="K50" s="104"/>
-      <c r="L50" s="104"/>
-      <c r="M50" s="120"/>
+        <v>323</v>
+      </c>
+      <c r="F50" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="G50" s="100"/>
+      <c r="H50" s="100"/>
+      <c r="I50" s="100"/>
+      <c r="J50" s="100"/>
+      <c r="K50" s="100"/>
+      <c r="L50" s="100"/>
+      <c r="M50" s="117"/>
       <c r="O50" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F51" s="60"/>
       <c r="G51" s="60"/>
@@ -6380,85 +6432,85 @@
     </row>
     <row r="52" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="F52" s="103" t="s">
+        <v>326</v>
+      </c>
+      <c r="F52" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="104"/>
-      <c r="H52" s="104"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="104"/>
-      <c r="K52" s="104"/>
-      <c r="L52" s="104"/>
-      <c r="M52" s="105"/>
+      <c r="G52" s="100"/>
+      <c r="H52" s="100"/>
+      <c r="I52" s="100"/>
+      <c r="J52" s="100"/>
+      <c r="K52" s="100"/>
+      <c r="L52" s="100"/>
+      <c r="M52" s="101"/>
       <c r="O52" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="53" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="F53" s="103" t="s">
+        <v>328</v>
+      </c>
+      <c r="F53" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="104"/>
-      <c r="J53" s="104"/>
-      <c r="K53" s="104"/>
-      <c r="L53" s="104"/>
-      <c r="M53" s="105"/>
+      <c r="G53" s="100"/>
+      <c r="H53" s="100"/>
+      <c r="I53" s="100"/>
+      <c r="J53" s="100"/>
+      <c r="K53" s="100"/>
+      <c r="L53" s="100"/>
+      <c r="M53" s="101"/>
       <c r="O53" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="54" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="F54" s="103" t="s">
+        <v>330</v>
+      </c>
+      <c r="F54" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="104"/>
-      <c r="J54" s="104"/>
-      <c r="K54" s="104"/>
-      <c r="L54" s="104"/>
-      <c r="M54" s="105"/>
+      <c r="G54" s="100"/>
+      <c r="H54" s="100"/>
+      <c r="I54" s="100"/>
+      <c r="J54" s="100"/>
+      <c r="K54" s="100"/>
+      <c r="L54" s="100"/>
+      <c r="M54" s="101"/>
       <c r="O54" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="55" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F55" s="60"/>
       <c r="G55" s="60"/>
@@ -6471,85 +6523,85 @@
     </row>
     <row r="56" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="F56" s="103" t="s">
+        <v>333</v>
+      </c>
+      <c r="F56" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="104"/>
-      <c r="J56" s="104"/>
-      <c r="K56" s="104"/>
-      <c r="L56" s="104"/>
-      <c r="M56" s="105"/>
+      <c r="G56" s="100"/>
+      <c r="H56" s="100"/>
+      <c r="I56" s="100"/>
+      <c r="J56" s="100"/>
+      <c r="K56" s="100"/>
+      <c r="L56" s="100"/>
+      <c r="M56" s="101"/>
       <c r="O56" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="57" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="F57" s="103" t="s">
+        <v>335</v>
+      </c>
+      <c r="F57" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="104"/>
-      <c r="J57" s="104"/>
-      <c r="K57" s="104"/>
-      <c r="L57" s="104"/>
-      <c r="M57" s="105"/>
+      <c r="G57" s="100"/>
+      <c r="H57" s="100"/>
+      <c r="I57" s="100"/>
+      <c r="J57" s="100"/>
+      <c r="K57" s="100"/>
+      <c r="L57" s="100"/>
+      <c r="M57" s="101"/>
       <c r="O57" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="58" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="F58" s="103" t="s">
+        <v>337</v>
+      </c>
+      <c r="F58" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="104"/>
-      <c r="H58" s="104"/>
-      <c r="I58" s="104"/>
-      <c r="J58" s="104"/>
-      <c r="K58" s="104"/>
-      <c r="L58" s="104"/>
-      <c r="M58" s="105"/>
+      <c r="G58" s="100"/>
+      <c r="H58" s="100"/>
+      <c r="I58" s="100"/>
+      <c r="J58" s="100"/>
+      <c r="K58" s="100"/>
+      <c r="L58" s="100"/>
+      <c r="M58" s="101"/>
       <c r="O58" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="59" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C59" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>3</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F59" s="60"/>
       <c r="G59" s="60"/>
@@ -6562,13 +6614,13 @@
     </row>
     <row r="60" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C60" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F60" s="60"/>
       <c r="G60" s="60"/>
@@ -6581,17 +6633,18 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F45:M45"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:M48"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F53:M53"/>
     <mergeCell ref="F12:M12"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J17:M17"/>
@@ -6608,18 +6661,17 @@
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:M48"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F50:M50"/>
-    <mergeCell ref="F46:M46"/>
-    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J43:M43"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6632,16 +6684,16 @@
   <dimension ref="B2:O79"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="5" max="5" width="29.125" style="79" customWidth="1"/>
-    <col min="6" max="13" width="4.75" style="79" customWidth="1"/>
+    <col min="5" max="5" width="29.125" style="75" customWidth="1"/>
+    <col min="6" max="13" width="4.75" style="75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E2" t="s">
         <v>341</v>
-      </c>
-      <c r="E2" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.15">
@@ -6686,49 +6738,49 @@
     </row>
     <row r="6" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="F6" s="106" t="s">
-        <v>344</v>
-      </c>
-      <c r="G6" s="104"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="105"/>
+        <v>539</v>
+      </c>
+      <c r="F6" s="99" t="s">
+        <v>539</v>
+      </c>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="101"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F7" s="106" t="s">
-        <v>347</v>
-      </c>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="105"/>
+        <v>538</v>
+      </c>
+      <c r="F7" s="99" t="s">
+        <v>540</v>
+      </c>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="101"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -6781,17 +6833,17 @@
         <v>106</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="106" t="s">
+      <c r="J19" s="99" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="104"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="105"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="101"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="18" t="s">
@@ -6808,17 +6860,17 @@
         <v>106</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="106" t="s">
+      <c r="J20" s="99" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="105"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="101"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -6828,18 +6880,18 @@
         <v>19</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="106" t="s">
-        <v>350</v>
-      </c>
-      <c r="G21" s="105"/>
-      <c r="H21" s="106" t="s">
+      <c r="F21" s="99" t="s">
+        <v>346</v>
+      </c>
+      <c r="G21" s="101"/>
+      <c r="H21" s="99" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="104"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="105"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="101"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -6849,22 +6901,22 @@
         <v>19</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="106" t="s">
-        <v>350</v>
-      </c>
-      <c r="G22" s="105"/>
+      <c r="F22" s="99" t="s">
+        <v>346</v>
+      </c>
+      <c r="G22" s="101"/>
       <c r="H22" s="17"/>
       <c r="I22" s="10" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="K22" s="106" t="s">
+        <v>348</v>
+      </c>
+      <c r="K22" s="99" t="s">
         <v>133</v>
       </c>
-      <c r="L22" s="104"/>
-      <c r="M22" s="105"/>
+      <c r="L22" s="100"/>
+      <c r="M22" s="101"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -6874,18 +6926,18 @@
         <v>19</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="106" t="s">
+      <c r="F23" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="104"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="106" t="s">
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="105"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="101"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -6895,18 +6947,18 @@
         <v>19</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="106" t="s">
+      <c r="F24" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="106" t="s">
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="105"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="101"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -6916,18 +6968,18 @@
         <v>19</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="106" t="s">
+      <c r="F25" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="104"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="106" t="s">
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="101"/>
+      <c r="J25" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="105"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="101"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -6937,25 +6989,25 @@
         <v>19</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="106" t="s">
+      <c r="F26" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="104"/>
-      <c r="H26" s="104"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="106" t="s">
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="104"/>
-      <c r="L26" s="104"/>
-      <c r="M26" s="105"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="101"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="18" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="7"/>
@@ -7000,18 +7052,18 @@
         <v>19</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F29" s="106" t="s">
+        <v>350</v>
+      </c>
+      <c r="F29" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="104"/>
-      <c r="H29" s="104"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="105"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="100"/>
+      <c r="I29" s="100"/>
+      <c r="J29" s="100"/>
+      <c r="K29" s="100"/>
+      <c r="L29" s="100"/>
+      <c r="M29" s="101"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -7021,16 +7073,16 @@
         <v>19</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="106" t="s">
+      <c r="F30" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="105"/>
+      <c r="G30" s="100"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="100"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="100"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="101"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -7040,16 +7092,16 @@
         <v>19</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="106" t="s">
+      <c r="F31" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="105"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="100"/>
+      <c r="J31" s="100"/>
+      <c r="K31" s="100"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="101"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -7059,16 +7111,16 @@
         <v>19</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="106" t="s">
+      <c r="F32" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="104"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="105"/>
+      <c r="G32" s="100"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="100"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="100"/>
+      <c r="M32" s="101"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -7078,16 +7130,16 @@
         <v>19</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="106" t="s">
+      <c r="F33" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="104"/>
-      <c r="H33" s="104"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="105"/>
+      <c r="G33" s="100"/>
+      <c r="H33" s="100"/>
+      <c r="I33" s="100"/>
+      <c r="J33" s="100"/>
+      <c r="K33" s="100"/>
+      <c r="L33" s="100"/>
+      <c r="M33" s="101"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -7097,16 +7149,16 @@
         <v>19</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="106" t="s">
+      <c r="F34" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="104"/>
-      <c r="H34" s="104"/>
-      <c r="I34" s="104"/>
-      <c r="J34" s="104"/>
-      <c r="K34" s="104"/>
-      <c r="L34" s="104"/>
-      <c r="M34" s="105"/>
+      <c r="G34" s="100"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="100"/>
+      <c r="K34" s="100"/>
+      <c r="L34" s="100"/>
+      <c r="M34" s="101"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -7116,16 +7168,16 @@
         <v>19</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="106" t="s">
+      <c r="F35" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="104"/>
-      <c r="H35" s="104"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="104"/>
-      <c r="K35" s="104"/>
-      <c r="L35" s="104"/>
-      <c r="M35" s="105"/>
+      <c r="G35" s="100"/>
+      <c r="H35" s="100"/>
+      <c r="I35" s="100"/>
+      <c r="J35" s="100"/>
+      <c r="K35" s="100"/>
+      <c r="L35" s="100"/>
+      <c r="M35" s="101"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="18" t="s">
@@ -7135,16 +7187,16 @@
         <v>19</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="106" t="s">
+      <c r="F36" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="104"/>
-      <c r="H36" s="104"/>
-      <c r="I36" s="104"/>
-      <c r="J36" s="104"/>
-      <c r="K36" s="104"/>
-      <c r="L36" s="104"/>
-      <c r="M36" s="105"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="101"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -7154,16 +7206,16 @@
         <v>19</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="106" t="s">
+      <c r="F37" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="104"/>
-      <c r="H37" s="104"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="105"/>
+      <c r="G37" s="100"/>
+      <c r="H37" s="100"/>
+      <c r="I37" s="100"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="100"/>
+      <c r="L37" s="100"/>
+      <c r="M37" s="101"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -7173,23 +7225,23 @@
         <v>19</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="106" t="s">
+      <c r="F38" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G38" s="104"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="105"/>
+      <c r="G38" s="100"/>
+      <c r="H38" s="100"/>
+      <c r="I38" s="100"/>
+      <c r="J38" s="100"/>
+      <c r="K38" s="100"/>
+      <c r="L38" s="100"/>
+      <c r="M38" s="101"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="7"/>
@@ -7203,7 +7255,7 @@
     </row>
     <row r="40" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>19</v>
@@ -7212,23 +7264,23 @@
       <c r="F40" s="7"/>
       <c r="G40" s="9"/>
       <c r="H40" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="J40" s="106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J40" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="K40" s="104"/>
-      <c r="L40" s="105"/>
+      <c r="K40" s="100"/>
+      <c r="L40" s="101"/>
       <c r="M40" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="41" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>19</v>
@@ -7237,23 +7289,23 @@
       <c r="F41" s="7"/>
       <c r="G41" s="9"/>
       <c r="H41" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="J41" s="106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J41" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="K41" s="104"/>
-      <c r="L41" s="105"/>
+      <c r="K41" s="100"/>
+      <c r="L41" s="101"/>
       <c r="M41" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="42" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>19</v>
@@ -7262,23 +7314,23 @@
       <c r="F42" s="7"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="J42" s="106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J42" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="K42" s="104"/>
-      <c r="L42" s="105"/>
+      <c r="K42" s="100"/>
+      <c r="L42" s="101"/>
       <c r="M42" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="43" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="18" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>19</v>
@@ -7287,23 +7339,23 @@
       <c r="F43" s="7"/>
       <c r="G43" s="9"/>
       <c r="H43" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="J43" s="106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J43" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="K43" s="104"/>
-      <c r="L43" s="105"/>
+      <c r="K43" s="100"/>
+      <c r="L43" s="101"/>
       <c r="M43" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="44" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>19</v>
@@ -7312,23 +7364,23 @@
       <c r="F44" s="7"/>
       <c r="G44" s="9"/>
       <c r="H44" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="J44" s="106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J44" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="K44" s="104"/>
-      <c r="L44" s="105"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="101"/>
       <c r="M44" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="45" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>19</v>
@@ -7337,23 +7389,23 @@
       <c r="F45" s="7"/>
       <c r="G45" s="9"/>
       <c r="H45" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="J45" s="106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J45" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="K45" s="104"/>
-      <c r="L45" s="105"/>
+      <c r="K45" s="100"/>
+      <c r="L45" s="101"/>
       <c r="M45" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="46" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>19</v>
@@ -7362,23 +7414,23 @@
       <c r="F46" s="7"/>
       <c r="G46" s="9"/>
       <c r="H46" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="J46" s="106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J46" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="K46" s="104"/>
-      <c r="L46" s="105"/>
+      <c r="K46" s="100"/>
+      <c r="L46" s="101"/>
       <c r="M46" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="47" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>19</v>
@@ -7387,23 +7439,23 @@
       <c r="F47" s="7"/>
       <c r="G47" s="9"/>
       <c r="H47" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="J47" s="106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J47" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="K47" s="104"/>
-      <c r="L47" s="105"/>
+      <c r="K47" s="100"/>
+      <c r="L47" s="101"/>
       <c r="M47" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="48" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>19</v>
@@ -7412,26 +7464,26 @@
       <c r="F48" s="7"/>
       <c r="G48" s="9"/>
       <c r="H48" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="J48" s="106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J48" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="K48" s="104"/>
-      <c r="L48" s="105"/>
+      <c r="K48" s="100"/>
+      <c r="L48" s="101"/>
       <c r="M48" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="49" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="7"/>
@@ -7445,199 +7497,199 @@
     </row>
     <row r="50" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C50" s="18" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G50" s="104"/>
-      <c r="H50" s="104"/>
-      <c r="I50" s="105"/>
-      <c r="J50" s="106" t="s">
-        <v>361</v>
-      </c>
-      <c r="K50" s="104"/>
-      <c r="L50" s="104"/>
-      <c r="M50" s="105"/>
+      <c r="F50" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G50" s="100"/>
+      <c r="H50" s="100"/>
+      <c r="I50" s="101"/>
+      <c r="J50" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="K50" s="100"/>
+      <c r="L50" s="100"/>
+      <c r="M50" s="101"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E51" s="11"/>
-      <c r="F51" s="106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G51" s="104"/>
-      <c r="H51" s="104"/>
-      <c r="I51" s="105"/>
-      <c r="J51" s="106" t="s">
-        <v>361</v>
-      </c>
-      <c r="K51" s="104"/>
-      <c r="L51" s="104"/>
-      <c r="M51" s="105"/>
+      <c r="F51" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G51" s="100"/>
+      <c r="H51" s="100"/>
+      <c r="I51" s="101"/>
+      <c r="J51" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="K51" s="100"/>
+      <c r="L51" s="100"/>
+      <c r="M51" s="101"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G52" s="104"/>
-      <c r="H52" s="104"/>
-      <c r="I52" s="105"/>
-      <c r="J52" s="106" t="s">
-        <v>361</v>
-      </c>
-      <c r="K52" s="104"/>
-      <c r="L52" s="104"/>
-      <c r="M52" s="105"/>
+      <c r="F52" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G52" s="100"/>
+      <c r="H52" s="100"/>
+      <c r="I52" s="101"/>
+      <c r="J52" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="K52" s="100"/>
+      <c r="L52" s="100"/>
+      <c r="M52" s="101"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105"/>
-      <c r="J53" s="106" t="s">
-        <v>361</v>
-      </c>
-      <c r="K53" s="104"/>
-      <c r="L53" s="104"/>
-      <c r="M53" s="105"/>
+      <c r="F53" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G53" s="100"/>
+      <c r="H53" s="100"/>
+      <c r="I53" s="101"/>
+      <c r="J53" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="K53" s="100"/>
+      <c r="L53" s="100"/>
+      <c r="M53" s="101"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105"/>
-      <c r="J54" s="106" t="s">
-        <v>361</v>
-      </c>
-      <c r="K54" s="104"/>
-      <c r="L54" s="104"/>
-      <c r="M54" s="105"/>
+      <c r="F54" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G54" s="100"/>
+      <c r="H54" s="100"/>
+      <c r="I54" s="101"/>
+      <c r="J54" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="K54" s="100"/>
+      <c r="L54" s="100"/>
+      <c r="M54" s="101"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105"/>
-      <c r="J55" s="106" t="s">
-        <v>361</v>
-      </c>
-      <c r="K55" s="104"/>
-      <c r="L55" s="104"/>
-      <c r="M55" s="105"/>
+      <c r="F55" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G55" s="100"/>
+      <c r="H55" s="100"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="K55" s="100"/>
+      <c r="L55" s="100"/>
+      <c r="M55" s="101"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105"/>
-      <c r="J56" s="106" t="s">
-        <v>361</v>
-      </c>
-      <c r="K56" s="104"/>
-      <c r="L56" s="104"/>
-      <c r="M56" s="105"/>
+      <c r="F56" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G56" s="100"/>
+      <c r="H56" s="100"/>
+      <c r="I56" s="101"/>
+      <c r="J56" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="K56" s="100"/>
+      <c r="L56" s="100"/>
+      <c r="M56" s="101"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105"/>
-      <c r="J57" s="106" t="s">
-        <v>361</v>
-      </c>
-      <c r="K57" s="104"/>
-      <c r="L57" s="104"/>
-      <c r="M57" s="105"/>
+      <c r="F57" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G57" s="100"/>
+      <c r="H57" s="100"/>
+      <c r="I57" s="101"/>
+      <c r="J57" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="K57" s="100"/>
+      <c r="L57" s="100"/>
+      <c r="M57" s="101"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G58" s="104"/>
-      <c r="H58" s="104"/>
-      <c r="I58" s="105"/>
-      <c r="J58" s="106" t="s">
-        <v>361</v>
-      </c>
-      <c r="K58" s="104"/>
-      <c r="L58" s="104"/>
-      <c r="M58" s="105"/>
+      <c r="F58" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G58" s="100"/>
+      <c r="H58" s="100"/>
+      <c r="I58" s="101"/>
+      <c r="J58" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="K58" s="100"/>
+      <c r="L58" s="100"/>
+      <c r="M58" s="101"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="18" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="7"/>
@@ -7651,13 +7703,13 @@
     </row>
     <row r="60" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C60" s="18" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="8"/>
@@ -7665,20 +7717,20 @@
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="103" t="s">
-        <v>373</v>
-      </c>
-      <c r="M60" s="105"/>
+      <c r="L60" s="112" t="s">
+        <v>369</v>
+      </c>
+      <c r="M60" s="101"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="18" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="8"/>
@@ -7686,20 +7738,20 @@
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
       <c r="K61" s="9"/>
-      <c r="L61" s="113" t="s">
-        <v>373</v>
-      </c>
-      <c r="M61" s="105"/>
+      <c r="L61" s="114" t="s">
+        <v>369</v>
+      </c>
+      <c r="M61" s="101"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="18" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="8"/>
@@ -7707,20 +7759,20 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="9"/>
-      <c r="L62" s="113" t="s">
-        <v>373</v>
-      </c>
-      <c r="M62" s="105"/>
+      <c r="L62" s="114" t="s">
+        <v>369</v>
+      </c>
+      <c r="M62" s="101"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="18" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="8"/>
@@ -7728,20 +7780,20 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="9"/>
-      <c r="L63" s="113" t="s">
-        <v>373</v>
-      </c>
-      <c r="M63" s="105"/>
+      <c r="L63" s="114" t="s">
+        <v>369</v>
+      </c>
+      <c r="M63" s="101"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="18" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="8"/>
@@ -7749,20 +7801,20 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="9"/>
-      <c r="L64" s="113" t="s">
-        <v>373</v>
-      </c>
-      <c r="M64" s="105"/>
+      <c r="L64" s="114" t="s">
+        <v>369</v>
+      </c>
+      <c r="M64" s="101"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="18" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E65" s="21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="8"/>
@@ -7770,20 +7822,20 @@
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="9"/>
-      <c r="L65" s="113" t="s">
-        <v>373</v>
-      </c>
-      <c r="M65" s="105"/>
+      <c r="L65" s="114" t="s">
+        <v>369</v>
+      </c>
+      <c r="M65" s="101"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="18" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="8"/>
@@ -7791,20 +7843,20 @@
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
       <c r="K66" s="9"/>
-      <c r="L66" s="113" t="s">
-        <v>373</v>
-      </c>
-      <c r="M66" s="105"/>
+      <c r="L66" s="114" t="s">
+        <v>369</v>
+      </c>
+      <c r="M66" s="101"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="18" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="8"/>
@@ -7812,20 +7864,20 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="9"/>
-      <c r="L67" s="113" t="s">
-        <v>373</v>
-      </c>
-      <c r="M67" s="105"/>
+      <c r="L67" s="114" t="s">
+        <v>369</v>
+      </c>
+      <c r="M67" s="101"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="18" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="8"/>
@@ -7833,17 +7885,17 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="9"/>
-      <c r="L68" s="113" t="s">
-        <v>373</v>
-      </c>
-      <c r="M68" s="105"/>
+      <c r="L68" s="114" t="s">
+        <v>369</v>
+      </c>
+      <c r="M68" s="101"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="18" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="7"/>
@@ -7857,226 +7909,226 @@
     </row>
     <row r="70" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C70" s="18" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="F70" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F70" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G70" s="104"/>
-      <c r="H70" s="104"/>
-      <c r="I70" s="104"/>
-      <c r="J70" s="104"/>
-      <c r="K70" s="104"/>
-      <c r="L70" s="104"/>
-      <c r="M70" s="105"/>
+      <c r="G70" s="100"/>
+      <c r="H70" s="100"/>
+      <c r="I70" s="100"/>
+      <c r="J70" s="100"/>
+      <c r="K70" s="100"/>
+      <c r="L70" s="100"/>
+      <c r="M70" s="101"/>
       <c r="O70" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="71" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C71" s="18" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="F71" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F71" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G71" s="104"/>
-      <c r="H71" s="104"/>
-      <c r="I71" s="104"/>
-      <c r="J71" s="104"/>
-      <c r="K71" s="104"/>
-      <c r="L71" s="104"/>
-      <c r="M71" s="105"/>
+      <c r="G71" s="100"/>
+      <c r="H71" s="100"/>
+      <c r="I71" s="100"/>
+      <c r="J71" s="100"/>
+      <c r="K71" s="100"/>
+      <c r="L71" s="100"/>
+      <c r="M71" s="101"/>
       <c r="O71" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="72" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C72" s="18" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="F72" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F72" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G72" s="104"/>
-      <c r="H72" s="104"/>
-      <c r="I72" s="104"/>
-      <c r="J72" s="104"/>
-      <c r="K72" s="104"/>
-      <c r="L72" s="104"/>
-      <c r="M72" s="105"/>
+      <c r="G72" s="100"/>
+      <c r="H72" s="100"/>
+      <c r="I72" s="100"/>
+      <c r="J72" s="100"/>
+      <c r="K72" s="100"/>
+      <c r="L72" s="100"/>
+      <c r="M72" s="101"/>
       <c r="O72" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="73" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C73" s="18" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="F73" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F73" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="104"/>
-      <c r="H73" s="104"/>
-      <c r="I73" s="104"/>
-      <c r="J73" s="104"/>
-      <c r="K73" s="104"/>
-      <c r="L73" s="104"/>
-      <c r="M73" s="105"/>
+      <c r="G73" s="100"/>
+      <c r="H73" s="100"/>
+      <c r="I73" s="100"/>
+      <c r="J73" s="100"/>
+      <c r="K73" s="100"/>
+      <c r="L73" s="100"/>
+      <c r="M73" s="101"/>
       <c r="O73" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="74" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C74" s="18" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="F74" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F74" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G74" s="104"/>
-      <c r="H74" s="104"/>
-      <c r="I74" s="104"/>
-      <c r="J74" s="104"/>
-      <c r="K74" s="104"/>
-      <c r="L74" s="104"/>
-      <c r="M74" s="105"/>
+      <c r="G74" s="100"/>
+      <c r="H74" s="100"/>
+      <c r="I74" s="100"/>
+      <c r="J74" s="100"/>
+      <c r="K74" s="100"/>
+      <c r="L74" s="100"/>
+      <c r="M74" s="101"/>
       <c r="O74" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="75" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C75" s="18" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="F75" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F75" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G75" s="104"/>
-      <c r="H75" s="104"/>
-      <c r="I75" s="104"/>
-      <c r="J75" s="104"/>
-      <c r="K75" s="104"/>
-      <c r="L75" s="104"/>
-      <c r="M75" s="105"/>
+      <c r="G75" s="100"/>
+      <c r="H75" s="100"/>
+      <c r="I75" s="100"/>
+      <c r="J75" s="100"/>
+      <c r="K75" s="100"/>
+      <c r="L75" s="100"/>
+      <c r="M75" s="101"/>
       <c r="O75" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="76" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C76" s="18" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="F76" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F76" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G76" s="104"/>
-      <c r="H76" s="104"/>
-      <c r="I76" s="104"/>
-      <c r="J76" s="104"/>
-      <c r="K76" s="104"/>
-      <c r="L76" s="104"/>
-      <c r="M76" s="105"/>
+      <c r="G76" s="100"/>
+      <c r="H76" s="100"/>
+      <c r="I76" s="100"/>
+      <c r="J76" s="100"/>
+      <c r="K76" s="100"/>
+      <c r="L76" s="100"/>
+      <c r="M76" s="101"/>
       <c r="O76" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="77" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C77" s="18" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="F77" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F77" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G77" s="104"/>
-      <c r="H77" s="104"/>
-      <c r="I77" s="104"/>
-      <c r="J77" s="104"/>
-      <c r="K77" s="104"/>
-      <c r="L77" s="104"/>
-      <c r="M77" s="105"/>
+      <c r="G77" s="100"/>
+      <c r="H77" s="100"/>
+      <c r="I77" s="100"/>
+      <c r="J77" s="100"/>
+      <c r="K77" s="100"/>
+      <c r="L77" s="100"/>
+      <c r="M77" s="101"/>
       <c r="O77" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="78" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C78" s="18" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="F78" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F78" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G78" s="104"/>
-      <c r="H78" s="104"/>
-      <c r="I78" s="104"/>
-      <c r="J78" s="104"/>
-      <c r="K78" s="104"/>
-      <c r="L78" s="104"/>
-      <c r="M78" s="105"/>
+      <c r="G78" s="100"/>
+      <c r="H78" s="100"/>
+      <c r="I78" s="100"/>
+      <c r="J78" s="100"/>
+      <c r="K78" s="100"/>
+      <c r="L78" s="100"/>
+      <c r="M78" s="101"/>
       <c r="O78" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="79" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C79" s="18" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="7"/>
@@ -8090,6 +8142,61 @@
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="K22:M22"/>
     <mergeCell ref="F73:M73"/>
     <mergeCell ref="F56:I56"/>
     <mergeCell ref="F78:M78"/>
@@ -8106,61 +8213,6 @@
     <mergeCell ref="F72:M72"/>
     <mergeCell ref="F71:M71"/>
     <mergeCell ref="F70:M70"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="J43:L43"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8172,12 +8224,12 @@
   <dimension ref="B2:N63"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="5.875" style="79" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="79" customWidth="1"/>
-    <col min="4" max="4" width="5" style="79" customWidth="1"/>
-    <col min="5" max="5" width="26.75" style="79" customWidth="1"/>
-    <col min="6" max="13" width="4.75" style="79" customWidth="1"/>
-    <col min="14" max="14" width="22.5" style="79" customWidth="1"/>
+    <col min="2" max="2" width="5.875" style="75" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="75" customWidth="1"/>
+    <col min="4" max="4" width="5" style="75" customWidth="1"/>
+    <col min="5" max="5" width="26.75" style="75" customWidth="1"/>
+    <col min="6" max="13" width="4.75" style="75" customWidth="1"/>
+    <col min="14" max="14" width="22.5" style="75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.15">
@@ -8269,14 +8321,14 @@
       <c r="E11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="125"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="105"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="101"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="18" t="s">
@@ -8288,16 +8340,16 @@
       <c r="E12" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="109" t="s">
+      <c r="F12" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="105"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="101"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -8309,16 +8361,16 @@
       <c r="E13" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="109" t="s">
+      <c r="F13" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="105"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="101"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -8330,16 +8382,16 @@
       <c r="E14" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="109" t="s">
+      <c r="F14" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="105"/>
+      <c r="G14" s="100"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="100"/>
+      <c r="K14" s="100"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="101"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -8384,16 +8436,16 @@
       <c r="E16" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="127" t="s">
+      <c r="F16" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="104"/>
-      <c r="M16" s="105"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="100"/>
+      <c r="K16" s="100"/>
+      <c r="L16" s="100"/>
+      <c r="M16" s="101"/>
       <c r="N16" s="56" t="s">
         <v>38</v>
       </c>
@@ -8408,16 +8460,16 @@
       <c r="E17" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="127" t="s">
+      <c r="F17" s="123" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="104"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="104"/>
-      <c r="M17" s="105"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="101"/>
       <c r="N17" s="56" t="s">
         <v>38</v>
       </c>
@@ -8445,8 +8497,8 @@
       <c r="J18" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="125"/>
-      <c r="L18" s="105"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="101"/>
       <c r="M18" s="54" t="s">
         <v>47</v>
       </c>
@@ -8468,8 +8520,8 @@
       <c r="G19" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="125"/>
-      <c r="I19" s="105"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="101"/>
       <c r="J19" s="55" t="s">
         <v>52</v>
       </c>
@@ -8491,16 +8543,16 @@
         <v>19</v>
       </c>
       <c r="E20" s="42"/>
-      <c r="F20" s="126" t="s">
+      <c r="F20" s="122" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="105"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="101"/>
       <c r="N20" t="s">
         <v>58</v>
       </c>
@@ -8513,16 +8565,16 @@
         <v>19</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="126" t="s">
+      <c r="F21" s="122" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="104"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="105"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="101"/>
       <c r="N21" t="s">
         <v>61</v>
       </c>
@@ -8535,16 +8587,16 @@
         <v>19</v>
       </c>
       <c r="E22" s="41"/>
-      <c r="F22" s="126" t="s">
+      <c r="F22" s="122" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="104"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="105"/>
+      <c r="G22" s="100"/>
+      <c r="H22" s="100"/>
+      <c r="I22" s="100"/>
+      <c r="J22" s="100"/>
+      <c r="K22" s="100"/>
+      <c r="L22" s="100"/>
+      <c r="M22" s="101"/>
       <c r="N22" t="s">
         <v>64</v>
       </c>
@@ -8557,16 +8609,16 @@
         <v>19</v>
       </c>
       <c r="E23" s="41"/>
-      <c r="F23" s="126" t="s">
+      <c r="F23" s="122" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="104"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="105"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="101"/>
       <c r="N23" t="s">
         <v>67</v>
       </c>
@@ -8581,16 +8633,16 @@
       <c r="E24" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="127" t="s">
+      <c r="F24" s="123" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="105"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="101"/>
       <c r="N24" s="58" t="s">
         <v>38</v>
       </c>
@@ -8605,16 +8657,16 @@
       <c r="E25" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="125"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="127" t="s">
+      <c r="F25" s="121"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="100"/>
+      <c r="J25" s="101"/>
+      <c r="K25" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="L25" s="104"/>
-      <c r="M25" s="105"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="101"/>
       <c r="N25" s="56" t="s">
         <v>38</v>
       </c>
@@ -8627,16 +8679,16 @@
         <v>3</v>
       </c>
       <c r="E26" s="41"/>
-      <c r="F26" s="126" t="s">
+      <c r="F26" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="104"/>
-      <c r="H26" s="104"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="104"/>
-      <c r="L26" s="104"/>
-      <c r="M26" s="105"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="101"/>
       <c r="N26" t="s">
         <v>74</v>
       </c>
@@ -8649,16 +8701,16 @@
         <v>19</v>
       </c>
       <c r="E27" s="41"/>
-      <c r="F27" s="126" t="s">
+      <c r="F27" s="122" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="104"/>
-      <c r="H27" s="104"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="104"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="105"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="100"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="100"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="101"/>
       <c r="N27" t="s">
         <v>77</v>
       </c>
@@ -8671,16 +8723,16 @@
         <v>19</v>
       </c>
       <c r="E28" s="41"/>
-      <c r="F28" s="126" t="s">
+      <c r="F28" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="105"/>
+      <c r="G28" s="100"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="100"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="100"/>
+      <c r="L28" s="100"/>
+      <c r="M28" s="101"/>
       <c r="N28" t="s">
         <v>80</v>
       </c>
@@ -8693,16 +8745,16 @@
         <v>19</v>
       </c>
       <c r="E29" s="41"/>
-      <c r="F29" s="126" t="s">
+      <c r="F29" s="122" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="104"/>
-      <c r="H29" s="104"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="105"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="100"/>
+      <c r="I29" s="100"/>
+      <c r="J29" s="100"/>
+      <c r="K29" s="100"/>
+      <c r="L29" s="100"/>
+      <c r="M29" s="101"/>
       <c r="N29" t="s">
         <v>83</v>
       </c>
@@ -8717,14 +8769,14 @@
       <c r="E30" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="125"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="105"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="100"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="100"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="100"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="101"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="59" t="s">
@@ -8736,14 +8788,14 @@
       <c r="E31" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="125"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="105"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="100"/>
+      <c r="J31" s="100"/>
+      <c r="K31" s="100"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="101"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="59" t="s">
@@ -8755,16 +8807,16 @@
       <c r="E32" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="127" t="s">
+      <c r="F32" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="104"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="105"/>
+      <c r="G32" s="100"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="100"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="100"/>
+      <c r="M32" s="101"/>
       <c r="N32" s="56" t="s">
         <v>38</v>
       </c>
@@ -8779,16 +8831,16 @@
       <c r="E33" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="127" t="s">
+      <c r="F33" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="105"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="105"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="121"/>
+      <c r="I33" s="100"/>
+      <c r="J33" s="100"/>
+      <c r="K33" s="100"/>
+      <c r="L33" s="100"/>
+      <c r="M33" s="101"/>
       <c r="N33" s="56" t="s">
         <v>38</v>
       </c>
@@ -8803,16 +8855,16 @@
       <c r="E34" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="125"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="104"/>
-      <c r="I34" s="104"/>
-      <c r="J34" s="105"/>
-      <c r="K34" s="127" t="s">
+      <c r="F34" s="121"/>
+      <c r="G34" s="100"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="123" t="s">
         <v>91</v>
       </c>
-      <c r="L34" s="104"/>
-      <c r="M34" s="105"/>
+      <c r="L34" s="100"/>
+      <c r="M34" s="101"/>
       <c r="N34" s="56" t="s">
         <v>38</v>
       </c>
@@ -8827,16 +8879,16 @@
       <c r="E35" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="125"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="104"/>
-      <c r="I35" s="105"/>
-      <c r="J35" s="127" t="s">
+      <c r="F35" s="121"/>
+      <c r="G35" s="100"/>
+      <c r="H35" s="100"/>
+      <c r="I35" s="101"/>
+      <c r="J35" s="123" t="s">
         <v>93</v>
       </c>
-      <c r="K35" s="104"/>
-      <c r="L35" s="104"/>
-      <c r="M35" s="105"/>
+      <c r="K35" s="100"/>
+      <c r="L35" s="100"/>
+      <c r="M35" s="101"/>
       <c r="N35" s="56" t="s">
         <v>38</v>
       </c>
@@ -8851,16 +8903,16 @@
       <c r="E36" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="125"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="104"/>
-      <c r="I36" s="105"/>
-      <c r="J36" s="127" t="s">
+      <c r="F36" s="121"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="101"/>
+      <c r="J36" s="123" t="s">
         <v>95</v>
       </c>
-      <c r="K36" s="104"/>
-      <c r="L36" s="104"/>
-      <c r="M36" s="105"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="101"/>
       <c r="N36" s="56" t="s">
         <v>38</v>
       </c>
@@ -8875,16 +8927,16 @@
       <c r="E37" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="127" t="s">
+      <c r="F37" s="123" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="104"/>
-      <c r="H37" s="104"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="105"/>
+      <c r="G37" s="100"/>
+      <c r="H37" s="100"/>
+      <c r="I37" s="100"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="100"/>
+      <c r="L37" s="100"/>
+      <c r="M37" s="101"/>
       <c r="N37" s="56" t="s">
         <v>38</v>
       </c>
@@ -8899,14 +8951,14 @@
       <c r="E38" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="125"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="105"/>
+      <c r="F38" s="121"/>
+      <c r="G38" s="100"/>
+      <c r="H38" s="100"/>
+      <c r="I38" s="100"/>
+      <c r="J38" s="100"/>
+      <c r="K38" s="100"/>
+      <c r="L38" s="100"/>
+      <c r="M38" s="101"/>
       <c r="N38" t="s">
         <v>99</v>
       </c>
@@ -8921,14 +8973,14 @@
       <c r="E39" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="125"/>
-      <c r="G39" s="104"/>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="104"/>
-      <c r="K39" s="104"/>
-      <c r="L39" s="104"/>
-      <c r="M39" s="105"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="100"/>
+      <c r="H39" s="100"/>
+      <c r="I39" s="100"/>
+      <c r="J39" s="100"/>
+      <c r="K39" s="100"/>
+      <c r="L39" s="100"/>
+      <c r="M39" s="101"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="59" t="s">
@@ -8940,14 +8992,14 @@
       <c r="E40" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F40" s="125"/>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="105"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="100"/>
+      <c r="H40" s="100"/>
+      <c r="I40" s="100"/>
+      <c r="J40" s="100"/>
+      <c r="K40" s="100"/>
+      <c r="L40" s="100"/>
+      <c r="M40" s="101"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="59" t="s">
@@ -8959,14 +9011,14 @@
       <c r="E41" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F41" s="125"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="104"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="104"/>
-      <c r="K41" s="104"/>
-      <c r="L41" s="104"/>
-      <c r="M41" s="105"/>
+      <c r="F41" s="121"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="100"/>
+      <c r="K41" s="100"/>
+      <c r="L41" s="100"/>
+      <c r="M41" s="101"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="59" t="s">
@@ -8978,14 +9030,14 @@
       <c r="E42" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F42" s="125"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="104"/>
-      <c r="L42" s="104"/>
-      <c r="M42" s="105"/>
+      <c r="F42" s="121"/>
+      <c r="G42" s="100"/>
+      <c r="H42" s="100"/>
+      <c r="I42" s="100"/>
+      <c r="J42" s="100"/>
+      <c r="K42" s="100"/>
+      <c r="L42" s="100"/>
+      <c r="M42" s="101"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="19" t="s">
@@ -9007,12 +9059,12 @@
       <c r="I43" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="109" t="s">
+      <c r="J43" s="110" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="104"/>
-      <c r="L43" s="104"/>
-      <c r="M43" s="105"/>
+      <c r="K43" s="100"/>
+      <c r="L43" s="100"/>
+      <c r="M43" s="101"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
@@ -9022,18 +9074,18 @@
         <v>19</v>
       </c>
       <c r="E44" s="42"/>
-      <c r="F44" s="109" t="s">
+      <c r="F44" s="110" t="s">
         <v>111</v>
       </c>
-      <c r="G44" s="105"/>
-      <c r="H44" s="109" t="s">
+      <c r="G44" s="101"/>
+      <c r="H44" s="110" t="s">
         <v>112</v>
       </c>
-      <c r="I44" s="104"/>
-      <c r="J44" s="104"/>
-      <c r="K44" s="104"/>
-      <c r="L44" s="104"/>
-      <c r="M44" s="105"/>
+      <c r="I44" s="100"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="100"/>
+      <c r="M44" s="101"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
@@ -9043,18 +9095,18 @@
         <v>19</v>
       </c>
       <c r="E45" s="42"/>
-      <c r="F45" s="128" t="s">
+      <c r="F45" s="125" t="s">
         <v>114</v>
       </c>
-      <c r="G45" s="129"/>
-      <c r="H45" s="129"/>
-      <c r="I45" s="130"/>
-      <c r="J45" s="109" t="s">
+      <c r="G45" s="126"/>
+      <c r="H45" s="126"/>
+      <c r="I45" s="127"/>
+      <c r="J45" s="110" t="s">
         <v>115</v>
       </c>
-      <c r="K45" s="104"/>
-      <c r="L45" s="104"/>
-      <c r="M45" s="105"/>
+      <c r="K45" s="100"/>
+      <c r="L45" s="100"/>
+      <c r="M45" s="101"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
@@ -9064,18 +9116,18 @@
         <v>19</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="109" t="s">
+      <c r="F46" s="110" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="104"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="105"/>
-      <c r="J46" s="131" t="s">
+      <c r="G46" s="100"/>
+      <c r="H46" s="100"/>
+      <c r="I46" s="101"/>
+      <c r="J46" s="124" t="s">
         <v>118</v>
       </c>
-      <c r="K46" s="123"/>
-      <c r="L46" s="123"/>
-      <c r="M46" s="124"/>
+      <c r="K46" s="119"/>
+      <c r="L46" s="119"/>
+      <c r="M46" s="120"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18" t="s">
@@ -9085,16 +9137,16 @@
         <v>19</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="106" t="s">
+      <c r="F47" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="104"/>
-      <c r="L47" s="104"/>
-      <c r="M47" s="105"/>
+      <c r="G47" s="100"/>
+      <c r="H47" s="100"/>
+      <c r="I47" s="100"/>
+      <c r="J47" s="100"/>
+      <c r="K47" s="100"/>
+      <c r="L47" s="100"/>
+      <c r="M47" s="101"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
@@ -9104,20 +9156,20 @@
         <v>19</v>
       </c>
       <c r="E48" s="5"/>
-      <c r="F48" s="110"/>
-      <c r="G48" s="105"/>
+      <c r="F48" s="109"/>
+      <c r="G48" s="101"/>
       <c r="H48" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I48" s="106" t="s">
+      <c r="I48" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="J48" s="104"/>
-      <c r="K48" s="105"/>
-      <c r="L48" s="106" t="s">
+      <c r="J48" s="100"/>
+      <c r="K48" s="101"/>
+      <c r="L48" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="M48" s="105"/>
+      <c r="M48" s="101"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
@@ -9160,15 +9212,15 @@
         <v>19</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="110"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="104"/>
-      <c r="I50" s="105"/>
-      <c r="J50" s="106" t="s">
+      <c r="F50" s="109"/>
+      <c r="G50" s="100"/>
+      <c r="H50" s="100"/>
+      <c r="I50" s="101"/>
+      <c r="J50" s="99" t="s">
         <v>133</v>
       </c>
-      <c r="K50" s="104"/>
-      <c r="L50" s="105"/>
+      <c r="K50" s="100"/>
+      <c r="L50" s="101"/>
       <c r="M50" s="12" t="s">
         <v>134</v>
       </c>
@@ -9183,16 +9235,16 @@
       <c r="E51" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F51" s="125"/>
-      <c r="G51" s="104"/>
-      <c r="H51" s="104"/>
-      <c r="I51" s="104"/>
-      <c r="J51" s="104"/>
-      <c r="K51" s="105"/>
-      <c r="L51" s="113" t="s">
+      <c r="F51" s="121"/>
+      <c r="G51" s="100"/>
+      <c r="H51" s="100"/>
+      <c r="I51" s="100"/>
+      <c r="J51" s="100"/>
+      <c r="K51" s="101"/>
+      <c r="L51" s="114" t="s">
         <v>137</v>
       </c>
-      <c r="M51" s="105"/>
+      <c r="M51" s="101"/>
     </row>
     <row r="52" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -9204,16 +9256,16 @@
       <c r="E52" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F52" s="113" t="s">
+      <c r="F52" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="104"/>
-      <c r="H52" s="104"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="104"/>
-      <c r="K52" s="104"/>
-      <c r="L52" s="104"/>
-      <c r="M52" s="105"/>
+      <c r="G52" s="100"/>
+      <c r="H52" s="100"/>
+      <c r="I52" s="100"/>
+      <c r="J52" s="100"/>
+      <c r="K52" s="100"/>
+      <c r="L52" s="100"/>
+      <c r="M52" s="101"/>
       <c r="N52" t="s">
         <v>141</v>
       </c>
@@ -9228,16 +9280,16 @@
       <c r="E53" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F53" s="113" t="s">
+      <c r="F53" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="104"/>
-      <c r="J53" s="104"/>
-      <c r="K53" s="104"/>
-      <c r="L53" s="104"/>
-      <c r="M53" s="105"/>
+      <c r="G53" s="100"/>
+      <c r="H53" s="100"/>
+      <c r="I53" s="100"/>
+      <c r="J53" s="100"/>
+      <c r="K53" s="100"/>
+      <c r="L53" s="100"/>
+      <c r="M53" s="101"/>
       <c r="N53" t="s">
         <v>141</v>
       </c>
@@ -9252,16 +9304,16 @@
       <c r="E54" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F54" s="113" t="s">
+      <c r="F54" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="104"/>
-      <c r="J54" s="104"/>
-      <c r="K54" s="104"/>
-      <c r="L54" s="104"/>
-      <c r="M54" s="105"/>
+      <c r="G54" s="100"/>
+      <c r="H54" s="100"/>
+      <c r="I54" s="100"/>
+      <c r="J54" s="100"/>
+      <c r="K54" s="100"/>
+      <c r="L54" s="100"/>
+      <c r="M54" s="101"/>
       <c r="N54" t="s">
         <v>141</v>
       </c>
@@ -9276,16 +9328,16 @@
       <c r="E55" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="113" t="s">
+      <c r="F55" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="104"/>
-      <c r="J55" s="104"/>
-      <c r="K55" s="104"/>
-      <c r="L55" s="104"/>
-      <c r="M55" s="105"/>
+      <c r="G55" s="100"/>
+      <c r="H55" s="100"/>
+      <c r="I55" s="100"/>
+      <c r="J55" s="100"/>
+      <c r="K55" s="100"/>
+      <c r="L55" s="100"/>
+      <c r="M55" s="101"/>
       <c r="N55" t="s">
         <v>141</v>
       </c>
@@ -9300,16 +9352,16 @@
       <c r="E56" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="113" t="s">
+      <c r="F56" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="104"/>
-      <c r="J56" s="104"/>
-      <c r="K56" s="104"/>
-      <c r="L56" s="104"/>
-      <c r="M56" s="105"/>
+      <c r="G56" s="100"/>
+      <c r="H56" s="100"/>
+      <c r="I56" s="100"/>
+      <c r="J56" s="100"/>
+      <c r="K56" s="100"/>
+      <c r="L56" s="100"/>
+      <c r="M56" s="101"/>
       <c r="N56" t="s">
         <v>141</v>
       </c>
@@ -9324,16 +9376,16 @@
       <c r="E57" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F57" s="113" t="s">
+      <c r="F57" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="104"/>
-      <c r="J57" s="104"/>
-      <c r="K57" s="104"/>
-      <c r="L57" s="104"/>
-      <c r="M57" s="105"/>
+      <c r="G57" s="100"/>
+      <c r="H57" s="100"/>
+      <c r="I57" s="100"/>
+      <c r="J57" s="100"/>
+      <c r="K57" s="100"/>
+      <c r="L57" s="100"/>
+      <c r="M57" s="101"/>
       <c r="N57" t="s">
         <v>141</v>
       </c>
@@ -9348,16 +9400,16 @@
       <c r="E58" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F58" s="113" t="s">
+      <c r="F58" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="104"/>
-      <c r="H58" s="104"/>
-      <c r="I58" s="104"/>
-      <c r="J58" s="104"/>
-      <c r="K58" s="104"/>
-      <c r="L58" s="104"/>
-      <c r="M58" s="105"/>
+      <c r="G58" s="100"/>
+      <c r="H58" s="100"/>
+      <c r="I58" s="100"/>
+      <c r="J58" s="100"/>
+      <c r="K58" s="100"/>
+      <c r="L58" s="100"/>
+      <c r="M58" s="101"/>
       <c r="N58" t="s">
         <v>141</v>
       </c>
@@ -9372,16 +9424,16 @@
       <c r="E59" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="F59" s="113" t="s">
+      <c r="F59" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G59" s="104"/>
-      <c r="H59" s="104"/>
-      <c r="I59" s="104"/>
-      <c r="J59" s="104"/>
-      <c r="K59" s="104"/>
-      <c r="L59" s="104"/>
-      <c r="M59" s="105"/>
+      <c r="G59" s="100"/>
+      <c r="H59" s="100"/>
+      <c r="I59" s="100"/>
+      <c r="J59" s="100"/>
+      <c r="K59" s="100"/>
+      <c r="L59" s="100"/>
+      <c r="M59" s="101"/>
       <c r="N59" t="s">
         <v>141</v>
       </c>
@@ -9396,16 +9448,16 @@
       <c r="E60" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F60" s="113" t="s">
+      <c r="F60" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="104"/>
-      <c r="L60" s="104"/>
-      <c r="M60" s="105"/>
+      <c r="G60" s="100"/>
+      <c r="H60" s="100"/>
+      <c r="I60" s="100"/>
+      <c r="J60" s="100"/>
+      <c r="K60" s="100"/>
+      <c r="L60" s="100"/>
+      <c r="M60" s="101"/>
       <c r="N60" t="s">
         <v>141</v>
       </c>
@@ -9420,16 +9472,16 @@
       <c r="E61" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="F61" s="113" t="s">
+      <c r="F61" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="G61" s="104"/>
-      <c r="H61" s="104"/>
-      <c r="I61" s="104"/>
-      <c r="J61" s="104"/>
-      <c r="K61" s="104"/>
-      <c r="L61" s="104"/>
-      <c r="M61" s="105"/>
+      <c r="G61" s="100"/>
+      <c r="H61" s="100"/>
+      <c r="I61" s="100"/>
+      <c r="J61" s="100"/>
+      <c r="K61" s="100"/>
+      <c r="L61" s="100"/>
+      <c r="M61" s="101"/>
       <c r="N61" t="s">
         <v>141</v>
       </c>
@@ -9457,23 +9509,51 @@
       <c r="J63" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="K63" s="110"/>
-      <c r="L63" s="105"/>
+      <c r="K63" s="109"/>
+      <c r="L63" s="101"/>
       <c r="M63" s="53" t="s">
         <v>166</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="F51:K51"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F60:M60"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F59:M59"/>
+    <mergeCell ref="F21:M21"/>
+    <mergeCell ref="F55:M55"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F20:M20"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F26:M26"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="F47:M47"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F61:M61"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F27:M27"/>
     <mergeCell ref="F11:M11"/>
     <mergeCell ref="J43:M43"/>
     <mergeCell ref="F54:M54"/>
@@ -9490,43 +9570,15 @@
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="J36:M36"/>
     <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="F47:M47"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F61:M61"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="F60:M60"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F59:M59"/>
-    <mergeCell ref="F21:M21"/>
-    <mergeCell ref="F55:M55"/>
-    <mergeCell ref="F24:M24"/>
-    <mergeCell ref="F20:M20"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F26:M26"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="F23:M23"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="F51:K51"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="F38:M38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9541,7 +9593,7 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -9551,13 +9603,143 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B4F3E6-51D7-4F53-A09C-34A858916412}">
+  <dimension ref="B2:M7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+    </row>
+    <row r="5" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="F6" s="99" t="s">
+        <v>530</v>
+      </c>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="101"/>
+    </row>
+    <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="F7" s="99" t="s">
+        <v>533</v>
+      </c>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="101"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="F7:M7"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -9566,7 +9748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35961C51-4C87-43E4-A01F-C0F08E028EB7}">
   <dimension ref="B2:W11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -9577,132 +9759,132 @@
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:23" x14ac:dyDescent="0.15">
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="76" t="s">
+        <v>395</v>
+      </c>
+      <c r="C5" s="77" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.15">
+      <c r="B6" s="78" t="s">
+        <v>397</v>
+      </c>
+      <c r="C6" s="79" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="80" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="C7" s="81" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.15">
-      <c r="B6" s="82" t="s">
-        <v>401</v>
-      </c>
-      <c r="C6" s="83" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="7" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="84" t="s">
+    <row r="8" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="82" t="s">
         <v>403</v>
       </c>
-      <c r="C7" s="85" t="s">
+      <c r="F8" s="83" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="8" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="E8" s="86" t="s">
+      <c r="G8" s="83" t="s">
+        <v>405</v>
+      </c>
+      <c r="H8" s="83" t="s">
+        <v>406</v>
+      </c>
+      <c r="I8" s="83" t="s">
         <v>407</v>
       </c>
-      <c r="F8" s="87" t="s">
+      <c r="J8" s="83" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="87" t="s">
+      <c r="K8" s="83" t="s">
         <v>409</v>
       </c>
-      <c r="H8" s="87" t="s">
+      <c r="L8" s="83" t="s">
         <v>410</v>
       </c>
-      <c r="I8" s="87" t="s">
+      <c r="M8" s="83" t="s">
         <v>411</v>
       </c>
-      <c r="J8" s="87" t="s">
+      <c r="N8" s="83" t="s">
         <v>412</v>
       </c>
-      <c r="K8" s="87" t="s">
+      <c r="O8" s="83" t="s">
         <v>413</v>
       </c>
-      <c r="L8" s="87" t="s">
+      <c r="P8" s="83" t="s">
         <v>414</v>
       </c>
-      <c r="M8" s="87" t="s">
+      <c r="Q8" s="83" t="s">
         <v>415</v>
       </c>
-      <c r="N8" s="87" t="s">
+      <c r="R8" s="83" t="s">
         <v>416</v>
       </c>
-      <c r="O8" s="87" t="s">
+      <c r="S8" s="83" t="s">
         <v>417</v>
       </c>
-      <c r="P8" s="87" t="s">
+      <c r="T8" s="83" t="s">
         <v>418</v>
       </c>
-      <c r="Q8" s="87" t="s">
+      <c r="U8" s="83" t="s">
         <v>419</v>
       </c>
-      <c r="R8" s="87" t="s">
+      <c r="V8" s="83" t="s">
         <v>420</v>
       </c>
-      <c r="S8" s="87" t="s">
+      <c r="W8" s="84" t="s">
         <v>421</v>
       </c>
-      <c r="T8" s="87" t="s">
-        <v>422</v>
-      </c>
-      <c r="U8" s="87" t="s">
+    </row>
+    <row r="9" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="128" t="s">
+        <v>424</v>
+      </c>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="128" t="s">
         <v>423</v>
       </c>
-      <c r="V8" s="87" t="s">
-        <v>424</v>
-      </c>
-      <c r="W8" s="88" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="9" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="E9" s="132" t="s">
-        <v>428</v>
-      </c>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="134"/>
-      <c r="K9" s="132" t="s">
-        <v>427</v>
-      </c>
-      <c r="L9" s="133"/>
-      <c r="M9" s="133"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="133"/>
-      <c r="P9" s="133"/>
-      <c r="Q9" s="133"/>
-      <c r="R9" s="133"/>
-      <c r="S9" s="133"/>
-      <c r="T9" s="133"/>
-      <c r="U9" s="133"/>
-      <c r="V9" s="133"/>
-      <c r="W9" s="134"/>
+      <c r="L9" s="129"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="129"/>
+      <c r="O9" s="129"/>
+      <c r="P9" s="129"/>
+      <c r="Q9" s="129"/>
+      <c r="R9" s="129"/>
+      <c r="S9" s="129"/>
+      <c r="T9" s="129"/>
+      <c r="U9" s="129"/>
+      <c r="V9" s="129"/>
+      <c r="W9" s="130"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.15">
       <c r="E11" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F11" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G11" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/doc/spec/Y8960_Specifications.xlsx
+++ b/doc/spec/Y8960_Specifications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\Y8960_Cartridge\doc\spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4649F2A9-B8E7-4B9B-B802-B24B97690E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8E1C45-CA0D-4528-B2B2-7E0094712BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3012,15 +3012,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3032,31 +3057,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3071,14 +3078,14 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3088,13 +3095,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -3739,12 +3739,12 @@
         <v>187</v>
       </c>
       <c r="G4" s="109"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="102"/>
       <c r="N4" s="66" t="s">
         <v>205</v>
       </c>
@@ -3765,16 +3765,16 @@
       <c r="F5" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G5" s="111" t="s">
+      <c r="G5" s="110" t="s">
         <v>209</v>
       </c>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100"/>
-      <c r="M5" s="100"/>
-      <c r="N5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="101"/>
+      <c r="L5" s="101"/>
+      <c r="M5" s="101"/>
+      <c r="N5" s="102"/>
       <c r="O5" s="49" t="s">
         <v>210</v>
       </c>
@@ -3792,16 +3792,16 @@
       <c r="F6" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G6" s="111" t="s">
+      <c r="G6" s="110" t="s">
         <v>209</v>
       </c>
-      <c r="H6" s="100"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="100"/>
-      <c r="L6" s="100"/>
-      <c r="M6" s="100"/>
-      <c r="N6" s="101"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="101"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="101"/>
+      <c r="M6" s="101"/>
+      <c r="N6" s="102"/>
       <c r="O6" s="49" t="s">
         <v>210</v>
       </c>
@@ -3819,16 +3819,16 @@
       <c r="F7" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="111" t="s">
+      <c r="G7" s="110" t="s">
         <v>209</v>
       </c>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="100"/>
-      <c r="N7" s="101"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="101"/>
+      <c r="L7" s="101"/>
+      <c r="M7" s="101"/>
+      <c r="N7" s="102"/>
       <c r="O7" s="49" t="s">
         <v>210</v>
       </c>
@@ -3846,16 +3846,16 @@
       <c r="F8" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G8" s="111" t="s">
+      <c r="G8" s="110" t="s">
         <v>209</v>
       </c>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="100"/>
-      <c r="L8" s="100"/>
-      <c r="M8" s="100"/>
-      <c r="N8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
+      <c r="J8" s="101"/>
+      <c r="K8" s="101"/>
+      <c r="L8" s="101"/>
+      <c r="M8" s="101"/>
+      <c r="N8" s="102"/>
       <c r="O8" s="49" t="s">
         <v>210</v>
       </c>
@@ -3873,16 +3873,16 @@
       <c r="F9" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G9" s="110" t="s">
+      <c r="G9" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="H9" s="100"/>
-      <c r="I9" s="100"/>
-      <c r="J9" s="100"/>
-      <c r="K9" s="100"/>
-      <c r="L9" s="100"/>
-      <c r="M9" s="100"/>
-      <c r="N9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="101"/>
+      <c r="L9" s="101"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="102"/>
       <c r="O9" s="49" t="s">
         <v>219</v>
       </c>
@@ -3900,16 +3900,16 @@
       <c r="F10" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G10" s="110" t="s">
+      <c r="G10" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="100"/>
-      <c r="L10" s="100"/>
-      <c r="M10" s="100"/>
-      <c r="N10" s="101"/>
+      <c r="H10" s="101"/>
+      <c r="I10" s="101"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="101"/>
+      <c r="L10" s="101"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="102"/>
       <c r="O10" s="49" t="s">
         <v>219</v>
       </c>
@@ -3927,16 +3927,16 @@
       <c r="F11" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G11" s="114" t="s">
+      <c r="G11" s="112" t="s">
         <v>222</v>
       </c>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
-      <c r="L11" s="100"/>
-      <c r="M11" s="100"/>
-      <c r="N11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="101"/>
+      <c r="N11" s="102"/>
       <c r="O11" s="50" t="s">
         <v>393</v>
       </c>
@@ -3954,16 +3954,16 @@
       <c r="F12" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="114" t="s">
+      <c r="G12" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="100"/>
-      <c r="N12" s="101"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="102"/>
       <c r="O12" s="50" t="s">
         <v>393</v>
       </c>
@@ -3981,16 +3981,16 @@
       <c r="F13" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G13" s="112" t="s">
+      <c r="G13" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="100"/>
-      <c r="M13" s="100"/>
-      <c r="N13" s="101"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="101"/>
+      <c r="J13" s="101"/>
+      <c r="K13" s="101"/>
+      <c r="L13" s="101"/>
+      <c r="M13" s="101"/>
+      <c r="N13" s="102"/>
       <c r="O13" s="50" t="s">
         <v>393</v>
       </c>
@@ -4008,16 +4008,16 @@
       <c r="F14" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G14" s="112" t="s">
+      <c r="G14" s="100" t="s">
         <v>228</v>
       </c>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="100"/>
-      <c r="K14" s="100"/>
-      <c r="L14" s="100"/>
-      <c r="M14" s="100"/>
-      <c r="N14" s="101"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="101"/>
+      <c r="N14" s="102"/>
       <c r="O14" s="50" t="s">
         <v>393</v>
       </c>
@@ -4035,16 +4035,16 @@
       <c r="F15" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G15" s="99" t="s">
+      <c r="G15" s="103" t="s">
         <v>230</v>
       </c>
-      <c r="H15" s="100"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="100"/>
-      <c r="K15" s="100"/>
-      <c r="L15" s="100"/>
-      <c r="M15" s="100"/>
-      <c r="N15" s="101"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="101"/>
+      <c r="J15" s="101"/>
+      <c r="K15" s="101"/>
+      <c r="L15" s="101"/>
+      <c r="M15" s="101"/>
+      <c r="N15" s="102"/>
       <c r="O15" s="50" t="s">
         <v>393</v>
       </c>
@@ -4062,16 +4062,16 @@
       <c r="F16" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G16" s="99" t="s">
+      <c r="G16" s="103" t="s">
         <v>233</v>
       </c>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="100"/>
-      <c r="L16" s="100"/>
-      <c r="M16" s="100"/>
-      <c r="N16" s="101"/>
+      <c r="H16" s="101"/>
+      <c r="I16" s="101"/>
+      <c r="J16" s="101"/>
+      <c r="K16" s="101"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="101"/>
+      <c r="N16" s="102"/>
       <c r="O16" s="50" t="s">
         <v>393</v>
       </c>
@@ -4089,13 +4089,13 @@
       <c r="F17" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G17" s="113"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="100"/>
-      <c r="M17" s="101"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="101"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="102"/>
       <c r="N17" s="10" t="s">
         <v>176</v>
       </c>
@@ -4116,14 +4116,14 @@
       <c r="F18" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G18" s="112"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="100"/>
-      <c r="N18" s="101"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="101"/>
+      <c r="I18" s="101"/>
+      <c r="J18" s="101"/>
+      <c r="K18" s="101"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="101"/>
+      <c r="N18" s="102"/>
       <c r="O18" s="50" t="s">
         <v>394</v>
       </c>
@@ -4141,14 +4141,14 @@
       <c r="F19" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="112"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="100"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="100"/>
-      <c r="N19" s="101"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="101"/>
+      <c r="I19" s="101"/>
+      <c r="J19" s="101"/>
+      <c r="K19" s="101"/>
+      <c r="L19" s="101"/>
+      <c r="M19" s="101"/>
+      <c r="N19" s="102"/>
       <c r="O19" s="50" t="s">
         <v>394</v>
       </c>
@@ -4166,14 +4166,14 @@
       <c r="F20" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G20" s="112"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="100"/>
-      <c r="N20" s="101"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="101"/>
+      <c r="J20" s="101"/>
+      <c r="K20" s="101"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="101"/>
+      <c r="N20" s="102"/>
       <c r="O20" s="50" t="s">
         <v>394</v>
       </c>
@@ -4216,16 +4216,16 @@
       <c r="F22" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G22" s="99" t="s">
+      <c r="G22" s="103" t="s">
         <v>530</v>
       </c>
-      <c r="H22" s="100"/>
-      <c r="I22" s="100"/>
-      <c r="J22" s="100"/>
-      <c r="K22" s="100"/>
-      <c r="L22" s="100"/>
-      <c r="M22" s="100"/>
-      <c r="N22" s="101"/>
+      <c r="H22" s="101"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="101"/>
+      <c r="K22" s="101"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="101"/>
+      <c r="N22" s="102"/>
       <c r="O22" s="50" t="s">
         <v>534</v>
       </c>
@@ -4243,16 +4243,16 @@
       <c r="F23" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="G23" s="99" t="s">
+      <c r="G23" s="103" t="s">
         <v>533</v>
       </c>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="100"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="100"/>
-      <c r="N23" s="101"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="101"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="101"/>
+      <c r="N23" s="102"/>
       <c r="O23" s="50" t="s">
         <v>534</v>
       </c>
@@ -4311,8 +4311,8 @@
       <c r="C26" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>19</v>
+      <c r="D26" s="62" t="s">
+        <v>426</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>249</v>
@@ -4323,11 +4323,11 @@
       <c r="G26" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="H26" s="131"/>
-      <c r="I26" s="132"/>
-      <c r="J26" s="132"/>
-      <c r="K26" s="132"/>
-      <c r="L26" s="133" t="s">
+      <c r="H26" s="106"/>
+      <c r="I26" s="107"/>
+      <c r="J26" s="107"/>
+      <c r="K26" s="107"/>
+      <c r="L26" s="99" t="s">
         <v>541</v>
       </c>
       <c r="M26" s="32" t="s">
@@ -4353,16 +4353,16 @@
       <c r="F27" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="110" t="s">
+      <c r="G27" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="100"/>
-      <c r="N27" s="101"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="101"/>
+      <c r="N27" s="102"/>
       <c r="O27" s="49" t="s">
         <v>219</v>
       </c>
@@ -4380,16 +4380,16 @@
       <c r="F28" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="110" t="s">
+      <c r="G28" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="100"/>
-      <c r="M28" s="100"/>
-      <c r="N28" s="101"/>
+      <c r="H28" s="101"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="101"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="101"/>
+      <c r="N28" s="102"/>
       <c r="O28" s="49" t="s">
         <v>219</v>
       </c>
@@ -4412,16 +4412,16 @@
       <c r="F31" s="97" t="s">
         <v>514</v>
       </c>
-      <c r="G31" s="104" t="s">
+      <c r="G31" s="113" t="s">
         <v>494</v>
       </c>
-      <c r="H31" s="105"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="105"/>
-      <c r="K31" s="105"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="105"/>
-      <c r="N31" s="105"/>
+      <c r="H31" s="114"/>
+      <c r="I31" s="114"/>
+      <c r="J31" s="114"/>
+      <c r="K31" s="114"/>
+      <c r="L31" s="114"/>
+      <c r="M31" s="114"/>
+      <c r="N31" s="114"/>
       <c r="O31" s="77" t="s">
         <v>516</v>
       </c>
@@ -4439,16 +4439,16 @@
       <c r="F32" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="G32" s="102" t="s">
+      <c r="G32" s="104" t="s">
         <v>494</v>
       </c>
-      <c r="H32" s="103"/>
-      <c r="I32" s="103"/>
-      <c r="J32" s="103"/>
-      <c r="K32" s="103"/>
-      <c r="L32" s="103"/>
-      <c r="M32" s="103"/>
-      <c r="N32" s="103"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="105"/>
+      <c r="K32" s="105"/>
+      <c r="L32" s="105"/>
+      <c r="M32" s="105"/>
+      <c r="N32" s="105"/>
       <c r="O32" s="79" t="s">
         <v>523</v>
       </c>
@@ -4466,16 +4466,16 @@
       <c r="F33" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="G33" s="102" t="s">
+      <c r="G33" s="104" t="s">
         <v>218</v>
       </c>
-      <c r="H33" s="103"/>
-      <c r="I33" s="103"/>
-      <c r="J33" s="103"/>
-      <c r="K33" s="103"/>
-      <c r="L33" s="103"/>
-      <c r="M33" s="103"/>
-      <c r="N33" s="103"/>
+      <c r="H33" s="105"/>
+      <c r="I33" s="105"/>
+      <c r="J33" s="105"/>
+      <c r="K33" s="105"/>
+      <c r="L33" s="105"/>
+      <c r="M33" s="105"/>
+      <c r="N33" s="105"/>
       <c r="O33" s="79" t="s">
         <v>219</v>
       </c>
@@ -4493,16 +4493,16 @@
       <c r="F34" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G34" s="102" t="s">
+      <c r="G34" s="104" t="s">
         <v>502</v>
       </c>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="103"/>
-      <c r="K34" s="103"/>
-      <c r="L34" s="103"/>
-      <c r="M34" s="103"/>
-      <c r="N34" s="103"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="105"/>
+      <c r="L34" s="105"/>
+      <c r="M34" s="105"/>
+      <c r="N34" s="105"/>
       <c r="O34" s="79"/>
     </row>
     <row r="35" spans="3:15" x14ac:dyDescent="0.15">
@@ -4518,16 +4518,16 @@
       <c r="F35" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G35" s="102" t="s">
+      <c r="G35" s="104" t="s">
         <v>503</v>
       </c>
-      <c r="H35" s="103"/>
-      <c r="I35" s="103"/>
-      <c r="J35" s="103"/>
-      <c r="K35" s="103"/>
-      <c r="L35" s="103"/>
-      <c r="M35" s="103"/>
-      <c r="N35" s="103"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="105"/>
+      <c r="K35" s="105"/>
+      <c r="L35" s="105"/>
+      <c r="M35" s="105"/>
+      <c r="N35" s="105"/>
       <c r="O35" s="79"/>
     </row>
     <row r="36" spans="3:15" x14ac:dyDescent="0.15">
@@ -4543,16 +4543,16 @@
       <c r="F36" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G36" s="102" t="s">
+      <c r="G36" s="104" t="s">
         <v>504</v>
       </c>
-      <c r="H36" s="103"/>
-      <c r="I36" s="103"/>
-      <c r="J36" s="103"/>
-      <c r="K36" s="103"/>
-      <c r="L36" s="103"/>
-      <c r="M36" s="103"/>
-      <c r="N36" s="103"/>
+      <c r="H36" s="105"/>
+      <c r="I36" s="105"/>
+      <c r="J36" s="105"/>
+      <c r="K36" s="105"/>
+      <c r="L36" s="105"/>
+      <c r="M36" s="105"/>
+      <c r="N36" s="105"/>
       <c r="O36" s="79"/>
     </row>
     <row r="37" spans="3:15" x14ac:dyDescent="0.15">
@@ -4568,16 +4568,16 @@
       <c r="F37" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G37" s="102" t="s">
+      <c r="G37" s="104" t="s">
         <v>505</v>
       </c>
-      <c r="H37" s="103"/>
-      <c r="I37" s="103"/>
-      <c r="J37" s="103"/>
-      <c r="K37" s="103"/>
-      <c r="L37" s="103"/>
-      <c r="M37" s="103"/>
-      <c r="N37" s="103"/>
+      <c r="H37" s="105"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="105"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="105"/>
+      <c r="N37" s="105"/>
       <c r="O37" s="79"/>
     </row>
     <row r="38" spans="3:15" x14ac:dyDescent="0.15">
@@ -4593,16 +4593,16 @@
       <c r="F38" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G38" s="102" t="s">
+      <c r="G38" s="104" t="s">
         <v>506</v>
       </c>
-      <c r="H38" s="103"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="103"/>
-      <c r="K38" s="103"/>
-      <c r="L38" s="103"/>
-      <c r="M38" s="103"/>
-      <c r="N38" s="103"/>
+      <c r="H38" s="105"/>
+      <c r="I38" s="105"/>
+      <c r="J38" s="105"/>
+      <c r="K38" s="105"/>
+      <c r="L38" s="105"/>
+      <c r="M38" s="105"/>
+      <c r="N38" s="105"/>
       <c r="O38" s="79" t="s">
         <v>516</v>
       </c>
@@ -4620,16 +4620,16 @@
       <c r="F39" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G39" s="102" t="s">
+      <c r="G39" s="104" t="s">
         <v>507</v>
       </c>
-      <c r="H39" s="103"/>
-      <c r="I39" s="103"/>
-      <c r="J39" s="103"/>
-      <c r="K39" s="103"/>
-      <c r="L39" s="103"/>
-      <c r="M39" s="103"/>
-      <c r="N39" s="103"/>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+      <c r="J39" s="105"/>
+      <c r="K39" s="105"/>
+      <c r="L39" s="105"/>
+      <c r="M39" s="105"/>
+      <c r="N39" s="105"/>
       <c r="O39" s="79" t="s">
         <v>516</v>
       </c>
@@ -4647,16 +4647,16 @@
       <c r="F40" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G40" s="102" t="s">
+      <c r="G40" s="104" t="s">
         <v>508</v>
       </c>
-      <c r="H40" s="103"/>
-      <c r="I40" s="103"/>
-      <c r="J40" s="103"/>
-      <c r="K40" s="103"/>
-      <c r="L40" s="103"/>
-      <c r="M40" s="103"/>
-      <c r="N40" s="103"/>
+      <c r="H40" s="105"/>
+      <c r="I40" s="105"/>
+      <c r="J40" s="105"/>
+      <c r="K40" s="105"/>
+      <c r="L40" s="105"/>
+      <c r="M40" s="105"/>
+      <c r="N40" s="105"/>
       <c r="O40" s="79" t="s">
         <v>516</v>
       </c>
@@ -4674,16 +4674,16 @@
       <c r="F41" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G41" s="102" t="s">
+      <c r="G41" s="104" t="s">
         <v>509</v>
       </c>
-      <c r="H41" s="103"/>
-      <c r="I41" s="103"/>
-      <c r="J41" s="103"/>
-      <c r="K41" s="103"/>
-      <c r="L41" s="103"/>
-      <c r="M41" s="103"/>
-      <c r="N41" s="103"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="105"/>
+      <c r="N41" s="105"/>
       <c r="O41" s="79" t="s">
         <v>516</v>
       </c>
@@ -4701,16 +4701,16 @@
       <c r="F42" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G42" s="102" t="s">
+      <c r="G42" s="104" t="s">
         <v>510</v>
       </c>
-      <c r="H42" s="103"/>
-      <c r="I42" s="103"/>
-      <c r="J42" s="103"/>
-      <c r="K42" s="103"/>
-      <c r="L42" s="103"/>
-      <c r="M42" s="103"/>
-      <c r="N42" s="103"/>
+      <c r="H42" s="105"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="105"/>
+      <c r="K42" s="105"/>
+      <c r="L42" s="105"/>
+      <c r="M42" s="105"/>
+      <c r="N42" s="105"/>
       <c r="O42" s="79" t="s">
         <v>516</v>
       </c>
@@ -4728,16 +4728,16 @@
       <c r="F43" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G43" s="102" t="s">
+      <c r="G43" s="104" t="s">
         <v>497</v>
       </c>
-      <c r="H43" s="103"/>
-      <c r="I43" s="103"/>
-      <c r="J43" s="103"/>
-      <c r="K43" s="103"/>
-      <c r="L43" s="103"/>
-      <c r="M43" s="103"/>
-      <c r="N43" s="103"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="105"/>
+      <c r="K43" s="105"/>
+      <c r="L43" s="105"/>
+      <c r="M43" s="105"/>
+      <c r="N43" s="105"/>
       <c r="O43" s="79" t="s">
         <v>516</v>
       </c>
@@ -4755,16 +4755,16 @@
       <c r="F44" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G44" s="102" t="s">
+      <c r="G44" s="104" t="s">
         <v>498</v>
       </c>
-      <c r="H44" s="103"/>
-      <c r="I44" s="103"/>
-      <c r="J44" s="103"/>
-      <c r="K44" s="103"/>
-      <c r="L44" s="103"/>
-      <c r="M44" s="103"/>
-      <c r="N44" s="103"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="105"/>
+      <c r="K44" s="105"/>
+      <c r="L44" s="105"/>
+      <c r="M44" s="105"/>
+      <c r="N44" s="105"/>
       <c r="O44" s="79" t="s">
         <v>516</v>
       </c>
@@ -4782,16 +4782,16 @@
       <c r="F45" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G45" s="102" t="s">
+      <c r="G45" s="104" t="s">
         <v>499</v>
       </c>
-      <c r="H45" s="103"/>
-      <c r="I45" s="103"/>
-      <c r="J45" s="103"/>
-      <c r="K45" s="103"/>
-      <c r="L45" s="103"/>
-      <c r="M45" s="103"/>
-      <c r="N45" s="103"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="105"/>
+      <c r="K45" s="105"/>
+      <c r="L45" s="105"/>
+      <c r="M45" s="105"/>
+      <c r="N45" s="105"/>
       <c r="O45" s="79" t="s">
         <v>516</v>
       </c>
@@ -4809,16 +4809,16 @@
       <c r="F46" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G46" s="102" t="s">
+      <c r="G46" s="104" t="s">
         <v>500</v>
       </c>
-      <c r="H46" s="103"/>
-      <c r="I46" s="103"/>
-      <c r="J46" s="103"/>
-      <c r="K46" s="103"/>
-      <c r="L46" s="103"/>
-      <c r="M46" s="103"/>
-      <c r="N46" s="103"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="105"/>
+      <c r="K46" s="105"/>
+      <c r="L46" s="105"/>
+      <c r="M46" s="105"/>
+      <c r="N46" s="105"/>
       <c r="O46" s="79" t="s">
         <v>516</v>
       </c>
@@ -4836,16 +4836,16 @@
       <c r="F47" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G47" s="102" t="s">
+      <c r="G47" s="104" t="s">
         <v>501</v>
       </c>
-      <c r="H47" s="103"/>
-      <c r="I47" s="103"/>
-      <c r="J47" s="103"/>
-      <c r="K47" s="103"/>
-      <c r="L47" s="103"/>
-      <c r="M47" s="103"/>
-      <c r="N47" s="103"/>
+      <c r="H47" s="105"/>
+      <c r="I47" s="105"/>
+      <c r="J47" s="105"/>
+      <c r="K47" s="105"/>
+      <c r="L47" s="105"/>
+      <c r="M47" s="105"/>
+      <c r="N47" s="105"/>
       <c r="O47" s="79" t="s">
         <v>516</v>
       </c>
@@ -4863,16 +4863,16 @@
       <c r="F48" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G48" s="102" t="s">
+      <c r="G48" s="104" t="s">
         <v>496</v>
       </c>
-      <c r="H48" s="103"/>
-      <c r="I48" s="103"/>
-      <c r="J48" s="103"/>
-      <c r="K48" s="103"/>
-      <c r="L48" s="103"/>
-      <c r="M48" s="103"/>
-      <c r="N48" s="103"/>
+      <c r="H48" s="105"/>
+      <c r="I48" s="105"/>
+      <c r="J48" s="105"/>
+      <c r="K48" s="105"/>
+      <c r="L48" s="105"/>
+      <c r="M48" s="105"/>
+      <c r="N48" s="105"/>
       <c r="O48" s="79" t="s">
         <v>516</v>
       </c>
@@ -4890,16 +4890,16 @@
       <c r="F49" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G49" s="102" t="s">
+      <c r="G49" s="104" t="s">
         <v>493</v>
       </c>
-      <c r="H49" s="103"/>
-      <c r="I49" s="103"/>
-      <c r="J49" s="103"/>
-      <c r="K49" s="103"/>
-      <c r="L49" s="103"/>
-      <c r="M49" s="103"/>
-      <c r="N49" s="103"/>
+      <c r="H49" s="105"/>
+      <c r="I49" s="105"/>
+      <c r="J49" s="105"/>
+      <c r="K49" s="105"/>
+      <c r="L49" s="105"/>
+      <c r="M49" s="105"/>
+      <c r="N49" s="105"/>
       <c r="O49" s="79" t="s">
         <v>516</v>
       </c>
@@ -4917,16 +4917,16 @@
       <c r="F50" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G50" s="102" t="s">
+      <c r="G50" s="104" t="s">
         <v>525</v>
       </c>
-      <c r="H50" s="103"/>
-      <c r="I50" s="103"/>
-      <c r="J50" s="103"/>
-      <c r="K50" s="103"/>
-      <c r="L50" s="103"/>
-      <c r="M50" s="103"/>
-      <c r="N50" s="103"/>
+      <c r="H50" s="105"/>
+      <c r="I50" s="105"/>
+      <c r="J50" s="105"/>
+      <c r="K50" s="105"/>
+      <c r="L50" s="105"/>
+      <c r="M50" s="105"/>
+      <c r="N50" s="105"/>
       <c r="O50" s="79" t="s">
         <v>516</v>
       </c>
@@ -4944,16 +4944,16 @@
       <c r="F51" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G51" s="102" t="s">
+      <c r="G51" s="104" t="s">
         <v>525</v>
       </c>
-      <c r="H51" s="103"/>
-      <c r="I51" s="103"/>
-      <c r="J51" s="103"/>
-      <c r="K51" s="103"/>
-      <c r="L51" s="103"/>
-      <c r="M51" s="103"/>
-      <c r="N51" s="103"/>
+      <c r="H51" s="105"/>
+      <c r="I51" s="105"/>
+      <c r="J51" s="105"/>
+      <c r="K51" s="105"/>
+      <c r="L51" s="105"/>
+      <c r="M51" s="105"/>
+      <c r="N51" s="105"/>
       <c r="O51" s="79" t="s">
         <v>516</v>
       </c>
@@ -4971,16 +4971,16 @@
       <c r="F52" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G52" s="102" t="s">
+      <c r="G52" s="104" t="s">
         <v>495</v>
       </c>
-      <c r="H52" s="103"/>
-      <c r="I52" s="103"/>
-      <c r="J52" s="103"/>
-      <c r="K52" s="103"/>
-      <c r="L52" s="103"/>
-      <c r="M52" s="103"/>
-      <c r="N52" s="103"/>
+      <c r="H52" s="105"/>
+      <c r="I52" s="105"/>
+      <c r="J52" s="105"/>
+      <c r="K52" s="105"/>
+      <c r="L52" s="105"/>
+      <c r="M52" s="105"/>
+      <c r="N52" s="105"/>
       <c r="O52" s="79" t="s">
         <v>516</v>
       </c>
@@ -4998,16 +4998,16 @@
       <c r="F53" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G53" s="108" t="s">
+      <c r="G53" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="H53" s="103"/>
-      <c r="I53" s="103"/>
-      <c r="J53" s="103"/>
-      <c r="K53" s="103"/>
-      <c r="L53" s="103"/>
-      <c r="M53" s="103"/>
-      <c r="N53" s="103"/>
+      <c r="H53" s="105"/>
+      <c r="I53" s="105"/>
+      <c r="J53" s="105"/>
+      <c r="K53" s="105"/>
+      <c r="L53" s="105"/>
+      <c r="M53" s="105"/>
+      <c r="N53" s="105"/>
       <c r="O53" s="79" t="s">
         <v>515</v>
       </c>
@@ -5025,16 +5025,16 @@
       <c r="F54" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G54" s="108" t="s">
+      <c r="G54" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="H54" s="103"/>
-      <c r="I54" s="103"/>
-      <c r="J54" s="103"/>
-      <c r="K54" s="103"/>
-      <c r="L54" s="103"/>
-      <c r="M54" s="103"/>
-      <c r="N54" s="103"/>
+      <c r="H54" s="105"/>
+      <c r="I54" s="105"/>
+      <c r="J54" s="105"/>
+      <c r="K54" s="105"/>
+      <c r="L54" s="105"/>
+      <c r="M54" s="105"/>
+      <c r="N54" s="105"/>
       <c r="O54" s="79" t="s">
         <v>515</v>
       </c>
@@ -5052,16 +5052,16 @@
       <c r="F55" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G55" s="108" t="s">
+      <c r="G55" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="103"/>
-      <c r="I55" s="103"/>
-      <c r="J55" s="103"/>
-      <c r="K55" s="103"/>
-      <c r="L55" s="103"/>
-      <c r="M55" s="103"/>
-      <c r="N55" s="103"/>
+      <c r="H55" s="105"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="105"/>
+      <c r="K55" s="105"/>
+      <c r="L55" s="105"/>
+      <c r="M55" s="105"/>
+      <c r="N55" s="105"/>
       <c r="O55" s="79" t="s">
         <v>515</v>
       </c>
@@ -5079,16 +5079,16 @@
       <c r="F56" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G56" s="108" t="s">
+      <c r="G56" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="H56" s="103"/>
-      <c r="I56" s="103"/>
-      <c r="J56" s="103"/>
-      <c r="K56" s="103"/>
-      <c r="L56" s="103"/>
-      <c r="M56" s="103"/>
-      <c r="N56" s="103"/>
+      <c r="H56" s="105"/>
+      <c r="I56" s="105"/>
+      <c r="J56" s="105"/>
+      <c r="K56" s="105"/>
+      <c r="L56" s="105"/>
+      <c r="M56" s="105"/>
+      <c r="N56" s="105"/>
       <c r="O56" s="79" t="s">
         <v>515</v>
       </c>
@@ -5106,16 +5106,16 @@
       <c r="F57" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G57" s="108" t="s">
+      <c r="G57" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="H57" s="103"/>
-      <c r="I57" s="103"/>
-      <c r="J57" s="103"/>
-      <c r="K57" s="103"/>
-      <c r="L57" s="103"/>
-      <c r="M57" s="103"/>
-      <c r="N57" s="103"/>
+      <c r="H57" s="105"/>
+      <c r="I57" s="105"/>
+      <c r="J57" s="105"/>
+      <c r="K57" s="105"/>
+      <c r="L57" s="105"/>
+      <c r="M57" s="105"/>
+      <c r="N57" s="105"/>
       <c r="O57" s="79" t="s">
         <v>515</v>
       </c>
@@ -5133,16 +5133,16 @@
       <c r="F58" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="G58" s="102" t="s">
+      <c r="G58" s="104" t="s">
         <v>525</v>
       </c>
-      <c r="H58" s="103"/>
-      <c r="I58" s="103"/>
-      <c r="J58" s="103"/>
-      <c r="K58" s="103"/>
-      <c r="L58" s="103"/>
-      <c r="M58" s="103"/>
-      <c r="N58" s="103"/>
+      <c r="H58" s="105"/>
+      <c r="I58" s="105"/>
+      <c r="J58" s="105"/>
+      <c r="K58" s="105"/>
+      <c r="L58" s="105"/>
+      <c r="M58" s="105"/>
+      <c r="N58" s="105"/>
       <c r="O58" s="79" t="s">
         <v>524</v>
       </c>
@@ -5158,16 +5158,16 @@
         <v>519</v>
       </c>
       <c r="F59" s="87"/>
-      <c r="G59" s="106" t="s">
+      <c r="G59" s="115" t="s">
         <v>520</v>
       </c>
-      <c r="H59" s="107"/>
-      <c r="I59" s="107"/>
-      <c r="J59" s="107"/>
-      <c r="K59" s="107"/>
-      <c r="L59" s="107"/>
-      <c r="M59" s="107"/>
-      <c r="N59" s="107"/>
+      <c r="H59" s="116"/>
+      <c r="I59" s="116"/>
+      <c r="J59" s="116"/>
+      <c r="K59" s="116"/>
+      <c r="L59" s="116"/>
+      <c r="M59" s="116"/>
+      <c r="N59" s="116"/>
       <c r="O59" s="81"/>
     </row>
     <row r="61" spans="3:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -5382,41 +5382,6 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="G14:N14"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="G16:N16"/>
-    <mergeCell ref="G32:N32"/>
-    <mergeCell ref="G34:N34"/>
-    <mergeCell ref="G22:N22"/>
-    <mergeCell ref="G23:N23"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="G35:N35"/>
-    <mergeCell ref="G36:N36"/>
-    <mergeCell ref="G37:N37"/>
-    <mergeCell ref="G28:N28"/>
-    <mergeCell ref="G33:N33"/>
-    <mergeCell ref="G4:M4"/>
-    <mergeCell ref="G27:N27"/>
-    <mergeCell ref="G8:N8"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="G5:N5"/>
-    <mergeCell ref="G6:N6"/>
-    <mergeCell ref="G13:N13"/>
-    <mergeCell ref="G18:N18"/>
-    <mergeCell ref="G17:M17"/>
-    <mergeCell ref="G9:N9"/>
-    <mergeCell ref="G12:N12"/>
-    <mergeCell ref="G11:N11"/>
-    <mergeCell ref="G15:N15"/>
-    <mergeCell ref="G46:N46"/>
-    <mergeCell ref="G47:N47"/>
-    <mergeCell ref="G38:N38"/>
-    <mergeCell ref="G39:N39"/>
-    <mergeCell ref="G40:N40"/>
-    <mergeCell ref="G41:N41"/>
-    <mergeCell ref="G42:N42"/>
     <mergeCell ref="G58:N58"/>
     <mergeCell ref="G31:N31"/>
     <mergeCell ref="G59:N59"/>
@@ -5433,6 +5398,41 @@
     <mergeCell ref="G43:N43"/>
     <mergeCell ref="G44:N44"/>
     <mergeCell ref="G45:N45"/>
+    <mergeCell ref="G46:N46"/>
+    <mergeCell ref="G47:N47"/>
+    <mergeCell ref="G38:N38"/>
+    <mergeCell ref="G39:N39"/>
+    <mergeCell ref="G40:N40"/>
+    <mergeCell ref="G41:N41"/>
+    <mergeCell ref="G42:N42"/>
+    <mergeCell ref="G4:M4"/>
+    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="G8:N8"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="G19:N19"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="G6:N6"/>
+    <mergeCell ref="G13:N13"/>
+    <mergeCell ref="G18:N18"/>
+    <mergeCell ref="G17:M17"/>
+    <mergeCell ref="G9:N9"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="G11:N11"/>
+    <mergeCell ref="G15:N15"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="G36:N36"/>
+    <mergeCell ref="G37:N37"/>
+    <mergeCell ref="G28:N28"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G16:N16"/>
+    <mergeCell ref="G32:N32"/>
+    <mergeCell ref="G34:N34"/>
+    <mergeCell ref="G22:N22"/>
+    <mergeCell ref="G23:N23"/>
+    <mergeCell ref="H26:K26"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5552,16 +5552,16 @@
       <c r="E12" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="F12" s="115" t="s">
+      <c r="F12" s="120" t="s">
         <v>262</v>
       </c>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="102"/>
     </row>
     <row r="13" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -5577,12 +5577,12 @@
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="115" t="s">
+      <c r="J13" s="120" t="s">
         <v>264</v>
       </c>
-      <c r="K13" s="100"/>
-      <c r="L13" s="100"/>
-      <c r="M13" s="101"/>
+      <c r="K13" s="101"/>
+      <c r="L13" s="101"/>
+      <c r="M13" s="102"/>
     </row>
     <row r="14" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -5594,16 +5594,16 @@
       <c r="E14" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F14" s="115" t="s">
+      <c r="F14" s="120" t="s">
         <v>262</v>
       </c>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="100"/>
-      <c r="K14" s="100"/>
-      <c r="L14" s="100"/>
-      <c r="M14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="102"/>
     </row>
     <row r="15" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -5619,12 +5619,12 @@
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="35"/>
-      <c r="J15" s="115" t="s">
+      <c r="J15" s="120" t="s">
         <v>264</v>
       </c>
-      <c r="K15" s="100"/>
-      <c r="L15" s="100"/>
-      <c r="M15" s="101"/>
+      <c r="K15" s="101"/>
+      <c r="L15" s="101"/>
+      <c r="M15" s="102"/>
     </row>
     <row r="16" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="18" t="s">
@@ -5636,16 +5636,16 @@
       <c r="E16" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F16" s="115" t="s">
+      <c r="F16" s="120" t="s">
         <v>262</v>
       </c>
-      <c r="G16" s="100"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="100"/>
-      <c r="L16" s="100"/>
-      <c r="M16" s="101"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="101"/>
+      <c r="I16" s="101"/>
+      <c r="J16" s="101"/>
+      <c r="K16" s="101"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="102"/>
     </row>
     <row r="17" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="18" t="s">
@@ -5661,12 +5661,12 @@
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
       <c r="I17" s="35"/>
-      <c r="J17" s="115" t="s">
+      <c r="J17" s="120" t="s">
         <v>264</v>
       </c>
-      <c r="K17" s="100"/>
-      <c r="L17" s="100"/>
-      <c r="M17" s="101"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="102"/>
     </row>
     <row r="18" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C18" s="18" t="s">
@@ -5681,13 +5681,13 @@
       <c r="F18" s="33"/>
       <c r="G18" s="34"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="115" t="s">
+      <c r="I18" s="120" t="s">
         <v>270</v>
       </c>
-      <c r="J18" s="100"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="101"/>
+      <c r="J18" s="101"/>
+      <c r="K18" s="101"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="102"/>
     </row>
     <row r="19" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C19" s="18" t="s">
@@ -5740,12 +5740,12 @@
       <c r="I20" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="J20" s="115" t="s">
+      <c r="J20" s="120" t="s">
         <v>281</v>
       </c>
-      <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="101"/>
+      <c r="K20" s="101"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="102"/>
     </row>
     <row r="21" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -5763,12 +5763,12 @@
       <c r="I21" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="J21" s="115" t="s">
+      <c r="J21" s="120" t="s">
         <v>281</v>
       </c>
-      <c r="K21" s="100"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="102"/>
     </row>
     <row r="22" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -5786,12 +5786,12 @@
       <c r="I22" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="J22" s="115" t="s">
+      <c r="J22" s="120" t="s">
         <v>281</v>
       </c>
-      <c r="K22" s="100"/>
-      <c r="L22" s="100"/>
-      <c r="M22" s="101"/>
+      <c r="K22" s="101"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="102"/>
     </row>
     <row r="23" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -5803,16 +5803,16 @@
       <c r="E23" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="F23" s="115" t="s">
+      <c r="F23" s="120" t="s">
         <v>285</v>
       </c>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="100"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="101"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="101"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="102"/>
     </row>
     <row r="24" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -5824,16 +5824,16 @@
       <c r="E24" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F24" s="115" t="s">
+      <c r="F24" s="120" t="s">
         <v>287</v>
       </c>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="101"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="102"/>
     </row>
     <row r="25" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -5849,12 +5849,12 @@
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="115" t="s">
+      <c r="J25" s="120" t="s">
         <v>289</v>
       </c>
-      <c r="K25" s="100"/>
-      <c r="L25" s="100"/>
-      <c r="M25" s="101"/>
+      <c r="K25" s="101"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="102"/>
     </row>
     <row r="26" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -5904,16 +5904,16 @@
       <c r="E28" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="F28" s="112" t="s">
+      <c r="F28" s="100" t="s">
         <v>262</v>
       </c>
-      <c r="G28" s="100"/>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="100"/>
-      <c r="M28" s="101"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="101"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="101"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="102"/>
     </row>
     <row r="29" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C29" s="18" t="s">
@@ -5929,12 +5929,12 @@
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="27"/>
-      <c r="J29" s="112" t="s">
+      <c r="J29" s="100" t="s">
         <v>264</v>
       </c>
-      <c r="K29" s="100"/>
-      <c r="L29" s="100"/>
-      <c r="M29" s="101"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="102"/>
     </row>
     <row r="30" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -5946,16 +5946,16 @@
       <c r="E30" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="F30" s="112" t="s">
+      <c r="F30" s="100" t="s">
         <v>262</v>
       </c>
-      <c r="G30" s="100"/>
-      <c r="H30" s="100"/>
-      <c r="I30" s="100"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="101"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="101"/>
+      <c r="I30" s="101"/>
+      <c r="J30" s="101"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="102"/>
     </row>
     <row r="31" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -5971,12 +5971,12 @@
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="27"/>
-      <c r="J31" s="112" t="s">
+      <c r="J31" s="100" t="s">
         <v>264</v>
       </c>
-      <c r="K31" s="100"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="101"/>
+      <c r="K31" s="101"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="102"/>
     </row>
     <row r="32" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -5988,16 +5988,16 @@
       <c r="E32" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="F32" s="112" t="s">
+      <c r="F32" s="100" t="s">
         <v>262</v>
       </c>
-      <c r="G32" s="100"/>
-      <c r="H32" s="100"/>
-      <c r="I32" s="100"/>
-      <c r="J32" s="100"/>
-      <c r="K32" s="100"/>
-      <c r="L32" s="100"/>
-      <c r="M32" s="101"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="102"/>
     </row>
     <row r="33" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -6013,12 +6013,12 @@
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="27"/>
-      <c r="J33" s="112" t="s">
+      <c r="J33" s="100" t="s">
         <v>264</v>
       </c>
-      <c r="K33" s="100"/>
-      <c r="L33" s="100"/>
-      <c r="M33" s="101"/>
+      <c r="K33" s="101"/>
+      <c r="L33" s="101"/>
+      <c r="M33" s="102"/>
     </row>
     <row r="34" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -6033,13 +6033,13 @@
       <c r="F34" s="25"/>
       <c r="G34" s="26"/>
       <c r="H34" s="27"/>
-      <c r="I34" s="112" t="s">
+      <c r="I34" s="100" t="s">
         <v>270</v>
       </c>
-      <c r="J34" s="100"/>
-      <c r="K34" s="100"/>
-      <c r="L34" s="100"/>
-      <c r="M34" s="101"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="101"/>
+      <c r="L34" s="101"/>
+      <c r="M34" s="102"/>
     </row>
     <row r="35" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -6092,12 +6092,12 @@
       <c r="I36" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="J36" s="112" t="s">
+      <c r="J36" s="100" t="s">
         <v>281</v>
       </c>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="101"/>
+      <c r="K36" s="101"/>
+      <c r="L36" s="101"/>
+      <c r="M36" s="102"/>
     </row>
     <row r="37" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -6115,12 +6115,12 @@
       <c r="I37" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="J37" s="112" t="s">
+      <c r="J37" s="100" t="s">
         <v>281</v>
       </c>
-      <c r="K37" s="100"/>
-      <c r="L37" s="100"/>
-      <c r="M37" s="101"/>
+      <c r="K37" s="101"/>
+      <c r="L37" s="101"/>
+      <c r="M37" s="102"/>
     </row>
     <row r="38" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -6138,12 +6138,12 @@
       <c r="I38" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="J38" s="112" t="s">
+      <c r="J38" s="100" t="s">
         <v>281</v>
       </c>
-      <c r="K38" s="100"/>
-      <c r="L38" s="100"/>
-      <c r="M38" s="101"/>
+      <c r="K38" s="101"/>
+      <c r="L38" s="101"/>
+      <c r="M38" s="102"/>
     </row>
     <row r="39" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -6155,16 +6155,16 @@
       <c r="E39" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="F39" s="112" t="s">
+      <c r="F39" s="100" t="s">
         <v>285</v>
       </c>
-      <c r="G39" s="100"/>
-      <c r="H39" s="100"/>
-      <c r="I39" s="100"/>
-      <c r="J39" s="100"/>
-      <c r="K39" s="100"/>
-      <c r="L39" s="100"/>
-      <c r="M39" s="101"/>
+      <c r="G39" s="101"/>
+      <c r="H39" s="101"/>
+      <c r="I39" s="101"/>
+      <c r="J39" s="101"/>
+      <c r="K39" s="101"/>
+      <c r="L39" s="101"/>
+      <c r="M39" s="102"/>
     </row>
     <row r="40" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18" t="s">
@@ -6176,16 +6176,16 @@
       <c r="E40" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="F40" s="112" t="s">
+      <c r="F40" s="100" t="s">
         <v>287</v>
       </c>
-      <c r="G40" s="100"/>
-      <c r="H40" s="100"/>
-      <c r="I40" s="100"/>
-      <c r="J40" s="100"/>
-      <c r="K40" s="100"/>
-      <c r="L40" s="100"/>
-      <c r="M40" s="101"/>
+      <c r="G40" s="101"/>
+      <c r="H40" s="101"/>
+      <c r="I40" s="101"/>
+      <c r="J40" s="101"/>
+      <c r="K40" s="101"/>
+      <c r="L40" s="101"/>
+      <c r="M40" s="102"/>
     </row>
     <row r="41" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18" t="s">
@@ -6201,12 +6201,12 @@
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="27"/>
-      <c r="J41" s="112" t="s">
+      <c r="J41" s="100" t="s">
         <v>289</v>
       </c>
-      <c r="K41" s="100"/>
-      <c r="L41" s="100"/>
-      <c r="M41" s="101"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="102"/>
     </row>
     <row r="42" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18" t="s">
@@ -6241,12 +6241,12 @@
       <c r="G43" s="69"/>
       <c r="H43" s="69"/>
       <c r="I43" s="70"/>
-      <c r="J43" s="118" t="s">
+      <c r="J43" s="121" t="s">
         <v>308</v>
       </c>
-      <c r="K43" s="119"/>
-      <c r="L43" s="119"/>
-      <c r="M43" s="120"/>
+      <c r="K43" s="122"/>
+      <c r="L43" s="122"/>
+      <c r="M43" s="123"/>
     </row>
     <row r="44" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
@@ -6258,16 +6258,16 @@
       <c r="E44" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="F44" s="116" t="s">
+      <c r="F44" s="118" t="s">
         <v>281</v>
       </c>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="117"/>
+      <c r="G44" s="101"/>
+      <c r="H44" s="101"/>
+      <c r="I44" s="101"/>
+      <c r="J44" s="101"/>
+      <c r="K44" s="101"/>
+      <c r="L44" s="101"/>
+      <c r="M44" s="119"/>
       <c r="O44" t="s">
         <v>311</v>
       </c>
@@ -6282,16 +6282,16 @@
       <c r="E45" s="23" t="s">
         <v>313</v>
       </c>
-      <c r="F45" s="116" t="s">
+      <c r="F45" s="118" t="s">
         <v>281</v>
       </c>
-      <c r="G45" s="100"/>
-      <c r="H45" s="100"/>
-      <c r="I45" s="100"/>
-      <c r="J45" s="100"/>
-      <c r="K45" s="100"/>
-      <c r="L45" s="100"/>
-      <c r="M45" s="117"/>
+      <c r="G45" s="101"/>
+      <c r="H45" s="101"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="101"/>
+      <c r="M45" s="119"/>
       <c r="O45" t="s">
         <v>311</v>
       </c>
@@ -6306,16 +6306,16 @@
       <c r="E46" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="F46" s="116" t="s">
+      <c r="F46" s="118" t="s">
         <v>281</v>
       </c>
-      <c r="G46" s="100"/>
-      <c r="H46" s="100"/>
-      <c r="I46" s="100"/>
-      <c r="J46" s="100"/>
-      <c r="K46" s="100"/>
-      <c r="L46" s="100"/>
-      <c r="M46" s="117"/>
+      <c r="G46" s="101"/>
+      <c r="H46" s="101"/>
+      <c r="I46" s="101"/>
+      <c r="J46" s="101"/>
+      <c r="K46" s="101"/>
+      <c r="L46" s="101"/>
+      <c r="M46" s="119"/>
       <c r="O46" t="s">
         <v>311</v>
       </c>
@@ -6349,16 +6349,16 @@
       <c r="E48" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="F48" s="116" t="s">
+      <c r="F48" s="118" t="s">
         <v>281</v>
       </c>
-      <c r="G48" s="100"/>
-      <c r="H48" s="100"/>
-      <c r="I48" s="100"/>
-      <c r="J48" s="100"/>
-      <c r="K48" s="100"/>
-      <c r="L48" s="100"/>
-      <c r="M48" s="117"/>
+      <c r="G48" s="101"/>
+      <c r="H48" s="101"/>
+      <c r="I48" s="101"/>
+      <c r="J48" s="101"/>
+      <c r="K48" s="101"/>
+      <c r="L48" s="101"/>
+      <c r="M48" s="119"/>
       <c r="O48" t="s">
         <v>311</v>
       </c>
@@ -6373,16 +6373,16 @@
       <c r="E49" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="F49" s="116" t="s">
+      <c r="F49" s="118" t="s">
         <v>281</v>
       </c>
-      <c r="G49" s="100"/>
-      <c r="H49" s="100"/>
-      <c r="I49" s="100"/>
-      <c r="J49" s="100"/>
-      <c r="K49" s="100"/>
-      <c r="L49" s="100"/>
-      <c r="M49" s="117"/>
+      <c r="G49" s="101"/>
+      <c r="H49" s="101"/>
+      <c r="I49" s="101"/>
+      <c r="J49" s="101"/>
+      <c r="K49" s="101"/>
+      <c r="L49" s="101"/>
+      <c r="M49" s="119"/>
       <c r="O49" t="s">
         <v>311</v>
       </c>
@@ -6397,16 +6397,16 @@
       <c r="E50" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="F50" s="116" t="s">
+      <c r="F50" s="118" t="s">
         <v>281</v>
       </c>
-      <c r="G50" s="100"/>
-      <c r="H50" s="100"/>
-      <c r="I50" s="100"/>
-      <c r="J50" s="100"/>
-      <c r="K50" s="100"/>
-      <c r="L50" s="100"/>
-      <c r="M50" s="117"/>
+      <c r="G50" s="101"/>
+      <c r="H50" s="101"/>
+      <c r="I50" s="101"/>
+      <c r="J50" s="101"/>
+      <c r="K50" s="101"/>
+      <c r="L50" s="101"/>
+      <c r="M50" s="119"/>
       <c r="O50" t="s">
         <v>311</v>
       </c>
@@ -6440,16 +6440,16 @@
       <c r="E52" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="F52" s="112" t="s">
+      <c r="F52" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="100"/>
-      <c r="H52" s="100"/>
-      <c r="I52" s="100"/>
-      <c r="J52" s="100"/>
-      <c r="K52" s="100"/>
-      <c r="L52" s="100"/>
-      <c r="M52" s="101"/>
+      <c r="G52" s="101"/>
+      <c r="H52" s="101"/>
+      <c r="I52" s="101"/>
+      <c r="J52" s="101"/>
+      <c r="K52" s="101"/>
+      <c r="L52" s="101"/>
+      <c r="M52" s="102"/>
       <c r="O52" t="s">
         <v>434</v>
       </c>
@@ -6464,16 +6464,16 @@
       <c r="E53" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="F53" s="112" t="s">
+      <c r="F53" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="100"/>
-      <c r="H53" s="100"/>
-      <c r="I53" s="100"/>
-      <c r="J53" s="100"/>
-      <c r="K53" s="100"/>
-      <c r="L53" s="100"/>
-      <c r="M53" s="101"/>
+      <c r="G53" s="101"/>
+      <c r="H53" s="101"/>
+      <c r="I53" s="101"/>
+      <c r="J53" s="101"/>
+      <c r="K53" s="101"/>
+      <c r="L53" s="101"/>
+      <c r="M53" s="102"/>
       <c r="O53" t="s">
         <v>141</v>
       </c>
@@ -6488,16 +6488,16 @@
       <c r="E54" s="23" t="s">
         <v>330</v>
       </c>
-      <c r="F54" s="112" t="s">
+      <c r="F54" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="100"/>
-      <c r="H54" s="100"/>
-      <c r="I54" s="100"/>
-      <c r="J54" s="100"/>
-      <c r="K54" s="100"/>
-      <c r="L54" s="100"/>
-      <c r="M54" s="101"/>
+      <c r="G54" s="101"/>
+      <c r="H54" s="101"/>
+      <c r="I54" s="101"/>
+      <c r="J54" s="101"/>
+      <c r="K54" s="101"/>
+      <c r="L54" s="101"/>
+      <c r="M54" s="102"/>
       <c r="O54" t="s">
         <v>141</v>
       </c>
@@ -6531,16 +6531,16 @@
       <c r="E56" s="22" t="s">
         <v>333</v>
       </c>
-      <c r="F56" s="112" t="s">
+      <c r="F56" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="100"/>
-      <c r="H56" s="100"/>
-      <c r="I56" s="100"/>
-      <c r="J56" s="100"/>
-      <c r="K56" s="100"/>
-      <c r="L56" s="100"/>
-      <c r="M56" s="101"/>
+      <c r="G56" s="101"/>
+      <c r="H56" s="101"/>
+      <c r="I56" s="101"/>
+      <c r="J56" s="101"/>
+      <c r="K56" s="101"/>
+      <c r="L56" s="101"/>
+      <c r="M56" s="102"/>
       <c r="O56" t="s">
         <v>141</v>
       </c>
@@ -6555,16 +6555,16 @@
       <c r="E57" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="F57" s="112" t="s">
+      <c r="F57" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="100"/>
-      <c r="H57" s="100"/>
-      <c r="I57" s="100"/>
-      <c r="J57" s="100"/>
-      <c r="K57" s="100"/>
-      <c r="L57" s="100"/>
-      <c r="M57" s="101"/>
+      <c r="G57" s="101"/>
+      <c r="H57" s="101"/>
+      <c r="I57" s="101"/>
+      <c r="J57" s="101"/>
+      <c r="K57" s="101"/>
+      <c r="L57" s="101"/>
+      <c r="M57" s="102"/>
       <c r="O57" t="s">
         <v>141</v>
       </c>
@@ -6579,16 +6579,16 @@
       <c r="E58" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="F58" s="112" t="s">
+      <c r="F58" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="100"/>
-      <c r="H58" s="100"/>
-      <c r="I58" s="100"/>
-      <c r="J58" s="100"/>
-      <c r="K58" s="100"/>
-      <c r="L58" s="100"/>
-      <c r="M58" s="101"/>
+      <c r="G58" s="101"/>
+      <c r="H58" s="101"/>
+      <c r="I58" s="101"/>
+      <c r="J58" s="101"/>
+      <c r="K58" s="101"/>
+      <c r="L58" s="101"/>
+      <c r="M58" s="102"/>
       <c r="O58" t="s">
         <v>141</v>
       </c>
@@ -6633,18 +6633,17 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:M48"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F49:M49"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F50:M50"/>
-    <mergeCell ref="F46:M46"/>
-    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J43:M43"/>
     <mergeCell ref="F12:M12"/>
     <mergeCell ref="F30:M30"/>
     <mergeCell ref="J17:M17"/>
@@ -6661,17 +6660,18 @@
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="J25:M25"/>
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F45:M45"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="F44:M44"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:M48"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="F57:M57"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F53:M53"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6746,16 +6746,16 @@
       <c r="E6" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F6" s="99" t="s">
+      <c r="F6" s="103" t="s">
         <v>539</v>
       </c>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="100"/>
-      <c r="L6" s="100"/>
-      <c r="M6" s="101"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="101"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="101"/>
+      <c r="M6" s="102"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
@@ -6767,16 +6767,16 @@
       <c r="E7" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="F7" s="99" t="s">
+      <c r="F7" s="103" t="s">
         <v>540</v>
       </c>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="101"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="101"/>
+      <c r="L7" s="101"/>
+      <c r="M7" s="102"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
@@ -6838,12 +6838,12 @@
       <c r="I19" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="99" t="s">
+      <c r="J19" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="100"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="101"/>
+      <c r="K19" s="101"/>
+      <c r="L19" s="101"/>
+      <c r="M19" s="102"/>
     </row>
     <row r="20" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C20" s="18" t="s">
@@ -6865,12 +6865,12 @@
       <c r="I20" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J20" s="99" t="s">
+      <c r="J20" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="101"/>
+      <c r="K20" s="101"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="102"/>
     </row>
     <row r="21" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18" t="s">
@@ -6880,18 +6880,18 @@
         <v>19</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="99" t="s">
+      <c r="F21" s="103" t="s">
         <v>346</v>
       </c>
-      <c r="G21" s="101"/>
-      <c r="H21" s="99" t="s">
+      <c r="G21" s="102"/>
+      <c r="H21" s="103" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="100"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="100"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="102"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18" t="s">
@@ -6901,10 +6901,10 @@
         <v>19</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="99" t="s">
+      <c r="F22" s="103" t="s">
         <v>346</v>
       </c>
-      <c r="G22" s="101"/>
+      <c r="G22" s="102"/>
       <c r="H22" s="17"/>
       <c r="I22" s="10" t="s">
         <v>347</v>
@@ -6912,11 +6912,11 @@
       <c r="J22" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="K22" s="99" t="s">
+      <c r="K22" s="103" t="s">
         <v>133</v>
       </c>
-      <c r="L22" s="100"/>
-      <c r="M22" s="101"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="102"/>
     </row>
     <row r="23" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18" t="s">
@@ -6926,18 +6926,18 @@
         <v>19</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="99" t="s">
+      <c r="F23" s="103" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="101"/>
-      <c r="J23" s="99" t="s">
+      <c r="G23" s="101"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="103" t="s">
         <v>115</v>
       </c>
-      <c r="K23" s="100"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="101"/>
+      <c r="K23" s="101"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="102"/>
     </row>
     <row r="24" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18" t="s">
@@ -6947,18 +6947,18 @@
         <v>19</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="99" t="s">
+      <c r="F24" s="103" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="101"/>
-      <c r="J24" s="99" t="s">
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="103" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="100"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="101"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="102"/>
     </row>
     <row r="25" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18" t="s">
@@ -6968,18 +6968,18 @@
         <v>19</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="99" t="s">
+      <c r="F25" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="100"/>
-      <c r="H25" s="100"/>
-      <c r="I25" s="101"/>
-      <c r="J25" s="99" t="s">
+      <c r="G25" s="101"/>
+      <c r="H25" s="101"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="100"/>
-      <c r="L25" s="100"/>
-      <c r="M25" s="101"/>
+      <c r="K25" s="101"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="102"/>
     </row>
     <row r="26" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18" t="s">
@@ -6989,18 +6989,18 @@
         <v>19</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="99" t="s">
+      <c r="F26" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="100"/>
-      <c r="H26" s="100"/>
-      <c r="I26" s="101"/>
-      <c r="J26" s="99" t="s">
+      <c r="G26" s="101"/>
+      <c r="H26" s="101"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="100"/>
-      <c r="L26" s="100"/>
-      <c r="M26" s="101"/>
+      <c r="K26" s="101"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="102"/>
     </row>
     <row r="27" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C27" s="18" t="s">
@@ -7054,16 +7054,16 @@
       <c r="E29" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="F29" s="99" t="s">
+      <c r="F29" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="100"/>
-      <c r="H29" s="100"/>
-      <c r="I29" s="100"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="100"/>
-      <c r="M29" s="101"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="101"/>
+      <c r="I29" s="101"/>
+      <c r="J29" s="101"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="102"/>
     </row>
     <row r="30" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18" t="s">
@@ -7073,16 +7073,16 @@
         <v>19</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="99" t="s">
+      <c r="F30" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="100"/>
-      <c r="H30" s="100"/>
-      <c r="I30" s="100"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="101"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="101"/>
+      <c r="I30" s="101"/>
+      <c r="J30" s="101"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="102"/>
     </row>
     <row r="31" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18" t="s">
@@ -7092,16 +7092,16 @@
         <v>19</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="99" t="s">
+      <c r="F31" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="100"/>
-      <c r="H31" s="100"/>
-      <c r="I31" s="100"/>
-      <c r="J31" s="100"/>
-      <c r="K31" s="100"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="101"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="101"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="101"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="102"/>
     </row>
     <row r="32" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18" t="s">
@@ -7111,16 +7111,16 @@
         <v>19</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="99" t="s">
+      <c r="F32" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="100"/>
-      <c r="H32" s="100"/>
-      <c r="I32" s="100"/>
-      <c r="J32" s="100"/>
-      <c r="K32" s="100"/>
-      <c r="L32" s="100"/>
-      <c r="M32" s="101"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="102"/>
     </row>
     <row r="33" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18" t="s">
@@ -7130,16 +7130,16 @@
         <v>19</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="99" t="s">
+      <c r="F33" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="100"/>
-      <c r="H33" s="100"/>
-      <c r="I33" s="100"/>
-      <c r="J33" s="100"/>
-      <c r="K33" s="100"/>
-      <c r="L33" s="100"/>
-      <c r="M33" s="101"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="101"/>
+      <c r="I33" s="101"/>
+      <c r="J33" s="101"/>
+      <c r="K33" s="101"/>
+      <c r="L33" s="101"/>
+      <c r="M33" s="102"/>
     </row>
     <row r="34" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18" t="s">
@@ -7149,16 +7149,16 @@
         <v>19</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="99" t="s">
+      <c r="F34" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="100"/>
-      <c r="H34" s="100"/>
-      <c r="I34" s="100"/>
-      <c r="J34" s="100"/>
-      <c r="K34" s="100"/>
-      <c r="L34" s="100"/>
-      <c r="M34" s="101"/>
+      <c r="G34" s="101"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="101"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="101"/>
+      <c r="L34" s="101"/>
+      <c r="M34" s="102"/>
     </row>
     <row r="35" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18" t="s">
@@ -7168,16 +7168,16 @@
         <v>19</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="99" t="s">
+      <c r="F35" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="100"/>
-      <c r="H35" s="100"/>
-      <c r="I35" s="100"/>
-      <c r="J35" s="100"/>
-      <c r="K35" s="100"/>
-      <c r="L35" s="100"/>
-      <c r="M35" s="101"/>
+      <c r="G35" s="101"/>
+      <c r="H35" s="101"/>
+      <c r="I35" s="101"/>
+      <c r="J35" s="101"/>
+      <c r="K35" s="101"/>
+      <c r="L35" s="101"/>
+      <c r="M35" s="102"/>
     </row>
     <row r="36" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C36" s="18" t="s">
@@ -7187,16 +7187,16 @@
         <v>19</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="99" t="s">
+      <c r="F36" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="100"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="101"/>
+      <c r="G36" s="101"/>
+      <c r="H36" s="101"/>
+      <c r="I36" s="101"/>
+      <c r="J36" s="101"/>
+      <c r="K36" s="101"/>
+      <c r="L36" s="101"/>
+      <c r="M36" s="102"/>
     </row>
     <row r="37" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18" t="s">
@@ -7206,16 +7206,16 @@
         <v>19</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="99" t="s">
+      <c r="F37" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="100"/>
-      <c r="H37" s="100"/>
-      <c r="I37" s="100"/>
-      <c r="J37" s="100"/>
-      <c r="K37" s="100"/>
-      <c r="L37" s="100"/>
-      <c r="M37" s="101"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="101"/>
+      <c r="K37" s="101"/>
+      <c r="L37" s="101"/>
+      <c r="M37" s="102"/>
     </row>
     <row r="38" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18" t="s">
@@ -7225,16 +7225,16 @@
         <v>19</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="99" t="s">
+      <c r="F38" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G38" s="100"/>
-      <c r="H38" s="100"/>
-      <c r="I38" s="100"/>
-      <c r="J38" s="100"/>
-      <c r="K38" s="100"/>
-      <c r="L38" s="100"/>
-      <c r="M38" s="101"/>
+      <c r="G38" s="101"/>
+      <c r="H38" s="101"/>
+      <c r="I38" s="101"/>
+      <c r="J38" s="101"/>
+      <c r="K38" s="101"/>
+      <c r="L38" s="101"/>
+      <c r="M38" s="102"/>
     </row>
     <row r="39" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18" t="s">
@@ -7269,11 +7269,11 @@
       <c r="I40" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J40" s="99" t="s">
+      <c r="J40" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="K40" s="100"/>
-      <c r="L40" s="101"/>
+      <c r="K40" s="101"/>
+      <c r="L40" s="102"/>
       <c r="M40" s="12" t="s">
         <v>120</v>
       </c>
@@ -7294,11 +7294,11 @@
       <c r="I41" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J41" s="99" t="s">
+      <c r="J41" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="K41" s="100"/>
-      <c r="L41" s="101"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="102"/>
       <c r="M41" s="12" t="s">
         <v>120</v>
       </c>
@@ -7319,11 +7319,11 @@
       <c r="I42" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J42" s="99" t="s">
+      <c r="J42" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="K42" s="100"/>
-      <c r="L42" s="101"/>
+      <c r="K42" s="101"/>
+      <c r="L42" s="102"/>
       <c r="M42" s="12" t="s">
         <v>120</v>
       </c>
@@ -7344,11 +7344,11 @@
       <c r="I43" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J43" s="99" t="s">
+      <c r="J43" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="K43" s="100"/>
-      <c r="L43" s="101"/>
+      <c r="K43" s="101"/>
+      <c r="L43" s="102"/>
       <c r="M43" s="12" t="s">
         <v>120</v>
       </c>
@@ -7369,11 +7369,11 @@
       <c r="I44" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J44" s="99" t="s">
+      <c r="J44" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="K44" s="100"/>
-      <c r="L44" s="101"/>
+      <c r="K44" s="101"/>
+      <c r="L44" s="102"/>
       <c r="M44" s="12" t="s">
         <v>120</v>
       </c>
@@ -7394,11 +7394,11 @@
       <c r="I45" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J45" s="99" t="s">
+      <c r="J45" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="K45" s="100"/>
-      <c r="L45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="102"/>
       <c r="M45" s="12" t="s">
         <v>120</v>
       </c>
@@ -7419,11 +7419,11 @@
       <c r="I46" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J46" s="99" t="s">
+      <c r="J46" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="K46" s="100"/>
-      <c r="L46" s="101"/>
+      <c r="K46" s="101"/>
+      <c r="L46" s="102"/>
       <c r="M46" s="12" t="s">
         <v>120</v>
       </c>
@@ -7444,11 +7444,11 @@
       <c r="I47" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J47" s="99" t="s">
+      <c r="J47" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="K47" s="100"/>
-      <c r="L47" s="101"/>
+      <c r="K47" s="101"/>
+      <c r="L47" s="102"/>
       <c r="M47" s="12" t="s">
         <v>120</v>
       </c>
@@ -7469,11 +7469,11 @@
       <c r="I48" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J48" s="99" t="s">
+      <c r="J48" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="K48" s="100"/>
-      <c r="L48" s="101"/>
+      <c r="K48" s="101"/>
+      <c r="L48" s="102"/>
       <c r="M48" s="12" t="s">
         <v>120</v>
       </c>
@@ -7503,18 +7503,18 @@
         <v>19</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="99" t="s">
+      <c r="F50" s="103" t="s">
         <v>356</v>
       </c>
-      <c r="G50" s="100"/>
-      <c r="H50" s="100"/>
-      <c r="I50" s="101"/>
-      <c r="J50" s="99" t="s">
+      <c r="G50" s="101"/>
+      <c r="H50" s="101"/>
+      <c r="I50" s="102"/>
+      <c r="J50" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="K50" s="100"/>
-      <c r="L50" s="100"/>
-      <c r="M50" s="101"/>
+      <c r="K50" s="101"/>
+      <c r="L50" s="101"/>
+      <c r="M50" s="102"/>
     </row>
     <row r="51" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C51" s="19" t="s">
@@ -7524,18 +7524,18 @@
         <v>19</v>
       </c>
       <c r="E51" s="11"/>
-      <c r="F51" s="99" t="s">
+      <c r="F51" s="103" t="s">
         <v>356</v>
       </c>
-      <c r="G51" s="100"/>
-      <c r="H51" s="100"/>
-      <c r="I51" s="101"/>
-      <c r="J51" s="99" t="s">
+      <c r="G51" s="101"/>
+      <c r="H51" s="101"/>
+      <c r="I51" s="102"/>
+      <c r="J51" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="K51" s="100"/>
-      <c r="L51" s="100"/>
-      <c r="M51" s="101"/>
+      <c r="K51" s="101"/>
+      <c r="L51" s="101"/>
+      <c r="M51" s="102"/>
     </row>
     <row r="52" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -7545,18 +7545,18 @@
         <v>19</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="99" t="s">
+      <c r="F52" s="103" t="s">
         <v>356</v>
       </c>
-      <c r="G52" s="100"/>
-      <c r="H52" s="100"/>
-      <c r="I52" s="101"/>
-      <c r="J52" s="99" t="s">
+      <c r="G52" s="101"/>
+      <c r="H52" s="101"/>
+      <c r="I52" s="102"/>
+      <c r="J52" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="K52" s="100"/>
-      <c r="L52" s="100"/>
-      <c r="M52" s="101"/>
+      <c r="K52" s="101"/>
+      <c r="L52" s="101"/>
+      <c r="M52" s="102"/>
     </row>
     <row r="53" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18" t="s">
@@ -7566,18 +7566,18 @@
         <v>19</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="99" t="s">
+      <c r="F53" s="103" t="s">
         <v>356</v>
       </c>
-      <c r="G53" s="100"/>
-      <c r="H53" s="100"/>
-      <c r="I53" s="101"/>
-      <c r="J53" s="99" t="s">
+      <c r="G53" s="101"/>
+      <c r="H53" s="101"/>
+      <c r="I53" s="102"/>
+      <c r="J53" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="K53" s="100"/>
-      <c r="L53" s="100"/>
-      <c r="M53" s="101"/>
+      <c r="K53" s="101"/>
+      <c r="L53" s="101"/>
+      <c r="M53" s="102"/>
     </row>
     <row r="54" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18" t="s">
@@ -7587,18 +7587,18 @@
         <v>19</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="99" t="s">
+      <c r="F54" s="103" t="s">
         <v>356</v>
       </c>
-      <c r="G54" s="100"/>
-      <c r="H54" s="100"/>
-      <c r="I54" s="101"/>
-      <c r="J54" s="99" t="s">
+      <c r="G54" s="101"/>
+      <c r="H54" s="101"/>
+      <c r="I54" s="102"/>
+      <c r="J54" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="K54" s="100"/>
-      <c r="L54" s="100"/>
-      <c r="M54" s="101"/>
+      <c r="K54" s="101"/>
+      <c r="L54" s="101"/>
+      <c r="M54" s="102"/>
     </row>
     <row r="55" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18" t="s">
@@ -7608,18 +7608,18 @@
         <v>19</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="99" t="s">
+      <c r="F55" s="103" t="s">
         <v>356</v>
       </c>
-      <c r="G55" s="100"/>
-      <c r="H55" s="100"/>
-      <c r="I55" s="101"/>
-      <c r="J55" s="99" t="s">
+      <c r="G55" s="101"/>
+      <c r="H55" s="101"/>
+      <c r="I55" s="102"/>
+      <c r="J55" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="K55" s="100"/>
-      <c r="L55" s="100"/>
-      <c r="M55" s="101"/>
+      <c r="K55" s="101"/>
+      <c r="L55" s="101"/>
+      <c r="M55" s="102"/>
     </row>
     <row r="56" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18" t="s">
@@ -7629,18 +7629,18 @@
         <v>19</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="99" t="s">
+      <c r="F56" s="103" t="s">
         <v>356</v>
       </c>
-      <c r="G56" s="100"/>
-      <c r="H56" s="100"/>
-      <c r="I56" s="101"/>
-      <c r="J56" s="99" t="s">
+      <c r="G56" s="101"/>
+      <c r="H56" s="101"/>
+      <c r="I56" s="102"/>
+      <c r="J56" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="K56" s="100"/>
-      <c r="L56" s="100"/>
-      <c r="M56" s="101"/>
+      <c r="K56" s="101"/>
+      <c r="L56" s="101"/>
+      <c r="M56" s="102"/>
     </row>
     <row r="57" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18" t="s">
@@ -7650,18 +7650,18 @@
         <v>19</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="99" t="s">
+      <c r="F57" s="103" t="s">
         <v>356</v>
       </c>
-      <c r="G57" s="100"/>
-      <c r="H57" s="100"/>
-      <c r="I57" s="101"/>
-      <c r="J57" s="99" t="s">
+      <c r="G57" s="101"/>
+      <c r="H57" s="101"/>
+      <c r="I57" s="102"/>
+      <c r="J57" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="K57" s="100"/>
-      <c r="L57" s="100"/>
-      <c r="M57" s="101"/>
+      <c r="K57" s="101"/>
+      <c r="L57" s="101"/>
+      <c r="M57" s="102"/>
     </row>
     <row r="58" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18" t="s">
@@ -7671,18 +7671,18 @@
         <v>19</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="99" t="s">
+      <c r="F58" s="103" t="s">
         <v>356</v>
       </c>
-      <c r="G58" s="100"/>
-      <c r="H58" s="100"/>
-      <c r="I58" s="101"/>
-      <c r="J58" s="99" t="s">
+      <c r="G58" s="101"/>
+      <c r="H58" s="101"/>
+      <c r="I58" s="102"/>
+      <c r="J58" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="K58" s="100"/>
-      <c r="L58" s="100"/>
-      <c r="M58" s="101"/>
+      <c r="K58" s="101"/>
+      <c r="L58" s="101"/>
+      <c r="M58" s="102"/>
     </row>
     <row r="59" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C59" s="18" t="s">
@@ -7717,10 +7717,10 @@
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="112" t="s">
+      <c r="L60" s="100" t="s">
         <v>369</v>
       </c>
-      <c r="M60" s="101"/>
+      <c r="M60" s="102"/>
     </row>
     <row r="61" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="18" t="s">
@@ -7738,10 +7738,10 @@
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
       <c r="K61" s="9"/>
-      <c r="L61" s="114" t="s">
+      <c r="L61" s="112" t="s">
         <v>369</v>
       </c>
-      <c r="M61" s="101"/>
+      <c r="M61" s="102"/>
     </row>
     <row r="62" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C62" s="18" t="s">
@@ -7759,10 +7759,10 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="9"/>
-      <c r="L62" s="114" t="s">
+      <c r="L62" s="112" t="s">
         <v>369</v>
       </c>
-      <c r="M62" s="101"/>
+      <c r="M62" s="102"/>
     </row>
     <row r="63" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C63" s="18" t="s">
@@ -7780,10 +7780,10 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="9"/>
-      <c r="L63" s="114" t="s">
+      <c r="L63" s="112" t="s">
         <v>369</v>
       </c>
-      <c r="M63" s="101"/>
+      <c r="M63" s="102"/>
     </row>
     <row r="64" spans="3:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C64" s="18" t="s">
@@ -7801,10 +7801,10 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="9"/>
-      <c r="L64" s="114" t="s">
+      <c r="L64" s="112" t="s">
         <v>369</v>
       </c>
-      <c r="M64" s="101"/>
+      <c r="M64" s="102"/>
     </row>
     <row r="65" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C65" s="18" t="s">
@@ -7822,10 +7822,10 @@
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="9"/>
-      <c r="L65" s="114" t="s">
+      <c r="L65" s="112" t="s">
         <v>369</v>
       </c>
-      <c r="M65" s="101"/>
+      <c r="M65" s="102"/>
     </row>
     <row r="66" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C66" s="18" t="s">
@@ -7843,10 +7843,10 @@
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
       <c r="K66" s="9"/>
-      <c r="L66" s="114" t="s">
+      <c r="L66" s="112" t="s">
         <v>369</v>
       </c>
-      <c r="M66" s="101"/>
+      <c r="M66" s="102"/>
     </row>
     <row r="67" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C67" s="18" t="s">
@@ -7864,10 +7864,10 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="9"/>
-      <c r="L67" s="114" t="s">
+      <c r="L67" s="112" t="s">
         <v>369</v>
       </c>
-      <c r="M67" s="101"/>
+      <c r="M67" s="102"/>
     </row>
     <row r="68" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C68" s="18" t="s">
@@ -7885,10 +7885,10 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="9"/>
-      <c r="L68" s="114" t="s">
+      <c r="L68" s="112" t="s">
         <v>369</v>
       </c>
-      <c r="M68" s="101"/>
+      <c r="M68" s="102"/>
     </row>
     <row r="69" spans="3:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C69" s="18" t="s">
@@ -7917,16 +7917,16 @@
       <c r="E70" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="F70" s="112" t="s">
+      <c r="F70" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G70" s="100"/>
-      <c r="H70" s="100"/>
-      <c r="I70" s="100"/>
-      <c r="J70" s="100"/>
-      <c r="K70" s="100"/>
-      <c r="L70" s="100"/>
-      <c r="M70" s="101"/>
+      <c r="G70" s="101"/>
+      <c r="H70" s="101"/>
+      <c r="I70" s="101"/>
+      <c r="J70" s="101"/>
+      <c r="K70" s="101"/>
+      <c r="L70" s="101"/>
+      <c r="M70" s="102"/>
       <c r="O70" t="s">
         <v>141</v>
       </c>
@@ -7941,16 +7941,16 @@
       <c r="E71" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="F71" s="112" t="s">
+      <c r="F71" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G71" s="100"/>
-      <c r="H71" s="100"/>
-      <c r="I71" s="100"/>
-      <c r="J71" s="100"/>
-      <c r="K71" s="100"/>
-      <c r="L71" s="100"/>
-      <c r="M71" s="101"/>
+      <c r="G71" s="101"/>
+      <c r="H71" s="101"/>
+      <c r="I71" s="101"/>
+      <c r="J71" s="101"/>
+      <c r="K71" s="101"/>
+      <c r="L71" s="101"/>
+      <c r="M71" s="102"/>
       <c r="O71" t="s">
         <v>141</v>
       </c>
@@ -7965,16 +7965,16 @@
       <c r="E72" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="F72" s="112" t="s">
+      <c r="F72" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G72" s="100"/>
-      <c r="H72" s="100"/>
-      <c r="I72" s="100"/>
-      <c r="J72" s="100"/>
-      <c r="K72" s="100"/>
-      <c r="L72" s="100"/>
-      <c r="M72" s="101"/>
+      <c r="G72" s="101"/>
+      <c r="H72" s="101"/>
+      <c r="I72" s="101"/>
+      <c r="J72" s="101"/>
+      <c r="K72" s="101"/>
+      <c r="L72" s="101"/>
+      <c r="M72" s="102"/>
       <c r="O72" t="s">
         <v>141</v>
       </c>
@@ -7989,16 +7989,16 @@
       <c r="E73" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="F73" s="112" t="s">
+      <c r="F73" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="100"/>
-      <c r="H73" s="100"/>
-      <c r="I73" s="100"/>
-      <c r="J73" s="100"/>
-      <c r="K73" s="100"/>
-      <c r="L73" s="100"/>
-      <c r="M73" s="101"/>
+      <c r="G73" s="101"/>
+      <c r="H73" s="101"/>
+      <c r="I73" s="101"/>
+      <c r="J73" s="101"/>
+      <c r="K73" s="101"/>
+      <c r="L73" s="101"/>
+      <c r="M73" s="102"/>
       <c r="O73" t="s">
         <v>141</v>
       </c>
@@ -8013,16 +8013,16 @@
       <c r="E74" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="F74" s="112" t="s">
+      <c r="F74" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G74" s="100"/>
-      <c r="H74" s="100"/>
-      <c r="I74" s="100"/>
-      <c r="J74" s="100"/>
-      <c r="K74" s="100"/>
-      <c r="L74" s="100"/>
-      <c r="M74" s="101"/>
+      <c r="G74" s="101"/>
+      <c r="H74" s="101"/>
+      <c r="I74" s="101"/>
+      <c r="J74" s="101"/>
+      <c r="K74" s="101"/>
+      <c r="L74" s="101"/>
+      <c r="M74" s="102"/>
       <c r="O74" t="s">
         <v>141</v>
       </c>
@@ -8037,16 +8037,16 @@
       <c r="E75" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="F75" s="112" t="s">
+      <c r="F75" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G75" s="100"/>
-      <c r="H75" s="100"/>
-      <c r="I75" s="100"/>
-      <c r="J75" s="100"/>
-      <c r="K75" s="100"/>
-      <c r="L75" s="100"/>
-      <c r="M75" s="101"/>
+      <c r="G75" s="101"/>
+      <c r="H75" s="101"/>
+      <c r="I75" s="101"/>
+      <c r="J75" s="101"/>
+      <c r="K75" s="101"/>
+      <c r="L75" s="101"/>
+      <c r="M75" s="102"/>
       <c r="O75" t="s">
         <v>141</v>
       </c>
@@ -8061,16 +8061,16 @@
       <c r="E76" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="F76" s="112" t="s">
+      <c r="F76" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G76" s="100"/>
-      <c r="H76" s="100"/>
-      <c r="I76" s="100"/>
-      <c r="J76" s="100"/>
-      <c r="K76" s="100"/>
-      <c r="L76" s="100"/>
-      <c r="M76" s="101"/>
+      <c r="G76" s="101"/>
+      <c r="H76" s="101"/>
+      <c r="I76" s="101"/>
+      <c r="J76" s="101"/>
+      <c r="K76" s="101"/>
+      <c r="L76" s="101"/>
+      <c r="M76" s="102"/>
       <c r="O76" t="s">
         <v>141</v>
       </c>
@@ -8085,16 +8085,16 @@
       <c r="E77" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="F77" s="112" t="s">
+      <c r="F77" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G77" s="100"/>
-      <c r="H77" s="100"/>
-      <c r="I77" s="100"/>
-      <c r="J77" s="100"/>
-      <c r="K77" s="100"/>
-      <c r="L77" s="100"/>
-      <c r="M77" s="101"/>
+      <c r="G77" s="101"/>
+      <c r="H77" s="101"/>
+      <c r="I77" s="101"/>
+      <c r="J77" s="101"/>
+      <c r="K77" s="101"/>
+      <c r="L77" s="101"/>
+      <c r="M77" s="102"/>
       <c r="O77" t="s">
         <v>141</v>
       </c>
@@ -8109,16 +8109,16 @@
       <c r="E78" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="F78" s="112" t="s">
+      <c r="F78" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="G78" s="100"/>
-      <c r="H78" s="100"/>
-      <c r="I78" s="100"/>
-      <c r="J78" s="100"/>
-      <c r="K78" s="100"/>
-      <c r="L78" s="100"/>
-      <c r="M78" s="101"/>
+      <c r="G78" s="101"/>
+      <c r="H78" s="101"/>
+      <c r="I78" s="101"/>
+      <c r="J78" s="101"/>
+      <c r="K78" s="101"/>
+      <c r="L78" s="101"/>
+      <c r="M78" s="102"/>
       <c r="O78" t="s">
         <v>141</v>
       </c>
@@ -8142,6 +8142,61 @@
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="F73:M73"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F78:M78"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="F74:M74"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="F75:M75"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="F77:M77"/>
+    <mergeCell ref="F76:M76"/>
+    <mergeCell ref="F72:M72"/>
+    <mergeCell ref="F71:M71"/>
+    <mergeCell ref="F70:M70"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="F35:M35"/>
+    <mergeCell ref="F32:M32"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="F34:M34"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J42:L42"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="L65:M65"/>
     <mergeCell ref="J54:M54"/>
@@ -8158,61 +8213,6 @@
     <mergeCell ref="J47:L47"/>
     <mergeCell ref="J48:L48"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F32:M32"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="F34:M34"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="F73:M73"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F78:M78"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="F74:M74"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="F75:M75"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="F77:M77"/>
-    <mergeCell ref="F76:M76"/>
-    <mergeCell ref="F72:M72"/>
-    <mergeCell ref="F71:M71"/>
-    <mergeCell ref="F70:M70"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8321,14 +8321,14 @@
       <c r="E11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="121"/>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
-      <c r="L11" s="100"/>
-      <c r="M11" s="101"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="102"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C12" s="18" t="s">
@@ -8340,16 +8340,16 @@
       <c r="E12" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="110" t="s">
+      <c r="F12" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="102"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
@@ -8361,16 +8361,16 @@
       <c r="E13" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="110" t="s">
+      <c r="F13" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="100"/>
-      <c r="M13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="101"/>
+      <c r="J13" s="101"/>
+      <c r="K13" s="101"/>
+      <c r="L13" s="101"/>
+      <c r="M13" s="102"/>
     </row>
     <row r="14" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18" t="s">
@@ -8382,16 +8382,16 @@
       <c r="E14" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="110" t="s">
+      <c r="F14" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="100"/>
-      <c r="K14" s="100"/>
-      <c r="L14" s="100"/>
-      <c r="M14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="102"/>
     </row>
     <row r="15" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18" t="s">
@@ -8436,16 +8436,16 @@
       <c r="E16" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="123" t="s">
+      <c r="F16" s="126" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="100"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="100"/>
-      <c r="L16" s="100"/>
-      <c r="M16" s="101"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="101"/>
+      <c r="I16" s="101"/>
+      <c r="J16" s="101"/>
+      <c r="K16" s="101"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="102"/>
       <c r="N16" s="56" t="s">
         <v>38</v>
       </c>
@@ -8460,16 +8460,16 @@
       <c r="E17" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="123" t="s">
+      <c r="F17" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="100"/>
-      <c r="M17" s="101"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="101"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="102"/>
       <c r="N17" s="56" t="s">
         <v>38</v>
       </c>
@@ -8497,8 +8497,8 @@
       <c r="J18" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="121"/>
-      <c r="L18" s="101"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="102"/>
       <c r="M18" s="54" t="s">
         <v>47</v>
       </c>
@@ -8520,8 +8520,8 @@
       <c r="G19" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="121"/>
-      <c r="I19" s="101"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="102"/>
       <c r="J19" s="55" t="s">
         <v>52</v>
       </c>
@@ -8543,16 +8543,16 @@
         <v>19</v>
       </c>
       <c r="E20" s="42"/>
-      <c r="F20" s="122" t="s">
+      <c r="F20" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="101"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="101"/>
+      <c r="J20" s="101"/>
+      <c r="K20" s="101"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="102"/>
       <c r="N20" t="s">
         <v>58</v>
       </c>
@@ -8565,16 +8565,16 @@
         <v>19</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="122" t="s">
+      <c r="F21" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="100"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="100"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="101"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="102"/>
       <c r="N21" t="s">
         <v>61</v>
       </c>
@@ -8587,16 +8587,16 @@
         <v>19</v>
       </c>
       <c r="E22" s="41"/>
-      <c r="F22" s="122" t="s">
+      <c r="F22" s="125" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="100"/>
-      <c r="H22" s="100"/>
-      <c r="I22" s="100"/>
-      <c r="J22" s="100"/>
-      <c r="K22" s="100"/>
-      <c r="L22" s="100"/>
-      <c r="M22" s="101"/>
+      <c r="G22" s="101"/>
+      <c r="H22" s="101"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="101"/>
+      <c r="K22" s="101"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="102"/>
       <c r="N22" t="s">
         <v>64</v>
       </c>
@@ -8609,16 +8609,16 @@
         <v>19</v>
       </c>
       <c r="E23" s="41"/>
-      <c r="F23" s="122" t="s">
+      <c r="F23" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="100"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="101"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="101"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="102"/>
       <c r="N23" t="s">
         <v>67</v>
       </c>
@@ -8633,16 +8633,16 @@
       <c r="E24" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="123" t="s">
+      <c r="F24" s="126" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="101"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="102"/>
       <c r="N24" s="58" t="s">
         <v>38</v>
       </c>
@@ -8657,16 +8657,16 @@
       <c r="E25" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="121"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="100"/>
-      <c r="I25" s="100"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="123" t="s">
+      <c r="F25" s="124"/>
+      <c r="G25" s="101"/>
+      <c r="H25" s="101"/>
+      <c r="I25" s="101"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="126" t="s">
         <v>71</v>
       </c>
-      <c r="L25" s="100"/>
-      <c r="M25" s="101"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="102"/>
       <c r="N25" s="56" t="s">
         <v>38</v>
       </c>
@@ -8679,16 +8679,16 @@
         <v>3</v>
       </c>
       <c r="E26" s="41"/>
-      <c r="F26" s="122" t="s">
+      <c r="F26" s="125" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="100"/>
-      <c r="H26" s="100"/>
-      <c r="I26" s="100"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="100"/>
-      <c r="L26" s="100"/>
-      <c r="M26" s="101"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="101"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="101"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="102"/>
       <c r="N26" t="s">
         <v>74</v>
       </c>
@@ -8701,16 +8701,16 @@
         <v>19</v>
       </c>
       <c r="E27" s="41"/>
-      <c r="F27" s="122" t="s">
+      <c r="F27" s="125" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="101"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="102"/>
       <c r="N27" t="s">
         <v>77</v>
       </c>
@@ -8723,16 +8723,16 @@
         <v>19</v>
       </c>
       <c r="E28" s="41"/>
-      <c r="F28" s="122" t="s">
+      <c r="F28" s="125" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="100"/>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="100"/>
-      <c r="M28" s="101"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="101"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="101"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="102"/>
       <c r="N28" t="s">
         <v>80</v>
       </c>
@@ -8745,16 +8745,16 @@
         <v>19</v>
       </c>
       <c r="E29" s="41"/>
-      <c r="F29" s="122" t="s">
+      <c r="F29" s="125" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="100"/>
-      <c r="H29" s="100"/>
-      <c r="I29" s="100"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="100"/>
-      <c r="M29" s="101"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="101"/>
+      <c r="I29" s="101"/>
+      <c r="J29" s="101"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="102"/>
       <c r="N29" t="s">
         <v>83</v>
       </c>
@@ -8769,14 +8769,14 @@
       <c r="E30" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="121"/>
-      <c r="G30" s="100"/>
-      <c r="H30" s="100"/>
-      <c r="I30" s="100"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="101"/>
+      <c r="F30" s="124"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="101"/>
+      <c r="I30" s="101"/>
+      <c r="J30" s="101"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="102"/>
     </row>
     <row r="31" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C31" s="59" t="s">
@@ -8788,14 +8788,14 @@
       <c r="E31" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="121"/>
-      <c r="G31" s="100"/>
-      <c r="H31" s="100"/>
-      <c r="I31" s="100"/>
-      <c r="J31" s="100"/>
-      <c r="K31" s="100"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="101"/>
+      <c r="F31" s="124"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="101"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="101"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="102"/>
     </row>
     <row r="32" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C32" s="59" t="s">
@@ -8807,16 +8807,16 @@
       <c r="E32" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="123" t="s">
+      <c r="F32" s="126" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="100"/>
-      <c r="H32" s="100"/>
-      <c r="I32" s="100"/>
-      <c r="J32" s="100"/>
-      <c r="K32" s="100"/>
-      <c r="L32" s="100"/>
-      <c r="M32" s="101"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="102"/>
       <c r="N32" s="56" t="s">
         <v>38</v>
       </c>
@@ -8831,16 +8831,16 @@
       <c r="E33" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="123" t="s">
+      <c r="F33" s="126" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="101"/>
-      <c r="H33" s="121"/>
-      <c r="I33" s="100"/>
-      <c r="J33" s="100"/>
-      <c r="K33" s="100"/>
-      <c r="L33" s="100"/>
-      <c r="M33" s="101"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="124"/>
+      <c r="I33" s="101"/>
+      <c r="J33" s="101"/>
+      <c r="K33" s="101"/>
+      <c r="L33" s="101"/>
+      <c r="M33" s="102"/>
       <c r="N33" s="56" t="s">
         <v>38</v>
       </c>
@@ -8855,16 +8855,16 @@
       <c r="E34" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="121"/>
-      <c r="G34" s="100"/>
-      <c r="H34" s="100"/>
-      <c r="I34" s="100"/>
-      <c r="J34" s="101"/>
-      <c r="K34" s="123" t="s">
+      <c r="F34" s="124"/>
+      <c r="G34" s="101"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="101"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="126" t="s">
         <v>91</v>
       </c>
-      <c r="L34" s="100"/>
-      <c r="M34" s="101"/>
+      <c r="L34" s="101"/>
+      <c r="M34" s="102"/>
       <c r="N34" s="56" t="s">
         <v>38</v>
       </c>
@@ -8879,16 +8879,16 @@
       <c r="E35" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="121"/>
-      <c r="G35" s="100"/>
-      <c r="H35" s="100"/>
-      <c r="I35" s="101"/>
-      <c r="J35" s="123" t="s">
+      <c r="F35" s="124"/>
+      <c r="G35" s="101"/>
+      <c r="H35" s="101"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="K35" s="100"/>
-      <c r="L35" s="100"/>
-      <c r="M35" s="101"/>
+      <c r="K35" s="101"/>
+      <c r="L35" s="101"/>
+      <c r="M35" s="102"/>
       <c r="N35" s="56" t="s">
         <v>38</v>
       </c>
@@ -8903,16 +8903,16 @@
       <c r="E36" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="121"/>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="101"/>
-      <c r="J36" s="123" t="s">
+      <c r="F36" s="124"/>
+      <c r="G36" s="101"/>
+      <c r="H36" s="101"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="126" t="s">
         <v>95</v>
       </c>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="101"/>
+      <c r="K36" s="101"/>
+      <c r="L36" s="101"/>
+      <c r="M36" s="102"/>
       <c r="N36" s="56" t="s">
         <v>38</v>
       </c>
@@ -8927,16 +8927,16 @@
       <c r="E37" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="123" t="s">
+      <c r="F37" s="126" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="100"/>
-      <c r="H37" s="100"/>
-      <c r="I37" s="100"/>
-      <c r="J37" s="100"/>
-      <c r="K37" s="100"/>
-      <c r="L37" s="100"/>
-      <c r="M37" s="101"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="101"/>
+      <c r="K37" s="101"/>
+      <c r="L37" s="101"/>
+      <c r="M37" s="102"/>
       <c r="N37" s="56" t="s">
         <v>38</v>
       </c>
@@ -8951,14 +8951,14 @@
       <c r="E38" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="121"/>
-      <c r="G38" s="100"/>
-      <c r="H38" s="100"/>
-      <c r="I38" s="100"/>
-      <c r="J38" s="100"/>
-      <c r="K38" s="100"/>
-      <c r="L38" s="100"/>
-      <c r="M38" s="101"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="101"/>
+      <c r="H38" s="101"/>
+      <c r="I38" s="101"/>
+      <c r="J38" s="101"/>
+      <c r="K38" s="101"/>
+      <c r="L38" s="101"/>
+      <c r="M38" s="102"/>
       <c r="N38" t="s">
         <v>99</v>
       </c>
@@ -8973,14 +8973,14 @@
       <c r="E39" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="121"/>
-      <c r="G39" s="100"/>
-      <c r="H39" s="100"/>
-      <c r="I39" s="100"/>
-      <c r="J39" s="100"/>
-      <c r="K39" s="100"/>
-      <c r="L39" s="100"/>
-      <c r="M39" s="101"/>
+      <c r="F39" s="124"/>
+      <c r="G39" s="101"/>
+      <c r="H39" s="101"/>
+      <c r="I39" s="101"/>
+      <c r="J39" s="101"/>
+      <c r="K39" s="101"/>
+      <c r="L39" s="101"/>
+      <c r="M39" s="102"/>
     </row>
     <row r="40" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C40" s="59" t="s">
@@ -8992,14 +8992,14 @@
       <c r="E40" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F40" s="121"/>
-      <c r="G40" s="100"/>
-      <c r="H40" s="100"/>
-      <c r="I40" s="100"/>
-      <c r="J40" s="100"/>
-      <c r="K40" s="100"/>
-      <c r="L40" s="100"/>
-      <c r="M40" s="101"/>
+      <c r="F40" s="124"/>
+      <c r="G40" s="101"/>
+      <c r="H40" s="101"/>
+      <c r="I40" s="101"/>
+      <c r="J40" s="101"/>
+      <c r="K40" s="101"/>
+      <c r="L40" s="101"/>
+      <c r="M40" s="102"/>
     </row>
     <row r="41" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C41" s="59" t="s">
@@ -9011,14 +9011,14 @@
       <c r="E41" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F41" s="121"/>
-      <c r="G41" s="100"/>
-      <c r="H41" s="100"/>
-      <c r="I41" s="100"/>
-      <c r="J41" s="100"/>
-      <c r="K41" s="100"/>
-      <c r="L41" s="100"/>
-      <c r="M41" s="101"/>
+      <c r="F41" s="124"/>
+      <c r="G41" s="101"/>
+      <c r="H41" s="101"/>
+      <c r="I41" s="101"/>
+      <c r="J41" s="101"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="102"/>
     </row>
     <row r="42" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C42" s="59" t="s">
@@ -9030,14 +9030,14 @@
       <c r="E42" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F42" s="121"/>
-      <c r="G42" s="100"/>
-      <c r="H42" s="100"/>
-      <c r="I42" s="100"/>
-      <c r="J42" s="100"/>
-      <c r="K42" s="100"/>
-      <c r="L42" s="100"/>
-      <c r="M42" s="101"/>
+      <c r="F42" s="124"/>
+      <c r="G42" s="101"/>
+      <c r="H42" s="101"/>
+      <c r="I42" s="101"/>
+      <c r="J42" s="101"/>
+      <c r="K42" s="101"/>
+      <c r="L42" s="101"/>
+      <c r="M42" s="102"/>
     </row>
     <row r="43" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C43" s="19" t="s">
@@ -9059,12 +9059,12 @@
       <c r="I43" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="110" t="s">
+      <c r="J43" s="108" t="s">
         <v>109</v>
       </c>
-      <c r="K43" s="100"/>
-      <c r="L43" s="100"/>
-      <c r="M43" s="101"/>
+      <c r="K43" s="101"/>
+      <c r="L43" s="101"/>
+      <c r="M43" s="102"/>
     </row>
     <row r="44" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18" t="s">
@@ -9074,18 +9074,18 @@
         <v>19</v>
       </c>
       <c r="E44" s="42"/>
-      <c r="F44" s="110" t="s">
+      <c r="F44" s="108" t="s">
         <v>111</v>
       </c>
-      <c r="G44" s="101"/>
-      <c r="H44" s="110" t="s">
+      <c r="G44" s="102"/>
+      <c r="H44" s="108" t="s">
         <v>112</v>
       </c>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="101"/>
+      <c r="I44" s="101"/>
+      <c r="J44" s="101"/>
+      <c r="K44" s="101"/>
+      <c r="L44" s="101"/>
+      <c r="M44" s="102"/>
     </row>
     <row r="45" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18" t="s">
@@ -9095,18 +9095,18 @@
         <v>19</v>
       </c>
       <c r="E45" s="42"/>
-      <c r="F45" s="125" t="s">
+      <c r="F45" s="127" t="s">
         <v>114</v>
       </c>
-      <c r="G45" s="126"/>
-      <c r="H45" s="126"/>
-      <c r="I45" s="127"/>
-      <c r="J45" s="110" t="s">
+      <c r="G45" s="128"/>
+      <c r="H45" s="128"/>
+      <c r="I45" s="129"/>
+      <c r="J45" s="108" t="s">
         <v>115</v>
       </c>
-      <c r="K45" s="100"/>
-      <c r="L45" s="100"/>
-      <c r="M45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="101"/>
+      <c r="M45" s="102"/>
     </row>
     <row r="46" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18" t="s">
@@ -9116,18 +9116,18 @@
         <v>19</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="110" t="s">
+      <c r="F46" s="108" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="100"/>
-      <c r="H46" s="100"/>
-      <c r="I46" s="101"/>
-      <c r="J46" s="124" t="s">
+      <c r="G46" s="101"/>
+      <c r="H46" s="101"/>
+      <c r="I46" s="102"/>
+      <c r="J46" s="130" t="s">
         <v>118</v>
       </c>
-      <c r="K46" s="119"/>
-      <c r="L46" s="119"/>
-      <c r="M46" s="120"/>
+      <c r="K46" s="122"/>
+      <c r="L46" s="122"/>
+      <c r="M46" s="123"/>
     </row>
     <row r="47" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18" t="s">
@@ -9137,16 +9137,16 @@
         <v>19</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="99" t="s">
+      <c r="F47" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="G47" s="100"/>
-      <c r="H47" s="100"/>
-      <c r="I47" s="100"/>
-      <c r="J47" s="100"/>
-      <c r="K47" s="100"/>
-      <c r="L47" s="100"/>
-      <c r="M47" s="101"/>
+      <c r="G47" s="101"/>
+      <c r="H47" s="101"/>
+      <c r="I47" s="101"/>
+      <c r="J47" s="101"/>
+      <c r="K47" s="101"/>
+      <c r="L47" s="101"/>
+      <c r="M47" s="102"/>
     </row>
     <row r="48" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18" t="s">
@@ -9157,19 +9157,19 @@
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="109"/>
-      <c r="G48" s="101"/>
+      <c r="G48" s="102"/>
       <c r="H48" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I48" s="99" t="s">
+      <c r="I48" s="103" t="s">
         <v>123</v>
       </c>
-      <c r="J48" s="100"/>
-      <c r="K48" s="101"/>
-      <c r="L48" s="99" t="s">
+      <c r="J48" s="101"/>
+      <c r="K48" s="102"/>
+      <c r="L48" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="M48" s="101"/>
+      <c r="M48" s="102"/>
     </row>
     <row r="49" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18" t="s">
@@ -9213,14 +9213,14 @@
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="109"/>
-      <c r="G50" s="100"/>
-      <c r="H50" s="100"/>
-      <c r="I50" s="101"/>
-      <c r="J50" s="99" t="s">
+      <c r="G50" s="101"/>
+      <c r="H50" s="101"/>
+      <c r="I50" s="102"/>
+      <c r="J50" s="103" t="s">
         <v>133</v>
       </c>
-      <c r="K50" s="100"/>
-      <c r="L50" s="101"/>
+      <c r="K50" s="101"/>
+      <c r="L50" s="102"/>
       <c r="M50" s="12" t="s">
         <v>134</v>
       </c>
@@ -9235,16 +9235,16 @@
       <c r="E51" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F51" s="121"/>
-      <c r="G51" s="100"/>
-      <c r="H51" s="100"/>
-      <c r="I51" s="100"/>
-      <c r="J51" s="100"/>
-      <c r="K51" s="101"/>
-      <c r="L51" s="114" t="s">
+      <c r="F51" s="124"/>
+      <c r="G51" s="101"/>
+      <c r="H51" s="101"/>
+      <c r="I51" s="101"/>
+      <c r="J51" s="101"/>
+      <c r="K51" s="102"/>
+      <c r="L51" s="112" t="s">
         <v>137</v>
       </c>
-      <c r="M51" s="101"/>
+      <c r="M51" s="102"/>
     </row>
     <row r="52" spans="3:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18" t="s">
@@ -9256,16 +9256,16 @@
       <c r="E52" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F52" s="114" t="s">
+      <c r="F52" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="100"/>
-      <c r="H52" s="100"/>
-      <c r="I52" s="100"/>
-      <c r="J52" s="100"/>
-      <c r="K52" s="100"/>
-      <c r="L52" s="100"/>
-      <c r="M52" s="101"/>
+      <c r="G52" s="101"/>
+      <c r="H52" s="101"/>
+      <c r="I52" s="101"/>
+      <c r="J52" s="101"/>
+      <c r="K52" s="101"/>
+      <c r="L52" s="101"/>
+      <c r="M52" s="102"/>
       <c r="N52" t="s">
         <v>141</v>
       </c>
@@ -9280,16 +9280,16 @@
       <c r="E53" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F53" s="114" t="s">
+      <c r="F53" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="100"/>
-      <c r="H53" s="100"/>
-      <c r="I53" s="100"/>
-      <c r="J53" s="100"/>
-      <c r="K53" s="100"/>
-      <c r="L53" s="100"/>
-      <c r="M53" s="101"/>
+      <c r="G53" s="101"/>
+      <c r="H53" s="101"/>
+      <c r="I53" s="101"/>
+      <c r="J53" s="101"/>
+      <c r="K53" s="101"/>
+      <c r="L53" s="101"/>
+      <c r="M53" s="102"/>
       <c r="N53" t="s">
         <v>141</v>
       </c>
@@ -9304,16 +9304,16 @@
       <c r="E54" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F54" s="114" t="s">
+      <c r="F54" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="100"/>
-      <c r="H54" s="100"/>
-      <c r="I54" s="100"/>
-      <c r="J54" s="100"/>
-      <c r="K54" s="100"/>
-      <c r="L54" s="100"/>
-      <c r="M54" s="101"/>
+      <c r="G54" s="101"/>
+      <c r="H54" s="101"/>
+      <c r="I54" s="101"/>
+      <c r="J54" s="101"/>
+      <c r="K54" s="101"/>
+      <c r="L54" s="101"/>
+      <c r="M54" s="102"/>
       <c r="N54" t="s">
         <v>141</v>
       </c>
@@ -9328,16 +9328,16 @@
       <c r="E55" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="114" t="s">
+      <c r="F55" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G55" s="100"/>
-      <c r="H55" s="100"/>
-      <c r="I55" s="100"/>
-      <c r="J55" s="100"/>
-      <c r="K55" s="100"/>
-      <c r="L55" s="100"/>
-      <c r="M55" s="101"/>
+      <c r="G55" s="101"/>
+      <c r="H55" s="101"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="101"/>
+      <c r="K55" s="101"/>
+      <c r="L55" s="101"/>
+      <c r="M55" s="102"/>
       <c r="N55" t="s">
         <v>141</v>
       </c>
@@ -9352,16 +9352,16 @@
       <c r="E56" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="114" t="s">
+      <c r="F56" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="100"/>
-      <c r="H56" s="100"/>
-      <c r="I56" s="100"/>
-      <c r="J56" s="100"/>
-      <c r="K56" s="100"/>
-      <c r="L56" s="100"/>
-      <c r="M56" s="101"/>
+      <c r="G56" s="101"/>
+      <c r="H56" s="101"/>
+      <c r="I56" s="101"/>
+      <c r="J56" s="101"/>
+      <c r="K56" s="101"/>
+      <c r="L56" s="101"/>
+      <c r="M56" s="102"/>
       <c r="N56" t="s">
         <v>141</v>
       </c>
@@ -9376,16 +9376,16 @@
       <c r="E57" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F57" s="114" t="s">
+      <c r="F57" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G57" s="100"/>
-      <c r="H57" s="100"/>
-      <c r="I57" s="100"/>
-      <c r="J57" s="100"/>
-      <c r="K57" s="100"/>
-      <c r="L57" s="100"/>
-      <c r="M57" s="101"/>
+      <c r="G57" s="101"/>
+      <c r="H57" s="101"/>
+      <c r="I57" s="101"/>
+      <c r="J57" s="101"/>
+      <c r="K57" s="101"/>
+      <c r="L57" s="101"/>
+      <c r="M57" s="102"/>
       <c r="N57" t="s">
         <v>141</v>
       </c>
@@ -9400,16 +9400,16 @@
       <c r="E58" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F58" s="114" t="s">
+      <c r="F58" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="100"/>
-      <c r="H58" s="100"/>
-      <c r="I58" s="100"/>
-      <c r="J58" s="100"/>
-      <c r="K58" s="100"/>
-      <c r="L58" s="100"/>
-      <c r="M58" s="101"/>
+      <c r="G58" s="101"/>
+      <c r="H58" s="101"/>
+      <c r="I58" s="101"/>
+      <c r="J58" s="101"/>
+      <c r="K58" s="101"/>
+      <c r="L58" s="101"/>
+      <c r="M58" s="102"/>
       <c r="N58" t="s">
         <v>141</v>
       </c>
@@ -9424,16 +9424,16 @@
       <c r="E59" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="F59" s="114" t="s">
+      <c r="F59" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G59" s="100"/>
-      <c r="H59" s="100"/>
-      <c r="I59" s="100"/>
-      <c r="J59" s="100"/>
-      <c r="K59" s="100"/>
-      <c r="L59" s="100"/>
-      <c r="M59" s="101"/>
+      <c r="G59" s="101"/>
+      <c r="H59" s="101"/>
+      <c r="I59" s="101"/>
+      <c r="J59" s="101"/>
+      <c r="K59" s="101"/>
+      <c r="L59" s="101"/>
+      <c r="M59" s="102"/>
       <c r="N59" t="s">
         <v>141</v>
       </c>
@@ -9448,16 +9448,16 @@
       <c r="E60" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F60" s="114" t="s">
+      <c r="F60" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G60" s="100"/>
-      <c r="H60" s="100"/>
-      <c r="I60" s="100"/>
-      <c r="J60" s="100"/>
-      <c r="K60" s="100"/>
-      <c r="L60" s="100"/>
-      <c r="M60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="101"/>
+      <c r="L60" s="101"/>
+      <c r="M60" s="102"/>
       <c r="N60" t="s">
         <v>141</v>
       </c>
@@ -9472,16 +9472,16 @@
       <c r="E61" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="F61" s="114" t="s">
+      <c r="F61" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="G61" s="100"/>
-      <c r="H61" s="100"/>
-      <c r="I61" s="100"/>
-      <c r="J61" s="100"/>
-      <c r="K61" s="100"/>
-      <c r="L61" s="100"/>
-      <c r="M61" s="101"/>
+      <c r="G61" s="101"/>
+      <c r="H61" s="101"/>
+      <c r="I61" s="101"/>
+      <c r="J61" s="101"/>
+      <c r="K61" s="101"/>
+      <c r="L61" s="101"/>
+      <c r="M61" s="102"/>
       <c r="N61" t="s">
         <v>141</v>
       </c>
@@ -9510,13 +9510,59 @@
         <v>165</v>
       </c>
       <c r="K63" s="109"/>
-      <c r="L63" s="101"/>
+      <c r="L63" s="102"/>
       <c r="M63" s="53" t="s">
         <v>166</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="F51:K51"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="F39:M39"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="F11:M11"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="F40:M40"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F17:M17"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="F47:M47"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="F56:M56"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F61:M61"/>
+    <mergeCell ref="H44:M44"/>
     <mergeCell ref="F60:M60"/>
     <mergeCell ref="F14:M14"/>
     <mergeCell ref="K18:L18"/>
@@ -9533,52 +9579,6 @@
     <mergeCell ref="F26:M26"/>
     <mergeCell ref="H33:M33"/>
     <mergeCell ref="F23:M23"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="F42:M42"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="F47:M47"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="F56:M56"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F61:M61"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="F22:M22"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="F31:M31"/>
-    <mergeCell ref="F27:M27"/>
-    <mergeCell ref="F11:M11"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="F16:M16"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="F40:M40"/>
-    <mergeCell ref="F12:M12"/>
-    <mergeCell ref="F30:M30"/>
-    <mergeCell ref="F17:M17"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="F51:K51"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="F39:M39"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="F38:M38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9690,16 +9690,16 @@
       <c r="E6" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="F6" s="99" t="s">
+      <c r="F6" s="103" t="s">
         <v>530</v>
       </c>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="100"/>
-      <c r="L6" s="100"/>
-      <c r="M6" s="101"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="101"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="101"/>
+      <c r="M6" s="102"/>
     </row>
     <row r="7" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
@@ -9711,16 +9711,16 @@
       <c r="E7" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="F7" s="99" t="s">
+      <c r="F7" s="103" t="s">
         <v>533</v>
       </c>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="101"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="101"/>
+      <c r="L7" s="101"/>
+      <c r="M7" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9852,29 +9852,29 @@
       </c>
     </row>
     <row r="9" spans="2:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="E9" s="128" t="s">
+      <c r="E9" s="131" t="s">
         <v>424</v>
       </c>
-      <c r="F9" s="129"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="130"/>
-      <c r="K9" s="128" t="s">
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="131" t="s">
         <v>423</v>
       </c>
-      <c r="L9" s="129"/>
-      <c r="M9" s="129"/>
-      <c r="N9" s="129"/>
-      <c r="O9" s="129"/>
-      <c r="P9" s="129"/>
-      <c r="Q9" s="129"/>
-      <c r="R9" s="129"/>
-      <c r="S9" s="129"/>
-      <c r="T9" s="129"/>
-      <c r="U9" s="129"/>
-      <c r="V9" s="129"/>
-      <c r="W9" s="130"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="132"/>
+      <c r="N9" s="132"/>
+      <c r="O9" s="132"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="132"/>
+      <c r="R9" s="132"/>
+      <c r="S9" s="132"/>
+      <c r="T9" s="132"/>
+      <c r="U9" s="132"/>
+      <c r="V9" s="132"/>
+      <c r="W9" s="133"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.15">
       <c r="E11" t="s">
